--- a/inst/app/app_binary_data_extraction/user_logs.xlsx
+++ b/inst/app/app_binary_data_extraction/user_logs.xlsx
@@ -1,65 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkStation\Products\AIMetaAnalysis\inst\app\app_binary_data_extraction\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F33BBA-9DA1-48B4-9596-A7971312DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="my_inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="my_inputs" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">trial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pub_year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">section_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">free_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image_base64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEYNOTE-671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table_one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">survival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EventFreeSurvival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subgroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+  <si>
+    <t>trial</t>
+  </si>
+  <si>
+    <t>pub_year</t>
+  </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>outcome_name</t>
+  </si>
+  <si>
+    <t>section_name</t>
+  </si>
+  <si>
+    <t>free_text</t>
+  </si>
+  <si>
+    <t>KEYNOTE-671</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>table_one</t>
+  </si>
+  <si>
+    <t>survival</t>
+  </si>
+  <si>
+    <t>EventFreeSurvival</t>
+  </si>
+  <si>
+    <t>subgroup</t>
+  </si>
+  <si>
+    <t>NADIM-II</t>
+  </si>
+  <si>
+    <t>Here is the table formatted with the original English terms, without translation:
 ---
 ### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
 | Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
@@ -121,131 +123,7 @@
 † Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
   </si>
   <si>
-    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
----
-### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
-| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
-|----------------|------------------------------|-------------------------|
-| **Age** | | |
-| Median (range) — yr | 63 (26–83) | 64 (35–81) |
-| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
-| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
-| **Race or ethnic group — no. (%)*** | | |
-| American Indian or Alaska Native | 1 (0.3) | 0 |
-| Asian | 124 (31.2) | 125 (31.2) |
-| Black | 6 (1.5) | 10 (2.5) |
-| Multiple | 3 (0.8) | 10 (2.5) |
-| White | 250 (63.0) | 239 (59.8) |
-| Missing data | 13 (3.3) | 16 (4.0) |
-| **Geographic region — no. (%)** | | |
-| East Asia | 123 (31.0) | 121 (30.2) |
-| Other | 274 (69.0) | 279 (69.8) |
-| **ECOG performance-status score — no. (%)†** | | |
-| 0 | 253 (63.7) | 246 (61.5) |
-| 1 | 144 (36.3) | 154 (38.5) |
-| **Smoking status — no. (%)** | | |
-| Current smoker | 96 (24.2) | 103 (25.8) |
-| Former smoker | 247 (62.2) | 250 (62.5) |
-| Never smoked | 54 (13.6) | 47 (11.8) |
-| **Pathological stage at baseline — no. (%)** | | |
-| II | 118 (29.7) | 121 (30.2) |
-| III | 279 (70.3) | 279 (69.8) |
-| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
-| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
-| **Tumor stage — no. (%)** | | |
-| T1 | 55 (13.9) | 61 (15.2) |
-| T2 | 106 (26.7) | 126 (31.5) |
-| T3 | 121 (30.5) | 109 (27.2) |
-| T4 | 115 (29.0) | 104 (26.0) |
-| **Node stage — no. (%)** | | |
-| N0 | 148 (37.3) | 142 (35.5) |
-| N1 | 81 (20.4) | 71 (17.8) |
-| N2 | 168 (42.3) | 187 (46.8) |
-| **Histologic features — no. (%)** | | |
-| Nonsquamous | 226 (56.9) | 227 (56.8) |
-| Squamous | 171 (43.1) | 173 (43.2) |
-| **PD-L1 tumor proportion score — no. (%)** | | |
-| ≥50% | 132 (33.2) | 134 (33.5) |
-| &lt;50% | 265 (66.8) | 266 (66.5) |
-| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
-| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
-| **EGFR mutation status — no. (%)** | | |
-| No | 111 (28.0) | 127 (31.8) |
-| Yes | 14 (3.5) | 19 (4.8) |
-| Unknown | 272 (68.5) | 254 (63.5) |
-| **ALK translocation status — no. (%)** | | |
-| No | 104 (26.2) | 133 (33.2) |
-| Yes | 12 (3.0) | 9 (2.2) |
-| Unknown | 281 (70.8) | 258 (64.5) |
----
-*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
-* Race and ethnic group were reported by the participant.  
-† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
----
-### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
-| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
-|----------------|------------------------------|-------------------------|
-| **Age** | | |
-| Median (range) — yr | 63 (26–83) | 64 (35–81) |
-| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
-| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
-| **Race or ethnic group — no. (%)*** | | |
-| American Indian or Alaska Native | 1 (0.3) | 0 |
-| Asian | 124 (31.2) | 125 (31.2) |
-| Black | 6 (1.5) | 10 (2.5) |
-| Multiple | 3 (0.8) | 10 (2.5) |
-| White | 250 (63.0) | 239 (59.8) |
-| Missing data | 13 (3.3) | 16 (4.0) |
-| **Geographic region — no. (%)** | | |
-| East Asia | 123 (31.0) | 121 (30.2) |
-| Other | 274 (69.0) | 279 (69.8) |
-| **ECOG performance-status score — no. (%)†** | | |
-| 0 | 253 (63.7) | 246 (61.5) |
-| 1 | 144 (36.3) | 154 (38.5) |
-| **Smoking status — no. (%)** | | |
-| Current smoker | 96 (24.2) | 103 (25.8) |
-| Former smoker | 247 (62.2) | 250 (62.5) |
-| Never smoked | 54 (13.6) | 47 (11.8) |
-| **Pathological stage at baseline — no. (%)** | | |
-| II | 118 (29.7) | 121 (30.2) |
-| III | 279 (70.3) | 279 (69.8) |
-| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
-| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
-| **Tumor stage — no. (%)** | | |
-| T1 | 55 (13.9) | 61 (15.2) |
-| T2 | 106 (26.7) | 126 (31.5) |
-| T3 | 121 (30.5) | 109 (27.2) |
-| T4 | 115 (29.0) | 104 (26.0) |
-| **Node stage — no. (%)** | | |
-| N0 | 148 (37.3) | 142 (35.5) |
-| N1 | 81 (20.4) | 71 (17.8) |
-| N2 | 168 (42.3) | 187 (46.8) |
-| **Histologic features — no. (%)** | | |
-| Nonsquamous | 226 (56.9) | 227 (56.8) |
-| Squamous | 171 (43.1) | 173 (43.2) |
-| **PD-L1 tumor proportion score — no. (%)** | | |
-| ≥50% | 132 (33.2) | 134 (33.5) |
-| &lt;50% | 265 (66.8) | 266 (66.5) |
-| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
-| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
-| **EGFR mutation status — no. (%)** | | |
-| No | 111 (28.0) | 127 (31.8) |
-| Yes | 14 (3.5) | 19 (4.8) |
-| Unknown | 272 (68.5) | 254 (63.5) |
-| **ALK translocation status — no. (%)** | | |
-| No | 104 (26.2) | 133 (33.2) |
-| Yes | 12 (3.0) | 9 (2.2) |
-| Unknown | 281 (70.8) | 258 (64.5) |
----
-*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
-* Race and ethnic group were reported by the participant.  
-† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+    <t>好的，已将您提供的文本数据整理为以下表格。
 | Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
 | :--- | :--- | :--- | :--- |
 | **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
@@ -290,18 +168,68 @@
 | No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
 | Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
   </si>
+  <si>
+    <t>Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>image_base64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -329,9 +257,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -613,11 +550,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.4609375" customWidth="1"/>
+    <col min="4" max="4" width="15.61328125" customWidth="1"/>
+    <col min="6" max="6" width="16.3046875" customWidth="1"/>
+    <col min="7" max="7" width="17.921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -637,53 +580,92 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
+      <c r="B2">
+        <v>2023</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2023</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>2023</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
         <v>2023</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3"/>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/inst/app/app_binary_data_extraction/user_logs.xlsx
+++ b/inst/app/app_binary_data_extraction/user_logs.xlsx
@@ -1,26 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkStation\Products\AIMetaAnalysis\inst\app\app_binary_data_extraction\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F33BBA-9DA1-48B4-9596-A7971312DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="my_inputs" sheetId="1" r:id="rId1"/>
+    <sheet name="my_inputs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>trial</t>
   </si>
@@ -212,24 +205,3761 @@
     <t>image_base64</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pub_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">section_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">free_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_base64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEYNOTE-671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">survival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EventFreeSurvival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subgroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIM-II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAA6oAAAN0CAYAAAC9SNVBAAAAAXNSR0IArs4c6QAAAARnQU1BAACxjwv8YQUAAAAJcEhZcwAADsMAAA7DAcdvqGQAAP+lSURBVHhe7L1ndFzXlab9VEIoFAqhkHMkSBAgwATmHERRJEUq20qWZKvdarnDeLpn1vzyr1kz35rptqfbPe5uOSgHZjFnEAwAQeSccw6FWDl9P6buXYgkFWir1edZ6y6JqHPTqbrnnn323u9WeDweD98hHA4H4+PjTExM4Ha70ev1hISE4OvrO7fpA3G73VgsFoxGI9PT0yiVSkJDQwkLC0OhUMxtLhAIBAKBQCAQCASC7wiK75qhKhAIBAKBQCAQCASC/9go5/5BIBAIBAKBQCAQCASCPyXCUBUIBAKBQCAQCAQCwXcKYagKBAKBQCAQCAQCgeA7hTBUBQKBQCAQCAQCgUDwnUIYqgKBQCAQCAQCgUAg+E4hDFWBQCAQCAQCgUAgEHynEIaqQCAQCAQCgUAgEAi+UwhDVSAQCAQCgUAgEAgE3ymEoSoQCAQCgUAgEAgEgu8UwlAVCAQCgUAgEAgEAsF3CmGoCgQCgUAgEAgEAoHgO4UwVAUCgUAgEAgEAoFA8J1CGKoCgUAgEAgEAoFAIPhOIQxVgUAgEAgEAoFAIBB8pxCGqkAgEAgEAoFAIBAIvlMIQ1UgEAgEAoFAIBAIBN8phKEqEAgEAoFAIBAIBILvFMJQFQgEAoFAIBAIBALBdwqFx+PxzP2jQCAQCASPC4/HI28KhQKlUqyZCgQCgUAgmI0wVAUCgeAxIhlkAAqFAoVCMbcJfIV23wesVitjY2PY7Xb0ej0hISFzm8xjpnE7E6VS+UfvK8nA/mPgdrtxOp0AaDQa+bwL9Yf0u1ns2ua2X4jF9vd4PLjd7lm/0Zl97/F4cLlcuFwu1Go1KpVqzhEEAoFAIPhqCENVIBAIHhMul4upqSnMZjM+Pj4EBQWh0WjmNgPA6XTKxptOp0On030vJ/sej4eWlhauXr1KX18fmzZt4oknnljQOJJwOByYTCa5Lx0OB0qlEn9/f0JCQggMDPyjGawOh0P+Pv39/ed+/K3idrsZGhqisrIShULBli1b8PPzw+l0MjU1JfeHy+VCpVIREBBAcHAwAQEB8/rD6XQyOTmJ2WzG7XbPOo+E1KfBwcGzfnsulwuz2czQ0BBjY2O43W70ej1hYWEEBQWhUqkwm820tLTQ3t5OdnY2ycnJ38vfr0AgEAj+eAhDVSAQCB4T4+PjFBQUUFxcTHJyMgcOHCAiImJBg2pkZITjx4/T1dXFxo0b2bRpE0FBQQu2/feM2+3mzp07/OM//iPV1dW8/vrr/Jf/8l8WvU+Xy8Xdu3e5e/cuPT09mEwmnE4nCoUCPz8/DAYDS5YsYf369WRkZCx6nK+Cy+WCOd5aj8fD5OQkZWVlFBQUkJKSwpEjRwgICPhWzjkXt9uN0Wjk2rVrHDt2jM2bN/P2228DUFpaSn5+Pv39/bKhqlQqCQgIICoqiszMTFatWkViYiJKpRKPx4PRaOTixYtUVlYyPT09yzsqodVqyc3N5ciRI+j1ejweD9PT05SVlVFUVERLSwvj4+O43W50Oh2JiYls3LiRvLw8lEolN27c4NNPP2X16tW8+eabGAwGEdYtEAgEgq+N6he/+MUv5v5RIBAIBN8co9HImTNn+Pzzz3E4HKxfv57Q0NAFDZuBgQH+9V//latXrxIdHc3y5csJDAxcsO2/ZzweD21tbdy4cYPOzk5ycnLYtm3bovfpdDo5efIkH3/8MZWVldhsNhQKBdPT0/T29lJRUcG9e/fo7u4mIiKCqKior20cuVwuenp6uH//PkajEZ1Oh5+fH3gNx4GBAU6fPs1vf/tbxsfH2bp162NbTLBardTU1PD5558zODjI888/T0pKCmazmfPnz/PBBx9QW1uL0+mUPfednZ2Ul5dTXl6O0WgkNDRUXhgZHh7m008/5csvv6SpqYmhoSEGBwfp6+uTt9HRUUJCQlizZg1arZbJyUkuX77Me++9x/Xr1xkZGZGvrbe3l/7+fgIDA8nMzESv12OxWKisrKSoqIi0tDRiY2MXjSAQCAQCgeBhfL23uUAgEAgeitvtxmazMTU1hcViWTTkEm9bs9nM1NQUNpvtgW3/vaOYkUv5MKPS4/FgNpuZnJwkPDycgwcP8s477/DOO+/w53/+5zz33HP4+/tz+vRp/vVf/5WBgQHZI/pVsVqt3Lp1i9///vfk5+djNBrlzyQPbkJCAjk5OWRkZDy20F+3283Y2Bjl5eU0NzezadMmVq5ciUqlwuPxYLVaMZvNREdH8+yzz8r98fbbb7N3717sdjsnTpzg2LFj9Pf3y8e0WCw4nU6ys7N55ZVXePfdd+XtL/7iL/jJT37Czp078ff3x2q1UltbywcffEBlZSW5ubm89dZbvPvuu/zsZz/jL/7iL/jhD3/I6tWr0el0+Pj4kJqayrZt27BYLFy7do3h4eGv/V0IBAKBQPDgGYJAIBAIvhGSMfYoXjelUvnIbf8983XuT6FQEB4ezurVq9m+fTu7du3i4MGDvPrqq7zwwgv4+Phw/fp1ampqcDgcc3d/JFwuF+3t7dTU1DA4ODjrOAqFgtDQULZv387PfvYzXnjhBUJDQx9qaH8dHA4H3d3dVFVV4evry6ZNm9Dr9bPaKJVKoqKiWLt2LTt27GDXrl0cPnyYV199lX379skh03V1dfI+CoUCHx8fli1bxv79+3nuuedmbU8//TRr167Fz8+Pqakp7t+/T2VlJXFxcfzgBz/gueeeY8+ePezZs4cjR47wzDPPsHbtWnQ6HUqlksDAQFasWMGSJUsoLS2lpaUFm80267oFAoFAIHhUvv03rEAgEAjm8TDjTPp8bjvJo9jW1sbt27c5d+4cp0+f5tq1azQ1NWGxWORcQ7fbzfDwMOXl5dy6dYvbt2/L2507dygsLOTOnTvcv3+f4eFhOWx0aGiIiooKrl69ypkzZzh//jz37t1jcHBw1rUAcnhnVVUVY2NjsucvPz+ftrY2ud3MnM4LFy7w5ZdfcuPGDTo6OrDb7fPu80FIbZVKJb6+vmi1WrRaLYGBgcTHx7N582ZiY2MZGxujs7MTh8Mhex67urooKiri4sWLnDlzhqtXr1JTU8PExIR8fLfbTV9fH6WlpbS1tTExMUFPTw9lZWXcvXuX2tpaJiYm8HjVfn18fFCr1eC9TwmPx8PU1BRNTU3k5+dz9uxZzp8/T2FhId3d3bJ674OQrru1tZXW1lZSUlJYunTpPINYoVCgUqlkUaeAgACCgoJITU0lLy+P+Ph4hoaG6OrqAm/fSftpNBoCAgIIDAyUN71eT2BgoBzqbDab6e7uxmKxEBUVxZIlSzAYDAQEBBAQEIBeryc0NBS9Xi+LJqnVaqKiolixYgVjY2PU1tZiMpnm5cIKBAKBQPAoiBxVgUAgeExMTk7KXqmEhAR27969aI7qxMQEFy9epK+vj9WrV7Nq1Sr0ej0mk4mqqipOnTrF9evXKSwspLi4mLKyMtrb21GpVISGhuLn54fL5aKmpobTp09z5coVSkpKKCkpobS0lLKyMu7fv09RURG1tbXExcURGRlJd3c3V69e5eLFi9y6dYvi4mJKSkqora2V8xwNBoN8nUNDQ3zwwQeyp66+vp5jx45RXFyMXq8nMzMTh8NBV1cXFy9e5MSJE1y7do2ioiLq6uoYHh5mYGCAuro6xsfHWb16NVu3bl2wT5ghplRRUUFYWBibNm0iKSlJ/tzj8TA2NsbFixcZHBzkqaeeIisrC5VKRUVFBRcvXuTKlSuygV5WVkZbWxt2u52wsDB0Oh0Oh4N79+7xxRdfcP/+fQYHB7FYLAwMDFBfX8/ExAQRERH4+PhQVFTE8ePHmZiYYMWKFfj6+qJQKOT81oKCAs6dO8eVK1e4ffu23Jf9/f3yd+Xj4zPrHmciCR8VFBRQVlbG5s2b2b17t2wYW61WSktLKS8vJzIyks2bNxMTE4NiRlmZ4eFhSktLGRoaYs2aNaxdu5aJiQlu3rxJV1cXWVlZrFq1atGyQB6PB5PJRGVlJSUlJej1elatWkVERMSsEjkzzymhVCoZHx+nqKgIlUrFqlWrCA4OnmdoCwQCgUDwMMSbQyAQCB4j0kTebDbT399PV1cXnZ2ds7auri76+vpmeUclbDYb3d3dNDc34+vrS2JiIqmpqQBcvHiR3//+91RVVWGxWMBr2NlsNiwWCxaLBavVisViYXx8nLt373L58mUaGhrksNaBgQFaWlqYnp4mPDyc5ORkDAYD7e3tfPDBBxw7doypqSn5uiwWCyUlJdy4cYPTp09z8uRJ6urqcLvdKJVKXC4Xg4ODHD16lN/85jdUVlai1WqJj48nICCAmpoa8vPz6erqWtDQeRBz2zqdTtkbPDQ0RGxsLKmpqWg0GlwuFx0dHbS3twMQGxtLQkICKpWK4uJiPvzwQwoKCmQvp0KhwDOjNql0vzPPabFYaG5u5vLly5SWlmK32/F464v29/dz9uxZPvjgA4qKinC73cTGxmIwGBgeHubMmTP8/ve/p6io6IGhyW63m/HxcQYHB1EqlcTGxuLr6zu3GSxQQ1byxo6MjDA6Ooqvry/BwcHyZ9J/pRI709PTszaz2SwrKgcGBpKVlUVMTAxtbW2cOnVKVl5erMSNwpvHGxsbi16vp6OjQ1YJFggEAoHgqyI8qgKBQPCYmJycpKSkhIqKCux2Ow6Hg5aWFjl0Vtqqq6spLy+npKQEq9VKXl4eK1euRK/X43a7cTqdBAcHs23bNjZt2sSaNWuIi4ujqamJiooKIiMjSU9Pl8Mwg4ODSU9PZ8WKFaxYsYKlS5cCcO/ePZRKJQcPHmTnzp0YDAZsNht+fn5kZ2ezZcsW1q1bR2ZmJgC3bt2iv7+fdevWERERgVKpZGRkhJMnT9La2srU1BShoaFs2rSJbdu2kZWVhY+PDwUFBfzmN79hcHCQgwcP8uyzz7Jjxw6WL1+ORqOR621qNBrWrFnDli1b5hmhEjM9qlqtlrS0NPz8/BgaGqKzs5O7d+9y4cIFJiYmeOqpp3jqqafQ6/UoFArMZjMGg4G8vDw2b97M6tWrSUhIwGg0ysbk+vXrZXXfkJAQRkZG6O/vZ8WKFTz99NNs3ryZzMxMYmNjsdls3L9/nxs3bhATE8PTTz+NVquVxYM+++wzhoaGWLduHYcPH2bXrl3k5OQQHBxMX18f5eXlmM1msrKyCA4OXvCeHQ4HbW1t3LlzB6vVyu7du1myZIn8+UyPalhYGHl5eYSFhWG32xkbG6O+vp4rV65QXl5Oeno6hw8fJjY2Vi6V1NzcjL+/P2q1Wl6kaG1tpb29ndHRUfz8/NDr9ajVarRaLSaTie7ublpbW+nv72d0dBSLxYJCocDX13eed1ihUGAymbh79y5DQ0NyWLZQ/xUIBALBV0UYqgKBQPCYkHI0y8rKMJlMmM1m+vr66OjomOdRbW9vp7u7G4VCwdq1a2VDVa1WExwcTFJSEklJSQQFBeHr64ter6evr4+ysjL0ej25ublERkbKtTSTk5NJTU0lPj4egNu3b1NXV8euXbt44403SE9Px8fHB61WS2xsLMnJyfL+Wq0Wj8dDSUkJbW1t5Obmsnz5ctRqNUajkfPnz9PS0kJ8fDzPPPMMTz/9NEuXLsVgMDAwMMAf/vAHbt26xaZNm/jZz35Gbm4ucXFxREVFERMTw/j4OM3NzTgcjkc2VMvKypicnMRqtdLW1kZJSQl3796loKCAwcFB9u7dyw9+8AOSkpJQq9UoFAqCgoJITEwkMTERg8GAv78/Wq2WiYkJ7t69i8ViYd26dSQkJBAQEEBISAgNDQ00NzeTm5vLgQMHyMnJITIyEn9/f6ampuTyK8nJyRw6dAh/f38GBgb47W9/S0VFBWvWrOGll15i48aNxMfHEx0dTVRUFAqFgtLSUjo7O0lMTCQzM1PO7ZyJw+GgublZDp3dtWsXCQkJ8ueSoVpSUoJSqSQ0NBSTyURrayslJSVcvXqV0tJSgoOD2b9/P9u3b8ff3182VOvr65mammJwcJCGhgZ5saSuro6xsTGioqKIj49H6a3LGh4ejkajYWJigt7eXhoaGmhtbWV0dFT2vPr5+cnfn8JbOujevXv09fWRl5dHcnLyol5hgUAgEAgWQ4T+CgQCwWPE7Xaj8CrW5uXlsXXr1gW3devWYTAYUHhDUCVUKpUscNPW1kZRURGXLl2ioKCAoaEhnE4nIyMjTE5O4na70Wg0BAYGEhwcjE6nw2w2k5+fT0FBARkZGbzyyissX75cNhz8/PzQaDSMjo5SVVVFfn4+V69epaqqSi5p0t/fPy8k2eVysWTJEtatW0diYiLBwcGoVCoGBgYoKSlBpVKxd+9elixZQkBAgCyEFBcXR3Z2NtHR0bNCbB+FqakpWltbZS90VVUVLS0tqNVq8vLySE9Pl3M5FQqFbHB3d3dTXFzM9evXKSgooK2tDafTydjYGENDQ+AVAvLz85ONXJVKJQs3+fr6ykalYk64stPppLOzk6qqKvk6MjMzCQwMlMWOoqOjWb16NcuWLWNgYICioqJF1XCl8F2bzYavr6/83c/F6XTS3d3NhQsX+Pjjj/nkk084c+YMdXV1REZGcuTIEfbt2yeH/koovGJQOp0OvV4/a9NqtXL/Afj6+rJ8+XJefPFF3nrrLZ588kliY2Pp6uri1KlTfPjhh9y5c4fJyclZ51Aqlfj5+eHxeLBYLKJEjUAgEAi+FsJQFQgEgseIZIglJiZy5MgRXnnlFV577bVZ26uvvsqzzz5LQkLCPEPVZrPR0dHBuXPn+Jd/+Rc+/PBDLly4IIdxSkaNpHQr4Xa7GR0dJT8/ny+++AKAV199lQ0bNhAQECCfZ2xsjHv37vHRRx/xb//2bxw/fpyrV69y//59WenWZrPNO7ZGoyEmJkY2rqVrHR4eZmhoiMDAQHJycuaFfEplTCQj8lENVYVCQWxsLLt27eIHP/gBL774Ik8++SRLliyRPdfS9eI15Hp6erh69Sq/+93veP/99zlz5gw3btygtrYWh8Mh5/NKSNfzVa5LMhgnJiYICQkhJSVlnnGoVqsxGAykpqbKOceL5Xni7V9pgWOmUTwThUKBWq3G19cXtVpNYGAgGRkZHDp0iB//+MccOXKElJSUeV5bPz8/Vq5cyYsvvsiPf/xjfvKTn/CTn/yEN954g0OHDpGcnDyrva+vLykpKezevZtXX32Vt99+m6eeegqtVkthYSHnzp2jsbFxljEqXbfHm7/7qH0pEAgEAsFMhKEqEAgEjxFpku7v709UVBQJCQlyOKq0JSQkEB0dPSuEEq/B0t3dzbFjx3jvvfcoLy/Hz8+P3Nxcdu/ezapVq9DpdDPO9v/weFVby8rKOHr0KCMjIxw+fJhDhw7Nyo00m83cvHmT9957j7NnzzI2NkZiYiIbN25k69atctjwXEPD4/Gg0WhmeRrxellNJhMOhwMfHx+CgoIWNLQW+tvDUCgUREVFsXnzZg4fPswzzzzDD3/4Q44cOYJKpeLMmTOUlZXhdDrxeDwMDw9z+vRp/vCHP3Dv3j0Ali1bxtatW1m7du08Y/Lr4na7mZ6exu124+fnN88riffapZIwgJyvPLdfJVQqFSqVCpfLtag3Uq1Wk5yczOHDh2Vj88c//jE/+MEP2L59O/Hx8fMWCQA0Gg2xsbHk5OSQl5dHXl4e69atIy8vj+XLlxMaGjp3F1QqFUFBQaSkpLB582ZeeOEFORe4vLycyspKWcwLb584HA7Ziy4UfwUCgUDwdRBvD4FAIPgjsZgHDe9ncw0Xk8lESUkJX3zxBaOjoxw+fJi3336bl156iUOHDrFhwwZ0Ot08z5vD4aC+vp7jx49TV1fH5s2beeWVV4iKipplNLS3t3Pq1CkKCwtJTU3lzTff5PXXX+e5555j375987xrM1nI2FSpVLJQj91uZ3x8fN49McNj+FWRjh8YGCh7Lzdt2kRWVhZdXV3k5+djtVpxOByUlZVx+vRpenp62Lp1Kz/5yU94+eWXOXLkCFu2bFnQIPs6KJVKtFotKpUKi8XC9PT0PFVfj1dpd2pqSs799PWWtZmLUqnE398fPz8/WZl3IZRKJSEhIWRmZpKXl8fq1atZunQp0dHRaLXaBY8toVQqUavVaDSaWZtarX6gUanwhlMnJibKId9jY2OyYrWE0+nEZDKhVCrR6XTzDHeBQCAQCB6Fxd9IAoFAIPijMdegUygUGI1Gampq6O3tZdmyZTz33HPk5uYSGxuLTqdbMETV7XbT2dnJ2bNnuXnzJsnJybz++utkZGTMM16ampqoq6sjICCAHTt2sGPHDlJTUwkLC8PPz2/RPErmlDuR8PHxISIigrCwMKampigvL58XNizlhk5NTc0zsB/G3HtVq9VERESQlZWF0+mksLCQqakpHA4H1dXVdHV1kZqayu7du1m7di0JCQkEBwfLhvSDmHuuxVCr1SQmJhIYGMjIyAjNzc0YjcZ59zw8PExDQwP+/v6kpKSg1WoXNAqVSiXBwcHo9XomJycxGo1zm8xCoVCgVCpRzilV8yAe5d483rDdhRYUFN6w45n5vNK53d685vHxcVn0SxiqAoFAIPg6zH9LCgQCgeBPxkwjwmazyWGlkrCOZECMjo5y//59JicnZ+0zPDzMlStXOHv2LHq9nh/+8Ifk5eWh9NY4dblcsvd2enoam82G2luKxMfHB7fbjclkoqWlhZqaGljEe7oQarWaqKgoVq1ahcVi4fTp0zQ2NmKz2XB7y+x0dnZSVFREZ2fnVzZUF0Kr1ZKamoper6etrY2BgQEcDgcmkwmXy4WPj48cfupyuRgeHqauro6+vr65h0KpVOLj44NCoWBqako+xkLebgkpBDcnJwe73U5BQQHV1dWYTCY5BHZgYIDbt29TWVlJdHQ027dvn1fWRUKlUhEaGkpYWBjT09MMDg4ueu7F/v5tYLPZ6Orqore3F5vNJveDw+FgdHSU6upquru7CQ8PJyEhQV44sdvtDA4OMj4+TlRUFEFBQfPyZAUCgUAgeBSEoSoQCASPEclAczqdcz+ah8vlwul04nK58Hg8BAUFER8fj4+PDzU1NRw9epTKykru3LnDe++9R0FBAVNTU/KxLRYLBQUFfPHFF3R0dBAYGIjVauXixYscPXqUo0eP8sUXX3Dq1Cna2tqIiooiMjKSwcFBrl27xo0bNygtLeX06dN89NFHDAwMyNcl4fF4Zl3nTJRKJRERETz99NMkJiZSXFzM//f//X988sknXLp0iS+++IJf//rXFBcXo1QqUalUj9QvkqEoGekSCoUCf39/kpKSiI2NZXp6mvLycpxOp9xvFRUVXLp0icLCQm7fvs1nn33G2bNnsVgs8r1IqNVqoqOjUalUlJaW8uWXX3Lp0iWqq6uZmJiQr8XtdsvfkUKhICwsjIMHD7JkyRIqKir4/e9/zxdffEFBQQGXLl3ivffe4+OPP0ahUHDw4EE2bNiwqJdRqVQSFBREXFwcGo2G9vZ2+dwSM/viUY3Vme0ftp/b7WZkZIQTJ07w3//7f+ef//mfOXXqFJcuXeLEiRP85je/4fPPP2diYoK1a9eyatUqWUXabDbT2trKxMQEGRkZhISECENVIBAIBF8LUUdVIBAIHhPT09NUVlbS1NREcnIy27dvJzQ0dEEv4vj4ODdv3sRoNMqTf4PBgFqtZmxsjJaWFhobG2lsbKS4uJi+vj4SEhIwm80EBQWxdetWAgMDOXfuHDdu3JCP29XVRUlJCaWlpXL9zbq6OmJjY8nIyMDtdtPV1UVLS4tcV7Ourg6FQkFqaip9fX2sXLmSrVu3otFoGBsb49q1a0xOTrJx40ZWrlw5S9BJo9EQGhqKv78/vb291NTUUF9fT0VFBSUlJUxOTpKdnU1ISAhms5nMzEy2bt26YJ/gNZJLSkpoamoiOjqajRs3kpiYKH8ueUqbmppob28nPDyczZs3ExYWxsjICO3t7bS1tdHQ0EB5eTnd3d1y+R6Hw8GGDRvIycmBGZ7jjo4OWltbaWlpobm5eZbhW19fT2VlJampqRw4cEAWTzIYDAQEBGA0GmlqaqKmpoaKigoKCwuprKxEo9HwzDPP8PLLLxMfH7/o/Up/n5iYoKmpiZGREXJzc4mOjgavp7O6upr6+nri4uLYuHEj0dHRix5PYnJyknv37jE0NER2djYrV65cVFDK41WDvnHjhmyoV1ZWcv/+fe7evUtFRQUAW7Zs4fDhw2RlZeHj44PH46Gvr48vv/yS7u5unn32WbKyshYtsSMQCAQCwYMQhqpAIBA8JiTPm8FgYNWqVWRnZ8ulYeYieSmTkpJYt24dKSkpBAQEoNfriYuLIzQ0VBa7iYuLY8+ePWzfvp2IiAjS0tJYuXIler2e6elpgoODycnJIT09nZiYGKKjo+UtKiqK+Ph4srOzSU1NJTY2lqioKFmAJzg4mNzcXJ544glWr16Nn58fa9euZdmyZbISrcPhICUlhQ0bNpCSkiJ70/AaWn5+frKacXh4uFy3MyMjg71797Jz507i4uKIiIggNzeX9PT0BftEwmq1EhQUxIoVK1ixYsU8ISRJZCkoKIiMjAxycnKIiIggKiqKsLAwfH195XI6GzZsYMeOHSxZsoTIyEhWr15NQkICeK9dp9MRHh5OSEgIWq2WkJAQMjIyyMjIQKfT4Xa7CQ4OZu3ateTm5sphxf7+/sTExJCYmEhERIT899DQUFatWsWhQ4d48sknSUtLWzA3dSYKhQK3201vby9VVVVER0eTk5ODUqnE7XZjt9vR6XTk5uaSlZU1S8l5MSTPvhSanZqailarndtMRqVSERgYSHR0NAaDQRZ4ioyMZNWqVTzxxBM88cQTZGVlyQsVVquV8vJyjh8/TnJyMs888wxRUVHCoyoQCASCr4XC86D4H4FAIBB8bSThoPHxcbRarWy0LYSU22e1WgkODiY4OBiNRoPb7Zbrk/b39+NwOAgNDSU+Ph61Ws3w8DBOp5Pw8HB8fX0ZGRmZFSo6d4j3eDyo1WrCwsIICgoCr/euv7+f8fFx/Pz8iI6OJjQ0FLvdTm9vLyEhIURGRqJUKrHb7fT392Oz2QgNDZXFiebicrmwWq309fUxNDSEx+PBYDAQGRmJVqtlcnKSyclJAgMDiYyMnLu7jMfjYXR0lLGxMXx9fQkLC5tnYDmdTiYnJxkaGsLX15fY2Fg0Gs2suq6SsSudf3p6momJCcLCwmYZvm63G7PZzMDAAMPDwygUCiIiIoiOjkatVjM+Po7RaESr1cp/m7mv1WrFaDQyNDSEyWTCx8cHg8FARETEgqVrFsLj8TA+Ps6VK1d47733iIiI4Be/+AVpaWm4XC7GxsYYGxvD399fNiIfhsPhYHh4GJPJRFBQECEhIQuWr5GQfndTU1MMDw8zOTmJw+HA19eX0NBQDAYDOp0OjUaDQqGQ84//8Ic/cPbsWf78z/+cZ599dtEIAoFAIBAIHoYwVAUCgeAxIonQPEyZVcodXKyt5MmUDE21V3FVypWU2kvHWAyPN69SpVLJnj3J2+ZyuVB6S5eoVCrZIyzlk0r7S+eceYzFcDgccnvpuJJncO6xF0PqQ+m6F+pD6Xhz20iearfbjUqlkvttZl/PPb90j1L+rLSfdB7pWhYzOmeeU2q32HUvhsPhoK2tTc51/cEPfsDLL78sh9hKfTf3d7IYD/t9LYbUr9J3uND9eDwepqamuH37Nu+99x7BwcH8/Oc/Jz09fdGFGYFAIBAIHoYwVAUCgUAg+I7h8Xgwm83U1NSQn59PTEwMzz33HH5+fo9kYP4xcbvdTE1NUVpaSmFhIStXrmTbtm0PrecqEAgEAsGDEIaqQCAQCATfQdzeMGQpdDoxMXFRL+6fEo/Hg8PhwGg0MjExQURExCPlzQoEAoFA8CCEoSoQCAQCwXcUKWRXCrX+rhp//16uUyAQCAT/fhCGqkAgEAgEAoFAIBAIvlM8WAVDIBAIBAKBQCAQCASCPzLCUBUIBAKBQCAQCAQCwXcKYagKBAKBQCAQCAQCgeA7hTBUBQKBQCAQCAQCgUDwneJ7JaYkFSaXVAcftaC5QCAQCP70uN1uHA4HTqcTAJVKhY+PDwqFQozlAoFA8C0hTf3FuPr1EX34x+GPYqjOlK2f+cVKhuS38SW7XC7Gxsbo6OjAbDYTGxtLXFwcvr6+c5sKBALBd5q5Y+XDxsiv2v67iMPhYGRkhNLSUpqbm3G5XKSkpLBhwwYiIiJQqVRzd5HfLTP/zYw++FP3hfS9/KmvQyAQPH6+yjj8oLbSZ9LnM/mm45rb7cZms+FwONBoNPj6+qJUzg+unHnur3uuR2VmPzwMaTz9Nphrl0hI/TuzX2a+ZxQKBR6PB6vVitPpxNfXV15QFXz7PHZD1WazMTAwQHNzM+3t7YyPj6NSqQgPDyc5OZn09HQMBsM3LmJus9moqKjg888/p6+vj3379nHgwAHCwsLmNhUIBILvLG63m/7+fjo7O7FarcTGxpKamrroGOnxeGhubqa/v5/Q0FASExPR6/Vzm32nsVqtNDY28sUXX3D9+nUGBwcBWLNmDX/3d3/HihUr8PHxmbWPxWJhYGCAnp4epqammJ6exul0olarCQkJISYmhpiYGPR6/YJG7uPE4/FgNpvp7+/HbDYTExODwWAQExmB4HuK1Wqlr6+PgYEBtFotiYmJBAcHL/jMu1wuRkZG6O7uxul0EhMTQ1RUFD4+PrhcLkZHR+nt7WV0dJTp6WlsNhsA/v7+hIWFERMTQ3h4OP7+/gsamYvh8Xjo7u7m9u3bjI+Ps3nzZpYuXTprbHW5XNhsNsxmM263Gz8/P/z9/VGr1QveC959pGjGhVAqlXKU40xcLhfT09NYrVZ8fX3RarVoNJoFzyONqdPT0wQEBKDVaucd71HxeDxMTU3R3d1NR0cH/f39TE5O4vF4CAwMJDo6muTkZJKTk9Fqtbjdburq6hgZGSEiIoL4+Hg0Gg2lpaWUlZURHx/P1q1bCQ0NXfDaBd+Mx2aout1uRkdHKS4u5sqVK1RXVzMyMoLNZkOhUKDVaklISODgwYMcPnyYkJCQb/QFm81mbt68yT/8wz/Q3t7Oa6+9xltvvUVMTMzcpgKBQPCdxeFwcPXqVY4fP05XVxerVq3itddeY+nSpQu+mJ1OJ//2b//G5cuXWb16NS+88ALp6enfaDz9Y+JyuWhvb+eDDz7gww8/xOPxsGXLFoKDg4mJieGZZ54hJSUFjUYj7+N2u2lra+PUqVNcvXoVi8UihwsrFAo0Gg0Gg4HMzEy2b9/OypUrCQkJmXHWb47b7cZqteLxeOZNGG02G8XFxZw+fRqj0cju3bs5dOgQOp1u1jH+2EjXrFAoFvWkCASCr87AwABXrlzh5s2bREVF8fzzz5OVlbXgIpnFYqGoqIgvv/wSs9nMvn372L59OyEhIZhMJs6dO8fZs2fp6+vDbrfL3jyVSoVWqyUuLo41a9awefNmUlNT8fPzm3uKBRkdHeXixYucPn2amJgY3njjDZYvXy4vgg4ODlJaWkpJSQk9PT04HA7CwsJYsWIFa9asITk5ed65pLGupqaG6enpWZ95vGl4MTExrF69mqSkJHx8fPB4PIyPj3Pnzh3u37+P0WhEp9ORk5PDunXriIuLmzXeA0xPT3P58mXa2trYt28fGRkZ89o8CpOTk9TW1nLz5k0qKyvp7e1lcnISu90OgEajISgoiOXLl/PWW2+RnZ2N2+3mf//v/01hYSFbtmzh8OHDJCQkUFxczIcffojZbOa1115j69atBAQEzD2l4Bui+sUvfvGLuX/8png8HsbGxigoKODTTz/lzp07qFQqMjMzycrKIi4uDpVKhc1mIzExkRUrVuDv7/+NJlYOh4OOjg7u3LnD6Ogoubm5rFq1isDAwLlNBQKB4DuL0+mkqKiIs2fPUlpaytDQEDqdjuXLl8+bJOA19I4fP86lS5fQ6/WsXr2aqKiobzSe/jExm83cu3eP3/72txiNRl555RV+/OMfs3nzZlasWEF0dDS+vr6z7sftdtPR0SEbqmq1muzsbGJjYwkJCcFut9Pa2kplZSUdHR3odDqioqLw9/efde6vg8fjwWKxUFdXx5UrVxgdHSUyMnLWNdrtdu7du8eJEydobGwkJiaGNWvWfCvn/7qYTCYqKiq4ffs2k5OThISE/EmvRyD4PjE6OsqdO3fIz8/H6XSycuVK4uLiFlwMstlsVFVVceHCBbq7u0lJSSEjIwOdTofFYuH8+fOcPHmSkZER4uLiSE5OJiIiAh8fH0ZGRqivr6ehoQGTyURERAShoaGLRtxI2O12qqqqOHPmDKOjo+zcuZO1a9cSEBCAx+OhtbWVo0eP8umnn1JSUsLAwAD9/f00NDRQW1uL0WgkKCgIg8EgG4hutxuj0chnn33G0aNHKSwspKKiQt7Ky8upqalhamqKxMREYmNj0Wg0TE5O8uWXX/L5558zMDCAx+Ohvb2d2tpaXC4XERER6PV6ue9sNhv19fV89NFHuFwuVq9eTVhY2IJ9+yCGhoY4f/48n3zyCVevXmVoaIiQkBDS0tJYtmwZKSkphISE4HK50Gg0rFu3jqioKJxOJ++//z43btwgIiJCfi/5+/szPDxMeXk5ZrOZpUuXEhQU9JWvS/BgHktvSpOEy5cvU1NTQ1paGj/60Y945513ePvtt/npT3/Kz372M/7sz/6MLVu2oNPpvpVJleIbxu4LBALBnxqPN+/S4XAAMDIywqVLl7h37x4ul2tuc/Aaq5II0cxcmu86Ho8Hk8lEW1sbbW1tREdHc+jQIbKzs0lNTSUhIYGAgIAFX/xSH2k0GlasWMGf//mf8/bbb/Nnf/ZnvPvuu7z55pvExsZSWlrKyZMnqa+v/1b6RlqIvXDhAv/2b//G3bt3sVgss8Le1Go1KSkp7Nixg927d5OTk/MnNQqlCKdTp07x8ccfU1paytTU1NxmAoHga+LxeHC5XDidzkcah91ut9x25rju8XhwOBzYbDZiYmI4cOAAb731Fm+//TbvvPMOP/3pT9m+fTsmk4mrV6+Sn5/P6OjorGMvhNFopKKigq6uLtLS0li5ciVBQUF4PB4GBgY4fvw4H3/8MRMTE+zevZuf/vSnvPvuuxw4cACVSsWVK1c4efIkLS0t8rtJOm5LSwtGo5GEhATWrVvH5s2b5W3Tpk1kZ2cTFhaGSqXCbrdTXV3NsWPHMJlM7N27lx/96EccPHgQj8dDQUEBFRUVTE9Py+9Co9FIQUEBY2NjrF+/npiYmAU91Yshjdlffvklf/jDHygvLyclJYWXX36Zd999l3feeYc/+7M/48/+7M/48z//c959911effVVkpOT0Wg0eDwenE6n/I6Vxvrw8HDWrFlDXFwc1dXVVFdXY7Va555e8A2Z//b/FrBarXR0dNDY2IhSqWTz5s088cQT5ObmsmTJEjIzM9mwYQO7du1i2bJlX8t9vxiLGakzJxFfha+731flj3WehfhTnlsgEMxHGseioqJISEigubmZEydO0N3dveDzuti4txCeBcQjHhePci6r1cro6CgOh4Po6Gg5/0etVj8wL0r6u0ajITo6muzsbJYvX05OTg5btmzh2WefZf/+/ej1eioqKqiqqpoXmrYQj3rNra2tNDY2MjY2hmeOwIdarWbp0qW89NJLvPHGG6xfv/6hwn6Pct5vgtlsprm5mba2NiYmJhZd9JjJ47wegeD7hjQGPIrD5GGfA+j1elJTU8nKymLFihWsXbuWffv2cejQITIzMxkbG6OsrIyhoaEHPqtut5uuri5qamoAWL58uWzsWa1WSktLuXjxomw4/vCHP+SZZ57hmWee4ZVXXuGJJ55ApVJRXFxMeXm5vMjldrsZHx9ndHSU8PBw9u/fLxvV0qLhW2+9xaFDh2Sjz2w2U1hYSFtbG1lZWWzZsoW8vDx27drFkiVLGBwcpL6+nrGxMdxuN2azmbq6OkpLS1m2bBkrV64kMDDwkfpPwul0cufOHY4dO0ZbWxurV6/m1Vdf5YUXXmDHjh2ybZKRkUFubi5bt25l48aNs3KM5/4X77snKSmJrKwspqenuXfvHuPj4w/8LgRfncdiqDocDiYmJpiamsLHx4fIyEjCwsLw8/NDo9Hg4+ODVqslMDAQPz8/+Yt3Op2MjIzQ0NBAY2MjRqNx3svU5XIxNDREVVUVzc3NTE5Ozlu5kgYJu91OV1cXBQUFnDp1itOnT3P79m26urqw2WwL/pjcbre8wj9zv6KiIgYGBpiYmJCN8OHhYXnlbGpqivb2dvm6TSYTDQ0NXL16lfv378sPnXSOyclJmpqayM/P59SpU5w6dYobN27Q2NjI1NTUvGuz2Wz09fVRX19Pe3u7vNo0t400GHV3d8ur/A6Hg8HBQRobG+ns7MRkMjE5OUldXR2XL1/m5MmTnD9/nrKyMvmeBALBn57o6Gjy8vIICQnh7t27XLlyBZPJNLfZQ5HGzfv373Pu3DmOHz/O2bNnKS4uZmBgYNYK+TfB6XQyOjpKRUUF58+f5+jRo3z55ZcUFhbS29sr5wHhjbzp6+ujurqajo4OPB4Pdrud+vp6SktLaWxslHNAF2Pm5EGtVuPr64uvry8BAQFERUWxbt06YmJiGBsbo6uri4mJiVn7e7zKjX19fRQXF3PhwgVOnDjBmTNnKCoqmnXNHq/3t7W1lerqagYHB7FarQwNDVFZWUlpaSkNDQ2yKIc03kvq9nO9wh6voEd9fb3srZC+k/7+/nnjsNVqpbm5WQ7Ds1gsdHZ2cvv2bc6dO8fly5cpLy9nZGRk1jvRYrHQ0NBAdXU1o6OjmEwm+vr6qKmpoaysjMbGRrlfpHtsaWnh2rVrnDhxgtOnT3Pnzh06OztlUReBQPD4UXjz7X18fPD19cXf35/Q0FDS0tJIS0tDqVQyMDAgjzmLIS2sdXZ2yvvrdDo8Xk9jSUkJLS0tZGRksG3bNpYsWUJoaCghISGkp6ezceNGlixZwvj4ODU1NYyOjuL2KuaOj48zNTVFZGQky5cvJzs7e9aWlZVFSkqKHMprsViora3F6XSSnp5OVFQUWq1WFinyeDz09fUxMTGBw+Ggv7+fu3fv4na72bJlC9HR0V/Jm+pyuejr6+Ps2bNUVVWRmprKwYMH2bx5M/Hx8eh0Olm1V6PR4OfnJ4s1Pew8CoWC0NBQli5dSmBgIJWVlfT19c2zWwTfjMeSo2qz2WhtbZXDi1JSUkhNTSUwMHDey3omFouFmpoaLly4QGNjIzqdjvDwcNnj6vF4sNlslJSU8MUXX9DX10dYWBghISF4PB46OzspLCxkdHSU5ORkVCoVt27d4sKFCxQUFHDv3j1qa2sZHh5Go9Gg1+tnSUpLhvL9+/c5f/48Fy5c4M6dO1RUVNDc3IzRaMRoNHLv3j1qamrw9fUlPDwcpVJJT08PN27c4N69ezidTnp7e2UDcGJiguTkZIKDg3E6nXR3d3Pnzh0uXrzItWvXuHv3LqWlpVRXV9Pa2orFYiEwMHDWg2I0GiksLOTGjRsMDQ0RFhZGcHDwrP4cHR3l2rVrXLlyBavVSnh4ODqdTs5NunHjBr29vTgcDiorKzl37hzXrl3j9u3blJaW0tTUxNTUFFqtFp1O90BvhkAgeDw4nU5qamq4d+8eBoOB3bt34+vrK4+nS5cuJSYmRn423W43165do6qqipSUFDZu3Eh0dDQKr4S+2WyWc5POnTvH7du3uX//PmVlZdTX1zM4OIharUav1z/U6/cgzGYzDQ0NXLx4kfPnz3Pz5k15Bb62tpbe3l5UKhVBQUH4+PgwNTXF3bt3OXHiBOXl5QwPD+N2uxkbG6OqqoqRkRHS09MJCAiYNw55PB76+/spLCyko6OD7Oxsdu/ePS9Pa2pqSl6cXLZsGWvWrJFFlSQjtb6+ni+++IL8/HyKiopm9c3IyAj+/v4EBwejUqno7++X76+2tlaesA0PD1NTU8PQ0BCRkZHo9XoaGxu5dOkS1dXV6HQ6kpOT5etyuVwMDAxw48YNzp49S35+vtxXkpdWmpSqVCo8Hg9Go5GTJ09y+/ZtVCoVPT09XL58mcuXL1NQUMD9+/dpbm7GbDaj1+sJDg7G4/EwNDTE0aNHuXr1KnV1dYyPj2O32xkcHJSVLA0GA+Hh4YyOjlJUVMSpU6fkcHPpmmw2G7Gxsd9aqo5A8H1ifHyc6upq6uvrCQkJYdOmTcTHxy8453U6nbS0tFBaWorNZiMnJ4fly5ej0+mwWq0UFhZSWlpKZGQkmzZtIiEhQR7bFAoFk5OT1NTUUFdXR3BwMNu2bSMhIWHR53J0dJSbN29SV1dHRkYGW7duJSIiArfbTXd3N6dPn6aqqoq9e/eyZ88eDAaDPPdUq9W4XC66urqor69HpVKRm5tLdHQ0AOXl5eTn55Oamsq2bdvkspBSRIxarUalUsnvI6PRyLFjx5iYmGD//v1kZGTg6+uL2+2mublZHi9XrVqFn58fJSUl3Llzh+XLl7Nr166vrJ5us9koLCzk008/ZWxsjOeff569e/cSHR2NZhGF4bnY7XbOnj1LU1MTy5YtY+3atURFRcn3Z7FYqK6upr29XU5b+TYjRf+jM/8J+hbw9fUlPj6epKQkbDYbt27d4vLlyzQ0NDA+Pr7oaoPdbqezs5OCggIKCgro7u6et9LvcDhobW3l3Llz3Lp1i4GBgVkrzwqFAqvVSk1NDefPn+fevXtYLBaCgoJQKBTU1NTw+eef8/nnn1NZWTkrDl5Khv/kk084d+4cAwMDhISEEBERwfj4OFevXuXTTz/lxIkT3Lx5k66uLlmRbWxsjPLyci5cuMCpU6f4/PPPuXnzJkNDQ9hsNtzefKqOjg45mbugoIDJyUkMBgNhYWFMTk5y9epV3nvvPc6ePUtPT498byaTifr6evLz8ykpKZm3ai6thFdUVHDp0iXKy8uZmJjA7XbLnuVbt25x9uxZjh07JudsqVQq9Ho909PT3L59mw8++IAvv/yStra2Wd4PgUDwx0ehUBATE8OOHTtISEigvLyc06dPywbSwzCZTJSWlvLb3/6WDz74gNbWVvR6PfHx8Wi1WhoaGvjss8/44IMPKCkp+VreWmYsMn700Ud88MEHVFVV4evrK5do6Ojo4LPPPuN3v/sdhYWFTE5O4vKWJhgZGZHHYYvFwuDgIP39/RiNxln5QF8VyYCcnJxE41Vy1Gq1s9rY7XY6OjooLCxkfHycsLAwUlJSCAoKoqmpSR4r29ra8Hg9vmNjYwwNDckRK2azmaGhIQYGBhgdHcVut8uLlbdv3+b69eu0tbXNuq7R0VHOnj3L+++/T3l5Ob6+viQlJRESEkJ7ezsnTpyQ88E83pBg6bv88ssvOXHiBF988QXFxcWYTCbUajUjIyPk5+fz4YcfcvHiRUZGRmBGfdrh4WEsFovc79I1G41GrFYr09PTVFRU8NFHH3HhwgW5rE5oaChTU1P09fWJ/CuB4CF4vFFsU1NTjI2NMTo6Om8zGo1MT0/jcDgeOL4pFgghttls9Pf309PTg0KhICEh4aFVM4xGI/39/SgUClmoSKVS4faG1kreS51ON0/BHECn02EwGOSFr/HxcTmacHx8HKvVit1up6enh7q6Opqamujv78dkMs17T828p5n37vHm+CoUCrlcTk9PDyUlJfj5+bF+/XoMBgMmk4mxsTEsFsu8Yy+EzWajpqaG/v5+IiMjycnJITIyct6i5tdFqVSi1+uJjo7G4XDQ1tYmxslvmcdiqPr5+ZGWlsb27dtJTU2lublZngxdunSJmpoaRkZG5hmsbq90/vj4uPzjn/sQSw/W6OiovDI898dqNptpb29namqKNWvW8IMf/IA333yT1157jW3btuFwOLhx4wZXrlyhq6sLh8OByWSirq6OixcvUlZWRnh4OIcOHeLNN9/kzTff5LnnniMxMZH29nbq6+sZHh7GbrfL1+f2hgx3d3dTWFhIV1cXK1eu5Pnnn2f79u0YDAbGxsa4e/cuFy9epKenh8zMTF544QXeeust3nzzTZ5//nmWLl1KS0sLJ0+elCdPbrcbl8slDyhTU1PzDHi8q/RTU1OMemtvzZzkORwOhoeHqayspLi4GLVazZ49e3j11Vd56623eOmll1i+fDl9fX1cvnyZoqKiR54MCwSCx4PD4UClUpGdnc2ePXtwuVxcvHiR27dvPzQM0+l00tHRwRdffMGFCxcICAjg8OHD/OhHP+LHP/4xP/rRj3jiiSdQKpVcvXqVM2fOzDKoHhW3201nZydnz57lwoULuFwu9u3bx+uvv85PfvIT3nzzTZ5++mkCAwO5efOmrISr0WhYvnw5e/bsISMjA7VaTUJCAocPH+bZZ59l27Zt6PX6B07AJBRzQmulNIg7d+7Q19dHZGQkqamp8+rLajQaYmNj2b17Ny+88AKvv/46b731Fq+//jpbtmzBbDZz/fp1SkpKsNlshIaGsnHjRp588kmSkpJQq9WkpaVx8OBBnnnmGbZv305kZCQKhQKbzcbExIQ8qcI7GTObzZSWlvLFF18wMjLC5s2befXVV+XvZOfOnbjdbq5evcrNmzflxQO3243FYqGnp4e7d+8yNjZGXl4eL730Eq+//jqHDx8mPj6epqYmrly5Qm1tLQqFguDgYHbu3MmTTz5JXFwcAQEBLFu2jCeffJJnnnlG9q4MDw9TVFREUVERwcHB/PCHP+THP/4xb775Ji+88AIbNmxYtC6kQCD4fzgcDvr6+igoKODLL79ccJNC/IeHh2XjbCHsdjtGo5GBgQF6e3tpb2+npKSEGzdu0NTURHR0NOvWrZPHnMUYGxtjZGQEtbfG9My6qT4+Pvj7+6NSqZiYmFjQuJQWyxwOB2azWXa+2Gw2RkdH5fSC48eP89vf/pbf//73HD16lNu3b9Pd3S07PSQjNDo6GpfLJS+eebzRLUajEYCwsDBcLhc1NTX09vaSnZ1NVFQULS0tXL58mTNnznDz5k3a2towmUzz7ASJmWOmxWIhPj5+nkL7t4G/vz8RERFydOXD3s2Cr8ZjMVSVSiURERFs376dI0eOkJ2dzejoKOfOneNf/uVfeO+99zh//rwc5rrQj+xBPyJpRWZum5l/Dw0NZdOmTTz77LPs3r2bzZs3s3//fn74wx+yefNmpqenuX//Pk1NTUxPTzM6OkppaSmVlZUEBQXx1FNP8cwzz7Bx40bWrFnD3r17OXToEEuWLJm18jPz3HhzAWw2G7m5ufzoRz/ipZdeYuPGjej1ejo6Orh58ybd3d0sXbqUI0eO8OSTT5KXl8e6det46qmneOmll1iyZAn19fXyQy4ZpXPvdzHmtpP6xG63Mz09TVhYmDxJ2bZtG1u3buWZZ57hhRdeYOnSpXR3d3Pv3r1ZA4xAIPjj4/SqQkZFRbFnzx5WrFhBR0cHn3zyCe3t7TgcjnnPu8Tk5CQlJSVcvnwZpVLJiy++KI9HK1euZOvWrbz88svs3LkTl8tFQUGBbJB9FaxWKxUVFVy+fBmbzca+fft45ZVX2Lp1K7m5uWzYsIEXX3yRZ555Bo1Gw61bt7h//z42m40lS5awZcsWOVQqJiaGJ554ggMHDrBhwwZ0Ot281f25OL15sfX19dTV1VFVVcXt27f54osvuHjxIi6Xi40bN5KdnT2rvI9CocDPz4/MzExeeukldu/eTW5uLpmZmfJ4nJKSQk9Pj5wXGhwczOrVq9m5cycJCQmoVCqSkpLYu3cvTz31FJs2bZLTQaTvZea7yuXNFT579iytra2sX79efs9kZWWRl5fHwYMHWb16NUNDQxQVFdHd3S0fR6lU4na7USqVbNmyhSNHjrBnzx527tzJ4cOH2bNnD8HBwTQ1NVFVVYXb7Uav17Nx40Z27dpFdHQ0Wq2W9PR0du7cyf79+9mwYQNhYWEYjUY6OjqYmpoiKSmJ7du3s3r1atatW8fevXtZv369MFQFgofgcDjo7Ozk/PnzvP/++wtuH3/8Mfn5+QwMDMwzCmcyMDDArVu3OHnyJEePHuWjjz7id7/7HdeuXSMgIIC9e/eyadMmgoOD5+4q4/F4mJycZHJyEh8fHwIDA+WwVMlwTUxMRKfTUVtbS11dnRzxIjlgOjo6aGlpwWw2zzquw+GQxxN/f38GBgbkyL9PP/2U3/72t5w9e5b29nbsdjsKhQKtVsuKFSvw8fGhoqKCpqYmhoaGaGxspKWlBa1WS3x8PKOjo1RXVxMSEiI7cD755BPOnDnDlStX+Pjjjzl69Cj19fWYzeYF7Qi3Vz9Gis4JCwtDq9V+62OYr6+vXCJo1CsMKPj2ePAM4Bvg4+NDcnIyTz31FD/+8Y85fPgwqampGI1Grly5wnvvvcenn35KfX39gp5TFjC4Hoa06qPValm+fDkbNmyQw7gCAgIIDQ0lOzubrVu3EhUVxdDQEO3t7UxMTDA0NCTn72RmZrJ+/Xri4uLQarX4+voSEhJCdnY2ubm5C9Zmlc6t8IZiSJO0mJgYgoKCcHhDlhsaGvD19WXNmjVIkt3+/v74+/sTHh5OXl4eGzZsQKlU0tTU9K0LWEix/+vXryc2NpbAwEB03hqDeXl5rF27FpVKRUdHBz09PSKEQSD4DuDn58fSpUs5dOgQQUFB3LhxgwsXLjDmVZxdiOHhYe7fv8/w8DCZmZkcOHBANlR8fHzkvMmdO3eSmppKV1cXFRUVDA0NzT3UAzEajVRWVtLS0kJSUhJ79uwhKSkJnU6HRqNBq9USGxvLE088QXp6OsPDw1RXVzM0NCSL6klaARqNhsDAQAwGgxye9iA83pDY+/fv86tf/Yp/+qd/4pe//CW/+tWvOH78OCaTiW3btnHo0CFZfGQmSqWSwMBAIiIiUCgUDA0N0dLSQnNzM1NTUyi8qSSDg4OMjY2hVqvR6XRynq3C6yHQ6/WEhoai1+tn5SbNfYdJGgX5+fmyRzkgIICpqSlGRkaYmprCz8+PmJgY/Pz86OjooL29fdbxNBoN6enpbN68WX6/BQUFERsbS2ZmJnFxcUxOTsrjt5TeMVN3wM/Pj6CgIPmaZwqJ4K032NTUJHs49Ho9QUFB31q4nEDwfUUaEwIDAwkODiYkJGTeFhwcTEBAwKLPkzRuDA0NUVhYyPnz5zl9+jQnTpzgypUrjI+Ps2rVKnbt2kVSUtID8yE93igOq9WKRqOZFdqrVCoJDQ1lzZo1pKSk0NDQwJdffkl+fj5VVVVUV1dz+/ZtLl68SGlpKWazmYCAAHx9fVEqlfj5+bFp0yZ++tOf8hd/8Re8+eabvPTSS2zdupWAgADKy8s5duwY169fl9PV/P39Wb9+PdnZ2dTX13Pu3DnOnz/PmTNn6OvrY9myZURGRtLS0sLExARZWVk4nU5ZDCklJYX169fj8Xi4ePEi169fZ2BgYF6EpnTvDocDhzfEWqPRzFpE/LZQq9Xy9ykZ+YJvj8dmqCoUCnx9fYmLi2Pr1q28/vrr/NVf/RWvvvoq6enpdHR0yIqQvb2939oX6/F48PX1JSYmhujo6HkDQUBAACkpKSQmJuJ0OuUcJqPRyODgIAqFgsTERKKiouZNkrRaLQaDYcEYfgm1Wk1iYiJpaWmzhEmmp6fp6+vDZDIRHh5OUlKSnDcroVQqMRgMZGRkEBkZyfj4OIODg9+aoapSqQgNDSU5ORmDwTDvHgwGA6mpqXIewMjIyLd2boFA8PVReKNEdu/ezY4dOzCbzRw7doza2lrsdvuCL9/R0VGamprQaDRkZGQQHx8/r41KpSIzM5Pk5GRsNhudnZ0MDAzMavMgPB4PIyMjdHd3o1AoSElJIS0tbd55FN4FvIyMDPz8/Ojr65ONIGmRT+KrvgtcLhdGo5GqqipKS0tl72diYiIvvfQSb731Fnl5eQQEBMzdFY83L7atrY1r167x8ccf8+tf/5p/+Id/4F//9V+pqqrCbrdjt9tnjYWeGaq+0vUvtmAg4fGKAUohfE6nk6amJs6fP8/x48c5duwYx48f59y5c9TX12Oz2TCZTAwPD886jlqtJioqioiIiFkTVLVaTXBwsCzaZzKZ5IXGmdcr/XsmarWayMhIVq5cSUJCAvX19fzjP/4jn332GcXFxXJ+6tz9BALBbHx8fEhLS+Oll17i5z//+bztP//n/8xf/uVfcvDgQeLj4+fNM2ei1+tJT09n5cqV5OTkkJqaSnBwMHa7nYmJiUeen0mROQqFQhY2wjsua7Va1q9fz/79+4mIiODOnTv85je/4Ve/+hW//OUv+f3vf095eTl2u10WeNPr9ajVavz9/cnOzmbv3r3s379fjkR86623ePnll1myZAnt7e3cuHGD5uZm7Ha7/D568cUXWbZsmaww3tbWxvLly+X0vJaWFqKiokhNTaWxsZHq6mpycnI4cuQIzz33HAcPHkStVlNWVkZra+uCfSEtGkiLiiaTSTZav00UXtV5hTfl40FecsFXZ2Fr61tEpVIRGBhIUlISGzdu5MUXX+Ttt99m8+bN9Pf3c+PGDWpqar5Vz53Cu+o810hlxgq6pBRsNpuxWCyYTCZsNhu+vr4EBQUtqH4pPeRzDbyZKBQKdDrdvEmRxWJhYmIChTdnKDg4eMFVMLVaTVhYGKGhodjtdkwm04KCInMnghKL/R3vvfv5+cn5CHPx8fEhJCSEoKAgXC6XfG6BQPCnR61WEx8fzwsvvEBqaip1dXWcPXuWoaEh1DOUFSXMZjMjIyP4+PgsuPAmERYWJi9cTU9PM+WtkfeoTE1NMTExgZ+fHxEREQQFBc1tAt7wKKkUgTTuzh3Xvg5arZacnBzeeOMNXn31VX7yk5/wd3/3d/zX//pfee2111i1atW8RUFmeBqqq6v5l3/5F371q19x6dIlWSTPx8dHnnxI7b8pdrtdXgCcmJiQS6BJRuqxY8dkBU7J2+EzI5+MGZOihRYnVCqV/N5ze7UNHgXpXJs2beKFF14gISGByspK/vCHP/A//+f/5NNPP6WxsVHOtRUIBAujVqsxGAxkZ2ezfv36edu6devIy8tjyZIlBAUFoVQq540t0r/j4uLYv38/b7zxBu+88w5/8zd/w4svvkhISAilpaXcvHmTwcHBefvPRbGIgBHe642Li+PFF1/kjTfeYOXKldi9InODg4OEhISQk5NDWloaoaGhxMTEEBISIo9B/v7+BAYGyluot/zN7t272bZtG/7+/rS2tsqhw9Icedu2bfz0pz/lhRdeYNeuXfzwhz/klVdeISoqisbGRux2O6tWrUKr1dLc3AxAXl4eqampREZGsmbNGlJTUxkcHFw0L1SpVKLT6eTrHRwcZGpq6ls3JD3edEC8/Tl3XBZ8Mxa3uL5lJCMpNjaWLVu2sH//fmJjY+nv7/9KKlnf9Afg8a58u91u2fCc+xC7XK55D7PEYn+fiWKBmnkS0v4POo50jdJx5t7z3H8/KtJ+j7L/g+5BIBD8afDz8yMvL48XXngBjUbDhQsXqKmpweVyLbgw91XGG7zj9GIG7WJI+888zkLMPc+3Mb4ovJE7S5Ys4fnnn+ell17iueee44knnmDNmjXExsYuuOiIN5eso6NDFv5QKBTs27ePn/3sZ/zd3/0df/VXf8W6devw9ZZO+KZI9+9yuVAqlYSFhbF+/Xp27NjB7t272bVrF7t27WL37t0cOnSI1157jRdeeIHly5fPPdQD+/nr4uPjQ0pKCi+++CI///nPee6554iMjKS6upoPP/yQzz77TKjBCwSPiDS/VM8o0zJzk+Z2D5qPabVaoqOjSU5OZsmSJeTl5fHkk0+yZs0axsbGKCwslLUKHoSfnx++vr64XC7sCwiQajQaUlNTef755/nbv/1b/vZv/5Z3332Xv/7rv+btt98mOzsbu92On58fKSkphISEPHD8ViqVREdHy/VYLRYLo15FdLx9ExQURE5ODvv27ZPz65OTk2lra6Ojo4Pk5GSWLl2K3W5naGiIoKCgWVEkISEhhIeHY7FYGB8fX9BTKhnSksp9Z2cn3d3di+a0fl1cLpesqK7T6b7yO1TwYBb/pT0mFAoFAQEBJCQkEBMTI4coubziRNIXPDOufCZut3veQzYXaTKwUDu3283ExARGoxGVt6ZfQECAHHdvNpsxeoupz0V6yO0z1H4XY+7n/v7+6PV63G43RqNRfrDm4vTWch0dHcXPz0/OeZImdh5vzP1CXtaH9Y3b7ZZDQObui3e1f3R0lLGxMTQz6swKBILvBkqlkuDgYH7wgx+wdu1a+vv7uX79OqOjo/MmDn5+fhgMBux2O/39/YuODcPDw3J4qZQ/JbHQODEXKWfTarXKpQsWwuFw0Nvbi8lkQq/Xz4s6+boovBE0QUFBcn3ph6k6ery5rVJ9WYA33niDH/zgB2zbtk3WEJCUHB+lHx6GwusJDfbWvw4JCWH//v289tprvPHGG/O2119/naeffpr09PS5h3osSEZ/fHw8u3bt4p133uG//tf/ypEjRxgfH+fSpUuUlJQwOTk5d1eBQOBFGiukhamFmNnmQcz9XKPRkJCQQFZWFkFBQfT19dHR0YHpAWXFpDm3VqvFarUyNTW1YKScSqUiMjKS3Nxcdu3axZNPPsm2bdsICgqiubmZrq4uoqKiWL58+aJRMzORFj0lp8fciB9mRFyGhoYSEBBAR0cHpaWlqNVqVq9eTXh4OHZv2oWvr68cwovXc6nRaPB4HU9z+0rCz8+PnJwcoqKiGB4e5s6dO3R2di44//66OBwOucRPcHDwgovGgq/PH91QxWswTU9PMz4+jnpGErJarZbFHKQaVDM9rR6Ph7GxMXp6erB7FcQWwu4tZj46Ojr3I0wmkyyWoVKpiIqKIigoCIPBQExMDAqFgpaWFnp6euZN7EZHR2lra/taoQOBgYHExsYSEBDA4OAgra2tTExMzGrj9tbXkyS5g4ODiYqKwtfXV06Cd7lcjIyMMDY2Nm+wGR4eZmhoCLfXWzwXl8vFxMQEg4ODs9TbJIxGI62trYyOjhIYGEhkZKT8fQgEgu8GKpWK5ORkXnvtNUJDQ7l+/TrV1dXYbDbZqPJ4PISFhZGeno7FW+O0vb19wZd5dXU1LS0t+Pn5kZqaSlxcHB7vYp/Van1g+KhCoSAyMpKEhAQcDgeNjY00NjbObYbH46GtrY3a2losFguxsbGEhYUtOE59HR40KVwIjzc3tauri9HRUWJjY1m3bp1cBN7jDQs2m80L3r9iThTOzH8/CCmqKDIyUh6vg4KCiI6OJiYmZt4WHh6Ov7//3MN8Yx7UXwpv3lpSUpIcCpySksLY2BgdHR1MT0/P3UUgEDwm5j6ner2ehIQEIiMjsVqtdHZ2PjBdQ+FNNwsJCcHhcCzqJJFQeqMfAwICGBsb48qVK5w/fx6n00leXh5Lly59pHnh6Ogo7e3tjI+Po9PpiI6OfuB+k5OTFBYW0t/fz/Lly1m2bBkBAQGyN1gqiyP1h9VqxWw24+Pjg1arXTTk1sfHh9zcXDZu3IhWq+Xy5ctcunSJnp6eeXPor4vVamV0dBSXy0V0dLRw8HzLPBZD1Wq10t7eLic5T05OYrfb5VWH6upqrly5QltbGxEREaSmpsqrJWFhYbI7v7a2lpaWFqxWK06nk6GhIQoKCrh9+zYOh0MOnZiJUqnEZDJRVlZGfn4+3d3dsgfRZDJRXl7O1atXGR8fJzk5mfT0dEJCQoiOjiY3N1eO/T979iw1NTVMTU1hMplob2/nwoUL3Lx5c56B+ShotVoyMjJYtmwZ09PTFBQUcP/+fVm1UzJSr1+/zs2bN+WHS+obrVZLWFgYvr6+9PX1UVVVRW9vL06nE5vNJouB1NbW4likZIXb7WZ4eJjbt29TUlIya8IxPj5OYWEhRUVFqFQqli1bRkJCwgMHFoFA8KdBpVKxe/du9u3bh9FopLGxUVaplbaoqCg2btyIwWCgoaGBTz/9dFY5BKfTSV1dHWfOnKGhoYGUlBRWr15NUFAQw8PDHDt2jP/xP/4H58+ff+DExmAwsHLlStLS0mhqauLEiRM0NzfL5/F4PHR1dXH06FGamppISEhg7dq1REdHzz3UnwSXt0a1tADp8XiYnp6mqKiI2tpaeQFAGlMVMzy4Tq+K78DAABaLZdFoFbz7+XjV8Hft2oXRaOT48eMUFhbKkxxm1BOfmpp65JSYh6HweksDAwNxu9309/czPDwsL0S4XC5sNhvj4+NMTEzI16LwRjlJi58+Pj4irE0g+BOi0WgwGAxERETgcrno6up6aJSDwWAgKipKjthbSB9AirizeuuZlpaW8v777/PBBx8wNDTE+vXr2bVrF1FRUSi9ZbLGxsbo7u6e5ThxekVKb9++TX5+PjabjczMTJYuXYpWq511zpnU1tZSWVlJeHg4a9askee7BoOB6OhojEYjnZ2d8pjY19dHV1eX7NBZzDhUetMsnnvuOdavX8/4+Diffvopf/jDHygqKmJgYACz2SxHcU5PTzM0NER/f/+Cea9zkRY1+/v7UXgFBcW8+dtF9Ytf/OIXc//4TTEajVy/fp2jR49y584dWltb6ejooLa2lps3b3Lq1Clu3ryJn58fR44cYe/evRgMBlQqFS6Xi4GBAZqbm+np6ZGFOpqbm7l8+TJXr15laGgIu91OREQEGzZsICkpCaVSSXt7O0VFRRiNRjQajZxkLa0E37p1i2PHjlFcXExkZCRPP/00GzZsIDQ0VDaUJycnaWxslEvDtLe3U1FRwYULF7h//z6jo6OYTCZCQ0PJy8sjIyMDjUZDf38/xcXFtLe3s2zZMjZt2jQrPEKpVOLj4yNPbJqbm+nt7ZXvr6WlhUuXLnH8+HE6OjpYt24dzz77LJmZmfj5+aFUKrFYLHR2dtLW1sbAwABTU1OMjo5SWVnJl19+SUlJiZwHkJGRwZo1a4iIiMBms9HQ0EBJSQkjIyOYzWYGBweZmJhgcnKStrY2rly5wvHjx2lpaWH58uUcOHCAFStWEBAQsKDRKxAIHg9Op5Oqqiru3buHn1f+f6HSKlqtloCAAOrq6uju7sZisZCZmcmGDRvkVV0/Pz+mp6eprq6mra2NsbExHA4HAwMD3L9/n48++ojLly8TEBDACy+8wP79+9HpdFRXV/MP//APXL16FaPRyKZNmwgMDFxwLFCpVPj6+mK1Wqmvr6e5uZnBwUFcLhejo6NUVVXx6aefcvbsWVQqFUeOHGH//v2yoWo0GikuLqaiooLk5GT279+/YAmwmXg8Hnp7e7l79y4dHR1kZWWxZ8+erxRyJS0OSoaiRqNBo9EwMDBAfn4+Z86ckYX+kpKSWL9+PfHx8eAN9err6+P69etMT09jt9sZHh5mbGxMTploaGjg3r17WCwWuR6pZDAGBATQ2tpKTU0NHR0dsne1o6ODuro6ioqKKC0txeFwkJSUhMcbTXT16lU6OjpYtmwZW7duRa/Xy/fjcrno7+/n3r17tLa2kpGRwc6dO+UQa4fDQVtbG2VlZbKROjo6ytTUFCqVit7eXs6cOcPt27cZHR1lYGCAiooKTp06RVlZGQkJCRw8eJBly5bhu0jer0DwH5Xx8XEqKyupq6sjKCiIDRs2kJCQMG/cxhv119jYKNeTzsnJISsrC51Oh9Vq5c6dO5SUlBAREcGmTZtITEyUxzaFQoHFq1ReW1uL2+0mNzf3gQrCCoWC7u5u6urqUCqVcgkYqb3L5aKpqYmioiLu3LnDxYsX5Xm63W5n+/btPP/88+Tk5MjjyfT0NJcvX+azzz6jvr6ewcFBurq6qKqq4uLFi5w8eZKmpiYyMjI4cuQIq1evRqfTzbmy/8fw8DBnzpyht7eXdevWsXbtWlloCmBiYoLS0lKMRqNcleL8+fMUFxezcuVKduzY8UDBQKW3okZgYCDT09O0tLTQ0NBAQ0MDTU1NtLe309raKpfjuXDhAmVlZbJwlNPp5PTp0zQ1NbF06VLWrl1LVFQUarUau91OXV0dly9fBuDZZ58lKSlp0WsRfHUei6FqNptpa2uT6zBVV1dTXl7O/fv3qaysZHh4mLi4OA4dOsThw4dJSkrCx8dHNubU3lpEkkFXW1tLVVUVPT09JCYmkp2djclkIjg4mLy8PBITE1EqlfKDqNPpWLduHQEBAVRVVVFcXMy9e/fk2PTk5GQOHTrEnj17iIuLk1eJpVh5X19fxsfH6ejooKmpiY6ODhwOB0uXLiUqKor+/n4CAgJkQ9XHx4eRkRFqa2sZGhoiKyuLdevWzZpE4A1BCAoKwt/fH5O3iHJNTQ3l5eXyxMRms7Fhwwaee+458vLy5IdVpVLh443Pl0KQm5qaqKmpoaamhsnJSXJzc4mMjGR6eprU1FRWrlxJeHi4bKhWVFSgUCjIzMzE4/FQUVHBvXv3uHv3LoWFhYyPj5Odnc2hQ4fYuHEj4eHh4mETCP7IuFwuGhsbqa2tRa/Xs2nTJpKTk+dNeBTekC6z2czAwABOp5OsrCzWr19PZGQkSqUSrVZLREQEHo+H4eFhKioqqKuro7i4mJs3b9Lc3ExsbCzPPvsshw4dIjk5GYD29nZOnTpFd3c3oaGhcv3WhQxVhTdUNNRb8Hx4eJj6+nqqq6tlZcqqqirCw8M5cOCAnHcpiWJIUTbSJGDPnj2LTmgkZt7P0NAQubm5bNu27ZENVYU3b8rHxwe73U5XV5c8aSkuLqapqYmgoCDCw8MBiIiIYO3atSQkJMCM/Ctp5b25uZnGxkZsNpssICItzno8HvLy8li1ahUKb55qaGioLDLS3d1NbW0t5eXl3Lt3j+LiYjmaJyEhQR6vp6amKCoqor+/n5ycHDZs2DDrHSNFzNTW1jI4OMjy5cvZunUrWm+Be5VKhcfjob+/n+7ublpbW+WSETExMdhsNm7cuMHNmzcpKyujuLiYwsJC2traSEhI4NChQ2zdupWwsLB5v0WB4D86k5OT8nwxPDxcrlW/0LPicDjo7Oykvr4epVJJbm6uHOpqs9moqKigsbGR+Ph4Nm3aRHx8/KyxzePxMD4+TltbGw6Hg/T0dFJSUhZNE1CpVExNTdHc3MzY2BgJCQkkJSXJnj+n08mlS5f45JNPKCgooKGhAbPZTGpqKk8++SQHDx5kxYoV6PV6+X5MJhOlpaVcv36dkpISeY5/584dysvLsVqt5Obm8vTTT7N58+ZFxw2n08nNmzfJz88nISGBHTt2EB8fL78f1Gq1rBTf1NREfX09JSUl1NfXk5KSwlNPPSXXo17o/cSMaJbIyEji4uLQ6XTY7XZ6e3tpaGiQS5uVlJRQVVVFZ2cnarWa3NxcoqOjcbvd5Ofn09/fT3Z2NmvWrJENfaPRyK1bt7h37x7Z2dk8+eSTGAyGRa9F8NV5LIaqUqkkICCAyMhIoqOjMRgMhIaGEhERQVpaGhs2bGDfvn3s2LGDlJQU2QDD+6MMCgoiMjISg8Eg54/GxsbKimdZWVmEhoayZMkSsrOzZYPK6XTi4+Mj12Javnw5Op1OnrBFR0ezZs0aDhw4wPbt20lMTMTPzw+FN1ROo9EQGhpKXFwciYmJxMbGEhMTQ2ZmJlu3bmXDhg3Y7XYqKioIDAxk48aNpKen4+tVhVSr1cTExLB69WqWLFkyz/2vUqkICAggKipKztHSarX4+/sTHBzMkiVL2LlzJ08++SSrVq2SJbWZEboVEhJCREQEBoOB4OBgDAYDycnJbNu2jT179pCUlERkZCTZ2dmkp6ej1+uxWq2yoerv78/+/fvZtGmTPKgFBAQQHx/P5s2b2b9/P+vWrSMyMnLRUAqBQPB4cTgc+Pn5sXTpUnJzcxfN5/Tx8ZHLXaWlpZGXl8eyZcvQ6/XymBYSEkJiYqKsfOjv74+/vz9hYWHk5eVx4MABdu3aNWsslsLAIiIi2L59O5s3b8b3AQJF0ridkJBAbGysLGjk5+dHSEgIubm5HDhwgD179pCWloa/v798LLdXBM5gMLBu3TqysrIeyWPn8grwSe+GJUuWLDgRWoyZ7wWDwSB7qIODg1mxYgW7du1ixYoVxMXFkZGRQWZmpjwBkRY2pRX30NBQoqOjyczMlIVOnE4nvr6+pKWlsXr1atkbq1Ao8PPzIzo6WhYVDA4ORq/XExISQmRkJOnp6axdu5bc3FzZWJa+k+joaNatWyfXpJWQUkik99CaNWvkhVS87x/J+DYYDBi8ugxLly5l6dKlhIWF4efNTZO2yMhIVq9ezf79+9myZQsxMTFoNJpFfwcCwX9UpLSBoKAgsrKyyMrKIiQkZNFnxeVy4e/vT1pamuwR9fHxweMVzAwKCmLlypWsWLGC0NDQWWObWq3G19cXnU5Hgrc+dVxc3Lw5p4S078DAAO3t7fj6+sppbwqFAo/HQ19fH5OTk4SHh7NixQp5Trlp0yZSU1PlufRMfL3lHGeWpzEYDCxZsoTt27ezb98+1q5dS2RkpGx4zsXpdNLa2opSqWTt2rVkZmbOMjqV3hIzkZGRcuqCRqNh+fLlPPHEE6xcuZLg4OCHOlWkcTcqKoqkpCRSU1NJTEwkKioKg8FAWFgY0dHR8ni9ZcuWWe9SSVth7dq1LF26lKCgIDweD62trVy8eJGRkRGeeuopVq9eveiCgeDrofDMDVT/FpAeNJPJxPj4OJOTk3Kst5+fH0FBQQQHB6PVahf88bq8NTyHh4cxGo3yC1/KX3U6nYx6hZIktTCFt5jv2NgYCq+nQaFQMDIywvDwMDabTX5RSz/4hV64Ho8Hu7d+6eTkJFarVX4YzWYzn3zyCe+//z5paWm88847bN68Ga1XTW1sbIzp6Wn0ej0Gg2HevUkTDZvNhsViYXJykomJCaxWK0pvArtkfAYEBMx78DweD06nk4mJCYaHh5mYmMDj8RAQEEBERAQhISFyH/j5+REaGoqfnx8jIyOcPHmS3/72tyiVSn72s5+xfft2pqamMBqNuFwuuX+lCZtqAYU2gUDw+PF4PExMTDDqVfINDw9/4GqxzWZjeHgYk8mETqfDYDDMM2DsdjvT09P09PRg8qqsSwtzYWFh8ngoYTab6e7uxmg0EhkZKadXPAhp3J+ampJTC5xOp2zERkVFodPp5o27drsdo9Eoh81GRkY+kmfU4i15IEXXhIeHP/Qa5+LxeLBarQwPDzMwMIDdWz9VGgvdXpV4hUKBwWCY5el1u92YzWb6+vpk3QLJYJVCrqXcU4PBQEhIyIwz/7/9Ld7SCmNjY3LemORBkARQJKPd7i3TMDU1RUhICGFhYfO8LNJ7yGQyERgYOK+Ny+VienpaTh1RKBTy4qePj4/8TpjyKoNK3520qKpeRLBEIPiPjsMrVDQ5OYmPjw8Gg2HWgtxM3F5B0bGxMdxuN0FBQej1etRqNS6XC6PRiNFoxM/PT372Zh7H4xWDGx0dxWq1yotcD3IuTE9Pc+PGDT755BOcTicvv/wyO3fuRO+tRtHf3y/XZJUW7HQ6HX5+fgvOB91uNzabDaPRyOjoKGazGafTKS8ASmOev7//vLnsTJxOJz09PVgsFsLCwmY5aCQ8Hg82m43R0VGGhoZwOp2EeMvT6L5iORhpHm21WuU5uMVbWkbpjbIJDAwkJCSEAK/Qq8cbiTI9PS1/5ufnh9Fo5MyZM3z++efExsbyF3/xF2RlZc2b+39TPHNKu/1H47EYqhIe7wqva4ZYg8lkkkUnlDOKBUs/COlh8HhVJ13emqYKb8iUFL7k8oo9KGfU45NW5hUzaoBKxqH0d5VKhUqlWvDLdnnLz3g8HjTekjButxulUonNZuP+/fv827/9G+Xl5ezcuZM333xT/lFK9yq1VyrnCz1NTU1RX19PW1sber2ezMxMOSF+cHCQmpoaRkZGyM3NJTc3d97DKjGzT/H2gdpbl2tuHygUCoaHh2cZqn/1V3/FgQMH8PPzw+kV/1B6Q9kWGpAEAsEfF+k5Zs4YtxgubzmuxcYeZhiSbu/K/8wxdW576WXu8tZnXWwsWoiZ+0rnUXnrCc49j9T+YWPnQkjvgZnj10yka5Duc7E+lM4vvSdmjqczzyGNj3P3XWgsVni90o/yHUrfndSWGaHFM/d5lH6S2kj9vlgb6V7xelql38Dc+5n7uUDwHwG3d46F9/e/2LM7k5nPpzTmPeiZedD4II0JDzrOo4wHMxkbG+PevXucPHmS5uZmtmzZwiuvvEJqaipKpRKn04nD4cA1w2Bb7Nwzcc8YO2eOO8oZCvTSeLbQsaTxaLExdiYul0tuu9i766vgcDiwe2u7SseSrn/usee+Y91uNxUVFXzyySd0dXVx+PBh9u3bh06nQ+GNZnrUa5P60OPxzIowlXB5bYTh4WF0Op1cH3xuu+8rj9VQZcaqcX9/P42NjbS2tjI8PIzZbEblDZ+Ki4tj2bJlJCcnExoa+q2vRjwKLm/Zl4aGBoxGoxxeq/YmS3d2dnLp0iXy8/MxGAz88Ic/ZP/+/URFRT3yj6W3t5eTJ09y+fJl4uLiePnll1m7di0ul4uSkhJ+97vfUVlZyVtvvcWbb76Jnzcs+ZsiGarvvfceSq+heujQIQK+pTqGAoFA8F3A4/EwOTnJ4OAgQ0NDTE9Po1Kp5JDasLCwh4Zlebyr95LYnNlsRqFQEBERQVRU1NzmAoHge4LVKzA2ODgoR+eFeKtCLBQl91WRImVcLheBgYFyigQzIktmqm4vhlqtlr2oj2KwmM1miouLKSgoYGhoCKVSSWJiIvv27WPJkiXgnSf29/fPikqU7nsh42kxzGaz7GUdHx/HbrfLEX5S5N9CC58Wi0WO5ljo/pVKJXq9nvDw8Ad6jh8FKYqmv7+fiYkJ1Go1BoNBTjlc6PrmYrfbKS0tJT8/H6VSyerVq+VIGqVSSWhoKJGRkXK0ytz+c3sjcoaGhuSSkx6Ph9DQUMLDw4mKipJtAKdXYPH69esolUr27t0rC7n+R+CxGqoul4uxsTFqamq4c+cOpaWlDA8Po/YW6nU6nZjNZtRqNZmZmWzevJn169eTmJj4SDlK3yZ2u53m5mbOnDlDSUkJOp2OiIgINBoNFm+9vc7OTvR6Pbt27eKpp56alyP0MDo7O/nggw84ceIESUlJvPPOO2zduhWn08mtW7f4+7//e4qLi/n5z3/Of/pP/2leuMfXZXh4mNOnT/O73/0OlUrFu+++y4EDB4ShKhAIvjc4nU4GBwe5e/cuFRUVcnkBhUJBYGAgaWlprFu3ThYFWQi73U5fXx+tra00NDTIYb0hISHs3LmTHTt2zN1FIBD8O8fjFSurr6/n3r17NDQ0MDY2Bt7SLtnZ2bL6+qMYhgsxNTXF3bt3KS4uxul0kpOTIwvfKRQKBgcHuXXrFhUVFVgslrm7z0Kn05GVlcWmTZuIiYlB+QCPr9vtpr6+nk8++YSWlhbWrl0rlyGLjo5Gq9XS1tbG7du3qa2tZXx8HICQkBCys7PZsGED6enpD0w/wXueoaEhqqqqqKqqoqOjA6PRiN1ux9fXl+joaLKzs1m/fj3JycnzjM3W1lYKCgpoamqSS9DMRKPRkJmZyZNPPklERMQDr+VBTE1NUV1dTVFREY2NjYyPj6NSqeTc3E2bNsl6DQ/C4XDQ09NDVVWV7ICTqmp4PB75nbNlyxYyMzMJnKGa7/SW26yoqKCkpISenh7MZjNutxutVkt8fDxbtmwhJyeH4OBglEolTU1NfPjhh1RVVbF3715efPHFRbUrvm88FjElvD/a8fFxiouLOXnyJDdv3sRsNsuCHzk5OaSkpBAQEMDo6CjNzc20t7cDEBYWRlBQ0ANDAL5tJM/v8PAwfX19DA0NMTg4KNebczqdpKWlsXfvXnbt2kVqauqi+QeLMTExQUVFBQ0NDQQHB7N27VoSExNxu910dXVx9+5dent72bhxIxs2bPhKoQMPwuFwMDo6yuTkJDExMbJ65aOsGgkEAsF3HZe3FM7Jkyf55JNPaG1tRa1WExAQICts1tTUMDw8jMFbl2/m+Ofx1tmurq7m7NmznDlzhnv37tHT08PExAQ+Pj6kpaWRnp4+67wCgeDfPyaTifLyck6cOMH169dlr6NUBqaurg673U50dPQjCffMxeFwUFlZyaeffsqZM2dobm4mMDCQJUuWYDAYABgdHaWoqIiSkhK6u7sZGhqatQ0ODtLa2kplZSWdnZ0EBQWRkZGBwWB4oKE6OTnJtWvX5GjAffv2sWrVKqKjo1GpVDQ2NnL06FEuXLjA0NAQGo0Gq9VKa2srTU1N2Gw2wsLCCPWqui+G3W7nzp07HD9+nJKSElkbxmazMTIyIpd9dDgcxMfHz1IQ9nirUJw4cYI7d+7Q09MjezylbWhoCK1Wy4oVK2QNmq+KlML3+eefc+vWLcbHx1EqlZhMJpqbm6mvr8fpdBIbGzvr+hbD6K03m5+fT0tLCwqFAp1Oh9PppL29nZKSEoxGI9HR0XK0qEKhYGhoiOvXr3Ps2DHKy8tlDztAV1cX9+/fp7+/n/DwcMLDw/Hz88PX15fJyUkqKioYGBggNTVV/g6/7zw2Q9VsNlNVVcWpU6e4e/cuwcHBPPXUUzzzzDNs2bKFFStWkJWVJddzGhsbo6GhgYGBAfR6PbGxsXKs9x8DpVfMKCIigtTUVDIyMkhPTycjI4OcnBw2btzIjh07WLduHXFxcV/ZSMVrqFZWVi5oqHZ3dz82Q1XpVU1LTExkxYoVshrwwx5CgUAg+PeAxWLh/v37/PKXv6Srq4t9+/Zx4MABtmzZQnZ2NoGBgXLdQR8fHzIzM2d5Va1WK8XFxXz44Ydcu3aNyclJUlJS2LBhA5s2bWLNmjUsXbqU4ODgWecVfH+Q8v0U3jy1PxZSHh9eZdKH/V3w7eJyuWhubpbrhup0Ovbu3csTTzxBdnY2arWahoYGWlpaCA0NJSkp6StFu3k8Hnp6euTj9/b2yiVlJFVvaS6m0WiIjIyUVcalLSsri/T0dFwuF93d3fj6+pKXl0dubu5DjbampibOnDnD0NAQmzZtYvPmzYSHh6NQKOjr6+PUqVOcPXsWrVbL/v372bdvn6yR0traSmdnJ1qtlsTExFlewbk4nU4qKytpb28nPj6erVu3snXrVtasWUNCQgJms5n6+np6enqIi4sjKSlJjpyU0t/y8/MBWLt2rTzmZmRkyFt2djZpaWlotdo5Z380Ojo6+OCDD8jPzycqKoonnniC3bt3yyXA6uvr6ezsJCQkRHZGLYbZbObOnTscO3aMwcFB1q9fz8GDB+V3TmhoKFVVVdTU1BAWFkZycjJ6vR6Xy8X9+/f57LPPaGxsJCcnhyNHjrBt2zZWrlxJTEwMzc3NVFVV4e/vT2pqqizepFar6e7uprq6msDAQJYvX/61bJF/bzwWQ9XlctHX18eFCxe4evUqGo2GQ4cO8cwzz5CRkUFISAg6nY5Ar5R1XFwcWq2Wzs5OWltbcTqdJCQkyPlANpsNp9OJYoZI0kw83mRsu92OyyueMbedy+XCarUyPT2NyWTCZrPh8SZ5K71J6BqNhsDAQCIiIoiNjSUlJYXMzEyWLl1KXFwcwcHBBAQE4Ovri9KbTG2327FYLJjNZsxmMzabbVbC9UweZKg+To+qZKhGRUURHR2NXq//D7EKIxAIvv94PB7GxsY4efIkp0+fZsWKFfzN3/wNa9asIT4+nri4OKKiohgZGaGqqgqA3Nxc4uLiwPt+aWho4De/+Q137twhLi6OI0eOcOTIEXnSkZycTEhIiBg3v6dI6qVSuKfGK6b4uHE4HIyNjWH0Vjfw8daTd7lcmM1mLBbLQwVmBN+MqakpCgoKOH36NA6Hg6eeeorDhw+Tm5tLUlISERERDA4OUlZWhkKhICMjg4iIiAd6FyWkSI0rV65w5swZFN4SKR6Ph4yMDLnWvUqlwsfHRy7huGzZslmGamZmJuHh4XR2dtLe3k5aWhpPPPEES5YseWCanMPh4Pbt21y5cgWDwSDv4+Pjw/T0NCUlJXz22WeMjIzw/PPP8+yzz5KdnU1qaioREREMDw9TU1OD3W4nOTmZ6OjoB+ZFSpEnGzduJC8vj6VLl5KWlkZycjI6nY62tjZaWlrQ6/Xk5OQQ4lVCdzgcFBYWUlZWxpIlS3j22WfZuXOnXJ5H2lJTU7+2k8XlcnH+/HmOHj2KWq3m2Wef5cCBA/L9hoaGMjAwQF1dHTabjZUrVz7QW93X18f58+cpLCwkIyOD119/nfXr15OQkEB8fDzp6em0tbVRXV2Nn58fy5cvJyoqiomJCS5fvsylS5eIioriRz/6Edu3bycpKYnY2FhSU1MZGxujvLwcm81GdnY2cXFx+Pj44O/vz/j4OCUlJVgsFlatWvXAa/y+8Fjuzmq10tzcTHFxMePj46xcuVKuWzo3vl+tVhMWFsa6devYunUrvr6+1NTUUFVVxeDgIH19fZSWllJaWsrg4CDuGcqIElarlc7OTkpLS6mpqZGT1fEOFFarlZ6eHoqKijhz5gxHjx7lyy+/5O7du3R3d8tlAaT209PTdHZ20t3djdvtxuFwUFtby5UrVygrK8NkMuF0OhkZGaGmpoYbN25w+vRpjh07xtmzZyksLKSnp0dWE/tTo/CqXvr5+clS4wKBQPB9wWq10t7ejsPhIDU1lfj4eHQ6HT4+Pvh5a5YmJiai0+mYnp5mamoKvJOX4eFhjh49Sn5+PomJibzxxhs8//zzrF69Wq4JGxAQ8MAJmuDfL263m+HhYW7cuMGXX35JTU0NJpNpbjN5Qdxiscib1WpdUPjlUfB4PBiNRnleUlJSIguq2Gw2enp6aGxslEsfCR4PAwMDVFZWMjIyQnJyMuvWrSMpKYmAgAA5vHbDhg0YDAbq6upobm6eNWd8EHa7naqqKs6dO4fJZGLVqlWkpqbi462XOhOVSkVAQIBcMmzmFhwczPDwMC0tLfj5+ZGTkyPnjT4Io9FIY2MjU1NTxMfHk5iYiL+/Px5vCbTy8nJ6enpIS0tj8+bNJCUlodPp0Ol0LF++nLy8PEJDQ+nq6qKhoUEeNxdCpVKRmprKunXrWLZsGWFhYfKxoqOjyc3NZdmyZSiVSlpaWpicnJT7wOktOelwOIiMjCQxMZGYmBiio6PlLSoqiuDg4EdaIJiLxyuyd/v2bXp7e1m2bBkrV64kOjpa/p6XLVvGhg0b0Gq11NfXy2HPizExMcHQ0BAej4fY2FjZ4yy9c6Sybv7+/hiNRjl3dWpqiv7+fkwmE+Hh4aSnpxMUFISPjw++vr4YDAbS0tLQ6XSMeUteSnaPVqslOTmZmJgYuru7aWxs/M7YGY+Tx2KomkwmWlpa6OrqQqfTyfmoi/3AlEqlXFg8ISEBk8lEa2srvb291NbW8v777/PLX/6S/Pz8eS8Qj8fD4OAgp0+f5v/8n//DsWPH6OrqwuMNmzGbzVRXV/OHP/yB//W//hf//M//zO9+9zt+/etf8/d///d8/PHH1NXVycnrNpuNxsZGPvzwQ/7v//2/5Ofnc+7cOf7+7/+ef/zHf+Ty5ctMTEwwMjLC1atX+fWvf80//MM/8Jvf/Ib33nuPf/qnf+J//+//zYcffkh9fT0Oh2PW9QoEAoHg20XpLXWmUCgwGo2YTKZZi5pWq5WJiQnsdjsBAQHo9Xo83lqElZWVnDx5EqVSyYsvvsj69esJCAjAYrEwPT2NxVtOTfD9xOl00tfXR3FxMUVFRTQ0NMhqpTM3s9lMT08P9+/fp6ioiKKiIqqrqxkaGsJiscxr/7DNarUyNDREeXk5hYWFVFVVyYvsdrud0dFReUIreDxI88eOjg5UKhUpKSnExsbKQjoKhQJ/f39SUlKIjIykp6eH9vb2RzJUpd/VuXPnqKmpITc3l02bNske1K+C0WikuLiYxsZGoqOjWblyJREREQ/1pPX399PR0YGPjw/x8fEEBQXJHnuj0Uh9fT0mk4klS5YQExMzazFOq9WSkJBAbGwsJpOJ7u5uzGbzrOPPRKFQyEaaek4pMpVKJdeGVqvV8xZ47HY74+PjeDwe9Ho9vr6+OJ1OnN6SLd8Ut9tNZ2cnTU1NKJVKMjIy5nmHg4ODSU9PJzw8nImJCRobGx94vxqNBl9fX1wuFxMTE3LtaWY4yCYnJ3G73RgMBlmMSqPRyCKsk5OTGI1G2U7weEvIjY+P43A4MHhrd0u/F4VCQWRkJKmpqUxOTgpD9ZswNTVFd3c3VqtVjkXXzSiUvhC+vr7ExcWRmpqKRqNhYGCAyclJ/P39mZ6eprCwkMLCQgYHB2ft53Q65fxOKURBCs21Wq3U1NTw/vvvc/ToUVwuFzt37uTIkSNs2LABk8nEmTNnOH78uBxy7PGGarS1tVFYWMixY8f49NNPaW5uJigoiPDwcDQaDdPT0/T29uJ0OsnKyuKpp57i4MGDrFixgoGBAT744AOOHj1Kd3f3115xFQgEAsHDCQwMJC8vj8DAQEpKSjh79ix9fX3YvLW7S0tLKSoqAiAnJ4fExER5lb2oqIienh7ZE1BaWsq//uu/8vd///f88z//M+fPn6erq0sYq99T3G43NpuN6elpJicn6ezspLq6mvLycnkrKyujqKiIs2fP8v777/OHP/yB999/n88++4zLly9z//79We0fdautraW/v19eEJk5YZVyZr+NibpgYRxeocnR0VE58mKuuq1SqSQ4OJjQ0FAsFguDg4PzFsLmInnO8vPzuXLlCjExMezdu/eBDpvF8Hg81NbWUlxcDMCKFSvIyMh4pDzNkZERhoaGCAwMJCoqSg4Tlu67v78fpVIpa8LMRbpvp9O54ALgV8HprfKBV0l5Zsjy1NQUU1NT2Gw2BgYGKC8vl9WXJeXgb/IcuN1uOjo6GBsbIygoiMTExHmiWBqNhpCQEEJDQ3G5XPT29j7QoyqFafv4+FBRUcGlS5fo6enBarVitVq5e/cu9+7dQ6VSydE5arWa0NBQMjIyiIyMpK2tjbNnz9La2orFYsFms1FdXc21a9fk0N7ExMRZBnVISAjx8fE4nU56e3v/Qxiq33qOqtvtpq+vjxs3btDd3c3SpUvZsmULcXFxD8y3VCgUWCwWuSyASqUiJyeHtLQ0hoaGqK2tRaFQsHz5clJSUuT9JiYmuH37NteuXcPf35/9+/ezdu1afHx86O3t5cSJE5w5c4aUlBTefvttDh06xNq1a8nJyUGn09HY2Eh3dzcGg0H+QfT29nL//n3q6uoYGxsjPj6el156iWeeeYa8vDy5LlJYWBirV69m+/btbNiwgVWrVpGVlYXHq2A2NjZGeno6SUlJqNXqP1mOqkAgEHxfkVIbQkJC5Aia2tpauru76evr4+7du5w8eZKenh527NjBiy++SHJyMi6Xi87OTj755BPa29vZtGkT1dXVnDp1imvXrnHv3j3KysrkUjeBgYHExMR8ZW+I4LuN5Pmqrq5mdHSUiYkJOjo6qKmpobKyksrKSioqKqisrKS+vp6+vj7Gx8cZHx/HaDTKIbrV1dVy+0fdJAFJgLi4OJYuXUp4eDh2u53h4WFMJhMxMTFCxOsxYTabKSsr4+7du/j6+rJx40YyMzNnGYFSZF5FRQV1dXUkJyezZs0awsLCFh0LLBYLpaWlfPDBB4yMjPDSSy+xd+9eXC4XxcXFdHR0kJKSwqpVq2aJKS2E0WjkzJkzXLt2jYSEBA4ePCiL6DyMiooKCgoKCA0NlUN7Nd6Si7W1teTn5+Nyudi9ezfZ2dnzyi1KpVwaGxsJDQ1l5cqVREVFLXrfiyFFKp49e5aenh727t3L5s2bZUG7zs5Obty4IY/b0nXfvXuX2tpabDYb4eHhX1s4yOVycefOHQoKCggMDGTv3r1yrq6EQqFgbGyMiooKWltbCQ8PZ8eOHYs+e5L3eGpqioaGBurq6ujs7KS/v5/i4mI++ugjurq6eOqppzhy5AhJSUn4+Pig0Wjw9/fHbrfT0tJCdXU17e3tDAwMUF1dzYcffkhZWRlbt27lpZdeIiMjY17KZFdXF3fu3EGv17N582aCgoK+Vr/8e2Hxp+NrIrm8TSYTHo+HgIAA/P39H/ggSmg0GgICAlCpVFitVmw2GwEBAWRmZpKYmEhXVxe1tbWzQmFGR0dpaGjAarXKar16vR6r1UpjYyNlZWVotVoOHjzIzp07iY+PJzIykpSUFDZt2kROTg4mk4mqqir5hYH3Pmw2G6GhoTz11FM899xzbNy4kcTERHx8fNDr9WRmZso5B5JQkVR+JzExkYGBATo7Ox8pTEQgEAgEXw+1Wk1cXBxvvfUWTzzxBN3d3XzxxRf8n//zf/jNb35DUVERcXFxPPHEE2RmZqJSqXA4HHLYn91u5+7duzQ2NrJmzRreffdd/vIv/5LNmzczPj7O8ePH+eijj6iqqhJj+fcUhUKB2+1mYmKC7u5u2tra5K29vZ2uri65xqTCqwzscDgYGRmhs7NzVvtH2drb2+nr65Nz177PE83vKnZvSLfNZkOlUi2o4TEzXFOtVmO327F5xTgXwuFw0NHRwZkzZ2hqamLHjh3s3r37a9e8bGhooKSkBLwicEuXLn1obireBRiTyYTVasXf339WCKnk3XR6Bby0Wu2Cnl6NRiPn09pstnkhu4/KyMgI9+7do62tTS6RKAkp4Q0NXrZsGdu3byc3N5eIiAgcDgfV1dV8/vnn/PKXv+Tjjz+mv79/0X5/EB5v9IzD4UCj0SzqBFKpVLJRaLFYHug9VqvVZGRkcOTIEdavX09/fz/Hjx/nH//xH/n1r39NQUEBqamp7N+/n9TUVNmDrFAoSExM5MCBA+zatQuLxcK5c+f4p3/6J371q19x6dIloqOjOXDggLxoMvNaVd5c5oCAAEwmE1NTUw+8zu8DD7cevyKeOSEr0oD+VZH28fX1JTk5mbS0NCYmJqipqZFFlex2O93d3TQ1NeHj4yOrY6nVaiwWCy0tLXR0dBAcHExwcDCjo6O0t7fT1tZGZ2cnk5OT+Pn5YbPZ6O7uxmg04vHmtrrdbnx8fOSE8vDwcHx9fVGpVCi8qsIajQa3283g4CDl5eVcvXqVM2fOUFxczOTkJBaLhfHxcaxW69d6uAQCgUDwcDweD3a7nY6ODjo7O9HpdGRlZZGRkSHnhLW2tnLz5k1qampwOBw4vIqrw8PD4M3Jevnll/nxj3/M66+/zptvvslf/uVf8vzzz6PT6bh16xbXrl0T4jbfUzweDxqNhoSEBDZu3MiePXvYu3cve/fuZc+ePWzevJmEhARcLpe8+fv7s2zZMnbs2CG3fdRt9+7drF27VvaoiTnCHx+Px4PL5ZLnqkrl/6sAsRCL/X0m7hnCXMXFxSxfvpynn36apKQkVCoVyhlVJqT/fxDj4+Pcv3+fhoYGEhMTWbNmDZGRkfOM6YWQwtklI9zHqyjNnPtWeVWlF7q/mfP3r/v7HB8fp7i4mKtXr2K329m9ezdZWVmzvLexsbEcOXKEv/7rv+bnP/85f/u3f8t/+2//jXfeeYesrCyampr4+OOPKSgoeKCg02JI9+v2VuRY6F4lFAqFbAc8DLPZTG9vL8PDwwT8/+zdZ5Ac55ng+X/5alPtTbX33gDdDe9IAIQhQRiSAAVSIuU1c7szo9HNXcRGzO6N9iJmZ2ZjpZ3QSaOVKFEjUaITARCGIAnvgYZpA7T33tvyPu/DVeW1gyMJEADfX0RGINBZVZlVWVnv85rnCQmhoKCAvLw8YmJi0Gq1dHR0cObMGTo6OmbFAXa7naGhIQYGBlCr1eTm5lJYWEh8fDzBwcEMDQ1x7tw5mpqa5EG/AIW/40Sr1eJwOL4SA2F3/pZ8Bgr/gurAEL3NZrvnQM3lcskZrgI9BkFBQRiNRoqKioiMjKStrY3W1la8Xi9ms5nW1laGhobkfaKjo5H8STKGhoYYHh6ms7OTd999l3/8x3+ctf385z/n9OnTjIyMYDKZsFgscm+RJEno9XqSkpIWnOoQaBQdPXqUn//85/z3//7f+dd//Vd+//vfc/LkSQYHB/H5fHg8HvmGIAiCIHyxJH9egfPnz/Pzn/+c3t5e9uzZw9/+7d/KDZ+9e/ei1Wo5cuQI7733Hi0tLXi9XqxWK9PT0wQFBbFjxw42bdpETk4OUVFRxMbGUlJSwtatW1m0aBFjY2PU1NTIga3wZJH8gWpWVhbPPPMMO3fuZMeOHezYsYOdO3eyc+dOtm7dyrp161izZg1r165l/fr1bNu2Td7vXrfAc69Zswaj0YjCP5orPFyBAE6tVs8K3uby+as/+Hy+O47ImUwmbty4walTp/B6vaxevZqUlBSsVisTExNMTU1h9ydnCwxkmEymBUdoJUmSq2d4PB4WLVpEfn7+Pa1NZc4xBwLOwDEHBlqU/sRKt0taFPhbIDgKPOZeWa1WqqurOXToEF1dXVRUVLB161bi4+NnvX9hYWHk5uayePFiysrKWLZsGRs2bOBrX/sar732GoWFhfT19cnt9YWO9U4UCoU80BQYRFtI4D0L7L/QZxwwNTXF2bNn2bdvH+Pj4zz//PPyb87/+X/+n3z7299GpVJx8OBB/vznP9PR0SGPcldWVvLuu+/S1tbGU089xQ9/+EP+9m//lv/j//g/+Iu/+AuioqI4fvw4f/zjH2lsbJy3VjbQyRHoMLvd+Twp7v2Ku0dKpVJOsY0/9ffo6KicJOB2JH9ZmKGhIdxuN1FRUURFRaHT6eQU4enp6XR3d1NdXY3dbmd8fJzm5mZ8Ph+FhYVkZmYSFBSEz+eTpx8HvqgWi4Xx8XFGR0flzWQyERERwaJFiygtLSUqKkq+MBUKBSp/prKZi77xB6ltbW0cOHCAP/zhD1y+fBmfz0d2djYVFRVyRrbAeQmCIAgPhtdft3vfvn1cv36dZcuW8corr7B+/XqWL1/O5s2bee2113juuedQKpWcOXOGy5cvI/lHEwKdkhUVFURFRcmNMaVSiV6vJyUlRU7yNzo6KtfaFJ4MKpWKsLAwYmNjiYmJISUlhfT09FlbWloaubm5rF27lj179vDyyy/z8ssvs337dpYuXUpWVta8x9xpS0tLIy0tjYyMDJKTk4mJiSEyMvKegxDhi6HVajEYDOj1enk67Ny2quRfzmY2m3G73QQFBS24VtLtdtPX18f58+e5efMmJpOJhoYG3n33XX71q1/xq1/9infeeYdbt24xMTHBzZs3ef/99zlw4MC8UiiSPxnTpUuXuHnzJikpKVRUVBAfH7/gFN2FBILwQHA2M0DTaDQYDAY0Gs2sc5srMGKnUCgICQkhNDT0nl/farVSVVXF/v37qa2tJTs7m127ds0bTcUfN6jVarRarbwFBweTkJDA0qVLWbp0KRqNhvr6+lnlJ++VQqEgMjISnU6H0+nE6XQu+BxutxuLxQJAeHj4Hc+1tbWVY8eO0d7eTlFREbt372bDhg0sX76cTZs28e1vf5tt27bhdDo5duwYNTU1mM1menp6OHnyJNXV1SQnJ/O1r32NzZs3s3z5ctavX883vvEN9uzZg06nk3MlTE5OzurICnQgqNVq1HMyLD+JvvBAVaFQyEkn1Go1vb29dHZ23nW43uFw0NvbK2ffTUhIIDo6GrVajU6nIy0tjYKCApxOJw0NDfT399Pd3U1bW5s8zWtmuu5AQ0OtVpORkcH27dt5/fXX+eY3vylv3/72t/nBD37Af/gP/4Hdu3eTmZk5q7dobi9UwOTkJJWVlZw4cYKRkRGWLFnCN77xDb75zW+yd+9etm7dSlpa2qzHCIIgCF8syb92qquri8rKStxuN5s2bSIvL09ugBoMBjnIyMrKore3l9raWjweD2FhYXKpmtv94Ot0OkJDQ9FoNHIDQXhyqFQqEhISePrpp9myZQulpaVyGY3ApvGvUYyPjyc/P5+CggLy8/PJzMyUG8Az97+XTavVEhcXx/Lly9myZQtLliwhOjr6vkashM9Hp9MRERGBwWDA5XIxMTExb/QqMNAxOTmJSqUiKiqKkJCQeZ+T1+uVazTr9XqUSiV1dXWcOHGC48ePc+zYMS5cuEBvby8Wi4Xu7m4uX77M1atXGRwcnBUo+nw+WltbuXz5MjabjUWLFlFQUDAvI/GdaPw5X7RaLW63G4fDIQc7Go2GqKgoOZ/L2NgYDodj7lNgNpuZmppCqVQSHh6+4HkvJBCk7tu3j8rKShISEti1axcrV668r8Q/arWa8PBwEhMT0Wq1TE9P3/MMzZmUSiVGo5Hg4GBMJpN8vjODP5/Ph9VqZXJyEoW/DIx2RrKlmbxeL+3t7dy6dQu1Ws3ixYvl/Dh6vZ7Q0FBycnLYsmULycnJcsK1yclJOjs7qa+vR5IkSkpKKC4uJiIiAr1eT0hICOnp6WzZsoXc3FwmJydpampidHRUDqxnDsQFXutePpPH2QM5u5CQEDnBUCDTbUdHx4I9GPgbGyMjI9y4cYO+vj65nlFg8blKpSIuLo7CwkJiYmLo7OykurqaxsZGRkdHSU1NJScnB4PBAP6LUq/XE+Ev1B4cHExBQQHPPPMMmzZtmrdt2LCBsrIyoqOj7/oF8vl8jI2NUVdXx9DQEOnp6TzzzDOsXbuWwsJCMjIyiIuLQ6/X3/eXSRAEQbg/LpeLsbExRkdHUSqVJCcno9frZ82O0el0xMfHyyUmJiYmUCgUxMXFkZKSgtufAGWhIDTQy+5yudDr9WLU6wmjVCqJjIxkyZIlPP3002RnZ88b8WHGLCudTidv9zsVciaFQkFYWBilpaWsW7eOoqIiuQ0jPBwqlYro6GhiY2Ox2+309/djNptntd28Xi8jIyOMj4/LI+7BwcHzPvdAO3XDhg28/vrrvPrqq2zbtm3WuuTAOufQ0FBSU1NZuXIly5Ytm1XDNDC78OLFi9y8eZPk5GTKy8sxGo3yPvdCrVZjMBgIDg7GbrfPGjVV+8ukpKSkoFQq6e3tnXfePv9625GREfR6vRzo3a2NPDdIjY+PZ+fOnWzYsGHBZXR3EwjMJEnCYDDMmpIr+euO2u12HP5ETwu1u5VKJenp6cTGxmI2m+nu7p43Smmz2RgcHJRLFQVmaC7E4/EwOTnJ5OQkan/G+Zm/OfhH61NTU4mMjMTtdmP2l9+Znp6WHxcVFTVvdF7tTwwYWLtuNptnrUOd+VxhYWEYDIZ51+KT5oGcXVBQEDk5OVRUVBAcHExVVRWnT5+mvb19Xs0fr9fL8PCwnDra7XZTWlpKSUkJ4eHhMGM6cW5uLrm5uQwODnLq1Clu3LiBwl+yZm6R5uDgYNLS0jAajQwODsojtQaDQe5FD2yBL7N6gWH+uRe95F8PFZh+EBsbS2JiIuHh4fIU4bGxMcbHx+/6hRYEQRA+H5U/W6dOp8PnL+w+dxqbz+fDZDJhNpsJCgoiOjpaHtEqKSnB7XZz/vx5BgcHZwWrHn+tus7OTpRKJSkpKcTExMx6buHxp9FoiIiIICYmhhB/5YGHQa1WExYWRkxMDAaD4aG9rvD/CYycZWVloVAoaG9vp6OjA6u/soTX62VyclIemMjMzCQrK4ugoCC8Xi9jY2M0NzfT2tqKxWLBaDSyYcMGvv71r/Paa6/x+uuvz9p27dpFfn4+kZGRFBUVsWPHDp599lkyMzPl9qvH46Gjo4OLFy9iMplYvHgxhYWFhIaG3lebUqFQEB4eTnh4OBaLhbGxMbn9rVKpiIyMlJ+3qamJjo6OWQHR2NiYXD4pJiaG7OxsQkND8Xq9TE1N0dzcTGNjI1NTU3LAFyjjc/DgQaqrq0lKSmLXrl1s2rRJriM6VyDYXGidrMPhoLu7m4aGBlwuF3l5eURGRsqB2eTkJLW1tZw5c4b6+npMJtO858D/XiQkJFBUVCRPIe7p6ZFHzyVJYnh4mFu3bjE1NUVycjK5ublyh9XY2BgNDQ20tbVhMpnAPxqv0+nkEemF1hmPjo5iNpvl+0tQUBA6nQ6tPxHS2NiYnPV7psB6ZkmS5JHswGdvtVoZHR1FoVAQGxt7T50Hj7svvI4q/sBSp9OhVCoZHR2lvb2d4eFh3G43Sv8CYJvNxuTkJB0dHZw7d45Dhw7R0tJCbm4uO/y1TsPCwuQPQOHvzRwaGuL69esMDAwwOTmJ0Wjk2WefJT8/f1YvqMKfnGBgYICmpiZMJhNaf9Yzh8OBxWJhYmKCoaEheUpHYIpEb28vlZWVDA0NsWTJEpYvXz6rt2R0dJSamhq6u7sxGAxkZGTIN4O2tjZOnDjB+fPn8Xg8lJeXU1FRgcFgwGQyybXT5tZRDUwDEXVUBUEQ7k3g/uh0OmlsbKS9vV0eVdVqtfJ0vK6uLk6cOMHFixeJiori+eefp7y8HI2/pmB1dTWDg4PyLBwAi8VCR0cHx44d4/z580RHR8u/TfczsiE8HhS3WerzoM19Xck/nX3UX0c1ISHhtrUchc9Po9FgtVppa2ujv78fpVIpT/0eGxvj2rVrHD58mJGRETZt2sTGjRuJjo7GbDZTWVnJ0aNHaWpqQqvVYjQa5anEcwdEwsLCcDqd1NTU0NPTQ35+PmvWrCEtLU1uX0qSxNTUFJ988glHjx4lMjKSF198kYqKivua9htgs9loaGigt7eXpKQkCgoKCPPXLlUqlXg8HlpbW2lvb5dH+NRqNVNTU1y+fJmjR48yOjrKihUreOaZZ0hMTMRut1NVVcXBgwe5du0aISEhcjmZ6upq9u3bx+nTp5EkiYqKCoqKilCpVIyPjzM8PMzw8DDj4+MolUq0Wi12u53m5ma5EofdbsdisTAyMkJdXR0ff/wx58+fJyQkhJdeeoklS5bIo5C3bt3iwIEDch3cjIyMBQN6hb/WtsNftrK/v5/g4GAiIiJQKBSMjY1x+fJlPv74YywWizz7MiIiAq/Xy4kTJzhy5AjNzc1yx5LZbKa9vZ3e3l4Auc5rYDCrt7eXQ4cOce7cOYxGI9u2baO4uBiPx0NnZydtbW14PB5iYmLk87Hb7QwODnL8+HE+/fRTNBoN27Ztk2MIhUIhr3Ht7+9n3bp1LFmyRB4ke1I9kEBV4c/8GxYWhk6nkxsKra2tcj2ytrY2qqqqOHnyJKdPn2ZgYICcnBx27NjBU089NS8Ft9KfpcxisXDz5k1aW1tRKpWsWbOGjRs3Lri/3l8TK9Dr1dbWRl9fHx0dHTQ1NVFVVcXly5fp6ekhIiKC2NhYvF7vXQNVt7/+XltbG4ODg3LQ3dTUJBcoHh4exuPxUFpaSnl5OWFhYXcMVHt6ekSgKgiCcJ8CDR6Ajo4O2tvbGR8fZ3JyksHBQXmdWGDGzsaNG3n++eeJj49H408qYrPZ5Abb2NgYQ0NDNDQ0cPr0ac6fP4/X62XTpk1s27ZtXsZKQfgiiUD14QqsF7bZbHR1ddHZ2cno6ChDQ0NUV1dz/Phx2tvbWbx4Mbt27aKwsBCdTsfAwAAff/wxH374IR0dHURHR5OVlSWvwVxom5iY4OrVq3R1dZGRkUF5ebk8xRP/Mobm5mbef/99GhoaWL9+Pc8///xtRyPvRqVS0dXVRUNDA6GhoRQUFMjroAMzUVwuF52dnbS0tDAxMcHo6CjV1dUcO3aMtrY2CgoKeP755yktLSUkJITx8XE++eQT/vznP1NdXU1iYiL5+fkMDg7y5z//mY8//pju7m65Pd7b20t1dTVXr17l2rVrXL9+nbq6OsLCwoiPj2dsbIzDhw9z7Ngx6uvraW9vp7GxUc4DU1lZiVqtZvPmzTz//PMkJCSg8ifBO3/+PB9++CFjY2OUlpZSXFx824BeqVRiMBiYnp6mo6ODnp4exsfH6e/v59q1a5w8eZLe3l5KS0vZvXs3OTk5cnD7+9//noMHD9LR0UFqaiqZmZlERETg9Je27OnpYXBwkMnJSYaHh6mvr+fYsWMcP34cQK6ZGpg+7XK5GBgYoLu7m97eXib9ZdKam5s5ffo0H330ESaTiY0bN/Lcc8+RlpaGRqPB4/Fw69YtPv74YzQaDTt37iQrK+szXRuPkwcSqOIPVvV6PXFxcXIdu6mpKXkaVXNzMy0tLQwNDaHT6Vi6dCk7d+5k3bp1s+brzzRzuH9iYoKsrCw2bdrEokWL5vWiBILl6OhooqKicLlcDA8P09/fLzdmAjekwFTlhIQEAMbHx+nq6kKSJJYtW8bixYvRarXyzUar1aLRaLDZbIyNjdHX10dXVxd9fX04nU5ycnKIi4tDkiSKi4spKSnBYDDI0xgmJibkdQdJSUnya3Z2duL1pzQvKytDfZvkHoIgCML/RzFjDWpwcDDT09MMDQ3R2dlJU1OTPM3LYDCwfv16duzYQUFBARr/+sLQ0FASExPx+Xz09fXJSfqampro7e0lLCyMDRs2sGPHDvLy8hb8bRKEL4oIVB8uhX+pWHh4OJI/X0rgHtDe3o7ZbJazuq5YsYKwsDCUSqWc1be1tRW9Xk9JSQmFhYXyiOVCAqNwNpuN/Px8SkpKZk1ldTgc3Lp1ixs3bhAWFsYLL7zAkiVLPvP0Tq1Wy8TEBA0NDVitVtLS0khOTpZnPOr1ejlwHRwclM+7ubkZk8lEfn4+27dvZ/Xq1cTExKBUKrFarTQ0NNDY2IjP52P58uWUlJTIAzxjY2OE+EtLut3uedU2RkdHmZ6eJi8vj4yMDKxWK7W1tTQ0NNDe3k5rayvNzc20t7czPT2N0Whk8+bN7Nixg5ycHHn00OFwcPLkSS5evEhKSgrPPPMM2dnZcqflQoKDg4mKipLXHQcG0Nrb23E4HJSWlrJz506WLVsmrxf3eDxcvnyZ9vZ2QkJCWLZsGbm5uURHR8trU81mM4ODg/JvTkNDAx0dHYSGhrJ161Z27Nghr33X6/VERkYSEhIij6AGOgrq6+tpaWkB4Omnn+bFF1+ksLBQDr4nJyc5d+4cly5doqCggJ07d95Tbp3HnUKaOzn6C+bz+TCbzQwMDNDW1kZbWxsDAwPYbDb0ej0JCQlkZ2eTk5NDUlLSHddpBIbUGxoaaGhoICIigpKSElJSUm57cQamfvX09MjTCyb95QUMBgNGo5GsrCw5eZPP52N4eJi6ujrGx8cpKCiguLh41vNL/sXu7e3t1NTU0NbWhsvlIi4ujvz8fHJychgfH6ejo4O0tDSKi4sJDw/HarXS0tJCZ2cnYWFhFBUVYTQakSSJwcFBbt68yejoKKWlpZSWlj7xvSSCIAhflMCascbGRnm6m9VqRafTkZSURF5eHnl5eSQmJs5aJiJJEi6Xi76+Pm7evCkn6QOIj4+nsLBQzoMw83GC8CD4fD6mp6epr69nZGSE8vJy0tPT5+4mfMEcDod8D6ivr2diYgK9Xk96ejqLFi0iLy+P8PBwOai0WCxUV1dz7do1tFoty5Yto6ioSF46sJCpqSnq6uoYHBwkKSmJ/Px8IiIi5Oe02+00NTXR2NiITqejoqKClJSU27aJ70VzczNvvPEGN27cYOPGjbz66qukp6ejVCqR/OtDBwcHqamp4datW4yOjqLT6UhPT6e0tFReFxpoj9psNurr6zl37hwul4tNmzZRVFTEwMAAt27duqfyMTqdjvLycrKzs+WpsE1NTXR2djIyMoLL5SIkJITk5GTy8vLIzc3FaDTKA0YAfX19/Pf//t85ceIEO3bs4Nvf/vY9jS46nU56enqora2lsbGR8fFxgoODycrKoqSkhOzs7Fmfidfr5fz581y8eJGwsDDWrVsnr191u92MjIzIHZvd3d3YbDY0Go38+ebn55OQkIBuRhIoj8cjxwiNjY10dHRgNptR+RNy5eXlyb85QUFBKJVKfD4f1dXV/PrXv6a+vp7XX3+dvXv33rFj5EnxwANV/A0Br9eL0+nEarVis9nweDyo/HVKQ0JC5Gm6d+sZCPQ22u12VCoVQUFB9zTy6PV6sdvtWK1WeQG1RqMhKCgIvV6P1r9+VZIkPB6PnEFMp9PNmvYbEPiCWywWLBYLXq8Xvb8UQlBQEC6XC4fDgVarlc/N5/PhdDpxuVxyb5ZGo5Ff0263y8+z0GsKgiAId+Z0OjGbzVj9dbQDvzMGf7maQANkLp/Ph91ul0sg4E8MGLinf57GoiDcKxGofnm8Xi9Wq1XOqqpSqQgNDSU0NHRWkMSMgROLxYLCX5bxTvcX/M/vcDjweDxoNBp0Ot2s+4rPn+E28NpBQUGfewaH3W7no48+4o9//CPBwcG8+uqrrF27lrAZOWB8Ph82m02+980875kBFv7zdjgccrKfwKiiy+XC6XTiWSBz+lwKhYKgoCD5PQ20f61WKw5/2Ri1Wk1wcLB8DDPfV0mSuHz5Mv/8z/+MxWLhO9/5Dtu2bZPXnN5N4HM2mUy4XC7UajWhoaGE+Mv5zH0Oi8XC9PQ0an/ys5ntc5/Ph8vlwmKxyL85Sn8C2MDyx4WuiUAMEbjeXC4XCv/o/tzfHMm/dnnfvn288847pKen88Mf/pDCwsK7BuZPgocSqAqCIAiCIAh3JgJV4YvW1dXF22+/zaVLl6ioqGDv3r3yGszHkc/n47333uO3v/0tpaWlvP766xQWFt52ZuXjzuv1cu3aNd58802GhobYu3cvzz///FdiNJUHuUZVEARBEARBuHeBWWNijarwRQkJCSEqKorIyEgSExNJTU2dNY35cSP5l9/FxcWxdu1a8vPzP/M63sdBYEQVYMmSJTz11FNERUU9sec7lxhRFQRBEARBeASIEVXhQQgsvcOfVGjulN7HSWDatdPplJfvPa5B972QJAmbzYbNZkOr1RIaGvqVWory5H6ygiAIgiAIgvAVp9PpiIqKIioq6rHPgaJQKAgNDSU6Oprg4OAnOkjFf74hISHExsYSHh7+lQpSEYGqIAiCIAiCIAiC8KgRgaogCIIgCIIgCILwSBGBqiAIgiAIgiAIgvBIeWiBaqBmkMlkYmxsjOnpaVwu19zdBEEQBEEQBEEQhK+4hxaout1uOjs7OXjwIL/85S959913aWxsxOfzzd1VEARBEARBEARB+Ap7KIFqoOZRbW0t7777Lr/97W/5/e9/z4ULF3A4HHN3FwRBEARBEARBEL7CHkqg6vV6GR8fp76+nra2NsxmM+3t7VRXVzM8PIzX6537EEEQBEEQBEEQBOEr6qEEqi6Xi6GhIbq6utBqtRQXFxMaGkpLSwuNjY243e65DxEEQRAEQRAEQRC+oh54oCpJEna7na6uLvr7+0lISGDdunXk5OTQ29tLXV0dVqsVSZLmPlQmSRIul4vp6WkGBwfp6+tjbGwMu92Oz+fD5XJhs9lwOBwLjs76fD7sdjujo6P09fXR39/P5OQkTqfzjq8rCIIgCIIgCIIgPHyqH//4xz+e+59fJJ/Px+DgIKdOneLGjRsUFBSwefNmrFYrlZWVREZGsnjxYiIjI1GpVHMfjsfjYXp6mpaWFq5evcqlS5eoqqqip6cHp9MJQH9/P62trdhsNkJCQtDpdDAjwB0aGqK2tpZLly5RWVlJQ0MDg4ODuN1udDodOp0OpfKBx+yCIAiCIAi3JUkSTqeT0dFRrFYrCQkJREREzN1NEAThK+GBB6pOp5OmpiaOHTvG8PAw69evZ8OGDZhMJi5evIgkSRQWFpKSkoJWq531WK/Xy9jYGOfPn+ett97i4MGD1NbW0tLSQk1NDS0tLYyNjXHlyhVOnDiBzWYjPT2dqKgoJEnC4XDQ1tbG4cOHefvtt7l8+TIdHR00NDRw/fp1Ojo60Gg0xMTEEBISgkKhmPX6giAIgiAID4sIVAVBEP5/D3wY0WKx0NbWxsDAAHFxceTm5hIXF0dGRga5ubmMjo7S3Nw8b/qvJElMTU1x4cIFfv/733PmzBn0ej1PPfUUO3fuZM2aNTidTg4fPsyRI0eoq6tjfHxcXu/qdrvp7u7mwIEDvPPOO5hMJtasWcPu3bvZtm0bSUlJVFdX8/7771NZWYnJZJpx1IIgCIIgCIIgCMKX5YEGqj6fj+npaZqbmxkfHyc9PZ2MjAy0Wi2pqamUlpZiMploaGhgeHh4VlIlh8NBU1MTR48epaamhoKCAv7jf/yP/O3f/i3f/e53+Zu/+Ru++93vkpKSwuTkJHa7HaVSiUKhQJIkTCYTly5d4tNPP0Wv1/P666/z13/917zyyit897vf5Qc/+AFlZWV0dnZy7tw5ent7RU1XQRAEQRAEQRCER8ADDVQdDgc9PT10dHSgUqkoKSkhMzMTpVKJ0Whk8eLFBAcH09bWRmdnp7zmFMBkMnHz5k3q6+uJioriueeeY+vWraSmphIfH09KSgqrV69my5YtJCcno1arAVAoFLjdbnp7e7l69SpjY2M8/fTT7Nixg5SUFGJiYoiPj6eiooKnnnoKvV5PQ0MD3d3duFyuGUcvCIIgCIIgCIIgfBkeaKBqsVhobW1laGiI8PBwYmNj8Xq9TE1N4XA4iImJISUlhfHxcVpaWjCbzUiShM/nw2Qy0d3djclkIiMjg5KSEsLDw2c9f3h4ODk5OSQmJsoJlAA5y3CgHE5MTAxOp5O+vj55m5ycRKvVotPpmJ6eZmhoCKvVOuv5BUEQBEEQBEEQhIfvgQWqgWm/HR0dDAwM0NPTw/vvv8//9X/9X/zn//yf+Yd/+Af+8Ic/0Nvby/DwMHV1dfL0X6/Xi8lkYnx8HI/HQ2xsLDExMXNfApVKhV6vn5e11+VyMTY2xtjYGH19ffzxj3/kr/7qr/gP/+E/yNsPf/hDfvGLX9DY2IjZbMZkMuFwOGY9vyAIgiAIgiAIgvDwPbBA1eFw0N3dTVtbG2azGZ/Px8DAAFVVVVRVVVFdXU1XV5ec4a6zs5Oenh4cDodcG9XpdOLz+dBqtfMyAs80N1tvoG6q0+lEo9Gg0WhQKBQolUp5U6lUxMTEsGTJElavXk1GRgZ6vX7W8wiCIAiCIAiCIAgP3wMLVAPZfgcHBzEajWzfvp3vf//7fOtb35K373znO+zevZvMzEzGx8dpamrCZDKhUCjk+qYKhQKHw3Hb0c7AVOGZGYPxj7bqdDoSEhJ47rnn+Ou//ut52w9/+EN+9KMf8Z3vfIclS5YQGho66zkEQRAEQRAEQRCEh++BBKqB+qetra1YLBYKCgrYtm0bO3fuZMeOHezcuVPetm3bRklJCRaLhbq6OoaGhpAkCYPBQHR0NGq1msHBQYaGhua+DA6Hg/Hxcaanp/F6vfL/a7VaoqKiMBgMSJJEdHQ0FRUVrFq1at62cuVKFi9eTEJCwh1HbQVBEARBEARBEISH44EEqg6Hg97eXlpbW/F6veTl5ZGfn09cXNysLT4+nuzsbIqKitBoNHR2dtLZ2Yndbic8PJzMzEwiIyPp6OjgypUr9PT04PF4APB4PHR3d1NZWUlvb++sjMF6vZ7U1FRSUlIwm83cunWL3t5e1Go1QUFB8zadTodarZ43hVgQBEEQBEEQBEF4+FQ//vGPfzz3Pz+vqakpLl26xMWLFwkODmbz5s2Ul5ej1+tRKBSzNrVaLQeTk5OTGI1G8vLyiIqKAmBkZITm5maGhobkOqvT09M0NTVx8uRJzp07R3d3NxqNhuLiYsrKyoiNjUWpVGIymWhra6O7u1ter+p2uzGbzUxMTDAwMMDg4CAej0cOVgVBEARBEL4Mgbwdo6OjWK1WEhISiIiImLubIAjCV8IXHqj6fD56e3v55JNPaGlpIT8/n02bNpGRkTErM2+ASqXC6XTS3NxMW1sbWq2WgoICkpOTCQ0NRafTYTab6ezspLW1lba2Nurq6rh69Sp9fX1oNBrsdjtKpZLCwkIWL15MbGwsWq2W4OBg3G43PT09NDc3097eTltbG7W1tdy4cYOLFy/S1NSERqPBaDQSHBw89/AEQRAEQRAeChGoCoIg/P++8EDV6/UyPDxMQ0MDWq2W1atXs3TpUnmEdC6FQoEkSVitViwWC1FRURQUFJCYmEhoaChRUVHExsai1+txOp1YrVasVit6vZ4lS5aQn5/P0NAQNpuNoqIiysrKiIqKQq1WExYWRnx8PKGhoTgcDsbGxhgcHKSnp4ehoSGmp6fR6/VkZWWRmpoqAlVBEARBEL40IlAVBEH4/ymkuelyPyefz8fY2BhNTU04HA5SU1NJS0sjKCho7q4yp9NJb28vHR0dqFQqsrKySExMRKvV4vV6sVqtDA0N0dfXJ2cFjo6OJikpiZaWFn72s58xNDTEK6+8wt69e0lOToYZN/yxsTG6urro7e1lamoKl8uFXq8nIiICo9FIeno6RqMRnU4399AEQRAEQRAeikAN+vr6ekZGRigvLyc9PX3uboIgCF8JX3igij/RkcvlAkCtVst1TG9HkiQ8Ho+8BlWj0cjJjSRJkkvQuN1uvF4vCoUClUqF1Wrl8OHD/PKXv0StVvOXf/mXPP/880RGRs56/kBdVpfLhdvtRpIklEqlfGwajQaVSnXHYxQEQRAEQXiQRKAqPAhutxubzYYkSQQFBaHVakWb9zEhSRJ2ux2Hw4FGoyEkJGTBpZRPqgcSqH5RPB4PFosFh8OBVqtFp9OhVCrlkdK6ujr+/d//nfPnz1NeXs5//I//keXLl88qM+P1enG73bhcLjweD2q1muDg4FmJkwKBssvlmlXmZiaFQoFWqxVfbkEQhMeI2+3G6XQiSRIajQatViv/yAd+S5xO513v64Hkf4HfIUF4EESg+uUJDGrY7XbcbjcKhQKNRvOZAjuPx4PT6bxrm1Kj0dz2fuL1euXnmHvvuh9er5fOzk4aGhrkxKMJCQmz2sFOpxObzfa5zzvwHjqdTtxuNz6fD6VSiVarJSgo6LYVNiRJmvU4r9eLUqmUj+NuA16fReAzmvnbcL+v4fP5cDqdOBwOPB6PPBCm0+kIDg5GpVLNfcg8Xq8Xh8OBz+db8JrweDy0trZSX1+PwWCgoqKCqKioz3QtPI4e6UB1amqKq1evUltbS0hICKmpqRgMBlwuF729vZw7d46LFy8SHR3NN77xDXbt2kVSUhLM+OAnJibo7e2lr6+PyclJEhISWLFiBTExMfIF5HK5GBgYoLm5mbGxMRT+jMQBgR6onJwcsrKy7jiNWRAEQXg0eDweOjs7aWlpwW63k5aWRn5+vlxj22azUVdXJyfVuxOtVktycjIlJSWEhITM/bMgfCFEoPrl8Hq9TExM0NLSQmNjIyMjIygUCoxGI6WlpeTk5BAaGnpPwYHH45FztYyOjoI/MA3w+XyEhISQkZFBZmYmoaGh8/7udDoZHBykra0Nk8lEZmamfAz3G0wNDw9z4MABzpw5Q1FREXv27CE7Oxu1Wo3P58NqtdLQ0MCtW7cYHh6Wz7ukpITs7GzCwsLuGnBJkoTb7WZ8fJyOjg7a29sZGRnB4XAQHBxMcnIyxcXFcj6Yme+j2+1menqazs5O2tra5LwzOp0Oo9FIYWEhWVlZGAyGe3r/7yYQH/T19dHe3o7b7SYrK4vs7Gz0ev3c3RcU6OQcGxujra2N9vZ2xsbGcLlccrxSUVFBQkICOp1uwc/M5/Nht9sZHR2lsbERk8lEXl4eeXl5cpWUwH5Xr17l97//PSaTiVdffZX169d/ZfLqPNKB6vDwMPv27ePdd99lZGQEg8FAaGgoLpeLyclJXC4XKSkp7Nixg23btpGeno5Go8HpdDIwMMD169e5ePEiDQ0NDA8P43K5WLt2LT/84Q/Jzc2VR14nJiY4deoUf/zjH6mvr19wGnB8fDx79uxh9+7dxMXFzfu7IAiC8OiQJImhoSF+97vfcfjwYVwuF9u2beM73/kO6enp+Hw+BgcH+eUvf8kHH3xw2waQz+fD5/MRGhrKxo0b+du//Vu5Q1QQvmgiUH34fD4ffX19nDhxgo8//pimpibsdjsAOp2O0tJSXnnlFdatW0d4ePhd238Wi4UzZ87wxhtv0NDQsGCbMjExke3bt/PCCy+Qmpoq/z0Q7F2/fp1jx45x/fp17HY7e/bs4dVXXyUlJeWuQeNMHo+HU6dO8eabb+J2u/na177GM888Q2RkJJIkMTY2xokTJ/jzn/9MS0sLLpcLSZLk837hhRd46qmn5LKPt+P1eqmtreWTTz7h4sWL9Pb2yqOEkiRhMBhYsmQJu3fvZtWqVYSFhcmPbW5u5pNPPuH06dN0dnbicDjkkejg4GCKi4t54YUX2LBhA1FRUfPey/vhdrsZHBzk8uXLnDp1itraWoKCgnjppZd45ZVXiI6OnvuQBVmtVmpra/n444+5cuUKg4ODs2ZlBgcHs27dOl599VUWLVpESEiIfNySJOH1ehkZGaGyspKTJ09y5coVbDYb3/zmN/nWt741L84YHR3lT3/6E/v27WPRokX87//7/056evodP5MnxRee9feLpFQqCQ0NJS4uTh7m9ng8GAwGSkpK2LZtG7t372b9+vUkJSWh1WqxWq1UVVXxxz/+kbfeeovr168jSRKFhYWsWLGCVatWUVhYOKtnbHJykitXrnD+/HnMZjOJiYnExMQQFhZGeHg4YWFhcq9abm4uQUFBn+uLIgiCIDxYLpeLo0eP8oc//IHq6mpsNhuZmZksW7ZMbow4nU659z4hIYGEhASMRqO8xcfHo1KpGB4eljPLP/XUU2JEVXhgAiM1IuvvwzM8PMyRI0d466236OrqoqysjOeff56SkhKmpqaoqqpicHCQxMREEhMTbzt9NcBqtXLlyhU++eQTzGYzSUlJxMTEEB4eTnh4OAaDgYSEBAoLC8nNzcVgMKBQKHA4HNTV1fHmm2/y29/+lkuXLtHV1YXJZCI/P5/y8nIiIyPvKzgZGBjg4MGD3Lp1i/LycrZu3UpiYiJKpZLp6WmOHTvGr3/9axoaGli2bBm7du2itLSUyclJqqurGR4eJioqiqSkpDuONrpcLo4cOcIHH3yA1WqloqKCTZs2UVZWRnBwMD09PTQ0NDA4OEhOTo58bwU4deoU77zzDkNDQ5SUlPDMM8+wbNkyIiMjGRwc5NatW3R0dJCenk5ycvJdZ7/cjs/no7Kykt/85je8/fbbXLt2jZ6eHnw+n/z+3uu9fXJykqNHj/LBBx/g9XpZtWoVmzdvpqysDLVaTX19Pbdu3cLhcJCZmTlrFqfb7aampobf/OY3vPXWW1y6dInu7m6mpqYoLS1l2bJl80bOg4KCkCSJ1tZWWlpaMBqNZGVlzVrq+KR6pANVtVpNZGQkWVlZlJWVsXLlSp5++mk2btzI6tWrKSsrIycnh4iICNRqNRaLhWvXrvHWW29x7NgxgoOD2bVrF9/+9rfZsWMHa9eupbCwkMjISHluviRJjI6OUllZSU9PD8uWLeO73/0uO3fuZMOGDWzcuJGNGzfy1FNPUVRURFRU1H31ZgmCIAgPl8fjobq6mjfeeIOhoSF5RKOgoIBVq1bJvfKB6bzLli3j6aef5qmnnpK3devWsXTpUhwOBy0tLcTHx/Piiy9SXl4ufgOeMIGJZXcKPh4WEag+XG63m6tXr/Luu+/S29vLunXr+Na3vsUzzzxDUVERRqORrq4url27RkhICHl5eYSHh98xWLRYLFy8eJHa2lrWrFnD97//fXbs2CG3Jzdu3Mi6desoKSkhJiZGbo/a7Xaqq6s5evQoWq2WtWvXolQqMZvNlJaWsmTJkvtem3j16lUOHTqERqNh8+bNLFq0iKCgIBwOB/X19fz2t7/lxo0bbN26le9///usX7+esrIyYmNjGRgYoKGhAaVSSXZ2NtHR0be99/l8Pmw2G8nJyTz33HM8//zzrFy5krKyMgoLCzEYDLS1tdHZ2UlMTAz5+fmEhoaC//2KjY1l06ZN7NixgzVr1lBWVia/P4GqIMHBwZSUlNzTqPZCvF4v586d4/jx48TGxlJaWopSqcTn81FcXMySJUvuOVCV/Gtq09LS2LVrF9u2bWPZsmUsWrSIxYsXo9FoaGhooK2tjZycHDIyMuRBLpfLxfXr1zly5AjBwcFs3rwZh8PB1NQUS5cuZfny5XLnRYBCoSAoKIixsTGuXbuGJEkLBrRPokc6UFX4k1fo9XrCw8OJiooiJCREHrafnJwkJSWFoKAg3G43zc3N7Nu3jwsXLpCamsrrr7/O7t27KS4uxmg0Eh4ejl6vn/VFkyRJfr6RkRFWrFjBpk2byM7OntWzHhcXh8FgmLX4XBAEQXi0SJLEyMgIb775JpcvX2bJkiVoNBpGR0fJz8+XA1UAlUpFSEgIMTEx87bIyEjMZjOnT5+mpaWF1atX8+KLLxIXFzf3JYXHVGD6XW1tLaOjo+h0ui89Wda9Bqo+n4+pqSlaWlro6OjA6/USEhJy20BCWNjQ0BCffPIJ586dIyEhgZdffplVq1YRGRlJaGgokZGRWCwW6urqcDgc5Ofnk5ycfMeRLJPJxKlTp2hubmbjxo0899xzZGZmyjM2EhISiIuLIywsbMHRwZSUFLZu3UpJSQnt7e10d3fLgdT9BKpms1meVpqTk8PWrVtJSkpCpVIxOTnJ6dOn+fTTT4mOjua73/0uq1evJjw8nNDQUGJiYjCZTDQ1NWG1Wu9aalKhUBAVFUVubi65ubnEx8djMBgICQkhOjoag8FAT08P7e3taLVali9fTkxMDAqFgvDwcLKyssjPzychIYGwsDBCQkKIjIwkLCyM0dFRmpqacLlcrFq1CqPReM/vwUwKhQKv10tmZiabN28mJSWFnp4epqamKCwsvK9AVa1WywF3bm4usbGxhISEEBISQlRUFFFRUdTV1dHZ2Ulqair5+fnyZxfoGEtNTWXbtm2UlJRQW1tLb28vFRUVCwaq+Kehm0wmamtrmZiYoKioiMTExCf+O3//n/SXQJIkpqenqaqq4je/+Q3/9E//xIcffsjw8DA+nw/860yvXr1KdXU10dHRvPDCCzz77LOkpqYSFBQk96jP/eAlf9rn6elp1Gr1rJvHzE2tVn+mL4YgCILw8Njtdj7++GNOnz5Nbm4uzzzzDEajUf6tmEupVKJSqVAqlbM2j8dDVVUVN2/eJCYmhuXLl5OSkjL34cJjzOl0Ul9fzwcffMDhw4dpbW3F4XDM3W2WwMjR+Pg4Y2NjjI+PYzKZcPvL630RZl6Hc9ssAS6Xi+7ubo4fP87+/fu5du0a09PTc3cT7mJoaIiWlha8Xi9ZWVlkZWXJo1QqlYqIiAg5S25HRwetra1ymZeFBBLkTE1NAZCQkEBUVNQ9tSk1Gg2ZmZls3LiR5cuXExcX97kGR4aHh2lvb0epVJKamkp0dDQajQafz8fk5CS1tbVMTU1RUFBATk6OnORoZtCZkJDAxMQEbW1tWCyWuS8hUyqVhIeHExMTQ2hoqDw9WqFQoNPpiImJkZfojY2NzfqeBQJjg8GAxp/dV+HPPBwVFUVqaqrc2Wi1Wm97L78bhUJBbm4umzZtYsmSJcTGxn7m9zdwbcTGxsrZfWced2ZmJikpKWg0GiYmJrDZbPJxq9VqMjMz2bRpE8uWLSM2Nvaegk2VSkVSUhIZGRmMj4/T0NCA0+mcu9sT55GOvAJfpqtXr/K73/2Of/3Xf+XQoUOo1Wo2bNjA8uXLCQkJwev10tvbS2VlJWazmYqKCoqLixkdHeX48eN89NFHXLp0icHBQXmh88zXsFqtTE9P4/V65decmJjA5a8FKwiCIDz6PB4PNTU1vP/++3i9Xp577jnKysrQ6XT31bjxer309PRw8eJFhoeHWbRoEUuXLr3jGi3h8eN2u5mYmJBHevr7+zGZTFgsFsxm87zNYrEwMjLClStX2L9/Px988AH79u3j2LFjNDU1MTExcdvH3utmsViwWCzYbDbsdvuCz2exWDCZTAwPD9PT00N3d7e81lq4d16vl9HRUYaGhtDr9aSmphIZGTkraAgMYMTExDA5OUlfX9+soGMur9fL9PQ0JpMJlUqFJElMTEwwOTkpl0K5HaVSSVBQEBEREV9ILpTh4WH6+/sJCQkhKSlJzhLr8XgYHx+nq6sLt9tNWloaERERswLnwHnHx8fjcrkYGRm5Y4COPxC8XefKzP8LDB7N/NvdHqdQKNDr9XIg+1mFhobK769yxujmZ3Gn48Y/ECb5E1MFAnf8n3NwcDARERHo9fr7Oo7o6GjS09NxOBx0d3d/oR1kj6pHMlANBIuB9ab/9m//xieffILP52Pz5s1897vfZc+ePRQUFKDT6bBarbS3t9PV1SX3apw/f55f/OIX/OxnP+N//s//yU9/+lN++ctfcubMGSYmJuSbjNvtxmQyMTU1RVdXFx999BE/+9nP+OlPf8qvfvUrjh07xuDg4G1vSoIgCMKXz+v1Mjw8zJ/+9Cc6OjpYv369PJWNGesQ74XL5eLatWvcvHmTyMhIli9fTnp6+m0bJMLjK9CYNJlM3LhxgyNHjrB///7bbgcOHODIkSMcP36cEydOcPz4cT7++GMOHTrEgQMH5u3/WbYjR45w+fJlamtrOXHixLy/79+/n8OHD3PlyhVGRkbw+TNTi3bK/XE6nUxOTmIymdDpdERHR8+b2qpUKjEYDPJygenp6TsGqoHOj+npacbHxzly5Ag//elP+clPfsIvf/lLPv74Y7q6um47Ena34Od+TE5OMjk5KS9vCExXDhzj1NQUOp2OuLi4eecNYDAYCA8Px+fzyR04cwd77oXH42FqakoeLEpLS1twautcPp8Pi8XCwMAAXq+X9PT0eQH1/VL4Rz3v9tqfh8/no7+/n76+PiRJIikpad5xBz7n+xUaGkp8fDySP7+O3W6/r9+2x9H9v0sPkNdfx+r69eu88847vPnmm5w8eRK3282aNWt47bXX5BThaWlp8jQFi8VCT08PY2NjTExMcOvWLW7cuIHJZCI6Oprg4GBaWlp49913+e1vf8vFixcxm81IkoTH4wEgKiqKsLAwBgcHuXTpEocOHeK3v/0tP/vZz3jrrbeoq6u77Y1FEARB+PJIkoTZbObw4cOcPHmSoqIitm/fTmpqKkp/sox7FZihc+HCBYaHhyktLaWiouKe1y4Jjx+FQoHNZuPmzZt88sknHDp06LbbsWPHaGhokNsb4+Pj9PT0cPnyZT766KN5+9/vdvjwYT799FOuXbtGXV0dp0+fnrfPoUOHOHr0KNevX2diYmLu6Qj3yOl0YjKZsNls8nr1uVNBFf6ka4HprIGR7tsFBz6fD6/XS0REBHFxcQwNDXHp0iWOHDnC7373O37+85/zxz/+kerqarkd+iB4vV7MZjM2m42goKBZOVYCAzQulwu9Xn/btbJ6vV4OYG02Gzab7TMFqmazmfr6elpbWwkJCaGsrIzIyMi5u81jt9tpa2ujtrYWSZKoqKiQ17U+qiT/GvMrV67Q1dVFSkoK+fn58wLVz0qj0RAWFoZOp2N6ehqz2Xxfv2+Po8//rn0BfP66YTdv3uTDDz/krbfe4uTJk9jtdpYtW8bXv/519u7dKweoM+e/408FPjIywvT0NBaLBbVaTXl5Oa+88grf+973+N73vseOHTuIiIjg4sWLHD16lPb2dlwuFxqNhuzsbPbs2cNf/uVf8tprr7F79242bdpEYmIijY2N/OEPf2D//v309PR8JYbZBUEQHheSJGGz2bh+/Tpvv/02wcHB7Nmzh5KSEoKDg++7UeN0OqmqqqKuro6IiAiWL19OZmbmfT+P8HhR+NfSBQcHExoauuAWEhIiT1t0u924XC7cbjc+nw+tVisnU5n7uPvdQkJC0Ov18vEEasjP/Htgn/uZNijM5vV6cTqduN1ulEolGo1mwbWCKpVKXlPq9XrxeDy3fc81Gg3p6em8+OKLcpvy5Zdf5tlnnyUtLY2Ojg4++OADPvzwQ1paWh7YAIjb7cZqteJwONBqtfI6Smact9frRaPRoNPp7nje+EdFPR7PfQdFDoeDtrY2zp07x+joKIsXL6asrIxQf8bf2/F4PPT09HD27Fk6OzvJzc1l2bJlnznj78Pidrupr6/n448/xmw2s27dOgoKCj7Tb9FCVCqV3IFgs9lEoPqwBBIa/OlPf+K9995jYGCARYsW8fLLL7N3717Wr19PRkaG3CM098N2Op1MT0/j8/lITEzkqaee4oUXXmDjxo0sW7aMDRs28PWvf52tW7cCUFNTQ11dHVarFZ1OR1ZWFlu3bmXv3r3s3buXb37zm/zgBz/gO9/5DsuXL5cLIl+/fh2LxXLbG5QgCILwcLndbjo7O/nzn/9Md3c327dvZ926dURERKBQKO7rfu3z+eQRkJGRERYtWkRFRQUGg2HursITIDDt1+fzERwcLNfPfPHFF3nppZfmbS+++CLPP/88S5cuJT09ndTUVFJTUyksLGT9+vXs3Llz3mPud3vxxRfZsWOHXIJvy5Yt8/Z56aWX2LFjBytXriQ2NlY+F+H+BKZfzpxqu9D7GLhOJEmS978drVZLeno6W7du5ZVXXmHv3r289tpr/OAHP+B73/seq1evxmazcenSJaqqqpiamlrwNT8vt9uNw+HA4/GgVCrlQDsgcM4zz22umdPJ575P98Lj8dDd3c2JEyeorq4mISGBZ599lszMzAVHcAN8Ph+Dg4OcPXuWCxcuYDAY2Lp1q7zc71EV+C364IMPqKqqoqCggE2bNpGcnDxvpP7zUKvVaDQaubNsoc/uSXL7b9tD5PWniL958ybd3d2EhYVRUlLCokWLSElJWXA6xkw+nw+3241OpyM7O5uKigoyMjIIDQ2VpzxkZ2fLWRvHxsbo6urC4XCgVCrR6XSEhYURGRlJVFQUsbGxZGVlyT882dnZdHZ2Ultbi8lkeuIvCkEQhMeBz+djfHycs2fPcvz4cbRaLTExMTQ2NnL+/HnOnj3L5cuXGRoawu12MzAwwNWrV7lx4wYjIyNznw6n00lNTQ1VVVWEhISwbNky0tPT79gwFR5fMxvw4eHhFBcXs3btWtavX7/gtmHDBp555hm2b9/Oiy++KAe0u3bt4tlnn2Xjxo3zHvNZtjVr1lBaWkpeXh7Lly+f9/f169ezbt06SktLifHX4bzdaKBwexqNhuDgYLRaLV6vF5fLNW90SpIk3G43drsdj8eDTqdDr9ffNmALTBUOtCkjIyOJjo4mLS2Np59+mueff56cnBzGxsZoaGhgdHT0M02nvZvbHR/+QCc4OBi1Wi0HtAsdQyAQUvhreM5NgnQnHo+Hvr4+Tp06xcmTJ1EoFGzatGlW3oCF+Hw+RkdHOX/+PB9//DFWq5Wnn36ajRs3Eh0dfcfz+jK53W66u7v58MMP+eijj4iKimL37t2Ul5ff03rc+xHoXAt0tHyRz/0oeiR+fbVaLRkZGaxevZqcnBzGx8c5f/4858+fp7W1VR4tvZ3AlA2dTofBYCAsLGxejSu1Wk1sbCxxcXG43W7MZjPuO0zjVavVhIeHk5eXR2ZmJiaTiYGBAex2+x2PRRAEQXg4vP6snZcuXZJLF3z44Yf89Kc/5V/+5V/4l3/5F37xi19w69Yt7HY71dXVvPHGG7z55pvU1dXNeq5AA+nUqVMMDg5SWlpKWVnZgjUshSeDRqPBaDRSXFxMSUkJaWlpREZGYjAYbrvFxMRQXFzMM888w+bNm9m0aRMrV66UE73M3f9+t0AHu1arRe2vIx8aGjpvv/DwcBITE8nLy6O4uFheFiXcO51OR0REBKGhobhnrNucSfIvLZiamsLn88k1Pu81YAtQqVQYDAby8vLIysqSB2hMJtOCQeLnpdFoCAoKQqPR4PV6cfunqONvcwcy39rtdiYnJ+edN/51qWazGYVCIV+b93LeXq+XgYEBTpw4wZEjR+QpsNu2bSM5Ofm2zyFJktz+P3jwIH19fSxZsoRdu3aRnZ19x1HYL5PL5aKrq4vDhw/zwQcf4PP5eOmll9i8eTNxcXG3Pd/PItBx4nK57tpp8qR4JAJVjUZDbm4uX//61/n2t79NQUEBHR0dvPvuu/zud7/j2LFjNDc3Mz09LSc/mkmv1xMZGYl6xkL3hYLJmVM3VP66eXei8K9Z0el08hQJQRAE4dGh0WhITk5m1apVlJSUoFar8fkTmnj9Jcfw388lSZr1fzN5PB5qa2u5fPkyGo1GHk39IhsZwqNFp9NRUFDAyy+/zM6dO8nKyrrr1MLALCyDv1PcYDDIo1NfVIPxTtMxAzQaDSkpKWzatIndu3ezZMkSDGKK+n3RarVERkYSERGBw+GQS7DM5PP5mJqaYmJigpCQEOLj4z9z6ZiZbcq7tT8/L41Gg8FgQK/X43Q6sVqtckCs8dcnjYmJwePxLFjaSJIkuVRjYP9AAtM78Xq9DA4Ocvz4cQ4ePMjY2BirV6/mxRdfJDc3d94gUkAgSD137hwffPABbW1tLFq0iJdeeomSkpI7vuf38n15UAL1jI8cOcL777+P3W5n165d7NmzR67/+kXy+es42+12eT383T6Tx90jcXaBaQUZGRls2rSJ733ve3zjG98gOzubxsZG3nzzTblUTHt7O2azeVbAGhYWRmpqKjqdjqGhIfr7++d96QJ1o0ZGRggKCiImJuauF5DH42F0dJTR0VFCQ0MxGo1fid4LQRCEx4FarSYtLY2//Mu/lEtA/I//8T/4H//jf/CTn/yEn/zkJ/zDP/wDS5cuJTg4mFWrVvGf/tN/4u/+7u8oLy+Xn0eSJKanp/n0008ZGRmhpKSE8vLye8pMKTy+lEolERER8swpg8Hw2DT6lEoloaGhpKWlkZOTQ1xc3B2XSAnzKRQKYmJiSEpKwul00tXVxejoqNy+lCQJh8NBV1cXIyMjJCcnk5GRISfGcblccl1bt9t910DJ4/EwMjLCyMgIGo2GuLg4wsLCHkhnmNJfVickJASr1crk5KQ8i1ClUhEZGUl2djZ6vZ6Ojg7GxsZmjew6HA76+/sZGhqSr7OQkBB5RC9Q03dmW9zn8zE8PMyxY8c4cOAAo6OjrFmzhj179lBcXHzbYDMQFJ85c4b33nuP1tZWFi9ezN69e1m6dCmG20yddblcTE5OMjQ0xPj4+F3r1H5WLpdLTtY683wDCZ+OHj3Kvn37sNvt7Ny5k29+85t3XYf7WTkcDqampvB4PPIMjoXemyfJI3VHDkyNyMzMZMuWLfxv/9v/xre//W1ycnK4efMmv/jFL/jFL37B8ePH6e7uxuYvPhyYopuQkMDQ0BDXrl2jra1NXkjudDrp7+/nxo0b9Pb2YjQayc3NJTg4WL4Ap6ensdvtuFwuXC4XFouF7u5uLl68SGNjI6mpqZSUlBAeHv7Y/JAJgiA8yQKdnGlpaRQUFFBYWEhRUZG8FRYWyqUBVCoVUVFR5ObmkpWVNWudlMfjoa6ujgsXLqBSqVi9ejXp6ekPpKEhPFoCS4e+yBHRh0WhUMjrU0W75LNJTEykqKiI0NBQ2traqKmpkde02+12uru7qaysZGRkhPz8fHJyctDr9bjdbjo6Ojhx4gRnzpyht7dXbj+aTCa53qrLnxnabrfT09PDpUuXaGhowGAwkJubS0xMzG0D1c8bdEVFRREdHY3JZGJ4eBiHwwH+6yYiIoLFixcTExNDQ0MDN27cYHR0VD6HtrY2bty4wdjYmFxiJTQ0VF57evz4cT755BP6+vrweDzyVOajR4/yzjvv0NfXx4oVK9i1axdZWVn4/DVRzWYzVqtVDuwDI9YnT57krbfeoqGhgdLSUl566SWKiopQ+ktQBjoEZgajfX19ctmf8+fPy9Oz79ed3mdJkmhra+Po0aOcPn2agYEB3G63vCb1yJEj/PnPf8ZkMrF161b27NlDfHw8DodDDuZnnu/nNT09TX9/PyqVCqPRKM/4fJKpfvzjH/947n9+2QJTayIjI0lNTaWoqIjU1FSsVitVVVVcuHCBgYGBWdMwtFotVquV5uZm2tvbcTqd6HQ6vF4vXV1dHDx4kP379+Pz+XjuuefYsmULERERtLW18emnn1JdXc3U1BRWq5Xh4WGqq6s5cOAAhw4dwmq1smXLFnbs2IHRaLztTUUQBEF4uBQzCrgvtFksFk6cOEFLSwuFhYWsWrVqXlIOk8nE//pf/4srV65QVlbG3r17yc7OFvd64aGT/HUYA2uuExISxDrpBygw1XtgYICmpiaGh4fR6XRotVq6u7s5fPgwx44dIzQ0lD179rBy5UpCQkIYGhpi//79vPHGG9y4cYPg4GCMRiNjY2McO3aMq1evMjU1hcPhYGxsjNraWj788EOOHDnC9PQ0q1ev5tlnn71jh9jY2Bjnz5+nvb2d4uJili5dSlRU1D13Svh8PlpbW2lpaSEmJoaSkhI5G7pGo0Gr1TIwMEB9fT39/f3o9XqCg4Pp7e3l4MGDHDt2jODgYJ577jnWrFlDZGQk4+PjHDlyhF/+8pd8+umnREZGkpGRgcVi4eDBg/zpT3+irq6O6OhoMjMzkSSJrq4uGhsbaWxspKGhgc7OTrRaLQaDAavVyqeffsof/vAHKisrCQkJITc3F51OR29vL01NTfJjW1tbUSgUct3XCxcu8NZbb3Ht2jUSExMpKSkhLCzsngO33t5eKisrGRsbo7CwkIqKilnrvCVJwm6385vf/IY333yTqqoqYmNjSUlJYXh4mP379/POO+/Q0dGB0WikoKAAm81GS0uLfMx1dXX09PQQEhJCWFjYgp/d1NQUn3zyCV1dXVRUVLBixYoFR0olSaK1tVVOMvXss89SVFR02+nUT4pHMlANUPjn80dERJCenk5xcTGZmZlMTk5SW1tLUFAQJSUlhIaGEhwcTFRUFC6Xi4aGBq5evUplZSVnz57lyJEjnDp1CqfTyfbt23nllVfIyMjA5XJx9epV3n77bY4cOcLFixc5c+YMn376KUePHqWyshK1Ws2uXbv4+te/Tk5ODlqtdt7FIwiCIDyazGYzJ0+epKWlhaKiIlauXEl0dLT890Dd1J/97Ge4XC6+/vWvs3bt2ke+Xp/wZBKB6sOlVCoJCwsjKCiIoaEhamtruX79OhcvXuTTTz/l0qVLaDQaXnnlFXbu3Cknx+nv7+f06dNcunQJi8VCamoqmZmZ9PT08Mc//pEDBw5w6dIlzp49y6effsqRI0e4cOECkiSxZcsWvva1r9211vPY2BgXLlygs7OTkpISlixZcl+Bql6vZ2BggNraWhQKBXl5ecTHx8uZrgPt5uHhYaqqqqiqquLy5cscPXqUc+fOoVKp2L59Ozt27CAlJQW1Ws34+DjHjh3j3LlzDA0NkZuby6JFi2hqauKdd97h2rVrWCwWLBYLbW1tXLp0iTNnzsjbuXPnuHnzJklJSWRkZNDR0cEf/vAHzp07J89s7Orq4sqVK7Med+bMGSorK4mMjCQnJ4eQkBDOnDnDyZMnCQsLY/369RQWFhIUFDT3bbit3t5erl69ytjYGEVFRSxZsoSQkJBZ+9hsNt5++22uXr2K2WymqKiI/Px8bty4wZ/+9Cc5UZ/FYqGxsZFz585x9uzZWcfd2NhIdnb2bTslpqamOHbsGD09PVRUVLB8+fIFA1W32821a9c4evQo8fHx7N27l4SEhHu+Hh5Xj3SgGqBUKuUsZWlpafKUrry8PFJSUtBqtahUKsLCwkhPTyc9PR2tVsvExASjo6MALFq0iNdff52XXnqJ7OxseTG7Xq/H4K/PGsjs5nQ6iYyMZM2aNXzzm9/kxRdflJMszL1wBEEQhEdXYGpZZGQky5Yto7i4eFavudPppLm5mampKVauXMnu3btJSUkRo6nCl0IEqg+fVqslLi6O1NRUDAYDJpOJsbExVCoV5eXlvP7662zfvp2kpKRZ64CtVisOh4OMjAyefvppCgsLiYiIkCtP2Gw2JicnsVqtGAwGVq1axauvvsquXbvkqbR3alO6XC5sNhtRUVEsXbqUgoKCuz5mJrVajdPppK2tjcHBQeLi4sjMzJSDMY1GQ3R0NFlZWYSFhTE1NcXIyAiSJFFRUcGrr77K888/T2Zmpjzy7PP5cDqdTE1NkZqayvbt2ykqKsJkMmE2m4mLiyMvL4/s7GySk5NJTEwkKSlJ3hITE8nIyGDp0qWkpaXJ62ejoqLkx6Wmps57XFJSEqmpqVRUVJCTk4PL5eL48eNUV1dTXl7O1q1b75hReCEOhwO73U5sbCzl5eXk5uai1+vlvysUClQqFRMTE0xPT8t1UbOzs+U1q4mJiRQUFJCVlUViYuK8405MTCQrK4tly5bdtp6qx+OR34PVq1dTUFCw4Hre3t5ejh49SmNjI2vXruWZZ565r+vhcaWQvohJ0w+R5M/aaLfbAQgODp51YXo8HsxmM6Ojo0xOTuJwOFCr1URERBAfH09ERIR8oUiSJC+GHx8fZ3p6Wp7/rtfriYiIIC4uDoPBcF8XvyAIgvBoCCQwMZvNhIWFER0dPWuqlMfjYWxsjImJCfR6PYmJibMaK4LwMPl8Pqanp6mvr2dkZITy8nLS09Pn7iZ8wXw+H3a7nbGxMUZHR7HZbKjVaiIjIzEajfOSHs1M0KlQKIiPjycyMhKfz4fZbGZiYoKpqSnsdvusNmVMTAwGgwGNRnPXAMPpdDI2NobVaiU8PJzIyMh7etxMExMT8ghvYWEh3/3udykpKZFH9mZ2jAwPD2O1WuXzjouLIzw8fNYooMfjYWpqiv7+fiRJIjk5mcjISCwWCxMTEzgcjruuE1X7y0WGh4djt9sZHx/HZrPd9XFKpZLo6GgiIyNpbW3ln/7pn2hoaOC1115j7969xMfH39d7Y7PZ5GMOvL8LBZKDg4P09/ej0+lISkoiPDwck8nE+Pg4LpfrjmtPJUlC4y+DdbtkbW63m6GhISwWC1FRUURFRc0befV6vRw/fpxf/OIXeDwe/u7v/o61a9feNUv5k+CxC1QDAoe90EUp+RdoSzPSVSuVSpS3KYy70P4K//qm2z1GEARBeDwE7u+Be/pcgb/j/60Q93zhyyIC1S9PoA04935wu3uCz+fD5/PNai8yp00ZCL4Cz3G751pI4HgC967Adj+8Xi9VVVX8/ve/p7Ozk82bN7Nr165Zo48zzztwPvdy3sx4f2ae670IPPfMc7wXgWM7dOgQP/nJTzAajXz/+9+X1w7fj7nv70K/Dcw5X5VKJR/3Zznf27nTb5TX66W5uZnf/e533Lhxg61bt/L6668TFxc3b98n0WMx9Xchd/rCzvySBb6IVqtVnkqj0Wjkiy3A4/HgcDhwOBxy1jOn0znr/7iHi00QBEH48jgcDvr6+ujq6pJLlWm12jvWLgz8Zrjdbvr7++ns7GRkZAS3241Op1uwl10QHgRJTP390igUCpxOJ8PDw/T09DA+Po7P50Ov1y84q+52Ad3cNqhKpUKpVOLzj9ra7XZ8Pp+8z1xut5uJiQl6e3vp6+tjenoapT/J6EL730ngcX19fdTU1KBQKCgoKJDX2gYEZp709PQwNjaGJEnysrq5bd6Fznvm/808L5fLJWcbVqvV8nsReJzkLwFkt9vltrbT6Vxwc7lcciDd2dmJ3W5nzZo1LFu2jMjIyPt+bwKv7XQ6YUYQOtfdzjdw3QwMDNDV1cX4+DhqtRq9Xi+vB17oeWdS+GOawHd/amoKpVKJWq1GkiSqqqr46KOPUKlU7Nixg/z8/Cc+iVLAYzuiejdut5uxsTGamppoamqiv7+f6elp8vLy2LFjB0lJSfKX1G6309LSwpUrV+jp6ZF7NmaKiIhg2bJlclHtu110giAIwsPh9XoZHx/n6tWr1NbWyvd7j8dDeHg42dnZrFy5Us56OZfH46GhoYFz587R3NzMxMQECoWC2NhYSkpKWLVqFdnZ2SJgFR44nxhR/VI4HA46Ozu5evUqN2/eZHh4GKVSSXx8PBUVFaxdu5bExMTP3PZzOBxUV1dz7do1XC4XxcXFlJWVERsbi9I/Immz2Whra+P69eu0tLQwOjqK3W5Hp9ORkpJCeXk5ZWVlJCYm3leQ0tbWxptvvkllZSXr1q3j1VdfJTMzE5VKhcdfC/TChQvU1NTIeV3i4+MpKytj+fLlpKam3tfrBUrV3Lp1i4aGBnw+H6WlpSxdunRWWTD8GdfPnj1LbW0tFotlXtsbf7CtUqnQaDQUFBSwdu1aecpwXFwcRqPxvhKd+nw+OXFWY2MjSqWSsrKyBZMp3U3gM7t06RL19fWMj4+jUqlISEhg9erVrF69+o4JsCRJwmKx0NHRQW1trRzoRkREsG3bNoqKiggKCqK6uppf/epXtLa28sorr7B3717CwsLmPt0T6bEdUb0dr9fLxMQE169fZ9++fezfv59z587R1NTE6OgoUVFRlJaWEhERIV8409PTXLlyhQ8++IDTp0/T0tJCS0sLzc3NNDc309TUxMjICEajkZycnDtmaRMEQRAeLofDwc2bN/nZz37GxYsX5XVH4+PjNDU1UV9fz+DgICEhIRiNxllrUO12O1evXuU3v/kNH330EWNjY3Kw0NDQQF1dHWazmaioqK/MVCvhyyNGVB8+h8NBXV0d+/fv58iRI3KJw8nJSerr62loaECSJBISEm67zvBOJEmiubmZd999lwMHDtDY2EhwcDBZWVnySKDNZqOqqkquQtHe3o7FYmFqaorOzk7q6uro6OjA6/USHR09b83s7dhsNs6ePcvp06eJjY3lueeeo6CgAL1ej8vlorW1lXfffZf33ntPfv7JyUkaGhpoamrC7XbL60nv9no+n4/x8XGuXbsml4Q8efIk7e3thIeHU1BQgMFgmPWY6elpjh07xrFjx6itraWlpYXW1tZZW1NTE9XV1dTV1RESEkJpaSnJyckYjUZ5De29tMklSWJiYoLKykr279/P/v37OX36NJ2dnURHR1NQUEBwcPDch92WzWajurqad999l6NHj9LX1zfrPWhubiYoKAij0UhISMi8Y7Tb7bS2tsq1WD/55BO5oxWguLiYxMREdDodQUFB2Gw2mpqamJiYICcnh9jY2Lt+Jk+CRyJQDfSgzP0Q75fX62V4eJizZ8/ywQcfcP78eVwuFwUFBaxcuZLly5dTUVFBVlbWrGBzfHycK1eucOPGDTkzW1lZGbm5ueTl5ZGfn09RURGLFi0iNTVVZP8VBEF4hASmrd28eZPi4mKefvppVqxYQVFREREREfT399Pc3IwkSWRmZmI0GlEoFHJD7Ze//CXHjx8nOzubbdu2sW7dOoqLiwkJCaGzs5PGxkZUKhXZ2dnzRgQE4YskAtWHS/LX+Tx8+DAnTpxAoVCwbt06Nm7cSFFREQD19fV0dnbKNTT1ev19tQFHRkY4dOgQx44do7OzE4fDQWZmJosWLZJHVG02G42NjVRVVREWFsbatWtZs2YNZWVlpKWlYbPZaG1tZWxsjKioKJKSkhYMfuZqb2/n0KFD9PT0sGLFCp566iliY2PlUcVDhw7x5z//GUmS2LRpE8888wylpaUoFAra2tro7+/HYDCQmpp61wyzTqdTHvS5cuUK4+PjTE1N4XK5yM7Opry8fN79M7D+MzY2lvz8fEpKSmZteXl5hIaG0tXVxdTUFBs2bGDZsmVERESg0WjuaVptgMfj4cKFC7z99ttcv36dqakpxsfH8Xg85OXlUVFRcc8jqj6fj5aWFvbt28epU6cwGAxs2bKFp59+mqKiInkEfXBwkLS0NIxG46zYwWKxUFtby3vvvcfhw4cZGBggOTmZFStWsGLFCpYuXUpRURFRUVGo1Wp0Oh0qlYquri7q6+uJiIigsLDwK5H475EIVN1uNyMjIwwNDeHz+eR58fdDkiTGx8c5f/48+/fvp7m5maysLLkG1IYNG6ioqCAjI4PQ0FD5+SVJYmRkhMrKSnp7e1m+fDlf//rX5f2XLl3K0qVL5ZtFaGjoffemCYIgCA+OUqmUe643btzI8uXLKSwspLCwkMzMTKampmhqasLpdModkAqFgqmpKT799FN+//vfExkZyV/91V+xbds2SkpKyMnJIS0tDYvFQl1dHdPT06Snp5OZmSl+Ax5zXq8Xk8nE6Ogokn8t3r02dh+0mYFqoDRJ4HhVKhVqtfqROdYngcVi4cKFC3z44YeYzWaeeeYZ9uzZw/Lly8nNzcVoNDI4OEhtbS0ajYa8vDxiYmLuuY1qt9s5c+YM+/btw2azoVKpkCSJvLy8eVN/lUolcXFxrF27lo0bN7J48WL5PhYcHExvby89PT0EBweTnZ191+PweDxcvnyZTz/9lLCwMDZv3iyPptpsNmpqanjvvffo7+9n586dvPrqq3IZnPj4eEZGRmhoaMDr9ZKZmSnXYL0dl8tFY2MjPT09pKamkpubK68/zc/PZ8mSJfMCVY1GQ0JCAsXFxZSXl7NkyRJ5q6ioIDs7G5PJRH19PXFxcbz66qvk5+ff8yjqTD6fj1u3btHZ2UlOTg65ublYLBacTifFxcX3NfXXZDJx+vRpDhw4gM/n44UXXmDPnj0sXryY/Px8jEYjzc3NNDQ0EBERQXZ2tjx67nQ6qaur49133+XEiROEhoayZcsWdu3axdatW1m+fDkFBQVER0fL56lQKNDr9YyPj3P9+nXcbjfl5eWzZoc+qR6Js3M6ndTX1/P+++9z4MABqqqqGB0dxePxzN31tux2Ow0NDRw7doyOjg5KS0t57bXXeOmllygrK5N7JUNCQmZ9sSX/uoDp6Wk0Gg2pqamkp6fLNZsCW2Ji4j1NfRAEQRAeLpVKRXR0NGvWrCE7O5uoqCjCwsKIjIwkOzubkpISYmJisFqtmEwmJH+Zs/HxcS5dusTk5KS8nshoNBIaGkpERAQ5OTmsXbuWzMxMurq6qK2txWazzX154THi8/kwmUxUVVVx+PBhqqqq5BIij4rAKFFg1Ov06dMcP36c7u5uObGj8MUYGRmRp1smJSWxYsUKsrKyCA8PJyoqiuLiYtasWUNERAR1dXW0trbicDju6Xpxu920tLRw9OhRxsfHKSkpITs7G51ON+/xOp2OrKwsnnnmGZYvX05CQgLh4eGEh4eTmJjIihUrKC4uxu12093dzcjIyF2vhenpaZqbm5mcnCQ5OZmMjAyCg4ORJAmTyUR1dTWdnZ2kpaXx9NNPy/VUw8PDKS0tZdmyZRgMBtrb22lsbMRiscx9iVm0Wi3FxcW8/PLLfOtb32Ljxo1y7dm55xugVCoJCQkhMjKS6OjoWVt4eDgOh4Pm5mZcLhfr1q0jPz//vke0A1QqFSUlJbzyyit8+9vf5umnnyYhIeGOwfftDA4OUlNTw8jICNnZ2axZs4akpCT5d2f58uWsXLkSjUbDjRs36OnpkWOagYEBjh8/zvnz54mMjGTv3r28/vrrrF27ltTUVKKjoxcsYWQwGMjJycFoNNLV1UVLSwtut3vGUT2ZHolAVaFQ4PF4aGtr48CBA7z55pt8+OGH1NTUMDY2dteAVZIkRkdHuXz5Mg0NDSQlJbFt2zaWLl1KUFCQ3KPj9XrnPhRJkrDb7UxPT6NSqYiKipKH0hVzsph9li+GIAiC8OCpVCqCg4NnjThJkoTH48Fut+N2u+UGkdKf4XdkZISWlhZUKhVlZWWEh4fP6p3W6XRkZGSQkpLC9PQ0bW1tTE1NzXhV4XEj+depXblyhcOHD1NZWcnU1BQej0eehhjYPB4PJpOJrq4ubt26RW1trTwiY7Va8Xq98x7zRW34R357eno4ceIEp06dorW1Vc5QKnx+kiQxPDxMR0cHCoWCzMxM0tLS5HWKSqWS0NBQeWS1p6eHjo6Oe+rYCCxFO3r0KFVVVRQWFrJmzZrbjkoqlUr0ej0GgwG9Xj/rPqT01w+NiYlBoVBgs9lw3EO90sHBQTo6OlCr1aSkpBAREYFKpcLn8zExMUF9fT0mk4nc3Nx5y9oMBgOZmZkkJiZiMpno7u7GarXOfYlZVCoV6enpLF26lPz8/Hn30/tlMpm4efMmN2/eJDIykrVr1xIfH/+ZnzPwGa9cuZLc3Ny7TmW+k97eXlpbW9HpdOTn589LOBUaGkpJSQmRkZF0d3czMDCAw19FpLa2lrNnz6JQKHjuuefYunUr0dHRuFwubDYbbrd7wetLqVRiNBrJzMyUOyHu1lnxJPhsn/YXLCgoiNLSUrZv305+fj7d3d289957vPHGGxw+fJj6+nomJydvG7C63W66urqoqqrC4XDIX5Bbt25x5MgRDh48yIkTJ7h16xYTExOzAlav14vVamVqagqLxcLo6CiNjY00NDTQ09PD1NTUV6LHQhAE4Ungdrux2WyYzWaGh4e5ceMGlZWVOBwOCgsLyc7ORukvFWGz2TCZTCgUigWTpCgUCkJDQ4mMjESSJMbGxu7aWBMebZJ/au3U1BQTExP09/fT0tJCW1vbvCQuzc3NXL16lX379vHGG2/w61//mt/85jfs37+fmpqaeft/EVtbWxsdHR0MDAwwMjJCX18fIyMjmEwmzGbzgh3uwmfj8XgYGxtjdHQUvV5PUlLSvKoOgQGMqKgozGYzQ0NDWK3WOwaJkiRhNpu5fPkyx44dIzQ0lI0bN8qjgZ9FoGyLSqUiNDSU4ODgu87wGx0dZWhoiJCQEBISEggKCgL/eQeufUmSSE5OJiwsbNZ5K5VKoqKiiImJkato2Gy2O563QqFAo9HIZVkU/nqjn4XH46Gvr49Lly4xNTXFkiVLKCoq+szvHzOOLygoSO4s+CzH5/V6GRoaYnBwEL1eT2JiIkFBQbPeP4VCIXcOBH6LLBYLAwMD3Lhxg97eXjIyMigpKaG3t5dPP/2UAwcOcPjwYa5cuUJ/fz9Op3Pe8UVGRpKamorL5aK3t/cr0XH1SKxRDQz9p6amUlBQQGJiIk6nU07X3NHRgcPhkBcUB+oSBUxPT3P58mXOnj0LQEJCAh0dHRw4cIBjx45x/vx5zp07J/ecR0dHExwcjFKpxG6309TUxIULF+js7GR4eJja2lquX79Oe3s7U1NTaDQaQkJC5g3DC4IgCI8Or9crd1o2NjZy6dIl9u/fT2trK4sWLWL37t2Ul5ejVqvlBExnz55ldHSUpUuXUlpaOqsh5PP5mJyc5Pr161RXV2M0GtmwYQNGo3HW6wqPD58/K+fNmzfp7u5GkiSGhoZoaGigtrZ23lZTU0NDQwO9vb2Mjo4yMjIiB5CNjY3z9v8itps3b9Lc3Exvby9DQ0NMTk4SFBREYWEhOTk5n3nqozCb3W6nurqaS5cuodVqWbVqFUVFRbMyv0r+5WHV1dU0NDSQkZHBkiVLiI6Ovm2g6HA4aGho4K233qK9vZ3t27fz7LPPolQquXbtGt3d3WRkZFBeXi6vUb0TSZJoaWnh5MmTDA0NsWjRItasWYPRaLztMUiSRG1tLefOnSMyMpI1a9aQkZGBVqvFbrfT2NjIqVOn8Hg8bNq0iUWLFs0LAk0mE3V1dbS0tBAdHU1ZWdkdX3OugYEBrl69ytDQELm5uQuuUb2dqakpLly4wKFDh1Cr1bz88suUlZXNO8bPo7e3l8rKSsbGxigsLLznNaoOh4NLly5x4cIFIiIiWL9+PTk5OfNK+NhsNs6fP09PTw95eXkUFxfT19fHxx9/zPDwMBkZGbhcLj788EM++ugjLly4wMmTJ6mpqcFqtcpLWOauS+/p6eHixYuEh4ezdu3aeZ0MT5o7fzseIpVKJU81ePbZZ/mbv/kb/vIv/5KysjI6Ojr41a9+xc9+9jOOHj1KZ2cnFotF7lk0m8309vYyOTnJyMgIN27coLm5mYSEBNauXcvixYtRKBScOHGCX/ziFxw7dozJyUkk/zoltVpNWloaGRkZKBQK+vr6uHbtGm+//Tb//M//zM9//nNu3LiBzWab17shCIIgPBo8Hg/nz5/nH//xH/kv/+W/8D//5//kzJkzxMbGsn37dpYvXy438rVaLXFxcWRlZeHxeDh37hw9PT3YbDa8Xi9utxuTySSXK3M4HCj8y0GEx9vMRp3ZbKahoYGqqipu3Lgxa6uurqatrU1e14w/ADCZTHKG1rmP+SK2mzdv0t7eTl9fH8PDw2JW1wPicrmwWCw4HA5UKtWskbaAwL0iODgYjUaD0+m84xrVwGhboNTI8uXLefbZZ2et1bzdY2/HarVy8+ZNGhsbCQsLIz8/n7i4uHnHOpPX68VisWCz2QgKCpIDHvz3SYvFgtvtRqfTERISsuBz6XQ6OTC02+23XUL3RfP5fPT29nLp0iVMJhOLFi1i0aJF9xREPgwOh0Oe+q/X6wkKClrwdyE4OJigoCC5s8PpdMqJYwOdACdPnkSlUrFixQrWrl1LUlISzc3N/PrXv+bdd9+ls7Nz1mxStVotj6ibzWamp6fvOMr9JJj/zn7JAtMa0tPT2bRpE3/913/Nj370I9auXUt7ezv/+q//yk9/+lM+/fRTBgcH5fVHExMTmM1m7HY7cXFxfO1rX+Pv//7v+fu//3v+4R/+gR/96EcUFxdTV1fHoUOHaGhowG63o9frKSkp4Xvf+x7/9b/+V3784x/z93//9/zVX/0Va9euxWaz8eGHH/LWW299ZeaDC4IgPI6U/qyZgdIGycnJBAUFMTw8zLVr12hoaJCnSqlUKmJjY3nqqacIDw/nwoUL/PrXv+bixYt0dnbS1NTEkSNH+P3vf8+1a9fAnyxEo9HMeVXhcWYwGCgsLKS8vJzy8nLKysooKyujvLycxYsXk5WVNWs6qMI/HTw/P3/eYz7vFni+0tJSsrKySEpKIi4uDo1GIwc49xvkCLcX6JDyeDwoFApUKtVtR6YC/+/z+W77GUiSxOTkJOfPn+fMmTMYjUZeeukliouL0el0MON5FP5Mrnfj8Xiora3l1KlTTExMUFRUREVFBVFRUXd8fCAIdzqd8mzEQDDl8/lwu934fD6USuW8EbuAwDFKkiSvnb7duX+RLBYLt27dorq6mpCQENasWUNiYuI9j+Q+aB6PB5fLhSRJqFSq2143Sn9+m8D3NtBBYLVasVgsKBQKnn32WTlW+S//5b/wj//4j2zZsgWHw8GBAwe4du0aZrNZft8VCoXcgRDIv/MwPpMv0yMx9XchCv9c8rCwMFJSUli0aBHFxcV4vV7OnTtHZWUlwcHB5OTkMDk5yblz5+jq6iI3N5fXXnuNZ599Vi7OHBkZSVpaGgqFgpqaGsxmMykpKeTm5mIwGAgNDcVoNJKSkkJKSgoZGRnk5+dTUFCAJEk0NDQwNjaG0WgkOzt7Vg1WQRAE4dGgVCqJj49n2bJlPPXUU6xcuZK0tDQ6Ojo4f/48Y2NjJCUlkZKSIv/GxMTE4HA4uHXrFvX19dy4cYOzZ8/yySefcOHCBXlNqtvtZtGiRWzatOmep68Jjx6fz8fY2BjV1dV0dXVRWFjInj17WLduHUuXLqWiokLeFi1aRGJiovy4sLAwORPs9u3bWbdunVxG44vcCgoKiIyMJCIigoiICIaGhgDkqb9z18MJn43D4aCxsZHq6mqCgoJYsmQJWVlZs6aXSpIkLy+7efMmubm5rFq1asERzUDJl3fffZfBwUG+9rWvsXnzZkJDQwEYHx+nsrJSnvq7ePFioqOjUSoXTtYpSRLt7e384Q9/4MSJE2RnZ7N7926WLFly10RAdrudGzducP36dbk+Z1xcHEqlEofDQVtbG1euXMHn87FmzRry8vLmTV0NLHtoamrCaDSyatUqUlJS5p337XyWqb+Sf5rzwYMHaWxsZPHixezevZvk5OQFRy0/j8869dfpdFJdXU11dTVRUVGsWLGC9PT0eZ2Y09PTHDt2jK6uLsrKyigqKqKtrY3KykqCgoLYuXMnr732mpxl2mAwEB8fT3R0NI2NjbS0tGA0GsnLyyMqKgqlUonX66W7u5uLFy8C8NRTTz1SQfyD8MV+6g9AoPcgIiKC6Oho1Go1ExMTDA8PMzk5idefdc/tdhMUFERWVhY5OTmzagsplUrCw8PJz88nKysLq9UqZ+BSKBRyb1NgCwoKIjIykry8PDZt2kRpaSkDAwPU1dVhMpme+GF2QRCEx5FCoSAsLIzk5GSysrJYunSpXIogOTmZs2fP8tFHHzE6Ogr+Gn6pqan89V//Nf/3//1/8/TTT+P1ehkcHEStVvP888/zyiuvkJOTQ1hYGJmZmURERMx9WeExo1ar0ev1aLVaIiIiSEtLIy0tjdTUVPnfaWlpZGZmsmLFCr7xjW/wox/9iL/7u7/jRz/6Ed/4xjcoKyuTy9fNfMzn3VJTU0lJScFoNBIdHU1sbKycI0On09129Ea4f4Fpr3q9Xp6dN3dqqyRJuFwurFYrbrcbvV4v5ziZyePx0Nvby7Fjx6ipqZHbqp988gnvvPMOb7/9NocPH6a5uZmpqSkaGxs5evQox44do7Ozc8HZer29vbzzzjt8/PHHxMbGsmPHDlauXElERMRdrwGlUolKpZo1ohcYedNoNISGhspTmW0226zppQFOpxO73Y5CoSA4OHheeccHwWw2U1tbS1VVFcHBwaxateqRC8T0ej0hISEo/XlubpdkKjB6GvhdUqvVuN1uvF4vRqORMn8d3ZmBv1arlYPaoKAg+vr6GB8fn3VdBka4AyO2d7sWHnePdKDq89c7q6mp4X/9r//Ff/7P/5lPP/2U0tJS/uZv/oYdO3bItYZCQkLQarW3HYZXKBSEhIQQHh6O1+vF6XQueGHNpNVqMRqNGI1G7HY7k5OT8nC/IAiC8OhR+KerKZVKdDodMTExLF26lMLCQqxWKy0tLQwODsr7azQaUlJS2L17N//1v/5X/u3f/o1/+7d/47/9t//GK6+8gl6vZ2hoiLi4OPLz8++px114dCmVSmJjY1m3bh0vvfQSa9euJSoqCrVaLbcfAlugQZ+UlER+fr68BaaUL/SYz7sFGp+BaYVZWVls27aNLVu2UFhY+IUmk/mq0+l0REZGEhoaisvlYmpqal4WVUmSsFqtTExM4PP5iIiIWDBQDZS76uzsZGxsjI6ODv70pz/xL//yL/zTP/0T//zP/8yvfvUrqqqqGB0d5fr167z55pu89dZb1NXV4XA45Ofy+Xz09PTwxz/+kX379hESEsJLL73Epk2b7rk8i1arJSQkBJ1Oh8fjwTGjnI1WqyUqKorg4GCsViujo6OzXj/AYrHIWdHDwsIIDQ1F9QADRkmS6Ozs5OrVq0xOTlJQUMCyZcvuOgr7sOn1eiIiIggJCcHhcMjlreYaHx9namoK1YzM0aGhoWi1WtRqNVqtdl6sAhASEkJERISc+Gpm9l9JkuQ1soFOk4We40ly96v9S+Dz+Zienub69ev85je/4R//8R/54IMPUKvVfO1rX+M//af/xMsvvyxn2QoODiYuLg6VSsXU1BRms3nBINTtduPwZw/W6/X3/IWTJEl+zFeh90IQBOFJEeikDASYgR/+mQINidzcXCoqKuQ6gBMTE1y4cIHh4WGKioooLS29598N4dGkVCoJCwtjyZIl7N69W663frvfdYV/1pVWq5XXKN/r1MfPKjD6pVAoiI+PZ9OmTTz33HNy1lbhi6FWq4mMjCQqKgq73c7AwMC88lNer5fx8XEmJyeJjo4mOTl5weBA6V92sHHjRr71rW/x6quvsm3bNjZv3syWLVvYsmULa9asISUlBYPBQGpqKitXrmT58uUkJibK15TXn7n8rbfe4t1330WtVrN79262bdtGSkrKvOmlt6PRaDAYDAQFBeFwOLBYLHIwpVariYqKIjExEYVCweDg4Lzzxj/1d2xsDJ1OR1xc3ILn/UUym83U1NRQVVVFaGgoK1euJDk5+YF/3+5X4LNOSEjA4XDcNuFZb28v09PTREREEBsbS2RkJNHR0RgMBqxWK8PDwwsGuC6XC7vdjsfjITg4GN2M+rZef0lNu91OWFjY565V+zh4pM5O8q8FuHLlCm+88QY/+clPOHToEEqlkm3btvEXf/EXvPzyy5SXl2M0GuXeiPDwcDIyMtDr9XIR3rlF2V0uF/39/fT19ck9pIHF7bfjcrno7u6ms7OTqKgo0tPT77ouQBAEQXh0+PzlSEZGRvB6vQQHBxM8o/xEgMKfTEXjL0PW0tLC+++/z+XLl0lJSWH9+vUkJyfPfZjwGFKr1YSHh5OYmEh4ePgj1/kwc9aWTqcjNjYWo9F4x4BauH+BjoD09HQ8Hg9tbW309vbKo4uB0dTGxkb6+/tJS0sjKytL/hycTicTExNyezM5OZmtW7fyve99j7/4i7/gBz/4gbx9//vf55VXXqG0tFQu9bJ371527dpFTk4OOp0Ot9tNR0cHb7/9Nu+//z4ajYaXX36ZnTt33ncnhcI/CmowGDCbzYyPj8vBlFKpJDIyksLCQkJCQmhqamJgYGBWsDU9PU1rayu9vb2Eh4eTlZUlr7X1er1MTEwwMTGxYID2WfX29lJdXc3k5KTcaRgWFjZ3N5nVaqW1tZUrV67Q0NDwwDLgut1uxsfHmZ6exu12I0kSKSkpZGZmYrFYaGxsZGBgQA46A9fNzZs3mZiYIDs7m8TERHQ6HUlJSSQnJzM1NUVDQ4M8Uj9TT08P7e3t2O12UlJSiI2Nle9RVquVsbExAKKjo+UpyE+yR+LsJEliamqKS5cu8cYbb/Czn/2Mjz76CJ/Px6ZNm/jOd77D1772NVauXCl/2DM/mNDQUAoKCigoKMBsNnPu3DmqqqrkkVWHv6bVqVOnGBkZISsrS66VNTU1RWtrK11dXXKPk9vtZmJigqtXr/Lhhx/S0tJCVlYW5eXlhIWFPfEXhSAIwuNC8pcLuXTpElVVVfJ93Ov14nK56Ojo4OOPP+bWrVtER0dTXFw8rw5qIPun1Wqlo6ODQ4cO8f/8P/8PR44cITg4mG3btrFmzRqCgoJmPU54fClnrOF7lCn809jFbK4Hw2g0snjxYoxGI11dXVy8eJHu7m55XerNmzc5d+4cVquVRYsWkZ2djU6nw2w2y23Wf//3f6e6uhqfz0dCQoKcKyU7O3vWlpqaSlhYGFqtlvDwcJKTk0lOTiYsLAyPx0Nrayvvv/8+Bw4cwOv1smXLFp5++mmioqKw2WxMTk7KgfHMqby3ExsbS1xcHCaTSc7Lgv+aCg8PZ/HixSQnJ9Pa2sqJEyfo7u7G7XbjdDqpqanh8uXLOBwO8vLy5GUPVquVa9eu8cYbb/Bv//ZvXL9+HavV+rmXxNlsNm7evEltbS0Gg4Fly5aRlpZ2x+C8ra2Nd955h1//+tdcunQJi8XyuY9jLkmSOHfuHL/85S/593//d+rr63E4HCQmJrJo0SI58dGZM2fkEVKn08mFCxe4ePEikiTJ56LRaMjIyKCiogKdTsf169c5e/Ys4+Pj+Hw+vF4vIyMjHDlyhIaGBhISEigpKZkVqE5OTtLT04NGoyEpKemO78+T4pHI+mu326mqquK9997j8uXL6HQ6ufbU+vXrKSgoIDY2dl6AGqD0r0WSJIn+/n5aWlro7u5maGiI7u5uKisrOXjwIOfPnyc2NpYXX3yR1atXo9frqaurY9++fRw/fpy6ujqam5upqqri5MmTHDp0iMrKSiIiIti9ezcbNmyQM28JgiAIXz6Px0N3dzdvvPEGx48fp6mpiZaWFurq6jh//jyHDh3i+PHjWK1W1q1bx4svvkh2drb8w2+z2bh48SIHDhzg+PHjfPzxx3zyySfU19cTHx/PCy+8wPbt20lLS3vkRt6EJ48kSTidTkZHR7FarSQkJIgEXg9QYCq3yWSio6ODrq4uxsbG5Iy1hw8fpqqqitzcXPbs2UNpaSlBQUH09/fz0UcfsX//flpaWjAYDHKytUDHwtwtkPW3s7OT9PR0ysvLiYuLw+fz0dHRwb59+9i3bx/Nzc0o/WVjuru7uXz5MmfPnpW3uro6vF4v0dHRd+w8UyqVdHR00NDQQHh4OEVFRXIbVu1PImq1WmloaKC1tZXJyUmGhoa4du0ahw8fpqamhvT0dLZv305FRQUGg4Hx8XGOHDnC+++/z40bN4iOjiY7O3tWCaeAvr4+KisrGRwcJCcnh6VLly643lSSJJqbm/nwww+5desWhYWFPP/882RmZt4xELtw4QL79++nv7+fgoICSkpK7mvWY09PD5WVlYyMjJCfn8/SpUvlUWP8x2Wz2fjNb37DgQMHaGxsJDExkfT0dMLDw9FqtUxOTtLc3ExXVxcTExMMDAxw+fJl3nvvPerr61mxYgUvvfQSubm5aLVa9Ho9Go2GiYkJWlpa6OjoYGhoiMHBQerq6jh8+DCHDh3CYrHw/PPPs3Xr1lk1eJuamvjoo4+QJIkdO3aQm5t7z9PBH1ePRKBqs9loa2tjYGCA7OxsNm3axMaNGykuLiYmJuaua0MV/oLM4eHhBAUFYTab6ejooLGxkVu3blFTU0Nvby/Jycns2rWLzZs3k5iYiNef5rmyspIbN25QV1cn719fX8/U1BRZWVm88MILbN26ldTU1Cf+ghAEQXicBKb2VlZWUltbS1NTE/X19XL5gK6uLkJDQ1m/fj0vvvgi5eXl8npVSZIwm80cOXKEP//5z9TX1zM0NERwcDDLli3jhRdeYNOmTWRkZIh7v/BQiED14VL4M9oaDAbcbjeDg4M0NzdTV1dHXV0dQ0NDZGVlsWfPHp566ik50JuamqKmpoZbt26hUCgoKiqiqKhowUAsYHp6Ws76m5uby+LFi4mKisLj8dDZ2cnp06fp6upCp9Oh0Wgwm8309PTQ2dkpbx0dHZjNZoxG46zpuAvRarWMjY1RX1+P0+kkIyNDHoVTKpXo9XoiIyPxer309vbS1tZGQ0MDNTU1DA0NkZmZybZt21i3bh3x8fGoVCosFgs1NTVUV1djt9upqKigtLR0wUB1bGyMlpYWHA4HBQUFLF68eMGpvB6Ph6qqKq5cuYJer2f9+vWsWrWKqDvUinW5XJw6dYqzZ89iNBp55plnyM3NveuSvpmGh4dpaWnB5XJRUlLC4sWL5y0L8Xg8nDp1irq6OlQqFcuWLSMvL4/Q0FBCQ0PlhEo9PT00NzdTX19PTU0NIyMjlJeX88orr7B06VJ5NqZKpcJgMBARESG/742NjfJv1s2bN9FoNGzatIkXX3yRvLw8eaq5xWLh4sWLnD17loyMDF544QW55NCT7JEIVPH3aqWnp7NixQpKSkqIi4uTEx7d7kKdSaVSEeqvh5qUlERMTAwhISEEBweTkJDAsmXLeO6551i/fr28IF3hX5MUHh4u1y4KCwsjJiaGvLw81qxZw7PPPsvTTz9NSkrKHXt2BEEQhIdP4U92ExERQXJyMnFxcYSGhhIeHk5KSgpLly6VE5qUlpYSFhY26zfF6/UyOjqKJEmUlJSwcuVK1q9fz5YtW1i6dCnx8fEiSBUeGhGoPnwajYaIiAgSEhLkckDBwcEkJSWxYsUKeep/IFjDf9/Bn6G1qKiIlStXkpGRcddASavVkpaWxqJFi8jIyJA7zbxeLzqdjuzsbJYsWUJ5eTmlpaUUFxdTUlIya1u0aBElJSV3zbWiUqnw+Xx0dXXR09NDeHg4mZmZ8j1QpVIRERFBUlISRqOR0NBQ9Hq93GZ+9tln5fIwgfZv4H6r0WjIy8tj/fr18sjnzPuqQqFAkiSCg4PJyMigtLSUtLS0BY/X5/NhNpsJCQmhvLyc5cuX37XNPTo6yieffEJTUxMrVqxg48aNGI3G+571EhwcTFZWFosWLZo3GBV4j7xeL0FBQZSVlbF69Wo5htD6sycnJiYSGxtLUFAQer2elJQU1q1bx86dO1m2bBlRUVGzjkur1RIbG0tqairx8fGEh4fL12BJSQmbN29m27Zt5OfnExoaKgeibW1tfPTRR/T398vJueYG1k8ihfRFT+j+DCRJwuPx4PP5UKvVdxw9vRuvv/TM9PQ04+PjWK1WdP4SBVFRUej8dcjwv25gf4vFwuTkJCaTCfzrXgOBq9Zf9kYQBEF49Ph8PpxOJ06nU87Q6XK50Ov1xMTEEBERIU+5mvvb4vF45LrcBoMBg8GATqdD6y8hMHd/QXiQAlUP6uvr5VGZ9PT0ubsJXzBJknC73ZjNZkZHRzGbzWi1WuLi4oiIiJi39CzwOY2OjqJSqYiNjZ0VVCzE6/XicDhwu91oNBp5MCbQBrbZbLjd7jvecyR/2SKdTifPNrwTs9nMgQMHeO+994iNjeUb3/gGK1eunDWrJPDagftgoM0cGRk5r0KGz+fDarUyODiIz+cjMTHxtuft8ZfFcbvdaLVagoKCFtzP5/PJ2djV/gobC92rZ7p27Rr/8i//wvDwMN/61rfYuXMn0dHRd3zMXJ4ZtXN1Ot28zzhgamqKgYEBdP7sxzMTGEn+Ortms5nh4WHMZjNBQUEkJiZiMBjk0eu5Ateb1WplfHyc8fFxAGJiYuQkSTN/f8xmMwcPHuQPf/gDMTEx/PCHP6S8vPwr0Yn6SASqD4LP55O3QK/IQhdLQCBoDSxODwzR389FLwiCIHy5vF4vXn9x9Hu59+N/jCRJKP1ryQThyyIC1S/XzLbg3e4fgX0V/oRXX0R7MdAkv91z3e3vc0n+dY1/+tOfqK+vZ+3atbz44oukpqbOO6/AvfNezxv/qO3djkXyl1q6k/s5L0mSOHjwIG+88QaZmZm89tprlJaWon9ANYbv5XOee93cayenJEn4/ImU8L+fc1/D5/PR0NDA7373OxobG9m1axd79uwhIiLinl7jcbfwVfgEUPoXi2v9dc9u94ULCFxYWn+ttHu9yARBEIRHh0qlku/j93Lvx/+YwGweQRC+uma2Be92/wjsey/B2r1SKBR3fK67/X0uhUJBeno6mzdvZvny5QQFBeF0OuXAaKbAvfNez/te28n3us+97Ic/cAsKCmLFihVyDoE7TRP+vO7lc5573dxuv7kU/k6BwG/WQq8RGMWOiopi8+bNrF+/fsE1wU+qJ3ZEVRAEQRAE4XEiRlSFL5okSdjtdsxmM5IkERYW9ljX5JX8Jcnsdru8nnjm9OQnjeRP+heYjh4REfGVmPIbIAJVQRAEQRCER4AIVIUHZWZz/3ENUgOepHO5F5IkyVOovwrnO9Ptx/YFQRAEQRAEQXjsBYKcJyHQeZLO5V4o7rA+9kknAlVBEARBEARBEAThkSICVUEQBEEQBEEQBOGR8sADVclfK8hms2GxWLDb7Xg8nrm7zRNI9ex2u/F4PLPmo9+J5K8J5Xa75VIzM//m9XrxeDxyOQJBEARBEARBEATh0fJAkin5fD6mpqZoamqipaWF0dFRrFYrHo8HlUpFeHg4CQkJ5OTkkJubO69YsMvloq+vj9raWvr6+ggPD6e8vJzCwsLbpsyWJInJyUnq6upoamrC6/VSUFDA4sWLiYiIAMBkMlFTU0NTUxPJycmUlZURFxf3RGcLEwRBEATh8SCSKQnC/8vefYfJUV6J/v/2dPf0zHT35JxzUJikjBKSEEkICUlIIgmwWQO21/b19a7X6bes73rver04gJdoQAQhBAihLCSN0iiN0oxmNDnnnKdzqN8fd7o8SQkQSPB+nvQlpNAAAP/0SURBVKceY011dXV3dXWdOuc9ryD8nfK55557buw/flEOh4Pa2lo++eQTPv74Y06ePElZWRnV1dWUlpZy/vx5Tp8+zcWLFxkaGiIgIAC9Xi8HjEajkYKCAj788EN27NhBeXk5Go2GxMREtFrt2KcDwGazUVxczPvvv8/HH39McXEx7u7uJCcn4+fnB0BnZye7du1iy5YtDA0NkZSURGBgICqVauzmBEEQBEEQvlKSJGGxWOQb/GFhYfLNdkEQhG+bidOTX5DrRNve3k5nZydBQUEsW7aM73znOzz++OM88MADxMbGcunSJTZt2sTOnTtpbW2VJyC22+309fXR2NhIXV0dZWVlXLhwgYaGhrFPJRsaGqKyspKCggIqKytpaGigtbUVo9Eor2O32+np6aGhoYGuri4sFoso/xUEQRAEQRAEQbjJ3JBA1UWSJDQaDSkpKdx77708+OCDrF+/nscff5zvfOc7zJo1i5qaGg4fPkx1dTVmsxmGM7JmsxlJkvDx8cHd3Z3a2lqqq6uxWq1jnwZJkuju7qaiogKTyYS/vz8ajQaLxYLNZpPXUygU8lxEgiAIgiAIgiAIws3phgaqrnl/tFotAQEBBAcHExoaSlxcHLNnz2bBggXodDpaW1tpbW2Vg1Cn04nVakWhUMiP6evro7S0lN7e3rFPg9VqpbGxkerqajw9PUlMTMTHxweLxYLFYhm7uiAIgiAIgiAIgnATu6GBqoskSXLQ6ubmhkqlQqfTERAQgEajGZfldDqdclluYGAg8fHxaDQaysvLaWpqGpcRHRgYoLy8nPb2doKDg0lMTESv12O1WkdlVAVBEARBEARBEISb31cSqCoUilH/3+Fw0NXVRUVFBUajkZCQEEJDQ3F3d4cRGVVXoJqWlkZwcDC1tbVUVFTIf2M4CG5vb6e4uBir1UpCQgJRUVGo1WrMZrNcQiwIgiAIgiAIgiDcGm54oOp0OhkYGKClpYW6ujoqKys5d+4cO3bs4NixY4SFhbFo0SKSkpLQaDQwHMi6glEfHx8SEhKIiIigvb2doqIi+vr65O2bzWbq6+upqqqSOwMHBgYCiNJfQRAEQRAEQRCEW9ANDVQVCgUmk4mSkhK2bdvGW2+9xauvvsrzzz/P66+/Tnd3N8uWLeO+++4jJCREnibGFag6HA48PDwICwsjISEBlUpFWVkZTU1NOJ1OAHp6eiguLqa3t5ewsDCioqLw8vKSy4dFZ19BEARBEARBEIRbyw0NVBnOatbW1nLkyBF27NjB3r17OXPmDO3t7Xh5eRESEoJGoxnVkddut2M2m3E4HLi7uxMQEEBycjLh4eHU1dVRUlKCzWbD4XDQ1tZGaWkpCoWClJQUQkNDUavVKBQKLBbLhF2CBUEQBEEQBEEQhJvXDQ9UPTw8SEtLY8WKFTz++ONs2LCBVatWkZGRQWNjI6+99hqffPIJTU1NOBwOeXyqK1BVKpV4eHgQGRlJdHQ0ra2t5OfnMzAwgMFgoLa2ltraWvR6PWlpaQQFBaFSqXBzc8NisYgxqoIgCIIgCIIgCLeYGxqoSpKEl5cXU6dOZc2aNTz11FN8//vf51e/+hXPPfcc9913H62trXz44Yfk5ubS398vz6FqMplwOp1oNBq8vLwIDQ0lNTUVlUpFeXk5jY2NdHd3U1ZWxtDQEPHx8cTHx6PT6XB3d5cDVZFRFQRBEARBEARBuLXc0EDVxZUV1el06PV6AgICyM7OZt26dUybNo2WlhZOnz5Na2srNpsNi8WCyWRCkiQ0Gg2enp74+/uTnJxMWFgYzc3NlJWV0d7eTm1tLV5eXmRkZBAaGopKpUKtVqNWq+USYtd4VkEQBEEQBEEQBOHm95UEqhOV3rq7uxMdHU1qaipms5m6ujp6enqwWq2jSn/d3d3lJSoqivj4eDo7OyksLKSyspLGxkb8/PxITEzE29sbNzc3NBoNHh4eAJhMJtH5VxAEQRAEQRAE4RbylQSql+NqnqRQKHBzc0OhUOB0OjGbzVgsFhQKhVzGq1KpiIqKYsqUKbi5uVFUVMTRo0fp7u4mOTmZqKgoNBoNbm5ucmDLcDMnUf4rCIIgCIIgCIJw6/hKAlWFQjH2n7Db7TQ2NnLp0iXc3d2JjIzEz89PHltqsVhQKpVyB1+FQoGvry8pKSkEBwdz6dIljh8/jlqtJi0tjcDAQJRKpZxRdc3J6gp6BUEQBEEQBEEQhFvDDQ9UJUnC4XDIi8lkoqmpiX379vHmm2+Sn59PcHAwM2bMIDg4GIVCIQeXSqVSzpK6squJiYlMnjyZvr4+uru7iYmJITk5GZ1OBzAqUJUkCaPRKAJVQRAEQRAEQRCEW8gNC1QlScLpdDI4OMipU6d48cUX+dd//Veee+45/u3f/o3nn3+egwcPEhgYyIoVK5g7dy6+vr5IkoTVasVut6NSqeRAleGmTNHR0WRmZuLl5YVOpyM1NZWIiAg5g6pQKORmSpIkjSr9dZUau/ZtorGzgiAIgiAIgiAIwtfrhgSqCoUCT09PgoOD8fX1pbOzk6NHj7Jt2zb27dtHQUEBCoWCO++8kx/96Ec8+OCDxMbGymW+Xl5eREREkJSURFBQkByoKhQKfHx8yMrKYvHixcyfP5/s7Gy5ZJjhjKpOpyM6OpqkpCQCAgLk0mO1Wk1ISIg8ptXLy2vCsmRBEARBEARBEATh66OQbkBa0el00tvbS0lJCVVVVQwODuJwOGA4WPT09CQgIICoqCiio6Px9fVFpVKhUCiwWCw0NDRQVVWFSqUiNTWV8PBwlEolDGdFOzs7KS0tRaFQkJCQQHBwMGq1Wv774OAgVVVVNDQ0EBQUxKRJk/Dz82NoaIjy8nLq6+sJCgoiLS0NPz8/eduCIAiCIAhfF6fTSX9/P8XFxXR0dJCdnU1sbOzY1QRBEL4VbkigyvDJ1mazYbfbR81j6mqMpFQqUalUKJXKUVlN15hWu92OQqGQ1xnJ6XRit9sBUKlUcjbVRZIk7HY7DodD7hjs5uZ22X8XBEEQBEH4uolAVbgRHA4HNpvtstfVwo1nt9uxWq0olUrc3d1FRec1umGB6q3ObrdjsViw2WyoVCo8PDxQqVRjVxMEQRBuMg6HA6PRKM/FrdFoxIWZcEsQgeqtyel0yj1R3Nzc8PT0vGmuGY1GI9XV1bS1tRESEkJ8fLzcgNTFNTWk1Wr9wudMp9OJ1WqV+8NoNJqbKjBz9cJxNVr9ovs38r1zDX10DWUcqbe3l7KyMgwGA/Hx8URFRcnVoMLliUB1BLvdzuDgIC0tLTQ0NNDV1YXRaESj0RAWFkZcXBzh4eF4eXmNysQ6nU4MBgPNzc20tbWNm7dVkiTc3NwIDAwkJiYGHx+fz30CEARBEMaz2+309fVRV1dHS0sL3d3dWK1WdDodkZGRxMXFERISIjfeG8lkMlFUVMTAwMCoCiCGz9+u/gaxsbFotdpRfxeEL5MIVG8tdrud3t5e6uvrqauro6+vD7VaTVhYGImJiYSHh+Ph4TH2YaOM3EZPTw9Op3NckMNwDxYAnU5HRETEZc9nIzmdToqLi9m2bRudnZ0sWbKEhQsX4ufnB8M39To7O6murqa+vp7BwUG0Wi1RUVHy0Dp3d/exmx1HGm5e2t7eTkNDA21tbfT39wPg7+9PVFQUsbGx+Pv7X/b6V5IkTCYTbW1ttLW1ARAREUFYWNg17cOVSJKEzWajra2NxsZGWltb6e/vR5Ik/Pz8iIqKIiYmhoCAgGu6weAcbhbb0tJCc3Mz7e3tDA0Nydf6sbGxJCQkoNPp5M+to6OD7du3c/r0aTIyMli1ahXh4eGisvMqRKA6zGaz0dzczOnTpzly5AjFxcX09/fjcDhwOp0EBAQwZ84c7rrrLrKyskY1cLJarVRWVrJ161ZycnIYHBwcV87s7u7O3Llzeeihh5gyZcpVT1yCIAjCtbFardTW1nLw4EGOHj1KTU2N3D0eICoqittvv50777yTSZMm4enpKT/WbrdTX1/Pb37zG6qqquR+CiN5e3uzePFiHnvsMRE0CDeUCFRvHXa7nebmZnJzczl48CDl5eWYzWYA/Pz8mD9/Pvfffz+TJk3Cw8NjwuCT4Yxnfn4+7733Hvn5+fLQt7EUCgWSJBEXF8cDDzzA0qVLCQwMHLvaKD09PXz44Yds376d+Ph4Hn30UbKysvDw8MBms9HQ0MBnn33Gnj17aG1tla95o6KiWLp0KXfeeScJCQlXDYgHBwe5ePEiOTk5nD17ltbWVqxWKw6HA09PT5KTk1m6dCmLFy8mMjJyVDAoSRJms5mOjg6Ki4vJzc0lPz8frVbLypUrWbZsGf7+/qOe73q4MqgFBQUcPHiQ06dP09raisViwW634+HhQVJSEnfccQdLliwhOjr6qpnO3t5e8vLy2LdvH0VFRfT09GC327Hb7Wg0GqZOncrq1auZO3euHJxbLBZycnJ44403sNlsPPXUUyxZskTc/LwK5XPPPffc2H/8NhoaGuLMmTNs3ryZc+fO4e3tTXx8PBERESiVShoaGigsLKS3t5fQ0FCCg4PlL67FYqGqqordu3dz9uxZGG4axYgpcdzc3IiKimLq1KmEhIRc0x0bQRAE4cqk4QZ6+/fv549//CM9PT2Eh4cTFxdHcHAwNpuNmpoaiouLsVgsxMTEEBgYKF8I2mw2SktLeeWVV2hpacHDw0PuaeDKrmo0GmJjY8nMzMTX13fMHgjCl8eVmers7MRgMBAWFiaOuZuQJEm0t7ezb98+tmzZQkVFhTyrhF6vp7m5mYKCAqxWK9HR0VfMJNpsNjo6OigtLaWnp0fu4eJaXGWknZ2dNDQ0oFarmTJlCqmpqVcMcpxOJ/n5+Xz66aeYzWbuuOMOZs2ahbe3Nw6Hg+bmZj788EPeeustOjo6SElJITk5GYVCQUVFBRUVFahUKiIiIvD29r5i5q+hoYF3332Xzz77DLPZTEREBDExMXh7e9PX10dZWRkVFRVotVri4uJGzbpht9u5dOkSH3/8MVu2bOHo0aNy0J+SksKUKVPGlSpfr/7+fl555RV2796NyWSS98/Hx4fBwUFKS0spLy9HrVbLmdCJbha4tLS0sG/fPo4ePYpSqSQmJoaoqCi0Wi3t7e1cuHCBhoYGYmNj5YywUqnE29ubrq4uCgoKcDqdTJkyBW9v7ys+17fdLRmoOhwOTCYTdrsdNzc3FMMNmr4Im81GT08PFouFadOm8Z3vfIeHH36YZcuWMWfOHFQqFZWVlTQ1NaHVaklMTMTPzw+FQoHZbKaqqoq8vDxUKhXr16/n4YcfZsmSJSxevJjFixezaNEiZs+eTXx8PFqt9opfeEEQBOHauUq6hoaGWLNmDU8//TSrV6/m7rvvZurUqZjNZsrLy2lrayMoKIjJkyfLpWQWi4WCggL27t1LcnIyzz77LPfff7987l68eDELFy5kxowZREREfOESNOHm4boZ4cqifxnXEl/UrRaoSsNNKp1Op3w99m1gNps5efIkW7ZsobGxkYULF/LMM8+wbt06brvtNry8vCguLqa4uJjg4GASEhLw9PSc8P1xc3NDr9eTkpLC/PnzufPOO0ctd911FxkZGZhMJrq6ukhOTuaOO+4gPj7+iucjg8HAgQMHyM3NJSkpiXvvvZeYmBiUSiX9/f0cOXKEd955h76+PjZs2MAPf/hDVq5cyfTp07FYLBQVFdHZ2UlISAhRUVGjKlHGMhqNNDU1ERERwdq1a9mwYQMrV67k9ttvJzIyks7OTioqKujt7SU9PX1UyavRaGTr1q1s374dNzc3wsLCMJvNuLu7k5WVRUZGxhcOVO12O+Xl5YSGhrJu3To2bNjAqlWrWLRoEdHR0fL40d7eXlJTU4mIiLhiQsl1roiPj2ft2rU88sgj3HvvvSxYsABfX1/KysooKSkhJCSElJQUecifl5cXJpOJ4uJiWltbiYuLu6YM7rfZLRWougYsNzU1ce7cOTo6OggICECj0Uz45b8eKpWKoKAgMjIymD17NrGxseh0Ory8vAgMDCQwMFCeFketVpOamkpoaChqtRqTyURFRQX5+fkEBwezfv16FixYQEJCgrzEx8fL41svd1dNEARBuD6K4S6WERERLFiwgFmzZhESEoJWq0Wr1RISEoKPjw81NTUUFhbi6+vL9OnT8fX1RZIkjEYjJ0+e5OjRoyxcuJBHHnmEzMzMUedvV3b2y/itEW4erkxWc3MzDGfOv+7fZ1eZYkdHx00fqDqdToaGhmhubqa7u1vOBH7d7+FXoampiV27dnH8+HHi4uJ4+OGHmTVrFr6+vvj4+BAUFERjYyPnzp2TrxlDQkImfG/c3Nzw8PAgICCA8PDwcUtISAitra2cOHECu93OokWLWLhw4ajKkIlUVlayc+dOuru7mTt3LnPmzMHHxwen00l9fT2bN2+moKCA+fPn8+STT5KWloaXlxdBQUFoNBoaGhqoqKjA09OTyZMn4+/vf9nn8/LyIikpiTlz5jB58mQCAwPRarXyewFQXFxMY2MjU6dOJTExUR4C5xrvGRUVxerVq0lJSaGhoQGj0UhGRgaZmZlXzBxfjes3IjExkQULFsj75+Xlhbe3N+Hh4QCUlpbS3d1NTEyM/F5cjoeHh1wlGR0djV6vx8vLCx8fH2JjY6murqayshIfHx+ys7MJDQ1FOTzLiUKhoKmpiaKiInx9fcnIyLjic33b3RJpvZEn7v379/Pcc8/xu9/9jqNHj2I0Gseu/rkolUp0Oh1BQUF4e3ujGp7X1fW36Oho0tLSUKvVdHd309XVJXcMczVhslgs+Pr64ufnh7u7+7hFJabDEQRB+NK5SqrCwsLGNbvTaDTExcURExODQqGgp6eHoaEh+e92u10emxUZGYlOpxt37nadvy93kSbcmjo6Ovjkk094/fXXOXToEH19fUhfQtsOV6bWNWbNtbhKya/GdTF7sx9vFouFS5cu8e677/Liiy/ywQcfUFZWhslkuubXeiuSJImWlhaqq6txd3dnypQpJCYmotVqUSgUcjOlGTNmEBYWRl1dHQ0NDVgslsseX4oR0zaOXQYGBjh37hyVlZVERESQnZ1NUFDQFa8nJUmioaGB2tpa/P39SUpKkrOSJpOJ2tpaSkpKcHNzY9q0afIwN4bPp4mJiUyaNAlJkuRGS67xtxNRq9UEBwcTGBgoD59gOAj39fUlKSmJ8PBwHA4HLS0tmEwm+bEajYZFixbxxBNPMH/+fPz8/JCGh819WZRKJSEhIfj7+4/bP39/f1JSUoiNjcXpdMrja69EoVCg0WjGdfhVKpX4+PgQEhIil/uO/ZyCg4NJTEwEoKqqip6engl7Iwj/z+WP8puEqyPZZ599xr/8y7/ws5/9jFOnTjF16lQWL16Mj4/Pl3Yyv9KPg3J43iM3Nzd5ca1ntVrp7+/HYrHIWVhBEAThq3O5czfDFyNqtVq+EBu5nqtsGCA8PPyKpXTCN8vg4CDFxcWUlpbS0NCAwWD4whfHkiRhMBgoKSlh7969fPLJJ3zyySccPHiQhoaG6wrgrnRM3wxcmbCmpiYKCwvZsWMHL7/8Mp988gn19fVXvdi/VZlMJhobG2lubkav15OQkICvr++oz8rd3Z3Y2FgCAwPlrP3nPb4uXbrEmTNncHNzIzMz86pjUxm+idDc3ExXVxd+fn6jug8PDg5SU1PDwMAAYWFhpKam4u3tPerxrlkqvL296e3tHRdcTuRyx6ubmxvu7u5yQDc2aePm5oaXl5d8k3CibXwZLrd/iuGbC2q1etz1/fWy2+3U1tZSUFDA4OAgCQkJBAQEjMqku2YSCQgIoLm5mYaGBuzDjf+E8W7arr92u5329nbOnj3Lrl27OHfuHCqViuzsbJYtW0ZWVhZBQUF4eHhgtVrp6uqip6dHnsfoWqhUKnx9fQkMDLzs2AGXpqYmXnnlFTZv3sy0adP44Q9/yMyZM1Gr1dTW1vLOO+/wySefEB4ezu23305gYCABAQHExsYSGxuLr6/vhCUfgiAIwo3jcDgoLS3lv/7rv9i3bx+rVq3il7/8JdHR0UiSRGNjIz/4wQ84fvw469evJzExEV9fX0JDQ+W57r7o+Cjh5lRSUsKLL75IdXU1qampzJ49+6pdVK9GkiS5eUx5eTlGoxGFQoFeryc7O5tJkyaNfcg4rvF+AwMDxMbGEhQU9LkCnBvN4XDQ3t7OuXPnKC8vx2azyRmltLQ05s+fT1ZWFoGBgd+o65+enh42bdrE66+/TnBwMN///ve54447RgV7NpuN4uJifv3rX3Pq1CmeeeYZnnrqKaKioq449nGs7u5uXn/9dd5++20SExN55plnWLBgAXq9fuyqo7S3t/Pyyy+zY8cOlixZwlNPPUViYiJKpZK6ujreeusttmzZQnx8PM899xwzZswYdQ0sSRLbtm3jhRdeYGhoiIcffpiHH36Y0NDQUc9zLfr7+zlw4ADPP/88zc3N/O53v+OBBx647Hn14MGD/OEPf6C1tZUNGzawYcMGgoODx672pTGbzRw8eJA//vGPtLe38/3vf5+HH35YnsLnSux2O2azGZPJhMFgoLKyki1btrB7924yMjL4p3/6J2bNmiVn2xl+b8+dO8cLL7xARUUFP/7xj1mxYsVVbz58W910gaprzMjZs2fZv38/Fy5cQKlUkp2dzZIlS8jMzJRry113ZOrr6/noo4/Yt28f7e3tYzd5WX5+fixevJgHH3yQlJSUy548JEnixIkT/OEPf6CiooKVK1fy3e9+l/j4ePki6M0332Tbtm2YzWb5rpW7uzshISHMmzeP5cuXfykDwgVBEIRrZ7FY2LZtGy+++CKDg4M8/fTTPPHEE2i1Wux2OxUVFfzwhz/k3Llz8lhANzc3PD09iYuLY/HixSxbtoyUlJRxJVzCra2kpIT/+Z//oaKiAqVSiaen55cSUDkcDiwWy6hST7fhcYjXMjWdNDznozQ8h+/NfNy5eodYrVacTieSJKEYLmNNTk7mvvvuY86cOTftONvPo729nb/97W+8+eabJCYm8pOf/IQFCxaMCjTsdjuVlZX86le/Yt++fTz11FP84Ac/ICEh4bLXmmNJkkRubi5//vOfKSsrY82aNTz++OPExcVd9ZioqanhT3/6E6dOnWLlypU8+uijREdH4+bmRmVlJS+99BI7d+4kKyuLX//612RkZIzdBHv27OGFF16gtbWVNWvW8OSTTxIZGTl2tSuSJIn6+nrefvttNm/eTGRkJL/97W+ZOXPmZd+HrzpQbWpqYtOmTbz55psEBwfzb//2b8ydO/eqU/Iw3O3YNeVNS0sLjY2NGAwGFixYwBNPPEFGRgZ6vX7c51VWVsarr75Kbm4u//AP/8BDDz00Lqst/D9XPtK/Qq669b179/L888/z4osvUlVVxdy5c/npT3/KP/7jP7J48WKio6PHdc318vIiOTmZ+fPnc8cdd7B06dKrLnfccQcLFixg0qRJ+Pj4jDuIRmptbeXYsWOUlJQQGRnJzJkzCQwMlEsEAgICWLRoET/4wQ/48Y9/zFNPPcWDDz5IamoqLS0tbN68mVdffZXTp08zODg4dvOCIAjCDeBwOKiqqiInJ4fGxkYmT57MjBkzRnWv9Pb2Zu3atfzTP/0Tzz77LN/97ndZvnw5ISEhFBUV8be//Y033niD0tLSUdsWvjkkSZKDS7PZLGdIPu9isViw2Ww4nU55cTgc2Gy2q27b9fxWq1Ve/2qP+boWs9mMzWaDMUOnXK9VkqQJx+jd6lwzT7gyyGNLWV3c3NxQqVTyseUK5K9VX18feXl5lJaWEhcXx4wZM646NtXFYrEwNDSESqVCq9WOGkdpt9sxDY8jdo2jnIhSqUSpVMrjra+nbN1laGiIwsJCTp48idPpZNGiRcTGxl72Ob9qZrOZoqIijh8/jlKpZP78+SQkJFxzF16TyURdXR0XL16kpKSEmpoa+vv75feMMUNNXDQaDXq9HudwQ7LP895+W9wUGVWz2cylS5fYsWMH58+fR6lUMmnSJKZPn86kSZMIDw+X70hM9IHbbDb6+/sZHBzEZrNNuM5YrhOoTqfD19d3wrp4abiEZ/fu3bz00ksMDAzw0EMP8dBDDxEdHY1KpUIabvQ0ODiIabh+3/Vvzc3N7Nu3j+3bt2Oz2Vi9ejVPPPEESUlJN82XVBAE4ZtIkiRaW1vZuHEjmzZtwsfHh6eeeorVq1fj4+Mjr2O1Wunu7sY+PN2Zw+HAaDRSWVnJtm3bOHz4ML6+vjz55JM8/vjj36jM0Ledq/S3pqaGuLg4MjMz8fPzu6ZA4HKcTif9/f2Ul5ePK/11jS+80u+/JEmYTCba2towGAxERETg7+8/drWbgmuIVmFhIfX19djtdhQKBX5+fkyaNInZs2eTlZVFSEjINV/43wpaWlp46aWXePfdd5kyZQo/+clPmDdv3qgbYHa7nerqan7zm9+wY8cOnnzySX70ox+RmJh4ze/FmTNneP7557l48SJr1qxhw4YNxMfHXzYTOVJhYSG///3vqa2t5ZFHHmH16tWEhISgUCgoLS3lL3/5C/v372fu3Ln8/Oc/Z8qUKWM3wWeffcYLL7xAY2Mjq1at4jvf+Q7R0dFjV7ssi8XChQsX2LhxI8eOHSM9PZ0f/ehHTJ8+/YrZyq8qo+pwOCgoKGDjxo0cPnyYSZMm8eyzzzJ79uwrTsUzUk9PjxygGgwGWltbycvLo7GxkYSEBL773e/KU9aMPK80Njby9ttv88knn7BmzRqeffbZayo1/ja6KQLVgYEB9u3bx//8z//Q3NzM4sWLWbt2LdnZ2Xh7e6Mcbul8JdJwh7DreTmubU70oyRJEgMDA+Tm5vLaa69RWlrK0qVLeeKJJ5g6deq4g3ii53bNQ/XGG2+wd+9epk6dyg9/+EPmzZt31fEFgiAIwucjSRL9/f189NFHbNy4kcHBQdatW8cjjzwil7+NNPZutiRJDA4OcurUKV5++WVOnTrFPffcwz//8z9PeEEn3JpKS0t54YUXqKqqYsGCBaxcuVKequLzcgWazc3NNDU1YTabUSgUeHp6kpCQQERExBWvZ6ThZkzl5eV0d3czefJkIiIixq52UzCZTJw/f55PP/2UqqoqdDodCQkJTJ8+nfT0dLkZz7UGZrcKV+nvW2+9RVJSEj/+8Y+ZP3/+qNJfm81GRUUFv/71rzl48CD/8A//wLPPPktcXNxVA01JkhgaGuLNN9/ktddeIyoqiqeffppFixZdcwPRixcv8l//9V/U1tby6KOPsmrVKjlQdZX+7tq1i6ysLH71q19NWPq7a9cu/vKXv9DV1SXPjXqtx6LdbqekpIQPPviAzz77jKCgIB5//HHuuusu/Pz8rvgavopAVZIkysvL2bRpE7t378bPz49HH32UZcuWERQUdMX9G8k1RtViseBwOBgaGqK4uJg333yTs2fPMnfuXH784x+TnZ09qux/ZKC6evVqnn322Zv2htTXbXyE9jXQaDTExsYybdo0IiMjaWpq4tChQ5w6dYq2tja5tORy7HY7/f39tLW10dzcTHNzMy0tLVdcXOv09/djtVpHBZlOp5OBgQFOnz7N+++/T1lZGTNmzGDVqlWkpqZOOMZEoVDIpcCuxdPTk+TkZLKystDr9XR3d9Pa2or5Ci2+BUEQhM/PdZNx9+7dbNmyhb6+Pu666y6WL19OZGTkuCCV4ZuVIxfl8HQ3U6ZMYdKkSajVatrb2+ns7Bz7UOEWptfrSU5OJjk5mfj4eEJDQ/H39/9Ci2suzMzMTJYuXcqyZcu49957ueOOO0hLSyMgIGDcY0Yufn5++Pj4oNPp8PT0xNvbe9w6N9MSEhJCVFQUkyZN4s4772Tt2rUsXbqUSZMm4efn940LUhnuP+Lj4yOPczeZTOOmF3HdsLBYLGi1Wnx9fa95Hman00lFRQUnT57EbDaP6vR7LY9nuFmoSqXC6XTKZegurv1XqVQMDQ2NuwZmeB9c5d1qtRq9Xn/Nn6XdbqesrEyuSNHr9Sxfvpx58+Zdc6B9I0mSRGVlJR9//DF79+7F3d2de+65hwULFuB/hbliJ+Iqrfb39ycoKIiYmBgWLFjAvffei5eXFydPnqSkpGRcea/dbpebv3p6ek74uyT8PzfFO+Pu7k5aWhqPPfYYGzZsIDY2losXL7Jx40beeOMNDh06RFNT02UD1t7eXo4cOcJLL73E73//e37/+9/zn//5n1dcfv/73/Piiy/KDZhcB5DT6aSvr49Tp06xefNmLly4wKRJk1i3bh3Z2dnodLrrOog9PT3x8fFBo9HINetjTwiCIAjCF+fKpO7evZu3336b1tZWFi1axOrVq0lOTr5qJmMkhUKBVquVM0LO4XGGwjeHv78/S5cu5cEHH2TmzJno9XoUI8Zaft5FqVTi4eGBt7c3vr6++Pr6otfr5SFGV1sYvhZxXSuM/fvNsmg0GuLj41m2bBkPP/ww999/P9OnTycsLGzUXJXfNBqNhqCgIPz8/DCbzXR1dWGxWEat43Q66erqYmBgAD8/P0JCQvDy8kJxletHVzY1NzeXwsJCoqKimDZtGqGhodd1/vLw8ECv18tZPteYYdffgoODcXd3p7e3l66urnHX10ajke7uboaGhtBqtQQFBV3T1F02m42ysjK2bt3KZ599hlqt5t5772Xp0qWEhoZesez9qyBJElVVVXz88cfs2LEDNzc3li1bxt13301kZOR1vccuI78TSqUSrVZLSkoKPj4+dHV10dLSMm5qIovFwuDgIIrh35lv6nfly3BTvDMKhQKdTkd6ejoPPPAATzzxBMuWLcPb25vTp0/z1ltv8dZbb3HkyBGamprkAcouNpuN7u5u6urqqKqquualrq6Ozs5OOcPpdDrp7e0lLy+PDz74gHPnzjFp0iQ2bNjAvHnzxtWYX4uhoSE6OjowmUzyXZdr+bILgiAI185VCbNv3z7+9re/0dTUxJIlS3j44YeZOnXqhJUwVyINl/92dXVhtVrR6/WiK+M3jKenJ2lpacydO5f4+Pgrjpv7PMYGdtfKdUF7s9/UViqVBAYGMm3aNObOnUtcXNyoGRm+qTQaDeHh4YSFhTE0NERtbS19fX2jPjeTyURlZSUdHR2EhoYSGRkpT4MoXWGoms1mo6qqiuPHjzMwMEBWVhZpaWnXlU0F0Gq1BAQE4HA46Ovrw2w2y8+n1WqJiYnB19eXrq4uqqqqGBgYGPX49vZ2amtrMRqNBAcHy/vP8OtzOBzj9t9ut1NeXi4Hqe7u7ixbtoz77ruPmJiYa87IXiubzUZfXx+dnZ3jMpYTkSSJmpoatm7dyvbt23Fzc+P+++9n5cqVJCYmXvH7P/LG0bVwZbFdwevI74RzeP7h7u5uVCqVPMRRmJjyueeee27sP34dFMOlsx4eHoSEhJCUlERsbCyenp60tbVRVFRESUkJHR0dOBwO3N3d5Tt2yuF5uxITE5k2bRqzZs26pmXmzJlMnTqViIgI1Go1vb29nDlzho8//pgLFy6QlJTEY489xuLFi+UxpWMPVqfTicVikVP4roNNkiSMRiPnz59nx44d1NfXk5WVxZIlS4iKihIHpSAIwpfEVQlz8OBBXnnlFZqbm1myZAmPP/44U6dOlStaxmapHA4HBoMBq9U6qium0+mkp6eH3Nxc9u7dy8DAAAsXLmTJkiUiWP0GcV13uC4krycQuFEkScJisdDZ2YnBYCAsLOymbuDleg9vlvfvq+Dm5obdbqehoYHS0lJsNhsxMTGEh4ej0WjkYPOTTz6hpKSEefPmcccddxAaGorNZqOuro6ioiI6OztRq9Xytaw0fHNs79697N69m8DAQB588EGys7OvKRs7kkKhoKamhoKCAry9vZk6dSrBwcEohzv52oenz6msrESlUpGamirPd2s2m8nLy2Pv3r0MDQ0xb948FixYQEBAAGazmZqaGi5evEhPTw86nQ6NRoPD4aCiooKtW7eyf/9+OUhdvnw5sbGxclXKyOvny72empoaTp48ydDQEBkZGWRkZIwa/+tSUVFBbm4upaWlqFQq/P39LxsMS8PT5Hz00Uds27YNgPvvv58VK1bIXX5d+ycNT7GkUCiwWq0UFxdz8eJFDAYDnp6euLu7YzAY5OBYpVLJr8Vut9PR0cHu3bs5duwYOp2OlStXMmXKFPkztNvtFBUVkZOTg0aj4a677iI2NvZzZXO/DW6aQNXFFex5enoSGhpKcnIyiYmJeHh40NjYyIULF7h48SKDg4PodDr8/Pzw9PTE39+fmJgYEhISrnmJjY2Vyx/6+/vJy8tjy5YtHD58GDc3N2bMmEFcXBw9PT3U1tZSV1dHbW0tra2t2O12PD09MRgMFBUVkZ+fT0dHB0ajkf7+fpqbm8nLy+Pjjz/m9OnTREVFsXz5cmbOnCkudARBEL4krkqYnJwcXnzxRc6fP09kZCQLFixAp9PR2toqn79dVTSK4S6sroZ5Z8+exWKxYDAY6O3tpba2lqNHj/Lxxx9TUVFBRkYGq1atIiMj4xufLRK+XrdaoPptpdFoMJlMVFdXU1dXh8ViQafT4XQ6qa2tZc+ePRw4cAB/f38efPBBeVqslpYWPv30U9555x3Kysrw9/cnNDQUjUaD1WqloqKCDz74gEuXLrFkyRKWLVtGeHj4dSc3VCoVHR0dFBYWYrPZSEpKIioqCo1Gg9vwtDlWq5XKykqqq6txd3dHp9ONmoWjoKCA5ORkli1bRlpaGu7u7jQ3N7N582Z5/xMSEggODqa6upotW7bwySef0N7eTnJyMmlpaQA0NzePOgf39vai1+svm8Gsrq7mxIkTDA0NkZ6eTkZGBjqdbtQ6NpuNHTt28Pbbb1NXV0dMTAyxsbETbtPpdNLQ0MDmzZt5//33aWxsJC0tjSlTpqBUKmlpaRm1fz09PfKY3JaWFl5++WU2bdpER0cHkZGR+Pr6cunSJY4dO0ZDQwMGgwGDwUBPTw9VVVXs37+fDz74gO7ubhYvXsx9991HVFSUHIgajUZOnz7N8ePHSUxM5J577rnmaYe+jW66QNVlZMAaFhbG5MmTSUtLQ6PRUFNTQ3FxMRqNhtTUVLnUxHVn9HoW152xqqoq+U5QT08PTqeT9vZ2Tp8+zYEDB8jJySEnJ4cDBw5w4cIFVCoVUVFRGAwGduzYwbvvvivPtVpQUMDBgwfZtm0bhYWFRERE8MADD3DXXXcRFhYmDkZBEIQvidVqpbS0lD/96U/k5eUhSRJOp5Pq6mqOHj3KwYMH5fN3Tk4OpaWl+Pr6kpKSQltbG6+99hpvvvkmpaWllJSUcPbsWfbs2cOuXbtobm5m8uTJrF27lkWLFk14V18QvkwiUL01qNVqtFotNptNviatrq6mvLycQ4cOcejQISRJYvXq1dx3332EhISgVCqpqalh37595ObmYjQaiY+PJykpCa1WS39/PwcPHmT//v1otVoeeughZs2aJZcMXw+FQoHZbKa8vJympia5UtHVZ8XVIMlgMFBZWSlPMVRcXMyePXvIz88nNDSU5cuXy9lUp9NJXV2dnIAZHBwkKyuLmJgYdu3axZYtW6ipqcFmszE4OEhxcTFHjhzh4MGD8uIawjdlyhQCAwMnfF21tbXk5eVhMpkum1Ht6upi+/btnDx5kri4OBYuXEhUVNSEGVVXUPvWW29RU1MjVzyWlJRw5MiRUdf3R44cob6+Xm4GVlJSwrvvvktBQQEAmZmZBAUFkZuby8aNG9m/fz+FhYUUFxdz+vRpdu7cyc6dOxkYGGDatGk8/vjjZGZmjirdbm5u5uDBg1RXVzN37lz5pqowsZs2UHVRjCgJDg0NJTMzk7S0NPR6PdHR0SQkJHyuL/FI9uG5wCoqKjCZTISEhBAYGIiHhwfK4cmcXYtarZYvcpKTk+XB6D09PbS3t1NVVUVlZSWtra14enoyZ84cHnroIe699165xFgQBEH44lwX9Y2NjVy8eBGdTkdkZKTcbXTkuVulUuHu7k5AQABTpkwhKSkJs9lMZ2cnAwMDNDc3U1lZSVVVFd3d3YSEhLBkyRIeeeQRFi1ahK+v7xf6nRGEayEC1VuDqyojNDQUb29vBgcHqa6upqysjO7ubmJjY3nwwQdZs2YNcXFxKIczokajkYaGBrq6uoiOjmbu3LkkJSWhVqvp6enh4sWL9PX1sWDBApYuXfqFkhsajYbW1laKiopQq9Wjynvd3NzQ6XRylrWzs5OKigrKysowmUxMnjyZBx98UN4HV3mryWSivr6e3t5eEhIS5JLmS5cu0dHRga+vLyEhIej1+nHXzmq1Go1GQ1hYGLNmzbpsoNrb20t7ezve3t5kZWWRnJwsj491qa6uZs+ePbS3t7N48WJuv/32y86BbLfbOXfuHB0dHXIG25UxHbuPGo2G0NBQZs6cSWBgoDzu1mAwkJ6ezty5cwkODpanpBkcHKSpqYmKigpqamoYGBggKiqKpUuX8tRTTzF79my8vb3l/XI4HJw/f549e/agVqu5//77SUlJEbHBFdwU86heL7vdLncoU6vVKK9hntUrcQ1sbmtro7+/f1QN/ViSJKFWqwkODpa7oJlMJtrb26mrq5Onn9EMD7ZPSkqS15voCyQIgiB8fg6Hg/7+fhoaGjCZTFc9z7puegYHB8t31l0XGr29vTgcDrnZSEJCAr6+vvJFmiDcaE6nk/7+foqLi+no6CA7O5vY2Nixqwk3CafTydDQEA0NDVRVVdHX14dOpyMpKYm4uDh0Ot2oc5LVaqWmpobq6mr0ej2pqakEBASgUCgYHByktbUVg8FAcHAwISEhqEeMnb9ekiRx7NgxXn75Zfr7+1m3bh3Lli0bFSA6nU6MRiMVFRVUVlZiMBgICAggNTVVbqA0cv9NJhO1tbVUVFQQEBDA1KlT0el0tLS00NnZic1mu+r+6vV6YmJixmVJXQYGBmhpacFqtRIUFERgYOC4QG7v3r384Q9/QKlU8swzz7B06dLLDqtzOp00NTXR2dk5rhnrSK6xqTqdjujoaLmUOz8/n/r6emJjY0lMTJT/3fW7U19fT39/P06nE29v71HrjY1POjs72bhxI1u3bmXOnDn85Cc/ISoq6qq/W99mt2Sgej1cB97VSFfowjYRV6bXxTncqMM5ouuYqxT5Wp5fEARB+Hyk4XLfa+U2pvGLc3jqGdf533V+H7ueINxoIlC9+Y29rnRdO7rOIa7zhyuLOpbrfDPyPMOY69BrOfeM3Y+J9Pb28t5777F161ZSU1P57ne/S0ZGxqjZJxwOBxaLBUmSxg2NG8l1fnS9VsXwED2FQoHzOrriKq7SCftq74PD4eDVV1/l9ddfZ+HChTz11FNXzUp+nv1z/bfD4cDpdI77TZCGf3dGbvtKn73T6eTQoUO89NJLWK1WnnnmGRYvXoyXlxeSJGG323E4HHKGV/h/bvrS38/L4XBgs9nkuydjv3BjuQ5M14F4tWXsF2fkwTnySz52PUEQBOHLdS3n7rHrjn38yHO3OH8LXxdJlP7e1FwVfc7hqUdGLmPPH5cz8hxkt9ux2+1yUOZarnbucTqd2Gw2HA7HFdf38PDAy8uLzs5OGhsb0ev1xMXFydlMm80mN3Cqq6sjKCgIHx+fcYGW65ra4XCgHB4SN/J5r+UcPPK1XW5/GXM9PnY9h8NBU1MTO3bsAGD58uVyV+QruZ79Y/h5rFYrzuGuvhP9Jri2OdFvx1g2m436+np27NhBQ0MDd955J/feey/e3t4ohscTHz58mA8++AA3Nzd5Ksuxr//b6BuVUbVYLLS0tFBSUsKlS5eor6/H4XAQGRlJdnY2WVlZhIaGjjuIrFYrzc3NlJaWyh0hR5IkCa1WK3cg/qJjYgVBEIQby+l00tXVRX19PXV1dTQ1NaHT6bjtttuYPHny2NVh+OKksbGR0tJS+vr6SE5OJjU19bIlaoLwZRMZ1ZuPJEkMDAxQWFjIiRMnqK6uRqPRkJaWxuzZs0lJSbmmZjjS8PyqTU1NcvO2hoYGbDYb4eHhZGRkMH36dCIiIibMqEmSRFdXF4WFhZw/f57q6moAkpKSmDlzJhkZGfj4+Ix9mHyN29nZiY+PD1FRUXh5eeEcbhr66quvsnPnTjZs2MD69etHdaDt7u6msLCQM2fOyN2BJ0+ezOzZs0lNTR03dvRauKbvKSsrw263M2XKFGJjY/Hw8Jjw2trhcNDb20tBQQFnz54lPz+fhoYGpkyZwqpVq5g1a9Zlx6deD4fDQU9PD+fPn+f06dPU1NTI42Tnzp1LTEzMZfdxIg6Hg6qqKs6dO8fFixepqKigs7OTuLg41qxZw8KFC+XeB1arlfz8fH784x8TFhbGL3/5S9LT0yfsYvxt840IVCVJoqOjgyNHjvDpp5/K09e4yisAAgICWLhwIRs2bCA7O3tU2UN3dzcHDhzg3XffpaioaMSW/y4oKIh169bx2GOPERIS8oW/EIIgCMKXz/V7cPToUfbu3UtBQQG9vb04nU6mTZvG97//fZYuXTrqMc7hMUxHjhxhx44dFBcXI0kSTzzxBI899hgRERGj1heEG0UEqjcXh8NBS0sLH330EVu3bqW1tRW34dkiJEliypQprF+/njvvvJPg4OArBjEWi4UDBw6wadMm8vPzGRoaQhouowXw8/Nj3rx5fOc732HatGmjrlNdc29++OGH7N+/n+7ubtTDc386nU5CQkJYvXo169evJzIyctx+OBwO7HY7CoVCzoYODAxw6NAh/vznPxMREcE//uM/kpWVhUajQZIkqqur+fjjj9m1axctLS0ohstglUolqampfOc737ni2NCxLBYLVVVVHD58mG3btlFbW4ufnx/PPvss999/P4GBgeOurS0WCxUVFbz//vvs27ePvr4+1Go1ZrMZh8NBfHw8a9as4b777iM6OvqK5b9XYrVaKS8v58MPP2Tnzp10dXXh6emJ0WjEzc2NWbNm8d3vfpc5c+bg4+Mz7v0dSRrufbB79242btxIRUWFPP/qwMAARqORxMRE1qxZw6pVqwgLC0OhUDAwMMALL7zAu+++y5NPPskjjzxCRETEuOz2t803ovRXkiQaGxvZt28fpaWlJCQksHTpUhYvXkx2djZ6vZ76+np5PqnExER8fX3lD7+3t5e8vDzOnDmDRqNh+vTppKenk5iYSFJSEklJSUyZMoVp06aRkJBwXXdUBEEQhK+Gw+GgvLycF198kffee4/i4mJCQ0OZPXs28+bN47bbbiM9PR1/f3/5MVarlZKSEp5//nl5eoW+vj4MBgNTp05l2rRpE2YpBOFGEKW/Nw+n00lnZycffvghb7/9NlarlbvuuosVK1aQkZGB1WqlrKyM9vZ2/P39CQ8Px8PDY+xmZFarlaKiIurq6oiKimLRokUsWbKErKwsfHx8aGxspLKyEkmSSExMxN/fX77WLC4u5r333uPAgQPo9Xruuece7r//fmbMmIGXlxfl5eUUFRXh4+NDbGzsuMo/t+G5U5XDY0rtdjsNDQ28//77VFVVsWrVKubPny9PX9PU1MRHH33Exx9/jN1u54477mDFihWkp6djtVopLi6mrq6O6OjoUV2BL2dgYIBjx47x17/+lW3bttHe3k5XVxcOh4MZM2YwadIk+bldbDYb5eXlvPHGG+zevRs/Pz9WrlzJypUrmTNnDmq1Wp4H1tPTU26AdKX9mIgkSdTU1LBlyxa2b9+OWq3mgQce4IEHHiAzM5POzk6Kioro7+8nOjqaoKCgKwbEDoeDo0eP8sILL1BTU8O8efNYt24d9913H9OnT0elUlFSUkJjYyO+vr4kJCSg0WhQqVTo9XpOnDhBc3MzqamphIWFfaGGWt8EN0WgarfbGRoawmw2yzXen4dOpyM9PZ0777yThQsXkpmZSXp6OmlpaUiSRFFREQMDA/K0Nq67Rh0dHeTl5dHY2MisWbN47LHHWLp0KbNnz2bOnDnMmTOHGTNmkJiYiLe39+feP0EQBOHGsNvt1NXV8cc//pHdu3fj7e3NqlWreOyxx7j77ruZOXMmaWlpBAUFjSqrs1qtVFRUsH37dnk+PpvNRn9/P5mZmUyfPl0Eqt9QTqdTzjJ9VReCrudkTNMWFxGo3jyMRiNnzpxh8+bNtLS0sGrVKh599FFmzpzJlClT8Pf3p62tTS7BTUxMJCgoaNxnOpJOp2PSpEksXLiQOXPmkJGRQXp6OgkJCZjNZioqKuju7iYzM5P4+Hjc3Nzo7e1l165dbN++Ha1Wy+rVq1m5ciXTp08nLS2NhIQEhoaGKCoqore3V+7Ye6VrVaPRyIULF9i1axfBwcGsWbOG+Ph4lEolJpOJI0eOsHXrVoaGhrj77rtZv349s2fPJi0tjfDwcOrq6rh06RKenp6kpKTg5+d3xdfd399PXl4ehYWFZGVlMXv2bNra2rBarfJwjLFBZldXFwcOHGD79u1oNBqeeuopVq5cSXp6OqmpqSQlJdHd3U1RURFWq5WoqCjCwsJGZaKvRV9fnzw+1Gw28+ijj7J27Vqys7OZPHkyQUFBFBcXU1ZWhr+/P7GxsaOmnBnJ6XTS09PD22+/TU5ODgsWLGDDhg3Mnz9fHj4YEBBAW1sb5eXluLu7k5mZiY+PD25ubnh7e1NXV8fZs2eJiIggISEBvV5/xff2m278u/w1MJlMnDt3jrfeeoudO3dSW1uL1Wodu9plKRQK/P39mTlzJkuXLiUrK4uoqChCQkIIDw9n6tSpzJ8/n4SEBHmuU4vFAiNS9H19fSiVSmJiYuSDyZVNTUpKIjY2Fn9//wnHDQiCIAhfH0mS6O/v57333mPfvn2Eh4fz9NNP8/jjj8vzFEZFRREUFDQu46FWq0lMTOSZZ57hJz/5CStXriQ8PFyc67/BXMfLyZMn2bJlC2fPnsVgMIxd7UtnNBrJz89n69atHD9+nN7eXqRbf/TVN5LT6aSvr48zZ85QXl5OcnIyixYtIiUlhcDAQHkuUFdmr6SkhIqKCoaGhsZuSqZSqYiKiiIrK4tJkyYRGRlJSEgIERERpKamkpmZia+vL21tbfT19cnHRl1dHefPn2dwcJDJkyczf/58OeAJDg4mNTWVRYsWERkZSWFhIYWFhQwMDOC8TCd01/FfVFREX1+fnLlzBbadnZ2cPXuWmpoa4uLiuP3220lJSSEoKIjw8HCmTZvGwoUL8fDw4OzZs1RXV2M2m694LGu1WmbOnMmzzz7L9773PZYsWSJPyzMRu91Oc3MzeXl59PX1MXPmTObNm0dMTAx+fn4EBgaSnp7OggULCAsLo66uTp7v9Hq1tbVRUFBAT08PkydPZvHixcTHx+Pn50dISAiLFy9m9uzZOBwOioqKaGpqkm82jeVwOOQMrMFgIDMzk0mTJhEYGIhOp8PPz4+0tDTS0tKw2+20tLTQ09ODY7iLsk6nIzs7G7VazaVLl2hra5NLw7+tbopAFcBgMHD27Flef/11/vKXv7Bjxw5qamowm81jV52QK2Xu4+Mjl+YqhjtyaTQagoOD5Ul6BwYG5INMGh7c3t/fj7u7uzxRsdsEncAu94USBEEQvj4mk4nz58/z0UcfAbBhwwbuvfde4uLi5BK4y53DVSoV4eHh3HPPPWRlZeHv73/Fsi7h1idJEt3d3Rw/fpydO3dy9uxZebygi8PhYHBwkMbGRqqqqqiurqahoYGBgYFR27oeAwMDnDlzhu3bt3PixAm59FG4+djtdjo6OigtLcVgMDBp0iTi4uLQaDTyucQVJAYGBtLb20tNTc0Vjw+FQoG7uzsajWZUF9mR5yeFQoFerx9VutvU1ERDQwMeHh7ExsYSHByMRqOR1/fy8iI5OZnY2FgMBgPV1dX09PRcMVDt6emhpKQEgOTkZLmpjyRJtLS0UFdXh1KplBM1rv1RKpX4+PiQnp6On58f1dXV1NTUYDAYrhioenp6kpaWxqJFi0hLS5Ovsy/HbrfT3t4ul0InJycTEBAgly4rFAo8PDxISUkhOjqawcFBGhoa6Ovru67vlNVqpampierqajw8PMjIyCAiIkLuuKtQKAgICCAzM5OAgACam5tpbm6+YmDuGO6Q7Bo/LI2YRsi1TWl4KiCNRjOqu69CoSApKYnQ0FCqqqpoamqSE2vfVpc/Sr5CHh4eTJo0iTvuuIOwsDAuXrzIm2++ycsvv8yePXuora29pg/KdQCMJQ3PdeRwOFCr1aMmMHY6nRgMBgYGBjCbzQwODlJXV0dNTQ09PT3YbLaxmxMEQRBuEpIk0dvby4EDB6ivr5eHajQ2NnLw4EF27tzJwYMHuXTpEv39/WMfDsPBqmtydtfvhfDNJQ2X13Z1ddHZ2Ul9fT1VVVXU1NRQW1tLbW0t5eXl5Obm8tFHH/HOO+/w7rvvsmXLFnJzc0etd61LXV0d1dXV1NbW0tbWRnd3N2azWRxrNymr1UpbWxsdHR14eXnJVXUjrzE1Gg2BgYEEBARgs9lob2+/7oye0+lkYGCAsrIyzp8/j8lkIisri+joaPk6dWhoiKGhIdRqNVqtdly1h0qlIigoiNDQUFQqFR0dHVfMqFosFjo6Omhra0Or1RIdHS13Nnc4HLS1tdHV1YWvry/R0dHjhryp1WpCQ0Px8/Ojr6+PtrY2jEbjZQM3hsfIenh4yPt/pXUZ3g9XtaMkSeh0unGvm+FGp/7+/thsNrq6uujv77+uQNVsNsvBp0ajIS4ubtxUN25ubnImt7e3V/6cJ3oNbsNTy7g6Ip85c4bi4mIGBgaQhhNjpaWlXLp0CQ8PD/lGx8j3NyIigqioKNrb22lvb8dqtU74XN8WN0WgqlariYuLY8WKFXzve99jzZo1hISEkJ+fz9tvv80bb7zB/v37qauru66SYIZ/kFwnnNbWVvz9/YmKipJr2K1WKwMDA/T19VFXV8f27dv585//zF//+lfeeecdDhw4QE1Nzbf+QBEEQbgZ2Ww2WltbOXv2LAxnB44cOcJf//pXnn/+eXn5n//5H3bt2kVTU9MVz+VX+pvwzeIKBBobG9mzZw8ffvihvHz00Ufs2LGDnJwcjh07xtGjRzl06BA7d+5ky5Yto9a9lmXLli3s27ePhoYGuUpLHGs3L5vNRnd3NwaDAW9vb0JCQtBqteOSIV5eXvIY9v7+/mtKqpjNZmprazlx4gSfffYZH330EZs2baK4uJjJkyezcuVK4uLi5OdSq9Wo1WqsVitGo3HCQMzV30WhUGAwGDCZTJc9vsxmMx0dHfJr8/X1lYNAq9VKd3c3AwMDaLVa/P39x02R4ubmhpeXl1y663rdl3u+z8NtuPmTu7s7DoeDoaGhCcttXd8lm82GwWC47ps/rtfb29uLRqO57BC/gIAAtFotQ0NDdHd3YzQaJ3wepVJJQEAAd999N+np6RQUFLBp0yZ27NjB0aNH2bNnD1u3bqW+vp5p06axaNGiceN7fX19CQkJwWKx0N3dfcXP8tvgpghUGT7Y/Pz8mD59Og899BDPPvssq1evJjAwkDNnzvDmm2/yxhtvkJOTQ0NDwzUHjg6Hg/b2di5cuEBzczOxsbFMmjRJHqfkGJ4sOSwsjODgYLq7uzl37hy7d+/m1Vdf5fnnn+edd96hqKjoW3+wCIIg3EwkScJsNtPQ0EBdXR0Oh4PS0lL27dtHd3c33t7e+Pj40NXVxd69e3nttdfYtWsXXV1dYzclfAu5SvA6Ojo4c+YMhw8fJicnh4MHD5Kbm0tlZSVGo1G+iHRNr3Ho0CFycnKue8nLy6OjowPFFUrRhZuDKziyWq14enqi1+snHBKgVqvx8vJCoVBgsVgmDKbG6uvrIzc3l5deeon//M//5M9//jO7du1CqVRy7733Mn/+/FEN3EJCQggNDWVwcJDKyspR5aCuLF1lZSV1dXVYLBa5uvByx5fVaqW3txebzSYPl3Ox2+0MDg5iMplwd3fHy8trXImuQqFArVaj1+tRqVQYjcZrvia/ViqVisDAQKKjo3E6nRQXF9Pa2jrq/TWbzXJ5rM1mu+zrvRK73Y7RaMRut+Pp6YmHh8e418twEyy1Wo3FYsFgMGCz2S77ejUaDfPnz+ehhx4iJCSEw4cP89e//pX//u//5k9/+hOHDx8mPDycFStWkJWVNa5vgru7u3zzwNWBfqKg+Nti/KfxNVIMz+/k5+dHdnY2Dz/8MD/+8Y9Zs2YNer2eY8eO8eqrr7J582ZOnz5NR0fHhHeWXJzD85GdPXuWo0ePolarmTNnDsnJyfIdIlcjjfXr1/PTn/6Un/zkJ3zve9/j/vvvJzo6mrKyMjZu3MiHH35IXV2dKAUWBEG4iVgsFtra2ujt7cVut1NbW8ttt93GP//zP/O73/2O3/72tzz77LNMnjyZ8vJyPvnkE86dO3fF3w7h20EaHjum0+mIiooa1UQxPj6ewMBA1Gq1fEHqypaMbbZ4LYtrDKFer5efW7h5OZ1OrFYrjuF5Q11jSsdy3XRg+DO91s/V4XDgcDhwOp24ubmhVqtxOBz09PTQ3t4+qj9LXFwc6enpuLu7k5eXx44dO8jLy6O6ulouUd+6dSv5+fmYzWa0Wu24LOhINpuNwcFBnE6nHIC5OBwOrFYrdrt9VJZ2LFfG083NTX4dXyaVSkVERAQzZsxAp9Nx4sQJtm3bxoULF+TS/CNHjrBt2zYuXbqEw+FAq9Ve9/SRrs/BFXxP9Bkz/N13vdZreb2enp4kJSURERGBSqWit7dXLv03Go3yGOPLZaK1Wi3u7u5ylniidb4tborpacZyffE1Gg1BQUGkpaUxdepU/Pz8aGho4OjRoxQXF+Pj40NMTMyEX0hJkjAYDBQUFPDBBx9w8eJFFixYwCOPPEJcXJyc2lepVPIPz+TJk5k8eTKZmZnMnDmTlJQUDAYDly5doqenh8jISOLi4q77iyAIgiDcGAMDA5w+fZqDBw/i5eXF448/zve+9z157E9wcDBxcXGo1Wp5bKGvry+zZs0a99shDY93PXbsGHV1daSnp4vpab6BJEmiq6uLCxcu0NLSQlJSEsuWLWPevHlMmzaN7OxsUlJS0Ov1WK1WlEoler2ekJAQ5syZwz333MO0adPIysq65mXatGlER0fT2dlJW1sboaGhZGZmjhufJonpaW4KRqOR0tJSLly4gFqtZsGCBSQkJIy79uvo6OD8+fPU1tYSHh7ObbfdRlhY2Kh1xnJ3dyciIoLp06czd+5ceWqWhoYGzpw5Q19fH9HR0QQGBuLm5oZWq0WtVtPb20tlZSXFxcVUV1dTWVnJ6dOnycnJobKykv7+fkwmE3PmzGHevHny48fq7e3l/PnzlJSUEBMTw5w5cwgICIDhG3/5+fkUFBTg5+fHjBkzxl1nS8Ndg3NzcykuLmbq1KnMmTPnss83ltPppLW1lQMHDtDb2zvh9DSK4cZT7u7udHR0UFlZSUFBAfX19VRWVnLy5EkOHDhAbW0tPT09qFQqsrOzr2s/GG7keuHCBQoKCggICGD+/PlycDlST08P+/fvp6mpiYyMDKZNmyY3dxpJkiRsNhsFBQW89dZblJSUkJqayvLly5k3bx7h4eGYTCaqqqpoaGhAr9cTGRk5Lq64cOECZ86cITIykuzsbEJCQsY917fFtX2SXxPFcIcxLy8voqKiWLBgAfPnz0elUlFeXk5ZWdmE5bjS8JQzZWVlfPrpp+Tl5TF58mTWrVvH5MmTR909cj2HawyAWq3Gw8ODgIAAZs2axdq1a8nIyKCpqYmCggL6+/uveidFEARB+Go4HA4sFgsOh4PAwEBWr15NcHCwfLdfqVTi7e3N1KlTSUlJoa+vj4qKiit25xS++VwZIVe3/6lTp44KLGfPns2dd97JmjVrWLduHevWrWPNmjXceeedzJgxY1wgerUlIyOD1NRUQkNDcXd3l4/PsYGPcHNwXXu6u7tjtVqxWq0TXvvZ7Xa5DNfVzfdq3N3dCQ0NZfLkydx2222sXbuWn/zkJzz44IMolUq2b9/O4cOH5emLlEolWVlZPP744zz44INERERQWlrK7t27OXv2LD4+PixevJjExES0Wi3h4eH4+fldNlhzJYMUw6XvI6lUKjkz6cqujl3HFYy5xst6enqOuq7+snh5eZGZmclTTz3FmjVrCA0N5cKFC2zdupXTp08THBws30Dw9/cnKCgIHx+fa/oMXJRKpdyzxmw2X7ak1/U3jUYjZzsn+u66gvBXX32VvXv3kpKSwo9+9CO+//3v8/TTT/PLX/6SH/3oR6SlpVFQUMD7779PSUnJuGpNaTg7r7hCCfe3xcRH8U3C6XRiNBppbm4mNzeXV155hffeew+73c4999zD7bffPm4iXGlEV60PP/yQzz77jJCQENavX8+CBQvG3bW4HNfdnOjoaOLi4hgaGpLLMSY6iAVBEISvnttwN0mVSoWnpye+vr7jLtDc3NzQ6/Xy1DMGg+G6u3MK3xxuw505s7KymDVrFunp6fKYMLfh5iweHh7yHJL3338/9913H0uWLCE+Pl5e53oXHx8fOfs0ZcoU/Pz8ruuiWvjquG5waTQauYHORIkR8/CUh5IkyQHMtXAFi65AKSIigiVLlpCZmYnBYODMmTM0NjbKwbGXlxezZ8/mf/2v/8V//Md/8Nvf/pb/7//7//j3f/93fvnLXzJlyhQGBwcJCgoiKSkJHx8f3C4TqLrOlW5ubvJNPheNRoOvry9eXl4YjUYGBgYmDKLMZjPd3d3Y7fYrBm5flE6nY9asWfziF7/g97//Pf/6r//Kb37zG/793/+dX//618THx2M2m+VGqa7xwtdKpVLh7e2Np6cnZrOZoaGhCW9I9PT0YDKZ5OZZl4slrFYr+fn55Obm4uXlxcqVK8nIyJBLrAMDA1m6dCmrV68mICCAiooKLly4gMlkGrUds9mMw+FAM2b6mm+jiY/ir5k03Km3vb2dQ4cO8R//8R/8y7/8C3v27GHy5Mny/7/tttvGtZE2m82UlJTw/vvvs3PnTnx8fNiwYQMrVqzA29v7uj9s14lE3NUQBEG4+WiG58n28vKiq6vrivMHuv5drVaPK/sVvj0UCgWBgYEsW7aMZ599liVLluDj4zPuN14xXHGlUqlQqVTytcDn5evry+LFi3nmmWdYvnw5ISEhlw0mhK+XRqMhNDQUHx8f+vv7aWpqkgNSF4fDQX9/v1x6GhISMu6a9Fq5u7sTHBwsZ9y7uroYHBwc9XxKpZLAwEBmz57NmjVrWL9+PQsXLsTNzY2TJ0/S0tLCnDlzSEtLu2LA7O7ujo+PDyqValynYpVKRXBwMH5+fgwODtLe3j4uQHc4HPT19dHT04Neryc0NPS6A8TroRruXTN37lzWr1/Po48+ypIlS7BYLOTl5dHa2kpiYiKTJk0a9/67MpOX4+HhQWhoKCEhIdjtdjo7O7FOMLtIa2srAwMD+Pn5ERYWdtl5YK1WK1VVVQwNDZGYmEhUVNSoKTEVCgXe3t7yOHen00l7e/uomwGSJDEwMIDFYsHHx2fCbtPfJuPf5a+Z0+mku7ubzz77jF/96lf87//9vzlw4ADp6ek8//zz/P73v+fOO+8kJCRkXA25xWKhpKSETZs2sXv3bvz9/Xn66adZt27d5xrjIQ1PitzW1oaPjw+RkZFotdoJD05BEAThq6UYnuw+KSmJ6OhojEYjFy5cGNWIhOHflb6+Pjo6OgAIDQ3F29t71DrCt4ubmxs6nY7Q0FB0Ot1X8ruuUCjQarWEhITIgYJwc3KV58bExOBwOKiqqqKzs3NU0NPb20tNTQ0dHR3o9Xri4+M/17Umw8HfwMCA3I1Xp9NNeDNNMSITq1Qq6enpYd++fRw8eBBPT09uv/12YmNjr3g8u/q/qNVqOSByUSgUhIWFERISQldXFxUVFXR3d4/KuppMJsrKyujv7ycuLo6kpKRx1Y1fNtfrdt006u/v55NPPuH48eOEhoYyZ84c4uLi5ABdGlGebDKZLnvz0tPTk+joaGJjYxkaGuLSpUsMDQ2NWsdms1FUVCSPLQ8LC7tiltNVLj1R2fRYiuEmsiO3NTQ0RE9PD5Ik4e/v/5Wdn25WN80rt9vtNDc3s23bNn72s5/x85//nHPnzrFgwQL++Mc/8oc//IGlS5fKg5fHHiAWi4WioiLeffddDhw4QHR0NN///vdZuXLlFTOprrmXxh5Qdruduro69uzZw9mzZ4mIiCA7O3vCsjJBEATh66HRaIiNjeW2227DbDazefNm6uvr5WkMXHenz507R0lJCVFRUcycOROdTjd2U8K30OWuDW4khajQuukpFAr8/f2ZOXMmERERnD9/nnPnzslZTkmSqK6uJi8vD5PJRGpqKqmpqej1eiwWC6WlpWzatImPP/6Y+vp6eSx9X18fQ0NDowI/SZLo7u7m2LFjnD17FqvVSlpaGhEREZe93jSZTBQWFvLqq6/yyiuv0N3dzerVq5k/f/6opkQT8fDwkG+W9PX10dTUNKr0NCIigoyMDAICAigvL+f8+fP09/fDcBBWX19PTk4OHR0dZGZmEhsbi/vwfKdFRUVyReOXPVOGNFxyXFxczPPPP8+7776L3W6Xp/RxddS22+1UVVXxhz/8gSeffJLXX3/9slOSKRQKIiIiSEtLw2q1cuLECc6fPz9qaMjZs2fJzc3FarUyefJkoqKiUA9PVXPp0iU2bdrEJ598QktLC25ubsTHx+Pp6cmlS5c4d+7cuCqfvr4+iouLKS0txd3dnfj4+FE3Jdra2mhsbMTPz4+goKArZse/DW6Krr+umu6XXnqJ9957j66uLmbNmsV3vvMd1q1bx9SpU/H19UWtVk/45TOZTBQUFPDee++xe/duBgYGiImJwdfXl9raWs6dOyefZM6fP09LS4s86L24uJiPP/6YEydO0NraSnt7O9XV1Zw4cYL33nuP7du3o1QqeeCBB7jvvvuuq5uYIAiCcGMphqcV8PX15eLFi5SUlNDW1gbDnTtra2vZtWsXW7Zsobm5mcWLF/Pwww8TGBg47vdEEl1/ha+ZJLr+3hRcmS6NRkNTUxMXLlygubkZhhMjFy9e5OOPP+bo0aOEhobywAMPMG3aNDw9Peno6OCdd97hlVde4cSJE3h7exMfHy8nUw4fPkxTUxOdnZ00NTVx8eJFtm/fzubNm6mtrWXmzJls2LCByZMny1l3g8FAVVUV58+f5+TJk3z66ae89dZbHDhwAKVSydq1a3n00UeJj4+/6rhnt+GxqVVVVVRVVcmBmuvmnftws6+WlhYKCgpoamqSA+3i4mI+/PBDjh07RmRkJE888QSZmZloNBpaWlp48803ef311ykoKMDLy4uYmJhxpatju/66xmxPFGAbjUYqKys5e/YsZ86c4dNPP+Wvf/0r+/fvx8PDg7Vr17Jq1Sri4+PlgM71+bzyyiuUlJRw2223kZmZOa4s2MU1d2prayslJSU0NDTg7u6OxWKhsLCQ119/nby8PKZNm8batWuZNGkSGo2G+vp6Nm/ezMsvv8y5c+fw8/MjKSkJPz8/ampqqKyspKGhAYfDgZubGyaTibq6Onbu3MkHH3xAd3c3ixYtYtWqVaOGAVy4cIFt27YRFRXFnXfeSUxMzA1pVnWruCkC1YGBAc6fP09RURGJiYmsW7eOBx54gKysLIKCgtAMzzd0OR0dHXz22Wfs2LGD6upqjEYjbW1tXLx4kePHj5Obm0tubq78362trURHR+Pv709FRQU7d+5kz549HDp0iH379sn/XVJSQmBgIA899BBr164lNjb2ssGyIAiC8PVQKpX4+/sTGRlJS0sLeXl55ObmkpOTw86dOzl69CgOh4N7772XDRs2kJqaOmHZpSuzkZOTMypQFYGC8FURgerNw1UeHhgYyMDAAIWFhZw6dYqDBw/y2WefyRUaq1evZunSpYSEhMBwSfDBgwc5deoUBoOBjIwM0tPTaWtrY//+/Rw4cICjR49y4MABdu/ezb59+zh79ixms5m5c+fy3e9+lzlz5owa99nU1MSHH37I66+/zq5du+QGPFlZWTzyyCOsWrWKhISEa8q+KYa7/fb393Px4kUUCgXZ2dnyzTuFQoGvry/e3t709fVRVFQkT4Ozb98+ioqKiIyM5Mknn2TJkiVypWFnZyc5OTmcPXsWSZJIS0tjypQp48qCnU4nTU1NHDhwgI6ODmbPns3UqVPHBaqSJNHW1sZ7773Ha6+9xp49ezh9+jRWq5WZM2fyxBNPcP/99xMfHz+qudHg4CBnz57l8OHDBAUFsW7dOpKSkiY85zP8+6HX69HpdPJ0QydOnODw4cPs3LmToqIiMjIyePLJJ7ntttvkRlVtbW0cP36c06dPY7fbycjIIDMzk4CAACIiIhgcHKSkpIQzZ85w6tQpcnJy2L59OwcPHsRsNrN06VIefvhhOfBluMpz165d5Obmcvvtt7NgwQICAgK+1QmymyJQZbh8KzU1ldtvv52srCzCwsJGDUC+EqfTiUKhICQkhGnTpjFv3jxmzpxJZmamfOC4lqysLKZPn056ejpBQUFotVr8/f0JDg6WO3/5+vqSkpLC0qVLWb9+PXfffTcxMTFXrEkXBEEQvh6K4S7t4eHhpKamEhYWJt899/f3Z8aMGaxatYr777+ftLQ0PDw8xm4CRpRkenl5kZaWxpw5c+SLIEH4KohA9eahGM6qBgQEEB8fL49NVKlUREVFcfvtt7N69WoWLVpEeHj4uKyXu7s7mZmZ3HnnnSQkJODt7U1wcDDR0dEEBATg4eGBTqcjKiqKWbNmsWLFCtasWcOMGTPGde11ddlVKBSkpKSwYMECli9fzgMPPMCcOXMIDw+/piDVxc3NDafTSXFxMTU1NaSkpBAbGyuPl1Sr1QQFBRETE0NoaCgeHh6o1WoiIiJYvHgxa9eu5fbbbyc4OFjO4CqVShwOB15eXmRnZ7NgwQLi4uLGjbV1nWd1Oh2ZmZnMnTuXqKiocUkphUKBxWKhq6sLSZJITU1lwYIFrFixglWrVjF79uwJx4u2t7dz5MgRSkpKmD59Ovfddx9BQUFXvH53H25mFRcXR0hICO7u7ri5uRETE8Pdd9/NI488wuzZs/H39x/1eiVJQq1Wk56ezp133kl0dDQajYbAwECSkpJISEiQ56gFCAoKYtasWfLvkasBlEKhkAP4V199FavVygMPPEB6evoNbVR1K1BIIwdmfk2cTqc8RlStVl/2rsfl2O12jEYjBoNBHpd0JRqNBr1ej0ajwW63MzQ0xMDAAAMDAxgMBpxOJzqdDj8/P/z8/EQDJUEQhFuA6yK/p6eH7u5u+vr65LLgwMBAvL29r3oxZ7PZ5AYjWq0WnU531VI6QfiyOJ1O+vv7KS4upqOjg+zsbGJjY8euJnyFpOHGOD09PbS3t2MwGNBoNPj7+xMQEDDuHOFwOOjt7aW1tRWVSkV4eDh6vR6n04nJZJKvN11Tv2g0Gry9vfHz88PHx2dcYMdwOWt3dzcDAwMolUo8PT3R6XRotdpxzXiuhSRJtLe3s2XLFt5++21uv/12nn322XGlwyaTST6fDg0Nya87MDAQLy+vUes6nU66urro6OiQAz+9Xj/h+dNqtdLX14fdbkev14/b1sj1Ojs76e/vR61W4+npiVarRavVTljhKEkS+fn5/OEPf6CsrIxnnnmGtWvX4ufnN2q9iTidTvmGgKvrsiujHhgYiKen56jns9vt9Pb20t7ejkqlIiIiYlRW2Gaz0d/fT29vLz09PVgsFjw9PfHz88Pf3x+9Xj/qs7NarWzevJnf/e533HHHHTz77LOkpKRc9Tfrm+6mCFS/LNfzUiY6uEcubm7/bzLksesJgiAINzfXedzhcKAYMbn9tZ7PXb8l17q+IHxZRKB683KdV1xVfK7zykRc6zKcvZzob06nU77edK1zue0xwTXulda9Fq5mQC+++CIVFRU8/fTTLF++fFzT0M/7uq92zr3W8+z1vG6j0ciBAwf4y1/+gr+/Pz//+c/JzMwcl+2+kpGv92q/HSP3baJ1XH93Op3y9iZ6/+x2OxUVFfzzP/8zPT09/OxnP2Px4sUTTpv1bfONShO6DqZrWcZSjGj5rRqe9Hui9QRBEISbm+t87qrQud7z+eV+JwRB+PZynVdU1zCnrmvdsUHqyL+pVCrUarW8rSttjwmucb8od3d3EhMTWbFiBZMmTcJkMmE0GicMDD/P677SelzHefZ6XrfNZsPd3Z0ZM2awbNky4uLiritIZczrvdrruNp+uf6mVCpHfdZjORwOOjo6CAgIYO3atUyfPn3c2N5vq29URlUQBEEQBOFWJTKqwlfJ6XTS09NDdXU1np6exMTEoNfrJwywbwVms5n29nb6+voICgoiODj4uocTfh3sdjsNDQ20tLQQHR0tj5MVgaoIVAVBEARBEG4KIlAVvg7XWoZ7K7haOe7NylVyfKUM7bfRrXnLRBAEQRAEQRCEL+ybFBxdrRz3ZqW4yvjfbysRqAqCIAiCIAiCIAg3FRGoXiOn04nNZsNqteJwOMYNNhcEQRAEQRAEQRC+HF9JoOocnifVYDDIc0cZjUbsdvstE/ANDg5SUVFBcXExra2t2Gy2satMyOl03nKBrevzGjm/rMlkuqU+L0EQBEEQBEEQbl03tJmSJEnYbDb6+vqoq6ujoqKCjo4OVCoVkZGRJCUlERMTg06nu+k7jOXl5fHGG2/Q1dXFPffcw/LlywkNDR272ig2m43u7m7MZjN+fn7jJoW+2Yz8vGpra6msrKSrqwu1Wk14eDgJCQlER0fj7e19039egiAIgnCrEc2UBEEQ/u6GBqp9fX2cOHGCDz/8kNzcXDo7O7FarSgUCjw8PIiOjuaRRx7hiSeeICgo6KYOfvbv38/vfvc72tvbWb9+PU8++SQxMTFjV5M5nU7Onz/P66+/TkNDA/fffz8rV64kNDT0pn2dg4OD5ObmsmXLFk6ePEl7ezsWi0X+vGJiYnjsscd4+OGHCQ8Plx839hD6MgeC36rd2wRBEATheolAVRAE4e9uWMTU09PDnj17+NOf/sTu3bvRaDQsXbqUJ598kvXr15ORkYFKpUKSpFtiriClUilPdny5CXtHslqt1NTUkJ+fT35+PpcuXWJgYGBcUHezMBgM7Nq1iz/84Q/s3bsXlUrF4sWL2bBhA2vXriU7OxtPT08UwxMXu5jNZi5dusTWrVvJycmhra0Nh8Mxatufh8PhoLOzk2PHjvHee++Rn5+P2Wweu5ogCIIgCIIgCN9ANySjarFYyM/P55VXXuHkyZOkp6fz6KOPMmvWLNzd3ZEkCYPBQE9PD1qtlri4ONRq9djN3FRycnL4j//4D9ra2li/fj2PP/440dHRY1eTSZJESUkJW7dupaOjg8WLF7Nw4UL8/f2vGuR+Hc6fP89f/vIXjh07xvTp03n00UfJzs5Gq9UiSRJGo5He3l68vb0JDw9Ho9EAUFpayssvv8zRo0dZsmQJTz75JKmpqV/48xwcHOT48eP89a9/paWlhZ/+9KesXLkSnU53U75/giAIgvBFiYyqIAjC392QjKrJZKK6uprKyko8PT1ZuHAhc+fOJTQ0lICAAAIDA4mOjmbKlCnExcWhUqnGbuKWp1AoSExM5JlnnuEXv/gFd9xxB76+vjdlkCVJEpWVlZSUlBAUFMTtt9/OjBkziIyMlD+vqKgoJk2aRFRUFO7u7vJjHQ4Hg4OD9Pf3y2XdX9ZrtFqt9PX1MTg4iCRJN23JtCAIgiAIgiAIXy7lc88999zYf/yiBgcHuXjxInl5eWg0GhYtWkRGRsaoLJurhHRkGa3D4WBgYIDOzk7MZjMqlQqLxUJNTQ1nz56ltLQUk8mEVquVy4XNZjMNDQ2cP3+eS5cu0dfXh0ajwcPD44qBjdFopLa2lgsXLpCfn09dXR1msxmNRjNhKXJtbS25ubkMDQ0xZcoUMjMz8fHxAcBut9PX10dbWxs9PT0oFAo0Gg12u52hoSEcDgcajQaNRoObmxtWq5Wenh66u7ux2+0olUpMJhM1NTWcO3eO8vJyjEYjHh4eE+6Li8PhoKenh0uXLpGXl0d5eTlmsxlPT08kSaK3t5fe3l6cTicqleqK78epU6fIycnB19eXBQsWkJaWhpeXl/x31+fl2obVaqW7u5vy8nJOnTpFQ0MDoaGhREVFwXBJsJubm3wTwm6309nZSUlJCefOnaOoqIjOzk6USiUeHh7yeg6HA4PBQGtrK0VFReTl5TE0NERaWhoBAQEYDAYcDgdqtVp+/V1dXVgsFrk02/V+uZpDdXZ20tnZicPhkN8H1zo2m422tjYuXrzIuXPnqK6ult97jUZz2fdeEARBEL5skiRhsVjo7OzEYDAQFhaGr6/v2NUEQRC+FW5IoGqxWKiurub8+fP09fURFxdHUlIS3t7eY1cdZWhoiNOnT/Ppp59SXV3NwMAAx44dY+PGjWzfvp1Dhw5x9uxZ+vr6CAkJwWQysXfvXt566y22bdtGTk4OZ86coampCU9PTwICAsaVoJpMJgoLC/nggw9477332LVrF0eOHOH48ePk5eVRV1eHSqXC399fLm/lCoGqyWSipKSELVu28Mknn9DZ2Ul4eDgBAQGUl5fz/vvvc/ToUZRKJSEhIXh4eNDe3s5nn33G3r17aW9vp6enh927d/P222+za9cucnJyOH36NK2treh0Ovz8/Ea9DqfTKTeq2rhxI5s2beLAgQOcPHmSvLw8urq66O3tJScnh1OnTgEQHByMp6envI2RFAoFpaWlnDlzBrPZPOrzmihQkySJpqYmNm3axKZNmygsLKSnp4fe3l5KS0vJzc2luroaX19f/P39aW9vZ8eOHbz55pvs2LGDI0eOkJuby/HjxyksLMRqteLn54eXlxdGo5GzZ8+yadMmdu/eTXV1NUNDQ7S1tZGXl0dubi4mk4ng4GCGhobYv38/n376KW1tbQQFBeHj4yMH05Ik0dbWxpYtW/j4448xm82EhISg1Wpxc3Ojo6ODgwcPsnHjRj766CMOHTpEbm4up0+fpq+vj4iIiMu+B4IgCILwZROBqiAIwt/dkECV4eY81dXV1NbW0tvbi1KpxMfHB61WOy54dBkaGuLMmTPs2bOH0tJSampqKCwspK+vD09PT/r7+ykrK6Ourg6TyURFRQV79uyhtbUVjUaDzWajtraW6upqbDYbERERhISEyIGGyWTizJkzvPnmm+zdu5fu7m6Cg4OJiIjAzc2NhoYGLl26RGtrK3q9nrCwMDlYnShQ9fLyoqqqiq1bt7Jjxw5MJhPTp08nMzMTvV5PSUkJH374IaWlpURHR5OamopOp6O9vZ1Dhw6Rk5NDdXU1paWlFBYWYjab0ev1GAwGKioqKC8vx+FwEBERgZ+fn9x8qqenhyNHjrBx40ZycnKw2+3Ex8cTFhbGwMAAVVVVFBcXc+rUKdrb24mNjSUxMRGdTjfmHf+7oaEhKioqqKysZGBgALVajbe3N15eXqhUqlHBmtPppLu7m7y8PIqLi+nu7sZkMqFWq1GpVNjtdry9vUlLSyMoKIjW1lZycnIoLS3F19eX5ORkgoKC6OrqoqioiObmZvR6PRERESgUCmpra8nPz6empobe3l4cDoccZDudTqKjo0lOTsZoNHLw4EGOHDmCQqFg8uTJhISEyM2enE4nbW1tfPDBBxw4cICQkBAmT56Mv78/BoOBI0eO8M4773Du3Dm0Wi0xMTF4e3szNDSEv78/U6ZMISAgQASqgiAIwldCBKqCIAh/d0MCVaVSiUajwel00traSnl5OZWVlTQ3NzMwMACAp6cnHh4eox5nMpkoLS3lxIkTVFdXo1AoyM7OZvXq1SxZsoSUlBSMRiOFhYVUVVXR3NxMREQEK1eu5J577iE9PR03Nzdqampob28nLCyM5ORkeV/Ky8t55513OHjwIEFBQaxZs4ZVq1axaNEisrOzCQoKoq2tjeLiYoxGI9HR0aOCp5GB6tSpU+nr62Pnzp3s27cPpVLJ8uXLueeeewgPD5f34+jRowwMDJCens6UKVPQ6XT09PRQUFDAuXPnaG5uxt3dnXnz5rFmzRqWLFlCRkaGvL/9/f2EhYURGxuLVqvFYDBw4cIFNm/eTF5eHklJSTz22GOsWrWKefPmMWXKFOx2O0VFRVRVVaHT6Zg2bZocJF+Ol5cXTqeThoYGKioq5Pd3cHAQhj8vVymsQqFArVYTHBxMcHAwPT09DAwMMH36dNatW8c999zD7NmzSU5Oludc9fb2JjMzk6VLl7Jw4UKmT59OXFwcXV1dFBcXo1AoiIuLIzg4GB8fH8LCwvDy8qK5uRmFQsEDDzzA2rVrWbhwIVlZWURGRjI4OMjZs2cpLy8nJCSE6dOnExYWJgeqkiTR1dVFTk4OlZWVTJkyhezsbAICAqirq2P79u2cP3+elJQUHnvsMe677z7mzJlDdnY2mZmZxMTE4OHhIQJVQRAE4SshAlVBEIS/uyGBqmJ43s2AgAB0Oh1ms5n6+nqKioooKSmhvr6ewcFBdDqdHMgoFApMJhPl5eWcPn2aoaEhbrvtNh5++GEWL15MYmIicXFx2O12Ll68SHNzM1FRUTz22GPce++9TJo0iejoaDQaDbW1tTQ2NhIcHMyUKVPw9fVlcHCQAwcOsHnzZjQaDWvXruXBBx8kIyODyMhIYmJiCA8Px263U15eTl1dHaGhoUyaNEneZm5uLgaDgfT0dEJDQzl9+jS7du3CZrNx77338sADDxAfHy+Pt6yrq+P48eMYjUays7PlQLW3t5eLFy9y6dIl3NzcuOeee3jssceYM2cO8fHxJCYm4u7uTnV1Nc3NzQQGBjJp0iT8/Pxob29n//79HD58GG9vbx577DHWrl1LcnIy4eHhxMfH4+vrS3NzMzU1NXh7ezN9+nRSU1PRarVjPyqZp6cnwcHB6PV6TCYTdXV18udVW1vL0NAQnp6e6PV61Go1Go2G8PBwPD09KS4upqmpiZkzZ7JmzRpuu+02YmNj0ev1KJVKOVuZlpZGTEwMgYGBBAcHExMTQ39/P4WFhdhsNuLj44mPjyc0NJTg4GCsVisXLlzAarWybt06VqxYwaRJkwgNDUWj0dDd3c2FCxeora0lIiKCGTNmjAtUe3p6OHr0KPX19aSnpzN9+nQCAwOpqqri4MGD9PT0cNttt7Fy5UomT55MZGQkiYmJREREiCBVEARB+EqJQFUQBOHvLt9d5wtSq9VER0dz//3388Mf/pAnn3ySWbNmYTKZ2L17Ny+++CJvvvkmly5dwmazjXqsUqkkODiYzMxMkpOTcXd3l7NyycnJREdHo9PpmDRpEhkZGej1ehQKBVqtltjYWBISEtBoNHR1ddHT0yOXgF64cIH29nZSU1NZsGDBqKBGqVQSGhrKzJkzSUtLo6+vj6KiIlpbW0ftG8DAwABnzpxh//79GI1G7rjjDlasWEF8fLy8vWuhVquJiopi5syZJCQkyI/18PAgKSmJxMRETCYTLS0tDA0NYbFYaG9vp7y8HJPJRHp6OjNnzsTf31/epkqlIiEhgYyMDIKDg6+5o7JCoSAyMpIVK1bwgx/8QP68DAYDe/bs4aWXXuKdd96RS5RdJEnC6XQiSdKoZeR2lUolarUaSZLo7++npqaG8+fPc+HCBbnJ0cDAAL29vVit1nHbZbiMd+R2vyiNRoNWq8VsNlNVVUVRURHt7e3Y7XYY3m8RpAqCIAiCIAjC1+OGBaoMB39BQUHMmzePp59+ml/84hc8++yzzJo1i7a2Nt599122bNlCY2OjHCAwHGzp9Xp8fHxGNTRSKBRyVs/d3R1vb290Op0c4Lm5uaHVavH19cXd3R2j0YjZbMbpdNLZ2UlDQwNqtZq4uLhx06wwHCBGRUURHx+Ph4cHLS0ttLW1jVrHZDJRUFDAp59+SnFxMTExMSxevJjk5ORrDgpdVCoV3t7e8v6O5OnpiU6nk7vgWq1WzGYznZ2dtLe3A8ilsmN5eHjg5+c36r25VgEBASxYsED+vJ555hlmzZpFZ2cnW7du5dNPP6WxsXHCoHFskOri6vibl5fHli1beO2113jhhRd4/vnn2blzJ62trVitVmw2G06nc+zDb4jIyEimTZuGn58fZ86c4fXXX+fdd9/lxIkTtLS0jLt5IgiCIAiCIAjCV+eGBqouKpWKwMBAZsyYweOPP87PfvYz7rzzTgYGBsjJyeH8+fOYTKZRj1EoFJedTkWhUEwYELmyYBNlwoxGo1y+6uvri1qtHreem5sbnp6eeHt7y4GuwWAYtU5PTw/nzp2joKCA3t5ejEYjAwMDcibwelxpfyf6m91uZ3BwEIPBIDenGjmFzEhXev+uxvV5TZ8+nccff5x//Md/ZNGiRZjNZg4dOkRRUdE1B3I2m42mpiZ27tzJ//2//5c//vGP5OTk0NnZiUajQa/Xfy3TwAQHB3PHHXewevVqYmNjyc/P509/+hP/5//8H95//30qKiqwWCxjHyYIgiAIgiAIwlfg80Uyn5NCoUCv1zNjxgxWrVpFYmIivb298hym18oVpI7N4E0UvI419jFjOZ1OucxUpVLJWVJX0ChJEsHBwcyYMYPw8HCKi4vZuXMnly5d+lzB6vVyBXROpxO73Y7D4Ri7iuxKr/NauLm54evry7Rp07j77ruJjo6mqamJmpqacQH8RKThMaIHDx7kb3/7G8XFxcyaNYuf/OQn/Nd//Rcvv/wyP/7xj5k8efKozPlXQalUkpyczBNPPMHPf/5zHnnkEZKSkigtLeWvf/0r7733HvX19aMy/YIgCIIgCIIgfDW+0kDVRaVSERQUREREBA6HA5PJdMWA68ug1Wrx9vbGaDTS2dmJ2WweF8i5ymx7enqwWq34+vqOa2Lg7+/P3XffzU9/+lMeffRR9Ho9x44dY9++fTQ2Nt7Q0lV3d3d8fHzw8fHB6XTS0dEhd1EeyW63YzabsVqt417j56HRaAgKCpLHwg4NDY0aS+oyNitqtVqpr6/n6NGjNDc3c9ddd/GLX/yCRx55RJ76RaPRfO7Mr6sJl9PpxGazYbPZxr3eK41tVSgUBAYGcvfdd/Ob3/yG3/3ud6xevRpJkvj00085e/YsRqPxso8XBEEQBEEQBOHG+HwRwjVwOp04HI4JAze73U5fXx9dXV2o1Wq5k+yN4ubmRnBwMHFxcdhsNnm6HKPROGo9g8FAZWUlpaWlmM1meXoaRmRivby8CA4OJjk5maVLl3L77bfjcDjYs2cPOTk59Pb23rDAxsPDg/DwcKKiopAkidLSUmpra0cF+dLwlCxVVVW0t7dfc5bX9XmN3XdpuANhb28vfX19uLm54efnN2pqoZFZ3pGPt1qttLW1UVdXh8PhYOrUqYSHh8t/d90YMBqNEx4nLq6/jQ2EPTw80Gq1OBwOuru75RsMLna7ndbWVrq6unA4HONKqUfSarVMnz6dRx99lMTERFpbW6murqa/v/+K+yYIgiAIgiAIwpfvhgSqFotFvtDv6urCZrPhcDhwOByYzWaqq6s5cOAARUVF+Pn5ER8ff0NLP5VKJdHR0cyePZuIiAhKS0v57LPPaGpqkhv4WK1WGhsbyc3NpaKigtjYWGbNmkVoaOiobUmShN1uR6FQkJCQwPLly8nMzKS5uZkdO3Zw9uzZL7VcdGTgp1QqCQkJYerUqej1es6cOcOuXbuorKyU3+Pu7m4OHz7MoUOH6O7uHhd4Xk5bWxtVVVVysOf6vCwWC/X19Zw6dYrW1lZiYmJITEyU52TVarXodDqcTifd3d10dXXJDawYUTLtGO7s68pkO51OGhsbyc/Pp7GxEavVOiqQdHNzw93dHYVCQV9fH+3t7XJA67pp4OvrS2hoKEqlkoaGBkpKSujt7ZUzrB0dHezfv5+ysjIkSRqVubXb7VitVux2O84R5d6ufVOr1Xh5eU04llkQBEEQBEEQhBvrhsyj2tHRwUcffcR///d/89lnn9Hc3ExbWxvl5eUcOHCAV155hV27dhEYGMjDDz/M8uXL8fX1xWw2U1ZWxvnz51EoFEybNo3U1FQ5e+d0Omlubub48eM0NzczdepU5syZI09PI0kSvb29FBQUUFZWRkBAALNmzSI6OhqlUolOp2NwcJDz589TVlZGd3c3DE83c+7cOd5//3127doFwKpVq1ixYoVc+ltTU8OxY8cYGhpi6tSpZGZmEhgYKM8VWl1dzcWLF7FarcTFxREWFjZq7tWMjAymTp2KTqejp6eHgoICysvL8fb2Zs6cOcTFxY14B6G3t5czZ85QUFBAREQE8+fPJzw8HK1Wi16vZ2BggNLSUvLy8igsLKStrY2ioiI2btzIzp076evrw+Fw4O/vT3Z29hXnUTUYDLzzzjv89re/5ciRIzQ1NdHa2kp5eTn79u1j48aNHDhwAA8PD9auXctdd92Fj48PDAfP1dXV5Ofn09raisFgwGAwYDKZ8PLyQqFQUFtbS01NDb29vXL2vLy8nHfffZfdu3fT2tqKr68vmZmZTJ48Gb1ejyRJDA4OcunSJaqqqujq6sJkMsmvy8vLCw8PD4xGI/X19ZSXl9PQ0CA3wLp48SKvv/46J0+epL+/H4fDQUZGBtnZ2fj5+VFQUMBHH33E+fPn6e/vp7e3l/z8fN577z3OnTtHamoqa9asITk5WQSrgiAIwlfCVcUk5lEVBEG4QYGq0WikurqawsJCLly4QG5uLnv37mX37t0cO3aM9vZ2UlJSeOKJJ1i/fr2cFTObzZSXl3PhwgXc3NyYPn36uEC1tbWVkydP0tzcTHp6OnPmzEGn08mBal9fHxcvXqSiooKgoCBmz55NdHQ0CoUCb29vIiIiUKlU1NfXk5eXx86dO9myZQs7d+6krKyM8PBw1q9fz9q1a4mJiZGzcLW1tZw4cQKDwSAHqq7pc7y9vbHb7dTU1FBRUYFarSYpKYne3l5OnDiB0WgkMzOTKVOmoNPp6O3tpbCwkIqKCvz8/CYMVPv7+zl37hyFhYVERUUxb948wsPDUSqV6PV6IiMj8fLyorOzk5KSEo4fP87JkyexWCwsXLiQyZMn09fXh4eHB9OmTSMlJeWKgWpFRQWFhYUUFBRw/Phx9u7dy549e8jNzaWtrY2kpCQeeeQRVq1aRVRUlPy+uLKe7e3tVFZWkp+fz+HDh2lqaiIxMZHExETc3d1pamoiPz+f/fv3s3nzZj755BN6e3uZNGkSer0egOTkZKZMmYK3tzdKpRIPDw8cDgf19fWUlJRw6tQpjh8/jkajIT4+Hh8fH7y9vQFobm6mrKyM06dPs3v3bg4cOMDQ0BDr1q3D39+flpYWEhISyM7OJiAggPLycrZt28bHH3/M1q1b5WOgqqqKxMREnnjiCebPn4+3t/fnHkMrCIIgCNdDBKqCIAh/p5CutTb0OrjmzSwpKaG4uJjm5mYMBgOSJKHT6YiMjJSzZ66gRKFQYDKZKC0t5cyZMyiVSmbOnElKSsqoQLWlpYXc3FwaGxvJysqSA1WGT/CuzFhpaSmBgYHcdtttREdHy/tms9lobW2loKCA8+fP09TUhNlsRqvVEhsbS3Z2NlOnTiU4OHjUuNmamhqOHDnC4OAgmZmZcqDKcKlzXV0deXl5NDY2EhcXx7x583A4HPJjpk+fTnp6Olqtlt7eXi5cuEBpaSl+fn7MnTt3XKDa19fHmTNnKCwsJDIyUg5UXUGT1Wqlu7ubsrIyiouL6e7uRqfTMWXKFOLj4zl+/DivvfYaXl5efO973+Ouu+667I+dw+Ggq6uLS5cucenSJVpaWhgaGgJAp9MRHR1Neno6ycnJ+Pv7jxtPbDQaKS4u5tSpU/KY2bS0NJYsWUJsbCyDg4NcuHCBkydPUltbiyRJhIeHM2vWLGJjY6mtraWjo4OUlBSysrLk99W1X6dPn+bMmTP09PTg5+fHggULmDFjBn5+fkiSRGdnJ/n5+fL7DxASEsLMmTOZPn065eXlXLx4kYSEBGbMmEFwcDCdnZ2cP3+e4uJi2tvbsVgs8hjgGTNmMHnyZHx9fa97HlpBEARB+LycTif9/f0UFxfT0dFBdnY2sbGxY1cTBEH4VrghgSrDJ1uz2YzRaMRiscjjNlUqFRqNBp1ON6ohz8jHGAwGFAoFWq0WDw+PUWWXNptN7jrr5eWFl5fXqGDC4XBgNBoxm82oVCq0Wi3u7u7y313rmEwmBgcHMZvNOBwOVCoVnp6e6HQ6PD09x2XRLBYLQ0NDctmpp6en/LySJGGz2TAYDJjNZrlBlEKhYHBwcNxjXPtoMpnkfRw7Rte1jtFoxN3dHZ1ONy5AdDqdWCwWjEYjVqtV3tbAwADvvfceb7zxBnFxcfz4xz9m/vz5l51zlTHvvWuMqiRJKJVKPD095X10fRauu759fX3ya3Zzc5PnV/X09JTnSJUkCZPJxMDAACaTCUmS0Gg0ckbaZDJhtVrx8PAY93k6nU6GhoYYHBzEZrOhUqnw9vbGy8tLnjrI6XRiNBoZHBzEZDKhUChwd3fH29sbrVYrv48ajUZ+nOsYcL13TqcTNzc3eW7XscedMDFpxHRPiis0qxIEQRCuTgSqwhcx8vdYuLWMDMfE5/d3NyxQvV52ux2LxSI3snF3dx8XLLpIww2NLBaL3HTHlZX9NpAkCcdwF9ux75HD4eDs2bO89NJL5OXlsWjRIp555hmmTp0qB3ZfhCRJWK1WioqKOHDgAJcuXWJoaIjIyEjuuece5s2bd9nMrfDNU1tby8GDB2lvb2fatGnMmjULPz+/b813Ubj5uH7Sxv7oX+2YvJafwqttQxC+KBGo3rzGnltc54PPc14Yuy2u8Tx1OQ6Hg87OTurr6/Hx8SEqKkruE+Iy9jm/yPMx5kY117G9iR438n+/LBM9z+d5ji/y2zDRez7yf11sNhsNDQ20tbURExNDcHDwuCTbt9VNEag6HA5qamo4ePCgPJZw/vz5xMbGTlh6abVayc/P59ChQwQEBLBgwQLi4uLGZSW/iSRJoru7m8LCQvr7+wkPDycwMBCVSoXNZqO2tpYdO3awf/9+goODefzxx7nvvvsICQkZ98X4PMxmM+fOnWPjxo0cPnwYh8OBVqslJiaGtWvXsmzZMoKCgsY+TPiGOn36NC+++CJlZWU88MADbNiwgcjIyHE3UAThRnM6nRgMBpqbm2lvb2dgYACn04lOpyM8PJyIiAi50mUsq9VKXV0dBoMBxlxESJKESqXC19eXoKCgcZVAgvBlEoHqzclms8nT7fX29qJSqQgKCiIyMpKAgIBrDiqk4Qqzjo4O2tra6O3txW634+XlRUhICJGRkf8/e/8dHsd15enjbyegkXPOAJFBgAAJgpkUxSRGUcmUlSwH2ZbsteyZ8fqZ73pke3Z3duzReNbjpGRlkRLFJDGJFAUmgASJnHPOqQE0Gp27f3/8qmoRSUqWPBRV7/PUQwld8VbVrXvuOedzPrU2hjguPHz4MIWFhWzfvp3Nmzfj6+uLQtBvmZqaoq+vj+7ubvR6PS4uLoSEhBATEyOl4N0q4jX09PTQ0dHB5OQkWq2WiIgI6fzn25/dbmdycpKenh56e3uZmJhArVYTGBhIVFQUgYGBn0s0m3i9XV1d0vW6u7sTERFBdHQ0np6en6p9+/v7pQoms8/N6XSi1WoJCQnBx8dnRqSlTqejr6+PwcFBJiYmUCgU+Pr6Eh4eTmhoKO7u7tJ5mM1mrl27xgsvvEBaWhr79u0jOjr6c3Ewfdm5LQxVq9VKQUEBzz//PJWVlcTHx/PII4+wc+fOOeVhEMR/Dh48yG9/+1vi4uJ4+umnWbVqlZSreifjcDhobm7mnXfeobCwUBJzcnFxkTrSnp4e/Pz82L17N3v27CEhIeGWO9EbYbPZ6O7u5oUXXuDNN98kICCAnTt3kpqaiq+vLwkJCcTGxuLm5jZ7U5k7lIKCAn7zm99QW1vLQw89xLe//W2ioqLm/UjJyHxRWK1WOjo6OH36NIWFhYyMjDA1NYXT6cTNzY3o6GjWr1/PXXfdRWRk5IzBht1up6+vj3//93+no6MDxzx1k93c3MjNzeXBBx8kMjJy9s8yMp8bsqF6e+EUKhCUlJRw6tQpampq0Ov1KBQKgoODWbZsGRs3biQtLW1BwUoRsQxiUVER165do62tjYmJCex2O66uroSEhLBixQq2bNlCXFzcnHSvhTAYDBQUFPCf//mfqFQqfvCDH7B69WppUm1gYIArV65w4cIFGhsbmZycRK1WExISwurVq9m6dSuxsbG3dDybzcbg4CAFBQWcPXuW1tZWTCYTLi4uREREsGHDBjZs2EBUVNSMcafZbKazs5MLFy5w+fJlent7sVqtOJ1OPDw8yMjIYNOmTWRnZ+Pn5/eZxxA2m43+/n4uXbrExx9/TEdHh3R+YWFhbNmyhbvuuovw8PBbNgJfe+01zp8/z8TExLze1ejoaPbs2cOKFStwd3fHarVSX1/PqVOnqKqqYnBwkKmpKRQKBW5ubixatIiNGzeyatUqgoODUalU2Gw22traeO6552htbeW//bf/xtatW/Hz8/tURvWdyBei+vtpcTgctLS08PHHH9PY2Mjo6CgKhYKIiAjCw8PnvDxms5mysjLOnj2Lu7s7K1asIDY29nMxxm53nE4nJpOJkZERqW5pf38/fX19ksrv4sWL2bNnj9TZfV6eZpPJRGVlJYcOHaK3t5f77ruPb33rW6xdu5akpCQCAwO/EvdA5v/R1dUlGQYZGRnk5OTg4+MzZ9ZRRuaLQpzdLy0t5fe//z3d3d34+vri5+eHi4sL/f39VFZW0tbWhpubGzExMTMGlFarlcbGRp5//nmqqqok/QKdTodOp2NsbIypqSmCg4PJysrCz89vxvFlZD5PnLLq722DaKQWFhby2muvceHCBZRKJSEhISiVSlpbW6mrq8NkMhEcHExAQMANjZ+JiQmp8kFNTQ0KhQIfHx9cXFwYHR2lurqahoYGEIwf0SN6I0QHwqFDhygvL2fnzp1s2rQJHx8flEolw8PDnD17lnfeeYfy8nJcXFwIDAzEZrNRX19PfX09SqWS6OhovL29b3g8h8PB4OAgH330EW+99RYVFRX4+voSEhKCyWSSygmKRqGXl5ekXdLW1sbBgwd577336O3tJSQkhIiICNzd3ens7KSqqoqRkRH8/f0JDg6eoYlyqzidTvr7+zl58iTvvPMOVVVVBAQEEBISgsVioaSkhObmZjw9PQkNDb0lz6rNZuOll17iww8/lN7JsbEx6fsgetfT0tKkyQWz2czp06d59913JaFT8X50dHRIJSW9vb2JiYnB1dUVlUolfZfy8/OxWq0kJibe9Jn6KnDbGKrt7e0UFBRIN91kMuHm5kZsbOycnDeLxUJNTQ0FBQX4+/uzcuXKGxqq02dAPu2D/1kRj/lZjud0OhfcTqFQSCEW6enpZGdnk52dzbJly1i7di133303mzdvZvny5YSFhc0x8m/EjY6LMGtXXFzM+fPncXV15aGHHmL58uW4CPnEC23717TFrXCz/X/W+/9Zt+MW2nI+bnYd83GzbW72+0Lc6rWLhurw8DDp6em3ZKje6r7n47O0q8ydjUKhwG63YzAYGB4e5p577uHee+9l48aN5OXlERkZydDQEDU1NVgsFhITE6WSZQgTnxUVFZw4cYKoqCgeeeQR7r77blasWEFeXh55eXmsXLmS3NxcYmNj5dDfLymftS+8EX9NX7YQTtlQvW2wWCw0NTXx1ltvkZ+fT0ZGBo8//jh79uwhNzcXrVZLU1MTHR0deHh4EBcXd0NjzySUYNTr9Sxfvpw9e/awbds2Vq9ezaJFizCZTNTV1dHR0UF8fLzk5VxofwhVF0pLSzl69Ch+fn489NBDJCcno1KpsFgsXLlyhXfeeYfGxkaWLl0qRStmZWWhVCqpqqqitbWV6OhooqOjb2gg6vV6rl27xptvvklDQwN33303Tz75JPfccw9ZWVmYzWaqq6sZHR2VDFGtVsvY2Bj5+fkcOHCAyclJ9u3bx6OPPir1s6GhobS1tVFbW4tWqyU+Pv4zeVX1ej2XL1/mrbfeor29nU2bNvHkk0+ybds2srOzMRgMlJWVMTo6SmRkJOHh4Te8XqdQ8vLgwYP09fWxfft2du3axZo1a8jLy2PFihXSd2Lx4sX4+/ujUqlwCKU0VSoVW7ZsYdeuXWzcuJHly5fj7+9Pf38/jY2NOJ1O0tPTCQgIQKlUolQqCQgIoKKigurqailK8fMIh/4yc9sYqmKdUqfTSUxMDGazmdHRUQIDA+cMDiwWC9XV1Vy+fFmqQzrbUHUKgkNTU1OMj48zMTGBxWJBoVCgVqtn3HRxXbPZLKnWLmR4ieuJKsbT13M4HFgsFvR6PWNjYxgMBux2u/QATt+fuO70mHez2cz4+DgmkwmlUrmgQJRKqKUaFhZGQkICycnJJCQkEBUVRUhICH5+fri5uc25ToRrtVqtUlsoFAqsVqt0XHH/87WPTqfj+vXrXLt2DQ8PD9avX09sbKxkPIgL0xSJ9Xo94+PjGAwG6Vpnt4W4vtgeCB99sS2NRqM062U2myUhKafgXdbr9ZIq8PR2Ez/4ExMT0v2f717MZr7nhgXaxWazYRFUkpVKJU6nk8nJSSk/Tq1WS+c+H+L9mP7MzH62ph/HIagTO51ODAYD4+Pjkhq1SqWStnEIKs4TExPzts1C2Gw2jEajdO1GoxGHwyFtN3vbGxmq4nlPf1+m3w9RAVo85+n7Fp8f8Z4pFApMJhPj4+NYLJYZ1yojo9FoCAwMZMmSJaxcuZJFixYRERFBVFQUcXFx6PV6GhoaMBqNJCUlkZ6ejkqlwinkMl25coXz58+zZs0avvvd77JmzRoyMzPJzMxk8eLFpKenExUVhZubm/zMfclwCKrwg4ODjIyMAHwuAz+73c7Y2Bj9/f2YzWY0Gs1N+9dbQfxuyYbqfy1Op5OJiQnOnTvHkSNHcHNz4xvf+AY7d+4kPj6emJgY/P39GRkZoaGhAYvFQlJSklTvfj5UKhUBAQFkZ2ezdu1aMjMziYmJITo6mtjYWNzd3WlubqaxsZGwsDDS09NvOPHrdDoZHBzk3LlzlJaWsmbNGjZt2iQ9L319fRw9epTz589LKXWbNm0iLi6OyMhI/P39aW9vp7KyEm9vb1JTU/H39593zOJwOOjq6uKDDz7g0qVLJCQk8P3vf59169YRERFBXFwcnp6etLW10djYiIeHB4sWLcLPz4++vj5OnTpFeXk5eXl5fPOb3yQrK4vAwEApL7erq4uKigpcXFxITU0lIiLiUzlaEMpIHjt2jCtXrpCSksJTTz3F6tWriYiIID4+Hh8fH+rq6qivrycoKIhFixZJns75cDqddHZ2cvToUWw2G08++ST33nsvOTk50rchMzOT5ORk/P39Jc+nSqUiLCyM7OxscnNzSUhIICIigtjYWCIiIiSdGbvdTkZGxowJCQ8PDyl02d/fn+TkZHx9fRc8x68Ct52hqlKpyM7OxsXFhdbWViwWCzExMYSFhUk36maGqt1uZ3x8nKamJgoLC7l06RLFxcU0NjYyMTGBq6urVCpGoVBgs9kYGBigsrKSxsZGHA4HXl5ec14SMcSitLSUrq4uVIKrXiXMXA0MDFBeXs6lS5coLCykoqKC7u5ubDYbbm5uuLq6StcwMTFBfX09jY2NWK1WbDYbVVVVnD9/nq6uLry9vW+YUC8aaX19fVRUVHDlyhWuXr1KeXk5zc3NjI+PoxZKAU03WKempmhoaKC2thabzYZCoaCmpobz58/T0dGBm5sbPj4+M0INLNPyKi5cuEBdXR12ux1vb2/Gx8cZGBhAo9FIYRQmk4menh4qKiooLCyUzqulpQW9kMQvhjqI5zUxMUFDQwPNzc2SgVJbW8vly5dpa2vDx8cHk8lEWVkZAwMDqFQqRkZGKCkp4dKlS5SUlNDR0YFdEHdSq9UMDQ1RXFzMxYsXKSoqoqWlBaPRiKurK1qtds7HxCGUwmlpaZGem5KSEurr66X21Gq1UntahZq8YhiHVqtlcHCQCxcuUFhYiEKhwN/fHxcXl3k/NDabTQr3EbcRQxStVivu7u5otVqsVitdXV1UVlYyODiIVqulv7+fgoIC6Rx7enpQKpVSCaLe3l6Ki4u5dOkS169fp62tDbPZLO1z9nPlcDgYGxujubmZoqIiCgoKuH79OrW1tfT29mKz2dBqtZL3XGQhQxVgcnKSmpoaSkpK6OzsZHh4mMrKSgoKCigqKqKmpoahoSHpvMWOWrwPpaWl1NbW4uPjg8FgkJ6/sbExfHx88PDwmHMdMl9d1Gq1FEYnvm8KYWKyt7eXyspKLBYLubm5ZGVlSe+/wWDg3LlzFBcXs2nTJlatWiWJgahUKtRqtTwx8iXGYrHQ0dHBhQsXKC0txcXFhfDwcGmSQvzeiBOg4nIzDAYD5eXlfPLJJwwPD+Pn5yeFOv41yIbq7YHdbqenp4cjR45QUlLC6tWr2bt3L9HR0dLYxc3NjYmJCaqrqxkbGyMmJoa4uLgFc1VVKhW+vr4EBwfj6ek5Ywyi0WhwdXWlubmZhoYGAgMDyc7OlsKM58NqtdLa2srx48cZGRlh27ZtLFmyREr3qqio4Pjx4/T397N+/XruueceSVhTJZQeHBsbo7q6GoPBQGZmJlFRUfOGmppMJmpqavjggw8YGBhg586dkmATQl/r7u5OR0cHFRUVaDQaUlJSCA0NZXh4mAsXLtDV1cXKlStZvXo13t7e0r7VajV1dXVUVlbi5eVFdnY2MTExC0ZJzofFYqG8vJwTJ05gMBjYtm0bW7ZskcYjAL6+vjQ3N1NdXY2HhwepqamEhobOGeuL2O12GhoaOHnyJD4+PmzZsoX4+Hhp/KpWq6Xvw/Q+QyFEPop2xPTf1Go1bW1tXL9+Ha1WK02siuegUCgwGAxcuXKFqakpMjIyiIiImPeefFW4rQzVS5cuoVQqWbt2LZGRkXR2dtLa2oqXlxdJSUl4eXnBTQxVu93O8PAwhYWFvPXWWxw4cICLFy9SXl7O5cuXKSkpwWKxEBgYiLe3N2q1GrPZTFVVFW+88QZHjhzBYrEQHx8/Jz9Ap9Nx/Phx/vjHP1JbW0tYWBiRkZE4hBzbDz/8kNdee40TJ05QUlLCtWvXKCgooLOzE3d3dwIDA3ETarR2dnayf/9+jhw5gk6no7u7mzfeeIO33nqLoaEhkpOTiYmJmffhFL12dXV1HD16lFdeeYWjR49KCfri9U5OTuLt7T1j8DY4OMi7777LW2+9xfj4OENDQ7z55pu8/vrr9Pb2EhsbK8XMi4yPj3P58mVeffVVLl68iE6nQ6/X09TUxOXLl2ltbSUkJITo6GjsdjvV1dUcPnyYN954gw8++ICioiKuX7/O+fPnqaioYGpqCl9fX3x8fKSXuKuri0OHDnHs2DFGRkbo6uriwIEDHDhwgN7eXlJTUxkYGOAPf/gDZWVl2Gw2ioqK2L9/P8ePH+eTTz7h8uXL9PT04O3tjdPp5OOPP+bFF1/k+PHjXLhwgfz8fBoaGtBoNISEhMzIT3A4HOh0Oq5evcqbb77Jm2++yeXLlykrK5Pa02g04u/vL5335OQkV69e5cUXX6S4uBgXFxc++ugj/vjHP3LmzBlCQ0NJSUmZd/BiF6Tkz5w5wwsvvMDBgwe5du0a169f59KlSxiNRkmi3Gg0cv78eV566SVpoHX27FleffVVPv74Y86dOyeFzfv6+jI+Ps6pU6d4/fXX+fDDDzl//jznz5+ntbUVDw8PIiIiZniGHA4H/f39nD9/njfffJP9+/eTn59PSUmJZLC3t7ejFlQOpyvVzWeoent7MzU1RVlZGX/4wx949dVXuXLlCteuXePEiRNcvnyZ0tJSyYgeHR3F19d3hnJiX18fzz//PO+88w7h4eEUFxfz5z//mcOHD2O320lOTiYkJGTOZIOMDEIfKf6r0+mkycqQkBC2bNlCUlKS9PxPTExw/Phx6urq2LFjB4mJiTMGF7ditMjcvhiNRqqrqzlz5gy1tbX4+fkRFxfH8PAw1dXVtLS00NXVxcjICCqVSvr2ORyOGy7Dw8NcunSJCxcuMDk5SURExOdSUkI2VG8PzGYzTU1NHD9+nL6+PrZt28batWvx9PSU+gRXV1d0Oh1VVVUMDQ0RFhZGWloa/v7+s3d3UxQKBWazmZKSEmpqaoiMjGTVqlUznDSzMRqN1NTUcPbsWby8vCRvr1KplMZIn3zyCW5ubtx1110sWbJEEh1VCJPCY2NjFBUV0dnZSXZ2NomJifNGHIyNjXHt2jU+/vhjFAoFDz74IJmZmTOMPJVKRU9PD/X19TgcDpKSkoiPj8dkMlFVVUVTUxM+Pj4sXrxYCncFGB4eJj8/n9raWhYtWsSaNWuIjIycd/y7EGNjYxQWFpKfn4+Hhwf33nsvKSkpM95HtVpNd3c31dXVOBwOKa90+nh3Ona7XdLDiYyMJC8vj8DAQGnSUlxuhvg9Eic/Ll68KF3rjh07iIiImDOWuX79Oi0tLWRkZLBo0aIbhijf6dx2hqo4452ens7Y2Bi1tbWMjY0RFhZGfHw8arV6QUNVo9EwMjLChQsXePXVVykpKSEzM5MHH3yQu+66i5CQEJqamigtLUWhUBAbG4uPICc9NTVFfX091dXV0kA4Ojp6RgfR0tLCsWPHqK6uJjExkQ0bNhAaGkp7ezvvvvsu7733Hna7nXvuuYfdu3eTk5ODxWLh2rVrdHd3ExISQnh4uOR5KywspLS0lP7+fsrLy+ns7CQmJoa8vDyWLl1KWFjYnIcXYWarurqa119/nXfffRej0cj69evZsWMHubm5eHh40NzcTFlZGZOTk4SGhhIUFIRGo2FsbEwyGoaHhykuLqapqYmIiAiWLVvGsmXL5oRc2Gw2KYR3fHwcvSD1nZmZSXp6OklJSWRmZhIYGEh1dTWvvfYahw8fxmKxsHbtWrZv386yZcvw9PSkoaGBK1euYDKZiIqKws/PT7pv169fp7Kykt7eXqk9wsPDWbZsGbm5uej1esngam5upqOjg9DQUJYvX05oaChDQ0M0NDRIExxnz55Fq9WyceNGEhMTMRgMVFdXMzQ0JIWbuAkKxXpBMOFPf/oTV65cYcmSJdx3331s3LiRiIgIOjo6KCsrw263S+dttVppamri/PnztLe309HRwdWrV9FoNKSnp7Nu3TqSk5Px8PCY08Ho9XouXbrEf/7nf1JbW8vatWvZvXs3K1euxM/Pj5iYGFJTUwkKCsJms1FTU0N+fj6NjY10dHTQ2NhIRkYGGzZswNfXl97eXqqqqtDpdJSVlVFcXIyvry9r1qwhJiaGsbEx6urq6O3tlcKTxI+ATqfj8OHD/OlPf6K0tJS4uDjuueceqd0mJye5fv06ZWVlBAcHEx0dLX3I5jNUXV1dqa2t5S9/+QunTp1iYmKCkZER+vr6SEtLY8+ePWzdupWkpCSGh4e5fv064+PjkmGuUqkwGAwcPnxYanNxPwkJCaxcuZKsrKwZHzoZGaZFmojpAENDQ5w/f16aENyyZQvbtm2bMfAfGxvj8OHDtLW1kZ6ejsViYWRkRArDVwheWflZ+3JiFtRGa2trmZiYkPLICgsLOXToEIWFhVy/fp36+nrpfuv1eoaHhyXRwtnL6Ogo3d3dUsSJl5cXycnJUs7bX4NsqN4eTE1NUVFRwcWLF1EoFGzfvl2K9hO/5wqFguHhYaqqqujt7SU4OJjs7GyCg4Nn7+6m2Gw2ent7pQn13Nxc1q1bt2AoLsI4oqysjOvXrxMVFcXdd98tVcqYnJzk8uXLXLlyheDgYDZs2CAZPCJ2u52RkREKCgpoaWlh+fLlZGZmzqm/CjA6OsrVq1cpLi4mKCiIXbt2ERcXN+PcVCqVFGWm1+tJSEggNTUVd3d3RkZGpHxYDw8Pqazi5OQkn3zyCadOnUKpVLJ582ZWrVo1R5vmZgwNDXHp0iWKiooICwtj165dkvdbRKlUStFmExMTpKamkpiYOO/1IrTP5cuXuXjxIr6+vnh7e0tjYZPJhFMoXTbboyoiRm3o9XomJibo7u7m1KlTnD59Gq1Wy44dO7jrrrvmjBFdXV0pLi6mrKyMjIwM0tPTFzzHrwK3naFqNBrJzMwkKysLNzc3Wltbqa2tRaVSkZiYSGBgIFardV5D1eFwUFlZKSmqbd26lb//+79n165dLF26lNzcXNzc3CguLmZgYICoqCiioqKkEMLx8XEaGhokz2JaWpr0UtvtdoqLizl69Kj0Mq1cuRKr1crZs2c5duwYbm5ufP/73+c73/kOq1atYsWKFSQlJTE4OEh5eTkAKSkpBAQEoNPpKCkpoby8nIGBAYKCgnj00Ud55pln2LhxI1FRUfPOoDidTsn7+OGHH+Ll5cVTTz3Fj370I7Zs2cKaNWvIzc3F1dWVhoYGWltb0U5LTtfr9ZSWlkrhy15eXjzyyCM888wzbNmyhVihvMz042o0GsLDw0lJScEiiAuEhYXxwx/+kO9+97usW7eOmJgY+vr6eP/99zl16hSBgYE89dRTPP3002zdupXVq1eTm5uLRqOhtraWhoYGfIWSNp6enoyNjVFeXk5JSQnd3d34+fmxb98+nnrqKTZv3kxUVBSdnZ0UFBRQVVWFVqvl3nvv5Xvf+x73338/S5cuRaPR0NTURGVlJd3d3axYsYK/+7u/4+tf/zrr16/Hx8dHqvvl4+NDSkoKfn5+OBwOGhoaeO211ygpKWHLli389Kc/ZdeuXeTm5pKXl4dWq6W2tpaBgQFCQ0OJiYlBpVLR3t7O1atXaW1tZXh4mA0bNvCDH/yAhx9+mCVLlkgTIdPb0yko0x0/fpzr16+zYsUKfv7zn3PvvfeyevVqVq1axdKlS6VBjzizW1xcTFdXF66urnzjG9/gRz/6ETt37mTZsmVMTk5K1z4+Ps6mTZt45pln2LdvH6tXr8bLy0sSaQgKCiIzMxNPT08cDgeXLl3i5ZdfpqWlhc2bN/PjH/+Yr3/966xbt45Vq1aRmJjIwMCAFMqekZFBaGgoarV6hqG6ePFilixZwuDgIO+88w7Hjx+XQtjHx8fZuHEjP/vZz7jvvvvIy8tj1apVBAUF0dbWRkNDA56enlKHrNfrOXv2LE1NTXR2dpKYmMjTTz/Nk08+ydq1a6Vwndnvh8xXG7vdLoV/ffLJJ7z//vu89957TE1Ncd999/HII48QHx8vPTcOh4OhoSGOHj1KT08PLS0tnD9/njNnzpCfn09dXR0A/v7+MyIJZL48iKkr9fX1DA4OSpN2dXV1jI6OSpoNer2enp4eqquruXbtGlevXqWoqGjBpbS0VCp9ERgYKOXVyYbqnYHBYKCiooKioiI0Gg1btmwhLS1tTh8wOjpKTU0N7e3tBAYGSkKWn5bJyUmKi4s5efIk4+Pj3H///axatWpe76aI6A2tqqpi0aJFrF69WvLm6nQ6KYowMjJSmrSe7oRwCJFk165do6WlhaVLl5KdnT2vGq7o2KivryciIoKNGzfO8fYqFAr6+vooKytjaGiIuLg4MjIyCAoKwsfHh6mpKaqrq7l69Srt7e0MDw9z8eJF9u/fj06nY8eOHezevfsz1Q8dGhriypUr1NfXExcXJxnts69jYGCAwsJChoaGJCNwupd8OjabjU8++YSysjK6u7spKSnh3LlzfPzxx1y5coXh4WFJ0Xe+8YjNZuPixYucPXuWs2fP8t5773Hy5EmUSiUPPvggDz74IMHBwXPOUaPRUFxcTHl5OUlJSWRkZOBzg1zaO53b8qoVQlHc5cuXs2HDBjw9PSksLOSTTz5hcnJy9uowLfG9pqaGzs5OUlJS2LNnD8nJyVKojuhhWrFihZQTOTExAYCHh4ckSCTmjw4NDUn71+l01NXV0d/fT2hoKKmpqXh6etLb20tRURF6vZ677rqLdevWSQaA0+kkIyODe+65By8vLxobG2lubmZqagqE63Q6nfj4+LB9+3YeeeQRsrOzCQ8PX3D2xGAwUFdXx9WrVzEajWzevJkdO3YQEhIirRMVFSUpyU1NTXHt2jUaGxsxGo3SOg6HA61Wy65du3jiiSdYtmwZkZGR83ZQSqUSV1dXvLy88PDwQKPRoFarcXd3l0J4nU4nNTU1FBcXo9Vq2bp1K9u2bSM8PBylIOITFRXF1772NdauXcvIyAjXrl2jtbUVs9ksHctiseDp6ck999zDww8/TF5e3pxQVQ8PD9asWcPWrVuJi4tDq9USFxfHpk2byMjIwNPTUzrW0qVLcXFxwcfHh9WrV5OdnY1VqLk4NDSEzWZjfHyc8vJyKisrCQ0N5ZFHHiElJQWEdvLy8mLNmjXk5ORIH6XR0VHsdru0jl1Iiv/e977Hjh07SElJwd/ff97OS/T6jI+PY7fbCQgIwNXVVXpmAgIC5i187XQ68fX15a677mLXrl1Srkl8fDzbt29n0aJF2O12Fi9ezD333ENKSgquQm22DRs2kJOTg1KppKmpCYPBAELY4yeffEJjYyOLFy/m/vvvJycnR/I0u7u7s2zZMh5//HFCQ0O5fv06hYWF6HQ6KZwF4VlWKBT09/fzwQcfSAqEW7duRaPREBQUJAkoaLVanE4nGo2G3Nxc1qxZg9FopKSkhOHhYRxCHUvx/XB3d+fb3/429913H1lZWYSEhMxpGxkZhIFBUVER//f//l/+4z/+g6NHj9Lf3092djb33HPPDCOVae9uWloaGzZsICMjg5iYGBwOhxS18txzz/HGG2/Q398/41gyXy6cgnDd0NAQbW1tjI2NoRLykFWCsNbg4KAUWVVTU7PgUl1dTWNjIyMjI9gEoTiZOwu7IKposVhwcXFBO4+uBYIXUTT+7Ha79P36NNiFVKCioiJ6e3tZsmQJ2dnZ3EhBGGG8NDExgc1mk8Zm038zGAyYzWbUgl7J7LGdQogW0Wg0KJVKKV97Pmw2m+RFdHNzm3dsgxBeq1KpsNvtWITcb7VaTWJiIt/85je5//77sVqtvP/++/zTP/0Tv/71r2lsbGT16tXs2LHjU9WPnY444aRSqXB3d1/Q0NUIomdWqxWzIM45fSwzHYVCQUhICHl5eSxfvpy0tDR8fX0lAat/+7d/49e//jWXL1+WxvXTsVgsfPTRR/z+97/nj3/8IydPnsRqtbJ+/Xo2btxIUFDQnHsi4uXlhYuLCxMTE0wJNcG/qszfQrcBCoWCoKAgNmzYQG5uLj09PZw5c4by8nJpUDz9xjkcDkZHR2ltbWVyclLKFenr66O3t1dazGYzXl5ekhDR2NiYJBQTExPD4sWL8fX1lYxKEVHMRq1WSzHjSiHXtLu7G41GQ0BAAGazecbxBgcHsdvtkpeot7dXMhIQ1AcTEhJYunSpFLJxIyYmJmhubmZwcJCQkBByc3OJjo6evRqRkZEsWbKEgIAABgcHaW1tlYxyhM4kNjaW5cuXExERseDLMhun0ykZVNPbX6/XS+G4fn5+ZGZmEhAQMGNbhUJBeHi4dM4DAwN0d3dLnR9CJxIZGUlOTs6C4TMhISEkJyfPSIJXCUrIYu5xZGQkAQEBMz4sXl5ehIaG4u3tjUlQxLUKisdNTU1SXqjT6Zzz3BgMBjQaDQaDge7ubsbGxma0g1arZcWKFURGRt60LZVKJV5eXlJo+ZkzZzh48CA1QiHx+TpOcbJFVOabLkQASNfl5uZGVFTUjLZBMDijo6NxcXFhbGxMavO+vj4aGhqwWq2kpaWRkJAwxyOg1WpJS0sjKysLjeC1Hh8fn3GOSqWSwcFBDh8+zLvvvktgYCDf/e53iY6OZnx8nODgYLy8vNDpdDPadUIQN1OpVAwPD9PX14dVUH52CmrSmZmZpKWlLTjrKSMjolarWb58OT/84Q/5yU9+woMPPkhcXBz5+fk899xzvPvuu4yNjc1YPz4+nueee46XX36Zv/zlL7zzzjucPHmS//zP/2T16tV0d3fz/vvv89FHHy04iJO5/VEIAieJiYmsX7+e+Ph4aTBtsVhQq9Wkpqaybds29uzZc9Nl8+bNkrDK7P5a5s5g+qTpQt+e2WOhT4vT6WRkZIT8/HzOnDmD0+lk+/btJCcnz151Bk7B867X67HZbJIBNv33Wz3/6f8utB5/RXuI4/OioiJJaFJUKE5PTwfg9OnTvP3225IeyKdFPK5CqCyxENPPbaFrENFoNDz00EP87ne/45VXXuG1117jgw8+4ODBgzz99NMEBARw+fJlDh48SEtLizR2EXFxcWHLli0888wz/OAHP2Dv3r34+Phw7Ngx/uVf/oUzZ84wOTk5p70Qwn9VKpU0eTDfOl8VFr6btwFarZbk5GS2bNlCcnIy5eXlnDlzhrGxMbRa7YzQWJvNxpggFS8atT/72c94/PHHpeWJJ57g2Wef5dixY4yOjjI2Nia95AqFAm9vbxYtWkRQUJAUcjw1NYXdbqejo4OGhgYCAgLIyMjA19cXo9HI0NAQOp2O1tZWXn75Zb73ve/xxBNPzDjuv/7rv0pGiF4oFYLwwqjVary9vW95EG4ymRgZGcFqtRIUFDRDEns6orHm7++P1WpFp9NhEsrPOJ1OVCqVpFJ4K8e9GUahpIlCmGCYLowjolAocHFxITo6mqCgICYnJxkZGcFsNksvoaurKwEBAVLI7HxoNBpcZqnPIuxfJahzKoVk9+moBdVejUaD3W7HarXiEMq4iM9DYWEhP/vZz3jsscdmPDc/+tGPOHbsGL29vej1esxms9RpO4QyNGFhYQuq/c3G39+fdevWsXbtWiYnJ/nNb37D008/zb//+79z5coVdDqd5LGdjngNs699+vXO9xFRqVTSdjabDZvNhtPpZGBggImJCXx8fAgPD8d7HqVppVKJj4+PlMsxPDyMQSi9JDI5OUl+fj4HDx6kv7+fuLg4UlJS0Ol0GI1GWltb+R//43/wjW98Y8a78d3vfpeXX36Zrq4uDAbDDE+1+ExERETMyeGQkZkPtVrN0qVLeeqpp/jpT3/Kb3/7W37729+yceNGGhoaeOWVVzh16pQUxSH2Sb6+vvj7+0v/RkZGsmvXLp555hmWLl1Ka2srly9fpqWlZfYhZW5zxAG7zWbD1dWVJUuW8MQTT/Doo4+yfft2tmzZwpYtW9ixYwePPvooTz31FM8888xNl0ceeYTFixej0WikSUuZOwelEEkmegdtNtu83lLx2WKaN/FWcQpibxcvXuT9999nYmKCPXv2sGnTJnymqdUuhPhsz/fsaTQa3IQyhQ4hcmT2ek6h9KDVasXpdOLq6rqgN1OlUkn5uTabbd7xCYJ32C6Uy3MVqk6Mjo5KQqQjIyN873vf409/+hOvvPIKr7zyCs8++yx+fn4cO3aMN998k6qqKmm8equoBBVeh1DqcKF2sVqt2O12aRypWiC/FOH74OnpKX0b/Pz8CAgIICcnR4ryUqlUlJWVUVFRMeec1Wo1GzZs4Lvf/S7/+I//yO9+9zt++ctfkpWVxdWrV3nppZckzZaFcAhOiq8yt7WhqlAo8PHxIS8vjw0bNqBUKrl06ZJUb3V6+J9TmF2amprCZrOhFkIdXF1dcXFxwcXFBY1Gg4dQ22n16tUsWbJEElZA8DolJSWRnJyM1WqlpqaGrq4uhoaGqK6uRqfTkZCQQHp6Ot7e3tiEmpPibJZoPIvHE48pej5XrlxJfHw82lkF4z9N52a32zGZTDiE0N3ZxqCIUqlEI4ToOoWQp9kdi0oIefo8sFgsmM1mlEqlZAzO9/IrBEl3FxcXbNNqkIqInc18huat4pxnRm+hvzuEep1im2oEifjZz42npydJSUmsXbuWnJycGc8N0wa8s428hdBqtWRkZPD000/z/e9/n/T0dFpbW/nzn//Mz3/+cw4fPkxfX9+ce8asGcEb/e1GiG07NTWF1WrFRQhtmu++KYQJADEs3CLUu51+zLGxMfr6+qSZvxpBiVAsteMilCSa/m6Ix4yJiWHNmjWsXLlyhoCYuP/5zklGZiHE99Xb25uAgAByc3P5+te/Tnp6OlVVVeTn59Pb2ztjG8U0Bcfpz3tubi7Z2dmo1Wr6+voYHBycsZ3M7Y84GRwUFERgYCDBwcGSouq3v/1tnn76aZ5++mkpBSYoKAhPT8+bLn5+fgQHB+MrKJb7+vou+D2W+fIhPjdarRaj0cjEtJrq0zGbzVJK2uzw2xvhdDoZGxvj0qVL7N+/n/b2dtauXcv9999PTEzMLY0lxHGuUqmcY5hptVopysokCMyJBrWIQ6gxPD4+DoCnpycuC5TTE8fP4nkbhTro0xH3ZzKZcHV1xUeoAdvc3MxHH33E4OAgO3fuZN++fSxatAh/f3/S09P51re+xb59+/D19aWsrIySkpI5UVs3w8XFBTc3N8lpNT2lbDqio8HDwwOvecrHzGb2t0EcW4sRiaKqcU9Pz5znQ6FQ4OrqKn2PgoODufvuu3nggQeIiYmhubmZgoIC9Hr9jO0QDGqHwyGNQb/K3PxN+C9GrVYTHh7Ohg0byM7Opr6+npMnT9Ld3S09OAgPhDhD4ufnx7p16/jJT37Cr371K375y19Ky69+9Sv+5//8n/z85z/noYcemlECRjQqU1NT8fPzo7GxkcbGRrq7u6mpqcHDw4PFixdLQjIqITdBq9USGxvLvn37+Kd/+qcZx/vlL3/JP//zP/O//tf/4sc//jFr1679q4QRxFk+hUKB0Whc8GW0CfkEFotlhvH4RSEaHnYhr2O6x3E6TqcTg8GAyWTCxcXlhrkEfwvEQalarcbDw4MVK1bw7LPPzrmHv/rVr/jnf/5n/uf//J88+uijkpjSZ0UhFHbOyMjgW9/6Fr/61a/4u7/7OxYvXkxTUxPvvvsuV65cQa/Xf6rOmgUM8tmIv2uFurDiJM98ISZOpxObkMtrF8LYp0czILyny5Yt43vf+x47d+5Ep9Px/vvvU1xcjNVqJSkpif/23/4bv/rVr+a8k2K7igb7F/mcyny1UAgTYwkJCcTFxeEUwt2Hh4dnrzoHhVAXMCAgADc3N6xCDpTMlwsXFxeSkpLYu3cvjzzyCMuWLUOr1Ur3NjAwkMDAQPz8/HATysfdCt7e3qxYsYJHHnmE3bt3f+bcOpnbE41GQ2BgIB4eHowL9eINBsOc76PBYGBsbAyFQoGfn98cR8R8OAVP6vnz53nrrbeoq6sjJyeHffv2sXjxYlxvQZBLIUyOewtlFo1G44zQU09PT0JCQvDy8sJgMKDT6eaEpjocDvR6PVNTU9K7sJCh6urqiq+vL2qhRv3ExMSciXSLxcLw8DDj4+O4u7vj7++PzWajvb2dpqYmXF1dycnJmVF1QKPREBoayooVK0hMTGR8fJyWlpYZ0VW3gvu0EpB6vR6dTjfHMLcL5SsnJyelCabpDq9Pg0ajkbysCoVC8uLeCIXgoRW/RyaTic7OTsbHx+dsOzk5iUXQbPk0/dKdyG1/5eJgYfHixWzevJnAwECKi4spLi7G4XBID5hKyFEMCgrCw8MDV1dXIiMjycrKIicnR1qys7PJzs4mMzOT6OjoGaJFCoUCLy8vUlNTJRXbqqoqSVI7PDycJUuW4C0kuLsKYapubm44BNGdpKQksrOz5xxzyZIlpKSkECSUiZnN7M5vIdzc3AgMDMTV1ZXBwUF6e3vnTeIeHx+no6OD0dFR3N3dCQkJwd3dffZqnxtubm74+fmhEnINBwYG5oQzOJ1OjEYjbW1tDAwMSDPSn7Wj+DwQB7K+vr5ohBCu6Ojoee+heB9jY2NnPDefFYWQMxUeHs7KlSt55JFH+Na3vsWiRYuk4tdjY2O3/Gx8GkRjNiQkBB8fH3Q6nfS8zP442O12RkdHqa+vx2g0EhYWhuesYuXe3t5kZWVx77338rWvfY2cnBwGBwdpb2+XvO3R0dFkZmbO27ZZWVkkJibOG3osI/PXohTSAcTn/lbfKZOQy26xWNBqtbcc2i9z+6BSqfD39yczM5OVK1cSFRX1ufQxGo2GmJgYVq5cKaUDfR77lbk9cHFxITQ0lODgYKampmhra2N0dHSGQTE5OUlvby9DQ0NotVoiIyPx8vIC4RvrEMI2p/c3TqeT0dFR8vPz2b9/Pw0NDWRnZ/Poo4+Sl5eHp1Dn9FYQx6AugujOdMeFRqMhODiYgIAARoTa9LPHimahdJNerycuLo7IyEjJSJ59/u7u7kRERBAQEMDk5KSkBzOdyclJSahSHI8rFAomJycxmUxoBK/sbOeEUqnE19cXLy8vHEKUm5ie5BQmys1m85xIrul4eXkRFRVFcHAwBoOB1tbWOddrMBhoaWlBp9MRHBxMcHCwNB6ffr23gsPhwGAwoNfrJfvj0zgvxPHjfNdjmSaS5ePj85VPffpS9KoqlYqAgABWrVrFmjVrGB0d5fr164yOjuKcljzt7+8vhdbW1dVRVVXF5OSk5DETvaCqG+QxagUF2dTUVBwOB4WFhXz88ccYjUapOLA4Y+bu7k5UVBSRkZEYDAbKyspob2+Xznn2McXj/jV4eXmxaNEiQkNDGRkZoaioiNbWVuxC/oFTCPMV66gaDAaio6NJSEiQOtAvAnGWKCoqipGREan8jeihE89LrKM6PDxMVFTUjJqc/xUohPDyRYsW4e7uTl1dHRUVFVLnI95D8T4u9Nx8WsROUbxvroI67+LFi4mIiMAilEuYz8P5eRIaGkpKSgru7u7U1tZKtQbFj5PD4WBiYoJr165RV1eHp6enNCib3gZieIufnx9ZWVns3r2bRYsW4RDyd1pbW7l06RKjo6MoBKXB2e/H59GuMl9NHELImRguJfY5DiFfqaWlhba2NlQqFYGBgVIJB7Ffsgn5Z9O3MxqNVFZWUl1djVKpJC4ujvDw8NmHlrnNEfsbd3d3KbTx80AheLS8vLy+8h6POxGxr0hPT8fHx4fq6mqam5ulb7LD4aC7u1uaUI6IiJAmW202G8PDw1RWVlJTUyOFsToFI/XChQscOnSIjo4O8vLyePTRR1mxYgWeQsUIu6AefLNvv1arlbygw8PDM7ycCoWC2NhY4uPjmZqaora2lvb2dilk12Kx0NPTI4XZZmRkEB0djUbQ8Ojp6aGiooLm5mYmJydxc3MjNjaWxMREnE4n165do7e3d8ZYoaWlhbq6OhRCNQKxgoWY7qXX6+nq6pohICRuOzAwwMjIiHRNHh4e0nl8/PHHHDp0iLq6ugWjCN3c3IiJiSEhIQGDwUBxcTF9fX2SwetwOGhubqa8vBy73U5CQoIUHWk2m+nq6qKiooLW1lZMgtikXchNnn4/xL93dXVRUlJCZ2cnvr6+xMbG4ioIq1mt1gW/R3q9ntbWVtrb21Gr1YSEhOA5S6NmdHSU/v5+tFqt5Az7Ko+Nbque9UYvpUajIT4+ni1btrBo0SKGhoYk5VWEl9LPz4/FixeTlJREf38/R44c4YMPPqC6upru7m76+vpobW2loqJCKk0jbi8iGsWLFy8mJCSEkpISLl26hJeXF9nZ2QQEBEgfJI1GQ3R0NMuXL8fPz4/Lly9z4MABLl68SGtrK319fXR1dUnGT1dX1wwv442udyHc3d1JTEyUasJeuHCB999/n/LycoaHhxkcHOTatWscPnyYa9eu4e/vL+XGTv9Af5Zj3witoAybm5uLUsglPn78OBUVFQwODtLX18f169d55513uHLlChEREaxcuVLqGEVu5bxuZZ1Pg6+vLzk5OWRlZaHT6Xjvvfc4duwYlZWVdHZ20tvbS2trK+Xl5dTV1S0odHSrOBwOxsfHqayslCYaRkdH6e3tpaamhv7+fimfYbrnVuzsPk+8vb1Zv3496enptLe38+GHH5Kfn09bWxvDw8O0trZy5swZDhw4wPDwsFSnd76aXmIH7ufnx9q1a2eUTRoaGmL//v0cPHiQ69ev097eTm9vL+3t7VRWVlJZWcnw8PBf1a4yX00cgqLkiRMnOHbsGBUVFXR0dNDb20tzczP5+fm89957VFdXExUVxfLlywkJCcHpdKLX67ly5QonT56kurqarq4uenp6qK+v5/Tp07z11ltUV1eTnJzMunXrpOdZRkbmzkb08uXl5ZGcnExDQwPHjx+ntLSUvr4+WlpayM/P58qVK7i4uLB06VJJBVqv13Pu3Dl++9vf8rvf/Y6ioiIMBgMjIyOcP3+eAwcOcP36dVxdXYmLi0OlUtHY2Mi1a9coKiri6tWrlJaWMjQ0NGeMOh1xgtvPz0+qojDdkBP7u/DwcOrq6jhz5gzV1dUMDAxIfVxpaSlBQUGsWLFC0ojo6+vj6NGj/PrXv+Yvf/kLlZWVWK1WIiIiyMvLw9/fn+vXr3PixAnq6+sZGRmhtraWEydOUFVVRVRUFMuWLSMsLAwvLy9iY2NJTk7GbDZz5swZLl68KFVT0Ol0lJWVcfr0aZqamggPDyc9PR1/f39MJhMlJSW8/PLLvPnmm3R1dS3YHkqlkujoaJYuXYq3tzelpaWcOnVKKiNVV1fH4cOHqa2tJSEhgZycHEJCQlAK1TsOHTrEb37zG1555RWam5sxGo00NTXx0UcfcfXqVZqbm+np6aG9vZ1r165x4MABTp8+jVKpZPny5WRkZKDVaiUj9ujRo5w9e5aqqirpu9LY2Mjp06f58MMP6ezsJCIigmXLlklRmiJdXV10dnYSHh5OeHj4nFSrrxqqX/ziF7+Y/ce/NQ6Hg7a2Ni5duoTFYiE7O1sqRyEizl56e3tjMBhoaGjAYDBIBk9MTIw0c6MSwk9FD1FzczN1dXWUlZVx4cIF8vPzGRoaIjQ0FD8/vzlhCAqFQpp9KSsrw2KxkJeXx+7du4mIiJDWVwjhvx4eHlgsFtra2qitraWhoYHGxkZqamooKioiPz+fiooKVCqVpGA6MjJCcXExLS0thIaGkpeXR1RU1IzzmA+lkG/q7u7O5OSklEcrPthiwWix89yyZQv33HOPVOh5fHyc4uJiamtrCQoKYvXq1fOWt5kPg1AAu6ysDK1Wy9q1a0lMTJQ8Ye7u7ri4uDA+Pk5bWxtNTU20t7fT3t5OcXExp06d4vz587i7u7N37162b99OZGQkGo2GkZERKioqaGxsJDAwkBUrVhAREYFqWiiFmHhuMplmPCPiCzw8PCwZfmFhYaxZs2ZG4W2TyUR5eTnl5eX4+PiQm5tLXFwcHh4eUrj4yMgIVVVVNDQ00NTURH19PeXl5Vy8eJFz584xODgoqRrb7XZaWlooLCxEr9ezYcMG0tPTpdCZhRBzNg4fPszJkyepr6+npaWFgoICTp06RWdnJ9lC3cekpCQAGhoauHbtGk6nkxUrVpCSkiJ59hEMwfz8fDo6OsjKymLZsmX4+/tLxuTExARlZWVUVlbi5+fHli1bCA4ORq1W4+vrK81civesq6uLhoYGLly4wMmTJ2loaCAzM5Mnn3ySZcuWSQZ0V1cXV69eZWhoiLS0NLKzs/H19ZXEAwYGBujo6MBisUjhR01NTTQ0NFBRUUFhYSHnzp2jtbUVPz8/wsLCUKvV6PV6Tp48SVtbG1lZWaxatUoOrZOZF/F9evHFF6WBgfh8nT9/ntOnT1NcXIynpye7d+9m165dRERE4HA46O3t5c033+TIkSPU1tZSX19PWVkZn3zyCR999BG1tbVERETw4IMPsnnzZskTKyPzReEUhCGHhoYwGAyEhYX9VboWMp8dpVKJh4cHNpuN5uZmGhoa6Ovro6Ojg0uXLnH27FlGR0dZsWIFu3btIjExURrPvP/++xw+fJi2tjbi4+NJSUmhrq6O/fv3c+nSJUZGRgDQ6XRUVVVx5coVCgsLKSws5MqVK1RWVkrCX7PHqCIKITeyvb2dhoYGwsPDZ4ydXQSBITEUVjS2mpqauHjxIufPn8disbB9+3Z27txJaGgoKpWK5uZmqSTXxMQEcXFxJCQkSOJMer2e+vp6mpqaGBgYoLm5mTNnznDu3Dk0Gg333HMPd999N6GhobgK4pQKhYK+vj7q6upoa2tjaGhIMvqOHz/OlStX8Pb2ZseOHWzYsIGgoCB0Oh35+fl89NFHeHp6sm3bNqKjo2eMC6fjIgg0TkxM0NTURGNjI/39/bS0tHDq1Ck++ugj3N3due+++7jrrrsIDg7G6XRSXV3N4cOHOXv2LOPj4+QI5REvX77Mm2++SWFhoRSlWVhYyJkzZzh//jxTU1Ns2LCB+++/n9TUVFxcXLBYLFRWVvLCCy9QUFBATU0NdXV1lJaW8sknn3D69Gnq6uoICwtj165dbNmyZYYDzOFwcOHCBc6cOcOSJUvYuHGjdF++qtwWhqpTCIfo7u7G39+fpUuXsmjRItzc3GaspxAEaDw9PTGbzbi4uJCSkiLNGIkvpWhIqFQqKfeuubmZ1tZW+vv7sdvtREVFkZKSQkBAwJxOQCmoeplMJiYnJ4mLi2PLli1S/sD0mQ21Wo2Pjw+hoaH4+vpisVjo6+ujubmZtrY2Ojs7GRsbw8PDg6SkJBISEnB3d8dgMNDb24vVaiUxMVGa3bkVXATBqJCQEOmlFI3k+vp6xsfHiYuLY8eOHezYsYOUlBSpLU2COpnBYGDRokUsX76c0Fuo34qgQtbf349OpyMiIoJVq1bNyPfRaDT4+/sTFBSEq6urlBRfV1dHU1MTY2NjxMXFsXfvXnbv3k1CQgIuQuK+wWCgv78fk8lEfHw8S5culWa7REZGRujt7cXb21t6RqZ7HMV8EZvNRlJSErm5uQRMq+VqtVrp7e1lfHycmJgYcnJyiIyMxEUQggoODiYkJAS1Wi3l+IrPjahoGxkZSWpqKkFBQTAtRMPb25u1a9dK13QjHA4HOp2OxsZGWlpaaG1tpbGxkdbWVgBycnLYu3cvy5cvx8fHB7tQDHx4eJigoCBJaW76cSYnJ6Ww82XLlpGZmTnD62kymejv72d8fJz4+HjWrFmDv7+/9E6FhIRIBmtvby8NDQ3U1dXR3t6ORqORcmjXrVsnKfkhqP12d3fj4uLCkiVLSE9Px9PTE41Gg4+PDz4+PlL5m4iICMTc6tbWVlpbW+np6cFoNBIcHExqaqo0EWQymWhoaMDpdErKq7NnHWVkEHKo9Xq9lBvV0tJCc3Mz9fX1tLa2YrPZSElJYffu3ezevZukpCTUQhmDyclJGhoa6OzspKmpiaamJurq6ujo6ECj0ZCdnc0DDzzA1q1biYiIkJ8/mS8c2VC9fRAdAyEhIXh4eKATShGKxparqytr167l3nvvJScnRzIQTSYTzc3NdHd3ExAQwOrVq0lNTaW9vV0KjRXDW61WKwaDgcnJSQwGg7Q4HA6ysrJISEiYM0YVUQiCouPj41RXV2O1Wlm8eDHBwcFSX+Xt7Y2/UMZwaGiIxsZG6uvr6enpwc/Pj7vvvpv777+fxMREaUwhjt10Oh3R0dHk5uaSkJCAh6CUGxwcjFKpZGBggMbGRmpra+nu7iYkJISdO3eyfft2qSa7QtDiCAwMxMfHB4fDIRnL1dXV1NTUMDY2RkJCAnv27GHLli3ExsaiVqvp7u7m3LlztLe3s379ejZv3iyJF82HSqXC29ubwMBAnE4nQ0ND1NfXU1dXJ3koRSeJ6LxBGFu2tLQwPj5ObGwsGzZsIDQ0lP7+fmms0tzcLDmGxsfHCQ8PZ8uWLezdu5esrCwpj1Qc33V2djI0NERbW5t0Dh0dHahUKjIzM9mzZ490HuL9dQqKym+//TbNzc3s2LGD5cuXf+XHPgrn5x1L+BlwOp0MDg5SX1+PzWaTcoG0Wi1OIQd1OpOTkzQ3N9PV1YWvry+JiYkEBgZKN9sh5BdNNxiHhoZQKpUEBwcTGxtLXFwcYWFhuLu7z+ulsVqt9PT00NDQAEBycvINZ7bsdrtkFDc1NdHZ2YnRaMTT05Pw8HDi4uKIjY0lICAAjUYjxan39fXh5+dHYmLip56tFw1Hcaanv78ftVpNTEwMGRkZJCYmzjHEp6amaG1tpaurC29vb8lYvxUsFgsdHR20tLTg4uJCWloaISEhc+6PaBTV1dVRV1fHwMCAFCadkZFBSkrKHO/Y5OQkbW1t9PX14e3tLbXH9H2L4SoWi4X4+HjJ8BHX0ev1tLS00N/fj5+fHykpKfhMq0Umnn97eztarZaEhIQZ4lZOIW9DDOtpampieHhY+qhERkZKxxVzSQYHB2lqasJgMJCWlnbDZ0TE6XQyNTUlhaK3trYyPDyMu7s7sbGxpKSkEBUVhYeHB0qlUjKwW1pacDgcJCYmEh4ePiNkemJigpqaGoaHh4mOjiY+Pn7GpIrRaKSjo4PW1la8vb1ZvHjxnM5vYmKC1tZWqquraWlpwWAw4OvrS0pKCunp6cTFxc0xwkdGRqivr0ev1xMVFUVcXJyUT+EQxAbE8G+xXQYHBxkeHsZqteLr6yu1a3R0tGRcG41GysvL6evrIy4ujsTExK+8oIDM/DidTkwmE319fdKgoK+vD5PJhKenJzExMaSmpkrlEMR+RzQIent7peiJwcFBrFarlLeelpZGbGzsF5rfLyMzHYeQGlJTU8Pg4CA5OTnExsbOXk3mb4jT6WRkZITKykoqKiro7+/Hy8uL5ORkSZhzumPFZDJRW1vL1atXcXFxYe3atcTHx0vpCPOlnU3HKYgXZWRkzIksm43ZbKa6uprf//731NXV8cwzz7Bnzx68vLyk76XVaqVPEAetq6tjdHQUX19f0tPTyczMJDQ0dMZ4Qq/XU1JSQk1NDcHBweTm5hIRESGtY7Va6e7upry8nOrqaiYmJggODiYzM5OMjIwZIkUi4sRge3s71dXVNDU1MTExgZugyp6enk5CQgK+vr6oVCosFgsFBQU8//zzDAwM8MMf/pA9e/bMGNMthNlspru7m4qKCmpqaqTzW7JkCZmZmfj7+884v9HRUUpLS6mrqyMiIkKayB8fH6e9vZ3a2lo6OjrQ6/WohUokqampJCUlERISMmNfDkEvoaenh7a2NhoaGhgYGMBqteLt7U18fDypqanExsbOGQfbbDauXLnCT3/6UwICAvi7v/s78vLy5nXafZW4LQxVEec0RUa7UITYLhQO1gg1QRXTStKIp36jm+YQxFysgiy3i4uLtJ9bQTyf+YzZhbBarQwPD9Pf349GoyE8PBwfH595O5tbuYab4RBU0iwWCwohHFn0VM7H9Fu+0DoLIbYHwmzjjbDb7ZJS262el1OYmJhvnZv9zi2sc7Pfp2MR6oUieIvVQn3X2fw199A5TcxF9OTf6DkRmX2sW7mnt3rtVqsVs9mM3W5HrVaj1WrnPSc+xfPgcDik361WK1ZBvU89TVBpNrd6vjIyIk7B+DSbzTiFfls7qzTXfM+SuJ1FKDGgUqlwc3O76aSTjMznjWyo/tez0Pd2+lhLpVLh6uq64HjS4XBgMplQzKqxfrNv9a1+98TfnEKpmyNHjvDiiy+SkZHBM888Q0ZGxoyJZYvFgtFonHHus7/t089NHDcrlcoZ5z99Xbvdjslkwm63oxFq0Iv7m92GCOc8fTubzYZKpUIrlMkTf0fw6n744Yf8+c9/JjY2lp/85CdkZmbOMYBvhN1ux2g0YrPZcBFquS801hCvV61Wo5lVW9UmlHu02+0ohLGsRqOZ0Sazr1e8lunfFbVQ93b6MyNu5xC0Fv7t3/6NEydO8M1vfpOHHnqI8PBwFAqFVJ9WI9QJn30/7mRuK0PVbrdjEBLOxVBHk1A4OCAggGBBanu2J+h2w2w2U1xczIkTJ9BqtWzbto3MzMwZOYUyMjIyMp8v4mz2Qt4KhVBve3okxmzEwag4uLnR5JqMzOeNbKj+1+FwOLBarVI5FQQ1WTGd5Vb7AdEYEyd8Z+MUJtFcXFwkg8chKJRbbqFWs9iPiQak1WqlpaWFP/3pT1RUVPDNb36TXbt24Suo89tsNjo6OqitrUWj0ZCRkSEJJyGcj9VqRa/XYzQaQRDu9PDw+NT9n1OITBMNK3HC283NDQ8PD1Qq1bz7s9vtWCwWbIJKb09PD0ePHuXixYts3ryZvXv3Sjmvn4eR5hRUeM1mMw6HQ2rP+c5tIcR9mEwmjEYjJkEtWKPR3FQNXGxzg8GA0WjEaDRSV1fHL3/5S1JSUvjRj34kCTRZhYoZ1dXV+Pr6ztEgudO5bQxVu5CHV1payqVLl6iqqqKvrw+j0YirqyuhoaEsXryYHTt2sHLlyk/VafwtcQpKku+++y7PP/88Pj4+PPvss+zYsQNvb+/Zq8vIyMjIfA44HA7Gxsa4du0aBoMB5zxpI1qtlpiYGBITE3GdJXrmEFJGRJEPvV5PfHw88fHxc0KvZGS+KGRD9b8Gq9XK2NgYra2tVFVV0d3djVKpJDY2lszMTClH81aMA5vNxuDgoKQ4OxunENobExMjCYFOCrVJOzs7pei4hXB1dSUiIoK4uDhJM8JisVBVVUVxcTGLFi0iJydHSqUZHBzkvffe4+TJkyQlJfHEE0+QkZGBRqgdL6b9lJWV0dnZCUBsbCyLFy8mPj5+wYjA2ZjN5hkpcF1C7VYvLy/i4+NJT08nKipq3pS70dFRmpqa6O/vxyaU9xHDdjMyMqS2Sk1N/atTMRxCGPLAwACdnZ1YrVZiYmIk1eZbYfo+2traaG5uZmBgAJvNhp+fHxkZGVJ63GwD2Gw2S/oe9fX1dAg17JubmxkfH+fJJ59k69atBAYGolKpsFqtfPLJJ7z44ouYzWaeeuopNm3ahLu7+4xzulO5LQxVp9PJ8PAwp06dksoBuLq6SuU5DAYD4+PjhIWF8eSTT7Jv3745N/52wel0Mjk5ycGDB3n++efx9vbm2WefZfv27X/1yyUjIyMjMz8Wi4WSkhL+7u/+jsHBwdk/o1AoCA4O5t577+XJJ58kMDBQ+s0qpGuUlZXx4YcfUlJSgslk4rHHHuORRx6R66fK/M2QDdW/PXa7ne7ubj7++GOOHTtGVVWVVG/U09OT3NxcHnvsMdauXTsj93MhJicnOX/+PC+//DLV1dUwLRQUYZwYGRnJvffey3333Ud4eDgdHR3s37+f48ePMzo6OseQE7Hb7QQEBLB161YefvhhkpKSbmhE2mw2zp07xyuvvILNZuPRRx/l7rvvloSNRkdH+fjjj9m/f79U5cJms+Hh4cHy5ct54IEHJBXehc4J4bmtqanhgw8+4MKFC7S2tqLX66X0qaCgIFauXMm+fftYtWrVnHYsKiritddeo7CwEIPBgHJaKpTVakWj0bBp0yZ+8IMfEBcXd9N7sBAmk4mRkRGKioqk8jweHh48+OCDPPzww7es2WIymSgoKJBK7g0MDGCxWLALtVejoqLYvXs3X//611m0aJEUxWO322kQSh19/PHHtLa2SvVvxe3y8vLYt28fubm5eHt7o1QqGR0d5e2332b//v1kZmby3//7fycmJuaG9+RO4bZQ/bXZbBQXF/Pyyy9TX1/PypUrefbZZ/n+97/PAw88wO7du1m/fj3Lly8nOzt7hqLZ7YjFYpES6V1dXVmxYsW8M/gyMjIyMp8PRqORgoICXn31VUlJWiw7pdVqcXV1xdfXl7S0NDIzM6XZaJvNRldXF//xH/8h1Tzs7u7GYDCQnp5OTk6OrLoq8zfDKav+/s0ZGhriww8/5NVXX6WtrY3c3FweeOABlixZwuDgIAUFBXR3dxMdHX1LgomTk5NSubnh4WF8hZJtYl/k4uKCv78/aWlppKSk4OXlhcFgkJTLXV1d8fHxwdvbW1q8vLwwm80MDAxgt9tJSUkhJyeHgICAG46He3p6OHz4MJWVleTl5bF9+3ZJBHNsbIyPPvqI559/npKSElasWMFjjz1GTk6OFJ3S09NDUFAQkZGRN0xfm5qa4uDBgxw4cICRkREyMjLYvHmzVM6uvb1dipRMTk6eUXLF4XBQXFzM6dOnJbFLLy8vKSxarVbj7u5OUlISy5Ytm1F54NPgdDopKyvjD3/4Ay+99BJFRUX09PRgt9tJSkpi6dKlknLzzTCbzVy+fJkTJ04AsH79eu655x4yMjKwWCw0NTVx5coVvLy8pNI+SqWSiYkJTpw4weuvv05/fz/p6els375dMt4bGhooLCxkaGiIhIQEqRKF6IVuFspthoaGsmjRohl5yHcqt4VHtb+/nzfffJOXX36ZkJAQfvjDH7J58+YZuajiaSpukmCOsO6N1r/Z7wsxfTsW2Ha6R/Xf//3f8fLyuqFH1TlPeNp0Zh/z08yeiNvOd54yMjIydwpOp5Px8XH++Mc/8vzzz/PQQw/xve99TypTIK6jUqmkEmfiIMloNHLhwgV++tOfotVqyc3Npa6ujsbGRh5//HG+973v3XKtaZkvJ04h18wp5A5+mu/s581f61EVv/sOQcDuv/JavgzYbDby8/P5wx/+QHNzM3fffTff+MY3SEtLw2w2U1hYyPPPP8+VK1d44okn+NGPfkR8fPwNjdWhoSFefPFF3nnnHdatW8cTTzwxo7zV9L5IzNsUhX9MJhMOh2PGmE2hUKDX6zl8+DBvvfUWvr6+PPXUU9xzzz34+flNO/JMnE4nZ8+e5fe//z0Oh4MnnniCzZs34+vri9lspqysjH/913/l0qVLPPDAA3z/+98nOTkZgAsXLvDCCy9QVlbGpk2beOaZZ0hPT19QzMhisZCfn097ezuJiYmkpaVJEyy9vb188MEHvPDCCwwPD/ODH/yAp556Sqpzb7FYePPNN3n11VeJiIjg4YcfJisrCxcXlxnjWHd3d7y9vW/Y9jfCYrHw6quv8sYbb0gVORoaGhgfH2ffvn1897vfJTg4ePZm82K1Wmlvb2dwcFAqbSjmk7a0tPD888/z4YcfkpqaynPPPceaNWtwd3fHarVKdXKTkpLIysqSconHx8c5evQov/71r+nu7uZnP/sZTzzxBFFRUaiEcptvv/02L7/8Mnl5eTz33HOEhYXd8eP726IHm5qaYnBwELvdLpUBEWcfRCNL7HCn3xAxp0hMfLfZbFLZj4aGBpqbmxkdHZWSs51C8rIYC9/Y2MjAwABGoxHHAuIbTFNvGxoaoqGhgaqqKtra2tDpdJKa163iFJLsjUYjExMT6PV6LBaLNJgScQhJ3sPDwzQ2NlJTU0NnZycTExPS9UzHYrEwOTmJ0WiUktLFXKvBwUEst5CgLyMjI/NlxWaz0dvbi0ajkUo4hYWFER4eTnh4OBEREYSGhuLt7T0jVE6j0ZCcnMyPf/xjXnrpJb7zne8QGRl5w3A6mTsHpzC5XFtbS1FREV1dXZjN5tmrfSlwCqWaWlpaKCwspKmpad7xhcz/o6+vj2vXrtHS0kJkZCR33323FKrp6elJTk4O27ZtIywsjOrqahoaGjALquILIY4zHQ4H8fHxJCQkSP3Q7L5IVIBVq9V4enoSGBhIUFAQgYGB0hIQEIDBYKCtrQ2FQkFWVpZUs/xGGAwGGhsbGRoaIioqiuTkZGmbiYkJSktLaW1tJTExkV27dpGUlISrqyuurq7k5uayYcMGvL29pXGvXq+ffQgJjUbDhg0beOyxx1izZg3BwcFSJEt0dDSbN29m1apVuLi4UFlZycjIiNSGNpsNnU6H3W4nLCxMKlEp9t8RERGEh4fj5+f3mY1UhHPMycnhH/7hH/j1r3/Nww8/TFRU1Gfap1qtJj4+Xqpr7+XlhYuLC+7u7iQmJrJx40YCAgLo7e2dYYeo1WpWrFjBN7/5TdavX09QUBCuQkWMgIAAybvq7u5OU1MTQ0NDkiCXj48PKSkpBAcH09LSIpVrvNO5LQxVMRZdnEkcGhqS8gNuxMjICB999BEvvfQSZ8+epbS0lPfee49f/OIX/PjHP+Yf/uEfeP7557lw4QJ6vZ7BwUFOnDjBL3/5S37yk5/w4x//mP/9v/83J06coK+vb47B6RTUy+rr63nttdf4+c9/zo9//GN+9KMf8fd///f867/+K8ePH6e3t1d6kG6G0WikoqKCl19+md/85jd8+OGH9Pf3z1jHbrfT3t7OgQMHeO655/jJT37Cj370I37605/y+9//nqKiIiYmJma85KWlpfznf/4nBw4coLKyklOnTvG///f/5n/9r//F6dOn503ol5GRkblTsNlsdHd3o1arCQsLw1VQh5y9zJ59VqvVREZGcv/995OcnIy7uzuKaflkMnc2drudjo4O3n//fV5//XUKCwsZHx+fvdq8iGOEqakpJicnMRgMkoroX4M4QT/7Wb0Zdrudvr4+Tp06xR//+EdOnjzJ8PCw/CzfgL6+PhobG3E4HCQkJBAXF4eHhwcIY1MvLy/S09MJCwujra1Nqpu+UJuKjg3xGQoKCsLLywuVSnXTvmi2Y0ZcRO9nRUUFfn5+ZGdnEx4eflMDq7e3l8bGRpRKJTExMfj7+6NWq3EIuamVlZWMjY2RmppKfHw8Wq1WOgdfX18WLVpEREQEY2NjtLS0MDk5OfsQEgqhbIu7u/uMcjaiEe7t7U1YWBguLi6Mjo7OmAyy2+2MjY1hE4SIfHx8pLDfG7XXp0WhULB48WI2b95MWlraX1WbXaFQoBJKZ05XMhb/Lp6vl5cXWq12RnuIBq34jRJRKpUEBQVJz+D4+PgMFXulUklYWBgJCQnodDrq6upkQ/VvhVhc3dfXl7a2Nk6dOsX169cZHx/Hbrcv2CGIRYmPHTvG/v37+dOf/sRrr73G1atX6erqoqysjHfeeYeXXnqJEydOcOjQIX7/+9+Tn59PZ2cndXV1HDlyhD//+c+cOHFihsEozrJevHiR3/zmN/zHf/wHFy5cYGJiAoD29nYOHz7Mb3/7W9544w0aGxtvaqxaLBbq6up49913efvttykrK8PhcEgDI4QXtqamhhdeeEEySlUqFZ6ennR0dPDee+/xwgsvUFBQIHUadrudlpYWPvjgAw4dOsSbb77JCy+8wAcffEBlZaXsUZWRkbnjsQpF7ZVKJZ6enphMJgwGgxRts9B3BGGm3dvbe8GwNpk7F7vdzvj4OP39/QwPDzM8PIxer8dkMt106e3t5cyZM7z++uu88sorvPrqq3zwwQc0NzfPWfdWF7NQd9Eq1JG3Wq1z1lloMRqN6HQ6+vr6pOsxGAx/teF8p2IT1GUHBwdxc3MjOjpaUsoVUalUkodzdHSUnp4epqamFuxPbDYbY2NjTExMoBFKYZnN5hmRf5/mfjidTlpaWrh69SpjY2OkpKSQmZl5S3mag4OD9Pb2SmGuonq5zWZjZGSE9vZ27HY7MTExM1LtmGY0hYSEYLVaGRwcvOF13wynEI6OUPJnupE9NTXFxMSEZOw6HA6pbIvVav1U7XUztFotHh4eUl//Wa9nOuK12YX6sJ2dnVy+fJmJiQmys7OJjo6+ZQFYcV9OpxM3NzfJYBfx9/cnNjYWk8lER0fHV2Jsf1uIKWk0GjQaDTqdjpaWFpqammhvb2d8fByVUHhdvFnTb7ROp+PatWtcuXKFjo4OnE4ny5YtY+/evaxfv56QkBC6u7upqamhvr5eCu24//772bZtGwkJCZIcucViITY2loiICFQqFWazmcrKSl599VXOnTtHTEwMX/va17jvvvu4++67ycjIQKFQ0NDQQEtLCy4uLkRFReHj44NFEFO6cuWKJKaUkJAg1YX6+OOPcXd3Z/v27WzcuJGQkBBUKhUOh4Ouri7efvttjh07RlhYGA899BD33Xcf69evJy4ujomJCRoaGpiamiImJoaQkBAcgtraxYsX6ejooLe3F7VazYYNG9i5cycrVqwgIiJCFnOSkZG5IxE9Sa+//jojIyMMDw9TUFDApUuXaGpqwmQy4eHhMWNmez6cTic6nY6LFy/S3t5OZmamJN4hc2dis9no6emhsrISnU7H1NQUPT09VFdXU1pauuBSUlJCUVERhYWFVFZW0tzcTEtLC+3t7XR1ddHQ0DBnm1tZSkpKKC0tpbq6mtbWVtrb2296LtOXiooKWlpamJqaIioqiszMTPz8/ORQ9nkwGo2Ul5dz6dIl1Go1K1euJCMjQ/KoMs1pUVpaSl1dHYmJiVIdy/na1GQy0dzczLlz52hoaKC/v5+ioiIuXLhAY2MjRqNRComd7olbCJPJxLlz5zh+/DgeHh5s27aN3NzcOaq581FRUcGFCxfw9vZmzZo1JCQk4OLigtFopLa2lo8//hiz2cymTZvIzs6eU4ZrYmKCqqoqmpqaCAoKYunSpQQHB9+wD50PmyBYd/bsWVpaWlixYgV33XWXlF/b3d1Nfn4+VVVV9PT0UFFRwaVLlySPr0ajwd3dXQqT/rzo6uqiqKiI4eFh0tLSWLZs2Yx7fytYrVZGRkbo6Oigo6ODoqIi9u/fz+XLl0lKSuLRRx8lKyvrlry3DoeDwcFBDh48SH19PWvWrGH16tUEBgbOaPOOjg4uX76Mn58fa9eunTPJcKdxWxiqSiG8wt/fH6fTSX9/P01NTdTU1FBbW0tfXx8qlUpyoYs3ZGxsTOqcVSoVGzdu5MEHH2TNmjUkJSURFhbG+Pg41dXV9PX1kZiYyDe+8Q3uvvtu0tLSiIyMxCKoc42PjxMdHS3lJgwNDUkeyoCAAL7xjW+wZ88eMjIyiIuLIz4+nqCgIKn2kcFgICYmhqioKBwOh2SoarVaVqxYgZubG2fOnOHEiROo1Wp27drFzp07iY2NlWZ2zGYzFy5c4K233kKlUvHwww+zc+dOUlJSiIyMlIzo5uZmurq6iIyMZNGiRahUKhoaGrhy5Qrd3d2Ehoayd+9eHnjgAZYvX05ERARubm539IMsIyPz1cVqtdLb20tBQQFqtRq9Xk93dze1tbVUVlZSVVXF4OAgnp6eBAUFzTvARDZUv5KIuc1VVVUMDw+j0+no7OyksbGRpqamBZfGxkap/qHJZMJisUhaEb29vXPWv9WlsbGR1tZWent7JZ0J8e+z151v6erqYnJyEqVSSVRUFEuWLMHf3/9TGxdfBQwGA6WlpVy9ehU3NzdWrVpFcnLyDIPN6XRiMBgoKSmhpqaGmJgYcnNzCQoKmjf01mKx0NnZSX19PQaDgampKbq6uqirq5P6opGREdzd3fH19b2pp625uZlDhw5RW1tLbm4u27dvJyYmZt5jT8dms1FWVkZBQQHBwcGsXr1aUiw2GAzU1NRw+fJlADZt2kRaWtocZ4Zer6eyspL6+nr8/PzIyckhLCzspseejU6no7CwkBMnTmCz2XjwwQfJycmRVIR7e3uprq5mZGQEo9FIf38/jY2NVFVVUVlZSUdHB1qtVsrnvFF7fRo+D0N1dHSUTz75hJdffpnjx49z7tw5iouLiYmJ4cknn2TdunULTmrMxmq1cvHiRQ4ePIhSqWTv3r3k5OTMMXI7OjooLCzE3d2dNWvWEBAQcEe/37fNlbm7u5OdnS2pLIrFbEtKSnjjjTf44x//yIkTJxgYGJjjqlepVERERLBq1SrS09Px9fXFx8dHKtQsJq1nZ2dLct4eHh5ER0eTlZVFaGgoBoOB3t5eJiYmsFqtdHZ2UlFRgdFoZMWKFWzYsIGIiAgp/t7X15fFixezbt06AgMDaWlpoaamhrGxsRnnphAkwC9cuMDp06cB2Lp1K9u2bSMmJkYyUh0OBzqdjtLSUjo7O0lPT5dm7ZyCAJOXlxeLFi0iPDwcvV4viUVNx8XFhSVLlrBp0yaSk5Px9/e/qRdBRkZG5suMSqUiODiYp59+mueee45//Md/5Nlnn+WBBx4gJiaGxsZG3n77bd59910pH01GZjZKpRJ3d3cCAwMJDQ0lJCRkwSU0NBR/f/85udDi+OBm2y+0hIaGEhwcjJ+fH15eXtK53Mr+wsLCCAgIwNXVdc44SWYuNpsNs9mMzWZDKZRBmW+spBJyEZVKJXah3uVCuLi4kJCQwGOPPcZzzz3H//gf/4Nnn32Whx56iJiYGFpaWnj//fc5cuSIJMy0EGazmfLycqqqqggICGDp0qVSGOnNsNlsUs60i4sLbm5ukrHkcDiwCEKgarV6TnipiFKpRKVS4XQ6sdlsWK3WT/1ciR7mCxcuMDIywtKlS8nJyZlRBSMoKIg9e/bws5/9jJ///Of85Cc/4bHHHmPJkiWMjIxw4sQJXnvtNSoqKm7YXv8VOAWR1qmpKaampqTQfZ1OR09PD6Ojo7fUblarlba2No4ePUpfXx8rVqwgMzNTEpYVUSgUaLVa3N3dJTHZO/17dlt4VEU0Gg0BAQHExcWRlJREXFwcXl5eDA0NUVdXR29vL76+vsTFxaHRaBgbG6OkpIS6ujpiYmLYsmUL8fHxKIUQYbvdTk9PD+Xl5TgcDjZt2sSyZcukGSyVSsXo6CjFxcUMDAxIhq2npyfl5eWcPXsWm83Grl27WLt27ZyZHLVazdTUFDU1NXR1dREeHk5GRgbe3t6SR1V8QK9fv053dzd5eXns3buXlJSUGbNXVkHq+sSJE9TW1hIWFoabmxvt7e3U1dVRV1dHQ0MDdXV1VFVVMTAwQGhoKJmZmQQEBFBXV0dhYSFOp5OtW7eybt26Oz4cQEZGRgbh4+3u7s6iRYtYvHgx6enppKWlkZqaSkJCAmazmYaGBgYGBggJCSE1NXXewZ7sUf3qIXpUKyoqMJlMpKWlcdddd7Fq1SqWLFmy4JKZmSlFUNlsNlxcXPD09CQmJoa1a9eyfv36OdvcypKZmUlycjJ+fn4EBgaSl5fH6tWr56w337J48WJCQkIYHx9nZGSEyMhIsrKy5NDfBTCZTNTW1lJWVoabmxvLli1j0aJFkqcPoU8YHx+XSookJiayatUqQoT6lrNRChGCcXFxpKens3jxYlJTU0lNTSU2NhaLxUJzczM6nY6goCBiYmLw9PScd6zW0dHB4cOHKS8vZ9myZZI39VZy6U0mEyUlJVy/fp3IyEhWrlwphe2KxmNRURF2u521a9eSnJw8p0/U6XQUFxdTX19PaGgoK1euvKU6siI2m422tjaOHz/O+fPn8ff35+tf/zq5ubm4C3WsEfJGIyMjSUtLIyMjY0bfrdVqaW1tpbm5GT8/P1JTU28p7PlW+Dw8qkqlEh8fH5KSkli+fDlZWVn4+/tLOjhGo5GIiAh8fX0XbDebzUZ/fz/vvfcehw8fJjQ0lMcee4zc3Nw5z4bdbqezs5PCwkIUCgXr1q2Toi3vVOZOofwXo1arCQwMJCcnh/vuu4/vfOc7fP3rXyc2NpaqqirOnDlDZ2fnjNkJcSZsvhslzgiJs53TEY1V0bAVE5hFcQW9Xi+FJM82UhHO1cfHh4CAACmcwmQyzVinr6+PixcvUl5ejsFgmHG86Yge1bGxMcxmM1VVVezfv5+XXnqJF198UVoOHTpEa2srGo1mTqeC8MJ7enqi0WjmHENGRkbmTkShUEh5TGIf6+7uTlxcHBs3buT+++8nNTWV7u5uysrK5kSiyHx1UQiqpC4uLmi1WmJiYsjLy2PdunULLuvXr2fDhg1s2rSJHTt2sGPHDrZv3y799+bNm1m/fv2c7W5lWb9+PatWrSIjI4PExERyc3PnrDPfsn79etasWUNOTg6hoaGSF1D9Oef13Um4uLjg4eEhCfhYLJY5opiix8wkCCFptVrc3NzmjCdFxL7I1dVVant3d3diY2O5++672bNnDykpKYyMjFBXVzej/Mh0RKXf0tJSfHx8yMnJISYmZt5x341QCArm4vgWYewq9pXitc13DlarFbPZjEKhwM3NTdrmVrDb7XR3d3P27FnOnj2LWq1m+/btrFmzBm9v7xnrajQatFqt5NnVarWEh4ezYsUK7r33XvLy8rDZbBQVFTE4OHhbeRDd3NxYtGgRmzZtYteuXezbt4/vf//77N27F51Ox8GDByksLESn08173na7ncHBQU6fPs3777+PSqXigQceYPXq1fj6+s77nDkcDhxCrd35fr/TuG2vUCkoN6amprJz5042btyIm5sbTU1NtLS0zPtS3ci17hTqqN4KorEqPlQ36+RFI1gxj5y80WjEzc2N5ORkXF1dqaiooKioiP7+/jnXYLPZsNlsqFQqQkJCSElJkWbiUlNTSUlJISsri02bNrF3715WrVqFv7//jH1MPxcZGRmZrzouLi4kJiYSHx+P1WplaGjohvUAZb5aqARV1/T0dNLT04mJicHLywu1Wr3golKpUKvVBAQEsHz5cnbu3MnevXvZvXs3a9eulfL4PsuiUqmkRZxon73OfItomPr5+ZGUlERWVpZU3/GrMJj9LLi6uuLj44OHhwcWi4WJiYk5KqpOp5OpqSnGxsZwOBx4e3vj7u7+mdrUzc2NxMREFi1ahEMQztHr9XPGgg6Hg/7+fgoKCujp6SEjI4MlS5bMUSS+ERqNRhIitQvq0eIYWKPR4Ovri5ubG0ajkbGxsTnXjaDGOzk5iUKhwNPTE09Pz1syVMVoxjNnzvDBBx8wOTnJhg0b2LFjB2FhYbd8Da6urkRERJCWloZWq6Wnpwe9Xn/LY/m/NaJBn5qaKk2O9vX1UVZWxuDg4Jz7bLfbGRgY4Ny5c7zzzjuMj4+ze/du9u7dS0REBOp5PLBOIQzbbDbj6uo6Q7fnTuXWnpb/QjQaDcHBwSQlJREYGCh1GPYblK35a1GpVHh4eODm5iYdzzJP0Wybzcbk5CQ6nQ6bzSapSk4nJCSEXbt28d3vfpfVq1czODjIRx99JJXfEfcpPuCuQh2qDRs28NOf/pRf/epX/OpXv+KXv/wlv/zlL/nFL37BP/3TP/HjH/+YHTt2EBISMuN4s89RRkZG5quOGIGiFnLQ7vQPu8yto1ariYiIYOvWrZJ4yfT8uRuhVCpxc3PDz8+PgIAA/P398fDwmHeA+WkQJ9Y/7fdcKZQUWb9+PQ8//DDr1q3Dz89Pft4XwMXFBX9/f3x9fTGZTAwMDGAwGGasI0a7jYyM4OHhQUhICG7TxCk/7X1SCzmhqgUUf51OJ2azWVKVdnNzIycnh9jY2DliRzdCo9Hg6emJVqvFJJTqEnNrNRoN/v7+BAUFSaHvs6/bKaRBjIyMoBHS8qYb6Atdt91up7e3V/IQDg4OsnbtWu677z4WLVqE5hbClqejFPK+p/fb048rehene4y/CBa63vlQKBRERkZKdWPFydHpHlXRSP3kk09488036enpYfPmzXzzm9+cIbI6G4dQumdqagoPDw88PT1v2fD/snJbXJ1TCEsQH7TZD6HJZGJychKr1YqrqyseHh5f6GBDLRSMDw0NZXR0lPr6+jkeUKfTiV6vp62tjd7eXmnmx9fXd8a+goODycrK4q677mLXrl3ExsZSX1/PyZMnqa6ulkKFVYIYSHh4uDTTZjKZ8Pb2JjAwkODgYGkJDAzE398fT0/Pv/qDKCMjI3MnMPvbIf5NDK0aHBxELaSW3KohIvPVwM3Njfj4eEl8caFB4u2OQqhDGRUVxbJlyyQ9jy9qrHQnEBAQQEREBGazmba2NoaGhrBarSD0H0ajkfb2doaGhoiKiiIuLg53d3cUCoXkhdXr9dI24nbz9UU2m43BwUEGBgYkJ4yPj88ML6XD4WB4eJjz58/T3t7O4sWLyc7O/tTKzUqlEm9vbzw9PTEYDOh0OukcVSoVfn5+JCYmotVqaWlpmePxMxqNdHZ20tfXh6enJ9HR0VJeqc1mY2JigvHx8RnXbRfKhJ08eZJ3332XwcFBNmzYwNe+9jUyMjIkka/52ma+v9vtdiYmJujp6cFut0slIMV2MJlMDA4O0tHRwdDQEGazec4+Pg8sFgtjY2PSfZ5+vvOdt8PhkNIHHQ6HFNYsvofTPalvvPEGnZ2d3H333Xz3u98lKSkJjUYz734RrnlsbAybzYafn99XQovm1p/6LxCTyURPTw/t7e3SjJbZbMZkMklx/NevX5c6itjY2FsKP/isuLi4EBMTQ2pqKg6Hg6tXr1JQUMDIyAg2mw273c7U1BQNDQ3S3xctWkRGRoZUF0pEIYQDe3l5kZeXx/bt2/Hz8+Pq1aucOnWKlpYWKdw3NDSUJUuWEBAQQHFxMZ988gldXV0YjUbsdjt2ux2LxSKpi4mzYzIyMjJfZaxWKwMDAwwNDUn5Vna7HaPRSHd3N+fPn6euro6IiAhp0CcjIyMTFhZGeno6np6eNDc3U1paSn9/v5S72dHRwZUrVxgcHCQtLU0qXyOqtJ4/f57Lly/T3d09Y9w6MjLC1NTUjL6os7OTgoICamtr8fb2Jjk5mYCAgBnjWbPZTEVFBdevX8fFxYXc3Fyp/umnJSAggICAACYmJhgYGJAUcxUKBb6+vmRnZxMcHExtbS0lJSUMDQ1JYaVNTU2UlpYyMjJCdHS0JGJktVrp6ekhPz+fc+fO0d3djdVqlYyv48eP8/bbb9Pb28uaNWt44IEHSExMxG63YzAYmJycxGAwSFGKNpuN0dFRhoeHMRgM0r5MJhN9fX0UFxdTVFQEwLJly2aUF+vu7ub48eP85S9/4fz584yOjs7wWt4qCxmFCL+1tbVx5swZLl++TF9fH1ZB5XdgYECyWWw2Gw4hz1mcaKirq0OhUJCYmEhgYCAqlUpqp48++ohXX32V5uZmVq9ezbe+9S1iYmIwm80z2ml6yDbA+Pg43d3daDQawsLC5tXPudO4LVR/e3p6OHz4MMePH6ezs1MKt+3q6uLatWscOXKES5cu4evry549e7jrrrvQarWMjY1RXFxMbW0twcHBrFy5kqioKGm2xWKx0NLSQlFREVNTU+Tl5ZGZmTljZqOnp4eCggIGBgZITExk6dKlhIaG4ipIzvf29lJZWcnQ0BBubm6o1WrGxsaorKzkyJEjfPLJJ7i7u7Nz506pgLHFYqGmpobCwkJcXV1ZsWIFiYmJ+Pr64uXlxfj4OI2NjXR1deHl5SWpvqmFBPehoSHKysro6OiQOhax8+vs7KSpqYmRkRHc3Nzw8PDAbrdTW1tLQUEBdrud5cuXs3jx4jlhyDIyMjJ3Gna7nf7+fvbv309VVRUI9RFHRkaora3l0KFDHDx4EJ1Ox6ZNm7jvvvuIiIiYvRsQBiWjo6NcvHiRjo4OWfVX5m+OUwj9HBoawmAwEBYWNidSS+bzQwzj7evro7GxkcHBQVxdXVGpVHR1dXH8+HFOnz6Np6cnDz30ECtXrsTNzY2+vj4OHTrECy+8wPXr13FzcyM0NJTh4WHOnTtHVVUVU1NTMxwuR44c4dixY4yPj7N27VruueceYmNjpcg4uxD9sX//fi5dukROTg73338/iYmJn8nL73A4aGxspKGhgYCAAMmZohAExDQaDV1dXVRVVdHb2yuNQ3t6evjwww85e/YsXl5e7Nixg3Xr1uHr68vo6CjHjh3j97//PWfPnsXPz4+4uDiMRiPHjh3j9ddfp6GhgYSEBJYuXYq7uzu9vb20tbXR1tZGe3s7vb29kpDV6OgoZ86coaSkhPHxcSlntqWlhTNnznDgwAGam5vJyMjgscceIzExUWqv8+fP8+KLL3L58mXCw8OlPN5bNdxmq/4uXboUT0/PGetYLBZefPFF/vSnP1FSUkJwcDCRkZG0trZy4sQJSSjVbDYzNjZGZ2cn+fn5vPzyy7S1tZGdnc3XvvY1UlNTcXV1ZXh4mFOnTvHqq69SWVlJdHQ0d911F66urnR2dkpt1NbWRmdnp6QmLhrnDQ0NnDx5EoPBwPbt20lPT/9Mz8aXidvGUD158iQfffQR+fn5fPzxx5w4cYIPPviAM2fO0NTURGhoKPv27eOhhx4iODgYhVCftLy8nMbGRkJCQli1atUcQ7W9vZ2SkhLMZrNkwE03VPv6+qQHNSkpiZycHKmQc1BQEJ6envT29lJeXs6lS5f4+OOP+eCDDzh69CilpaX4+/tz3333cd999xEbGysdV/QCu7m5kZeXJ4VYiIn4g4ODUh3UkJAQYmJi0Gq1BAYGEhISIhnDV65c4ZNPPuHEiRMcPXqUo0ePcunSJSYnJ4mLiyM0NBSHw0FDQwPXrl3D6XSSl5dHenq6bKjKyMjc8ZjNZurq6vjd737HoUOHOHfuHMePH+fw4cMcOnSIgoICALZv387jjz9OVlbWgiF0TiEvSxQxkQ1Vmb81sqH6t0WhUODj4yMZn2VlZVy6dEkSAiooKMDV1ZVHHnmEe++9Vyrx0t3dTX5+PteuXWNycpLIyEji4+Pp6urijTfe4MCBA5w5c4bjx49z5MiRGX3R1q1b2bdvH4sXL8bNzU06F6PRyNWrVzl48CBjY2N87WtfY+PGjZ85vNPDw4OBgQHKy8tRKBQkJydLZXWUSiUeHh4EBATQ39/PtWvXuHz5Mh9//DFHjhyhoKAAFxcXdu7cye7du4mMjESlUjE8PMzp06cpKChgaGiIhIQEMjMzqamp4Y033qCiokIKia6srOTMmTOcOnWK06dPc+rUKT766COuXbtGSEgIsbGxdHd38/bbb3PgwAFOnTrFyZMnOXLkCIcPH+bcuXOMjY2Rm5vLU089xYoVK6TwY4fDwYULF7h8+TJhYWFs27aNjIyMGe15M7q7uyktLWV0dHTe8jROIcXv9ddfp6ysjImJCdLS0khJSaG+vp79+/dLdsrJkyc5evQohw4d4sMPP2R4eJiMjAyefvppSelYqVRSWFjIG2+8QXFxseSZraqq4uTJk1I7nT59mpMnT3L+/HnpudJqtVitVq5fv87JkycJCwvjoYceIjQ0dMHv2Z3CbWGoivHvISEhUgy7GNcdFxfH1q1b+c53vsPu3bsJCgqSXlir1crY2BgKhYL09HSys7MJCAiQbpqYdKzX6wkMDGTFihXExcWhnibXLnpvvby8yMzMJC0tTZqRcXV1JSEhgaysLDw8PNDr9eh0OoxGI76+vmzYsIFvfvOb7Nmzh6ioKBRCmK/D4ZDyFqKjo8nLyyMyMhKNIBXv7e2Nt7e39P+BgYFERkZKD3J4eDjZ2dnExMSgUqkwmUyYTCYUCgX+/v6kpqayevVqqWar+DKNj48TEREhXednCRWRkZGR+TKhFMoZiMqdolKl2WzG09OTvLw8vvOd7/D444+Tmpp607QRi1Cs3dXVlaVLl5KWljaj5p+MzBeJbKj+7XFxcSEsLIzo6Gg0Gg1jY2OMjY2hUqnIzs7mW9/6Fvfffz8RERHS+FKhUKDX69Hr9cTGxnLXXXexePFi/P390Wq1M8afYl+0fPlynnzySfbt20dqauoco8pkMtHQ0MDQ0BBLly5lz549xMfH37TPWgilUDO1paWF3t5eAgMDiY+Pl7yGGo2GkJAQEhMTcXV1RafTodPpAMjKyuLxxx/n3nvvlXKdEZ5PsY+MiIhg165dZGRkSOUV/fz8iI2NJTw8HH9/fwICAggMDCQwMJCgoCApJzg3N5e4uDh8fHwkp4rRaESv12MymXB1dSUtLY2HHnqI73znO3Nqr46NjfHRRx9RVlbGsmXL2Lp166euJyrm7orlf5KTk2c4eBQKBS4uLoyOjqLX60lNTWXr1q2SuKtYmtJkMqHX6zEIJSjj4+N56KGHePbZZ1m5cqU0tgekHGVvb2/i4+OJiIiY007ivkNDQ1m1apUU+t3V1cWpU6eor69n3bp1bNmy5VPXff0yonAuFJj9N8QpCF6YzWbMZjMWiwWbzYZCqEel1WrnJCMjhEmYTCYsFgtqtVoKzZ2+X3HGwul04iao6k7fh81mw2g0YrPZpGPNFiiy2WxMTU0xPj7OxMQEDocDLy8vaRZOVCQTEV/kqakpANzd3XFxcZGO63A4sFqtUu6pZpqMuIjD4cBsNmM0GjGbzdjtdhRCuIarIEk9/bji8Ra6ThkZGZk7FbG/FPP3dTodTqdTmhT08PCY008vhJhPZrVacXFxwe0GNRNlZD5vRCGWmpoaBgcHJcVXmS8Wp5AvKRovBoMBFxcX/Pz88PLymtN/OBwOJicnGRsbQ6lU4uvri7u7uzT+MxqNGAwGxoQqFbP7ovkMKofDgdFoxGQySalgf21Y59jYGG+99Rbvv/8+aWlpfPvb35YiC5k2/jYajYyMjKDX63FxcZFS1cQwaBHxHIeHhwEIDAzE3d1dumb7LVTkUAp1rl0FFWOLxYJJEE0VSwS5ubnh4+ODp6cnrkJN2ulUV1fzf/7P/6Guro4nnniCffv2zXBk3QrTx+FarRZXIeVvNnq9nqGhIVxdXaWJCPE+m81m6byNRiMeHh7SeWu1WlSz1J3FdrLZbDdsJ6fTiUKhkKqJ2Gw2zpw5wx/+8AcUCgX/8A//wMqVK6U2vJO5LQzV2TiFxObpN/dGD594CQutc7PfucV1HNOUiVVCjbObMfs6ZnMrx53dHjdb90a/y8jIyNzJiP00Ql+pVH42hXi5L5X5r0A2VP/rEfuQm/Uf4tiMacKZs38Tx4zKW6xxfytjwk+Dw+GgrKyMv/zlL7S1tbFz507uu+8+QkNDZ68647rFa58P8brE9cRzFc/9Vph9fdPbS/z9Ru314Ycf8n//7/8lPDycb37zmyxfvvwzRb7cSntPv9752sQpGPu3ep8/bTs5nU5aWlp46aWXKCwsZMeOHXzrW98iMDDwhse5U5jb4rcB0x/Q6S/BQtxsnZv9zi2uo1QqpQT0+R7W+bjZPm/luLPb40bc7HcZGRmZOxmxn1ar1XNmsz8Nn3U7GRmZLzdiH3Kz/kMcm81nmIi/iWPGm+1L5FbGeZ8GpVJJUlISW7duJTExkbGxMYaHh7FOKyszfV3xum80xlUoFNI6089VPPdbWWajmNZeN2t7UZk4KSmJu+++m6SkpM/sWVzofKajmHa986GYJk51o/MWmd0WN1oQPL/d3d1YLBbWrFnD1q1b8fX1velx7hRuS4+qjIyMjIyMjMxXDdmjKvN54xTUzLu6unA4HERGRs4pi/Nlwm6309HRwdjYGCEhIQQHB//VIdK3MzabjZ6eHvr7+/Hy8iI2NlZSq/4qIBuqMjIyMjIyMjK3AbKhKvNF4BRycB0OByqV6pY8f7cr4rUAN/R03imI12u322/qbb4TubPvroyMjIyMjIyMjMxXGIUgTioKE32ZDR3xWj5NGt6XGfF6RbHXL/O9+yzc+XdYRkZGRkZGRkZGRkZG5kvF39RQFVW9xEVGRkZGRkZGRkZGRkZGZjZfuKEqyjaLBXHHxsYYHx/HYDBgsVgkKWoZGRkZGRkZGRkZGRkZGb5oMSW73Y7BYGBgYIDOzk56e3uZmJhApVIREBBAZGQkMTExBAcHzynmKyMjIyMjIyPzVUIWU5KRkZH5f3xhhqrdbmd4eJjy8nIuX75MaWkpHR0dTExMoFQqCQgIICUlhd27d7Nt2za8vb2/cgnCMjIyMjIyMjIisqEqIyMj8//4QkJ/nU4n4+PjXLlyhVdeeYW3336bjo4O4uLiuPvuu1m5ciVeXl60tbXR0tKCxWKZvQsZGRkZGRkZGRkZGRmZryhfiEfVYrFQUVHBiy++yIULF4iPj+f+++9n1apV+Pn5YbFY6OnpYXR0lOjoaNLS0u7oYr0yMjIyMjIyMjdD9qjKyMjI/D++EI/q1NQUTU1N1NTUoNFo2LZtG/feey/p6emEh4cTGxvL6tWr2bVrF1lZWXOM1FtRBV5ondl/dzgcUqHc+RB/t1qt2O32GdvO3tdsRKEoq9WK1Wq9oTDU7H2J24oFmG+GuP2NzkdGRkZGRkZGRkZGRuZO4AsxVK1WK+Pj45jNZry9vQkNDcXLy2v2anNwOBxMTU0xPDzMyMgIRqNxjhHndDoxGAwMDg6i0+kwm82SAWcymRgdHUWn02EymTAajfT29lJfX093dzdms1naj91uR6/X09XVRXV1NZWVlTQ3NzMyMoLZbGZycpLh4WEmJiaw2WxzzsFsNjM8PExTUxPl5eVUVVVJObizjWKxPUZHR5mcnMRsNqPT6Whubqauro6urq55t0M4lslkYmRkhKGhISYnJ+ddT0ZGRkZGRkZGRkZG5k5B9Ytf/OIXs//412IymWhubqakpAS9Xk9CQgKLFi3Cw8PjhoJJU1NTlJSUcPDgQcrKytBqtQQFBUkeV6fTidFopLCwkJdffpmmpib8/Pzw9fXF4XBQW1vLkSNHKCsrw26309DQwMsvv8yrr77KyMgIKSkpeHl5YbVaaWtr4/jx47z88su88MILHDhwgMuXLzM0NITD4aCyspJDhw4xOjpKREQE7u7uKBQKHA4HIyMjFBUV8c477/DnP/+Z1157jWPHjlFWVobBYMDX1xcfHx+Uyv//PEBfXx+nTp3i3LlzTExMMDIywtGjR/nd737HgQMHKCsrY2pqisDAQHx9fWe0idls5vr16+zfv5+rV6+iUqkICgpCq9XOWE9GRkZGRkbmy404ET40NITBYCAsLGzOuEBGRkbmq8IXYqgC6PV6mpqaaG9vR6/Xo9VqCQgIQKvVolQq5zVYJycnuXr1KkeOHKGtrY24uDgWLVo0wygzGo2cO3eOF198Eb1eT3p6OpGRkQBUV1dz9OhRysrK6O7uJj8/n4KCApxOJ8nJySxduhQPDw+qq6t55ZVX2L9/P52dnQQHBxMTEyMZu1VVVRQVFXHlyhX8/PxYtmyZ5BEeHBzk5MmTvPrqq5SXl+Pv709KSgre3t60trZy7do19Ho90dHRBAYGolAo6O3t5dSpU+Tn59PT00N1dTUXL16ktbUVnU5HZ2cnExMTxMXFERsbi0qlkq63t7eXDz74gCNHjjA1NUVmZiYJCQm4urpK68jIyMjIyMh8+ZENVRkZGZn/xxcS+qvVaklJSWHz5s3ExcVRU1PDCy+8wH/8x39w8uRJ2tramJqamhPCKuZtmkwmzGbznLBfcR2bzYbZbJ6TFyqGyba1tXH16lWMRiP3338/f//3f8+uXbvw9/enp6eHDz74gFOnTqFWq3nggQf4//6//49//ud/5h//8R/Zs2cPZrOZqqoqJicnZxjVBoOBwsJCDh48yNDQEFu3buUf/uEf+PnPf84//uM/8sQTT+Dr68vp06cl76nT6ZQ8sUNDQxQVFdHY2Eh6ejrPPPMM3/jGNwgPD6e+vp7Kykp0Ot2M6+np6aG2thaLxUJMTAwxMTG4u7tL68jIyMjIyMjIyMjIyNxpfCGGqlKpJDg4mE2bNvHwww+zZMkShoaGOHr0KL/5zW/4l3/5Fw4fPkxnZ+eCpWkUCsW8Xlem/TZ7HaVSicPhwGAw4O7uzpYtW/j2t7/N7t27yczMRKPRUFtbS35+PgBbtmzhoYceYs2aNaSlpbF8+XJ2797NunXrpBnM6cfo7u6WwoNzc3O59957ycvLIz4+nsWLF7N9+3bWr1+PyWTi6tWrtLa24nA4pH0YjUZsNhvp6el8/etf5/HHH2fv3r3k5ORgs9moq6ujt7dXEkwyGo20t7fT3t6Ot7c3aWlphISEzPC4ysjIyMjIyMjIyMjI3Gl8IYYqgEajITo6mp07d/LDH/6QJ554gvT0dHQ6HWfOnOGPf/wjr764UGcaAAD/9ElEQVT6KrW1tTNEjv5anE4nrq6upKamsnbtWpKSkvD398fd3R29Xk9NTQ0dHR1ERkaycuVK4uPj8fDwQKVS4ebmRmRkJFlZWcTExIAg8CT+29HRQVVVFRqNhuTkZIKCgrDZbJJAkoeHB9HR0Xh5edHS0kJ7e7tkdIqe1fDwcJYvX05mZiaRkZEkJCSQnZ1NUFAQ9fX1NDQ0SAJRQ0ND1NfXMz4+TmRkJGlpaXIIkIyMjIyMjIyMjIzMHc8XZqgiGKthYWGsXr2axx9/nJ/85Cd85zvfITMzk66uLg4ePMiRI0fo6uqao6z716DVaomIiCA8PHxG6RudTkdHRwc2m43IyEji4uLmhNGq1Wr8/Pzw8fGZ4a01m8309fXR19fHxMQE9fX1nDx5knfffZcDBw7w7rvvcvToUSoqKjAYDIyNjTEyMiIZuk6nE41GQ2hoKDExMXh7e6NUKvHy8iIlJYWoqCh6e3uprKxkdHQUp9NJX18fTU1NuLi4kJqaSlRUlCyiJCMjIyMjIyMjIyNzx/OFGqoI4bgeHh7Exsaydu1aHn74YZ566inWrl3L4OAg+fn5VFdXYzKZZm/6mXA6nSiVStzc3GYIDjmdTqamphgfH0elUuHr64u3t/ecGq4I4b6zw2tNJhNjY2NMTU0xNDQkiT69++67krF6+PBhSkpKcDqd+Pv7o9VqZxi7arUaT09PvLy8UKvVALi6uhITE0N6ejoajYbq6mra2towGAy0t7fT1dVFYGAgGRkZBAQELBgOLSMjIyMjIyMjIyMjc6fwhRuq0xE9rOvWreOee+4hPDycvr4+Wltb54T/OoXaqLO5VUNtdv7q9L+Jgkx2u33eYyAcfzr/P/buM7qN+0z0/xcgCsEG9gb23psoUaSKLUuWLNmSZVsuseNsnNz0ZG/Zc7beF7n37tl79uTuuXuzyaY4iRN3x022JduyuqhGilXsvYAVBAmC6P3/4k/MsqrYli3J8zlnXkicATADYDDPPL/f83i9XqH4k1qtJjs7m/LycjZs2EBlZSWVlZVs3LiRe++9l0OHDvH444+Tn58vtKhh8fmlUumyAk0ymUwIRDUaDb29vXR1dTE9PU1PTw8LCwukpaUJ7X1EIpFIJBKJRCKR6G73hQaqLAZr/rmcCQkJeDweoQLw0kymy+VaVdUXwOPx4Ha7VwWS1yORSAgJCSEyMlLoharX61cVc/J6vdjtdux2+7LnUCqVhISEoFQqSUhIYM+ePXznO9/hJz/5ybLlxz/+MT/4wQ/42te+RkFBwbLMrD/4XvnaVSoVOTk5ZGdnMzc3x9WrV2lra6O3t5fg4GCKiopISEhYM/srEolEIpFIJBKJRHebWxKo+nw+XC4XDocDt9uN1+sVAjR/IGgwGDCZTCgUCoKDg5FKpchkMlQqFQEBAVgsFmZnZ7FYLMK2brcbvV7P+Pg4brd7Vcb0eiIiIsjIyCAwMJCRkRG6urowGAx4PB68Xi9ut5uFhQWGh4eZmprCt1gAicV5r4mJicTExGC321lYWEClUhEfH09iYiIajUaYF5uQkEBsbCwqlWrlS1iTXC4nOTmZ0tJS1Go1LS0tHD9+nNHRUTQaDfn5+YSFhd30/opEIpFIJBKJRCLRneiWBKoOh4Px8XHa29vp7e1Fp9NhMpkwm83odDo6Ojq4cOECo6OjxMfHC8GjQqEgKiqKqKgobDYbPT099Pf3YzQasVgsTE5OcvnyZa5cufKpAtWwsDCKi4vJyclhamqKM2fO0NjYiFarRa/XMzY2RlNTE+fPn2d0dHTZ8GGZTEZGRgalpaVYLBYuXLjAlStXGB8fx2Kx4HA4sNlsGI1G9Ho9ZrN5VeZ0Pf6iSkVFRWRnZ9Pf38+JEycwGAxkZGSQkpIiFlESiUQikUgkEolEXxkBP/3pT3+68j8/K4PBwLlz5zh8+DAtLS3odDr0ej1arZYrV65w5MgRTp06hVwuZ9++fTzwwANERUUREBCA2+1menqagYEBJiYmcDgceL1eJicnuXDhAsePH2dwcBC32018fDzV1dWkpqYilUoZGRnh4sWLGAwGysrKqKioIDQ0VHhd/iJLTqeT7u5uent7mZycZHZ2lrGxMa5cucKJEyfo7OzEbDYjkUgoLS2lqqqK0NBQgoKC8Hq9DAwM0N3dzcTEBGazGavVil6vZ2RkhI6ODjo6OpBKpcTHxyOVSpmdneXKlSv09fWRlJTEpk2bSExMXDYsWCqVEhgYyNjYGPX19UxOTpKWlsZDDz1EWVkZISEhwroikUgkEonuPj6fD4fDwczMDBaLhYSEBLEtnUgk+sq6JYHqwsICLS0tnDt3jgsXLlBfX8/ly5c5d+4cZ86cobe3l+joaPbv38/TTz9Neno6crkcqVSKUqlEIpEwMzPDwMAA7e3tNDQ0UFdXR0tLC2FhYVRUVGCz2QgLC2Pjxo2kpqYSEBCAVqulubkZm81GeXk5ZWVlywJVgODgYGJiYpDL5czMzNDX10dzczMNDQ309fWhVCopLCwUAszS0lKqq6sJCQkhMDCQqKgoQkJCMBgMdHd3C6/twoULnDlzhnPnztHV1UViYiKFhYUEBAQwNzdHW1sbWq2WlJQUNm7cSHx8/LJAVSKRoFQq0ev1tLW1YbVa2bJlC3v37iU5OVmoEiwSiUQikejuJAaqIpFI9B9uSaCqUCiIjY0lJSWF6OhoZDIZXq8XuVxOSkoKu3bt4tlnn+WRRx4RgsyV2yYmJhIUFCQUVVKr1dx33318+9vfprKyEolEQnJyMiUlJULQZ7fbcblcJCQkUFFRQVZW1qohsxKJhIiICPLz8ykoKECj0RAREUF6ejq7d+/m0KFDZGRk0N3djVarpbq6mi1btgitZoKDg0lPTycvL4/Y2FgAbDYbLpcLpVJJWloaO3bsYPv27cTGxiKRSHC5XFgsFkJCQigqKqKoqIiIiIhlFYEB3G43g4OD1NfXo1Qqefjhh9m6das4P1UkEolEoq8AMVAViUSi/yDx3ehEyk/B4/Fgt9uxWq1C+xmFQkFoaOiqHqMreTwezGYzCwsLuN1ulEolarWaoKAgoVIwi0WO/NVw3W43DocDj8eDUqlEoVCsCgaXWlr0yZ/RtNlsnD17ln/7t39jcHCQ//bf/hvf/e53V2U0/duazWZsNhter5eAgABUKhXBwcEoFAphXX8BKZfLhUwmQ6lUrno8j8fDxMQEv/71r3nhhReoqqrir/7qr6isrFwVbItEIpFIJLr7eL1ejEYjHR0d6HQ6KioqSEtLW7maSHTT/F00ltZfEd0Zvsrv3fpR3OcgICCAoKAgoqOjSUxMFKrmrhWkut1uLBYLJpMJm80Gi8WPNBoNKSkpxMfHExQUhGSxhY3/MVwul9DfVC6XExwcTFhYGIGBgWsGqf4A02634/F4kMvlhISECD1K9Xo97e3tjI+Pk5CQQFJS0qqgksUPi0KhICIigoSEBDQaDfHx8YSHhy8LUlmcfxoUFERYWBhBQUGrHs8/L/fDDz/ko48+Qq1Ws3PnTvLz81EqlcvWFYlEItGt4a/+7v9duYX3cUUi0W3I353C7XYLXSs+i9vhnOLz+bBarUxNTTE2NobJZFpzv7xeLy6X63PZb5bs+2d9PP978mUcu9uBx+PBYDAwOjqKTqfD5XKtXOWudkszqjfK6/UKRYRmZ2dJTk6mrKxMKEa0ksvloqenh4aGBmHOqkajuaE+ow6Hg76+PqHicFxcHEqlErfbzdTUFGfPnuXtt99Gq9Vy8OBBfvzjH5OZmbnyYT4XPp8Pm83GyMgIx48f54033mBwcJBHHnmEH/zgB+Tl5d3QPolEIpHoP3i9Xmw2m9APOygoCJVKteoGqX9dh8OB1WplYWEBo9GIw+EQ+m6r1ep1b3yKRJ83MaP65fAttkA0m83Mzc1hNBqRSCRERUURERGBSqValWRYj8fjWdYJYn5+Ho/HQ2hoKBEREcKowmudU3w+H3a7XUiqBAYGCu0bb5bdbqeuro7z588TERHBzp07yczMFPbH7XZjtVqZnZ1lbm5OmCIXGRkpJFfWOneuxz/dbW5ujvn5eaRSKZGRkYSHhxMcHHzdffC/F3a7HYfDgd1ux+l0EhUVRWho6DWP241a+h6xODpTpVJ95sf2LQ7dN5vNeL1e4bfHv89ut3vZb9N6fIvtMf3Hv7m5mePHjxMUFMT+/fuXvX93u9siUHW5XFy4cIF//dd/pauri+zsbJ555hl2795NVFTUytWxWCy89dZb/N//+39JS0vjRz/6ETU1NUJW9Frm5uZ46623eOedd1AqlcTFxQlzYf0FnCwWC5s2beK5555jy5YtqzKknxebzUZ7eztvvvkmx44dY35+ni1btvDd736XqqqqNTPPIpFIJFqb/+bfzMwM58+fp7W1FZ/PxwMPPEBNTc2q3tb+oODSpUtcuHABrVYrBKpBQUGkpqZSU1NDdXU1CQkJ173AEok+KzFQ/eL5fD4sFgu9vb1cuHCB5uZm9Ho9UqmU2NhYKisr2bFjB2lpaddNHrhcLqampqivr6ehoUE4p7jdbkJCQsjMzGTbtm1UVlYSHR296pziv3E2NzdHY2MjjY2NWCwWqqur2bZtG9HR0TcVTPl8Prq6unjppZfo7Ozkvvvu49FHH0Wj0SCRSHA4HAwMDHDq1ClhvwFiYmKorKxk27ZtZGRkrHujbyWHw0FnZyfnzp2jpaVFOI7x8fFs2LCBnTt3kpqaum6Q5XK5WFhYYGhoiJaWFnp6epidnSUgIICnn36azZs3rzqP3wzv4lS8yclJGhoauHr1KlKpVDi+Kwuw3gzfYuba36HEZDKxb98+ampqiIyMRCqVMjo6ypkzZ2hqasJms617TCUSCTKZjB07dlBTU4Ner+ePf/wjLS0tPPzwwzzzzDNERESsu/3d5JYUU7pZ3sWWL5988gnd3d3Mz88jl8tJSkpaVR2XxS9CU1MTx44dIygoiM2bN5OamnpDAaXH48FoNDIxMYFWq2V4eJjBwUG0Wi1msxmNRsOePXs4dOgQFRUVBAUFrXyIz43/BHH27FlmZ2e57777ePbZZ9m4caMwzFkkEolE1+f1ejEYDJw8eZI//elPvPvuu1y6dIm+vj4yMzMpLCxcNd/f36rsF7/4BRcuXMBgMAg1EMbGxujo6GBwcBCpVEpycvJnuogRiW6EPyMjFlP64thsNpqamnjjjTf48MMPGRsbA8BqtdLX10draytOpxONRoNarV51TbqUxWLh8uXLvPbaa1y8eBGj0SjUXPG3MNRqtQQGBi6b0sbi9en8/Dx1dXW8+uqr/PnPf+bcuXN0dHQQHR1NYWEh4eHhNxWoms1mjh8/zsmTJ4mPj2fv3r1kZWUhl8ux2+10dnby4osv8u677zIxMUFAQAAWi4X+/n66urqw2+3ExMQQERGxbnDp53K5aGho4JVXXuHo0aOMj48jkUgwm8309PTQ1taG3W4nNTUVtVq9aj/sdjvd3d289957vPbaa5w4cYLu7m4mJydxOp3CTZsbudZfi9frRa/Xc/bsWV5//XUOHz7M+fPn0Wq1xMXFUVxcfEMJr/U4nU66urr45S9/yccff8zVq1dJT08nPz+fsLAwpFIpY2NjnD59mrNnzzIwMMDo6OiyRavV0tvby9WrV+nu7iY1NZWCggISEhKw2Wy0trYyOTlJdnb2mvHR3ei2CVSHh4e5cOGCcDfHZrMREhIifKCXBm1Op5OOjg4uXLhAVFQU1dXVN/zhDQgIICoqipycHEpKSqisrKSqqoqamhp27NjB/fffz7Zt28jOzv5CepdKJBKhzc6+ffsoKSkhJCREDFJFIpHoJthsNmpra/nFL35Bb28vAQEBGAwG7HY7mzdvpqKiYlWg6vP5MJlM9PX1UVxczCOPPMKuXbvYsmULaWlp6PV6uru7MZvNpKSkkJmZKZ6b7zA+nw/f4hw3yR1QiORWB6r+Y+F3ux+PW83r9dLb28s777zD2bNnCQ8P58CBAxw8eJBNmzahUqno7u6mt7eXyMhI0tLSrplIcDqd6PV6zGYzJSUlPPTQQ+zatYuamhoSEhKYnp6mp6cHj8dDSkoKcXFxQpbWZrPR0NDASy+9RH19PR6PB5PJhNlsprCwkA0bNgiZuRvV3d3N+++/j16vZ9u2bWzZsoWIiAg8Hg/j4+O8/fbbHDlyBLVazaFDhzh48CDV1dWoVCoGBwcZHh4mKCiItLQ0QkND191vn8/HwMAAr7/+OsePHycmJoaDBw/y8MMPs3HjRlQqFZ2dnfT19REdHU16evqyRJDNZqOxsZHXX3+do0ePotfrycrKYufOnTzwwAPs2LGDkpKSNTtm3CiXy8WpU6d444036OjowOFwYDKZ8Pl8wvH9tNf9nsWCqG+88QbHjh3DYrFgNBqpqqqivLxcCMylUikRERHk5eWxefNmtmzZIixbt27lnnvuQaFQCO0yd+/eTWlpKeHh4cjlcsbHx2lrayM0NJSioqLPlF2+U9xWgerFixdxu93Ex8djt9sxmUzExcWRnJy8rKiQ0+mkvb1dGG+/VqDqPxk7nU7sdjs2mw2n04nX60WlUhEfH09aWho5OTnk5eVRUFBAbm4uKSkpREZG3lDQ+1lJpVKCg4NJTk4mPz+fpKSkVRdSIpFIJLo+t9vN8PAw/f393HvvvVRWVjI+Po7JZKKmpmbNQFWyOAcoLS2NzZs3U15eTlZWFpmZmaSlpeF0Ounr62N2dpa0tDRKS0uvO/RPdPvwB31zc3MYDAYki9X917vYvh3cykDVP6JMr9fjdDqRy+XXzZLd7YxGI2fPnuX999/H5XLx4IMP8uijj1JeXk5aWhpxcXHodDpaW1uRSqXk5uYSGxu77nELCAggLCyM7OxsNm7cSFlZmXBOSUlJwWw2093djdvtJisra1nA5nK5GBsbQ6vVUlBQQE1NDQsLC8zMzFBcXMzGjRtvKlBzuVycP3+eEydOEB0dzZ49e8jJyUGhUGA2m7ly5Qp//vOfmZub44knnuDQoUOUlJSQkZFBXFwcMzMzdHR04HK5SE9PJyEhYd3zn9Pp5Pjx47zzzjtIJBIOHDjAI488QllZGZmZmcTExKDT6ejs7MRut1NeXi60cPR4PLS2tvL6669z7tw51Go1Dz30EIcOHeLee++lvLyc7OzsG8rqXovP56O3t5eZmRnKy8spLCzEZDJht9spKiqisrLyU2VUfT4fc3NznDx5kjfffJPg4GCioqIwGAyrAlWlUkl8fDw5OTlCm0z/kp+fT1paGs3NzXR0dLBp0yb2799Peno6crkclUqFwWCgsbERm81GRUUFUVFRN/x5uFPdNnvnv+sZERFBaWkp6enpaLVazpw5Q39/P57Fyr43wuv1YrVaGRoa4ty5c7z99tu89tprwrCO1tZWjEYjMpmMoKAgQkNDCQkJQaVSIZfLv7AfMYlEQmBgIFFRUYSHh3+mL6BIJBJ9lSkUCsrKyvjxj3/Ms88+y6ZNm4QLfN86pRikUikhISHCxVlISAhKpRKlUklsbCw5OTnExMTgdDqx2Ww39Tsk+vK53W4mJiY4c+YMR44cobOz85oVM5cWWPEXPHG5XOt+fm4V/zXI530tYjKZaG1t5aOPPuLChQtMT08vy65+FU1PT3P16lVmZmZIT0+nqqqKlJQUAgMDCQkJIScnh5qaGqKjo4WM4LUK4chkMmJiYsjNzSU5OVloVxgYGIhGoyE9PZ3w8HBhLurS469QKMjPz+frX/863/rWt9i2bRsxMTFCILLec65nbm6Onp4eTCYTycnJwn75fD6MRiPNzc1otVoyMzPZsmULycnJQlGhvLw8KisriYyMZGRkRBhZsp65uTmampqEYamVlZUkJiYSGBhIcHAwWVlZbNmyBbVaTVtbG/39/dhsNnw+H5OTkxw7doyLFy8SGxvL448/zpNPPsnmzZtJSkoSik991mGuAQEBVFRU8I1vfIOvf/3rVFVVrTlP+GZZrVba2to4cuQIVquVXbt2kZiYuObjBix2LQkJCSE0NHTZolKpGB0dpbGxEYVCwZYtW0hPTxcSZ0FBQWRkZKDRaNBqtXR3d+N0Olc+xV3ntglUWQww5XI52dnZbNq0ieDgYOrq6qitrUWv19/Ql9Q/T+nKlSu89tpr/Pa3v+WFF17glVde4aWXXuI3v/kNzz//PMeOHWNkZOQr8SaLRCLR3S4gIIDExES2bNmCRqNBJpPd0G/GUv4bpp7FHuBzc3PY7XbUajUxMTFiu7A7jNPpRKvVcvnyZc6ePStcbLtcrlWLzWZjamqKlpYWzp8/T21tLfX19QwNDa27za1a/O08vF4vHo9n1d8/7WIwGGhra+P8+fM0NjYyPT2N2+1eedi+Mnw+H9PT0wwPDyOTyYQgwP899ycT/BnGiYkJhoaGsFqtN3xuWXpOMZlMzM3N4Xa7CQsLE4Zz+slkMhISEqioqCAjI0MYAXKjz7XS5OQkw8PDKBQKkpKShHmSXq+Xubk5uru7sVqt5OTkkJiYuOy1+IvJJSYmYrFYGB0dxWKxLHv8pbRaLUNDQwQEBJCZmUlSUtKykYnBwcHk5OQQGxuLwWCgt7eXhYUFPB6P8J2TSCRs376drVu3EhYWxvz8PHNzc8L379MeBz+JREJycjIbNmwgNTV11QibT8PlcjE0NMQnn3xCb28v1dXV7NixA6VSeVM3gXw+H2azmWPHjtHd3U1BQQHl5eXLCiZJJBJiY2PJyMjAZDLR29uLw+FY+VB3ndsqUPV/mdVqNRUVFRQUFGAwGDh9+jQtLS3XfUN8Ph8LCws0NDTw6quv8s477zA5OUlqaiobNmygsLAQqVTKuXPnePHFFzl+/DgTExNf6RO1SCQS3S0+SwbK6XSysLDA3NwcY2NjXL58mdraWqxWK+Xl5RQVFX0hU0JEnx//6Cqj0YjBYGBsbIyuri66u7vp6uoSlu7ubqHuxXvvvcfrr7/O66+/zltvvcXx48eFwiZLt7lVS3d3N319fYyNjTE9Pc3AwMCqdT7t0tvby/j4OAsLC1gsFux2+01dTN9tXC4Xc3NzzM7OCsWNVg79lEqlhIeHExkZidVqRafTYbFYrnvcfIvtZRYWFpidnWVkZITa2lrq6uqQSqUUFhaSmZm5bI6hZHEO9Wc5jy2l1+vR6XSEhoaSkJAgBGYul4vZ2VkmJyeRSCRoNJo152ZGREQQFRWF2+1mbm7umvs9Pj7O7Oys8Fwri04pFAri4uKIiorC4/EwNjaG2Wxmfn6e+vp6RkdHSUtLIzExkf7+ft555x3++Mc/8tJLL3H06FE6Ojowm82fS7Dq57+J8Gn5fD5mZma4cOECFy9eJDk5mYMHD5KamnrTw3FdLhf9/f0cO3YMgG3btpGenk7giu4fERERJCUlCaNFHA7HZ9qHO8FtM0d1aGiI2tpabDYbZWVllJSUIJPJGBoaYmhoCKVSSVZWFhEREbhcrlVzVFNTU2Fx4vjbb7/NqVOniI6O5sknn+TrX/86e/bsoaqqiqSkJObm5mhra8NoNJKQkEBiYuJXYkKySCQSfRV4vV4mJyc5ffo009PTVFdXs2HDhnXvoHs8HkZGRjh79iyNjY2cP3+eDz/8kN7eXvLz83nssceorKwUM6p3GH9GtaurC71ej9vtZnp6mt7e3lVBXGdnJ62trfT09DA1NcXs7Cx6vZ7Z2VmmpqY+14Dxekt3dzf9/f2MjY0xMTHxuT13T08PWq0Wm81GbGws+fn5JCYmfmWnHVmtVpqbm7l48SJKpZKamhoKCgqWFfnxLbauaW5uprOzk/T0dDZs2HDNIaO+xXnGvb29XLx4kYaGBmpra/nwww+ZmJigsrKS/fv3U1RUdM3CTHq9nvPnzzM4OCjMobzRYko+n4/W1lZqa2uJjIxk69atQnsdq9VKZ2cnp0+fxu12c//991NSUrLq/GgymWhra6Onp4fIyEjKy8vXrTR76dIlamtrUalU1NTUkJ+fvyoIt9lsXL58md7eXjQaDZs3b2Z+fp733nuPkZERNBoNLpeLy5cvC1n/K1eucPXqVaanpwkODiYmJgaFQrHuMbsZWq2Wuro69Ho9BQUFNz1H1V/h+Z133sFoNPLoo4+ya9cuvF4vJ06coLe3l02bNi2bo7oW3+JQ7LfffpsPPviAgoICnnrqKaE688p91Wq1XLhwgbCwMLZt27aq4OzdZu2j9iXyLRZBUqvVbNiwgU2bNuH1eqmtreXChQuYTKaVmwiMRiNXr16lqakJhULBvn37eOyxxygsLCQuLo60tDTuv/9+HnvsMZKTk+nv7xeGv4hzj0QikeiryePx0NfXxyuvvMK///u/8+tf/5oTJ04gk8nYvHkzpaWla2YcRLc/f4bK7XYzNTVFc3Mz9fX1q5bGxkZGRkZwuVzIZDIhe67X67l69Sp1dXWrtrkVy5UrV2hqaqKvr4+RkRHa2tpWrfNpl7a2NnQ6HW63+3PN3N2pXC4XVqsVh8OBVCpdcx6kRCIRCtnIZDIcDscNZbHsdjvNzc288sor/PKXv+T555/n0qVLhIaGsmnTJvLy8ggODr5l74FnsSWO1WpFqVQSEhIi7Jvb7cZiseB2u1EqlQQFBa3abwC5XI5CoRAC72tl4P3H0b/NWvsllUpRqVQEBARgtVpxuVxotVp0Oh02m42+vj46OztRqVRs375d6IRhMBh48803+cMf/nDbzMt0u9309/dz/PhxRkZG2Lx5Mzt37iQ0NPS6n42VXC4Xg4ODHDt2DJ/Pxz333CMM/V55HAMCAoSaOiaTiYWFhXXfk7vFbReosnhiUCgUpKamcs8991BcXIxWq+XEiRP09PTg8/lWvXn+uan9/f2YTCZyc3PZuHEjcXFxy9bzF86oqKjA6XTS2dnJxMQErmsUWBCJRCLR3UsikRAVFUVJSQmbN29m06ZN5Obm4vP5aG5u5vLly8zMzNz0BYjo9uDz+QgICCA6Opr8/HyKi4tXLYWFhaSkpBAcHIxcLheKnvgL45SUlKza5lYsRUVF5OfnC/MDc3JyVq3zaZecnBwiIyMJCAgQP8uL141utxuPx4NEIiEgIGDVtaXfev+/Fn9wm5CQQGlpKVVVVVRWVpKZmYnD4aCpqYnm5mb0ev0tS5I4nU4sFgtOpxOZTIZSqVxWlMnj8eDz+ZBKpdfcbz//52W9z41/XvXN3gAxGAyYzWYsFgsymYwtW7bwk5/8hH/4h3/gv//3/87f/u3f8sQTTxAWFsbJkyc5c+YMc3NzX2pw5lsc8usfgZOVlcWBAwdISUlZM+D3XWOIsc/nY35+ntraWrq7u8nIyGDbtm1ERUWteRz9n63AwECh8Nt6j323uO2G/joXm/oWFBQQHh5OcHAwdrudnp4eRkZGiIiIID8/n5GREc6fP094eDjV1dVoNBomJiY4ffo0Wq2W8vJy7r33XmJiYlY+HR6Ph+HhYa5cuYJEIqG8vHxZZS2RSCQS3bluduivVColKiqKDRs2sGXLFqqqqsjIyGBycpJz584xMDBAZGQkmZmZ67ZnEN1+/EN/Ozs7sdlsbNq0iYMHDwotI5YuhYWFxMTEIJfLCQkJISYmBo1Gw4YNG9i1axfV1dWUlZWt2u7zXsrKysjLyyMiIoLo6Gi2bt3Ktm3bVq33aRaNRoPJZMJgMBAeHv6VH/rrcDjo6uqiubkZpVLJhg0byMzMXHae8AcSFy9e5OrVq+Tm5rJ161ZiY2PXDEr8lhZG2rZtG1VVVSQkJKDVarl06RJTU1NER0cTHx+/ZuaMzzj012az0dTURENDgzDMNjY2FqlUisPhYGhoiLq6OtxuN1u3bhXa1iw1NzfHlStX6OnpITExkZqaGpKSktb8vDQ2NtLY2EhQUBCVlZVkZWWtOt8uLCxw9uxZOjs7yczM5J577qG/v1+Yt/vYY4/xta99jZycHJRKJXK5XDhGQ0ND9Pb2AlBZWUlcXNwNHYdr+bRDf61WK2fOnOHNN9/Ebrezb98+qqqqkEgk2O12ZmdnhY4lZWVl5OTkCNl6qVS67L12uVz09vbyhz/8gbGxMZ544gn27NmzrIjSUh6Ph6GhIaH41D333LNuheG7xWd7l28xqVQqnKhramowGAycOnVK6Ge19Mvt9Xqx2+1YrVa8Xi9BQUGrviR+/rY0CoUCt9v9uVQTE4lEItGdSSKRoFKpiImJITk5mfLycp544gl++MMfUlZWRltbG0ePHmVwcHDlpqLbmFQqJSgoSCiG4+9ZnpeXt2opLi7m/vvv55vf/CY//OEP+dGPfsT3vvc9Hn30USorK8nNzV21za1acnNzhYxqVlbWqr9/2iUnJ4fk5GTUajXBwcHLsmxfRQqFQmh94vF4sFgsq0bX+RaHvZpMJpxOJ0FBQahUquseN6lUSnBwMLGxsaSkpLBhwwaeeeYZnn32WdLT0+ns7KS2tpaJiYlbklUNCAgQRgaweI3sv86VyWSEhIQgk8mEgk8r95vF4cs2mw3JYr/ppcOHV/K3V3E6nava7rB4HN1uN2azGY/HQ2hoKAqFAu9ideuEhAShHdjSQFgmkxEbG0tBQQHBwcEMDQ1hNBq/1Gv2wcFBPv74Y1pbW5FIJBiNRj755BMOHz7Me++9x4cffihMI+js7OSjjz7izJkzjI+Pr3qvDQYD58+fp62tjYSEBPbs2bNuNtXPu1gNXCaT3VA2/E537W/abUCpVJKZmcnu3bspLi6mvb2do0ePotfrl32YJYvDNvxfIv9wjrX4vzBer5eAgABkMtld/0aLRCKR6MbJ5XKKioooKytDoVAwNjbGyMjIytVEtzGlUklaWhr33HMPu3btIjc3d1XWyE+62FM3OTmZnJwccnJyyMjIICoqat2L81vBf33iWmwps951zKcRHh5OWVkZ9913H5s3b0aj0XylRwgolUrCw8MJDQ3F4XBgMBhWdZfwLbYNmZubg8Vj+GnnlvqnnhUWFmK32+nr67tlLYL881KVSiUul2vZ/FKlUklkZCQhISFYrVb0ej12u33lQ2AymTAajUgXKx/7g9u1REZGEhoaitVqFQLfpcGkx+NhYWFBCDJjYmIICgoiLCxMKLq0XvAplUoJDQ1FJpNhtVpvyfG6GePj48zMzAAwMDDA888/zz/+4z/yP/7H/+B//s//yf/7f/+PtrY27HY7tbW1/PznP+d3v/sdnZ2dy+bXulwuRkdHOXv2LG63m927d5Obm3vNon0+nw+bzYbZbEalUhESEnLdmyZ3ujti71QqFaWlpezcuRO5XM6FCxdobm7G6/UKb5D/gxwdHY1MJmN6enrd3qsmk4mpqSk8Hg/R0dGEh4ev++UTiUQi0VeTf56iQqHAs9jPUnTnkMlkaDQadu/ezZNPPklZWdlX+rc+ODiYDRs2cOjQIXbu3ElcXNynCrjuFjKZjKioKGJiYrDZbExMTGAymZZdN7rdbmZmZpibmxOyo0szqr5rzD9cy9ICRa7Fnrk3s/2NCggIIDQ0lKCgoGXBI4v77R9hIJVKGR8fX9X6xev1Cu1tAgMDiYuLW1bFd+VrTk5OJjY2FovFwtjYGHNzc8tustjtdrRaLTMzMwQFBZGdnY1arSYhIYHw8HCMRiMzMzPY7fZVj+1Z7EHrdruJiooSRkv6b+o4HA6cTueqLO7naen7nJqayr59+/jWt77FX/zFX/Dkk0/y5JNP8tRTT/HUU0/x8MMPk5aWhkKhoLCwkAcffJBdu3aRnJy87Pyj1+u5dOkS7e3txMTEsHv3bkJDQ5c862oulwuz2YzdbicsLEzojXs3uyP2TiaTERcXxz333EN1dTUTExNcvnyZhYUF4YPj/+Klp6ejUqno6emhra2N+fn5ZR96h8PBwMAA7e3tKJVKcnNzSUhI+ErfVRSJRKKvIq/XK1SzXMntdjM5OcnIyAgWi4WwsDAiIiJWria6zUmlUpRKJSqVas1WD18lEokEmUyGSqX6yg/79YuLiyMjIwOfz0d/fz+jo6PYbDZYPD8sLCzQ3t7O5OQkGRkZZGVlERQUhG8x0zo9Pb2st6rH48HhcKzKKLIYZIyNjTE2NkZAQAAxMTGEhYXdkoy9RCJBrVYTFhaG2WxGr9cLgapEIiEiIoKioiLCwsLo6upiZGRkWbbPYDDQ29vLxMQEkZGRZGVlERwcjHexN/HU1BRTU1PCdDuNRkNmZiY+n4/e3l6GhoawWq1CgGcwGGhtbWVmZobk5GSys7MJCQkhMzOT1NRUrFYrXV1dDA8PLzsfu91uZmdn6evrw+FwUFBQQGRkJBKJBLPZTG9vL3V1dXR3d9+yCrhms5mJiQl0Oh12u53MzEy+9rWv8Vd/9Vf8zd/8DX/7t3/L3/3d3/F3f/d3/PVf/zU//vGPKS4uRqlUsm3bNn7yk5/w3HPPkZeXJ8QaLpeLkZERLl26hMfjYefOneTn518zm8piSxy9Xk/AYnG4T5vdv5PcVmcp/5d65ZebxaEK+fn57N27l6SkJCYmJoSKaf43KSIigsLCQtLT05menubjjz+mtrYWnU6H0Whkbm6OlpYWDh8+TEdHB/Hx8ZSXlxMXF3dLThQikUgk+nL4L5DW+j1h8e8Wi4XGxkbOnj3L2NgYer0eg8HAzMwMvb29HDlyhCtXrhAcHExBQQHp6ekrH0Z0h7jbL+ZEn058fDwVFRUkJyczMjLC6dOn6e7uxmAwMDU1xeXLlzl9+jR2u52KigoyMzNRKBQsLCxQW1vLv/3bv/HrX/+a+vp6jEYjs7OztLS0CO2OZmdnmZubY2ZmhtbWVj766CNaW1sJDw+nqKiI+Pj4dbP8S89h653HriUmJob4+HgWFhYYHx/HarXC4nchLCyM8sVCogMDA3z44Yd0dHQwNzfH3Nwcly5d4sKFC7jdboqKiigoKCAkJASLxUJ9fT0///nP+Zd/+Rfq6+uxWq2o1WqqqqrIyspicHCQ2tpaent7mZubY3JykqamJs6fP4/H42H79u1ChVyNRkNNTQ0ajYarV69y6tQpent7mZ2dZX5+nqGhIY4fP05TUxMhISFs27aN+Ph4pFIpXV1dvPDCC/z85z/n3Llzq7LhN+pax9jj8XDy5En+5V/+hV/96le0trbidrsJDg4mPDyciIiIZYt/KLk/plAoFELm09+2x+fzMTs7S1NTk5BNvffee4UA/Frm5uYYHh5GLpeTnJz8lUiy3VZVf8+dO4fL5aK8vFz4UvhJFksyBwcHs7CwQFdXFzabjeTkZKqrq0lNTRUKKHk8HsbHx+np6WFwcJCJiQnGxsa4dOkSb7/9NhcuXCA8PJyHHnqI++67b90GxiKRSCS683i9XiYmJjh16tS6VX+9Xi9TU1O8+OKLvPbaa3R0dNDT00NHRwe1tbV88MEHnDp1CrPZTHV1NYcOHaKwsFD8rRDdUr7F4j0zMzNYLBZhaKTo1pAt9sy1WCwMDAzQ19fH1NQUExMT1NXV8cEHH9Dd3c2GDRt44oknKCwsRKFQMD4+ztGjRzl8+DCDg4NERESQnJzM5OQkb775Ju+99x7Nzc309vbS3t7OuXPnOHz4MBcvXgRg+/btPPDAA2RmZq6bRVtZ9Xfjxo03XPWXxeG/w8PDdHR0EBISQmFhIVFRUUilUmQyGYGBgTidTvr7+2lvb0en0zE9Pb1sv/Pz8zlw4AAlJSUEBQUxOzvLBx98wNtvv01zczOxsbHk5uaiVqsJCQnBZDIxMDDAwMAAk5OTjI+PU1dXx5EjR4T9ePrpp4Xson+Istlspr+/n97eXrRaLePj43R2dnLs2DGOHj2K0Whk7969PPbYYyQkJCCVSjl37hzvv/8+c3NzlJeXU1paelMZRq1Wy5UrV5ZV/V0ad/hvZv7ud7/jgw8+oL+/n+TkZNLT09d9Hp/Ph9Fo5NSpU/T39wsVxtVqtfC+ud1u2tvbeffdd9FqtWzdupWDBw8SHR295mP6eb1e2tvb+fDDD5HL5Rw8eJCsrKx1b3TcLW6LQNXn86HT6ejr6xPmUOTk5BAUFLRsPYlEIkwO9w/pzc7OpqqqCo1GIwzviYqKIiwsTBgT39vbS0dHBx0dHej1etLT0zl48CD79u0jLS1t3ZOESCQSie48vsWhZl1dXQDU1NRQVFS07FzvWxy619HRQWdnJ6Ojo/T09NDe3k5nZyeTk5Oo1Wp27NjBoUOH2Lhx4w21LhCJPgsxUP1iSSQSITsmkUjQ6XT09/fT2dlJT08PZrOZsrIynn76aaqrqwkNDUUikbCwsEBHRwfd3d0olUpKS0vJy8vD5XLR09NDd3c3g4ODQqDa1dXFzMwMcXFx7Nmzh/3791NUVERISMi6wcnCwgK9vb1YLBbKysooKytbFvBcj0KhwGAw0NnZicViISUlhaSkJKFjRuBin2CZTMbk5CSDg4N0d3fT2dmJyWSiqKiIgwcPUlNTIwS4FouFrq4u2tvb8Xg8bN68mZKSEkJCQoTjCKDT6RgYGKCrq4uenh6sViulpaU88cQTVFVVCfstkUgIDQ0lKioKmUyGXq8Xtmtra2N4eJjAwEDuv/9+vva1rwkF0ex2OydPnuTixYukpqZy//33k5WVtW6xtLXo9XoGBwfx+XwUFxcLwfhSHo+HS5cu0dvbS0hICJs3byY3N5egoKB13zebzUZ7ezsmk4mqqiqKiooIDQ0V3jeLxUJrayv19fVERUWxf/9+ysvLrxuLGAwGzp49y4ULF8jPz+fgwYM3lIW9090WgSqLd7ViYmKExtSxsbGrUtqSxfkVarWapKQkCgoK2LhxI3l5eajVaqHqb2hoKElJSWRlZQml2MPDw8nMzGTHjh3s37+frVu3kpycfN0PhkgkEonuLJLFKvBRUVEUFxdTXl6+auSMRCJBoVAQHx9Pfn4+SUlJREVFER0dTWZmJlu2bOGhhx7i/vvvp7CwkLCwsLv+gkD05RMD1S/e0uvK5ORkYRhnZmYm9913H/v376eyslIIZv3bKBQKIiMjKS0tpbq6mrS0NMLDw9FoNGRlZZGUlERkZCRxcXFkZ2ezfft29u/fz44dO8jJybluxVapVIparSY/P18Ynrxez9W1SKX/f8/O0dFRhoaGhDmh/v0ICAggLCyM5ORk0tLSiIiIIDQ0VLhW3rdvHxs3blzWMka62BoyNDSUkpIS7rvvPlJTU4XsaHh4OMnJycJxVKvVZGVlcd999/Hggw8Kx3HpfgcEBBAREUFqaioZGRnExMQQGhpKQkIC5eXl7Nu3jz179pCXlyeMipmamuKjjz5iaGiILVu2sGPHDmJiYq55PFeSSqVERESQl5dHaWnpqno1EolEyD6r1Wo2btxIdXU1iYmJ15zvLpVKCQsLIzc3lw0bNgiJNP/6/gJa8fHx1NTU3FCm3Ov10tXVxdGjRzEYDOzdu5dNmzat24bzbiLxrTUo+wvk8/nwer04nU6cTicSiQSlUimM5V7J5/Ph8Xiw2+04nU7kcjmBgYHIVrSY8S1WA/PPGbDb7SiVSqKioggPD18VBItEIpHo7uHxeLDZbHg8HqFy73q/KU6nk7m5Oebn53E6nchkMsIXe2/ezIWhSPRZeb1ejEYjHR0d6HQ6KioqSEtLW7ma6Bbwer1YLBZmZ2cxm83I5XKioqJQq9Wrrhn9IzIMBoMQ8PizbF6vF5vNxvz8PEajEZfLhUKhEOYwLg1arsXr9WK323G73cjl8k9VAMtqtfLhhx/y6quvolKpeOqpp9i+ffuyG2++xZYnMzMzGI1G5HI50dHRwn6vvLb2r+vz+VZVA2bxdfvb3phMJhQKhXDtfa1hqj6fD7vdztzcHEajEa/XS2hoKJGRkQQHBy/b94sXL/Kzn/0Mk8nEc889x759+5bdSLgR/orBHo8HhUKx7vtiMpmYmZkRbkyoVKo11/Pzv28ul0uIZ5a+dn8M43a7hSHY15pS4vP5mJub4+233+bNN98kNTWVv/zLv6SgoOCax/Nu8aUHqi6XC4PBIHw5/B/Itd403+J48ZmZGVwuF2q1moiIiFVfJJFIJBJ9dfizUEvbIazF/zshk8mE3w3/zVK3243T6RTudkulUhQKBQqFgoCvQFN10e1BDFS/PP7zgMPhwO12I1kcxadUKlclQ26Wd7EisNvtxu12C+eX6z2uPznjWtJTV6FQ3NR1b19fH3/84x+5fPky1dXVPPPMM2RnZwtBjm+xVc7ShJF8sY3OzTyP/1zqWuwB7D+XBgQECI93I+dS/3HyLraglMvlywI9r9fLe++9x5/+9Cdyc3P52te+dkMVc5fyH1f/a5TJZNd9L26Ue7EPstfrRS6Xr3kMV/7mLN1XpVK57Di5XC6uXLnCb3/7W0ZHR3nmmWd4/PHHCQsLW/aYd6svPVC1WCw0NzdTW1tLQEAAVVVVlJaWrhrq4r/T0trayokTJ/D5fGzZsoWNGzdet++QSCQSie5OPp8Pq9VKa2srU1NTa97kZEmQqlQqSUpKIicnB5lMJgyzHBkZYXh4mPn5edxuN0FBQSQlJZGdnY1Go7nuXXSR6PMgBqpfDo/HI1SZ7evrQ6/XI5FIiIuLIzc3l7S0tOsO1V2Ld7EFltFoRKfTMTU1hV6vJzQ0lPz8/HWnoPkDvoWFBWZmZpiamkKn06FQKMjNzSU9PX3VfMr1TExM8NJLL/HRRx9RWlrKc889R2FhIXK5HI/Hg9lsZnBwkJ6eHnQ6HSy27cnJySEtLe2GW+hYrVZmZmYYHh5mbGwMg8GAx+MhKChIaEmTmJi45igVf5DrPx+PjY1hsViIiYkhJydnWX0Aj8fD5cuXaWlpIT8/n/Ly8hvOpvqfx2q1Mj09zdjYGB6Ph+TkZFJTU9d8L26Gy+USirna7XZycnJITU1d9vvhdDoxGAxotVqGh4fR6XQ4HA6USiUajYa8vDw0Gg1BQUFIpVKcTidnzpzhV7/6FSaTie9///vs3bv3K1Mz4UsPVK1WK2fPnuXXv/41Wq2WXbt28eyzz1JQULDsi+F2u9Fqtbz44ou8+OKLZGZm8oMf/IBdu3aJgapIJBJ9Rfl8PiYnJ/nlL39JXV3dunfFvV4vXq+X8PBw7r//fr7+9a8jl8sZGxvjvffeE9pJmM1mXC4XAQEBJCYmUl1dze7duykuLr7hC0OR6NMSA9UvnsfjWdaKpqOjA6PRCIttDysqKti7dy8VFRWEhYXdcLDqXuwB2tvbS0tLi9CXdHZ2luzsbA4dOkRNTc2qa1i3283CwgIDAwO0tLTQ3d3N2NgYOp2OhIQEDh48yM6dO4mKilq23VpcLheXL1/mpZdeQq/X89BDD7Fv3z5iY2PxLQ4pra+v59ixY7S1tbGwsIDH4yE8PJyKigruv/9+NmzYQFRU1DWDVa/XS0dHB6dPn6ahoYGRkRFMJhMulwuZTCZ06Ni9ezcFBQWrhgs7HA70ej19fX00NDTQ0tKC1Wpl8+bNPPPMM2g0GmFdn8+HyWTC4XAQHBxMYGDgDb8nNpuN6elpOjs7qa+vp6OjA4VCIRS4ivgMvbK9Xi/T09O8++67fPzxxywsLPDss8/y4IMPEhsbi1Qqxe12MzQ0xPnz56mrq2NgYACDwYDD4cDr9ZKQkEBVVRW7d++mtLRUyJqOjo7y0ksvcfr0aTZv3sx3vvMdocXP3e5LL6Ykk8mQSqWMj4/T1taG0WgUJmL7P8i+xSG/9fX1vPHGG0xOTrJz504efPDBm548LRKJRKK7i8lk4uLFi4yMjCwbXudfHA4HExMTQhXPvLw8qqqqABgYGOAPf/gDo6OjaDQacnJyiIuLw+Vy0dXVRUdHBz6fj/T09Ou2DxCJPiufWEzpC+Vb7Gl55swZXn31VZqamoiMjKSkpIS4uDimpqZobm7GYDCg0WiIjY1d92bYUk6nk9HRUU6ePMmf//xnPvnkEwYHB/F6vURERJCTk0NRUdGqAj4ul4vp6Wlqa2t56623OHLkCN3d3TidTsLCwsjKyqKoqEgorHQ9MzMzHD16lIaGBgoKCti3bx+pqalIpVIWFha4dOkSf/zjH7lw4QLR0dFC4bnJyUmuXr2KwWAgOjqauLi4az6fx+PhypUrfPTRR4yPjxMbG0tmZiZxcXE4HA56enro6upCIpGQnZ2NWq0WjqHP52N0dJRTp05x+PBhjh8/TmNjI2NjY0RGRlJdXU1kZKTwXJLFWjbBwcFrDqtdj8/no7e3lw8//JB3332X06dP09LSgsFgID09nfLy8k+dpfQHzxcuXOD555+nvr6evr4+ioqKKC4uFqo12+12Ll68yOuvv05nZ6dQbCopKQmpVMrAwAANDQ1YrVZSUlKIiopCLpcLx6urq4u+vj5SUlJIS0tb9tm5W33pgapEIhHS2729vYyMjKBQKEhPTxeCULfbzdjYGEeOHOHMmTOUlJTwF3/xFxQXF6O4Rilq32IDX/+ddJ/Ph2SxHPZ6/Nt4PJ4b3kYkEolEXx6ZTEZ0dDTFxcVs376dLVu2CEtNTQ0lJSU4nU4mJyfJyMjgwIED5OXlLbvJWVNTw6FDh3jwwQfZsmULWVlZmEwm+vr6MBgMJCcnrxrpI7r7+H///fMBv+gb4bciUP2y9+l25nK5aGlp4fXXX6e9vZ2SkhK+/e1v8/TTT7N582bCwsLo7++nubmZ0NBQcnNzr5tVdblcjI2N8f777/PCCy8wMDBAXl4eDzzwAA899BB79+6lpqZGGBLqfyy3241Op+OTTz7h97//Pa2trSQnJ3P//fezf/9+9u3bx7Zt28jOzl7W7mQ9Xq+XpqYmPvjgA1wuF7t27aKiooKQkBBcLhd9fX28+OKLnD9/nvLycr773e/yzDPPsGXLFkJDQxkZGaGnpweZTEZmZuZ1K9M6nU7UajVVVVXC692yZQupqalYLBZ6e3uZnJykrKyMlJSUZXNkGxsbee+99xgdHSUqKgqFQoHT6SQtLY3t27cvC1Q/LY/Hw9mzZzl8+DAmk4m4uDi8i3NDi4uLqays/NSBqtPppLu7mz/96U+0t7ejUqmw2+1UV1dTUVEhBKoej4exsTFsNhs1NTU89thjHDhwgHvvvZeioiLkcrnQ3shfBdk/5FyhUDA9PU1jYyNSqVR4L+/2+ORLD1RZvMhQKpUYjUa6u7sxGo0kJSWRkpKCSqXCZDJRV1fHu+++i9VqFS4mrvUGeRerbs3NzTE5Ocn09DRmsxnJ4uR46WLZ7qU8Hg8WiwW9Xs/ExAQzMzPY7fZl24hEIpHo9iFZLPzhn9uTnZ29bMnMzEQikdDQ0MD4+Dj33nsvBw8eFFokhIaGChcpiYmJhIaGEhERQUpKCl6vl97eXmZmZsjIyGDDhg2feQ6T6PblXaz6OjExIcxR/DSVVn0rZlStvNa4Ft9iFWqdTve5Bao2m42JiQl0Oh0+n08o1iL6/3tpfvLJJxw/fpyYmBi+9rWvsXPnTqKjowkLCyM+Pp75+XmamppwOBzC/MH1Mller5fZ2Vk+/vhj/vjHPzI/P8+BAwf4T//pP/Hggw9SUlIitG5Z+tny+XwsLCxw7tw5fv/73zM4OMjOnTv59re/zcGDB6moqCA1NZWoqKgbHupqs9k4ffo0586dIyMjg7179wrDRefn5zlz5gyHDx9GqVTy/e9/n/vvv5/w8HDUajXx8fEsLCzQ3t6O2WwmLS3tullcfzuwoqIiNBoNarVaaM/j8/m4evUqExMTVFRUkJubKzyW1+tlbm4OmUzGli1bqKqqwm63Mz4+TlJS0ucWqHq9XnQ6HaGhoezZs4eioiJmZmaYn5+noKDgUweq/uDznXfe4eOPP6awsJCIiAimp6fZtGkT5eXlQqDqv6laVlYm3HTwV4NOSUkhIyOD9vZ2enp6iI6OpqioiOjoaAICAoR4qLGxkfn5ecrKyla1XbsbXf+T/gWJjY1ly5Yt5OTkoNPpqKurY2RkBIfDwdTUFFeuXGF0dJRNmzaxe/fuZcMGVnK5XOh0Ourr63n99df513/9V/75n/+ZX/7yl3zwwQf09vZitVrxer3CNk6nk4mJCc6fP8+f/vQn/s//+T/87Gc/47e//S2nTp1ienpauBspEolEojuDzWbj8uXLNDc3k5iYyJYtW4iPjxf+LpVK1yyUJJFIUKvVwg1RqVS6KgAR3V1cLhcDAwO89957vPbaazQ2NmKxWFauti5/kGmxWDCZTJhMJqxWKy6Xa+Wq6/KP4PIvn5XX62V8fJwPPviAV155hcuXLwvzL0UwPj5OR0cHdrudzMxMCgsLhRsDAYu9mCsrK0lJSWFgYICenh6sVuu65wKbzUZHRwdHjx5Fp9Px8MMP873vfY+NGzcSHBy87nvqdDoZHBzk6NGjDA4OsmvXLn74wx9y7733EhERcUOB6Uo6nY6+vj68Xi+pqanExcWhUCjw+XwYDAZaW1uZn5+npKSEoqKiZcmf+Ph4iouL0Wg0zM7O0tPTg8lkWvkUAv8Nw7WSOnK5nNDQUFQqlVDBd+lx8Gc0n3nmGR577DGys7NvyQ1BmUxGdXU13/72t3nwwQdJSkr6XIK8hYUFLl++zEcffURkZCQHDhy45lzXiIgIkpKShHZGflKplJSUFIqKiggNDUWn07GwsCDEKjKZDI1GQ0ZGBjqdjvb2dhwOx5JHvjvd/Cf/FlEoFOTk5LBjxw4iIiJob2+nvb2dqakprl69Sn19vVAEIycnZ90Pl3/IxeHDh/nf//t/8+///u9cvHiR9vZ23n//ff7pn/6JX/ziFzQ3N2Oz2YQhMWNjY7z55pv8r//1v/jVr37FuXPnuHTpEq+++iovvPAC7e3tN/VjIxKJRKIvl8fjYWRkhHPnzjE9PU1xcTGlpaXCkLP1uFwu5ubm6OrqEgqYZGZmEhISsnJV0V3E4XAwNjZGR0cH7e3tDA0NMTc3h81mw2q1XncxGAz09fVx6dIlzpw5w7lz57h8+TJDQ0NYLJZV66+3+HssejwenE7nqr/fzGIymdBqtcI+jYyMYLFY1g20vkq8Xi96vZ6pqSlUKhWpqamrkiABAQHExsYSFRWFTqdDq9VisViWJTr8fIvFiS5evEhvby+lpaXs37+fyMhIRkdH6evrY2RkhNnZWex2u/Ae+Hw+jEYjDQ0NtLa2kpSUxKFDh0hJSWFiYoLe3l6Gh4eZmZnBZrOt+dxrmZycZHR0lODgYKFyOYtDjOfm5hgYGMDhcKy531KplJiYGGGO6dTUFNZrBOhr8S22vZmZmaGnp4e5uTk0Gg2ZmZnLCtNJJBJUKhWhoaEoFvtd38zz3Izg4GBCQkKQy+X4Fqf6fRZOp5Ouri7ef/99TCYTBw8eZNOmTchksht+n5aSLBnBudboz+joaNLT07HZbAwODuJ0Opdtfze6LYb++snlcgICAoSSzTKZDIVCQV1dHU1NTWzfvp3HH3+cuLi4lZvC4klncnKSo0eP8uqrrzI3N8cDDzzAt7/9bQ4cOEB6ejrT09M0NzcLY98jIyMxmUycPXuWN954g+npaXbu3Mmzzz7L7t27ycrKIisri/LycmJiYtYNkEUikUh0e7FarRw5coSPP/6Y6OhoDh06xObNm1fd8fctaTQ/Pz/PwMAAx48f57333sNsNrN371727t17Q1U2RXcuu93OyMgIfX19mEwmoX2HTqdjaGiI4eHhay6dnZ2cPn2aTz75hMuXL9PU1CRU77XZbMK1zbWWkZERBgcHhQqxZrNZaPlxs4v/sbq6uhgaGsK3WBQsNzd3VWDyVWS322lpaeHcuXMEBARQU1NDcXHxshtSPp8Ps9lMU1MTXV1dZGdns3HjxjWznA6Hg97eXo4cOcLIyAj33HMPkZGRnDp1infeeUcoajQ5OQmLQZNSqcTr9TI6OsrRo0fp7OykpqaG5ORkLl26xNtvv82RI0e4dOkSo6OjeDyeG650e/XqVc6ePUtISAhbt24lKysLpVKJw+Ggq6uLTz75BJvNxq5duygvL19V1dxoNNLe3k5/fz8xMTFs2LDhugVMvYutX4xGo1DF98SJExw7dgyARx55hJ07d15zOPvMzAyNjY0MDAx8rkN/V9JqtdTV1aHX6z/V0F+Px8Pg4CBvvfUW586dY+PGjTz33HOEhYVx8uRJent7Vw39vRbfYmGvd999l46ODqqqqti6datQMdi/zujoKBcvXiQqKort27dfcxrk3eC2ClSli81u7XY7AwMDDAwMMDY2xtDQEBERETzxxBNUVlauGyz6e7K+9957zMzM8PDDD/Pcc89RXl5OcnIy+fn5qNVq2tvbmZycJCEhgZSUFEwmE6dPn6atrY38/Hyee+45du/eTW5uLhs2bKCiokIYMiESiUSi25/H42FgYIBXXnmF7u5u7r33Xvbv309sbOzKVfF4PLS1tfHKK69w7NgxDh8+zIcffkhAQACPPvoohw4dIisr67oXGqI7m8PhQKvV0tvby/T0tNDGoqGhgcbGxusuV69eZXR0FLPZjNPpFLKh4+PjXL169YYfp6Wlhf7+frRaLV1dXav+fqNLQ0MDzc3N9PX1YTQaUalUZGRkiIHqIovFQlNTE5cuXSIwMJCamhpyc3OXtU5ZGqh2dnaSlpZGZWXlmokL//zBkydPYjAYUCgUNDQ00NDQwPz8PHq9nq6uLhoaGhgdHUWlUhEXF4dksZrrxx9/zMjICEFBQVy9epXLly+j1+uZm5ujv7+fhoYGent7kclkxMbGXrOvq9frpbm5mfPnzxMdHc2WLVtITk5GLpdjsVjo6OigtrYWgF27dlFYWLhquK3JZOLq1at0dXURGRlJRUUFiYmJ1xyRYrVauXLlCh988AFHjhzh8OHDnDlzBrlczsGDBzl06BAajWbd180dEqj6g8rjx49z5MgRYmNjhf60NpvtUwWqbrebhoYGXnvtNSwWCw8//DCVlZWEhoYK31Wfz8fIyAgXLlwgJCSELVu2rHnT5G5yW+2ZRCIhPDyc8vJyiouLmZ+fp7a2loWFBbZt20ZlZeW6waJ/6ERXVxcTExOkp6dTXV1NQkKC8PegoCDy8/MpLCzEZDIxODiIyWTCs6SdgcPhwGq14vF4UCgUhIWFERYWtu7zikQikej2Y7fbqa2tpaOjg4SEBKqrq0lNTV25GiwpslFXV8elS5fo7+/HZDIhlUqFgidut3vlZqK7nGRxbvLNLGsFf5LF+aYr173e8mm3W+sx1npdX3Vut1sYZh0QEIBCoVgVfLI4/Nc/t9LlcuFyudYcMupwOJidnWV+fp6FhQWGh4dJTk7mO9/5Dn/zN3/D3/7t3/L000+TkJBAY2Mjhw8f5urVqxiNRubn55mdncVsNjMwMEBERATPPvssf/3Xf83f//3f861vfYvs7Gy6u7t5//33aWhoYGFhYeVLEDidTsxmM3a7XWjl4t83j8eD3W7H4/Egl8vXLa4VEBAg/L/b7cblcl13OKvL5WJ8fJympiauXLlCf3+/MM9SLpfjXezCcaez2+00NjbyySefAPDggw9SUVGxqt7BjX7vPB4P09PTvP/++4yNjVFZWUlpaemqG0pSqZSgoCCCg4OFufB3w/G8ltsqo8qSrKrZbKavrw+dTkdRURGPPPIIxcXFSNe5a+CfZ3rmzBk6OzuJjo4mOTkZi8XC6OgoWq2W8fFxYf7J4OAgcXFxFBcXEx4eztzcHL29vQwMDDA/Py98gf3Les8rEolEotuL1+tlaGiIV199dVk2NSEhYd0LB4VCQVJSEpWVlZSUlBAeHs709DS9vb0YjUaio6OXDcES3X0cDofQksPpdFJYWMh9991HdXU1paWllJWVXXPxD610uVzIZDJUKhVRUVGUl5eza9cuNmzYsGqbtZb8/Hyio6OJiYmhqqqKmpqaVevcyFJeXk5RURHh4eEYjUa8i0V1cnJyVl0AfxVZrVba29tpamoiKCiIjRs3kpmZuayyrT8JcvnyZa5evUpWVhbV1dXExcWtyiz6qwM3NDTg8XjYvXs3zz77rDDsNjMzk4yMDCQSCUNDQ+j1emJiYkhISECr1XLhwgUhMfPNb36T++67j+zsbDIyMsjOziYwMBCtVsvk5CQhISFCxdi1zkn+QOrKlStoNBrhNUulUmw2G319fdTV1eHz+di6dSs5OTmrEjLz8/M0NDTQ1dVFXFwcmzdvJjk5edV+LyVZnG+akpJCWVkZBQUFhISECH2sTSYTSUlJ675u7oCMqsfjoauri3feeYeuri5qamp45JFHhOrGZrOZU6dOCRnVkpISoZ3QWt8572LV4/fff5+XX36ZoKAgnnnmGaqrq4Xq9EvXHRkZ4dKlS0gkErZt24ZGo1nzRsPd4rYLVP1voslkoquri5mZGeEkv97cVBbv9gwNDXH27Fk6OjqYn59Hq9XS0NBAXV0ddXV1XL58mYaGBvr7+3E6naSnp1NWVoZGoyE4OBiXy8XExAR9fX10dHTQ09ODxWIhJCSEkJAQAgIC1vyQiUQikej2YbPZ+OSTT/jggw8ICQnh8ccfZ/PmzauGtvlJpVKCg4NJSUkhOzubvLw8cnJykEqldHZ20tXVhUqlEvoXiu5OTqeT8fFxent78Xg8lJeXs337dgoLC0lLS7vukpKSQmxsLPHx8WRkZJCfn09xcTFVVVVUVFSQnp6+apuVS2pqKgkJCQQEBBAUFER5eTklJSWr1rvRJTk5GYCRkRFsNpswR/VacwS/Kvy9RFtaWpDJZJSVlZGZmbls6K8/iKitreXq1asUFxezbds2oWXIUkajkaamJtra2oiJieGZZ55h+/btqNVqFAoFSqUStVqNz+djeHiY0dFRIiIiyMzMZGZmhoaGBhQKBU8++ST3338/0dHRKJVKlEoloaGhyGQyxsbG6O3tRaFQUFhYuO5QXKfTSUtLC01NTSQmJlJVVSXcaHO5XIyOjnLp0iXsdjubN28mLy9v1flxZmaG+vp6ent7SUlJYevWrdcNigICAlCr1SQnJ5OVlUVeXp4QnLe2tgrDiLOystYNCm/3QFWn03HkyBGOHj1KQEAAlZWVREZGCu0wh4aGqK2tZXh4mNTUVMLDw/F6vcJnYGkc4V1sZ3Ty5El+//vfo9PpeOyxx3j44YdJSkpCvqINksfjYWhoiPPnzyOTydixY8d135M73dq3M75k0sXGtgqFQiiotPILtJLX6xWG7vqH+arVaiIiIpYtcXFxlJSUsHPnTioqKoiMjCQwMJCMjAwOHjzIc889x5YtWwC4fPkyf/jDH3jttdfo6+sTq/6KRCLRbc7r9TI2Nsbp06eZnZ0VMqTXuwDxT/UIDw8nLi6OoqIioe+hTqejsbGR0dHRlZuJ7iIKhYLY2FgyMzPJzs4mJSVF6KepVquvu8TExFBcXMx9993H3r172bNnD/feey95eXmEh4ff8OOEhISgUqlQKpWEhISs+vvNLBEREWg0GrKzs8nKyiIhIWFZIPZVFhgYiFqtJigoCLfbjdlsXnWd5/P5sNlsLCws4PF4CAkJISgoaN1soH9UYEREBPHx8auOtVwuJyYmhtjYWLxeLwaDAafTSUBAADKZjNDQUOLj41cVNpJKpcKoDn/wbDab8azTNlEmkxEYGChUn106bFcul6NWq1EqldhsNoxG46r9ZvGGn8ViEW7kLR0+vB6JRIJCoSAkJITw8HDi4+OpqKhg3759FBcXMzc3x/nz55mZmVlz+PSdYGhoiJaWFiYnJ5mamuLo0aP87Gc/4x//8R/5p3/6J37+859z9epVYfrJL3/5S1544QW6urqWVen1eDzMzs5y7tw5XnnlFUZHR9mzZw+PPfYYaWlpq4JUllRSdjqdawa+d6O1v2m3Af8H2LdYPvp6H2j/ySEwMJCwsDBKS0t5+umn+cEPfrBq+fGPf8z3v/999uzZQ3x8PDKZjKCgIHJycti/fz8/+MEP+O53v8uWLVuYnZ3l/fffp7a2Vhg6IxKJRKLbk8PhoL6+nubmZsLDw6muriYlJeWmf8z9Q4FTUlKQy+XMzs6i1+tXria6iygUCtLS0ti5cyd79+6lqKjoujc4lgoICCA4OJiYmBji4+OJj48nOjp6VbByLf7rHe/iXL7rXftcj1QqJSEhgR07dvDQQw9RVlYmjgpYJJfLCQ8PJzw8HLvdjk6nw2q1LlvH6/ViNBqZm5tDpVIRGxu7bqAqX+wXqlAohPZAa10zSlb0ypXL5YSEhKBQKLDb7dfcTrpi/vF65HK5UB14ae0VFj/nkZGRREVF4XK5hNYzS/l8Pubn55mbm0MmkxEVFUXwNfrArkcikRAYGEhiYiIpKSnIZDJGRkYwm80rV/3UbjRO+LxIJBIhAPcPmbbb7dhsNhwOhzD/1+fzCQk0p9O57KaCx+NBr9dz7tw5XnvtNXp7e9m+fTvf/OY3KSoqIjAwcM1j7fV6sdls2Gw2goKC7vqKv9zOgerN8g83iIuLIzg4GKlUKnyQNm3atGopLy8nLS1t2RfPX0ltw4YN7N+/nyeffJKioiJGRkZoaWnBYDCsefIQiUQi0ZfP6/UyMzPD8ePH0ev1QkGKa12Y+wOClXw+Hw6HQxilI5VKr5tNEN3ZpFIp4eHhFBYWUl5eTmJi4ppZjVvt87zglkgkqNVq8vPzqaioICUlZdkczK8y6WKv0ISEBGF+sl6vF7KLvsW2VSMjI+h0OhITE0lLSxOynS6XS+iP63a7USqVJCQkoFar0ev1DA8PrwrIvF4vCwsLzM/PI5fLhYx9TEwMMTExWCwWhoeHMRqNyz4HvsW5sgaDAblcTmxsLGq1es1hvyxeE4eFhQlFd+bn54X9kkqlREREkJWVhUKhYHBwEL1evyyQstvtjI2NCfNhk5OThf12u91YLBYsFsuyInPrnUu9Xi9Op1M4l8pkss8luHK5XBiNRnQ6nbB/n+d3x8/lcmE2m4X3OS0tjUceeYQf/vCH/OVf/qWw/Of//J/5y7/8S771rW8JQ6n9LWueeuopsrOzkS+2vJqZmaG2tpY33niDrq4uNm3axLe+9S0qKysJCgpa9/g4HA5hX8PDw4W5r3ez23rvbuYDJ5VKiYqKIjs7m7CwMLq6urh06RJarRabzSaUivffWbLZbMvueFgsFqFCmsfjISgoiMTERKKjo/F4PDgcDtxu9029JpFIJBJ9cVwul1BtUq1Ws3XrVlJSUtYNMF2LzejHx8exWCzLfieMRiMdHR10d3fjdrtJSEhYs7WN6O4iXZx65B82eTeQLA7HDAwMXPe78FUVFxdHfn4+KpWK/v5+2tramJmZEVoLjY6OUl9fj06nIy8vTyhq5HK5GB4e5ty5c1y4cIGxsTHkcrlQ+MjtdgvzO61WqzBcc2Zmho6ODoaGhggNDSUzM5OYmBg0Gg35+fkEBgbS2NhIZ2cnJpMJp9OJy+Vifn6e7u5u+vv7CQoKIjs7m9jY2Gt+RiMjI4mMjMRkMjE9PY3D4YAlHTZKSkqIjo6mu7ublpYW9Hq9cP7zD2+dnZ1Fo9GQk5NDSEgIbreb8fFxzpw5w6lTp5iYmBCyhnq9Hr1ej9lsFrKIjsVKyJ2dnfT09OD1eoViXp/VxMQEx48f56233uLKlSurgvubsd52Pp+PoaEhTpw4wYULF5iamiIyMpLKykp27drF7t272bNnDw888AB79uzh/vvv59577xVucmVlZbF9+3aqqqqIj4+HxTm4/kxqc3Mz+fn5PPHEE5SUlOD1eoWbAP7PzdLXZjQamZiYEJJxK6sM341uu2JKLN6tmZiYoKGhgbGxMXJycti0adM1m61LJBLhCzs1NUVPTw+Tk5M4nU68Xi9msxm9Xs/4+DgDAwPCMA6FQsH8/Dzt7e309PQwPz+P2WxmcnKS5uZmamtrsdvt7Nixg+rqasLCwu76uxcikUh0p/Hfpf7Nb35Dc3MzNTU1PProo6SkpKx5zvYuzg87ceIE586dE+6az83NMTExQVNTk9AGIjo6mn379rF9+/ZVc8dEos+TP5M/MzODxWIhISFBLHx0CymVStxuN2NjYwwNDWEymYSMs7+TxPHjx5FIJDz88MNs3bqV0NBQ5ubmOHHiBG+88Qbt7e1C1lGtVmO32xkeHmZwcBCPx4NSqcThcDA9PU1dXZ3QL7WoqIjdu3eTlZWFSqXC4/EIfXwdDodQQVqv19PS0sLHH39MZ2cn6enp7N69m8LCwmsOK3e5XPT09DAwMEBsbCyFhYWoF6s9y2QypFIpo6OjdHd3YzKZhHPb5OQkJ06c4OTJk0gkEnbu3Mk999xDdHQ0CwsLnD17lpdeeomLFy8SFRVFcnIyc3NznDlzhra2NgwGg3AuHR8fp6GhgSNHjtDc3ExMTAyHDh2ioqJi3XOpvyZAf38/Go2G7du3r3n9X1dXx4svvsilS5eIiooiLy9vWc/R6/EXU5qZmaGgoIANGzYQEhKybB2n08nbb78t9OP2Z+BVKtWyYdj+hcX+vP6qv/5Cav4qx/45qa+99hoXLlwgKCiIzZs3k5iYyNTUFMPDw8Ki1WqFeeoBAQH4fD4GBgY4duwYRqOR3bt3U1JSguIub5952waqk5OTtLS0MD09TW5uLps2bbpu1S+ZTCYUIfC3t+ns7GRgYIDu7m6am5upq6ujoaEBk8mERqNBrVYzNTXFxx9/zLFjx4TmxleuXBHunlRWVnLgwAGys7NRKBQ3/CUQiUQi0RfD6XTS0NDA888/j1Kp5JlnnmHz5s2rLjz8vF4vU1NTvPnmm7z99ttCW5LW1lbq6uo4deoUbW1thIeHs2/fPvbv3/+p5rqKRDdDDFS/WP7qyhKJhImJCfr7+xkZGWFwcFC4DnQ4HDzwwAM8/PDDQnuWiYkJPvnkE06cOIFerxcyorGxsYSGhuLxeBgeHqarq4vh4WH6+vpoaGjgzJkzjIyMkJuby4MPPsimTZtQL1YF9k9RmJiYoL29naGhIQYGBmhqauL06dN0d3eTmJjI3r172bJlCzExMWvehPNTKBRMTEzQ1taGTCYjLy9PyMJKF/txKpVKZmZmaG9vR6vVMjIyQl1dHefPn8dqtbJ9+3YefPBBYZjw7Owsn3zyCceOHaO/v5/09HSKiorQ6XS8++67nDhxgs7OTrq7u7l69SqXL18W2kbGxsby4IMP8tBDD12zVZher6e1tZWRkRFSU1PZtm3bqut/r9fL6dOnOX78OHK5nK1bt1JcXLxu8LsWf7/X+fl5CgsL2bBhw7I56b7FQlovv/wyZ8+eZWZmhtzcXCG7vNbr9/l8LCwscO7cOYaGhoSphmq1GqlUSkdHB2+++SZnz57FbrcTFBSEw+Ggra2N+vp6rly5Iiytra0kJCSQnJyMQqEQfuOOHTtGVFQUjz76KElJSXf9KInbMlD1p75nZ2eRy+UUFxdTVFREWFjYylVXUSqVxMbGCi1nrFYr09PTwlj7+fl5lEolubm55OfnEx4ejtPpZGpqipGREUZHRxkdHWVmZobAwECqqqp45JFH2LhxIyEhIdc8KYhEIpHoy2G326mrq0Or1bJp0yYeeeSRa5btXzrtw2q1MjMzw9jYGKOjo+h0OiQSCcXFxTz88MMcOHBAaFcjEt1KYqD6xQsKCiI2NpawsDAcDgcTExMMDw+j1+uJiopi9+7dPPbYY+Tm5grZK3/xJbPZjEajYePGjeTl5REWFkZYWJjwvplMJkZHRxkcHGRiYgKZTEZlZSUPP/ywEGwGBAQIgWNiYiKRkZHYbDbGx8cZGhpCq9XidrspKiriwIEDQkuSaw37ZTFQtVgs9PT0oNfriY+PJzU1VajNolAoiIuLIyIiArvdLuz39PQ0UVFR7Ny5kwMHDggBoEQiwel0otPpMBgMREdHc88991BYWIhMJhOqI/vPpVqtlpmZGeRyOSUlJcK51F9UaT1WqxWdTofX6yUvL4+KiopV1/8mk4njx4/T3NxMaWkpu3fvvu7jrrSwsMD09DQqlYqSkhIKCgpWzd/2er0MDAxgsViEFj3+DPhagSqL80i1Wi0ej0do/eMPbIeGhujr6xOG7qrVaryLVZndbrew+If8lpeXk5GRgVKpFDLdV69epaqqir17995UBvlOJfGtNzD7S+T1ejGZTExMTLCwsEBUVBQajeaaQxxW8ng8GAwGRkZGmJ6exm63I1lsROwfqhAdHY1MJsPtdmMwGBgbG0On02Gz2ZAuTjZPS0sjMTFx3YsdkUgkEn35nE4n3d3dzMzMEBcXR1ZW1qqLjpX8d8wHBwcZGxtjYWEBl8uFTCYjLCyM1NRUUlJS1s3KikSfN+9ildmOjg50Oh0VFRWkpaWtXE10C5jNZkZGRhgeHmZhYQG5XE58fDy5ublER0cvCwicTidjY2MMDg4ik8nIyMggISFBKL7l8/mwWCwMDAwIVW4DAgKIjIwkIyMDjUaz5vnJf6PCn9Wdn58HIDw8nPT0dKGo0Y0GJ1NTU7z44ot8+OGHlJWV8dxzz1FQULDsdTqdTgYHBxkYGMBkMhEQEEBCQoIwf3ZpQTHXYpXg7u5uvF4vRUVFxMXFIZPJMBqNjI6OMjk5KbS8kclkqNVqUlJSSEtLu6HreKvVyvj4OLOzs4SHh5Oamrpqu+7ubv75n/+ZpqYmnn76aZ555hkSExNv6mai0WhEq9VisViIi4sjMTFxzWG0/f399PT0EBQUJGSl14sJ/O/f0NAQOp2O5ORkEhIShCq+MzMzjI6OsrCwcM330Ov1EhAQQGZmJnFxcXi9Xs6dO8dvf/tbFhYW+PGPf8yuXbtWHZe70W0ZqIpEIpFIJBJ91YiBqujz5PP5OH/+PM8//zxzc3M8/vjj7Nu3b1Xgfac5duwYP/vZzwgLC+M73/kO27dvv6lWUncarVbLiy++yLFjx9i6dSs/+tGPSEhIuKnA/E519++hSCQSiUQikUj0FSORSCgqKmLXrl1ERkYyMjLC7Ows3jXayNwpPB4PRqORyMhItm7dKlRLvlt5PB5GR0cZGxsjLy+PvXv3Eh0d/ZUIUhEzqiKRSCQSiUS3BzGjKvq8+Xw+oRuG2+0mJydn2TDlO43L5aKrqwu9Xk9qaipJSUkolcqVq901XC4X/f39DA0NERUVRWFhoTDP+KtADFRFIpFIJBKJbgNioCq6FfwFe1jskCGVSu/YQMdfCM/r9d7x+3Ij/Pvr8XiQSqXI5fK7en9X+mrkjUUikUgkEolEoq8gqVSKUqlEqVQSEBBwRwc6EokEuVx+V+zLjfDvb2Bg4FeyRaYYqIpEIpFIJBKJRCKR6LYiBqqfE6/Xi9PpxOl04vF4Vv5ZJBKJRCKRSCQSiUQ36JYFqv7x8A6HQ2hcux7/+GuHw4HT6VxVjczr9Qrjs29Hbrebubk5uru7aWtrY2Zm5rZ9rSKRSCQSiUQikUh0u7slgarP58NqtTI8PEx7ezsjIyPYbLaVqwlcLhfT09O0t7fT09PD/Pw8Xq9XaJw7NTVFf38/09PTuN3ulZt/6RwOB319fbz55pu88MILtLS0CJPWRSKRSCQSiUQikUh0c25JoOr1etHpdJw6dYrXXnuN8+fPMzc3t3I1gc1mo7m5mVdffZX33nuPoaEhXC4XbrebyclJTpw4wQsvvMCJEyeu+TjX4vV6cTgcmM1mbDbbqqztZ+F2u5mamqK+vp7a2lqGh4fFjKpIJBKJRCKRSCQSfUq3LFA1Go20tLRw9uxZ2tvbWVhYWLmawG6309/fz8mTJzl//jyTk5O43W4hADx//jwffPABdXV1zM7Ortz8uvwZ3u7ubk6fPk17ezsOh2Plap+az+cThic7HA7cbvc1hzqLRCKRSCQSiUQikWh9tyRQBfB4PDgcDmw225rzTpfy+Xy4XC6sVit2u13IRkqlUlQqFQkJCWRkZKDRaAgMDFy5+XV5vV4mJyc5evQof/jDH7h06RJWq3Xlap+ZRCK56/s5iUQikUgkEolEItGtdssC1ZVB2/WCN//6/m38fYNSU1PZv38/3/ve93jwwQeJj49ftp3P58Pj8eB0OnE4HELxJn9g7C/UNDk5yaVLl6ivr2dyclLIfHo8njWzn0szpP4iT/4Gw5/F0iJT/sdd7zUs5d/Ppdv6X4//bx6PR/j30gJU6z22f7vrrScSiUQikUgkEolEX6RbFqh+HiQSCSqVipSUFEpKStBoNMjlcuHvPp8Pm83GxMQEnZ2dNDY20traysDAAAaDAZfLhd1uR6fTMTExgdlsxuPxsLCwgFarZXR0FJ1Oh81mE4I0f3Z3fn6ewcFBWltbaWhooLW1leHhYYxG43WrGK/F6/UKr6Wnp4fm5maampro7OxkfHwcq9W6bhDs8/mEbbu7u2lubqa1tZXBwUEWFhaw2WzMzMwwPj6O2WzG6XQyNzfH2NgY09PTy/Zv6WM6nU5mZmYYHh5Gr9fjdDpXrScSiUQikUgkEolEX7SAn/70pz9d+Z+fldfrZXp6moaGBsbHx8nIyGDDhg3ExsauXBUAs9nM1atXaW5uJjQ0lM2bN5ORkYFUKkWn03HhwgXOnz+Py+UiLi6OwMBAfD4fCwsLtLe3c+LECT766CPOnj1LY2MjIyMjSKVSwsPDmZub4+zZs5w4cYKOjg7m5+eRSCQYDAZ6e3uZn58nPDyc0NBQpFKpUK344sWLHDt2jGPHjnHhwgUaGxsZHh7G4XAQGBhIUFAQMpkMiUSC3W5naGiIhoYGTCYTmzZtoqysDIVCAYvHY35+nq6uLs6cOcOxY8c4deoUly5doq2tjcnJSbxeL8HBwahUKqTS/7h/4N/Prq4uTp8+zUcffcTp06dpaGhgdHQUt9uN1Wqlrq6OlpYW4TGuXr3KqVOn0Gq1BAUFERYWtizI93g8TE1NcerUKWpra/F6vcKxvV72WyQSiUQi0efPt9jtYGZmBovFQkJCAuHh4StXE4lEoq+ELyRQTU1NpaysjKioKLxe76rFbDbT1tZGU1PTskAVYHBwkNdee413330XlUpFSUkJ4eHh2O12rly5wh/+8AeOHDnC2NgYdrsdvV7P+Pi4MGx4fn6eI0eOcOrUKXQ6HQ6HA4vFwtjYGMPDwwBkZmYSFxeHw+Ggo6ODt956i1dffZXGxkYsFgsOh4PR0VEaGhro7OzE6XQSHR1NeHg4MpnsuoGqwWDg/PnzvPjii7z//vv09/djs9kwmUz09fVx5coV+vv7USqVJCYmEhwcLASLZrOZ+vp6XnnlFd599116enqwWq2YTCYGBwfp6emhr6+PTz75hKtXr5KVlUVKSgpNTU28/vrrtLa2EhYWRlpaGqGhocJ7ZLPZaGho4Pnnn+fcuXOkpKRQWFhISEiIGKiKRCKRSPQlEANVkUgk+g+3PFAdGhpCpVKhVqsxm82MjY2tWgYHB2loaKC7u5uIiAghUJVIJExMTHD+/Hm6urrIycmhurqa8PBwxsbGeOONN/jwww/RaDR84xvf4Nlnn2Xr1q1kZGSQmZlJRkYGwcHBKBQKZDIZc3Nz2O12ysvL2bt3L5s2baK8vJzc3FxUKhUDAwO8/vrrvPPOO3g8Hh588EG+853v8Oijj1JcXIzb7aatrY3e3l4UCgXJycmo1WqcTue6gardbufixYv89re/5eLFi2g0Gg4dOsQ3vvENdu/eTUpKCnq9nqamJoaGhoiPjycjIwOZTIbb7aa5uZk//vGPnDx5krCwMA4cOMA3v/lN9u3bR0JCAkNDQ1y+fJmBgQFCQkKoqamhpKQEm81Ge3s7AwMDBAUFUVBQQGxsLBKJRMjwnjx5kk8++YTY2FgefPBBCgoKUCgUYqAqEolEItGXQAxURSKR6D/c0kC1sbGRjo4OhoaGaGlp4dSpU8Jw2qXLqVOnaG5uxmg0kpSUtGzo7/T0NHV1dQwPD1NSUkJ1dTVqtZq+vj6OHDmCxWJh//79PPbYYxQUFJCenk5hYSHZ2dmEh4ejVqvJyMggNDSUzs5ODAYDe/fu5fvf/z733nsveXl5qNVqZmdnOXXqFO+//z5ut5uvf/3rfPe736W0tJSEhARycnJIT0/HbDbT2dmJyWQiKSkJjUYDsG6gOjg4yBtvvMHZs2fJzs7mu9/9Lo8++ij5+fmkpKSQm5tLXFwck5OTtLa2IpVKyc/PJzo6mpmZGY4cOcLHH39MeHg4X//613n66acpKysjOTmZnJwcYmJiGBoaYmBggNjYWLZu3UpeXh5yuVyYu+t2u8nKyiI5ORmlUonb7Uar1fL+++/T1tbGvffey4MPPkhcXBwBAQEr306RSCQSiURfADFQFYlEov9wS4spLS1Q5K8uu3LxV6u92SI+/irB/hO6TqfDYrEgkUgIDAxEqVQKVYTlcjkKhUKoKCyTyVAqlSiVSuRyOV6vl6mpKVpaWjAYDGzYsIH77rsPjUZDQEAAUqkUhUJBdnY299xzD0lJSUxPT9Pd3Y3BYFj50gRut5uBgQGuXr1KUFAQW7duZdOmTURHRxMQEEBAQABhYWGUlZWxfft2oqOjuXr1Ku3t7Xg8HsbGxmhvb8fpdFJWVsaWLVtITExEJpMREBBAaGgopaWlVFdXExMTs+wYxsbGCgWoZmdn6ezsRK/XCz+Cw8PDDA8PExUVJQTjYpAqEolEIpFIJBKJbge3NFAFCA4OZtOmTXzve9/jH/7hH1Ytf//3f89/+S//hV27dqFWq/H5fNcNWqVSKfHx8RQVFSGRSDh16hR/+tOf+Oijj4Tg0e12L9vG/7hrPb7L5WJmZgatVovX6xV6ti4tagQQFBRERkYGWVlZeDwexsfHMRgMeBb7vq5ksVgYHR1lcnKSyMhIcnNziYiIWPa4AQEBqNVqMjMziYmJYXx8nLGxMZxOJ3q9nqmpKUJCQsjKyiI2NnZZQSR/sBoXF7ds/imASqUiMzOT3Nxc3G43vb29TExM4HQ6MZvNdHV1MT09TXZ2NgUFBeLcVJFIJBKJRCKRSHTbuOWBqkKhIC0tja1bt7Jnz541lx07dpCfn09QUNCqIHI9sbGx7Nq1i507dyKTyTh58iS/+MUv+Ld/+zeOHj3KyMgITqdz5WZrcrvdmM1mbDYbSqWSyMhIVCrVytWQSqWEhYURHR2NRCLBaDRisVjWDVRtNht6vR6TyURwcDDR0dFCgaWlZDIZ4eHhhIWFYbPZmJ+fx2q1srCwgNlsJjAwkMjISAIDA1duilQqRSaTrQqqJRIJGo2G4uJigoODGR4epq+vj7m5OWZmZujq6sJms1FUVERaWpqYTRWJRCKRSCQSiUS3jVseqPqH2gYHBxMWFrbmEhwcjFwuv6mMnlKppLi4mG9+85t861vfYtOmTbjdbmpra3n55Zc5evQo4+Pjq3qTSiSSVc/j8/nwer34fD5hSPHKdfz8w4lvhH/Is9frvebjrvU3/2vyv65PIzw8XJi3azab6enpEYpXabVaYdhvbGzsDe+TSCQSiUQikUgkEt1qX0h0stZw26XWG5J7LRKJhJCQEIqKinj00Uf50Y9+xDe/+U0KCgoYGRnh+PHjtLW14XK5Vm66SkBAACqVCoVCgcPhwGg04nA4Vq6Gz+fDbDZjMBiQSCSo1WqCgoLWDfKUSqWwjj9TutbrcbvdmEwmLBaLUCFZpVIREhJCUFAQdrtdqFi8lD8Qdjqdq4Y6A8jlclJSUigqKkIul9Pf309XVxft7e3Mzs6SnZ1Ndnb2mplakUgkEolEIpFIJPqyrB1h3SEkEglKpZKEhASh5cz9999PZGQkAwMDDA0NCcN//VlLr9crZDn95HI5UVFRxMXF4fV6GR4eZmJiYlXwZ7PZGBkZYWhoiICAABITE4mIiFh32GxQUBAajYaYmBjm5uaEobdLn9vr9WIymRgaGkKv15OYmEhycjKBgYFER0cTFxeH1Wqlv7+fqampZQG02+1mZmaG4eFhjEaj8P9LRUdHU1BQQExMDGNjY9TX19PW1gZAaWkpycnJa2Z5RSKRSCQSiUQikejLcksD1ZvJkPr5t1lr26V/82cZ/fM5vV4vSqWSsLAwYX6pP0srkUhQKBQEBgbicrmYnZ0V5o7a7XakUilxcXEUFBQQHh5OR0cHFy9eZGxsDJvNJhQg6u3t5cKFC4yPjxMXFycUR/IHeiuzwgqFgoyMDPLy8rBardTX19PS0sL09DR2ux273c7MzAytra3U1dVhMpkoKSkhNzdXCISLiopQKpW0t7dz/vx5+vr6mJ2dZW5ujpGRES5dukRjY+O6gWpQUBCZmZnk5ORgtVq5ePEi3d3dxMbGUlRURERExMpNRCKRSCQSiUQikehLdcsC1ZWB5sp/r7Q0yLveul6vl7GxMY4fP87HH3/MlStXuHr1KnV1ddTX17OwsEBqaiopKSkoFAokEgnh4eEkJSUREBBAZ2cnH3/8MbW1tfT09GA2m4mKiqKyspLi4mLm5+c5evQo7777LleuXKG9vZ3a2lr+/Oc/c/bsWVQqFVVVVUK13PVIpVJSU1PZtm0bKSkp9PT08M4773Ds2DGamppobm7m+PHjvPXWW7S1tZGamsp9990n9JCNjY1l8+bNlJaWMj8/z5EjR3jllVc4fPgwH3zwAW+//TYnT55Er9evm9UNCAggPj6ewsJCQkNDhexrfn4+mZmZyGSylZuIRCKRSCQSiUQi0Zcq4Kc//elPV/7nZ+X1epmdnaW9vR29Xk9WVhYVFRXExMSsXBUAq9VKd3c33d3dREVFUVVVRXp6OlKpVMg4Tk1NUVJSwqZNmwgJCaG7u5vDhw9z+fJlent76ejo4MqVK/T09BAWFsbOnTvZvn07MTExQmVcq9XKyMgI4+PjjI6OMjY2hs/nIz4+nujoaEJDQ1EoFMJQ3L6+PoaHh+ns7OTChQs0NTUREBDAjh072LdvH7m5uahUKhwOB1qtVuh5umnTJkpKSoQsblhYGAA6nY7BwUGGhoYYGBigubmZS5cu0dfXR1xcHAcPHmTPnj3ExsYikUiQy+VChthsNjM2NkZ/fz99fX309fUxMTFBaGgokZGRzM7OCr1ac3NzV7WxsVgs9Pb2otVqiY+P58CBA2zcuBGlUrnknRCJRCKRSPRl8S32Op+ZmcFisZCQkEB4ePjK1UQikegr4ZYEqgB2u11oy5Kfn09+fj5qtXrlarDYx3RhYQGfz0dWVhZlZWXEx8cjlUpxOBwsLCwQHBxMRUUFBQUFqFQqbDYbBoMBo9HI7Owss7Ozwvb+tjXp6elCNeGlhY18Ph9OpxOJREJSUhI5OTlERUURHBxMbGws8fHxBAYGYrFYmJ6eRqfT4Xa7yczMZO/evezbt4/CwkKCg4NhMTC3WCxYLBZiY2PZuHEj6enpyGQyJBIJYWFhaDQaoqOjCQgIwGg0Mj09jcFgQKlUUlZWxoEDB7j//vtJSkpaVpxJpVIRHx9PYmIiUVFRqFQqAgMDiYuLY8OGDWzfvh2FQkFbWxshISHcc889ZGVlLcuU+nw+9Ho9bW1t6PV6KioqeOihh0hNTRXnp4pEIpFIdJsQA1WRSCT6DxLf9cbZfgo+nw+r1cr09DQLCwuo1Wri4uIICgpauSosBqp6vR6dTodcLic+Ph61Wo1EIsFqtTI1NYXRaCQ6Opr4+HiUSiVut5vZ2Vm0Wi0zMzM4HA6Cg4PRaDQkJSURGhq6Kgjz+XwYDAb6+/uZnp5GLpeTnJxMSkoKISEhwvoul4vp6WkGBgaYnp7G7XYTGhpKSkoKqamphIWFLQsmPR4P8/PzTE5O4nK5SExMFILSpaxWK1qtluHhYebn55FIJERERJCamkpSUtK6x4fF51hYWBB+vIKDg4mJicHhcPDqq6/yq1/9itzcXP76r/+azZs3C/1afT4fs7OznDx5kj/96U8YDAa+/vWv88QTT6yb4RaJRCKRSPTF83q9GI1GOjo60Ol0VFRUkJaWtnI1keim+BZbHrI4LW3l9bHo9ra0VeXK2OJud0sC1U/D6/Xidrvx+XzCUN1rfZE8Hg9utxvJYp/W9VrE3On8vVRZcXLxLRaU6ujo4De/+Q1Hjx7lwIED/Nf/+l+FjKo/09vY2Mjrr79OfX09paWlfO9736OyslKcnyoSie46N/KTdq3fFlY8xvXWFYk+T2Kg+uXyrWiXKJFIhOVmrXwsFq/juM55Zb1z2MrXdDMsFgsGgwGv10tERATBwcHLrptXvtbPst9L3cy5dL39Xup6j3GjPu/99QeS/sfzX6/f6ONd6zh5PB6MRiNGoxGVSkVUVNSy6X13u9siUPUtZv36+vpYWFggOjqa9PT0ZRV1l3K73UxMTNDf309QUBAZGRlERkbelYHX/Pw8Y2NjuFwuwsPDCQ0NJSAgALvdjlar5aOPPuKtt97C7Xbzk5/8hK997WuEh4fj8XgwGAy0trby3nvvce7cOWJjY/mLv/gL9u3bR2Rk5MqnEolEojua2+3GaDQuawG2lEQiQaVSoVKp1ry56fP5cLlcWK1W3G63MNXiq3YHW/TlEQPVL4/H48FqtWIwGDCZTEgWp25FRkaiUqnWvB5di/88YrFYWFhYwGw24/V6UalUwnWcv9Dnyu3cbjdWq1Vorbjy71KpFKVSiUqluuFrXqfTSVtbG1euXCE4OJiamhpSU1OF7X2LoyBnZ2dZWFgQ9jsiIgKVSvWpzn9Lz6UejwelUklQUNCa510WRzL6u2ysF5YolUqCg4M/1etZyuv1YjabmZubw2w2I5VKUavVhIeHr/vbsB7/fppMJubn55c9XkREBEFBQdd8vf733GKx4HK5CAoKWvUanE6nUDA2JCSEe++9VygO+1VwWwSqbreburo6/v3f/52uri4KCwt5+umn2bp1K6GhoStXx2q18sEHH/Cb3/yG5ORkvvWtb1FZWSnMGb2bXL16lbfeeovBwUESExPRaDQoFArhh+zKlSu4XC4eeeQRvvWtbwmtbXQ6HadPn+att96ioaGB2NhYHn/8cQ4dOiTOTRWJRHcdj8eDTqfjo48+Yn5+fs1gNTg4mMLCQiorK1dNtfB4PMzNzTEwMEB3dzdWq5XS0lJKSkrW/B0SiW4FMVD9cjgcDsbGxmhtbaWlpYWxsTGkUikpKSlUVlYKBUGvFxz4zyO9vb10dnYyODjI1NQUbrebqKgo8vLyqKioIDs7m7CwsGWP53a7mZ6e5sqVK4yMjOByuZY9ts/nIygoiNzcXEpKSoiOjr6hoGp4eJiXX36Zy5cvU1NTw1NPPUVaWhpSqRSXy8XU1BTNzc00Njai1WqRSCQkJydTUVFBWVkZCQkJN5XBczqdzM3NMTg4SF9fH263m7y8vGueSycnJ2lqamJoaAiHw7EqWJXJZGRnZ1NdXb1uEutGuFwutFotjY2NNDc3Mzk5iVwuJz09nYqKCkpKSoiNjb3u+8yS72pvby8tLS309fUxMzODVCpFo9FQWlpKeXk5SUlJKJXKVa/Z5XJhMBgYGhqio6MDq9VKWVkZZWVlBAcHC+t7vV6am5v5/e9/z/DwME899RQHDx4UCrXe7W5ZMaWb4fF46O3t5ciRI1y9epXp6WkUCgUpKSlC1d6l7HY79fX1vPvuu0ilUiorK0lNTb0rK9jOzs7S2dlJS0sLTU1N1NXVcenSJZqamtDpdGg0Gg4ePMhTTz1FXl6ecIdsYGCA999/n4aGBuLj43n00Uc5cOAAqampN/QFFIlEojuJ0+mkqamJv//7v+fYsWPU19dz+fJlLl68yKVLl6irq6Onp4fg4GBKSkqEG5v+bEJ3dzdHjhzhhRde4JVXXuHcuXNERUVRUFDwlbkgEH35fGIxpS+c0+mku7ubP//5z7z88svU1dUxPT3NyMgIly9fpq2tDaVSiUajuWZWkMUhtnV1dTz//PO8+eabtLe3MzExgVarpbm5WXjssLAwYmNjCQwMFAISu91Oc3Mzv/rVr3jllVe4ePEily9f5tKlS8LS1dWFXC4nMzOTqKioa74WFh/z9OnTfPTRR4SFhbF3714KCgpQKpW4XC5GRkZ44403+NWvfkVdXR16vZ7R0VEuX75Me3s7EomEuLg4YTTftXi9XhYWFujs7OTo0aO89NJLvP766zQ2NhIUFLTuudTn89HS0sLvf/97XnvtNc6dOydc6/rP383Nzfh8PsrLyz91oOr1eunt7eXll1/mT3/6k3AdPTQ0RH19PV1dXchkMjQazbJAcS0+n4+5uTlOnz7N7373O9577z3Gx8dxOBxMT09TW1vLpUuXsNvtJCYmEh4eviyD7T9OH374IS+88AIvv/wy586dIzIykuLi4mV1cyQSCSEhIRiNRhobG5mZmaGgoOCGb1Tc6W6LQNXr9TI8PMz58+fR6XR4PB5cLheRkZGkpqau+sA4nU46Ojq4cOECUVFR1NTUkJaWJhQQupv4izhlZWWRlZVFbm4uhYWFbNiwgR07dvDII4+wZ8+eZcM4WLxT4/F4SEtLY9++fezevZuUlJQbHioiEolEdxK73c7Fixc5fPgwqamp7Nq1i4qKCoqKiiguLqa4uJiysjLKy8vJysoSbmy6XC56enr4+c9/zrvvvsvs7CwWiwWn00lZWRkbNmxYt2K9SPR5EwPVL5bP52N4eFjoTw+we/duDhw4QEVFBTKZjO7ubgYGBoiJiSElJWVZcLmS3W5naGgIrVZLRkYG999/P/feey+VlZVERUUxMzNDb28vHo9HSMb4r8tsNhvNzc0cP34cmUzG9u3bqaqqEs5fxcXFlJaWChnZtYqGrjQ4OMh7773H6OgoW7ZsYceOHURHR+P1epmenubdd9/l5Zdfxu12s2/fPh555BE2bdqEXC4XWhr6r0NXXouv5HA4qKur46WXXuL48eNMTExgMpmQSqXk5eWtey71er00NjZy9uxZfD4flZWVVFdXU1JSIpy/S0pKqKyspKCg4FOPnpyenuYPf/gDhw8fJiQkhAceeICHHnqIsrIyALq6utBqtcTFxV03+eVwODh//jx//OMf6e7uZsOGDTz55JM89NBDbNy4EbVaTXd3N21tbcTGxgqxjD+L3dTUxO9+9zuOHj3K7OwsRqMRq9VKRUWF0IZz6bFWKBRIpVJGRkbo7OxErVaTn59PYGDgstd1N7qtAtULFy7gdDqFarY2m42EhAQ0Gs2yYQdOp5P29nbOnz9PZGQk1dXV6waqHo8Hp9OJw+HA7XbDNSqe+daYXO0fP+50OvF4PML/r7X958X/nA6HA6/XS1hYGOnp6ZSUlLBx40aqqqrYuHEjpaWlpKWlERoaKvy4uVwufD4fKpWK1NRUSktLycnJISIiYlmBqrX2daWVk8NXruP1enG5XMLzer1e4disXHet5/N6vTidTpxOp7Dt0rtDSx/f4/Gs+vt6lj6u/3is9Zr8rrefN7KO/zlv5HMmEok+X77FrOiJEyeor6/n4Ycf5vvf/z579uxh27ZtbNu2ja1bt1JVVUVWVtayCy6Xy8XAwACnT5+moKCAe+65B5vNxvz8PGVlZVRWVq55cSW6M3k8HiwWizA83N/C7ovicrkwGo1YLBYki8Uglz6//7dcDFS/GBaLhfPnz/Puu+9isVjYu3cvzzzzDNXV1eTl5aHRaNDpdDQ3NyOTycjNzSUqKmrd7KJUKiUsLIzc3Fzuu+8+tmzZIgRaubm5WCwWenp6cLlcZGRkkJqaikqlgsXX4h8JUlFRwfe//33279/P9u3bhfPY5s2bycnJITw8fN3X4OfxeLh48SLHjh1DrVaze/du8vLyUCqV2Gw2mpqaePXVVxkfH+fxxx/nG9/4BlVVVRQVFZGYmIher6erqwuPx0NGRgZxcXHXTHY4nU5aW1sZHBwkPT2d4uJivF4vdrudvLy8dc+lLpeLS5cu0djYSF5eHt/4xjc4ePAg9957r7DfNTU1FBQUoFarb+g6cCWv18vx48d59dVXcTgcPP744zzxxBNs3LiRwsJCYmJimJycFN6b8vJywsPD1z03TE1NcfToUc6ePUtOTg7f+c532LFjB5mZmWRkZFBYWMjQ0BCdnZ0olUr+P/beKziu+87z/XRGoxs555xBMIAEmEkxkxJFiZRkOYytkWV7dr1VU1v7eF/m8dbeh52ZOzt37fHalmQlKlEkRYo5gSBI5JxzaGSgEzp335dzziIxSaRM0edTdcoWcXL49/+Xvr+CggLi4uJQqVS43W4pUzI7O5sXXniB6elppqenKSsro7y8fIUTQiHoK8zNzVFbW4vb7aa0tPRbR5d/SDwzhmp/fz+3b99GpVJRXFyMQqFgeHgYlUpFWloaUVFR0sNYbKhGRESsMFQDQp/U6elp+vr6aGtro7Ozk4GBAWZmZvB6vajV6iU/UH6/n4WFBUwmE+Pj4/h8PgKBAKOjo7S3t9PR0cHQ0BAWiwWlUolWq0WlUj3RFyQgKPmOjY3R0dEh1TdMTU3h9/sJCQkhLCwMo9FIcHCw1KZnYmKCjo4OWltbpfURCs8dDgfT09O4XC50Oh0ajQaP0A5oYGAAs9mMTqdbUdjvdDqZmJhgeHgYu90urRMQjOjZ2VkGBgbo7Oyks7OT3t5exsfHcTgcqNVqyfuDcG9tNhtDQ0OMj4+j0Whwu91SXn5XVxcTExO43W40Gg1qtZqFhQVGRkZob2+XvFxOpxONRoNGo1l1oPJ4PMzPzzM4OEhHR4fkBZ2cnMTpdKJSqaRnLl6rmKYxNDQkXefyiYvT6WRkZITR0VHcbjdarVaaXPiEtkGil6ujo4OBgQGmp6cJBAJL1pWRkXl62Gw2vvzyS3p7ezl27Bhbt24lOjoag8EgLcHBwSvGOoXQZzs5OZn9+/eTnZ1Nc3MzQ0NDkhd/tcmVzA8Pv9+P1WqlsbGRmzdvSs7w5WO+3+/HJ3QW8Pl8kiP1u47jgUAAk8nErVu36OzsRKvVEhoausQRLxuq3y/Dw8N88803VFdXk56ezvHjx1m3bh1GoxG9Xk9oaCh2u53m5mbm5+fJy8uT5purvQ9KpRKD0D4wMjKS4OBggoKCCAoKIiQkhImJCVpbWwEoKioiLy9PihBarVZu375NbW0tW7ZsYf/+/SQkJGA0GpeMYTqdbtU50HLm5ua4dOkSDQ0NFBYWsmfPHhISElAoFExPT3Px4kVu3rxJSkoKf/d3f8f69esxGAzodDoiIiKk9FSLxUJycjJZWVkravsXo1AoCAoKIjs7m61btxITEyPNSXNzc+87lrrdbq5fv05rayuFhYXs3r2btLQ0QkJClozfj3rdywkEAthsNv70pz9RWVlJaWkpr7zyipSKrNfrCQ4OxmKx0NjYyOzsLCUlJaSkpNy3NndgYICrV68yMDDAxo0bOXr0KPHx8Wg0GrRaLSEhIXR0dNDU1IRer2fTpk2kpKRI80GdTkdWVhY7d+4kIyOD6upqhoeH2bhx46qGKkJU1Waz0dLSwuTkJHl5eSuyKZ9HnilDtaKiAoVCwebNm4mJiWFwcJDx8XFJBVj0Oj3IUBWNoo6ODi5cuMAXX3zBlStXqK6u5u7du9y7d4+BgQEA6QVVKpV4vV6GhoY4d+4cFy9elBTBzpw5I6nm3r59m6amJmw2G2FhYYSEhNz3JX5cAoEAdrudxsZGPvvsM7766itu377NvXv3qKmpYXx8nPDwcKKjo6XrNJvNNDY2curUKT777DOuXbtGdXU1dXV1mEwm5ufnqaqq4urVq1gsFhITEwkNDcVqtXLr1i0+/PBDenp6SEpKWlELPD4+zqVLlzh9+jRjY2MkJSURGRmJ3+9ncnKSixcvcvLkSW7cuCHd26qqKjo7O/F6vUvkz0Wj9OTJk1y5cgWtVsvAwABffPEF58+f58aNG9y9e5fR0VHUQquh9vZ2vvrqK06fPs3169epqKigvb0dhUJBVFTUkjoR0cAXB44vvviCb775hrt371JdXU1lZSUdHR243W5CQkIkFTaFQsHU1BRXrlzhyy+/ZHR0lJSUlBUeqvHxcb788kvOnj3LwsICcXFxhIaGEggEmJycpKKigk8//ZTz589TVVUl3Q+v10tCQsIj1XbIyMh8N8xmM3/5y1+Ympri+PHjZGRkrHBMrYZSqUSv15OUlERsbCxOp5Nbt24xMDAgG6rPGT6fj/Hxca5fv86lS5cIBAIUFhYSFBREQOgzKTo8R0dHGRsbY2pqitnZWfx+PzqdTlrv2yxut5vOzk6++eYburu7CQsLW9FDXTZUvz8CgYA0V5ycnGTjxo1LjDmFkMVls9mor6+nt7eX3NxcioqK7psGK24jzmVExDleXV0d9fX1hIWFSdFRvV5PIBDAbDZz8+ZN2tra2LVrF6WlpZJjfrVjPYz+/n4uXLjAzMyMlIkXFhaG3+9neHiYr776io6ODrZs2cKhQ4eIiYmRjqPVapmdnaW9vZ3x8XHi4uJYs2bNA99FpVKJ0WgkPj6euLg4zGazNH99kKFqt9u5dOkSfX19lJSUsGHDBin19WHj96PgF7I233vvPSYmJqRMG7HGU6FQSEZgbW0tk5OTZGZmUlxcLNkdy5mamqK2tpbe3l6Sk5PZtGkTERER0jN3uVxcv36dhoYGMjMz2b59O0lJSZKhajQaSUxMJC4uDrfbzaVLlySj936GqkKhwOVySYJ/omDTg1KUnwce3zXxFBEH88jISEpLS8nNzWV8fJyrV6/S3NyMZ5kC2nJEr0ljYyOffPIJn376Kd3d3QQHB5OcnExMTAxms5mLFy/y7rvvcuXKFSYmJiSPqdVqpaOjgytXrvDFF1/w2Wef0dDQgFqtJjw8HJfLRXV1NZ988gnnz59nZGRESvP8rng8Hrq6ujh58iSnT59menqamJgYEhISCAoKwuVySanAAaEQu7q6mvfff58vvviCoaEhjEYjsbGxKJVK6uvr+eyzz/jyyy+5desWPT092O12ED6g/v5+qqqqaGhoYGZmhsAyhTW73U53dzd3796lubkZs9kMwjMSB6/p6WlCQ0NJSUkhKSkJr9dLVVUVn332Gbdv32Zubo6AkC5rtVppamri0qVLkiE+MDAgeQdFr+bHH3/M559/zqlTp2hqakKpVBIeHs78/DxXrlyRhA4Wt6Bwu910d3fz+eef895771FdXY1CoSAhIYGEhAR8Ph9VVVW89957nDt3jqGhIdyC9PvCwgI9PT3cu3dPus7l98Jms9He3k5lZSXt7e1YrVb8gmiA+D5UVFTg9/tJSkoiPj4enyBz/6TeDxkZmfsjTu7F8Xx8fJyGhgYaGxulDAen07ni2xZRq9UYjUbUQv/p+60n88NGfE9mZ2eZmppidHSUvr4++vv7paWzs5OKigq++OILPvjgAz744AM+/fRTrl69SldX15J1H3fp7e2lv7+fiYkJZmdnmZ+ff+i8Rubp4fV6mZmZYWpqSnJWLTcQVCoVUVFRREZGYrVaGR8fZ2FhQZp/3A/xXbNYLMzNzWEymaipqaG+vh6FQkFubi7p6elSjaHP58Nms2E2m6Wst+bmZhobG6XMsEc57mImJycZHx/HYDCQkJAgGV1iVtzo6CgAycnJK65boVAQGRlJdHS0dD6Pcnyd0IZGDOI8ylhqtVqxWq243W5JQLSxsZHu7m4mJiaw2+0PPe6DCAQC9Pf3MzMzQ0hICGlpaYSHhy9xJGi1WqKjo4mKisLr9UpZfPcjKipKCpC1tbVx69YthoaGMJvNzM7OUldXR1NTExqNhjVr1hAfHy8FLETD+HHvE0BERAQpKSm43W5GRkZwuVzLV3nueKYiqjdv3sTlcrF+/XqKi4sJBAL09PQwPDyMwWAgIyOD0NBQPB7PqhFVhUIhqd2KkbuDBw/y6quvsnPnTjZs2EBiYiKTk5O0trZK3sr4+HjUajWTk5PU1NTQ0NDA7OwsUVFR7Nmzh5deeoktW7aQkpLC3NwcnZ2duFwuUlNTSUpK+s7ejIDgabtx4wYnT54E4MSJE7z66qts2bKFtWvXUlBQQGZmJhEREfh8Prq7u/nyyy+5cuUKRqORo0ePcvz4cXbt2kVxcTFqtZru7m4p3z4vL4/S0lKio6Ox2WzU1dVRXV2N0Whk27ZtklS5iOgt6ujoIDIyks2bN5OcnAzCIKdQKCgpKWHPnj2Ul5dTWlpKQkICU1NTdHd3A5CTk0NMTAx+v5/x8XFu3rwp3ffU1FQOHDjAwYMHKS4uRikUiXd3dzM2NoZarWbz5s28+OKLbN26laioKEnqPDQ0lOzsbCIjI1EqlYyNjXHx4kVOnz7N/Pw8O3bs4LXXXmPv3r2UlZWRlZWFzWajra2NiYkJIiMjJfW+2dlZamtraW1tJSIigq1bt5KYmLjiXty8eZOenh7S09PZsGED0dHRmEwmzp8/T0VFBRkZGfz0pz/l4MGDlJWVUVBQQGFhISkpKSt6YsnIyDxZvEJv7ZMnT2K323E6nbS0tCyZ5CG0p7lfyh7CWDw3N8fNmzfliOpziN/vZ2ZmhpaWFvr7+6VoWX9/v1Qu0tbWRlNTEx0dHQwPDzMxMcHk5CQzMzNMTEzQ3d0trfu4S2dnJ11dXYyPj6NWq8nOzpZEcUREA0eOqD59RPGi27dvo9FopDpIMRWXRfOz+vp62trayMrKkoSRHpQp5Xa76enpoba2lubmZu7du8eFCxfo6+ujoKCAQ4cOsXbtWkJDQ1EoFHg8HkZGRqioqKCvr4+FhQW6urqor6+nq6sLk8mEV+jtrNPpHnhshPMWU9zDw8PZvn07GRkZaLVaHA4H7e3tXLlyBbfbzf79+ykpKVkRPbRarTQ3N9Pd3U1UVBQbNmyQ6iwfRiAQYGxsjHv37j00ojoyMsLt27fp7e3FbDbT399PY2MjHR0djI2N4XK5MBgM33ou5fV6qays5Pr16xgMBg4dOkRubu6SubtCoWBubo76+nr6+vqIi4tj165d9/32tEIpnFhiODw8LGVidnR08NVXX9He3i6lGYvHW+23Z35+ngsXLjw0oopwX4eGhrh9+zahoaFs375deoeeVx7/iT9FFELNnxhVLSsrY+PGjbhcLm7dusW9e/ewCwIELPNABISoXUtLC9XV1bhcLnbs2MGJEyfYuXMnpaWlbN68maNHj3L06FGio6Npa2ujpqaGyclJ/ItqUJRCMfyWLVs4fvw4O3bsYNu2bbz00kscOHCAqKgoRkZG6Ovrw2KxEBBSgbxe72Mv4vW6XC5MJhOTk5NERkZSXFwsCXls376dsrIyEhMT0Wg00nXW1tYSCAQ4cOAAb7zxBrt376a8vJzdu3dz7NgxNm/eLA0Ky19i8VqX/7vI4r8t/v9KpZLY2Fh27drFwYMHpUL0oqIiNm/ezPr160FojzM2NiZFLhUKBSqVCr/fT1hYGDt37uTQoUNs27aN/fv3c+TIEQoKCrDZbMzMzFBYWMiLL77Irl272L59OydOnGDLli34/X56enowmUx4BKGlnp4eKisrmZ6eprS0lNdee419+/axceNGNm7cyKFDh3j99dfJycmhq6uLqqoqhoeHl5zbo94P8e9+IQIvDqKicNX69evZuHEje/fuZe3atY8keCAjI/Pd8As1hYWFhWzcuBG1Ws3s7CxtbW188803/OlPf+LPf/4zVVVVWCyW5ZvL/I0hjuU2m42mpibu3r0rLbW1tfT392O1WqXfaYfDwcjICLW1tUvWfdylurqa3t5eHA7HA39vZL4fPB4Pdrsdl8uFWq0mODh4Rb2fYln0y+l04nA4HhjhCwjlSM3NzXz55Zd8+OGHfPzxx1RUVKBUKlm3bh1FRUVLonoBQfQxKSmJ9evXExYWhtlspru7mytXrvD+++/z5z//mevXrzMxMYH3IdlaYoTW4XCg1+sJCQmRrs3r9WKz2fB4POh0OgwGw4rrRjDGxLR4p9PJwsICPkFU9EmTlJREYWGhFLnu6enhxo0bfPjhh/zxj3/k4sWLkl7L4xIQshDdbjc6ne6+hr74DiBk0j3oWrVaLcXFxRw+fJisrCw6Ojr4+OOP+Y//+A9+97vfcfbsWUJCQti3bx/5+fkEBwc/ke9do9EQEhJCUFCQFIn+Nvfkh8QzZaguJigoiMzMTHbs2EFWVha9vb1cvXqVvr4+6YNejN/vl6Kdk5OTpKamsmXLFrKystAKIktKpZKYmBjKyspYs2YNdrudtrY2yVMlotVqycnJkYxDlUqFUqkkOjqagoICUlJS8Hq9UiqE1+tlfn5eEhfq6up6pKW7u5vR0VEcDgcqlQqj0YjRaGR2dpaWlha6u7ul2hitVivVW1ksFqluID09nW3bti25Tp1OR3Z2Nhs3biQlJeU7R3wXIw7aYo2myWSiq6uL5uZmenp6sFqtksDQ3NycZAwiPCOVSkVBQQFr166VPJLBwcGkp6eTnp6OwWCQDPXU1FS0ghhRcnIyRUVFREZGMj8/z/z8PF6vF7vdTm9vL729vYSEhLBlyxYKCwuX1PwYjUY2btwo1XuI3q/vkjKhEIrhQ0JCpGhwU1MTQ0NDWK1WNBoNQUFBqw6GMjIyTxZxbP/pT3/Kb37zG95++23eeustXnvtNdauXcv8/DzffPMNX3zxhaRiKSOj0+lITEwkNTVVWlJSUoiOjpYME3Esj4yMJCUlZcm6j7ukpKQQFRX12Ol+Mk8H3yLBLIXgTF8tYqcQAhgKoRPEozw3pVCvGRsbS2xsLJGRkYSGhuL1ehkcHKS/vx+LxSIZGSqVivj4eA4dOsQ777zDL3/5S37xi1/w5ptvsnnzZnw+Hzdu3ODUqVPU19djtVofeB7LjXDdIiEiMbASCARQqVSol9XTiix3zvufUllEVFQU+/bt45e//CXvvPMOb731Fj/60Y/Ytm0barWaO3fu8NFHH1FTU8PCwsLyzR9KQBBY9fv90nNcDfEdQHg3HnSt4t+0Wi16vV6a73k8Hubm5vB4PLgFUVdxLvyg/T0q4txTr9dLzoMnsd9nmZVv5jOCQqEgNDSU9evXs2PHDoKDg7l37x4VFRVYrVbUavUSD5Df75cEENxuN2lpaaQKhs7y/YriTABjY2PMzs4uqRNRq9VERUUtURpmkey4WDDtdDrxer04nU46Ozs5deoUf/rTn3j33Xcfuvz5z3/mgw8+kOpkg4ODKS4uprS0FJvNxunTp3nvvff4+uuvaWlpkc5RNAJNJhMul4uUlBQSExNXeMN0gmpbWFjYExN8YlFa0sjICDdv3uTjjz/m3Xff5S9/+QtffPEFtbW1khHpEtrKLN5WrVYTExOzQmJc9FiK3r2wsLAlz06lUhEREYHRaMQttIEJCCk5ExMTLCwsEB0dLfWqWk54eDjZ2dnExMRgsViYmpr6ToaqODFet24dKSkpdHZ28pe//IW//OUvXLt2jf7+/u9cVyEjI/NoqNVqYmNj2b9/PwcPHuTgwYMcO3aMn//85/zqV7/i8OHDqFQqKioquHPnDjabbfkuZP7G8Pv9REdHc+DAAU6cOMFrr73Ga6+9JrXFKCkpIScnh9zcXAoLC9m+fTuvvvoqr732GidOnHjsRdx3WVkZoaGh0nncb9Is8/RRKpWScRoIBFY1TgJCxpz4N9Gwe9BzUwitRDZt2sQvfvELfvvb3/Kf//N/5o033iA0NJTr16/z5Zdf0tjYKI1F4hhWXl4ujWFHjx7lpz/9Kb/+9a85duwYERERUgaAWI9/P7xCW0Wv14tSqVxioCkFsSeF0CbwfgaoeN0KoY2SKOz0pImOjmbTpk3s37+fQ4cOcfToUX7yk5/wy1/+khMnThAfH09TUxPXr1+XOio8DgqFQjr3wAMcDQGhqwWL+pbeD7sgjHX+/HnGxsYoLy/n7bff5j/9p//EO++8w+HDh7FYLHz66aecO3fuiWraKATHiehoed65/1N4BtBoNCQmJrJ9+3Y2btzIzMwM169fp6OjA6VSuSTf2+fz4XA4pIheiCBrvRpiJEylUuFyuSRPy2LED3sxordF/MDFF94rFKb39PTQ2tpKW1vbIy3t7e0MDQ2xsLCATqejuLiY1157je3bt2O32zl//jz/+3//b959911u3brFxMQETqcTu92OzWYjEAgQGhq6JHq4GHEQfpJ4PB76+/v56quv+MMf/sDp06dpbGyUUjI0Gs0Djynew+X3VkQhePBWG0xW287lcknp4GFhYZLS8HI0Gg2RkZGEhITg8XikSPjiYzzoh2c5CoVCqml9+eWXyc3Npaenh48//pj/7//7//joo49oaWnBZrOteLdkZGSeLOJERHR2iQ6vmJgY1q9fL5UWTExMSI4/mb89FEJGUIjQ6i05OZkNGzZI/cnLy8ultiDHjh3jxIkTHD9+nFdeeYWDBw+yZcsWqc/h4y5lZWVs2rSJ4uJiYmJiCAkJwWg0PvD3UubpotVqMRgMBAUF4fP5pODDcsR5hsfjkaJnD5svqNVq4uLiKC4upry8nMOHD/Pzn/+cI0eOoNVquXPnDrdv35YMTtEYFFvZ6ARRIjHD7NChQ6xfvx6n00l3dzfj4+NLAizLEed/ilWMUbVajcFgQCO0CrTb7fe9blFQSC+0cHka7+v9rrugoIC9e/eyadMmlIJI6PT09GPPqRRC4Eur1eJ2u1ed8yPMbxcWFlAoFJKNcD+Ghoa4cOECd+7cITY2ljfffJOf/OQnvPLKK5JzYvPmzQwNDUnioE8q+ik+z6cxx38WWTmjf8YICgoiLy+P3bt3k5ycTGNjI1euXGFubk5KhV1OQPCM3c/bJD7kxUbT8v2sZiitRiAQICgoiIKCAk6cOMGvfvUr3n777UdafvGLX7B//37i4+NRCqnFe/fu5T/9p//E3//937N582ZsNhtff/01H3/8MTU1NVJNrIh4LavxoGsQr/d+f18Nv6D4e+nSJd599116enpYt24dP/vZz/jVr37FO++8w6FDh0hOTkatVq+67wedE49wPqv9Xdznw+6F+E4oF3kTl69zP8S/Ld5Gq9WSkZHB8ePH+Yd/+AfefPNNcnNz6e7uliLMvb29S9KfZWRkvl/UajUpKSkkJyfjFzJvvk36mMwPH6WgIl9cXMyuXbtYv3494eHhkoNVpVKh1+tJSUlh06ZNvPDCC7zwwgtSeY1Op0MtZHN9myUoKIikpCRKS0spKysjOzv7vo5mmaePVqslPDxcytQym80rfq/9fj92u525uTkQsrOCF7XHe1Q0Gg0pKSls376dkpIS7HY77e3tj1RvqlQqSU5OJjU1FQTxHbGG+n6IjjutVitluInzI41GQ3h4OAaDAYfDwczMzKoZZna7HYvFgkqlIiws7Ht3rKiFDLyMjAx0Op0kMHa/ed79UCgUxMbGotfrsdvtzM/PS1l5In6/n4WFBebm5lAoFMTExKzIyBTx+/10dnZKHSY2b97Mpk2biIyMlLIZN2/ezOuvv056ejo9PT20tbUxNzf32Oe+nICQxuxwOAgKCkKv16+Yyz5vPN6X9ldAqVQSERFBWVkZO3fuxOVycePGDdrb2wkEAtJgoVKpMBgMknjNzMwM8/Pzq74UCwsLzMzM4PP5vtPHJ77kOp2OzMxM9u/fz/Hjx3n11Vcfuhw/fpyXX35ZaorMIq9PWVkZb731Fv/4j//IT37yE+Lj42lsbOT27dtMT08THBwsqQTOzs6uWqvgF3q2LR6cRERDTSXk06+WO+/z+fB4PAQW1QN7PB6Ghoa4ceMGIyMjbNu2jbfffps33niDF154gXXr1pGamnrfqOaTJiA4CcQ0qpmZGak2YDkul4vx8XHm5+cJDg4mPDxcSu1QKpX4BUGr5VFWhOte7d9ZFPXfv38/v/nNb/iv//W/8vLLL+P1erlw4QINDQ3Y7fZVt5WRkXn6iE4shO9Vq9V+q/Fe5oePaKiWlZXxox/9iO3bt2N4QD/MxcuTQKVSkZSUJAkI5ufnr1Balfn+0Gg0UpmX0+nEZDJJ2WoifkEpenZ2loiICJKSkqR3Rhxb/PdJnV0No9FIaGgofkGQ8WHCTCIBwSGvUqnQCLXTD5pnaQTRneDgYJxOJzabTTJsxeuOj48nEAgwOjq6Yh4ZCASYmZlhenoanU5HbGwswYsEgR73ur8t4nUrhNpM9aIgQ0AIQHiFOuP7nYtSqSQ9PZ3IyEgsFgvDw8OYzeYlwSyXoLQ9MzODRqNZ0jpIfM7iuXi9XiYmJpiYmECn0xEfH49uFS2Y3Nxc4uPj8Xg8TE5OPpEMO68ghOVwOAgNDV1RRvc88oO4OrVaTWpqKnv27GHt2rX0Cz1A7UJfUIQfgMjISOnl6unpoaOjY4WR4Ha7GRoaoqOjA7VaTWZmJnFxcWieYB3nt0X8CAKBACEhIaxbt44jR45QVlaGQqFgbGwMu91OSEgISUlJBAUFMTAwQF9fHw6HQ7rOgKBwNjQ0xOTk5BIPoUJILwkJCUGn0zE7O8vExMSSwdItFICLqcbiD7XH48FkMjExMYHBYKCkpIT09HQ0Gg2BQACHwyEZzg/y9D0JxPtkNBpJSkrCaDQyMTFBR0eHJEC1eF2TyURLS8uK/rRi6k8gEGBqaorp6WnJ0A0EAng8HkZHR5mamlr1msTzUKlUxMXFsWPHDo4dO0ZmZiZjY2OSKvDid1BGRubJs3giIRIQvM/Dw8MMDw+j1WpJSkpatUWCzN8GarWayMhIMjMziYmJ+d4neUFBQVJ0zGg0fu/Hl/k/KBQK4uLiSE9Px+v10tvby+joqBRd9Pv92Gw2qaVQeno6WVlZksEmRiNnZ2el3/nAfYzXgGDgzMzMMDMzg0IITCyOzorbr7bd0NAQg4ODqNVqkpKSiI6OfuC8Vdx/SEgINqFtiji3EefLYiuerq4uRkdHpeBEQJhD9vX1YTKZCAsLIzMzU5oruVwupqenmZ6eXhGB/jbc77rdbjeTk5P09vbi8XikFo3i/bLb7VIrm76+vvsagkqlktTUVHJycvD7/bS3ty8RUQ0IRnl7ezvT09PExsZSUFAgZTs4nU4mJyeZnZ2V0oYVQp2oRxCtWp7BGQgEWFhYwOVyoRJEQ7UPaI32qIiBtkAgQGRk5N/EGPKDuDqFUJheUlLCoUOHMBqNdHV1Sbnq4gsTERFBQUEBiYmJDA0NceXKFerq6jCbzZJHqbu7m8uXL9PU1ER0dDTr168nISEB9SrS3N8nHo+HmZkZRkdHmZ+fx+FwsLCwgMPhwOv1olKpCAoKklI2ioqKSEhIoL+/n+vXr9PS0oLZbMZutzMzM0N1dTXXr19nYGBgxUCi1Wql3myjo6Pcu3ePrq4uzGazJId+584dOjo6VqTIKYU0aZfQNN1isUj1G11Czy9xwPuuH+SjYDQaycvLo6ioCIfDwfXr17l79y5TU1OSjLzJZOLSpUtUVlai0+koKioiNTUVnaCcJqaEjI2NUV1dzcDAAFarFYvFQkdHB9euXaOnp2fJNfmFdCCxx57VapXqh51OJ36/n+DgYIKCgqR7JiMj8+QJCE6ynp4e+vr6pHHQbrdLCupff/01HR0dZGRkSClaMjIyMvHx8ZSUlBAdHU1vby+3b9+mr69PShFtaWnh1q1bmM1m1qxZQ3Z2NjqdjoWFBZqamvj88885ffq0FBgxm81SZ4epqSlsNhsLCwtYrVb6+vq4efMmTU1NGAwG8vLyiI2NRaVSYbfbGRkZYXBwkJmZGWw2m7S/zs5OLl68SENDg5S6LrYrfBAxMTGSgKTJZJLqTQFCQ0NZt24dSUlJdHV1Sb2jFxYWsNlsNDQ0UFlZicViITs7m/z8fIxGI06nk46ODr744gs++eQT2tvbcTqdS4zMx8EliHMODAwwPT2N1WqVrltszVNVVYVWq2XLli3ExsZKhll/fz+ffPIJ//Zv/yaVBK52Hgqh5nTHjh0kJibS3NxMdXW1FPyZn5+nubmZyspKPB4PGzZskDpp+P1+6uvrOXnyJF999ZXUeSQ5OZnk5GTm5uaoq6uTDGUxzXp6epqbN2/S19dHdHQ0ubm5REZGfudsnrm5OYaGhtBoNCQlJT30HXgeUP3TP/3TPy3/x+8bv99PX18f169fx+12s379egoLCzEajdI6orFqMBiYmZmho6MDh8NBUlISW7duldRetUIz4+HhYTo7OxkfH8fhcDA5OUlTUxOnT5/mwoULKJVK9u3bx4EDB0hJSQFgfHycmpoa+vr6yMzMZMuWLURHRy86UzCZTNy9exeTyUR6ejrr168nNjb2OxkiPp+P2dlZrl27JjX9FaODV65cobKyEr1ez86dO9m0aRMxMTHodDrm5ubo7u6mp6eHyclJ5ufn6e/v586dO1y9epXW1lbm5+fR6XQUFBRQWlpKTEwMCqG4vr+/n5aWFsbHx7HZbExPT9Pa2srly5eprq6WootJSUls3ryZ5ORk3G437e3ttLW1YbPZUKlU2IRedFeuXJGaO4eFhbFhwwby8/PR6XSYTCbJcC4tLWXTpk1LUhbm5uZobGykubmZkJAQtm3bRnp6uvRRBwIBWltbuXPnDgAbN24kLy8Po9GIXq/H5/MxODhIe3s7o6Oj2Gw25ubm6Orq4uLFi5w8eRKTycTu3bt55ZVXyMvLI0iQExej7H19fYyMjGC1WpmcnKSxsZGvv/6a5uZmZmZm8Hq95ObmUlpaSnh4OAMDA1y4cIG7d+8yMjLC2NgYTU1NnDlzhubmZgoLCzl8+DA5OTmrpoXIyMh8d3w+H0NDQ/zhD3+gsrISk8nE4OAgnZ2dVFVV8cUXX3Dt2jU0Go3URzsqKmr5bkAYZ2ZnZ6WxqqSkhI0bN9636buMzJNGjFiJ9XiiU1nm6aDT6dBoNMzPz9PT08Pg4CA2m435+XlaW1s5e/Ys1dXVZGZm8vrrr7Nu3TqCgoIYGRnhs88+449//CN1dXUYDAaSk5MxmUx8+umnXL16lYGBAUZGRujp6aG+vp6vv/6ab775hunpaTZt2sTRo0fJz89HpVIxODjI119/zZUrV+jp6ZG2q6mp4auvvuLixYu43W52797N4cOHpWy2B6FQKOjr66OtrU0ycCMjI1EImXU6nU5qdyj297VYLLS0tHDmzBlqampIS0vj5ZdfZtOmTYSEhDA9Pc3nn3/O7373O65fv054eDg5OTmEhISsmAeLgZDx8XGys7Oled9iTCYTX375JVevXqWnp4ehoSF6enqora3l3LlznDt3DqvVyq5du3j99ddJTU2V5oU3btzgo48+oq+vj+LiYtavX4/RaFxxHgj3IiwsjJGREZqamqTWkKKhefbsWerq6sjKyuKnP/0pBQUFkj3xb//2b9JzTkhIICMjg9DQUKxWKx0dHZKD1C3UOff09HD58mU++ugj5ubmOHjwIEeOHCElJWXVoNjc3Bznz59ncHCQDRs2sHnz5lXvZyAQoKOjg3PnzuHz+SQhz4e9Bz90nhlDVZzk63Q6SktLycvLw7BMtVchpDJoNBpJKS09PZ3y8nJSUlKkwuLIyEg0Go1k0NbW1lJdXc2tW7doa2sjKiqKQ4cOcezYMfLy8tDr9fgFoaCuri7m5+fJz89n48aNKzzv09PTUqQxKytL8sQtf6EeB7/fz9TUFDdu3ODcuXNUV1dTW1tLZWUlra2tGI1GXnjhBQ4cOCClNuv1esLDw/H5fIyNjdHa2srdu3e5d+8eTU1NBAcHk5mZKdWa5uTkSIaqUqkkSFBYs1gsjI6O0t7eTnV1tRSBLiwsJDc3FwSv3MaNG0lOTpZSXmZmZujt7aWzs5Pm5mZqa2txOp0kJycTEhIiRX1zc3MJCgpienqapqYm5ufnKSsrY8OGDYQIPUgBrFYrvb29jIyMEBMTw5YtW5YMSIB0PIPBwMaNG8nOzpauIyoqCqPRKKWC1NXVSc+8rq4OhULB3r17eeONN5YMZmJKhkqoaxYHsXv37lFdXY3L5aK8vJzY2Fi8Xi+ZmZmsXbuW8PBwBgcH+eabb7h69So1NTXU1NRw8+ZNBgcHSU9P5/jx42zbtm1JqoqMjMyTxePxMDIywtmzZ6msrOT27dtUVVVRUVFBZWUl4+PjpKam8sorr3D8+HGysrIeOF5bLBapT+H69etZt27dknYiMjJPE9lQ/f4xGAyEhITgcrkYGBigsbGR6upq7t69y/DwMKmpqfzoRz9iz549REZGolQqmZ6epqGhgc7OTjQaDQUFBeTm5rKwsMDdu3epqqri7t27VFZWUlFRwa1bt+jq6kKn07Fz505OnDjBxo0bCQsLw+fzYTKZuHXrFtevX6eyspI7d+5QUVFBRUUFAwMDREVFSW23ioqKltSL3g9x7tXS0oLb7SYjI4OEhARJnyMoKIjo6Gjpupubm6mpqeH27dsMDAyQmprKyy+/zJ49e6RIpsVioba2lpaWFjweD+vWrWPt2rWEhoYuOR+FQsHk5CSdnZ04HA7y8/NZv379irF0fHyc69evc+PGDe7cuSNdd2VlJb29vRiNRvbs2cOPf/xjiouLCRLqRt1uN9euXeP27dukpKSwf/9+8vLyHhgUCAkJITIyEqfTKQVqxOc8NjZGbm4ub7zxBrt27ZK+ObfbzcWLF+nu7kaj0VBaWirVnooR0snJSTo6OmhsbKS+vp5bt25x69YtvF4v+/bt480336SwsPC+wkdWq5U7d+5gt9spLS2ltLR0VUPVbrdz+/Ztrl27RmZmJidOnPirlC983zwThqpCqIEMDQ2lqKiItWvXSh/T8vXUajWhoaHEx8eTnZ1NWVmZ5CVSCa1jwsLCSE1NJSMjg9jYWAwGAzqdjpSUFLZt28bLL7/MgQMHltQaIKS1BgcHk56ezrp166S/Lz8HcZ2SkhIyMjLuK8bwOIj7jYuLIyEhgYiICEl58NChQ+zbt09SCFQIrRgiIiJIS0sjKSmJ8PBwQkNDSUlJYcuWLbz00kukpqYyMDDA3NwcWVlZSyKqGo2G6OhokpKSiIuLIyIigoSEBNauXcvBgwc5cOAAhYWFpKSkUFhYSF5eniRAJJ5jVFQUwcHBhIWFUVRUxMGDB9m9ezf5+fnk5uZKadhiXr6YplteXk56ejq6Re2FEFKSExMTWbduHcXFxYSHh6/4ACMiIigqKqKkpITY2FipsN5gMJCUlCQNxCEhIWg0GmJiYigtLeXIkSMcPXqU4uLiJQayQqEgKCiI2NhYEhMTiY6OJjIyksTEREpLS3nppZfYv38/WVlZZGRkUFJSQlZWluQwCQsLIyEhgdjYWMmzuG3bNl555RW2b9/+zNQ/y8g8ryweD5OSkoiNjSUkJITo6GiKiorYvXs3x44dY+/evaSnp6/q0V6OThDI27BhgzRWych8H8iG6vePWq2W5lxxcXEYjUaCg4OlOeOrr77Kzp07pTRdhDpPhLYtRUVFbNu2jezsbMLCwoiJiSE5OZn4+HjCwsIIDw8nIyOD8vJyjhw5wpEjRySHt1gaJM5dExISiIuLkxz+ubm57Nixg6NHj7J//35yc3OX1LU+CKUgFDk4OMjQ0JBUayoaQSpBzTc9PZ34+HgMQque5ORktm3bxrFjx9i5cycJCQnSPEYcbzUaDfn5+dL86H71l8HBwWRkZLB27VrS0tJWjKUqlYrQ0FASExOleVRkZCRZWVls3bqVF198kRdffFGqGRWPMTU1xTfffEN7ezubN29m3759xMfHPzC1VqlUEhsbKz3n4OBg9Ho9aWlp7Ny5k2PHjrFjxw6ioqKWPBe/349Op2PDhg3s2LGD1NRUgoKCJF2ctLQ0YmNj0Wq1BAIBwsPD2bhxIy+++CKvvPKKdO4PemZarVayadLT01fcz0AgQE9PD2fPnmV0dJT9+/ezffv2FTbK84gisFpC9/dMQBCtEXsM6XQ66SGJp6dc1NfU5/NJRcpqtZrg4GA0i1rVBAQlMDGNYW5uDrvdLkVbQ0ND0ev1kpGzfBu3241WqyV4lZ5RXq8Xh8OBx+NBq9USFBT0SBOfh+Hz+XC5XEtqU8Von/gxLb5GFt03m83GjKByrNVqiYyMJDw8nPr6ev7t3/6NtrY2Dhw4wK9+9SsKCgqk7f1+Pw6HA7PZzOzsLF6vl9DQUMIF2XK/oISrENKuxeOL9392dpb5+XkQJNsjIiLQarV4PB58Pp90fxQKBV6vl4WFBTyL+pAtvrc+oYeZy+WSHAbLr9flckk1s3q9foWh6/f7pVpksX5WFM4ICwsj+AHF7OI1zc/PSxLiERERhIeHo9fr8Xg80vsmvjviu+B0OllYWMDpdBIUFERwcLA04C9/f2RkZJ484ve7sLCA2WyW2niJkz2j0fjIY7XP58Mu9EzUCT39HjTBkJF5kvj9fsxmM62trUxOTkrOEpmnS0AQ77FYLMzOzmK32yUHmDgPWD5nEedOSqVSyupCEN9xOBxYrVYpJVSn0xEeHk5ISIhUprZ4LiLWNi4sLGCxWDCbzXg8HoxGo7Td8nnro2C1Wvnyyy/59NNPiYmJ4Sc/+QmbN29eUlrnFnqpTk9PY7FY0Apte8TrXjxu+gWBqYmJCQDJsF9tjPR4PDgEnRWtVrviHrJo7ud0Opdct16vJywsTBKcWn7d1dXV/N//9//N5OQkb731FseOHSMqKuqR7o3L5cJqtTI9PY3NZpOMzuXiViLz8/OMj4+j0+mIiYlZso44t7VarczOzrKwsIBWqyU6Ohqj0YhB6Ff7oPMSf3Pcbjd6vR69Xr/iHCwWC2fOnOH9998nKiqKf/zHf2T9+vV/E4GQZ8JQFREHCqvVytzcHPPz87jdbjQaDaGhoURERBAWFrbCQHkQfkF9zSf0z1QJfVOfZQKL2imIXp2H4RN6hCoW9YatqKjgX//1X+9rqIoEBFW5gKBe+6jHFO8rglfsWbmvotNBvB9qtfqRz+3bXpP4nikXOVRkZGS+XwKBgDRJ9Hq9KJVKdDodOqEO7X7jmuj0E8fd5SgEwb7lkyUZmSeNbKj+9RDnQg6HQ3Kai+VFyw0sFv3uI8wXlo8N4nxCnBsoBH0Qr9crzU2WjyniPFgMmiiVSjQajRTAedz5hV9QuX333XdpaGhg165dvPnmm0s0QFjk7HMKnR4WX/fy6xLnWNznun0+H263G4+gIixew8POf/n9UgoRYfG/xXsVCAQ4c+YMv//970lPT+dnP/uZVDv8qIhjvtvtRqFQoNVqVzyLxeuK80nxOS5HfHf8gtqzQgjqIERLlztJxfU9Hs+S+7Q4UCfi9/tpaGjg97//PR0dHbz++uu8+eabUr3x884zY6iKg3NPTw/Nzc10dHQwMjLCwsICQUFBJCQkUFRUxJYtW8jLy1vx0GVWUlFRwb/8y79Ihuqvf/3rVQ1VGRkZmR8yASFdcm5uThI2swutyfR6vdQOJCoqaoUHWty2ra1NisQuRyOUEaSkpPxNpFrJ/PWQDdW/Dj6fD5vNxtjYGIODg8zNzaFQKIiKiiIjI0NqCfhtDAO32y0JPE5OTjI3N4fBYJDaI2qFlFFRjMdkMjE6OorFYsHr9aLT6UhISCA1NZWYmJjHPo+xsTHef/99zp8/z9q1a/n7v/97ioqK0AitBe12O6Ojo/T39zM7OwtAdHQ0aWlpJCYmYjAYHmhgiogZfuPj44yOjjIn9LXXCX1YxRTZRwk2id/B0NAQVqtVSlE2Go34/X6pprW4uFgSPn2Uc2SRQ3NmZoaJiQm8Xi/x8fGrlhw+KuLzE4W4JiYmmJ2dxWg0kp+fT0xMDCqVSvq9EaO0Y2NjWCwWPB6PZOtkZmZK7YcUQmvIGzdu8O///u9YLBb+4R/+gcOHD6/Q8XleeSYM1UAggNls5t69e5w/f57m5mbsdjtaoTG76G3IyMjg9ddf5/DhwysmGzIrqays5He/+x2dnZ288MILvPXWW+Tl5S1fTUZGRuYHjcvlor+/nwsXLtDc3CxNPkTvfFpaGtu2bWP79u1kZmYucXT6fD5GR0f553/+ZwYGBiRv+GKMRiObN2/m2LFjJCUlLfmbjMyTRDZUv398Ph/T09PU19dTUVFBe3s7drsdpVKJQegZv3//foqLix9Lk8Tn80lCkW1tbXR3dzM0NMTc3BzZ2dm8/PLLlJaWYjQacQvdByorK6murmZkZASn0yllh8XHx1NeXs727dvJzc195PPwer3U1tby3nvvMTw8zKFDhzh69Kg0jonicVeuXKG9vR2Hw4HP58NoNFJSUsKuXbsoKSmR6mnvh9/vZ2BggJqaGmpraxkYGMBms+ERerdGR0ezYcMGdu/eTUFBwUONLLPZTHV1NefOncNkMlFcXMyPfvQjMjIyUCqVTE5OYrFYpBTlR7UJRIdmV1cXdXV1tLS0oFKp2Lt3LwcPHlyhSvwoeL1e5ufnGRgYoKWlhd7eXkkfJicnh5/97GcUFxej0+nw+/309vZy69Yt6uvrGR4exuVy4ROET+Pj49m6dSt79+4lIyODoKAgAoEA3d3dvPvuu1RVVbFnzx7+/u//noSEhAc+k+eFZ0JMyev10tHRwaeffkpFRQVarZaysjJ2795NeXk5eXl5xMXFER8fT1FRESkpKY/0gf6ts7CwgN1uJzIykuLiYvLy8lYorsnIyMj80BEjou+99x7j4+NERkZK4hZiq6/BwUF0Oh1paWmEhIRI23o8Hrq6uvj3f/932tvbpXoti8UiLW63m/j4eEnkTUbmaSFGXGQxpe+P+fl57ty5w5dffkltbS0KhYKkpCT0ej3Dw8M0NTVhs9kkEcnV0l2X4/F4MJlMVFRUcOrUKa5fv053dzdWqxWdIO6Zn59PfHw8Wq0Wp9NJZ2enJBCk1+uJi4vDYDAwJ7QiHBgYAKH3a3h4+CNlFs7MzHDhwgXu3btHdnY2hw4dIisrC7Vajc1mo6amhg8//JCbN2+i0WhITU1Fr9czOjpKR0cHNpuNyMhIoqOj0T1AVM7j8VBRUcHZs2fp6OiQotEGgwGr1Up3dzddXV0sLCyQlpZGRETEqunUCBHozs5OTp06xblz52hvb0er1bJp0ybi4uJQqVQYjUZp//fbz3ICgQC9vb1cvnyZr7/+mps3b1JXV8fk5CQpKSmsXbv2oQb0cjweD2NjY9y6dYvTp09z7do1uru7sdvtBAcHk5qaSklJCVFRUagFYabm5ma+/vpruru7Vzzn9vZ2Ojs7pXckNDRUul6v10tnZyfDw8OkpaXdt93N88YzYahaLBZu3rzJqVOn8Pv9HD16lBMnTrB582ZJ8js/P5+ioiLS0tLQ6/XLdwHCSxgQ6jtFr/jiwWQ1T/mD/n0xD1rnYcddjhjEFtd52LaL/754u4ehFRR6c3Nzyc3NJSYm5oFep0fZ/4PuA6ucKw/Zn4yMjMx3JRAIsLCwwMzMDGVlZRw5coTt27ezbt064uPjmZiYoL29Ha/XS05ODqmpqdK45HK5qK+v56uvviIhIYFjx46xZcsWqe2CuIgq7/f7/ZH54eIX6gb9i2oJ/1oE/oqGakCoxfN6vSBoZDzveL1eWltb+eKLL6ipqSE5OZlXXnlFUubV6/V0dHTQ2tpKREQEmZmZ9xUPEvF6vYyPj3Pp0iU+/fRTmpubiYiIoLS0lB07drB7927KysrIyMiQ9iWmHrtcLrKzszlw4AC7du1iw4YNpKSkYLFY6OzsxG63k5SUREpKykPHokAgIPVEFXuRlpeXExoaisfjob+/n5MnT3L58mVSUlJ44403OHLkCBs2bCAoKIj+/n56enoICgoiPT2dsLCw+1631+ulu7ububk5cnNz2bdvH3v27GHjxo2kp6fj8/no6OhgYGCApKQksrKyVj1/n8/HyMgIly9f5vr168zOzuJwOIiPj2fXrl3fKYro9/u5c+cOX3/9NePj42g0Gux2O36/n+LiYkpLSx/LUPX5fAwPD3Px4kU+++wz2tvbiYiIoKysjJ07d7Jnzx7Ky8tJTU0lWFAsVigUzM/P43Q6ycvLY//+/ezatYvS0lLS0tKYnZ2lsbERq9VKfn6+lI4s1viOjY3R0NCATqdj7dq10n6fZ54JQ3VqaoorV65w7949UlJSpP5SoaGhBAUFYTAYiIyMJDIyctVi6cAi9dvp6Wmmpqaw2Wz4/X5UKhV+vx+73S4Vx4s/RF6vF7vdjtPpJCAICS1/4B6PR9pWIQgVKYRibq9QdG+xWJiZmZEU03yLhJsW788vqNIuLCzgEwqzxTSEyclJ5ufn8fl8kvhPYFHNwtTUFPPz80vO434fq09QUXM4HCDUVy0uEhfvwWLcbjcLgpKyuM7icxfPZfF9XOzFEq9tbm6OqakpSf1M/OFffi9kZGRknhQqocVBTk4OmzZtIj8/n6SkJJKTk0lOTmZ+fp6Ojg5pclBUVCSNsQ6Hgzt37nD9+nW2b9/O22+/zdatW1mzZg0lJSWUlJRITtJHrdWS+eHgE9RbR0dHJcXOBwlvPW3E39rJycnv1VANCHV74+PjTExMoFAo0Ol0z/37Pjs7y9WrV7lw4QJarZZjx45x5MgR8vLySEpKIiYmhunpaerq6vD5fJLxcL9Ilt/vZ25ujps3b/Lxxx8zODjIxo0bOXHiBIcPH5bGp+W1n2LULCMjg3Xr1lFQUEBqaiqJiYmkp6fjdDrp6OjAYrGQlpZGfn7+QzPknE4nN27c4Pr16yQlJXHw4EEyMzPRaDRYLBYqKyv54osv8Hg8/OxnP+Pll18mOztbavM1MzNDa2srDodDqtN9UFRVr9eTk5NDWVkZ69atIz09XdIHCA0NlQxfo9FIaWkpkZGRy3fB/Pw8FRUVfPPNN5KBajabn4ihGggEGBoawuFwsGnTJnJycpiZmcFut1NUVMTGjRsf2VANBAJMT09z9epVPvnkE4aHh9m8eTNvvPEGhw8fZuPGjeTl5ZGYmIh+Uf9UhdCqMTMzU3rOKSkpJCYmkpqaCsC9e/cwmUxs2LCBnJwcafugoCDMZjN1dXVYLBbWrVsn9bd9nnkmDNXZ2Vnu3btHa2srUVFRlJeXk5aWdl8FrsX4Bans/v5+amtrpWbJHR0dzM3NEQgEsNlstLa2MjQ0hMFgkGS5p6enaW5upqenB6/Xi0Hot7p435OTk9TV1dHX14dKpSIkJAS1Wo3b7cZkMtHa2sq9e/eorKzk7t27tLa2Mj4+jtfrRS+0YRFfIofDIdUqiMXT/f393L59mxs3btDQ0MDk5CRqtRqDwYDL5aK3t5fKykpu3LhBbW0tIyMjeL1eqWXN8hfU4/EwOTlJa2srVVVV3Lp1i3v37tHW1sbExARuofXOchW7sbEx6urqGBgYQKlUStcpItZP1NfX09/fT0hIiJTL7/P5mJ2dpa2tjTt37nDr1i2qq6vp6enBYrGg1+sxGo33HdhlZGRkvgsKQbUxMjJyyeRPdOoNDw/T2NhIIBBg06ZNrFmzRhr/bDYbV65cobq6WopiREdHoxfaBIiL9iGKlTI/TJxOJ62trVy/fp2JiQnCwsIICwt75HRCEbHGzO1243a7v3WEVoyoTk5OsrCw8L0Zqn6/n4mJCW7evMndu3dRq9XEx8f/VY3274O+vj7Onz9Pe3s7hYWFHD16lNzcXNRqNSqVCr1ez8LCAs3NzYyPj5OXl0dOTs59BY3E9+mTTz6hqamJrVu38nd/93ds3ryZ2NhYgoQ2WcvHEtExEBoaisFgkOZL4r+PjY3R2NiI0+mUesk/zFCdmJjg4sWL9PT0sH79enbu3El0dDQA4+PjnDt3jurqaoqKinjzzTfJysqSgiAhISGYzWba2tqYmZkhMTGRvLy8JWUTi1EqlVIfWLFVoUKIIOqFFjd9fX10dXWh0WjYtWsXcXFxS+6hy+WiubmZr776iuHhYdauXUtcXBwDAwNERkZ+Z0NVoVBgMBjIy8tjw4YNqFQqmpqamJ6eprCw8LEMVbfbTX19PSdPnqSrq4utW7fy85//nPLycimodj8bZvlzFu+TRqPBZrNx4cIFbDYbu3btWtI/Vq1Ws7CwQFtbG0NDQ2RmZpKTk/OtBaB+KDwThqrb7WZgYEASUYqMjJR6FS1+iMsJBAJYrVYaGxs5c+YMZ8+elYzU/v5++vr6GB8fZ3BwkMuXL9PZ2UlGRgYJCQkoFAq6urr44osvqKysRK1WS14fETEl5MMPP+TevXtERUVJDYvn5uakFILKykp6enoYGBigs7OTlpYWqR4qPj5eGtDm5+e5desW58+fZ2BggPHxcW7fvs21a9eoqamhvr6e1tZWbDYbwcHBjI6Ocu7cOS5dukR1dTUNDQ20trZiMpnQC3ntiz01Xq+XwcFBLl68yFdffcWtW7dobW2lp6eHrq4u2traGBwcxOv1EhkZSUhIiPTB19fX8+GHH9LQ0EB4ePgKdUubzcbdu3c5efIkdXV1ZGVlkZGRAYs8YF9++SVXr16ltbWVvr4+enp6mJqaIjo6WlLMk5GRkXmaBBaVYoiOu5s3b9LY2EhiYiL79u0jOztbGjetVitnz56lvb2dQ4cOkZOTg0qlwie0Frjf74/M84HFYqGqqoqLFy8yOztLUlKSpCDq9XofuviEVhyimEpfXx8jIyOMj49js9kkg2f5dg9aHA6HtL3Yj3H5Ok9y8Ql93Pv6+vjmm2+4e/cukZGRFBQULJljPG/4/X5aW1u5fPkyVqtVEisSjTkRu91OXV0dnZ2d5ObmUlJSsmr6r9/vZ2pqiosXL3Lx4kViY2P5yU9+QlFRERaLhYmJCeyCGrloEK52bxePYT6fj7m5OaqqqqipqSE0NJRt27ZJBsyD6Orq4sKFCzgcDrZu3cq6deswGAz4fD4GBgY4deoUAwMD7Nq1i927dxMRESFtq1armZubo62tjdHRUeLi4li3bh0RERGrnjMPGSutVitNTU20trYSGRnJvn37iI+Pl9b3+/0MDw9z9uxZqqqqpPRnt9tNU1MTERERT8RQDQkJISoqSppj371791sZqlNTU5w/f55r166RlpbGj3/8Y/Ly8pibm2N8fBy73S4940d5zl6vF6vVyu3bt7l58yZJSUkcPnyY7OzsJU4Rt9tNf38/TU1NxMfHs2nTJvSrpFA/TzwThqparcbj8TA4OCgZlw6HA+Wi3kti6ujih+1yuWhtbeXjjz/mwoUL2O12CgoKKC8vJzMzE4/HQ0dHB/X19TQ3N+P3+ykvLycjIwOFQkF3dzdff/01XV1dJCYmUlxcvCQVwefz0dbWxqlTpxgaGqKgoIDCwkKCg4OlegGTyURCQgLbtm2jvLycuLg4xsfHqa6uxmw2k5WVRXx8PGq1WvpBvHLlCl1dXYyMjGC320lLS6OgoACdTkd3dzednZ3MzMzQ1tZGT08PMTExFBUVERERwfj4OJ2dnTgcDtLT00lISEAlSF6Pj4/z1Vdf8cEHH9Df309KSgrbtm2jrKyMuLg4ZmZmaGhoYGBggJCQEFJSUqSPsq6ujq+++gqTyUROTg4FBQVS5BlhkKmpqeH8+fOMjIywdetWCgsLCQQCNDU18f7771NVVUVUVBQ7duxg06ZNxMfHExYWRmZmJqmpqQ9MGZGRkZH5rgSEWlWLxcLs7Kykrnjp0iVcLhf79u1j79690oQsEAgwPz/P559/Tn9/PxkZGSwsLDA8PIzJZMLpdKIRehh+28mRzLON3W6ntbWVtrY2fD4fISEheL1epqamGBsbw2QyPXAZGxtjdHSU1tZWKioquHPnDo2NjdIE3+l0YrFYVmx3v2VsbIzh4WEGBgaYnJzE6/U+1vbfZhkbG2NsbIzu7m5aW1uZm5sjMzNTEpdZbZL9POB2u2lsbOTmzZsoFAq2bdsmGaEiYtZeXV0dra2t5OTkUFpaSkRExIoxwe1209vby5kzZ+jp6WHr1q1kZmbS3t7OtWvXuHPnjjS/CwQCBAcHr8jUCAgp2BaLhfn5eUkJWHSklJeXs2fPHpKTkx+apdbU1MS1a9fQ6/Vs376dnJwcdDodLpeLzs5Ozp8/j8ViYf/+/avWZ4rq0319fURHR1NaWkpMTMyK634Yi6P1nZ2dFBUVsXfv3iUOAbPZzJUrVzh37hxBQUEcPXqUNWvWMDg4SG1t7RMxVJczNDT0rQ3VlpYWTp8+jclkorS0lKysLJqbm7l27RqVlZV0dnYyOzuLUlCOXp6Z4Pf7cblcmM1m5ubmGBwc5N69e5w8eRKr1cpLL73Enj17JPEokYCQvrx4vv08f6M8S4ZqSEgIWq2W6elpenp6aGtro7e3l6mpKVwuFxqNRoqwikxMTHDmzBnOnDmDRqPh2LFj/OxnP+PAgQOUlZWRn5+P1+ulqamJoaEhUlJS2LVrF+np6SiVSkZGRrh79y7z8/MUFhaydu3aFYaqmJrrdDqllDHxPGJiYiT57m3btrF+/Xry8/MJDg6ms7OT3t5eSdlNr9djt9tpaWnh7t27TE1NkZqayquvvsqPfvQjaRCxWCw0NTXR1dVFIBBg//79/PjHP2b//v3k5+cD0N/fz+TkJMnJyeTm5qLX63G73Vy/fp0//vGPjI2NsXfvXn7xi19w5MgRNm/ezJo1a4iLi2N6epqWlhbm5+fJzMwkOTkZlUpFZ2cnd+7cwev1sn79eoqLi5cM1gsLC3R2dlJbW4vP52Pfvn0UFBTg8/m4fPkyX331FWFhYbz++uu88cYbbN++nfXr17N27VoyMzOXRG9lZGRkngY+n4+WlhYuXbpEZWUl58+f58KFC7jdbg4dOsSrr75KVlaWNBb5hLYUX3/9NSaTiampKerq6rh9+zbV1dX09/fjcrkICQkhNDRUHsOeQ8Tftu7ubmw2G5OTk3R2dtLQ0EB9fT0NDQ0PXBobG2lsbJR+t8fGxpiammJqaorx8XEGBgZoa2t75P01NDTQ3NxMd3c3w8PD9Pb20tzc/FjbP+4iXoNoRCkUCnJycp57Q1WMlFZWVhIUFMSWLVukKLJIQOgzWl9fT1tbG+np6WzcuJHo6OgV6eE2m436+nouXbrE9PQ0cXFx9PT0cPv2bSmzTbzn09PTGAwGoqOjl0TMvF4vXV1d3Lhxg1u3bnH58mXOnTvH9PQ027Zt49ixY1KbnAfh9/uldjtRUVFs376d1NRUNBoNCwsLtLa2cuPGDQKBAPv27aO4uHhF1pvVaqW5uZmOjg6ioqLYsGGDFHh5HOx2O83NzZw7d47Z2VmOHDnCli1bpGvweDzU1dVx8uRJJiYm2Lt3L4cOHSI4OJjW1lbq6uqeiqE6PDz8rQxVn8/H7du3pWh1aGgoXV1dVFZW0tvbS3d3NzU1NdTV1TE9PU1UVBSRkZHoFvWPdblc9PT0SL9VFy9e5MyZM5hMJg4ePMjrr79Odnb2km1EhoaGqKioIDQ0lO3btz8wyv088GSe9hMgKiqKAwcO8Otf/5qXX36Z6OhoGhoa+I//+A/++3//77z33ns0NDRgt9tBeFGGhoaora3F7XZTXl7O0aNH2bBhAwkJCSQmJrJu3TpeeuklysvLn3gOt16vJzU1lcLCQpKSklCr1ZJBnZubS1paGjMzM/T19TE3NyelkSEMfBEREezcuZP9+/eTm5tLSkoK5eXl7N69m4SEBPx+PwUFBRw4cIA1a9aQlJREcXExO3bsICsri4WFBQYGBpidnZXSTW7fvk1XV5dUZyFGUo1GIykpKezcuZPDhw8THx8vffxms3nJdT0uPkGpzuFwoNVqCQkJITg4GIPBQHx8PGlpaURGRq4Y0GVkZGSeNKKh+sEHH/DBBx/wzTff0NPTQ0REBIWFhcTHx6+Y5Gi1WqlH6saNG8nNzSUqKoqJiQlOnTrF//gf/4OTJ08yNDRE4K/fdlzmKeLxeJiZmWFoaOixluHhYaampnC73ahUKtRCDaLb7WZqamrF+g9bRkZGmJ6eZm5uDpPJxNDQEIODgyvWe1LL4OAgw8PDTE5OSoKNfwt4PB5JRFKpVKLT6VbMVRRCbaCY2ed2u3G5XKuOBWJt8czMjJTqOj8/z+bNm/nFL37BL3/5S7Zv347D4eDrr7/m888/p7OzE5cgYolwTt3d3Xz55Ze8//77nD59mtbWVrRaLdnZ2SQmJj5SdprX68Vms+F0OiVRUtHA9Hq9kqinVqtFr9evuG6EIJJarSYg1E27XC78fv/y1R6Iz+fDZDJRWVlJf38/aWlpbNq0aUnd9cjICOfPn6ezs5OSkhJeeOEFEhMTUd+nxvOvjdPplERDp6enJd2ZrVu38vbbb/PrX/+anTt3YrPZ+Pzzz/n000/p6+vDI/SURXhXurq6+PTTT/nLX/7C2bNnaWlpISwsTAosLY/CIohuBQcHExwcjM1mw2KxPPYz+aHxTERUEQaD4OBg0tLSKCwsJDMzk4iICFxC3URLSwuzs7PExcWRkJCA0+nk3r17nDt3Dp1Ox0svvURZWdmSGlPxAY+OjtLc3Ex4eDg7d+6UIqrDw8NUVVUxPz9PQUHBqhHVvr4+KioqcDgcbNy4keLiYqmw2Sc0cx4dHaW9vZ2amhqqq6tpbGykrq4Ok8lEdnY2GzZsIDo6GofDQXNzM83NzURFRXHo0CFKSkokIzoQCDA1NUVDQwMul4u9e/eyY8cOwsLCpMFyYWGB9vZ2hoeHpZqB6OhoWltbOXXqlOSNOXToEFFRUUsmZRqNhkAgIHmPIyMjKSkpISYmho6ODiorK6WIalFR0YqIakdHBzU1NXi9Xvbu3UtBQQEKhQKTICo1NjaG1+tFK6gmimrDyyeGMjIyMk8Lp9OJXlCfzMjIQKfTYTKZGBkZQaVSER8fj9FoRLFI6KOoqIjdu3ezb98+9u3bx9atW0lOTsZsNtPe3s7Y2BiRkZHk5uY+0iRR5oeDGFHt6uoiKCiIkpISSktLKSwsJC8vj/z8/IcuOTk5REdHS7VmKpWKoKAg4uPjWb9+PRs2bCA/P/+R9yfOfyKFHuhr16595G2/7ZKbm0tkZCRWq5WFhYW/iYiqKJJUV1eHwWCgrKyMrKysJZHFQCCAxWLh7t27NDU1kZWVxZYtW1aNLJrNZmpra6murmZhYYHNmzfzm9/8htdee42ysjI2bNhAQUEBgUCArq4uKeqakZEhiRQFBNVnnU5Heno62dnZGI1GpqenGRsbw+/3ExkZSWho6IrjL8bhcFBTUyN109iyZQtxcXEolUocDgednZ1UVVURCATYuXMnubm5KwI68/Pz1NbW0tbWRkxMDJs3byY5ORnNA9ocLiYgKONev36d06dP4/F4OH78OPv27ZPEOK1WK6dPn+b8+fOkpKTw2muvSZFNu91OW1sbdXV1REZG8sILL6zqbPy2fNuI6uzsrJR1I5YU/upXv+LEiROUlZVJ37zdbqezs5OxsTGys7PJyMiQoucBoVuJVquVRJGMRiPDw8MMDw+jVCqlQNNiJ4IYpKuqqgJgx44dJCYmrupoeF54ZgxVEbVaTVhYGFlZWZSUlEhpWiMjI3R3d6NWqyksLEShUFBVVcW1a9eIjIzkwIEDq35oTqeT7u5u6urqMBqNT8xQ9Xg8DA8PU1FRwZkzZzh//rykzNvR0cHw8DBut5vCwkLKy8uJiYmRDNWmpiZCQ0PZsmULWVlZ0kfv9/sZGRmhqqoKs9nMpk2bpOJ3cVI1NzcnKe8mJCSwadMmYmJiaGxs5PLly3i9Xl544QXKyspWfHBKpRKXy0VbWxudnZ1ERESwadMmkpOTv7WhKnohnU4nQ0NDdHR00NHRIdXfBgUFyYq/MjIy3wvij/umTZvYtm0bmzdvJiMjg/n5eaqrq+nr6yMqKors7GzJWy16qI1GIwZBFT46Oprc3FzCwsIYHh6mq6sLg8FAcXExMTExyw8r8wNGNFQ7OjqIjIzk0KFDHDhwgI0bNy5pUXS/Ze3ataxZs4a0tDQiIiKIjY0lIyOD3NxcNm7cyN69e6Xax0ddsrKyMBgMhIeHs2PHDnbs2CH18n0ay9q1ayksLMRoNNLb28vExAT5+fnPvaEqRrUaGhrQarVs2LBhRX9Pv9Bu5vbt2zQ1NVFYWMiOHTuIiYlZYRyIrUOampqIjo7mrbfeYu/evYSGhkqR9vDwcBQKhVQHHxYWRlFREdHR0dJ4FBMTw9q1a9m2bRtbtmwhPz9fqqft7e0lODiYlJQUQkJC7vtsXEJ/6NraWpKSkigrK5NamYgCplVVVbjdbrZu3UpeXt4KJ9z09DTV1dV0dXWRnJzM9u3bSUpKWnHd98NsNnP79m0+/fRThoeH2b59O6+//jrp6emoVCo8Hg9VVVW8//77TExMsGXLFoqLi/EJAlJjY2M0NTXR2NiIXq+noKBAGrc1Gs13Nli/raE6MzPDnTt3aG5uloSUdu/eTXh4OCqVCpVKRVhYGMHBwTQ2NkqaMbm5uYSHh6NUKlGr1cTGxrJ+/Xq2bt3K1q1byc/Px+PxSF1QEhISpH654nP2CSWJFRUVqFQqXnjhhcd6Jj9EvttTfkqoBEnwxMREduzYwU9/+lN2796Nx+OhsbFRaifjcrnweDyoVKr7vrSigbfax7xa6sZyVtvWK6jrfvXVV/zxj3/k5s2bqNVqdu/ezS9+8Qv+7u/+jjVr1hAQFL0el2+zjcvlwu12Sykqy8+ZRSksYnqLV1D74xGOudr+RFJSUjh+/DhvvfUWW7ZsweVycfHiRf7X//pf/OUvf6G1tXVJaouMjIzM00Kr1UqGZ1xcHDt27OD1118nPz+fzs5Obt26xcTEhLS+QqFAKSgziota0E0oLS2lpKQEhZA5MjU1teRYMj98tFot0dHRUr/HuLg4QkNDMRqNhIaGPnQJCQkhPDyc7Oxs9u3bxxtvvMGPf/xj3njjDfbu3UtGRgZGo1Gqc37YEhISIpXQiCmb4r8tX/dJLeK+Y2JiSE1NJS0tjdjY2FVTD58ngoKCJINCTJVdnJ7JMnEjr9dLSEgIhof0U1YLGiarGZNarZb4+HgSExPx+XxMTk5is9mWzMHUajV6vR6DwUBUVBRlZWUcP36cdevWMTExwd27dxkYGHjgvEqtVkstUvyCerB4DK1WS1hYmBRkENslLsfhcGC321EIvT+XR/cexPz8PJWVlXz22Wd0d3ezbt06Tpw4QU5OjhS4mJ+f5/r16zQ3NzM7O0tdXR3vvfce//qv/8o///M/8/vf/56rV68yPT1Nb28v7733Hv/zf/5PampqVtyz7xPx2SuVSqKjo0lNTV1iTCoEh0NeXh7JyckEBLHTxWm64nxc/K2Kiopi06ZNvP3226xZs4bR0VFu377N6OjoktJBBBvE4/GgEcRmn3fu/6U9AyiVSoxGIzk5Oaxfv56YmBhmZmaYnJxEqVQSFBSERqPB4/HgcrlWPEyEQcbn8636t8VG6OKPeDnL/91qtVJbW8vFixeZnJxk27Zt/OpXv+KXv/wlP/rRj3jppZfIycn51obq46IQGgGLam4LCwt4vd4VxxZVxmw2G16hF6uY4rJ4IF2+3f3+TUSj0ZCZmckrr7zCb3/7W9555x02b96MxWLhm2++4dKlS4yPjz9wHzIyMjJPGqWguJiTk0NaWhoejweTycTs7OzyVVegEFoZREREoNPp8Ag9MmWeL/R6PSUlJbzyyiscPHiQtLQ0ydn7OIs4+Y+LiyMuLo7Y2FjCw8MlY+9Rl+Us//vTWlQqFQkJCezbt48333xTyspSrHJOzwtarZbw8HBCQ0NxOp3MzMzgdDqXrBMQUn/n5ubQarVSa5PVDFW1Wo1BUHgVAymrzXvUQu2nQkgBfdBcUSlkrWVlZZGZmYnX62VkZITJyckHjkdarRaDwYBOp8PtduNwOKR5sEajITIykvDwcFwuFxMTEzgcjuW7kK5bpVIRHh6OwWB4JEPVbDZTWVnJyZMnaWlpoaCggOPHj7N+/fol75TT6USpVJKamkp8fDwWi4Xu7m7a29vp6Oigu7ubiYkJad46ODhIR0cH09PTq85xvy8MBgOhoaFL7I/VzkWn0y0JHK22DoucpUFBQeTl5VFYWIhOp2NoaIiZmRm8Xq+0rt/vx+l04nA4JGfGau/i88QzcXUP+kjFB6gWah3FRfSCRkRE4HA4GBsbw2azLdnW7/djt9uZmprCarUu+Zu4D41Gg1foX7R4gAoI+eNms5mFhYUl52c2m+nq6mJ8fJyEhAR27dpFWVkZycnJhIeHL1Fw+z5QKBTExsYSGxvLgtBaQfyQF+N0OiUZ+kAgQHx8vFTQrtVq0Wq1uN1u7HY7brd7yTWL3ka3273qtWm1WmJjY1m3bh1Hjx7lxz/+MeXl5TgcDpqamjCZTM99wbeMjMyzyeLJoN/vv+/vzWICgQA2m435+Xm8Xq8U2ZJ5vtBoNCQnJ7NlyxbWrVv3ncT/xPmJ6gE9Mh+FR3k/nzRKpZLQ0FDWrFnDzp07ycjIeO6jNSqViqioKOLi4qTypdnZ2SWBDbfbzejoKFNTU5JApBg98wn9Z12CyJBOp5PqCqenpxkZGVlhAAYEFWGr1SoZjPczfBezeAx7lPdDpVJJ0d+FhQXMZrMUNVWpVERERJCeno5arWZgYIC5ubklczS32834+DgTExMEBweTlJREsNC3VTSWnE7ninnd/Pw8FRUVfPrpp7S1tZGfn8/x48fZsmWLlPYsEh4ezuHDh/nHf/xH/tt/+2/8l//yX/jNb34jLT//+c/ZunUrERERpKWlceLECd555x3J4PULrYNmZ2exWq1PzXj1+Xw4HA7pORuNRpKSkggLC2N+fp7R0dFVnQaiIJpCoSAqKgqjoI3wMMTfqNV+q9xuNxaLBbfbTVhYGCF/Ax01nomrcwvKeOPj48zPz0vRUdGAHBgYoKOjA7PZTGxsLAkJCej1elJSUsjIyJCkw3t6erDZbFKag0XoddrS0rJC3VapVBIcHExYWJjkoRobG8PhcEgf4dDQEM3NzZhMJgKBgOR5dLvdUlTSYDAQFhYmDVwOh4P+/n5GR0el9Z82KpWKlJQUCgoKUKvVNDc3U19fv8TrJA62NTU1DA4OEh0dTWFhIVFRUQCEhYURERGB3W5ncHAQk8kkeeBsNhvDw8N0d3czPz8PiyKwASEtxm634/V60el0REdHk5GRIfVOtdls9/U4ycjIyHxXvF4vMzMzTE9PLxlrfD6fJIg0MDCAWq0mLi5O6qMq/k7Mzs4ucc55BPXXuro62tra0Ol05OTkkJCQsOS4Mj98FEI0NDQ0FMMiZdS/RVQqlTSn+b4d7n8t4uPjycvLQ6vV0tvbS0dHh2S0eTwexsfHqa+vZ2JigpycHLKzs9Hr9Xi9XsbGxqipqaGhoYHJyUm0Wi3p6elkZGRIYka9vb2SERMIBDCbzXR3dzM4OEhwcDCZmZmEh4cvGYsWFhYkA1A0xsSWh0qlkoSEBKKjox/qSAgPDyciIgKr1bokAqtUKgkPD2fNmjVERkbS2dlJW1sbZrNZmj+PjIzQ0tIiGeg5OTkYDAa8Qo9hUahpcnISn8+HX6jlraio4JNPPqGxsZGMjAxeeuklSktLCQ4Oxul0srCwgMPhwCtk9RUXF7Nnzx5JBFRcDh48yO7duyksLCQkJITY2Fi2bdvGnj17JJG8qakp7ty5wzfffENTUxMWi+WJzzMDgQBjY2NUVVVJbYUUCgWZmZlkZ2djsVhoaGhgZGRE+u0JCP28xfl2REQEWVlZREZGSr9Jc3Nzkr3BosBaS0sLHR0duFwukpOTiYiIWOI4s1qtjI+Po1AoiIuLW5Jy/LzyTIgpTU9PSwpaJpMJu92OzWZjYmKC1tZWrl+/zq1bt3C73ezZs4d9+/ZJnpmZmRk6Ozul1FKtVovX62V6epqmpiauXLlCdXU1c3NzJCYmSmJKYmrG8PAwnZ2dzM3NodPpCA4OxiUoDd+6dYtbt24xMDCAwWBg06ZNFBcX4/f76erqor29HZ/PR0JCAqGhodjtdnp6erh69Sq3bt3CYrGQn5/Pli1blogpNTY2EhwcLCnMaRaJKQ0ODnL79m3m5uYoLS1dIWYwPT1NTU0NfX19JCUlUV5eTkJCAkFBQbhcLknC3uFwoNPpUAtKwQMDA9y8eZMLFy4wPT3Nli1bePHFF0lLS0OpVOL1eqX+taIIUlBQEHa7nY6ODq5du0ZVVRUmkwmj0ciePXsoKCjA4/FIQhRWqxWXy8Xc3BxdXV1UVVUxOjpKbm4u27dvJyEh4bn/oGRkZL5f/H4/s7OzXLx4kdbWVnw+H263G6vVKk0kz549S2NjI0lJSbz44ouUlZWh0+kwm83SBER0upnNZklk48yZM7S3t5Obm8vLL7/MunXr/qYNGZmnT0BoBTI1NYXdbichIUHKfJJ58mi1WmkuKIpgGo1GlEol4+Pj3Lp1i/Pnz+N0OnnxxRfZuXMn4eHhzM/Pc+PGDT777DNaWlrQ6/UkJSVhNBqx2Wz09/czPDyMSqXCaDRKzrT6+nrOnTtHZ2cnOTk5HDhwgOzsbGw2GzU1NTQ2Nko1o3a7ncnJSakH6d27dwkNDWXPnj1s2bJlRWeH5bhcLjo6OhgYGCA+Pp6CggKpi4RKpSIQCDAwMEBnZydut5twQQxocnKSGzducPnyZZxOJzt27OCFF14gLi4Om83G7du3+eCDD6iqqiIiIkLqxHH79m0+/vhjKioq0Gq1lJSUkJqaisvlkpTXh4U2SGKatFi2Js45Fy8ej4eOjg7q6+uJjIxk//79pKWlSen0dXV1fPTRR9y5c4fQ0FCysrJW1AQ/CHGcn5qaorCwkNLSUoyLREQRnJZnzpzhww8/pEPoJxsbG0twcLCUXWkymVAJ2jo+n4/5+Xmampo4efIknZ2dbNq0iSNHjpCVlSXN4VtbWzGbzVLga3JykpaWFk6dOkVFRQVGo5FXXnmFjRs3Erqoh3d/fz+XLl1iamqKvXv3sn79+oc6LH7oPBOG6vj4OFeuXOHq1as0NDRI3p2amhpJac3n87F582Zefvll8vLyUAuiQRqNhrm5OakX2NDQEH19fTQ0NFBbW8vIyAh+v5+FhQWioqIkQ1WtVqMSVMfGx8cZHh5mZGREUheura2lp6dHMiIVCgWlpaUUFRURLPQvGhoaYmxsjOnpacbHx+ns7KSurk6K7LrdbtLT0ykvLycuLg6Hw0Frayutra0YjUbKysrIzMxcYqgODQ1x9+5drFYrGzZsWGGoigPd4OAgKSkplJWVkZCQgFqtxmg0EhCKtoeE3m7Dw8O0tbVRWVlJZWUlMzMzrFmzhldeeYX169dLqRxarZaFhQVpIBkdHWVkZIT29nbq6uoYHBxEpVLh8/lQqVTs2rWLwsJCLBYLN27c4JtvvqG1tZXu7m4aGhqoqqqiu7ubqKgo9u3bR2lpqZw2JyMj88TxCArsH3zwATdu3GBgYICuri6ampqoqqri6tWrdHR0EB4ezqFDhzh8+DCJiYn4/X4mJib4/PPPOX/+vJS509jYyO3bt7l+/Tp9fX2kpKTw8ssvs3v3bikDRUbmaSEbqt8vKqGVkFi/Pjg4yOjoKIODg9TW1nLr1i1mZ2fZtm0bx44dk4IL4+PjXL58mQsXLmAymUhMTCQ/P5+YmBgMBgNOp5OBgQH6+voYHR2lt7eX2tparl+/TmdnJ4mJiRw6dIitW7cSFhbG6OiopOnR1tZGT08PLS0t3Lt3j2vXrlFfX49Wq2X79u2ScStqjNwPtVrN8PAwra2t6HQ66fzE1HRR3Xh0dJTu7m5MJhPDw8PU1NRQUVHBzMwMGzZs4PDhw+Tn5xMUFMTs7CyXLl3i7Nmz9PT0kJGRQUFBAWNjY3z++edcv36d2dlZdDodXkF4tKGhgbq6Ompra6mrq6O7u5vo6Gji4+PR3kf8E8Bms9He3k5jYyNRUVHs2LFDak/j9/u5fv06Z86cwel0rmgf+SiMjIxQW1vL3NwcRUVFlJaWYlik+hsIBHA4HHz44YdcuHCByclJKaoeGRmJXq9nYWGBoaEhKZNStD9Ex2l6ejqvvfYamzZtIiwsjL6+Pi5cuMC1a9ekObP4nK9evUptbS1arZZDhw5x5MgRUlNTJcPc4/FQX1/PN998Q0hICK+88oqkoPw880wYqm63G7PZLKU9TE5OYjKZpCJqMRL64osvsm7dOsm4UqvVhIaGEhERgVKpZH5+HpPJxOjoKHNzcxiNRtasWUNERASDg4MYF7WnUavVaDQaDAaDVJs5NzfHxMQE09PTBAIBCgsL2bZtm5QOtG7dOnJzcyVFPpVKhd1uZ2JiQqphUKlUFBYWkpWVhUqlIj09nfXr1xMdHY3X65WEPJKSkigtLSU5OVny0AcCAWZnZxkaGkKn07Fx40by8vKWfHg2m01KMRBFpqKjowEIDg4mJiaG0NBQ3G43k5OTkgE/OTmJXq9n06ZNHD16lPLyciIjI6X9ajQajEYjOp0Oh8MhPQdxwFmzZg2lpaVS8faWLVvIyMjA7XYzPDxMT0/PEuN4YWGBtLQ09uzZw65du577Pk8yMjJ/HcSUqbGxMSYnJxkbG2NwcFCaOIhjpdh2JCcnB61WK6VnDQwMSJPToaEhBgYGMJlMKJVK1q5dy0svvSS1AHhQ9EJG5kkgG6rfLwpBjFIUTbNarZKhOj4+jkajYfPmzbz66qvS/FOhUEhlUuPj40RERLB+/XopYhkSEkJMTAw6nW5JIGVwcBCn0ymNR7t27ZJaiywsLEhz37GxMWksGhoawmq1kpKSIqXIFhcXP1LkUKvVYrVa6ejoYH5+nqSkpCUKtTqdTjKszWazNAaOjIyg0WjYuHEjR44cYf369VIk1uFwMDg4yMjICAaDga1bt1JUVITJZKKpqQmn00lUVBShoaEEhHpcm82G1WrFZrNJ5XkFBQWkp6c/MMXc5XIxPj7O1NQUaWlplJeXEx0djVKpxG63c+XKFWpra8nPz+fAgQNkZGRIgZ9HYW5ujtHRUVQqFSUlJRQVFUnGO8K74fP5aG5uZmxsjJiYGLZs2SL1tg0LCyMmJgatVsv8/Lz0zAYGBjCbzRQWFnLs2DF27dpFXFwcarVayhYVbZXFz9lisZCWlsbBgweloNzi+f/k5CRXr16lrq6O9evX8+KLL66o+30eUQSedEL3t8DtdjMzM8PIyAhDQ0NMTU3hcDhQCUpjYi1qfHz8Cg9SQBC86O/vl/p3ut1uKQ0gPj6eGzdu8D//5/8kNjaW/+v/+r/YvXu3tB8x376rq4vu7m7m5ubQaDQkJSVRVFRETEwMfX19jI+Pk5WVJfXYcrvdmEwm2tvb6evrw2q1YjAYyMzMJDc3F4/HQ09PDwaDQeqR5Xa76evro6+vj6CgIPLz86VoKMKES0zzsNls5ObmkpmZueRDFlMNxsbGiI6OpqCgYEXv15mZGXp6eujq6mJqagqPx4PBYCA5OZm8vDzS0tJWLer2er2Mj4/T1tZGb28vVqsVvV5Penq69MH09fVhNpspLi4mLS0Nn8/H+Pg4XV1dDA8PY7FYQKiNyMjIIDMzU/qQZWRkZJ40fkFTYHR0lK6uLgYHB7FYLPh8PjQaDTExMWRlZZGdnU1MTIw0kRFTfcWsk+HhYWkSpdfriY+Pl8bgcKH3nYzM08bv92M2m2ltbWVycpINGzaQnp6+fDWZJ4zo3BfVZs1mszQXLC4uJiMjY0m0Tey/29LSglqtZs2aNdL8MCDogiyeT1ksFlRCj9Tc3Fyys7OJjo5GrVZLY9HExAS9vb309/czOzuLR2i/GBERQUZGBjk5OY9dlzgwMMC7777LzZs3KS8v56c//amUlYjwvk1PT0u1kWazGbVaTXJyMoWFhaSnpy8R7HE6nfT29lJTUyNlOmZlZWEymejo6GB2dha/IAIkLsvRC0rb6enp6HS6+16Lw+GQUpPDwsIoKSmRAiy9vb38P//P/8OdO3c4ceIEf/d3f0dqaupjBUSmpqZob29nfn6e9PR0cnNzV9gYfr9figSLmZCi/grC/RCvvaenB6vVilKpJCoqiuLiYql3qnheCwsLjI+P09vby+DgoPSc1Wo1YWFhZGdnk5eXR1xcnBRJRcgcunPnDv/xH//B2NgY77zzDi+//PKSd/J55ZkwVEX8fj9utxu3243f70exqO+n+FHdD5+gvuYUVMg0Gg1BQUFYLBZOnjzJv/zLvxAXF7fCUGWRwq/T6ZQGBp1OJ31AHo8Hv9+PSmjYLL444vk6nU68Xi9qoSeSRqPBLxTii9egEuoBvF4vXq8XpaBkvPyj8vl8eARJc/UiCXMRv9+PV+h/Kp7PahMor9eL0+nEJaiUqYWeWjqdbtX1RcR7IRa7i/dfTM8Q74V4buI2Xq8Xt9uNV1AaFrdTqVT3HYRkZGRknhSLx3G3IIykUqnQarUECf0EV0OcVIrjv7idOF4uH6NlZJ4msqH612Px/Mfj8aAUWoYEBQWtOm8Sxw2FEJVdPl8T13E4HLiFjgniuLLauuJcyrVISVghiH0FCe0Yl2/zMFwuF9euXeP999/H5/Px2muvsWfPHiIiIpbsa/F5imnB9xv/PB4PCwsLKBQKgoODUavV+AQBVP8jdnfQaDQPnR8GhPaS4rPQaDTSc7h+/Tr/43/8DwKBAG+99Rb79u0jNDR0+S4eyOL59GrzbRG30A1DLfS3XX7e4nuzsLAgzft1gubNavdvtecsXp94P5djMpn4+OOPOXv2LGvXruUf/uEfpMzN551nylB90vj9fqampvj000/513/91/saqjIyMjIyMjIyf21kQ1XmSTM2NsZXX33FvXv3WLNmDceOHftB1zb6/X7OnDnDp59+SlFREa+++uoSYdLnDb/fT0NDAx999BHT09O89tprvPDCC1IZ5PPOShfRc8Zir8dqnhIZGRkZGRkZGRmZ55G4uDj27t3LSy+9RE5ODhqNZtWU3B8KgUCApKQkXn75ZQ4ePEhKSsqqUcjnBb/Qo7e0tJTXXnuNsrKyv6lg29+EoarX64mIiCA0NPRbpU7IyMjIyMjIyMjI/NBQqVRkZ2dz+PBhdu7cSWxs7KqpzD8UFAoFhYWFHD16lJKSkiWdMZ5HlEolGRkZHD58mL1790qCUn8rPNdXKhqpBQUFHD9+nEOHDpGcnPyDTXeQkZGRkZGRkZGReRyUSiXBwcGEhYXdt+b2h4J4LXq9/rmOpIosf3bPs1G+Gs91jSpCyFwU2BAN1+c1j11GRkZGRkbmh4tcoyojIyPzf/jhulQeEaVSiU6nIzQ0lJCQENlIlZGRkZGRkZGRkZGRecb5qxmqoiz0anLWAaER+8jICF1dXZhMJtxu95J1HheFQvFMh8v9fj8zMzNLengtvy8yMjIyMjIyMjIyMjJ/C3xvqb8+nw+Hw8Hc3Bxzc3NYrVZcLhcAQUFBhISEEBUVRWRkJEqlkoGBAa5du0ZfXx9r165l7969xMXFgdAEeHZ2FoVCQXh4+BPJt/f5fNjtdqxWKyqVStrv94XD4eD27ducP38eg8HASy+9xLp169BqtctXBcGYd7lcTE9PY7FY0Ov1xMTE3LeoXLy+2dlZvF4v0dHRhIWFrbqujIyMjIyMzPePnPorIyMj839Q/dM//dM/Lf/HJ4nf78dmszEwMMDdu3e5ePEi58+f5/Lly9y+fZs7d+5QVVVFc3MzVquVqKgogoODGRwc5Ouvv+bWrVuEhIRQUlJCREQEHo+H9vZ2Tp8+TWdnJwaDgYiIiO+U0hsIBDCbzTQ0NHDlyhUGBgYIDw8nIiLiOxvAj4rT6eTWrVucPHmSyclJCgsLH9gXyufzYTKZuHDhAqdPn6a7uxuDwUBsbOyqTYudTiednZ2cO3eOe/fuERYWRmJi4vd2fTIyMjIyMjIPRnRCT01NYbfbSUhIIDw8fPlqMjIyMn8TPFUrxefzMTMzw927d/nggw/43e9+x+nTp+nq6sLhcKDValGr1dhsNjo6OmhsbGRmZkZKCbbb7ZjNZhYWFvD7/QQCAZxOJy0tLXz66aecPXuWtrY2HA7H8kM/Fn6/n7m5OWpqajhz5gwXLlygp6cHn8+3fNWnhvjjZLFYsFqtuN3uB/a58vv9zM/PU11dzVdffcXHH3/M119/zeDg4Krn7fF4GBkZ4datW1y8eJHBwUE5tVhGRkZGRkZGRkZG5pnkqRmqfr+f2dlZqqqqOHnyJBcuXMBqtVJcXMwrr7zCr371K37729/y29/+lrfffptXX32VjRs3EhUVJclNr1ZXqlQqpb6o4eHhBAcHf+d2MwqFArVaLck/i/tdfuynjXi9q133cgKBAF6vF6vVytzcHMPDw1y7do07d+4wPz+/wggVDeH5+Xnm5uZwOp1L/i4jIyMjIyMjIyMjI/Os8NQMVbvdTktLC2fPnuXevXuEh4fzyiuv8M477/Dmm29y8OBBdu7cyc6dOzly5Ag/+tGPVvQ5XW6sKRQKdDoda9eu5a233uLNN99k7dq16PX6JestJxAI4PP5VhhvIgqFgoiICLZs2cKPf/xjXn31VXJzcx9qAAcCAWl5EH6/H5/Ph8/ne+i6rHLd90Pcl9FoJDo6mrGxMS5fvkxraysLCwurHutRjGAZGRkZGRkZGRkZGZm/Jk/FUPV6vZhMJm7evElNTQ1Go5HDhw/z6quvsmnTJlJSUggNDUWr1RIUFER4eDjJyckkJSWh1+sfaEip1WpiYmJYt24dJSUlREdHo1arpYjh7OwsMzMzLCwsSP89MDBAZ2cnPT09jI+PS6nEIgqFgqCgIJKTk1m3bh1FRUWr1qcGAgHcbjfz8/OMjo7S19dHT08Pg4ODTE5OLklR9ng8mM1mRkdH6enpob29na6uLoaHhzGbzXi93iX7/i4YjUaKi4tJTEykoaGB69evMzo6uuIYspEqIyMjIyMjIyMjI/ND4KkYqg6Hg66uLqqrq7HZbGzYsIHdu3eTkZFxXxXbR8Xv9zMyMsLVq1epqqpibGwMj8cjiQvduHGDCxcu0NLSQmdnJ5cvX+a9997jd7/7HX/4wx/44osvaGpqWtL+JSC0w+np6eHOnTs0NDQwMzOzJCLp8/kwm810dnZy5coVPvroI/7whz/w+9//nj/96U+cPXuWrq4unE4nPp+PsbExbt68ySeffMKf//xn/vjHP/K///f/5qOPPuLmzZuMjo5+55Y7COeuUqkoLCxk27ZtBAIBKioqqKurw2w2rxpVlZGRkZGRkZGRkZGReZZ5KoaqzWajp6eHsbExIiIiWLduHRkZGQ9NpX0UfD4fnZ2dvPfee3zxxRf09vbicrnw+XyMjo5y6dIlPvnkE06dOsWXX37Jl19+yY0bN7hz5w5ff/01f/7zn/nwww+pr6/HZrNJhpzFYqGuro7PP/+cixcvYjKZpGOKPU4rKyv54IMP+NOf/sTnn3/OlStXuHnzJpcuXZKMY7vdjtPppLm5mVOnTnH58mUaGhro6OigurqaL7/8kr/85S9cvnwZk8m0qvDR4yK2m9m9ezdFRUX09/dz48YNuru7v7PQlIyMjIyMjIyMjIyMzPfNEzdUA4EANpuNkZER3G43SUlJpKWlYTAYlq/6rbFYLPT19TE8PIzVapXSbV0uFxMTEzQ0NHDx4kVqamoIDw/nyJEjvPHGG2zcuBGz2cy5c+c4f/48Q0NDeDweKVV3dnaWkZERJiYmltR42mw27t69y1/+8hfOnTvH7OwseXl5Ujrz3r17yc/PJzQ0FKVSSUAQOoqIiGDnzp385Cc/4a233uLEiROkp6fT1tbG2bNnaWxsZGFhYfnlPTZiRLmgoIDdu3djNBqpra3lzp07TExMrEgBlpGRkZGRkZGRkZGReZZ5Koaq3W5nZmYGv99PdHQ0ERERkpLvk+B+6rhKpRKFQsHCwgIOh4Pi4mL+/u//nrfffptf/vKX/PrXv+aFF17AbrdTU1NDZ2fnCkNR3J/4vz6fj76+Ps6cOcPdu3eJi4vjJz/5Cb/97W/5zW9+wzvvvMNvfvMbfv7zn1NeXk5oaCh6vZ5Nmzbx9ttv8/bbb/OjH/2I1157jZ/97Ge8/vrrpKenMzQ0RHNzM7Ozs0uO/23w+Xy4XC6MRiNbtmxh06ZNzM3NcevWLZqbm5dEjmVkZGRkZGRkZGRkZJ51nrih6vf7cbvdUsqpXq9Hp9N9LyI+4jGCgoIoLi7m4MGDbNiwgcjISCIiIti4cSO7d+8mOjqamZkZhoeHpfNcbPSK/ysa3fX19dy5cwej0ciLL77IsWPH2LBhA4mJiURHR5OcnExWVhZxcXFoNBrUajVJSUkUFBQQFRUl7QcgISGBpKQk/H4/o6OjzM3NfWcjMhAISFHl7Oxs9uzZQ3JyMm1tbVy/fp2BgQE8Hs/yzWRkZGRkZGRkZGRkZJ5JnrihimDoiSmwj9OW5bsiHiM4OJi0tDRSUlKWRHJ1Oh0JCQnEx8fj9/ux2+0PTIsNBAJMT0/T2trKxMQEWVlZbN68mZiYmIfW2wYCAaxWKx0dHVy4cEGqbT116hSdnZ1YrVZsNhtOp/OJ3huj0Uh5eTm7du1CqVRSVVXFvXv3mJ2dXTUKLSMjIyMjIyMjIyMj86zxxA1VpVJJUFAQISEhKBQK5ufnsdls9+1h+jRQKBRotdpV0401Go3Ud/VhBnQgEMBsNjM+Pg5AYmIisbGxaDSa5asuwev1MjQ0xOnTp/mXf/kX/vmf/5k//elPfPrpp1y5coXe3l4cDgeBR+jB+rgoFAqSk5PZtWsXJSUlTE5OcuPGDXp7ewHQarWyoSojIyMjIyMjIyMj80zzVAxVo9FIbGwsCoWC0dFRTCYTLpdr+apPlSdhAAYEUSSPx4NKpUKn00l1sPfD6/UyOjrKF198wf/7//6/VFVVkZSUxMsvv8xbb73Fm2++SWlpKaGhocs3fWJotVqKi4t54YUXiImJoaOjg3v37jE3N4dWq13RH1ZGRkZGRkZGRkZGRuZZ4qlYLCEhIaSlpWE0GhkdHaW5uZmJiYknYjw+CcTzeJDByaLIbFBQEG63m/n5eRwOxwNbyrhcLurq6jh16hQzMzMcOnSI//Jf/gu/+c1v+NnPfsaRI0coLi7GaDQu3/SJEh0dzdatW9m6dSs+n4979+7R1taG2+1GpVI9M89CRkZGRkZGRkZGRkZmOU/FUDUYDOTl5ZGXl4fH4+HOnTvcuXPniQgHfZ8oFArCwsJISEhApVIxODhIX1/ffXuTBgIBnE4nXV1ddHV1kZSUxI4dOyRRJaPRiFarxefzPfVUaKVSSUZGBjt27CA9PZ2RkREaGhqYmZmR61RlZGRkZGRkZGRkZJ5pnoqhqtPpyM7OZufOnaSlpdHV1cWXX37JhQsX6O/vx2Kx4HQ68Xg8uN1uFhYWmJ+fx2w2S31NnwUUCgWRkZEUFxeTmprK4OAgV69epb29nbm5OVwuF263G6fTid1ux+Vy4fF4sNvtOJ1O1Go1QUFBUq3swsICw8PDDA0NSSrATxODwcDatWvZtm0bISEh9PX1MTo6itfrldN/ZWRkZGRkZGRkZGSeWZ6KtaJUKomKimLbtm0cOnSI5ORkmpqaeO+993j33Xf5+uuvuXXrFtXV1VRVVXH16lXOnDnDtWvXMJlMUmqt2HJlOaII0XIxosCiNi33Y/F2i6Oaq+1ToVBIxt6OHTtQKBRcu3aNjz/+mPPnz3Pnzh2qq6u5desWN2/epKurC5/PR2xsLBEREZhMJurr6+nq6qKnp0e61ra2Nklg6n7n8KiI+1htO6VSSXx8PFu3bmXt2rUoFArm5uakVjXL15eRkZGRkZGRkZGRkXkWeCqGKoKgT3p6OkeOHOH111+nuLiY6elpvvnmG/7whz/w7//+7/z7v/87/+t//S9+//vf8/777y8xVFUqFUFBQRgMBoKCgpakqqrVagwGAwaDAbVaLf1t8Tb3692qVCrR6/UYDIYlCrhKpRKNRkNwcDBBQUFSxFGlUpGZmcnLL7/Mvn37UKvV3Lx5kz/+8Y/S+f/hD3/gs88+o7m5mUAgQHFxMeXl5TidTs6fP8+7777L+++/z6lTp+jt7SUkJISIiAiphU8gEEChUKDRaDAYDOj1elQq1arnL6IQWgDpdDqCg4PRaDSrRkmDgoLIyclh+/btFBQUEBYWhl6vX1URWUZGRkZGRkZGRkZG5llA9U//9E//tPwfnxRqtZqwsDASExNJTEwkIiICrVaLx+PBYrFgNptxuVzodDri4uLIz8+noKCAiIgI3G43ZrOZ4OBgSkpKKCoqIiQkBIDZ2Vnm5ubIycmhtLSUpKQk1Go1drsds9lMSEgIJSUl5OfnYzAYlpyTzWZjZmaGsLAw1q5dS25uLgaDQTqe3+8nIyODdevWScrFGo2GqKgo4uLiCA0NRalUSsey2+2o1WoSEhIoKCggIyOD6OhoDAYDPp8Pi8XC1NQUFouF0NBQ1qxZQ15eHtHR0aSmplJcXCz1dZ2dncVms5Gens6mTZtITk6+r0Hp9/txOp3Mzs6i1+vZtGkT+fn56PX6JQauQhCEEo1fvV5PZmYm5eXlpKenP7QfrIyMjIyMjMz3QyAQwOVyMTU1hd1uJyEhgfDw8OWrycjIyPxNoAh8D/mfPp8Pu93OzMwMU1NTTExMMDMzg9PpJCgoiMjISGJjY4mNjSUmJga9Xo/NZmNoaIj5+XliYmJIS0sjODiYQCCAyWSis7OToKAgyTBUKpXMz88zODiI1WolPj6elJQUqWeqyPz8PL29vdjtdhITE0lOTkan0+F0OhkbG8NkMhEcHEx6ejoRERFLjD6Hw8HExASjo6OMjo5iNptRKpVERESQkpJCSkoKkZGRqFQq5ubm6O7upru7G7PZjNFoJCMjg7S0NACmp6dRKpWkpqYSHR2Nz+djbGyMvr4+NBoNWVlZxMTE3NeQ9Pv9WK1WBgYGmJ2dJTk5mdTUVHQ63fJVQTj3sbExRkdHUSgUZGZmkpCQsGoUVkZGRkZGRub7x+/3YzabaW1tZXJykg0bNpCenr58NRmZx2ZxBt+DMvZknj3+lp/d92KoLsbn8+FyuXC5XPj9flQqFVqtFrVajc/nIxAIoFKppBYqfr8fpVK5JMXX6/XidDrxer1oNBopVTcg9D0V9ytGIxfvF5AEm9RqtZRiGwgE8Pl8eL1eFAqF9LfliMcQxaDEiKVOp1sR/RSFlTweD2q1WkrRFY+FkFosXqt4fACNRrPq8Rfj9/ul6118Lash3ktx//e7PhkZGRkZGZm/DrKh+tdnsX6IUqn8qzn0F2uQqFSq73QeTqcTi8WC3+8nJCQEvV6/Yn9P+rq/7f6+7XaPgzjnDgQC0jHuN39+2vj9fnw+n1TSt/x6/UJgymazodPpCAsLQ6PRLFnneeZ7N1RXIxAIMDc3R19fH3a7XYpQhoWFrXhgCIbn+Pg4AwMD6PV60tLSCA8PX2J4iQax1WrFYrHg9XoxGo1LajT/Wi+ljIyMjMzTIyC0ChOdkkFBQUs0CZbj9/ux2+2SA3E5CqEERKfTyQ4+maeKbKj+9fB6vTgcDiwWCzabDYVCQUhICKGhoQQFBX3nb9/tduNyuQgEAmg0GrRa7Yp9BgIBPB6PZFharVYAjEYjoaGh6PV6NBrNfcey1fB4PHR2dtLU1IRer2f9+vVLSst8Ph9OpxOz2Swdb/l1P87xVruPoaGh9zWQRcTtrFYrVquVQCCA0WgkJCSE4ODgJzJvd7vduN1u7HY7VqsVj8dDUFAQISEhi6IWRAAA//RJREFUkr7N/c7vURCfn8PhWPLbs3yfYtBLvE9Wq3XJfQoODl4SXGtvb6e+vh6DwcDmzZultpl/CzwThqrP56O5uZlPPvmEvr4+MjMzOXToEBs2bJDqUhfjdDq5ceMGJ0+eJD4+nldffZWioiIpzdfr9TI7O0tPTw9tbW0MDg7idDqJjY2V6mCTkpJWiDTJyMjIyPxwCQQCuN1uLBYLPT09jI2NEQgEKCoqIisrC61Wu3wTAoEAVquViooK5ufnJU/+YrRaLcnJyRQVFREWFrb8zzIyTwzZUP3r4HK5GB8fp6Ojg46ODsbHx1EqlSQlJVFYWEhBQQHR0dHf2jhwu9309PTQ09OD1+slNTWV7OxsSfcEYSxaWFhgcHCQrq4u+vr6mJycJBAIEBsbS2ZmJnl5eaSmpmIwGB5p/hoIBBgdHeXUqVPcu3ePkpISXn31VdLT01EqlXi9XiYnJ2lvb6etrY2xsTEUCgWJiYkUFhaSl5dHbGzsIxvHHo+HsbEx2tvb6ezslO5jcnIy+fn5FBUVERUVteI+ulwuRkdH6erqoru7G5PJhN/vJzY2lqysLIqLi0lKSrqvUOqjIN7bvr4+hoaGMJlMOBwOQkJCSEtLIy8vj5ycnBWBr8fB5XLR3d1NR0cHTqeT4uJisrOzlzyvQCCAw+FgdHSU9vZ2ent7MZlMACQlJZGbm8uaNWuk++7z+aivr+ejjz5icnKS48ePs3///lXto+eRpyqm9Kj4fD7a2tr46KOPuHnzJqOjo+j1elJTU4mMjFzhiXA6nVRUVPDee++xsLBASUkJqan/P3vvGR3HeeXpP50b6ICcc84EAQaQBEUxiFmiJMukPfLKWZ6Z3bO7Zz/s7tlv83F353hm9z/jsT22PF5LpkSRYqYo5giAAQSInHMGGuhGd6Nz+H/proNMSqZkkq7nnDq2iKrqeqveeuu97733d1NRKpXCS1ddXc3Jkye5cuUKnZ2dDAwM0NzcTHt7O3a7nejoaPR6/ZJwXRERERGRF4/gJK+1tZUbN25w8uRJLl26xKNHj4iLiyM7O3vZHH6v18vAwAD/8A//wPXr16mrq6O+vp66ujpha2lpwefzkZubKwrbiHyt+EUxpW8cl8tFf38/ly5d4vTp01RXV9Pb20tPTw/Nzc309vaiVCqJi4tb1SO4Ej6fj8HBQU6dOsXx48d59OgREomE1NTUBRUgbDYbTU1NnDhxgnPnztHa2srk5CTDw8O0tLTQ2tqK2WwmLCxMECd9Ek6nk5qaGi5cuIDX6+WVV14RHDsej4eRkREuXbrEp59+SnV1Nf39/fT09NDU1ER/fz/SQLlJnU73xHZ7PB76+/u5ePEip0+f5t69e/T09Cy4jwqFgvj4eEJDQwXDLejxvXDhAmfPnuXBgwf09/fT19dHU1MTHR0dzM3NERcXR1hY2FcyIn0+H/X19Xz22WdcvHiR+/fv09bWRnt7Oy0tLbS0tDAyMrLgOX9Zg9jj8TA6Osof//hHTpw4wZ07d4iKiiIjIwONRiPcP7vdTktLC+fOnePMmTM8evSIwcFB+vr6aGhooLW1FZ/PR0xMDFqtVvC+j46Ocv/+fcxmM/n5+ULfedl5LgxVn89Hf38/t2/fZnR0FKfTidvtJiYmhpSUFEJDQxfs73Q6aWpq4s6dO0RERLBlyxbS09NRKpWYzWbu37/Pp59+Sm1tLfHx8ezYsYO1a9cikUhobm6mq6uL0NBQUlNT0Wq1fxEPWkRERORlxu1209zczG9+8xvOnTtHV1cXfX19TE5OUlpaSllZ2RJxPQLfk+bmZn79619jNpvJzMwkJiaGsLAwwsLC0Ov1REREkJmZSWFhIXq9fvEpRF4A5gePfdkJ6DfJi2ioBu/t83xfV2NsbIwvvviCzz77jNHRUQoKCti6dSuZmZlYLBYeP37MyMgI8fHxJCUlrZpGsBwmk4lLly5x4sQJamtrmZ6eJjk5mTVr1hATE4NUKsXtdtPT08PHH3/M6dOnUSqVvPrqq+zcuZOioiIkEgkdHR10dnYik8lISUkhPDz8ifPX4eFhzp07R1tbG+vWrWP37t3Ex8fj9/uZmZnh8uXL/OEPf2BgYIDi4mJeffVVcnJysFgstLS0MDExQUREBElJSU803qampjh37hzHjh1jfHycwsJCtm7dSnp6OiaTifr6eoaGhkhOThbuI8DAwADHjx/n9OnTmM1mSkpKqKysJD8/H4D29nZaW1tRq9VkZ2ej1WpXvY7l8Hg8XLx4kcuXLwOQk5NDaWkpeXl5aLVaRkZGaGhowGg0kpaWRkJCwpdyZPn9fkwmE5cvX+b3v/89bW1tDA4OsmbNGkpLS4Vn5fP56Ojo4NNPP+XChQu43W42bNjAtm3byM3Nxe128/DhQzo7O4mJiSE5OVkoxymVSunu7qa9vZ34+Hhyc3OfarHiRee5MVT7+vqoqqrCZrOh0+mwWq1CeMTiWGyXy0VzczNVVVVERkayefNm0tPTkUgkdHd3c/r0aaqqqsjOzuanP/0p3/rWt9iwYYPw8tXX1wtlYBISEpZdZRcREREReXFwOBw8fPiQ06dPk56eztq1a5mdncXhcFBZWcm6detQq9ULjvEHclkfPnzI1atXKSsr4z/+x//IgQMH2Lp1K6+88gpbt25l69atlJaWEh0d/aUmLyLPB/55eX++gPjgl53oflO8aIaq1+vFbrfjdruRLiME87zjcDi4d+8ex44dY2RkhO3bt/PDH/6QvXv3snbtWuLj4xkcHKSurg61Wk1eXt6XCg31er08fPiQo0ePMjo6iiwgoFlYWEh5eblgqM7OznL79m1OnDiBz+fjpz/9Ke+++y7r16+npKSEjIwMLBYLTU1N2O12MjMzhVDYlfD7/Tx48IDz58+jUqnYs2cPJSUlhISE4HA4aG5u5sMPP6StrY29e/fyk5/8hN27d7Nu3TpiY2MZGxujubkZv99Pdnb2qqHPXq+X6upqoZ2vvfYa3//+99m9ezdlZWXExcUxODhIY2MjMpmMNWvWEBERgdvt5uLFi3z88cc4HA4OHTrEe++9x86dOykvLyc7OxuHw0F9fT3Dw8OUlpaSmJj4lcZhk8lEbGws+/bt4/XXX2fbtm1s2rSJ0tJS1Go1XV1dDA4OEhkZSUlJyZLylqtht9upr6/ngw8+EIz7ubk5tmzZQnl5uaC5MzMzw8WLFzl+/DhSqZTvfe97vPfee1RWVrJ27VoKCwsZHx+nrq4Ol8tFbm4u8fHxKBQKQkJCmJ6epra2Fq/Xy7p169Dr9c/tWPaseG5GFH9Adjk2NpbS0lKioqJobm7m1q1bjI6OLt59WaxWK+3t7TQ1NSGTydi2bRtbtmwhOjqasLAwSkpK2LNnDykpKQwODtLc3Mzs7OyClVYRERERkRcPhUJBbm4uP/3pT/kf/+N/8M477xAfHw+LvGmLcbvdjI+P43a7ycnJobCwkMLCQoqKiigqKqK4uFjQNVhtUijyfOIP5IN1dXVx8+ZN6urqMJvNi3cT+Qp4PB7Gxsaoqqri6tWrtLW1CcqyLwqTk5M8evSInp4eEhMT2bFjByUlJURGRhIXF0dFRQU7duxAo9FQX19PZ2enIIj0JIIhvxcuXKC3t5eCggJyc3OXjeyw2+1CecXCwkI2bNhAYmIiKpVK8CQGjbvZ2VkMBgMul2vxaRYQnBNPTk6SlJRETk6OYHyZzWbq6+tpb28nMTGRAwcOUFpaSkREBNHR0WzZsoVXXnmF0NBQ2traaGlpwWq1Lv4JAbPZTE1NDR0dHWRmZrJjxw6Ki4uJjo4mMTGRTZs2sWPHDrRaLffu3aO3txe3283ExAQ1NTWMjIxQUlLCrl27hBSLiIgICgsL2bt3L+np6XR3d1NXV4fJZHqq+z8fmUxGZWUl7733Hrt27SIrK0soi1lUVMTOnTtZu3YtbrebpqamVdu6mGDI85kzZ+js7KSyspKcnJxlvZ39/f08ePCAmZkZ1qxZw549e0hLS0On0xEREUFZWRmHDh0iKSmJuro62tramJubw+/3ExERQX5+PlFRUXR1ddHd3Y3b7V78Ey8dz42hSuClDgkJobi4mA0bNuD3+7l16xYPHjxgbm5u8e4L8Pl8mM1m+vv7MZvNZGRkUFRUtGAlUqFQkJGRQUFBAU6nk76+Pqanp/EESraIiIiIiLyYKBQKCgsLeffddyksLHzq1XCPx8P4+Dh+v3/VWtQiLyY+n4+ZmRkePHjAqVOnuHHjBuPj44t3eyJBg3d0dFQQxenr62NqauqZThYlEongdZN9SbXVbxq3201fXx+XLl3i448/5vjx49y8eZPe3l6sVusLYbCOj4/T3d0NgXDQoPANgdIoer2egoICEhMTGRgYoLu7G5vN9kRDyefzYTQa+eKLL7h58yaZmZm8+uqrJCYmIguUJJyPP1BC0BcoRxPc5v/dHyilolAoUCgUT/ReB/uqVColLS2NqKgo5HK5cG3Nzc2CYZyZmblAYDQiIoKcnBySkpKYnZ0VnulKjI6O0tnZicfjIScnh/T09AVjqU6no6SkhJiYGMbGxujo6BDm7AMDA8hkMrKzs5eMwSEhIWRlZZGbm4tUKqW1tZWZmZmv1LdCQ0OFnM/571XwOQcXNo1G41O/0z6fj4mJCa5fv87du3fJz8/n4MGDaLXaJc+YwH0aGhpCq9WSm5tLTEzMEi91UVERaWlpmEwmBgYGBJE/iURCfHw8WVlZGI1G2tranrhY8TKwei//hgk+1OAqVkZGBv39/Vy7do329vYVSwcQCDswmUwMDw/jcDhISkpaNsY8GGsfXEWfnp5+6g4pIiIiIvJ8IgnUvw6WU1hukrAcHo+HiYkJfD4fTqeTjo4O2traGBkZYW5u7itNiESeH3w+HzabjZmZGaamphgaGqKzs1MQeXnarauri7q6Os6fP8/HH3/MJ598wqeffsq1a9doaWmhu7t7yTFfdRsYGGBiYoLp6WmGh4eX/P152Xp7exkdHWV2dpaJiQlhMeDUqVPU1NQI87GnfRe/aTweDwaDgYmJCUJCQkhJSVkSSimTyYiJiSEqKgqTycTo6OgTDVV/QBjp4cOHXLhwAYlEwq5duyguLl4gIjQftVpNYmIiOp2Ozs5OamtrGR8fx+Px4Ha7GRgYoKWlBbvdTlJSklC5YjUmJycZGxtDp9ORmJi4oDLG9PQ0AwMD+Hw+UlNTl7RbIpEQFRVFTEwMbrebqampVds9NDTE5OQkOp2O1NRUwSgOolKpSEpKIjo6WmiP2WzGZDJhs9mQy+VotVrUavUCA1wqlaLRaAQF3OHh4Sc6rlZjuXtP4Jl5vV5kMhkajWaJ8bgSFouF2tpaLl26hEql4u2336awsBBpQCBrPsF+YbVaUSgU6HS6ZX8nNjaWhIQEFAoFU1NTC6IUIiMjSUtLw+l0MjAwgNPpXHz4S8dzlaN6584dnE4n5eXlFBcX4/V6hRIDer2erKwstFqtkKN69+5dIiIi2Lx5M0lJSYyMjAihwqWlpWzZsoWIiIgFv+X1euno6KCmpga1Ws3atWtJS0t74gsvIiIiIvJ8I5FIkEgk+Hw+xsbGuHHjBhMTE2zevHnFHNWZmRlOnjxJX18f7kC9uoaGBnp7ezEajfgCkT6ip/XFxOfzYTKZhHIfwbqFfX19NDc3C4qfT9qampp4/Pgx9fX1dHV1MTQ0xNDQEKOjo0JZjcXH/ClbZ2cng4ODDA8PP/NzP6uttbWVnp4eJicncTgceDwezGYzY2NjjI2N4XQ60el06HS6JU6D54FgXuHdu3eRy+VUVlZSVFS0IBrD7/djtVqFMMzs7GzWr19PZGTkskYGAU9zV1cXn3zyCU1NTezatYtDhw6hVqupra2lv7+fzMzMBTmqwbHLYDDQ1dXFyMgIDocDm81Gf38/V69e5d69e0RGRrJnzx42btxIRETEqoZXY2Mjt27dQqfTUVlZSWZmJkqlErvdTmtrK1evXsXpdPLaa6+xdu3aJSHJZrNZECCNjo6mvLyc2NjYZdtdU1PD7du3USqVVFZWCkZ5EIlEIuQDd3V1kZycTEVFBXNzc9y7dw+DwSCkWuh0ugXtstls1NbWCnnCu3btIikp6Yke5afF4/HQ3d3NtWvXGB8fZ9OmTbz66qtPLP/icrloaWnh5MmTdHV1sWPHDt566y3UajXXrl2js7OTjRs3UlZWJuSodnZ2ClGi+fn5y4r8OZ1Obt68SVtbG8nJyZSXly/Q6hkcHKS6uprw8HC2bt26ZJHhZePZPOVniNfrxev1EhUVRUVFBaWlpZhMJiG3xOFwCPvOX63w+Xw4HA6hgK9SqUShUAh/DyKXywkJCUEmk+FwOARxBRERERGRvyyCq+hxcXEUFRXh9XoZHh6mtraW48eP88///M988MEHVFdXYzKZFh8u8gIhkUjw+/2YzWba29u5d+/el9oePnxIa2sr09PTOJ1OwYgYHR3l8ePHS/b/U7ZHjx7R0dFBf38/DQ0NS/7+vGwPHz6kq6sLq9WKRCIRvEjBe1xXV8fQ0NBz6/VxuVxYrVbsdjtyuZzQ0NAlBrVEIkGlUgkho3a7HbvdvuK80ev1Mj4+ztWrV3n06BGFhYXs27eP9PR05HL5Ei9bEJVKRW5uLm+88Qbr16+ns7OT3/72t/zDP/wD//iP/8ixY8ewWCxs3ryZyspKYmNjVzXUvF4vZrMZm81GSEgIYWFhQtvcbjdWqxWXy4VarUav1y87Xw7mxxIwFm0224qRjcH7qFQql3hFmRfxEvRWWq1WnE4nCQkJxMfH4/F4hBqqVqsVfyAU2mq10t/fT29vLw6HQzDonyVGo5GWlhb6+vqEPFGtVrt4twX4fD5GRka4fv06jx8/Ji8vj/379wvhwysRHR1NfHw8VqtVUAYORh0EPa7Nzc309/cvG42gUCjQ6/Wo1WrMZvMLlxP+VVi5l/+ZCD6UkJAQcnJyeOWVV0hLS6Ojo4Pr168zMDCwbEf1+/14PB5cLhc+nw+ZTLbkRQkiDSjT+eblA4iIiIiI/OWh0+l4/fXX+ff//t/zox/9iHfffZeDBw9SUFDA7Owsly9f5vjx4zx+/FhME3mB8QcEG0NDQwVhmS+zZWVlkZiYKEzcg4aZXq8nLS1tyf5/ypaZmUlCQgLR0dHP/NzPcsvOziYlJUXwFgXnU3K5nPDwcGJiYp5bbyoBY87lcuH1epFKpcjl8mXnjVKpVMgXDjpTlsPv9zM7O8vDhw+5desWGo1GECkKlnYJbsF5aJCgIReskapQKHC73ZhMJsbGxpiZmcHlcuFyuXA4HLjd7lXnrm63G5vNhtPpFIzHoEfO5/MJx8tksie2O7ig5/F4VvxNl8uFx+NBtkputSSQfy2RSHC73fh8PhITEwXPcnNzMxcvXqS6ulooSXP79m3Onj1LY2MjDocDnU63JMf0TyFoGN69exer1cratWuF57Uas7Oz3L9/n5qaGiIiIti/fz9FRUWoVCqkAQ8586J8gqSmpgrnf/ToESdPnuT+/ft0d3fT2trK9evXBQ+ty+VCo9GgUqmEc0ilUtRqNWq1Grvdjs1me+kN1ecu9NflclFeXk5RURGRkZGo1WpMJhMdHR1MTU0RFxdHRkYG3d3dVFVVER4eLoT+TkxMcP/+fUFNq7y8fEnNO5fLRVNTE1VVVWg0GjZt2kROTs4TO6WIiIiIyIuB7ylDfyUSCUqlkoSEBHJycsjNzSU3N5eCggKysrLw+/30BHIGw8LCyM/Pf2I4mMjzRTD0t6Ojg4GBAaKjo9m2bRvbtm0TFJ6fZsvLyyMmJkYwasLCwoiOjqa4uJht27ZRXl6+5JivshUUFJCRkSGogG7YsIENGzYs2e952HICKrJTU1PMzMwAoNfryczMZMOGDWzatInc3Fx0Ot2yhtCfG4fDQWtrK3V1dYSEhLB+/XqysrIWjBNB47OmpobGxkZyc3PZsmULsbGxCwzwoDestbV1gfrrrl27CAsLw+12Mzk5yYMHDxgYGCAlJYWioiLByHe5XPT29nLp0iVqamqIiopi9+7dQj3XkJAQjEYjY2Nj+Hw+YmJiiIiIWHERwOl08ujRI2pra0lOTmbTpk3ExcUhlUpxOBz09PRw7949vF4vr7zyyrI1OY1GI48ePRLqdm7ZsoXk5ORlf7O2tpba2lo0Gg3r168nOzt7yXhrNpu5ffs2ra2tZGRksG3bNlJSUlCpVFitVkZHRxkYGGBgYIDe3l4aGhqEsjQGgwGLxUJZWRk7d+4kOjr6T+5TLpeLtrY2zpw5w/3790lJSeHtt9+mvLx8xVxi5t3bU6dOMTQ0RGVlJdu3bycsLAyXy4XJZOLGjRt0dXVRVlZGXl6eEMmp0WiQy+WYzWaGh4fp6+tjcHCQ3t5e6uvruX//PpOTk0xOTjI3N8crr7zCpk2biIyMRCqV4vV66e/vp7q6GolEwquvvkpSUtKy4dgvC8+toVoYKKyuDqiQjY6O0t7eDkBmZiZGo5Gamhr0ej2bN28mJSWFmZkZ6uvrMRgMFBQUCHHh8wnmJFRXVxMVFUVlZSVZWVli/pGIiIjIS8KXMVRlMhmhoaGEhoYSEhKCRqMhPDyc2NhY9Hq9IGKi1WopLS0lISFhwTlEnm/8gRzDgYEBxsbGSExM5NVXX2XNmjXEx8c/9RYXF0d0dDQREREkJyeTm5tLfn4+a9eupbi4mNTU1CXHfJUtLi6O8PBwvF4vcrmc4uJi8vLyluz3PGwRERFYLBa6u7uxWq0kJCSwdu1aKisrqaioICsri7CwsOd2Eu3xeOjp6aG+vh6pVEppaSnZ2dkLcit9Ph8Gg4Fbt27R1NTEmjVreOWVV5bUFPX5fIyOjnLp0iUuX76M2+0mNzcXuVzO4OAgfX19tLW18ejRI0ZGRlCpVCgUCrxeL0qlEpvNxvXr1zl9+jR+v5933nmHN998U5gPp6amYrfb6ejoEOp0pqamotFoljWoXC4XDQ0N1NXVkZCQwMaNG4X8UrfbzdDQEDU1NdhsNjZu3Eh+fv6S8XFyclLw9qWlpbF161ZBtXgxzc3N1NXVIZPJKC8vJzc3d8n5TCYT165do6Ojg6KiIrZt20ZsbKxQikatVuNwOJiZmcFgMGCz2YiMjCQ1NRWj0cj09DS7du1iy5YthIWFLdvup8XlctHd3c2FCxe4fv06arWagwcP8tprrwl5wysxNDTE2bNnuXLlChKJhOzsbCQSifCc29vbBTGxoEHtcDgIDQ1Fr9cTHh5OZGQkKpUKu93O1NSU0N7k5GSSk5MZHh7G5XKxZ88e1q9fj1arRRLw6Pf29gr5wDt27FjxmbwsrPwkngMkEgkajYbi4mK2b99ObGwsdXV13Lp1C4vFglKpFDqTNKAMFh4ejkKhYG5uDrvdvviUOJ1OzIEaamFhYc91WIqIiIiIyDePJBAimp2dTVZWFgqFAqPRyOzs7OJdRZ5zpIHw3OzsbNatW0dJSYmggPplNo1GQ0JCAuvXr2fnzp3s3LmTV199laKiIiIiIpbs/6dsarVaKEGiUqmW/P152bRaLfHx8eTn51NRUcG+ffs4ePAgW7ZsEbzCz/MEWqVSodfr0Wg0uN1uZmdncS0q9xH0lM7OzuL3+9Hr9ct624IKwr29vcJ56urqOH78OEePHuXjjz/m3LlzdHR0YDQaaW9v5/PPP+fKlSv09vYyMDDA/fv3GRwcpKysTKgnmpCQQHp6Olu2bGH//v1kZ2czPj5OQ0MDExMTK4YhKxQKQkJCUCgUC9Lign8LDw8nNDQUh8OB0WhcNo/YZrNhsViQSqXodDq0Wu2KzzMiIgKtVovD4cBqtS4JTfZ6vcJ99Pl8REVFERIIh9ZqtZSVlXH48GF+/OMf893vfpc33niDt99+mzfffJOsrCxcLhdhYWEUFhYSHh6+5P5/GVwuFz09PVy4cIGrV68CsHPnTnbt2rVAtGglRkdH6e3tZW5uDpvNxqNHj4Tn/Mknn3Dq1Cl6e3txBYRfz5w5w6VLlxgcHMTr9RIeHs7GjRt59913+clPfsJ3vvMdDh48yFtvvcXhw4eJj4/H5XKRlpZGenr6gsUIv9+Py+USQrqD9/Bl5rk2VAlIg0dHR1NRUcGmTZuwWCzcuHGDzs5OmCc1LZPJ0Ov1xMXFoVQqhVCUxbHbs7OzjI+PI5fLiYuLIzIyUjRURURERESWIJPJUCgUyAKaBy/7hOBlJDjJXrNmDfv376eyspLo6OjFuz0RiUSCQqEgLCyMmJgYoWTJlyll8bQEJ/gr5QM+LygUCtLS0njttdd466232LlzJ/n5+UJI6vP+vsjlciIjI4mMjMRutzM+Ps7c3NwSA2tmZobp6Wn0ej0JCQmEhoYKThL/vHqnarWa9PR0Nm/ezNq1a4mKihLyQ1UqFSqVClkgR1Mmk6FUKlEqlfj9fgwGA/39/bhcLrKyspaUV9RqtWRlZZGRkYHP52NychKz2byqoRos9xI0HoP7KhQKIiIiiI2Nxev1Mjo6uqTkiy9Qf9hgMKBQKIiJiVmx3QDx8fFERkYyNzfH5OQkFotlwfzb5XIxPj7OzMwMCoWClJSUBYJFGo2G7OxsXn31Vd5++20OHz7M3r17iYuLo6uri6mpKYqKiigoKBAWCvzztGmCOa9Pwh2o/XvhwgUuXbqE2+1mx44dHDx4UFiUXI7Fzzk7O5vKykpKS0uFNMUnPefgvZNIJOh0OvLy8ti1axff/va3OXLkCHv37kWn09HY2IjJZKKsrGxJfVuv1ys44rRaLVqtdlXv78vAC9E6pVJJRkYG27dvJysri46ODmpra7HZbMI+wVXTYCjE0NAQPT09C/bxeDwMDw/T3d1NSEgIaWlpoqEqIiIi8hdKcKLj8XgW/wmXy8XY2BjDw8N4A0r0kZGRi3cTeQFQKpXExsZSUFAglqN7hgTnXTk5ORQWFhIbG4tSqXzuDdQgUqmUmJgYUlJS8Hg89PX1MTY2JnhVg97UYAmelJQUMjIyhNBgu92O0WjEZDLh8XhISkri9ddf56//+q/5m7/5G372s5/x13/91/zsZz/jZz/7GUeOHBH0V0pKSnjnnXc4dOgQ6enpEDCifD6fYHjNNwT9ARVcv9+PNCD8FDSGlkMayKPW6XTMzc1hNBqFdslkMiIjI8nNzSUkJISenh7Gx8cXiMUF1XbHx8cJCwsjLS0NjUaD3+/H6XRiNBqZmZnB6XTi9/tJSkoiJSUFt9tNb28vIyMjgpfWH1CCDmrNxMbGkpOTg16vX2BkSaVSQkNDBe+syWTizp073Lp1C6VSyWuvvUZKSoowZ7fb7YyMjNDR0cHIyAh2u33BPVvMfCP14sWLOJ1Odu7cyVtvvUVhYeGK3km73Y7BYMBkMuFyuUhPT+fNN9/kb/7mb/jbv/1b3n//feEZ//SnP+Xdd98lOzsbpVJJeXk57777Lm+//TaZmZkL7A1ZIGc1IiICjUaD0Wjk/PnzVFVVERcXx5YtW5bkn9rtdmZmZvB6vURGRi4p5fMy8lwZqit1sOBgWF5ezq5du1AqlbS3twseU0lAVUun05GVlUVycjIGg4GHDx/S2dnJ3Nwcc3NzDA0Ncf/+fXp7e4mLiyM/P5/w8PCXfjVCRERE5C+N4Ar4St8VAsboyMgIAwMDzM7OYrVamZubY3Z2lr6+Pm7cuEFLSwsREREUFxeL+akvMNKAgumz9n7+pRP0Gr2o9zUuLk4IJ+3r6+PRo0cMDw8zNzcn1N+9d+8eJpOJoqIisrOzUalUOBwO2tvb+eKLL7h69SoDAwOEhIRQUFDA5s2b2bp1K6+88sqCbf369SQmJqLRaEhKSmLdunVCrnRsbKxglDQ1NdHV1YXFYsHhcAjGSWdnJ319fahUKsHRstp9j4qKIjo6GovFwvj4OI5AeUeJREJYWBhr1qwhISGBrq4u7t+/z/DwMFarFavVSnt7O48ePcJsNpOenk5eXh5arRan00lPTw9ffPEFn3/+OT09PTidTqKjoyktLSU6Opru7m7q6+sZHR3FarViMpno7u7m/v37zM3NCZ7CoDZM0Pi1Wq3Mzs4yNjZGfX09p0+f5uTJk0xPT7N161a2bdtGeHi40L6hoSHOnz/Phx9+SE1NzaqlWjweD4ODg5w/f56TJ08yMzPDxo0bhRxPp9PJ7Owss7OzmM1mwQD3+/20trYKYcKDg4NotVqKi4uXfc5bt26loqKCuLg45HI5qampVFRUUFZWJuQ1+3w+ob0mk4nR0VFqa2s5duwYJ06cwOl0sm/fPtatWyeIbQWZnZ1lZGQEuVxOQkLCAkXgl5XnTkzJ6XRSVlZGUVHRgrAAqVRKSCB3Y2xsjPb2dux2O8nJyWzZsoW0tDRCQkKQy+VYrVb6+vqEOkQej4ehoSFu377N559/jjNQ4HjXrl3ExcWt+qKLiIiIiLxYBMWUrl+/zuTkJFu2bFkiphQUSblw4QK3bt3CaDQyMjJCX18fra2tXLt2jcuXLzM9Pc2WLVt46623yM7OFhc2Rb5WgpP2qakp5ubmSEhIWDA5F3m2BEMyp6amBM+pO1BntKOjg6tXr3Lnzh2ioqL41re+xYYNG9BoNExMTHDx4kWOHTtGS0sLoaGhpKamCh6u5baZmRkePHhAf38/WVlZQlkWhUKBVCrFYrHQ399Pf38/TqcTr9eLxWJhZGSE2tpaLl26RGtrK+np6ezdu5fi4uJl82WD+Hw+uru76ejoIDIyUsinDi4uKBQKpqamaGtrY3R0VAgr7enp4fLly0JljX379rF582bCw8MxGo1cvnyZjz76iOrqaiIiIsjIyECv16NUKpmcnKSrq4vp6WncbrfgSb1+/bpQyuXdd9+lvLxcGI89Hg8dHR3U1dXR2NhIdXU1ly9f5s6dO1gsFrZu3cp3v/tdofxLkOrqaj7++GOam5tJT0+nuLh4WQ+jz+djfHyckydPcuzYMdrb24mKiiIjI0MQJwqWw2ltbWVoaEgI83e73Xz44Yd8+umntLa2EhsbS3JyMiEhIUgD6SDzNwCLxcK1a9fo7Oxk48aNlJeXL3CKWa1Wurq6ePTokdDe4HfI4/Gwb98+Dh8+LCyKBM/r9/vp6Ojg4sWLOBwODhw4QGFh4Yrhyi8Lz42hOjQ0xIMHDwAoLy+noKAAjUazYD+ZTCao+AYTmYP5ACkpKUKMuFarFZKlm5ubaW1tpba2lnv37mGz2QRX/3KqZCIiIiIiLzZ+v5+JiQlqamowmUxs2bKFtWvXLjFUJyYmOH36NGfOnBHKVDx48ICamhpqa2vx+/288sorvPPOO6xfv178Xoh87YiG6jeLVCpFq9USEhIieC1bW1tpbGzkwYMHNDY2otfreeedd9i3b5+gnDsxMcHt27cFYyozM5OioqJVn9XMzAx1dXWMjY2RnZ3N2rVrBS9bUNjJ6/UyODhIa2sr7e3ttLW1cf/+fW7dusXAwAAZGRkcPHiQrVu3Ehsbu+rCmUqlYnx8nMbGRnw+Hzk5OcTHxwt59yEhIYSFhTE7O0tTUxMdHR20trYKpXi0Wi379u1jz549Qsit0Wjk1q1b3Lhxg9HRUQoKClizZg1hYWHo9XpUKhVGo5Guri5aW1tpamri3r17NDU1ER4ezptvvsn+/fuJiYkRDDCHw8H58+c5duwYN2/e5NGjR0xOTpKYmMjevXv51re+xdq1axeoMXs8Hq5fv87NmzeJiopi165dFBYWLjtGe71eGhsb+fDDD2ltbRVydUdHR2loaODhw4fCVltbS29vL/Hx8UJI9okTJ6ipqcFisVBSUiJ4lxcbxATeX4vFwt27d+nr66OiooK1a9cu8IxOTExw+fJljh07xu3bt6mrq2NycpLMzEzefPNNDh8+TF5e3oLcVAJhv/fv3+fq1askJSXxzjvvEB8fv2ofeBl4LgxVArHjUqlUeHmTk5MXrJwQCFdQqVSEhYURFhZGYmIi69evF152uVyOPFAwOSEhgaioKCQSiZCnmpmZyb59+3jrrbcoKipaMR5dREREROTFJpjvlZaWRkVFBRkZGcuuPEsCIjlKpRKPx4PP5yMyMpLi4mL279/PW2+9xdq1a5csnIqIfB2Ihuo3j0qlIiYmhvj4eLRaLV6vF5fLRWhoKCUlJbz55pvs27eP1NTUBTmGTqcTmUxGXl4elZWV5OTkEBISsuDc8wmeNxgmm5ubK4jhyOVywsPDSU1NFQSb3G43FosFr9dLbGwsW7Zs4dChQ2zbto34+Pgn6qvI5XLcbjfd3d0MDw8TExNDVlaWEK0YFElKSkpCp9Ph9XpxOByo1WqKi4t5/fXX2bt374IwXZ/PJ4ytWVlZvPbaa4LTJ5gLPv8+BsuyrFmzhkOHDrF///4leZcej0fwwoaHh1NQUMCrr77KoUOH2LVr17I1WY1GI5cuXaKpqYn169eze/fuFcu0+P1+jEYjDoeD9PR0SkpKyMrKIjExkYSEBBITExf8//T0dNasWSPUeLVYLEgkEkpKSti2bRsZGRkrhtz6A7nEDoeDqKgoNm/eTHZ29gJ7w2q1Mjg4yPT0NNHR0RQWFvLaa6/xzjvv8Nprr5GcnLxsrvfAwAAXL16kq6uL7du3s2vXrr+I75LEv1oCzzeIw+EQ4ss1Gg2hoaHLdjgCL7vFYsFqtaJUKoVVnPkPNbjP+Pg4U1NT+Hw+YmNjSUhIWJLALSIiIiLycuFyuYQyEXq9ftkV8GCuULBGn9FoxO12o9friY6OJjo6Go1GI34vRL4xfD4fs7OztLS0MDk5SXl5ueDZEfl6cblcGI1GxsfHMZlMKJVK4gO1bRc7NnwBVdyxsTFkMhnx8fGEPaFmrMfjwWw243A4CAmU91m8eOb3+4Wc1OB1KBQKoqOjiYmJITxQgnHxWLYSRqORTz75hM8++4zs7Gx++MMfUlZWtsAR5PV6hdSHmZkZVCoVcXFxxMbGLhn/gnProaEhYSEwbFFN0+B9HBsbw2QyoVarhfMtF6rs9XoZGxtjdnYWuVyOVqtFp9Otqqjd2NjI//yf/5Pu7m5+8IMfcPjw4QVe2sUES+PMF4xaCblcLvy+VCrFYDAwODhISEgIiYmJ6HS6Vb8JHo+H2dlZbDabUNZn/qKCw+FgamqK2dlZVCqV0N75qsqLsdvtfPHFF3zwwQfI5XL+y3/5L2zatGmJQ+9l5LkxVF0uF3Nzc3g8HtRq9aqGqt/vx+FwYLPZkAWKtS/34gYToYNNlCyKIxcREREReXkJjv8rffyZJ+I3/1tB4Hux2nEiIl8HoqH652W5eeNK48Di/VabWy431X7S/r6Ayu/8uetqxyyH3+/n8ePH/Nu//RudnZ3s2bOHd955h5SUlAXtWq7dK/3ecvstZrnzrXQfWeac8/93MX6/n7Nnz/JP//RPJCcn86Mf/YiNGzeu6s1mmTF+JRb//uJrW+m65hM8ZqX9F59z/v8uxufz0draygcffEB9fT2vv/46P/jBD4iOjl7xmJeJ5yL01+fzMTo6yp07d3j06BEzMzPCatNyHdvj8dDZ2cmNGzcYGxtDo9GgXaEQscPhYGJigoGBAebm5ggNDUX+AtT3EhERERH5avj9fkwmEwMDA4yPjyORSFCr1ct+T4ITieBEShoQyAiGZw0PD2O321GpVEu8HyIizxq/GPr7Z8PpdDI+Pk5XVxfd3d0MDQ1hNBpXHD/mjx2L55R+vx+Xy8Xo6Cjt7e10dXUxODjI7OwsUql0wfmCz3xsbIy+vj5GRkYYHx9nYmJC2MbHxxkfH2dsbIypqSmcTidKpfKJ89nguDYwMEBzczMKhYKCggJiYmKEObPH42FiYoLOzk66u7sZHBxkZmYGAmJTskVlcFZrN0+4j6pAjdHFzD/X3NwcIyMjDA8PC97n+R5JX0AkymazUVlZyfr165eo4y5H8Dfcbjejo6PC9c1/LiEhIV+6vUH8fj9ut5upqSkGBgbo6+vDaDSiUqmWhPJKJBKcTicjIyN0dnbS2dlJf38/k5OTSOb1N4lEgsfjoaGhgUuXLuH3+9m/fz/5+fkolcoFv/+y8lx4VD0eD/fv3+eXv/wlbW1tZGRkCLHaMTExi3fHZrNx9uxZfv3rX5OSksKPf/xjQYmNQCd2OByMj4/T0tJCXV0dAwMDFBcXc/jw4RXj2EVEREREXlx8Ph9Wq5Xe3l5qa2tpamrC4/Hw+uuvs23btqfO57HZbNTU1HD9+nWmpqYoLS1l//79ZGZmLt5VROSZInpUv3n8gTqfra2tVFVV0djYKBhWkZGRrF+/nh07dpCVlbUkzWw5fD4fZrOZ5uZmocTV3NwcEomEuLg4Nm7cyNatW8nIyECtVuP1ehkfH+fq1avcu3cPq9W66m/o9XrhmpKTk1edz/p8Ppqbm/n9739PW1sbO3fu5Fvf+hbp6elIpVJsNhtdXV1cu3aN+vp6Zmdn8fv9REZGUl5ezrZt28jNzUWj0ax6TUHMZjNNTU1UVVXR3Nws3MeoqCjKy8vZsWMHOTk5S0JW/YGatSMjIzQ1NVFXV8fs7Cxr1qzhzTffJC4uTtjX5/MxMDDA9PQ0cXFxxMXFPbXRFry+W7du0draislkQiqVEhsby7p163j11VeFGqhPiz8Qrj08PCyISPX29mIwGMjOzuY73/kOBQUFC/J8Z2ZmaGxs5M6dO7S1tTE3N4fP50On01FaWsrOnTspLCxEq9Xi8/loaWnhd7/7HQ0NDbz++uu89957q4Y6v0w8Fx5Vr9dLV1cXn3/+OS0tLRgMBmQyGUlJScsmjDudTh4+fMi5c+eQy+WsX7+etLQ0lEolXq+XmZkZ6uvruXDhAmfPnuXmzZs0NDQQEhJCRUUFUVFRT1x5ERERERF5cfB4PIyOjnL58mVOnjzJxYsXqampoa+vj/z8fEpKSpYIcixHMGLn6NGjnD17lpaWFkJCQlizZg2JiYmLdxcReaaIHtVvHqvVSm1tLcePH+fmzZtYLBbBQOjv76etrQ2Hw0F8fDwRERGrGoZ+vx+r1cqDBw84evQot2/fFvLeg6JBnZ2dgkBS0BMYnLc2NDQwMTGByWQSttnZWUwmE0NDQ7S1tTE+Pk5MTAyFhYVPnM/Ozs5y7do1qqqqSElJYf/+/eTm5qJUKrHb7TQ3N/PJJ59w8eJFLBYL4eHh+P1++vv7aW9vF0SBIiMjnxhRYrfbefDggaBma7Va0Wg0gmHZ2tqK3W4nJSVlQbkW/zyV9nPnznHhwgXu3r1LT08PoaGhbNiwgYiICOF3JBIJGo2GmJgYwsLCnuhVDuJ0OqmpqeHo0aNUVVXhcDgE0afe3l7a2tpwuVwkJyc/lYeWgP1iMBh48OABJ0+e5OzZs9TX12MwGPD7/cTGxlJSUkJMTIxgyxgMBm7evMmxY8e4f/8+Pp9PuB/Dw8M8evSI6elp4uPjiYyMRKlUotVqcbvdwvPPysoiISFhiX30MvJcGKq+QB3Vu3fvMjU1BYEOFRoaSkpKilD3KYjT6aSpqYk7d+4QERHBli1bSE9PR6lUCmVpLl26xN27d7Hb7Xg8HqampkhOTmb79u2CHLiIiIiIyMuB0+nk0aNH/Pa3v2V0dBSlUonBYMDhcLBp0ybKysqeaKj6fD6mpqY4d+4c165dY3h4GJfLJRRtT05OXnyIyHNMMGDsaSaxXwfzA9ae9hpEQ/Wbxev10tHRwalTp7h79y4REREcOHCAgwcPUlpaikKhoKOjg66uLiIjI0lPT19WECiIy+Wis7OT48ePc/v2bVJTU/nWt77Fvn37KCoqwh+ohTk+Po5eryc5OVkQepPL5cTGxgoLa/O33NxcvF4vw8PDaLVaNm/eTFlZGXq9fsVrAWhvb+fcuXMYDAa2bt1KZWUlkZGRwrlOnDjB559/TlhYGIcOHeL111+nvLwchUJBT08PAwMDhISEkJaWtqqIkN/vp7Ozk88++4y7d+8SExPD/v372b9/P2vWrEGpVNLR0UFPTw8RERFkZmYK5Wb8fj+NjY2cPn2axsZGnE4nNpuNubk5UlNT2bp1K1FRUQt+TyaTIZfLhfDYp6Gnp4ePPvpIMNoPHjzIvn37WLNmDRKJhPb2dgYGBggPDycrK+uJOa8+n4/JyUlu3brF8ePHefDgAQqFgpKSErZs2cL27dvZuHGj0FapVIrD4eDBgwd8/PHHtLS0kJ+fz9tvv83evXspLy8nOjpa8MqGhISQnp5ORESEEDI9PDxMU1MTWq2W4uLiJSJfLyPPlaFaVVWF1+slKSkJp9OJ2WwWiuvOn2C4XC6am5upqqoiMjKSzZs3C4aqx+NhZmaGiYkJ9Hq9UOS9t7eXlJQUduzYsSA2X0RERETkxcfj8TA8PMzg4CAVFRWUlJQwNDSE2Wxm8+bNCwrMr4TNZuP27dt89tlnQr5S0ANQWVlJUlLS4kNEnkO8Xi9WqxWDwYDdbkceKF33TeEP5CcajUYMBgM+n++pQkYRDdVvnNnZWW7fvs2FCxfwer0cOHCAN954g+LiYpKTk4mOjmZycpLHjx8DkJeXR2xs7LL9ye/3MzMzw82bNzl//jwA3/nOd3j99dfJyckhNTUVvV7P+Pg4nZ2dSCQSsrKyiIuLQ61WEx0dTWZmJgUFBUu2iIgI+vr6GB4eJicnhz179iwbQjsfp9PJ3bt3uXbtGjExMcIxSqVS8PoeP36cmZkZDh8+LJRuTE1NJSYmBoPBQGtrK263m/T0dBISElYMiXU6nVy5coVz584hlUrZv38/Bw8epLi4mNTUVCIjI5mcnKS5uRm73U5paalQB9bn8zEyMsLk5CQpKSkUFRXh9XqZnp4mNTWVV199lcjIyMU/+aXweDxcuHCBkydPolKpeOutt9i3bx8FBQWkp6cTFhbGxMQEra2tuFwuoezlSoY5gMlkoqqqiuPHj9PV1UV+fj5vvfUWb7zxBhs3bqSgoIDk5OQF6sXDw8OcP3+eGzdukJCQwPe//3127txJZmYmycnJpKenYzabaWhoYGZmhry8PFJSUlAqlajVaoxGI3V1ddjtdtauXftEj/rLwHPXuvDwcIqLi0lLS2N4eJibN2/S2dn5VJLSBGSlk5KS2LVrF3/1V3/Frl27hELFIiIiIiIvJwqFgry8PL7//e9z+PBhwdvAIs/WSni9Xnp6ejh//jxTU1Ns3LiRvLw8ZDLZUx0v8vzgdDrp7Ozk2rVr3L59m/7+fubm5rDb7TidTrxe7+JDninBSfbDhw/54osvaGxsxOFwLN5N5DlgYmKCpqYmDAYD6enpbNiwgbS0NEJDQwkLCyM3N5eKigoiIyNpbW2lq6sLu92+7Jjg9XqZmpqisbGRiYkJCgoK2LBhA/Hx8YSEhKDX6yksLBTKw/T19dHf3y8spuh0OmJjY4W8y+AWGRmJ0WhkcHAQjUbD2rVrhdqcqzEzM0NnZydWq5WUlBRSUlJQq9X4A2Jzjx8/Znh4mKysLDZv3iy0W6vVkp+fz/r164mMjGRwcJCOjg6sVuvinxCYnp6moaGBsbExMjIyKC8vF4w0vV5PdnY2GzduRKfT0dzcTHd3t3AfpVIpGRkZvPHGG3z3u9+lsrJyQdrfcvf6yxBsb01NDaOjo+Tl5VFWVkZiYiIajQadTkdeXp6gHNze3k5nZ+eq76zb7aazs5NLly7R3d1NYWEh7777LgcOHKC4uJikpCTCw8MFcaYgg4ODNDc343a7KSoqEryoKpWKkJAQkpKSeOWVV0hMTKSnp4euri4sFgt+v5/Q0FAyMjJITExkaGiI9vZ2XC7Xgut6GXmuDFWfz4dCoRA6tFar5dGjR1RVVQkhwU9CJpMRERFBbm4ueXl5REZGIpVK/+SOLiIiIiLy/CKTyUhISGDjxo2kpqY+0Xs6H7/fj8Fg4PPPP6ehoYGCggK2bt1KTEwMPp9v8e4izzl2u53u7m6qq6u5efMm1dXV1NXV0dDQQHt7OwaDAZfLhdPp/Fo2m83G2NgYjx494saNGzQ1NWGxWBZfpsifGb/fz+TkJAMDA4KxlJSUJHgpJRIJoaGhZGZmEhcXx+joKP39/dhstmXnlE6nk9HRUfr6+vB4PBQWFpKSkrLAUAkLCyMjI4PY2FisViujo6PMzc0tOM9iDAYDDx8+pK+vj6SkJEpLS58qMnBiYoL+/n6USuWCvMuglkt7ezs2m42cnBySkpIW5KBqNBpSU1OJj4/HarUyNDTE3Nzcsu0m4Cns7+9HJpMJ3sH591Gr1ZKbm0tMTAwzMzN0d3cLBphEIhFybrOzs586P/Rp8fl8DA0N0dXVhVQqJTc3l4SEhAXtDYb7RkdHMzs7KyxIrITRaOThw4fU19cv8FbbbDb6+voYGhpidnYWj8ez4Ljp6WkmJiZQq9WkpKQsaatUKiUrK4uUlBScTidDQ0OYTCZ8Ph9SqZT4+HgyMjKwWCx0d3c/tRPvRebZ9YRngN/vx+v1EhYWRnl5OUVFRUJYRkNDw6qrG0EkEgkymQxlQLbbH6hFJSIiIiLy8hLM8QpOjlaaUC3GH1BsrK6u5vz58+j1evbu3UteXh5yuVz8fryABEN/jUYj/f393L17lzNnznD69GkuXLjAvXv3aG9vp7W19ZlvbW1tQk7j0NAQMzMzmM3mvwjPx4uG2+1mZmaG6elp1Go18fHxQr5oEKlUSkREBJGRkdjtdiYmJgSF1sU4nU4mJycxGAyoVCrBEJmPUqkkOjqa6OhooZTJSoYvgZDVtrY2Hj16hM/no7i4mJycHCG/czUMBgNTU1NotVri4uKEsTGYIhcs3ZWUlLSk3RKJhPDwcKKiovB4PExPT6/YboCxsTEMBgMajYb4+HjCwsIWGNJKpVLwDnu9XkZGRgRDlUA0pHKZUjjPAp/Px+DgIEajEZ1OJzyXxdcXGRlJdHS0cH1Op3PBeeYzNDREfX09VquV9PR09Ho9Dx8+5OOPP+aDDz7g6NGjXLt2jZ6engX3zePx4Ha7BVtlOcLDwwXRLqPRiNVqFY4PCwsjOTlZEA9c7RpfFp4rQ5XAwOH3+0lJSWHz5s0kJibS2trK9evX6evr+9pDdkRERERE/nJwu910d3dz/Phxpqenee2119i0adMClUmRFw9JoOahw+FgcHCQhoYGHj16xL1797h48SInTpz42rbTp08L4pBBRdKVDBGRPx9OpxOTyYTVakWpVBIWFrYkBzPoVQ0PD0cul2O1WrHb7csabG63G7PZjNPpRKvVCsfMRyqVCuG1Xq8Xs9mMw+FYsX8EQ8i7urpITk6mrKyMuLi4JeddjN/vZ3Z2FrPZjEajEdRjCei8mEwm5ubmUKvVREZGLpvrGgyL9QeUjOfm5lacg8/MzGC1WlGpVGi1WhQKxRKDPxj+HDTAvikjK+g5t9vtaDQawsPDl80ZV6lUwsKC0Whc4g0N4guoGPf09OD1egVtg/Pnz3Pnzh1u3brFZ599xq9+9SuOHj1Ka2ursBgREhKCRqPBbrczOTm5xPj3BUqs2Ww2fIFSm/O9piEhIUJeavCeL9cXXyaeO0PV5/Ph9XoFIaSKigokEglVVVVUVVVhNpuXdC4REREREZEvi9frZWJigrNnz/Lo0SM2b97Mvn37SExMRLpITVL87rxYBA1Vv98veDFcLhcWi4WBgQEeP35MU1PTM98aGxtpbGykr68Pa6Aepth3nk9cLhdzc3M4HA5kMhkhISFLDEBJIFJDrVYjl8uFkPHlDEuv14vD4cDr9RIaGopSqVz22csCirXB/T0ez7Ln8/l8dHR0UFtbi8/nY82aNeTn5z9VPWiPxyMY1SqVaoGgj8fjYW5uDo/HI/xtcbsJ5P0rFAr8AYEvh8OxolEUvI8KhQKlUrls6K5UKkWtViOVSrHb7d9Y2Ko/UCfX5XKhVCpRKBTLXt/8iBybzbaiUe5wOBgfH2dqaorZ2Vl6enoYHh4W9HF2795NWloanZ2dfPLJJ5w9e5bBwUHcbjfx8fGkpaXhdDppbGzk8ePHGAwGrFYrFouF8fFxbt++TUdHBzabDXlA2TiIXC5Ho9EQEhKCxWLBYrGs+ExeFpY+qecEhUJBSkoK27Zto7i4mJGREa5fv057ezv+QPK1iIiIiIjIV8Hn82E2m6murubUqVMkJCTw3e9+l5ycHGFyNn/yuPi/RZ5vgs8raGgEVTPDw8PJyclh06ZNbNy48WvZNmzYQF5eHnq9Hp/PJ/ab5xR/IN3M5/MhkUiWLE4Fmb/YsNo4EDwfAWN0pXnq/POt1j9MJhO1tbV0dHSQmprKunXrFogMrYbL5cJms+FyuVAoFKhUKuF6gtcZnEuvFm47/5jVrnXxfVyJYNtXO9ezxh9YrAq2d6W2Eri+YFtXIphWEPR6xsXFcfDgQX74wx/y3nvv8ZOf/IT/9J/+E7t27cJisXDp0iUaGxux2WykpqayadMmEhMTaW9v5+jRo5w+fZorV65w6dIlPv30U06dOsXw8DBerxetVrugBI1EIhHGMofDsWrY+MvCyr3pz4wkUNC3uLiY7du3ExMTQ21tLTdu3MBsNgurIqt1OBERERERkcX4Ax6C9vZ2jh07xujoKLt27SIvLw+Hw8HMzAxGo1HwIDidTiwWC2azeVWBDZHnD41GQ05ODps3b2br1q3s2LGDQ4cO8Z3vfOdr29555x1effVV4uPjhQmvOFd5/gjqmQQXpoLG1nyC/+52u/H5fMjl8hXnnlKpVPDWeTyeFT1yXq8Xj8eDVCpFFaiPufh8fr+frq4uHjx4gMvlErypT5ObSsAA9ng8gvE43ziWSqWC13N+2xYT/JtEIlnVU0ogx1MeyOkPGsGL8QfKNvkC5ZqexuB+FkgkEtRqNTKZbNlnHMTn8wntXS40OIjD4cBqteL1eklOTmbPnj3s3buXwsJC4uLiSE1NpbKyknfeeYfMzEwGBgZobW1lenqa8PBwtm3bxltvvUVCQgL37t3jgw8+4Be/+AW/+tWvuHTpEnK5nLCwMFQqFTExMej1+gX3PfgsfT7fN2rw/7lYvsc9J8hkMmJiYqisrGTr1q04HA5u3bpFXV0dAGq1esWOJCIiIiIishx+v5/p6Wlu3rzJzZs3cTqdDA8P8+GHH/LLX/6SX/ziF/zmN7+hrq6Oubk5enp6OH78OB999BENDQ0rTkBFng/kgVIfERERZGVlsWfPHt59912+973v8fbbb7Np0yaysrLIycn5Wrbs7GxBQTYiIoKwsLAnlhIR+eZRqVTodDpCQkLwBnINl8tLdDgcWCwW3G43Go2G0NDQZQ02uVwu/M1qta6Ye+p2u3E6ncjlcrRa7RKjyB/ICb137x5NTU2kpqayfv164uLiVhTgWYxMJkOhUCCTyZYYNAqFAp1Oh0KhEIyuldptt9sFx5FWq13RuNTr9YSEhAgh9ovb7ff7cbvdQp5r0BD7JpAEhKGUSiVOp1MwlhfjdruxBkrwhIWFrdhWAkatRCIhISGB/Px89Hr9gmcolUopKysjLS0Nb0CcyWg0ApCZmcnhw4f527/9W9555x3y8/OJjY0lJyeHN954g507d6LT6YiKiiIlJWWJoRpc6AiGZr/sdtDSN+05Q6lUkp6ezo4dO8jPz6elpYUvvviCiYmJZVehREREREREnkRQzCI0NBS9Xk9NTQ3Hjx8XBHHOnDlDZ2cnTqdTSD25ePEiXV1doqH6nBMaGkpRURH79u3jwIEDVFRUkJubS2ZmJikpKWi12sWHPFPkcjkJCQls3bqVt956iw0bNqDT6RbvJvJnRqVSERERgU6nw+l0MjMzs0Tgx+fzMTc3h8lkQiqVEhkZiUajWdZQVSgUhIeHExoaisViYWZmZonaszcgoGQ2m5HL5URFRREaGrpgLuvz+ejs7KS6upq5uTnWrl1LQUEBGo3mqee8SqUSjUaDSqXC4/HgdDoF40wZULjV6/U4HA4MBgOOZapqWK1WZmdnkUqlhIWFodVql203QFRUFHq9Hrvdzuzs7JI8Xq/Xi8ViwWQyARAbG7uk3V8XUqmUhIQEQkNDsVqtTE9PLxHE8vl82Gw2TCYTEomEuLi4JcJaQYKCSEFDdrFRHkSn0wnPzOl0CuHHCoWC9PR0Dh06xH/+z/+Z//bf/hv//b//d/7rf/2vvPvuu9jtdgwGgzBmzb9PvkCEj81mQ61Wr9gXXyae+9ZJAvWXSktL2bFjByqViqqqKh4/fiysaIiIiIiIiDwtEomEyMhIdu/ezX/+z/+Z//Sf/hPf//73ee+993jvvff4/ve/z1/91V9RVFSEWq0mLS2NAwcO8K1vfYvCwsKn9mqI/HlQqVTk5uby2muvUVlZSWxs7Dc6V5DJZERFRbFhwwYOHDjAmjVrvjHvkcjTI5PJhJIkNpuN4eFhzGbzAsPD4/EwMTGBwWAgJiaG5OTkBTmD81GpVMTHxxMXF4fb7aanp4fp6ekF+9hsNkZHR5mYmBD2nx/OG/Sm3rlzh8bGRtLS0li3bt1TKf3OJxhVEBISgs1mw2w2C+JFcrmcyMhIUlJSkEqlDA4OLigVQ8CwnJqaEmp+xsfHr9hugKSkJGJiYrBYLEJZpvleWrvdzsDAAAaDgdDQULKyspZ4Ib8qvnlhzssZjVKplPT0dGJiYjCbzfT19WE0GhcYqsHnMjU1hVqtJisra8UoCJ1OJ5QyMplMjI+PLysMFVRdJlByZr4nXhJQk05MTKSgoICSkhKSkpJobW3liy++wOFwsHnzZjIyMhYYzB6PB4vFgtPpRK/XL/G2voy8EK2Ty+XExcWxfft2KisrmZyc5OHDh5hMJvwBsQQREREREZGnQSKREBERwfbt23n//ff58Y9/zE9/+lNhe//99/nBD35AaWkpoaGhZGRk8Oabb3LkyBGKi4tFQ/U5RxLIqQuGaX6ZCf6zQhpQONXpdKKR+hwTHx9PTk4OUqmUnp4eent7mZubg4CxZjQaaWxsZHR0lMzMTLKzswkJCcHn82EwGGhtbaW9vR2j0YhcLicxMZHc3FzUajWNjY309PQsMGImJydpb2/HZDIRHx9PamrqAkPV4/HQ09MjVLlYt24dRUVFS+qcPg1hYWGEhYVhsViYmpoSvLvSQG3Y4uJidDodra2t9PT0YLfbBUPPYDDQ1tbG+Pg40dHR5OTkoNVq8fl8mEwmmpubaWpqYnZ2Fr/fT1JSErm5ucjlcrq6uujt7RXy+X0+H0ajkYaGBqanp0lPTyc7O/tLeYiXw2g0Ul9fz40bN2hpaVmyyBBEEgjRLSkpQaFQ0NLSwsDAgBCa7Q+Ur2lsbMRkMpGSkkJ+fr5gqBoMBhoaGmhvb2d2dhaFQkFmZiZpaWlMT0/T1NSEwWBYEGnj9/tpampiaGgIjUZDZmYmUVFRS74dwfabTCZqamr49a9/TVNTE2vXrqWyspK4uLgFhqjVamVychKJREJMTMw35pX+c/JcGarB1ZDgNp/gCumePXtISUlhdHSUmZmZZePMRURERET+sgl+R1ZbZQ8JCREmc/O34Ep1sLxE0OgJhtKJvBhI/sylYYK//1WuYbk+K/LsiY2NZe3ataSmpjI4OMjVq1epr69ncnKS4eFhoS6mz+djw4YNZGdno1QqMZvNVFVV8dvf/pb/9//+H7W1tdhsNqKioigvLyctLY2Ojg6uXLlCS0sL09PTDAwMcOvWLR48eEBISAhr164lLS1NGFN8Ph+zs7NUV1fT3NxMUlISGzZsICkpCYVCsfjSn0hcXBwJCQlYLBZGR0cXCMHp9XrKysrIzs5maGiICxcuUF9fj8FgYHR0lFu3bnHnzh28Xi/FxcWCkNPc3BwPHz7kgw8+4F/+5V948OABVqsVvV7Phg0byMrKor+/n1u3btHU1MTExARDQ0NUV1dz9+5dALZt20ZaWtqKC0jz7YDV3oOOjg6OHj3Kb37zG+7fvy8sMCxGEsix3bZtG9nZ2XR1dXHjxg1aW1uZmppicHCQu3fvUl1djUKhYMuWLaSmpiKXy3G73dy8eZNf/epX/P73v6exsRG73U52djYVFRUolUqqq6u5dOkS3d3dmEwmpqenqa+v5/Tp0wwPD1NcXExxcTHh4eFIJBI8Hg8mk4nBwUFaWlq4desWx44d4xe/+AW3bt0iOzubb3/72xQVFS3xYk9PT9Pf349KpSItLW3F8OSXCdnf/d3f/d3if/ym8fl89PX1cefOHVwuF+Xl5RQWFi7II5EEJJmDsf+dnZ3Mzc2RnJzMli1bln1gfr8fi8VCY2MjDx8+JCkpiZ07dxIdHb1kVUNERERE5OXA5/MxNjbGjRs3mJycZPPmzaxbtw61Wr1gv/mGxOLN6XRy+/ZtQcyksrKS5OTkBceLiDxr/AFF6snJSWw2GwkJCYSHhy/eTeQZIQ+ULrLb7QwODtLb28vExASjo6PU1tZy5coVBgcH2bBhgyB8o1QqGRsb4+LFi5w5c4bBwUFiYmLIyckhMjKSkJAQ7HY7vb299PT0YDAYGBkZoaamhsuXLzM5Ocm6devYt2+f4H0FFiiRt7e3s2vXLg4cOEBiYuKKRt1qyGQy+vv7aW1tJTQ0lIKCAqKjo5FKpYLH3+v1MjQ0RHt7uxDq+/DhQy5evEh/fz/FxcW8/vrrlJSUEBoayvT0NJcuXeLkyZM0NDSQlJREQUEBer0ejUaDzWajt7eXvr4+JicnGRkZ4eHDh1y9epWBgQFKS0s5cuQIubm5KxrfU1NTPHr0iJ6eHqFMZVRU1OLduH37NmfOnGFmZoY1a9ZQUlKyopdWIpGg0+mwWCz09vbS39/P1NQUw8PD3Lt3j6tXrzIyMkJ5eTnvvPMO2dnZyOVy7HY7f/jDH/j8888ZHBwkPT2dzMxMIiMjUalUzM7OCs85uLhRX1/P+fPnqa6uJjo6mm9/+9ts2bKFiIgIZDIZMzMzPHjwgIsXL3Ljxg2uXbvG3bt3mZycpLCwkO985zvs3LmT2NjYBc/d6/XS1NTExYsXUSqVvPXWW2RmZn6lvvEi8VwYqn6/H4PBQF9fHzqdjnXr1pGTk7MgHIJ5+aoqlQqLxYJUKiUvL4+NGzeuuOLkcDgYHh5mfHyc7OxsKisriYiIeOljukVERET+UvH7/ZhMJrq7u5FKpWzevJmioqIv5Q31eDx0dnZiNBqF70xsbOzi3UREnilBQ3Vqaoq5uTnRUP2akUgkQmSFTCYTPF3B8FWPx0NZWRlvv/22IIollUoxm810dXXR398v6KgUFhYSFhZGaGgo4eHhyGQyDAYD/f39dHV10dfXB8D69es5cOAAZWVlgpeNwHy1paWFx48fExkZyVtvvcW6deuWeNWeFoVCgclkoq2tjbm5OVJTU0lOTkatViMNlMaJjIxEqVQyMzMjtLurq0soifP6669TUVFBVFQUUqkUm81GZ2cnnZ2dwtgaNBA1Gg1hYWFIpVKMRiNDQ0ML7uOaNWsWiIut1CaLxcLg4CBzc3Pk5uZSUVFBWFjYgn0cDgdXr16lpqaG9PR0XnvtNcHbvRLB5yyRSJiZmWFgYIDOzk76+vrw+XyUl5fzxhtvsH79eiHU2uPx8ODBA/r7+wkLC2PTpk3k5uai0+kICwsjIiICiUTC9PQ0vb29dHZ20tbWxuTkJGlpaRw6dIjdu3eTnJwsKPQaDAaqqqq4du0aQ0NDeL1eEhMTqays5O2332br1q3ExsYusWlmZma4efMm9+7do7CwkDfeeIOoqKgV7+PLwnNhqDLPCM3Ly6OoqGjZhySRSJDJZOj1eqKjo8nIyKCsrIz8/HxhUFgOpVJJbGwsa9asITc39y8ipltERETkL5Xg+B4aGkpOTg6lpaUkJCR86ZVnqVRKUlISa9asITs7+2tXixUREQ3Vbx6ZTEZYWBgJCQnExcURGRlJbGwsmZmZbNq0ib1791JeXk54eLjg5AiWf4mMjKSkpIT169eTkpKCMlBPNCwsjKSkJGJjY4mIiCA2NpasrCwqKyt57bXXKC0tJTIycsG81ev14nA40Ov1rF+/noqKCmJiYlac2z6JoOd0ZGSEvr4+IVcyaExKpVJ0Oh1JSUnEx8cTERFBTEwM6enpbNq0iT179rBu3TpiYmKEsVMaqMGq1+spKSlh69atpKSkoAiUwll8H2NiYoT7uGfPHsrLy5/KWaRSqUhOTqakpITMzMwl0TCjo6NcvHiRgYEBKisr2b59OzExMaueVyqVEh4eTmJiIrGxscL1ZWVlsXnzZvbs2cPatWsXXF/wPoWHh1NeXk5FRQUJCQkoFApUKhXR0dGkpaUJ9y86Oprk5GTWrl3LgQMHeOWVV0hOThbSSAiUwbHb7ajVanJzc9myZQu7d+/m1VdfpaCggPDw8CXfKq/XS1tbGxcvXmR2dpYDBw6wYcOGJfflZUTiXy0A/BvE6XRitVrx+XyEhoYSEhKyYofzer3Mzc1hs9mE3CHVCsV5vV4vdrudubk5FAoFer0e2UtQ1sbtdmM0GpmdnSUkJITo6OjnosM6HA5mZmaw2+2EhoYK4REiIiIi3yRut/upah+uhD+gvmm321EoFGi12iWLpyIiz5pgnmJLSwuTk5OUl5eTnp6+eDeRr4FgHU2z2YzL5UIqlQpeQrVavWDe6PP5hH0lEongSQ2OMX6/H4/HI5SicbvdyGQytFoter1+yfnmnzM4t9XpdKt6CJ8Gm83GF198wccff4xSqeTw4cO8+uqrCzy5wdIxwbIyi9s9f9z0Bcq4GI1G/H4/kZGRS8bW4NhrsVieeB+Xw+PxMDc3h9PpRKlULlu/taqqiv/9v/83NpuNH/3oR+zbt0/wbj4Jt9uN2WwWru9Jz2V2dhaTyYRcLiciImKJh3vx+Qh4byMiIpbcm+D+s7OzWK1WpAGtBK1Wu+xvE+hLU1NTfPbZZ5w5c4aMjAz+9m//lsLCwiX35WXkufCoBlcQTSYTFosFr9eLQqFALpcv+9AIGEQmkwmfz4dKpRJc6gTOF1yZstlsOBwOpIEwB7lcjlQqXfG8LwLBsLZ79+5x+fJlDAYDcXFxS0IjViI4gM7MzDA1NYXX60WpVC55mb4KY2Nj3L59m6qqKiwWC7GxsWL9OBERkW+E4Ldkbm5OKGKvUqkEL8dK475/XjH6+RMOpVKJTqcjNDT0K3s1RES+DKJH9c+HVCpFJpMhl8uRy+Wo1WpCQ0NRqVRL3n+JRIJKpVoivBYkOA/1+XzC/FOj0aDValecbwXPqQnU6AzWJLXZbHg8HqQB795K49hyyAM5uMPDw7S3tyOXy8nMzFziNZzfbpVKtaDd839PEtCLCQsIzy1uNwFvc0hICHq9Hp1Oh1arFdq9eN/lCN6vkJAQZDKZ4IGUBKIqARobG2lubqakpITt27d/qTzeYFuDXnG1Wk1ISAgqlWrZ+6tWqwkPD0ev1y+wNYIEryt4/0JCQoTSQIv7DYHfD4aHh4WFodFohEVQp9OJy+XCH6hoIpFI8Pl8tLS0cPbsWYxGI/v27WPTpk1LDOaXlefCUA2KKZ0/f55bt24xPj6OTqcjIiJi2Y7ncrloaGjg9OnTDA4OEhkZKYT+ejweZmdnGRwcpK2tjYaGBhobG+nq6hLkuZVK5YoDxYtAcHXl8uXLXLhwAbfbTUlJCfHx8cI+Xq8Xl8uFx+NBIpEsaKvP52NycpJbt25x7do13G43sbGxK67mfBn6+/u5cOECd+7cQSqVUlBQQExMzOLdRERERJ4Zfr9f0CNoa2ujqamJ+vp6WltbGR4eFlau1Wr1gm+K3+/H5XIxNjZGR0cHTU1NPH78mJaWFgYHBzEFitOr1WrRmyryjSAaqn8egkqsPT09PH78mPr6ejo7O5mamsLv96NWq5/K0Ap6HEdHR2lvbxfGlNbWVoaGhoSxKOg4mX++oBPBaDTS2dm54DomJycFD2MwzPZpkEgkOBwO2tra6OzsJCoqitLSUiFM1ufzYTab6e7upr6+nrq6OqHdHo9HGPu+zHzZ6/UK96C7u5uRkREhWnK5Of18gmOyyWRieHiYnp4eOjo66O3tRR0o90TAy6nT6aioqCAvL++pU/p8gVI5nZ2d1NXV8fjxY7q6uoQqIsH2Ps25CBiWwZJD9fX1wvMyGAww79vxpPP5fD5mZmZoamqit7cXr9e7wIANlixyOp1UVlaSl5f3J3vbXxSeC0M1GHt99OhRrl+/zvDwMFqtlqSkJPTLFAR2Op3cvXuX3//+9xiNRgoKCkhMTEQmkzExMcG9e/e4cOECV69e5f79+4Kx+vjxYwYGBpAGakitFl78POP3+5mZmaG6uppHjx4RGRlJRUUFSUlJEAgrmJqaoru7m5mZGVQq1QIj1O1209vby/Hjx7l48SKhATW4+fkXX5Xh4WHu3r1LV1cXcXFxrF+/nri4uMW7iYiIiDwz3G43AwMDfPLJJ1y4cIH79+/z+PFjYZLY3t7O3NwcYWFhC/QMvF4vExMTnDp1ijNnzlBTU0N9ff2CyeXMzAw6nY7IyEjRWBX52hEN1W+e4DhQXV3N+fPnuX79Oo8fP6a5uZnGxkZGRkbQaDRERUU90Vh1Op10d3fz+eefC8qvwbGovr6e9vZ2bDYbOp0OvV6/wFh1u92MjIxw69YtTp8+LZR4aWlpoaGhgYGBAXw+H+Hh4U8d5eHxeIQSKF6vl8rKStauXYtOpxOMtpqaGk6ePMn169dpaGgQ2j06OopSqVw23HU5gn13YmKChoYGrly5woULF3j8+DFyuZzU1FQ0Gs3iwwS8Xi+zs7N0d3cLJV+uX79OTU0NbW1tpKWlCaJEWq1WqGUaFLh6Ev5AvdSgWvDNmzdpaGigqamJ5uZmJiYmUKvVQsrak9rrcDjo7u7m8uXLnDt3jpqaGpqbm2lubqauro6xsTHUajURERGrns/v92M2m7l+/ToffvghN27cQCqVCm2TyWR4vV7Gx8cZGBhApVKRl5e3rH30MvJcGKo+n4+enh6uXLlCd3c3s7OzACQkJJCUlIRqUY6j0+mkrq6OS5cuERoaSkVFBWlpafj9ftra2vj888958OABHo+HiIgIwQAbGRmhsbERg8FAREQECQkJz8SL+E3jD4T+1tXV0dbWRkJCApWVlYKhajabuXv3LidOnGBoaIikpKQFJXm8Xi/T09M0NzdjMBgoLCxk7dq1z8RQDUq6j4yMkJaWRkVFhaiUKSIi8rUS9Bh8+OGHzM7OEhERQVRUFKGhoRiNRtrb2+nr60OpVJKeni6kSbjdbvr7+/njH//I0NAQYWFhREVFodVqBXXLrq4u/H4/KSkpYnSIyNdO0KM0OTkpGqrfAMGF/7t37/LZZ5/x+PFjVCoVSUlJhIaGMjIyQnNzMxaLhYSEBEFYaKV549zcHI2NjVy7do2RkRH0ej1RUVFoNBqMRiMdHR0MDg6iVCpJTEwUhI08Hg9jY2N88cUXfPrpp3R1dREeHk5qaio6nQ6DwUBrayvj4+NotVri4+Ofyos4NTXFxYsXqa2tJS8vj/3795Oeno5MJsNisXDv3j0++ugj7t27R0hICGlpaWg0GkZHR2lra8NsNhMVFUVsbOySufhiPB6PMJe/cOECt2/fpq6ujomJCRITEyktLV0xRc3r9TI1NcW9e/c4d+4cV65coaOjA7vdjlKpFMSMgoJVwfDa1QzAxczNzXHlyhU++eQTWlpa0Gg0gtDRyMgIbW1tWCwWkpOTFwhILYfX66W7u5vTp09z7tw5xsfHiY2NJSUlhdDQUIaGhmhsbGRmZobExERiYmJW9Kza7Xaampr47W9/y40bN2hraxMEmYJqyxqNBq/XK3zLUlNTSUtL+4tYPH1uDNX+/n6qqqowm82o1WocDgcKhYKUlBSh7lMQl8tFS0sLVVVVREZGsmXLFtLT05EEJKKNRiPJycns37+fPXv2CDX0oqKi6Ovro6OjA4VCQXZ2NlFRUU9clfIH9KaCHcw/r5B8kMWd70l/D7L43MuxeJ+gofro0aNlDdX5da48Hg/r1q0jOTkZaSD2Phh2EhUVRWFhIRUVFaSnpy944f2B+Pj51/A0bZpvqKampq5a0iF4vsXtExEREfky+AMr+TabjT179rB3714qKyvZsGEDGRkZGAwG2tracLlc5OTkkJGRIYw3LpcLs9nM5s2b2b9/P9u2bWPjxo3k5uZitVppb2/HZDKRlpZGfn7+n7yYJ/Lnx+fz4XK58Hq9wnfxz40/EPbp8XhwOp0YDAbRUP0GcLvdNDY2cuLECRobG8nLy+PIkSMcOHBAUKjt7e2lqakJnU5Hdnb2qh48b0DAU6VSCYrBlZWVbNy4kbS0NIxGI21tbbjdbjIyMkhMTESlUmE2m7l37x4ff/wxvb297Nq1i3fffZedO3eyYcMGkpKSmJiYoLW1FbfbTVpa2rLVMebj9/tpaGjg3Llz2O124Vw6nQ632013dzcff/wxN2/epLCwkO9973vs37+fjRs3Eh4ezsDAAF1dXSgUiiV5rcvhdDqpqanh0qVLGAwGtFotHo8Hn89HQUEB69evX9ZQ9fv9TE9Pc+PGDU6cOEFdXR2hoaFs3ryZgwcPsnv3brZs2SKUhVntGlbC7/fT3NzMBx98QGNjI+vXr+fw4cOCErFGo6Gnp4fu7m4hylCzQk1WAqViLl26xGeffYbdbufgwYMcOXKEbdu2UV5eTnJyspCGotfrycjIWNYZ5PF4GBgY4NixY9y4cQO1Wo3VaqW4uJiKigrB/pEHco3Hxsaoq6tDLpdTVla26jW+LDw3hmpfXx/V1dUApKen43K5mJqaIiIigvT09AXhAi6Xi+bmZu7evUtkZCSbN28mPT0dtVqNVqslIyODdevWUVpaSkZGBklJSaSmppKUlCR4In0+H3l5eaSkpKBeRS3X4/HgcDgEJS+/34/dbsdkMjE7O4vD4UASSKSWSCT4A7lSJpOJmZkZbDYbzJO4nt+hvAHBJ6fTid/vX/J3Ar8/P7k62MmXM1QTEhJwu92Mj49TXV1NfX09UVFRrF+/npiYGMEolMlkgqGanp5OUlKSEAbt8/lwOp04nU58Ph+SQB2pubk5QWXYbrdDICFcEkj2DvI0hqrP58PhcDA7O4vRaBQU9gjcp8XnFBEREVkNWaAsQk5ODuXl5WRmZpKYmEhSUhJJSUmYzWba29ux2+0UFBRQXFwsjMmaQMmG0tJScnNzSUpKEo51uVx0dHQwNTVFVlYWZWVlfzF5QS8rPp8Pk8lEe3s7IyMjaAO12Vf65gQXUoOstN+fgt/vZ25ujoGBAQYGBoRKBQ6HQzRUv2YMBgNXrlzh8uXL6HQ63nnnHfbv309WVhYJCQnEx8djNBqpr6/H7XaTn59PYmLiigaiXC4nPDyc7OxsSkpKyMrKIikpieTkZJKSkpidnaW1tRWPx0Nubi7Z2dmoVCpGRkY4d+4cd+/epaioiB/96EdUVlaSmJhIfHw8ycnJOJ1O2tvbMRqNJCYmkpGRsWoorcPh4MaNG9y+fZu0tDT27dtHWloacrmc2dlZ7t69y5kzZ5DJZPzoRz/i4MGDpKenC79pNBppbm7GZrORnp5OSkrKql5Vn8/H9PQ0SqWSiooKCgoKhHljbm7uioZqMJ3v448/prOzk5KSEo4cOcLrr7/Ohg0byMnJITk5GY1Gs8TQe1pcLhfHjh3j3LlzJCYm8t3vfpddu3YJNkJ4eDjT09M0NTVhNpspLy8nLi5uRUdWc3MzJ0+epLOzky1btvCDH/yAsrIy4uPjSUhIICMjQwiBtlqtFBQUCGV8ggQN9CtXrnDixAnBIzs6Oio4keY76kJCQjCbzTx69IjZ2VnWrl276jW+LHy1J/414ff70ev1rF27loKCAqanp7l27RpNTU243e7Fuy9BJpMRERFBZmYmqamphIaGCn+TBurhlZSUoNPpMJvNTE9PCwbScvh8PiYmJrh48SInT56kvb2d9vZ2zpw5wz//8z/z85//nF/+8pd8/vnnDAwM4HA4GB0d5fLly/zzP/8zf//3f8//+T//h08//VSYJAU/ej6fj6mpKa5fv87Ro0epqanBbDYvvgRGRkY4f/68sMpktVoX7yJgs9morq7m008/pb6+HpvNxuDgIKdPn+bXv/41R48eFV6a6elpbt68yaeffiqc1x+Ik79//z6nTp2ipqaGgYEB6urqOHr0KP/n//wf/v7v/55//Md/5KOPPhLOtfhDvho+n4+xsTEuX77Mv/7rv/KP//iP/PznP+cXv/gF586do6enB6fTufgwERERkRWRSCSo1Wph3A8aExKJBJ1OR2xs7Io1UJVKpTBRCU4IgueLjo5ecNzXYaSIfHP4A573np4ezp07x6lTp+js7MTtduMPRA3N31wul6AEbTabsVqtwqLxs9yCYZ937tzh7NmzPHz4ELPZ/NJPQJ8HxsfHaW1tZW5ujszMTIqLi4mIiICA0RkfH8+6detISEigq6uLzs5O7Hb7guiy+UilUrRaLTExMUu8XTqdThhT5j9bl8slhNra7XbKy8vJy8tbYBSGh4dTUlJCdnY2c3Nz9Pb2CpUvVmJyclLo3ykpKcTHx6NUKvH7/RiNRh4/fszU1BQFBQVC+lfwehMTE1mzZg3x8fFMTEzQ2dm56vwTQKFQUFZWxpEjRzh06BAFBQVotdonGpd9fX188cUXdHR0UFJSwrvvvsuePXvIyMggJCRk8e5fmqABff/+fWZnZykpKSE/P1/wzspkMlJSUgRDur+/X3gWyxF0rnV0dKDRaCgpKRFyZwl8JyIiIti8eTPx8fH09vbS39+PzWbDP2++bLPZaGho4MyZMzgcDg4dOkRKSsqKIcdKpZLU1FTS09MF7/pqNszLwuq95xvGF5DxTktLY8uWLcTFxdHU1MT169cZGhpavPuXJuhJlD9liRqfz8f4+Diff/45f/jDH/jss8/4f//v//GHP/yBs2fPcubMGX73u9/xL//yL5w8eZLq6mrOnj3Lb37zG06dOsUXX3zBH//4R/7pn/6Jjz76iNbWVhwOBwQ+mBMTE5w7d45f//rX3Lx5E6PRuPgS6Ovr48SJE3z00Uc8ePBAyN9dDrvdTl1dHefPn6elpQW73S4Yzn/84x85c+YMra2tWK1WJiYmOHPmDP/3//5fbty4wezsLL6A+ltVVRUfffQRn376KSdOnOCDDz7gD3/4A59//jmXLl3ij3/8I//3//5f/uVf/oXq6mrh2Cfh9Xrp6enhww8/5P/7//4/Tpw4QVVVFVVVVZw8eZJf/epXHDt2jPb2dtFYFRER+ZPxBRTO29vbmZ6eJi4ujpSUlCcaAH6/n9nZWUH9MiYmhrS0tFWjb0ReDJwBlc7Ozk7a29vp7u7GaDRitVoXbAaDgZaWFiG879SpU1y8eJHm5mbBaH1WW1DhtKOjg9bWVvr6+pibm3viBF/kTyPoMBgdHUWtVpOenr4kHUwulws5hpOTkwwNDS1wOjwtQcdHT08PVquV6Oho4uLiUKlUuN1uoVyg3+8XjNz5SKVSYmJiSEhIEIR1TCYTXq93wX7zGR8fZ2hoiNDQUMEjGYySm5mZoaurC6fTSWZmJpGRkQvmxHK5nLi4OOLj43E6nYyNjS0xtBYjlUoJCwsjLi4OvV4vROmtdozH4+HBgwfU1tYSHR3Njh07yM7OFvJ5u7q6mJiY+JMMMr/fT19fH0NDQ4SEhJCdnU1MTMyC56zVagUdAofDQU9Pz4qGqsfjYXp6WhArjYqKWtbDnpGRQWxsrDAXN5vNwlzZ6/XS39/P559/Tnd3Nzt27GDnzp1P/MZER0eTkZGBzWajp6fnT7ovLwrP1SjoD6xgKhQKCgsLWbduHX6/nzt37lBdXY31Cas5T8JqtTI2NobdbhcS3J8UxuXxeLBYLIJIU1NTE3l5efy7f/fvePfdd8nPz6evr49jx47xr//6r1y5coXw8HC+973v8bOf/YytW7cyOzvLxYsXuX79ujAQ+QMruwaDgdHRUUwmEx6PZ/HP43A4MBgMTE1NCTVmV0KtVlNWVsb+/fspKCggJCSEhIQEdu3axZEjRzh48CD5+fmo1WpcLhczMzPCbwfP6w+ENg8PD3Pjxg3OnDnD2NgYmzdv5v333+ev//qvOXDgAFKplIsXL3Ls2DGam5sFA3wlvF4vY2NjnDhxgqNHj+J2uzl48CB/8zd/w3/4D/+BAwcO4Pf7uXz5MpcuXWJ0dHTVwU1ERERkMf6AMEp3dzetra1UV1fzySefcPfuXaKjo9m1axcFBQVLFin9gWiS3t5e2trauH//Pp999hlXr15FoVCwc+dOysrKnmjgijzfBL+9we+d0+mkqamJy5cvc/HixQXb559/ztmzZzl16hSnT5/m1KlTnDp1irNnz/L5558v2f9P2S5dusSDBw+YmJjA5/Ph8/lW/daLPBuC8yCTyYRarSY2NnZBJB4B4yuo+u31epmZmWFubu6J85Pgvj09PcJYdOzYMaqqqoiOjqayspLc3NwlHkOfzyfkdS5GFagt6vF4MJvN2Gy2VfvJzMwM09PT6HQ6wSgmkJcbNLQUCgXx8fFLrgNAr9cTERGB1+vFZDJhtVqXva7leNL9CTI1NUVdXR3T09OkpKTgdrs5c+YM//AP/8D/+l//i7//+7/nl7/8JZcvX2ZycvKpf38+Pp9PKA0UFhZGQkLCEk+vTCZDq9USFRWFP+BIWskInN+24Lu6XHt1gRrcvkC6wdzcnHD9k5OT3Lx5k/v375OXl8e3v/1tQWdmuXMF0ev1JCYm4gs40hwOx6r7vww8V4YqAcPQ4/EQHx9PZWUl+fn5DA0Ncf36dSGu/6vg9/sZGhqivr4en89HVlYWaWlpy76c8wnmSxqNRmw2G5s2beL73/8+P/7xj3n//fd59913ycrKoq+vT8gJ/f73v89PfvITfvzjH/PDH/6QDRs2CDkOw8PDCzr//AnT4slTkJX+fTEajYZNmzZx+PBhITk8NTWVQ4cO8bOf/Yy/+qu/orS0dMFALAmIKwV/QxLItw0a0aGhoRw8eJCf/exn/PCHP+THP/4x/+E//AcOHz6MXq/n9u3b3L17F4PBsOqA6XA4uH//PhcuXEAul/Ptb3+bH/7whxw5coQjR47wox/9iH379uH1eqmurqazs/OJxq+IiIjIfDweDw8fPuQXv/gFP//5z/n5z3/OH/7wBzweD2+99Ravv/76kpz54HGtra386le/4h/+4R/4+c9/zgcffIDBYGDPnj1861vfIj09ffFhIi8owe+60+mktbWVc+fO8dlnn3HixAlOnDjBZ599xrlz56itrWV8fByLxYLFYmFqaora2lpOnTq1YP8/dQuWRpqcnIR5Wg0iXy9Op1Mw+ORyOVqtdlnPmFqtRq/Xo1QqmZubw2azrWowBRf879+/z29+8xthLDp69ChOp5O9e/eyZ88ekpOTkcvlyOVyIiIiiI6OBqC3t1eowxkkaPhOTU3hcDjwer2rXoMvECE3NzdHaGgoYWFhQtvcbjdmsxmn0yn8bTmnTUhIiDBfnJubw2q1fuU5+EoMDAzQ39+Pw+FgfHycW7ducePGDbq6uhgaGqK2tpajR4/yz//8z5w9e1Zw9nwZ/IFcUKfTiVqtJjRQz3XxO6ZUKtHNq9O6UlsVCgVRUVFERkZisVjo7+/HYrEseR7Dw8OCIyi4AAVgsVi4f/8+ly9fRqlUcujQIQoLC5FKpcJi2kqoVCrCw8NRKpWYTKYFXtqXlefOUA0+oGDc9yuvvEJkZCQPHz7k+vXrTE5OCp1rtYc5H38gHr+mpoba2lri4+PZuHEjSUlJyw5KyyGTycjJyWH79u3k5+cTGRlJUlISZWVlFBYWotVqCQ8Pp6KigvXr1xMZGUlkZCRr165l/fr1qNVqxsbGGBkZWRJOsPhlmc9qf1uMNFDQXqfTCeJISqVSWBULDw9H/ZTleLxeryBUtX37drKystDr9YSHh5Ofn8/BgwdZt24ds7OzNDU1MTo6umIecXA16cGDBwwODrJu3TpeeeUVQcQpKIleXl5OfHw8k5OTdHd3/8kedBERkb8sgmN9sEh8W1sb4+PjEJh0BScCi/H7/VgsFnp7e+no6KC9vZ3h4WF884rUL3ecyIvJ/G+gTCZDqVSiVCpRqVSoVCrhv4P9JTjJ9AfECOfv+6w2hUIhhvp+w7jdbux2O263W5gvLY6aCC7eB5+Px+MRcppXw+v1YjQahVzG9vZ2xsfH8fv9wrmC/VAZKFVTVFREaGgod+/e5fLly3R3d2MymZiamqKhoYHLly9TX1+PPaAqrFih3AmBtlmtVhwOByqVCo1GI7TN4/Fgt9vxer3I5XJUKtWyfS/YbgLnc7vdz9woGh8fZ2ZmBovFwvDwMDKZjO3bt/OTn/yEv/3bv+W73/0uWVlZtLS08OGHH1JbW/tUHu35+P1+bDYbbrcbhUKBLCAEuhipVCq01xkQOV0OqVRKRkYG+fn52O12qquruXXrFoODg5jNZiYnJ3nw4AGnTp2iu7sbv99PSEgISqVSWBS9dOkSk5OTbNu2jW3btqHX6xf/zIrXGFxAsNvtWL+kTsyLyNKe+Zwgk8mIjY1l8+bNrF+/nrm5OW7dukVdXR0ejweZTLbsi7WY4KrSvXv3OH/+PBaLhU2bNrFhwwbCwsKW7QjLERoaSkpKCsnJyYQECh/LAkqTMTExhIeHEx0dTUpKilAXSxJIqE5KSkKj0WAPqAWvFE7wLJAso5gb/Lf522r4Ays60dHRFBYWkpCQIAyIEokElUpFdna2UBNrYmKC8fHxFdvldrsZGxsTcjPsgZpRly5d4sKFC1y4cIGrV6/S0tKC2WzGYrEwOjoqGqoiIiJfCplMRnFxMX/1V3/Fe++9x5EjR9i+fTtut5uLFy9y/vx5BgYGlnzYZTIZmZmZHDlyhO9///scOXKE3bt3o1KpuHnzJqdPn6a9vX3VqBGRF4eg0alSqSgoKODAgQO8+eabC7b9+/cLIjphYWGEh4cTFxdHeXk5b7zxxpL9/5Tt4MGDbNy4UajTG7w+ka+f4HzoaeZGPOV+koAYW0lJCd/+9rd57733+M53vsO2bdtwu91cvXqVS5cu0dvbi8vlQiaTERcXx9atW1m7di3j4+McPXqU3/zmN3z00Ud89NFH/PGPf6SqqkoI1w0LCyM0NHTFebDb7cbhcAhGeFCbZTFPmhcG+6F0mcoVzwKTyYTNZkMqlZKbm8uBAwd4++232bNnD3v27OHIkSO8++67pKWl0d7ezs2bN5mcnPyT3o/V2hA872r7AGRmZvLqq6+SkZFBV1cXH374Ib/73e/44x//yIcffsi//du/8fjxY2w2GwqFgvDwcEJCQhgdHeX69eu0tLRQUFDA3r17SUxMFJ7N/HYF5+KLkcvlKBQKXC7Xqgb1y8LSXvucEHzRg17M7OxsOjs7uXnzJiMjIygUCpRK5aqdyefzYbVaefz4sTDRKCsrY9++fWRkZCwb6rAScrmckJCQBStYkkDYrEKhEDpOcBV2/nGqgICTb5Xcg6+Tr9qJQ0JCiIiIWJLcLZFI0Ov1JCUlodfrsVqtmM3mFSdxHo8Hg8HAzMwMDoeDpqYmPv30U373u9/x29/+lt/+9rd88MEHfP7554yNjSGTyfDPyyMSEREReRqkUinZ2dns27ePt99+mx/+8Ie8//77VFRUMDw8zKlTp7h9+zZzc3NLjktOTmbPnj289dZbvPfee7z//vvs3LkTs9nM2bNnuXLlCtPT0wuOE3mxCE7Ig5N2tVpNfn4+27ZtY8eOHQu2nTt3snv3bvbu3btg2717Nzt37mT79u1Ljvmq27Zt21i7di0xMTHI5XJkMtkSz57Isyc4P1MoFPjm1dadj9/vF4w+j8cjeNNXm3sS8JJmZ2eze/du3n77bX7wgx/w/vvvs2nTJiYmJrh8+TI1NTXCmKLVaikvL+fIkSPs2LEDt9vNnTt3OHXqFNevX8doNBIfH09cXBzh4eHExMSg1+tX7Cf+RXXq5yOTyYQIE7fbjdPpXNJuAsZu0AER9PwvZ+z+KTgC5R9jYmLYtGkTFRUVpKamEh4eTlhYGCkpKWzZsoWysjIkEgn19fUYDIZl27USEolEiIzxer0r5pR6AuUgg/uv1taIiAi2bt3K4cOHWbt2LUajkWvXrnHy5Elu3bqF3+8XIhGDyvNer5d79+5x/fp15ubmSExMxO12097eTmNjI42NjUxOTuIJiDUFPfEzMzPfuN3wPLHyU3gOkAYUxMrKyti6dSsqlYrq6mpqampwOp2rDhY+nw+LxSJIPz98+JDMzEzefvttysvL0Wq1Kx67HF9m38XMP3a5l4M/8fxfF9KAbPdyL6s0sEIXNCpXe4l8gbqpTqcTeUBJLi0tjZSUFGFLTk4mLy+Pbdu2sXfvXkpLS4VcAREREZGnIbjAGRERISj1VlRUsH//flJTU+ns7OT+/ftCLuD841SB3J9gZEx5eTn79+8nNzeX4eFhHjx4QH9//4LjRF48lEolMTEx5OTkkJeXR1ZWFjExMUK6TnCLj4+npKSE3bt3c+jQId544w327t3LmjVriI6OXrL/n7IF+1xOTg65ublCmaXVvqsifzoqlQq9Xi8IFFmtVtyLUpj8gXzT4GK8Vqt9ohFDYEwJCQkRjMrU1FQqKirYs2cPmZmZgmbK+Pi4ECUYHR3N9u3b+dGPfsT3vvc9du7cSUVFBdu2bWPfvn0UFBSgVCoJDw8nOTlZUNZdDrlcjlqtFoyz+U4ShUKBXq9HrVbjCNS0X9xuApUkgurTWq12QfjwsyI4x9Tr9YIRLp9XnkUeqEubkpKCWq1mfHz8ierDi5FIJERGRqJWq7Hb7dhsNjwez5JzuFwuzIEykREREUIY8HLIZDJSU1PZv38/P/rRjzh8+DDbt29n48aNvPrqq7zzzjuCOFJycjKJiYnMzs5SW1srqNA3Nzfz8ccf85vf/IZ//dd/5fe//z0NDQ04HA7a2to4fvw4H3/8Me3t7QueT3ABQaFQrGoHvSws38OfI+QBafBgSMTIyAjXr19ncHBQWB1dTDDct6GhgdOnT1NVVUVcXBzf+ta32LZt2xL58S/L4s4dxD+vLtrif18OScAjywqhPvPPt/hvT2L+/svdo6fBH/BqLv5Y+gPqzBaLRch/CK7OLYdUKhVWLdVqNRs3buR73/seP/nJTxZsP/3pT/mbv/kbfvCDH/DKK68QLhY5FxER+YpIAukZOp2OzMxMkpOThTILJpNp8e4LkMlkaDQaMjMzycjIQCaTMTU1tUTgROTFIrggkZqaymuvvcbevXvJzs5ekNoS3GQBFdC4uDiSk5NJSkoiLi5OWOR+lpsioLy6adMm9uzZIyzULv72ijxblEqloN/hcDiYmppaoiHi8/mYnZ1lZmaGkJAQQRl4pfnOckjmjUUZGRnCWDQyMrKg6oJcLicmJoYNGzbwzjvv8OMf/5gf//jHHDlyhNzcXIxGI2azmfj4eLKyslasDU2gbVqtFnWgysN8hWClUikskrjdbiYmJrDZbItPIbRbLpcTGRmJRqP5Uu1+GsLDw9FoNHg8nmU92gTunzwgfiT5CvNZiURCSkoKOp0Os9nMxMTEkjxXt9sttFcmk5GUlIRqXh3b5VAqlSQnJ1NZWcl3vvMd4XkdPnyYxMREent7cTgcrFmzhtTUVAhEKgb7gM1mY3BwkL6+Pvr6+oQcV6/XK+TsBv8tOBZ4vV7B2NZoNF/a6fYi8mx73NeAJOCCLygoYMeOHcTFxfH48WPq6upwuVxLOm5wUGloaODcuXPU1NQQHR3NO++8w549e4iPj/+TjNRnRfDjFBISgkwmE3I35+N0OjGZTNhXKS69EsF74n+Ct3M5gvfUZrMxMzODc1FNU39AQa2vrw+z2SysCM9fBZtPcPCNjo5GIpHg9XqJj4+nqKiINWvWLNiChZgTEhKeOEiIiIiIBFlpMc/v9+MJqMn7/f4l34yVCB43f7HuaY4Teb6RyWRERUUJQofR0dGrzgmC/eVp+81XQRoogZKbm0t5eTlpaWkolcoV+7TIs0EaqE2amJiI0+lkcHCQ6elpPAG1V3+gjODQ0BBTU1MkJCSQlpZGaGgokkA9UrvdLqjwPonFY5F0mZxPSWDOm5CQICyUqdVqmpubefToEQqFgtLSUuHfVyLYpzQaDTabDZPJJHjlZDIZkZGRZGZmolAo6O/vZ3p6ekEbnE4no6OjTExMoNFoFtRhnW8sPU27VyMpKYmYmBjBMFtcqtHn82G32zEYDLjdbhISEoTrcAfqz46MjAiqvsu9M1KplLS0NJKSkrDb7XR3d2MwGBb8jsViYWBggOnpafR6PTk5OYQEqoJ4PB5sNtuyz1kmkwmpcFlZWaSmpiKVSrlx4wYPHjwgNjaWiooKEhISSEhI4LXXXuP999/nJz/5Cd/97nc5fPiwsL399ttCCcns7Gz27NnDgQMHyMzMFObXTqdT8ICHhYWh0+me+eLB88YL0brgS1VRUcHWrVux2+00NDRgMpkWdMqgkdrY2Mj58+e5c+cOoaGh7Nu3j+3btxMeHo7T6WRubo65uTmcTueXNuKeFZJAWEhMTAxqtZrh4WH6+/uxWq3C6ldPTw/Nzc1MTU0teTlWIxjyoVAocDgcQjHz4GrVci/yckxOTtLU1ER/fz92ux1PQO1udnaW+vp66urq8AVK/SQmJq6Y8yuXy0lISKCwsJDQ0FAePXpEXV0dMzMzuAMqcj6fT8iVCP6biIiIyNPgcrkYGxsTPCIul0sYT2ZmZmhpaaGvrw+VSkVSUhIREREQWEWfnJxkbGyMubm5BceZTCZaWlro6OjA6/USGxsriN2IvNjI5XJ0Oh1hYWErLrB+08hkMkJDQ9HpdMIi7dN+q0W+GhKJhLi4OPLy8ggJCaG3t5eWlhbBKHI4HAwPD1NXV4fBYCA3N5fs7GzUajVut5vh4WEePnxIXV0dY2NjOJ1OwTM7NTW1ZEyZnp6mtbWV3t5elEolSUlJhIeHCwslQUPW6XQK4pvd3d1cvnyZs2fPMjY2RnFxMZs2bXqi00USCHeNDJRQmZycFPJNpVIp4eHhlJSUEB0dTWdnJ42NjUxPT+MOhJX29/cL/5aYmEhOTg4ajQa32834+DgPHz7k/v37jI2NCQbwVyE9PZ38/HykUiktLS20tLRgNBpxu914PB4sFgvd3d20t7cDUFpaSlRUFBKJhImJCe7cucPZs2d59OgRs7Ozy74zwQWJ8vJydDodzc3NtLe3Cwafw+Ggr6+PR48eYbVayc7OJicnB7Vajd/vZ3BwkHv37lFXV8fU1NSChYzg85qbm8NgMNDW1sbZs2f5+OOPsdls7Nq1i7KyMkF4dcOGDRw8eJBDhw4tEVV74403yM3NRaVSkZGRwWuvvcbu3btJS0sTximLxcL4+DhSqZS4uDjUT1nJ40XmuTJUg+GvwW0+SqWSjIwMdu3aRV5eHrOzs8zOzgqGl9/vx2q10tjYyNmzZ7l8+TJTU1PExMSg0Wjo7e2lurqaO3fucPv2bWpqaujq6noqaef517Tcviv9+3wW7yORSAgLCyM7O5uoqCh6e3u5cuUKd+7cobGxkZqaGi5evEhdXZ0QkrH4HIv/O0gwPCUiIoLp6WkePHjAvXv3aGtrW7CKFDw+eN+DBFeOZ2ZmuH//PleuXOHBgwd0dnbS2trKrVu3OHnyJB0dHeTk5LBhwwbi4uKEF2nx/ZLJZERERLB582aKi4vp6enh5MmTXLx4kYcPH9Lc3CysFgZ/52mei4iIiIjP58NgMHDhwgVOnz5NTU0NTU1NtLa2Ul9fz5UrVzhz5gz9/f3k5uayYcMGoqOjhYXNGzducPz4caqqqmhoaKC1tZWGhgZu3rzJqVOnaG1tJSkpiQ0bNgjhWyIiXyfit++bIyoqirKyMvLz85mZmeH69evcuXNHGAeuXr3K/fv30el0VFRUkJ6ejkKhwGg0cvv2bX7729/yb//2b9y7d4+ZmRlGR0e5ceMGFy5coKqqisbGRlpbW3n8+DGXL1/mwoUL9Pb2kpycTGlp6YK5k8fjYWRkhMePH1NTU8Ply5f56KOPOHr0KL29vRQUFLB7926KiorQaDSLm7KEuLg4kpKSsNlsjIyMLJhXabVa1qxZQ3FxMUajkS+++ILbt2/T1tZGU1MTV65c4eHDh4SGhlJeXi54GK1WK9XV1fz2t7/ll7/8JTU1NVgslmX77OK54HJER0ezZcsW8vLy6Ovr44svvhDuf3t7O/fu3ePChQt0dXWRnp7O1q1biYmJQSKR0NXVxenTpzl9+jQdHR2rGswqlYpXXnmFoqIiBgYGuHz5MtXV1bS1tVFXV8fVq1epra0lLCxMKJ8oDYhNXbt2jV/96lf87ne/4/Hjx0LYsM1mo7+/n7q6Oqqqqrh48SL/9m//xtGjR5mammLnzp288cYbpKWlCaKrOp2OyMhIoqKilmzBWreSQMRlWFgYERERC/JQDQYD/f39hIaGfmlR2BcV2d/93d/93eJ//Kbx+XwMDAxQU1OD3++nvLycgoKCBfH3wQen0+lwOBxC7HdycjKbN28mOTmZqakprl69ypUrVxgaGsIfyLEcHBwUjKCHDx/y8OFD2tra8Pv9JCYmCuVkFuPz+RgfH6e2tpaJiQmKi4uXlLWZnZ2lra2N7u5uwsPD2bhxIxkZGcLffT4fHR0dPHz4EKVSSVlZGXl5eYK73u/3MzU1RV9fHwMDA8KKXlC4QxVQDFYqleTn51NSUkJ4eDgmk4mGhgZhwNu0aROJiYkQWJm12WwMDw8LMe7d3d1MTk6i1+uJjo7GbDZz//59hoaGWLduHRs3bkSv12OxWHj8+DGNjY0A6PV6Jicn6ez8/9l7z+i47jO//zN9MCgDYAa990IQlSQIdlIiKYpFkiVLlptsr2Pvxlt8cnKSvMvmRc5JNtms7Wxs2bIkq1ONkljF3itA9N57HbTBzGD6/F/8595FJylRFEXdzzn3iMLcuf3+5vn+ntZKc3Mz5eXlXLhwgdraWgwGA8888wzbt28nMjIShULB0NAQNTU1jI2NkZSUxNq1a8XPhJdwdHSUrq4ucZuCSL1+/Tr19fW43W7i4+PnXWcJCQmJpRCMu3fffZdLly5RX19PXV0d1dXVXL16lStXrtDW1kZkZCT79u0TU0CEsfeTTz7h888/FyfMBCPx8uXLNDQ0EBQUxM6dO3nyySdJSUlZ8rdCQuJ+4fOHmwoeuZiYGKlew1eI0t/RQbD3Ojs76e7upr29nfLycm7cuIHZbGbr1q0cOHBAFKpDQ0OcPXuW06dPMzIyQmxsLCkpKZhMJo4fP865c+eora2lvr6eqqoqcSzq6OggIiJCrB4dHx8/z1smTJxduHCBW7duUV9fj9frZe3atezfv5/169cTERGxojdVQKVS0d/fT0NDAyqViuzsbCL8laXl/n6cSqWSgYEBWltb6evro6uri5s3b3Lt2jUsFgvr168Xi8ppNBomJiY4ffo0x48fp6Ojg+TkZHJzcwkJCZlnr8lkMgYHB6murmZiYoLMzExKSkrQ6/XzjlEInfX5fAwODtLe3k5nZycdHR3U1NRw6dIlampqCAoK4qmnnmLnzp0YDAYALly4wPHjx/F4PKxfv568vDx0Ot287QsIziGXyyXmhfb19dHe3s7169e5ceMGTqeTLVu28NRTTxEfH49CoWB2dpZ33nmHM2fOMDIyInrVAwMDGRwc5NSpU3zyySdcvnyZW7du0dTUhFar5bHHHuN73/se+fn5d5VH6vP5sNvtXL16lZaWFrKysli3bh1Go1H8zXE6nVRVVXHy5En0ej3f+c53SExMvKtn4ZvMQyFUAcxmM1NTU8TExFBUVLRk/L3MHy4r3HS9Xk9eXh7FxcVERkYyMzNDb28vdrtdnEkKCgoS8wDkc/pABQQEkJiYSHp6+rJCVZgxmZiYQKfTUVJSIoavCg+d0+kUww1SUlIoLCwkKipK/Nzn8zE1NYXZbCY+Pp7CwkKSk5PF3NTAwEBRtM7MzGAymTCbzWi1WoqLi9m8eTMxMTEYDAays7PJzMwkODhYDE2TyWRkZ2dTWFgovrwKf+lxjUYj5hLMzs4SFBREZmYmcXFxeL1exsfHCQgIoLS0VJyhM5vNVFVVUVNTQ0xMDDt27CAiIoKhoSG6urro7+/H4/GQnZ3NU089xa5du0hMTBRngWw2G9PT0wQEBJCTkyMKa9mcvIvo6GjUajWzs7NMTExgMplE73hISAipqamkp6cvGvgkJCQkFiIY9iaTiZmZGcbHxxkaGmJgYIDJyUl0Oh2rV6/mwIED7Nq1i+TkZNEwdLlcjI+PMz09zeTkJMPDw/T39zM+Po5SqSQrK4s9e/bw5JNPkpWVJeXNS3zlSEL1waPVagkPDycoKAiHwyGOA5OTk4SGhrJ161aefvpp8vLyCAgIQCaT4fAXZhsfHycqKoo1a9aQlZWFQqFgcnJSLMwzMDDAwMAAExMTaP29Vffu3cvOnTtJTU2d5y2zWCzcvn2bqqoqrFYrer2e3Nxcdu/ezZNPPklRURHh4eF3Ha6uUqmwWq20trYyMTFBdHQ0SUlJBPiLX2o0GoxGI3q9HofDwcjICH19fZhMJvR6PZs2beLJJ5+cJ7acTicjIyMMDw+L3sdVq1bNs4sFBHswKCiIvLw8cnJylvQEBwYGEhkZiV6vx+PxYDKZ6O3tZXBwEKfTSVpaGk8++SRPPvmkKOxnZmY4deoUt2/fJi8vTwyRVa1QqVej0YgF0YTz7e3tZWpqCqPRyPbt2zlw4AA5OTliSK3P56OtrQ2TyURcXBwbNmwgLS2NgIAARkdHuX37No2NjbjdbgwGAwUFBWJvZOF8F16X5RAmS3w+H4WFhaxevXqePhkeHubMmTNUV1dTUlLCnj17vhUOHZnPt4w//gHi8/mYnp4WRVBUVBQGg2HZB85mszE4OMj4+DiBgYHExcURHBzM7Owsw8PDYnz7cvh8PlQqFUajkejo6CVfMGE9q9XKwMAAZrOZiIgIYmJiUM/p3yr8oIyPj6NWq0UP7dxtTExM0N/fD/5QjPDwcNFd7/W30enr66Ojo4ORkRGxklhaWhp6vZ6pqSksFgt6vV6MSbfb7YyMjGAymQgKChJFuYDH42FiYoLe3l4GBgZwOBxERkaSnp5OREQETqdTTFyPiIggMjKSgIAABgYGeO2113jzzTdJT0/n7/7u70hLS6Ovr4/+/n6c/n5XycnJJCcnExYWNm/QtFgsDA8PMzMzQ0hICDExMYtmuIR1hJwym82G2l9yPTw8nKioKIxG47ci9l5CQuLL4fNXIR8eHhbHldHRUXFyLi4ujtjYWDE3de6kpNPpZGxsjMHBwXm5qlqtlpiYGLHaq8FguGvjUELiyyCEpDc0NDA6OkpxcTHJyckLV5O4z7jdbqampuju7qazs5Px8XG0Wi2JiYmkpqYSExMzz3nicDjo6uqipaUFlUpFVlaW6AQwmUziWDQyMoLdbken0xEdHU1CQoKYm7pwTJmdnaWpqUnMpxdyTAUR90U8ZwMDA7zxxhucPXuW4uJifvSjH5GTkyPa18Lz1tPTQ1tbG6Ojo2i1WhISEsTzFoQt/jFzYGCAmpoaPB4PRUVFxMfHLxmCarFYxDE1LCyM6OjoZSf7vF4vU1NTYr2WoaEhvF4vRqNRtDfDw8PFa9Da2sr/+B//g4qKCl588UV+8IMfEB8fv6TTaS4+nw+TyURXVxcdHR3iZObc+zz3GH0+Hy0tLdTU1BAcHExeXh4xMTGoVCrGx8dpbm4WC06FhYUR7m9tdS8CVUCIDhoZGSE8PJzY2FhxYsTtdnPlyhVefvllxsfH+Zu/+RueeOKJRfb1o8hDIVRZEMsuu4sKe8K6zMmpXMhSp7bUeveThedwtwjGlt1uR6FQoPG3c/myeP1FirxeL0qlEqW/xDf+fQpJ5ENDQ2Jy/nvvvcebb75JRkYG/+k//Sc2b96MTCbDbrfj9XrR3KfGz945DbblcjkqlQqFQnFP101CQkJCQBhHZ2dn8Xg8YlifEPGxEi6XSywap1AoxIJ09zqWS0h8GSSh+vXi8Xiw2+04nU4xOm05W8ztb6kik8lQq9XzhORcm87r9Yp2nSDolhpTfD6fWERIsNfmrrvUd+6E2+3m8uXL/OUvf2F6eppnnnmGPXv2iHmeAj5/v1jBBl1p3PR6vdjtdvB7KZcS0IL9LdjD3OXxz71uPp9vWXvz1KlT/O///b/R6XT8/Oc/Z+vWrXcVYisgRBu6XC7xfOfax0utq1Ao5t1nj8eDy+XC53d+LbRf5577vTBXu8j8Xt2+vj7eeustTp8+TVlZGX/9139NQkLCouvyKPJQhP76fD4mJydpamqio6MDi8WCVqudFxIxF4/Hw9DQEPX19YyPjy/5ILv9zZtNJpMYWupyuVAqlYsepvuBIPqEnFCv10vgPfSckvn7RGm12kUD3pdB2O5yL9HY2BiHDx/m4MGDuFwujEYjHR0d1NbWEhYWxsaNG0lKShKv8Vzj7csiHJtarUalUolh2RISEhJfBJlMhtfrxWq1YrFYsFgsokEljDHLIRiSAQEBYjSH3W4XWzAo/I3pJSS+SnxS6O/XgiCQhDQ0q9WKy+VC5q+PstS7L0ywL/X5XJtOSMXy+dPJZv0tB+X+dLS535HL5Xg8HqanpzGZTExMTGC1WsGfT7twP3dC7s9FHR4epqamBrfbLUbWzbUzXS4XZrOZ6elp8fiWs5eFa7LUeQuCV0jrmnv8S62/kLnXbTl70+PxUFNTQ29vLxs3bqSsrIyAgABx0mCpY17I7OwsZrOZmZkZcTJhufOVy+Xz7NS5fxfs67n2q9frxWw2i4VQl9rmclitVvH5E66F2+3m1q1bfPrpp3i9Xp555hkKCgqW9GI/ijwUQtXj8dDc3Mzbb7/N8ePH6e7uJigoiIiIiHkueAGHw8G1a9d49dVX6e7uJjo6GqPRiEqlwuHv/VRRUcHJkyc5duwYZ8+e5erVqzQ3N2OxWNDpdAQGBt43MYj/mFpbW/noo4/45JNPmJ2dJTEx8Z5meB40Xq+X0dFRjh49yqlTp4iMjCQjI4Ouri5qamoICwtj06ZN80pjS0hISDxsCMZRS0sLFy9e5LPPPuPkyZNcunSJ8vJy+vv78fl8BAcHzwvfWw63201bWxtnz57l+vXrTE1NERoaSnBw8MJVJSTuK5JQfbD4/ClenZ2dXL16lePHj3PixAkuXLhAeXk5XV1duN1uQkJCvlQ6ktPppKGhgTNnzlBVVYXdbickJEQM7fR4PExNTdHc3MyFCxc4cuQIJ0+e5OLFi5SXl9PT04PP50On0y1yzNwJk8lERUUFfX19pKWlUVJSIhbp8Xg8DA8Pc/nyZQ4dOiRW/21pacHhcBAYGEiAv6bKSvj8aW6NjY2cO3eOY8eOcerUKS5dukRFRYU4Buv1+nnpc18UmUxGcnIyCQkJjIyMcPXqVVpbW1EqlYSGhqJaxgtut9tpbW3l9OnTHD58mNOnT3PlyhWam5uZnZ0lMDAQnU53T9d3Li6Xi/r6eo4ePcq1a9dQKBSEhoYue87Cb1dnZyfV1dWcP3+eEydOiM6isLAwFAoFY2Nj1NfXMz09TXZ29reqZsJDI1Sbmpr4+OOPuX79OoODg6jVahISEjAYDIseGEGoHjx4EKfTSUFBAUlJSQB0dHRw+PBhPvzwQ27cuEF/fz8mk4n29naqq6tpaWnBZrOJCeT3S4DZ7Xaampr47LPPuHz5MkajkZKSEsLCwpZ8OB8GBE/2tWvXaGhoIDs7m4KCAtETnZSUxPr168XqZxISEhIPI7Ozs1RUVPD73/+e48eP09zczMTEhBh5U1dXR39/P0p/T+cAfyP3pfD6C1p88MEHvPvuu1y7dg2v10t2djbR0dELV5eQuK9IQvXBMjs7S2VlJR9++CFHjhyhpqaGoaEhhoeHaWpqoqamhq6uLpRK5Yo1Te5ER0cHH3zwAR988AE1NTVotVrS0tLEvHm73U5DQwMHDx7ks88+o6WlhYmJCYaHh8UxTLCNDQbDXYup2dlZrly5wpkzZwgNDeXJJ59k9erVBAQEiBVwP/nkE95++22qq6sxm80MDQ3R0NBAe3s7Xn+eaHBw8Ip2oNfrpby8nPfff5/PP/+c1tZWTCYTg4ODNDY2UldXR19fH8HBwWKtlS+Dx+NhfHycK1eucOTIEU6dOkV/fz/R0dGkpaUtuX273c7169d57733OHHiBJ2dnUxPTzM4OEh9fT2tra3Y7Xaio6MJCQm5q+s7F7fbTU9PD6+++irvv/8+169fJy4ujoyMDLFo6lwcDgc9PT2cO3eODz74gKNHj3LlyhVxkmDVqlXEx8ej1WoJCgrCZrPR2NjIzMwMWVlZS+qjR5GHQqh6vV66u7u5dOkSw8PDYox+WFiY6JWci8PhoK6ujkuXLhEWFsaGDRtITk7G6/WKpaanpqZYvXo1O3bsoKysjPT0dNxuNy0tLfT09BAUFCRu+37caJ8/t8DpdBIeHk5ZWRn5+flfKKH6QeHzVyS+fv06jY2NZGZmsn79euLi4khKSqKwsJCsrKwv9MJKSEhIPAiEcLpbt25x4sQJ4uLi2Lp1Kzt27BCroY+NjdHY2IjZbCYmJoaEhIQljS6fvx/3mTNnOHToEA0NDczMzBATE8O6deuIi4tb+BUJifuKJFQfLFarlaqqKm7fvo1arWbt2rVs27aN4uJioqKiMJvNNDQ0MDw8LBZlWyocdSXGx8c5duyY2A/UbreTmppKfn4+ERERyOVysUhRa2srAQEBbNq0ie3bt4uVfkdHR2lpacFutxMbG0tUVNRdhX52d3dz+PBhurq6WLt2rdhOEGBsbIyjR4/y7rvvYjab2bZtG3v37qWgoACvv7Vif38/ISEhxMfHr2jP+nw+Ojo66OzsJDQ0lLKyMrZu3Up+fj56vZ6hoSExqlFok/NF7Uqn08nFixd5//33KS8vZ3h4mLGxMVQqlVhdeGGRIZ/PR21tLa+//jrXr18nJiZGbBGUl5eHQqGgtbWVjo4OdDod6enpi7axEj6fj/HxcQ4fPswHH3zAyMgI4+PjlJSUUFBQsKi7yOzsLA0NDXz44YccOnSI1tZWQkNDyczMpKysjA0bNrB69WqxyrNWq0Uul9PV1UVTU5PYCeTb4FV9aIRqV1cXV69exW63Ex4ejtVqxeFwiBUb53o+nU4n9fX1XLlyRRSFQm8rj8dDUFAQBQUF7NixQ2y9kp2dTVRUFCMjIzQ1NSGTyUhPTycqKmrZEIGFeDwenE6nWFFYNqfIhlwuJzAwkPj4ePLz81m9evW8HADfnMJPwv8LidgejweZPzdhLnM/F7670iAx9zOvv4iS0+kUP1v43YVCNSMjgw0bNpCZmUlaWtqiqr7CNoXzl0s5pRISEl8zMn9eqtAeYO/evWzdupWCggKys7NJS0tDpVLR0dFBd3c3BoOB1atXL2mEuN1uqqurOXjwIGNjY8j9Dd+TkpLYsGGDJFQfcbxeLw6HA5vNhtvtRr4gh/BB8E0Sqj6fD7fbjc1mw263i9frm2QXCLZYREQE69evZ9u2bWIrQkGsdHZ20tzcTGRkJDk5OUt6x5ZCuJfXrl3jo48+YnJyEpm/OE5WVhZFRUWiYJP5CzLFxsaydu1aNm7cSEFBAVlZWaSnp4vpZTMzMyQkJJCenr7IibMQt9vNzZs3OXnyJDqdjl27dpGbm0tAQACzs7PU1NRw8OBBuru7eeKJJ3jxxRcpLS0lOzsbg8HAyMgIzc3N+Hw+UlNTiYyMXDEKUe3vWLFmzRrWr18vjsFxcXE4HA6xQm5BQQEpKSl3JbSXwuFwcOvWLXp6esjIyCAhIQGz2YxSqaSwsFBslyMgTEC+8847HD9+nJiYGJ577jn27NlDQUEBmZmZREZGMjExIU5OLrTh74TFYuHGjRu8++672Gw2goODmZ6eprS0lOLi4nlC1el00tzczIcffsjnn3+OSqVi+/btPP300zz22GOibhHSHwX7XaPRMD4+TmVlJW63W9zuN+l9+yI8dEJVLpeTnZ0NIIY5CGWphZsxV6iGhYWJQlWr1YrtaoQy08HBweh0OoKCgjAYDExNTVFRUYHP5yMnJ0fsaboSTn/fqKamJm7fvk1DQwODg4M4HA5UKpUYe+5wOLBarTidToKCgsTBzOHv1zQ0NCQKx7GxMRoaGqiurqazsxOr1SoWK/L6y5s3NjZSVVVFW1sb09PTyP19r4TEbOFHwmQy0dPTg8PhQKPRYDabaWtro7q6mtraWnp7e7FarSj8xULmiueFQrWsrIzY2FiCgoLQarUoFArsdjtDQ0M0NjZSUVFBXV0dw8PDuN1usfjTo/6iSEhIPLwoFAr0ej0ZGRmkpaVhMBjEXCO9Xo9Go6GtrY3GxkYMBgOlpaWEh4fP24bX62VgYIB3332XiooKCgsL0el0DA0NERcXx8aNGyWh+ohjs9loa2ujtraWiYkJAgMDl+z7+FXi8xf1GR0dxWazPdRC1e12Mzg4SGVlpejtU6vVqNXqb4xgFcaOxMREUlJSiIiIICgoCJ1OJ+aQdnd309DQgNFopLCw8K4FjNfrpbW1lYMHD9Le3k52djZqtRqLxUJ6evo8oSr3Fz2KjIwkJiaGsLAwdDodAQEBhIeHMzU1RWNjI1arlfT0dPLy8ggJCVm4y3lMTU1x9uxZKisrycrK4rHHHiMuLg6ZTMb4+Dhnzpzh3LlzREVF8cMf/pA1a9ag1+vR6XSEhoYyNTUlCrf4+HhSUlKWnODDP2Go0+mIjIwkOjpaPH7hHKxWK9XV1ZhMJtavXy/2Kv2iCOJ5w4YNBAQE0NraisvloqCgYJFQ9Xq9dHR08Je//IWenh6eeOIJ9uzZQ3Jy8rx77XQ6qampYXh4mLS0NDIyMu7KY+lwOGhqauL999+nqamJTZs24fP5GBgYYN26dRQVFc0Tqv39/Rw7dozjx48TEBDAs88+y9NPP01+fj6xsbGEhYURGBiIckEVYuHZqa2tZXR0lJycHBITE1ecPHgUuPOU0APE5/Oh1WrJycmhpKQEuVzOtWvXuHnzJtPT0wtXX4RcLker1RIWFiYaJ8KDoVAoCA8PJz4+Hp1OJ4pKwVu5HHa7nebmZj7++GNeffVV3njjDd566y1ee+01PvroIxobG8US14ODg5w+fZp3332XyspKHA4HPp+PmZkZbt68yYcffsjp06e5fv06n332Ga+99hqvvPIKf/jDH3j11Vc5ffo0fX19dHZ2cvToUf7yl7/w5z//mZdffplXXnmFw4cPiz8GAjabjaqqKt555x3OnDlDbW0tJ06c4M033+S1117jz3/+M3/4wx947bXXOH78OO3t7fO+vxTC7I0gZCsrK/noo4944403eO+99zh48CCvvfYar7/+OhcvXmRkZOSO11FCQkLiq0IulxMcHCz2rxOMSGEWWujN7PMXTnE6nfO+L8y4nzt3jgsXLhAVFcXmzZslYfotw2KxUF1dzeeff86VK1cYHR1duMoDQ/gdfphx+/s+Xr58mcOHD3P48GEuXLhAS0sLU1NT3wi7QO6PhjMYDAQHB4thvTK/h9NoNIr9PwXPsW+J1ocL8Xq9jI2Ncfr0acrLy0lNTaWsrIyYmBgUCsWibcj8lXR1Op3oJBD+LjglvF6vmK94N+JkZGSEzs5O5HK5WPNFoVDg9XqZnJykoaGB6elpMjMzSU1NRefPv5XJZISFhZGenk50dLTYX9ZisSzcxTyWO36Zvw+oz+cjMDCQkJCQuzr+5VCpVOTm5rJp0yZyc3PFnrTLvS9er5fOzk4GBgYIDAwkMzNzXui0TCYjNDSUtLQ0YmJisFqtYj2bO+HxeBgcHOTcuXNUVlaSk5PDjh07li28Z7fbqa+v58KFC7hcLnbu3Mnu3buJiorCOactz1Lvv0KhIDo6muTkZCYnJ8Vc1kedh0qoer1efD4fERERrF27lrS0NPr7+zl//jxNTU1iyOlKCDd34Q1mTuiqx+NBrVbfsZKZ2+2mr6+Po0eP8vHHH9PR0SEaQwqFQmx74/F48Hg8YuWxI0eOUF9fLx7v7Owszc3NnDx5kk8++YTPPvtMzKNVKpVMTk5y4cIF3n77bT777DMOHz7MqVOnGBkZQa1WMzs7S3l5OR9//DFnzpxhYGBA/AFwu910dnZy+vRpPvvsMz788EOOHj1KR0cHSqWSoKAgZmZmuHbtGu+//z7Hjh2ju7sbt9u94GwXMzMzQ2VlJR9//DGnTp1iYmJCDDnxeDxcvHiRd955RzwXr9e7cBMSEhISD4Tlxn3mpFHI5XJ0Ot2idA+32019fT2HDx/G4/Hw2GOPUVhYiFar/UYY2xL3B8GT2dvbS3d3N11dXXR3dz/Qpaenh/7+fkZHRxkfH2dwcHDROg/L0tvby/DwMCaTiYGBASorKzl58iQnTpzgxo0b9Pb2YrPZHnrbYKWxwzun37t2hbaJcxEcFDdu3ODUqVNoNBq2bt1KTk6OWOV3JYTxymazMTo6SnV1NRUVFVgsFlJSUkhLS1vWszmX0dFRBgcH0el0YhE5QTROTEzQ19eH1+slISFhUQ6lQqHAaDQSGRmJy+VibGzsru+lcPxWq1UsBlVVVYXb7aawsJDU1NS78lQuh0wmIygoiJCQkLsKH/b5C4fa7XY0Gg3BwcGLIgEVCgUhISEYjUa8Xq8YNXknpqenqaio4OLFiwQGBrJ3716ysrKWnIzAnxd8+/Zturu7iY+PJy8vD5PJxPnz5/nkk084ceIEt27dor+/X3R2zSU8PJzExEQcDge9vb2LJl0fRR6q0N/Lly/jcDgoKSkhLy8Pr784Un9/P8HBwaSmporu+aVCf+/0wI6NjXH27FnKy8tJS0vjscceW/Z7Pn/J6Fu3bvH+++8zMTHBY489xt69eyktLRXzONPT08UHu6enh0uXLtHa2kpBQQFlZWVotVqmp6e5desW169fZ2RkBK1Wy6pVq9i8eTPFxcWEh4czNDREU1MTPT09mEwmYmNj2b59u1jcaHp6mo6ODrHtTXx8PGq1GrvdTnV1NZcuXaKnpweLxUJsbCybNm1i8+bNFBUVERMTg81mo729ndHRUYxGI4mJiWi12iWLKUVGRuL1emlububw4cNUVFQQExPDnj172LlzJyUlJcTGxmIymaitrcXj8ZCUlITRaPxSs2QSEhIS9xuXy0VzczNnzpxhYmKCTZs2sW3bNjGkU5gRf/311ykvL2fLli0888wzxMbGcu3aNWpra0lMTJRCf78FmM1m6urq6O7uxuFwYPf3Rm9tbaW5uZmWlpavdGltbRX/3dbWxuDgICMjI3R3d9PS0vJAjuFul9bWVlpbW+nu7mZkZESMVDCbzYyOjjIyMoLD4SA4OPhLe9C+LlwuF11dXZw8eZKuri42bNjAli1bxEq9yyGEgn7wwQe0tbXx+OOP8+STT6LRaKioqKCnp4eUlBSKi4sXFRUSnB4t/vtdXl7OqVOnqKurIzo6ml27dlFaWnrHiq8+n4+amhouXbqEXq9n48aNpKaminZjY2MjZ8+exeFw8Pjjj1NYWLgoDU54H9ra2sROFpGRkSs6eFwuF0NDQ7S2ttLQ0MDNmzdFZ1N8fDwHDhxgzZo19611o6ATysvLsdvty4b+dnZ2cvnyZex2OyUlJaSnp8+bNPB6vYyMjHDz5k3a2tqIiIhg586dhIWFzdnbfOx2O7W1tXz66af09fWxY8cO9u7di1ar5dy5c7S2ti4K/W1oaOD48eP09fWRmJiISqXi+vXrlJeXU1VVRVVVFU1NTZjNZkJCQggODp7nLfb5fPT09HDt2jXC/C0kQ0JC7su1fFhZ/in/mvB6vXg8HsLDw1m3bh2FhYVYLBYuXrzI7du3mZ2dFdddONOwEsLAUVFRgUajEWO7l5vV8fnzRAYGBujt7SUkJISioiLWrl0rVoXbsmULKSkp87Yh8xdFmvvQCH/zeDzI5XIyMzPFGPmdO3dy4MABNm3ahFKppLm5GY1Gw969e9mzZw87duxg3759bN++Hb1eT29vL52dnWIIhszf3Fgul2M2m4mIiGDv3r3s37+fbdu2iQna+/btIykpib6+Pm7evMnAwMCK129qaorq6moqKysJCAhg586d7Nq1i4KCAvLy8ti5cydPPvkkYWFh1NbWij2oJCQkJB4WfP70hdu3b9PT00NiYqJYhRL/783k5CRnzpzh5MmTJCcns2/fPrEA00pjpMSjifDbLVR7vXLlCpcvX35gy5UrV7hx4wZNTU10dHRQWVm5aJ2HZbl69aoYPoo/jNbj8TAxMUFzczPV1dUMDAx8I70+Xq+X6elpamtr6ejoIDY2VqzCupJQc7vdDA0Ncf78eWpra1m1ahW7du2a149+pXHF5XLR0tLCBx98wJ///GfeeOMNTpw4gdVqpbCw8K7EIn7Ba7FYsNlsaLXaeZMFLpeLmZkZnE4nWq1WDHleiMZfNwV/ZKDNZrtjhMns7Cx1dXV89NFHvPbaa7z55pucOXMGh8PBmjVrWLt2LaGhoQ9UWMnlcpKTk4mMjMRsNlNdXU1HR4d4DRwOByaTiba2Nvr6+sTom5WO0ePx0Nvby/nz52lsbCQnJ4ddu3YRExMDy9xjQQwPDg5is9no7+/n9u3bTE5OYjQaSUhIwOv1UlFRwdtvv82RI0fo7e2dFwGpUqkICQlBo9EwPT3NzMzMXXm5v8k8dELV5/Ph8+eqpqens3nzZpKSkmhpaeHs2bN0dXXBHUI1FuLy94o6f/48LS0tpKamUlpauuLLLohLrVZLQEAAMzMzdHV1MTAwgNVqRa1WE3IPDaC9Xi8ymYyYmBgKCgrIyMggPDyc0NBQEhMTyc7OFj2S2dnZlJSUEBERQXBwMHFxcWRnZxMbGysWTxJi54Xr5fP5CAsLo7S0VPTCBgcHExwcLFZhKywsRKFQ0NTURH9//4oDjlDMaWJigujoaBISEpDL5UxOTjIxMYHL5SImJoaIiAgGBwfp6urCarUu+XJKSEhIPGh8/rY1VVVVXLx4EZvNJo6DarVa/Lyuro4PP/wQuVzO008/TWFhoehtXTjhKPHtQa1WEx4eTkxMDDExMcTGxn7li7AvoRiNXq8nIiLigR7D3S7CMYWHh4uT9T5/bp1Go0Gv12MwGO5bC8AHic+fy97U1MSFCxeYnJyktLSUoqKiFT2BwsTXrVu3uHz5MqGhoezbt4/8/HwCAgLE6yDYr8tdF8Fh4/P5RLHocrlEkWM2m1e03/DbvUL3DLVaPS9v1OtPg/N6vSgUClQq1ZLHIvcXefL5KyMLeaZ3Qlgf/3ukUqmw2WwMDw/T39//wG1FuVxOSkoK69atIyQkhJs3b3Ls2DGuXbtGTU0NFRUVnDlzhtOnT9PZ2YnX6yX4Dn1jJycnuXHjBtevXyc0NJTHH39cLJY1V5/M/bfT6WRychKz2czs7Cwej4fc3FxefPFFfvazn/HLX/6SX/ziFxQXFzM0NMSRI0eorq5mZmZGvF6CLtHpdMzOzmKxWB55ofrQhf46nU6Ki4tZtWoVYWFhokhsbW1leHiYqKgo0tPT6ejo4OrVq+j1+hVDf91uNyMjI5w+fZpPPvkEuVzOgQMHePzxxzEajcs+iMLDJYQxtLe3MzQ0xPj4OLOzs+IAovZXt3O5XPT393Pz5k36+/tZs2aNGPprNpu5ffs2jY2NJCQksG3bNtLS0sTjFXJhKyoqsFqt7Ny5kw0bNsyb4RofH6e+vp7R0VESExPF/oB2u526ujpu3ryJwWBg3759FBQUzLsWcrkcr9fL6OgotbW1TE1NUVhYSE5ODhaLZVHob0REBJ2dnZw5c4bu7m6xd1Zvby9NTU00NTWJ4T+1tbUMDAyQkZFBcXExoaGhSw54EhISEg8Sh8NBY2Mj77//PhUVFeTk5PDd736XwsJCVCqVGNb39ttvc/HiRfbs2cO+ffvQ6/ViCOPly5epr68nLi6OkpISDAYDwDcyjFHizpjNZmpra+np6cFoNIpRSfn5+eTl5bF69eoHsqSlpaHX6wkPD6e0tJSysjJWr179QI/hbpbs7GxCQkIYGxsTW68EBweTkpJCaWkpGzZsICMjQ+yA8E3A50/7amtr4/Dhw1y9epWEhAReeOEF1qxZs6xzQpj4qq+v55NPPqGzs1N8foKCgnA4HIyOjoptVRITE8nNzSXE36de7vfgyWQyAgMDSUpKori4mKKiImJjYzGbzbS2tjI+Po5erycyMnLZY8EfllpZWUlFRQVxcXGsX7+eqKgo5HI5drud9vZ2bty4gdfrZdOmTWRmZi6yoScmJqioqKC5uZno6Gg2bNhAfHz8iuOf3F/YLiUlhcLCQvLz84mMjGRyclJsTxMdHU1kZOSSXtx7xefz3TH0V5g80el0Ym5uZ2cn7e3tNDQ0UF5eTmNjI2NjY0xMTOD1eiktLWXTpk1LFkWy2+1UVFTw8ccfMzw8zObNm9myZQtBQUE4nU6mpqY4f/48bW1tFBcXk5WVRUBAgPi9W7duIZPJ2LFjB9///vdZs2YN8fHxxMTEkJycTGBgII2NjbS2thIbG0tmZqZoW3s8HjH0VyaTsWXLFuLi4pbVMo8CD61Qzc3NJTg4WJwFEtqjeL1eUlNTmZ6e5saNG4SEhLB+/folharb7WZsbIyLFy+KDXh37tzJd77zHVJSUu74kigUCoKDgwkKCsJqtdLb2yvmkAwODiLzVwoLDAzE7XbfUag2NDQQFRXF+vXrxdh0/LMsnZ2d3Lx5k6mpKTZu3EhJSYk4GHi9XoaHh6mqqmJ4eJjk5GSKioowGo3zhGpoaCjbt28nLS1t0UDicrno6+ujqqqKqakpSkpKWLVqFTabbZFQNRqNdHZ2cvHiRTo7OzGbzQwODtLU1ERdXR319fXU19fT0tLC6OgoKpWKoqIiioqK7pi7ISEhIfFV43Q66ejo4L333uPcuXNERkbywgsviCkUPp+PiYkJTp8+zWuvvYbNZqO0tBSfz0dnZydtbW20tLRw/fp1urq6UKvV6HQ67P5ekXPbpUk8OlgsFlpbWxkaGiI2NpatW7eKNRkehEczLi6O6OhowsPD8Xg8qFQq8vPzycnJIfYBHcPdLnFxcRgMBlFAzczMEBMTQ3FxMVu2bKGsrEysK/JNMaJ9/r6nHR0dHD9+nNOnT6PRaPjOd77Dzp07MRgMy773Ho+H/v5+Tpw4wenTp/F6vaSlpeF2u2lvbxdF0e3bt+nv70flry5s9xf4EaqVy/1ViGNjY0lKSiI5OZn09HTUarWYK61SqUhNTV0xDNntdlNbW0tlZSWxsbGsW7dOjCIUHCvXr18Xx77s7GwxzFdAyNlsb28nOTmZzZs3E+OvWrwcgt0cGxsrtvxJSkpCq9VSV1dHY2MjgYGB5ObmiikYX4a7Ear4BbTBYMBoNKLVanE6nUxPT2OxWFAqlSQnJxMbG8vQ0BAej4cnnniCoqKiRXm7AD09PRw6dIjTp0+jVCpJSUkR7fj29nYaGxu5fv06/f39hIWF4fF4mJ2dRaFQ0Nrayu3btzEYDDz99NNs2LBBdAbJ/S0ow8LCRBs7LCyM/Px88bp7PB46Ozu5dOkSarWaHTt2EBsbu+I9+abzUCsKmUxGQEAAOTk5bN++nZiYGCoqKjh79izT09MrlqMWQmQvXbrEBx98QFdXF5s2beK5554jIyPjjiIV//5DQ0PZvHkzv/zlL/npT3/K2rVrmZmZ4eTJk7z33ntixdv7jc8fznsvCLNxS+Hz+fB6vWKIgMLfi3U5hPUDAgJITU1l/fr1bN26VVy2bNnCY489xve+9z1+/vOfs3XrVsl4k5CQ+NoRPKUHDx7k888/JzAwkGeeeYbHH39c9Ij6fD4xB9FkMuHz+Th//rzYDuzll1/mtddeo7q6GqvVSkdHB4cOHeLgwYPU1NQ88qFW31YCAwNZtWoVmzZtori4mOjoaDF0Ue3vD/pVLiqVCpVKhVKpRKFQoFAoUCqV4t8Xrv91LiqVCq1WS3R0NPn5+WzdupUDBw7w1FNPsWHDBhITEwkMDPxGTVw7nU66urr4/PPPOXnyJF6vlz179ojtQ1ayb4TovZaWFsbHx8WJsFdeeYU//vGP/PGPf+Tdd9+lrq6OiYkJampqeP/99/n4449pWdBmRLDl5P4wz/j4eLZs2UJBQQEWi4X6+np6e3tXrEqr8reKUavVuN1unE6nOG6p/WHtOp0Om83GxMTEktuy2WzMzMyIXtK7bYsjHL9CoUCn05GamsrGjRtZvXo1drudW7duMT4+fs827pclMDCQ0tJSXnrpJX7961/zq1/9il/+8pf89V//NU899RRGoxGn00lkZCQ5OTmLxK5AX18fbW1tYuGw06dP8+qrr/Lyyy/zxz/+kTfffJOWlhacTifl5eW88847HDp0iMHBQdRqNUqlEo1Gs2xYvMFgICoqCq1Wi9VqZXZ2Vrx3Pp8Pl8uFw+EQw8JXei4fBRZfoYcMhUIhNmjfvHkzNptNzDVdTph5PB7Gx8e5dOkSBw8epK2tjQ0bNvCDH/yA/Pz8e7qxMpkMvV5PSUkJ3/ve9/i7v/s7fvSjHxEfH099fT0XL14US3x/3bhcLpxO55IvvzB75HA4CPT3sVIvESqN/5zV/pyGkJAQCgsL+d73vie+0AuXn/70p5SVlS0qby4hISHxIPF4PPT19fH2229z6NAhtFotzz33HHv37iU2NnbeuB8YGEhhYSE//vGPefHFF1m7di2rV68mPz9fDPWMjIxEqVSi1+vJyMgQawnc7e+HxDeLoKAgiouLefrpp9mxYwfR0dELV3kgCL/hS/2WP0wInr29e/fywgsvsGPHDjIyMsRw1m8Sgkg9duwYR48exW63s3v3bp566imSk5OX9VgJTgWZTEZ4eDhlZWV897vfZf/+/axbt27emJKdnY3BYECj0RAREUFmZiYZGRmEhYUtu32BsLAwDAYDPp9PLKIzt8jOQlQqFUFBQWi1Wux2OxaLRcwbValUhIeHExUVhdffimVh3qjPH3ViMplQq9VERESIfVaFz+/2+VT4W79ERESgVCoxmUzY7fZ56wjOkbvd5hdFcL6UlZWxZ88e9uzZw7p16/B6vdTU1DA7O0tRUZFYIVlg7vkaDAY2b97Miy++yP79+xf9duTk5IihulFRUaxatYqMjAyMRiNhYWEEBQVht9uZmJhY8h7OnVjQarWi9x3/b5zVasVms4kter5p79q98o04O5VKRVJSEtu3bycnJ4empiauX7++6MXCHyY7Pj7OxYsXOXjwIB0dHWzatImf/vSnrFmzZt6Ldi+oVCoiIiLIz89n165drF+/HrlcTnd3NyaT6WsXqjKZDJPJxODgIPYFDam9Xi9TU1P09PQwOztLQkIC0dHRy86MyfyeZMGwGx8fB5hX1GHuEh0d/Y0K75GQkHj08Hg8DAwM8MYbb/DRRx8RHBzMD3/4Q77zne+QmJg478dcCAPbs2cPv/71r/mHf/gHfv3rX89b/uZv/oY1a9YQ6G8Q/8ILL/DSSy9RUlLyyBsG31aUSiXh4eEkJSURExOzKBRSYj5CmGpCQgIpKSl3JbgeRtxuN11dXRw+fJijR4/idrvZt28fzz33HOnp6ctG4Am57DMzM8hkMpKSknjqqaf427/920Xjya9//Wt+8pOfUFhYSEREBMXFxeIkWW5u7h2ftampKdEWCwoKQqfTrXitZTIZISEhYura5OQkTn/1ZblcTlhYGNnZ2eh0OlpbWxkZGZlnx1osFrq7uxkYGCAoKIiUlBQC57T0mp6eZnp6ekmhtRCv14vNZmN8fByXy0VISMi8a2q1Wunr66O9vZ3h4WEcS/QPvd8olUoCAgJQKBR0dHRw4sQJMUz68ccfJyIiQtQKbrebyclJcXIgNTWVZ599ll/96leL7vHf//3f8+/+3b8T7+n69ev52c9+xve+9z2ysrKIi4sjJiaG6elpWlpasFgsi851cHCQ3t5eZmdniYmJwWAwiPd6dnaW8fFxPP7uKMt5ZR8lvhFnJ5PJ0Ol0FBUVsWfPHoKDg2ltbWVsbAyvv5ou/pdneHiYM2fO8N5779HU1ERubi579+4lNTWV2dlZTCYTJpOJiYkJLBbLsi+Zz+fD7XYzPj7O8PAwNptNfJiEmR+5XC6GwHwR8Xu/EPY9NDTEpUuXuH37NlNTU3j9leOGhobEPk1er5eCggKSkpJWfLiFcJ6QkBBqa2s5deoUTU1N81rQuN1upqammJqawuVyzfu+hISExINCCPd99dVXee+995DJZOzdu5fNmzcTGBjI9PQ0JpOJ8fFxpqamsNvtqFQqoqKiSEtLW3JJTU1Fr9ejVCoJDAwkLi6OhISEB95aQUJC4qvD5XLR1tbGp59+yuHDh5mZmaGsrIytW7diNBqxWCzz7EYhDFOoKP7WW2/x3nvv0djYiMzf2SElJWXJ8SQhIQG9Xo9arUav1xMfH09cXJzoYRP65ZpMJtH7Kdi1ly5dorKyEpVKRUZGBvHx8cu2VxQwGo1ERERgNpsZGhoSw3tl/kjBoqIioqOjaWxs5MKFCwwMDODxeHA6ndTX13Pjxg1mZmZIT08nJydHPM6GhgbefPNNXnvtNRoaGnA4HNhsNtrb22lra2NyclK0rV3+rhvC8Xs8HoqKiubl+zY0NPD666/zxz/+UdznV4nH48FsNtPR0cGpU6d4/fXXOX78OFqtlr1791JSUiLmpnq9XsrLy/nzn//MwYMHaW1tRaFQEBMTQ2pq6pL3OTExUSwgFhYWRkJCArGxsQQGBpKWlkZhYSEymYzy8nKuXLkiFnASvOWnT5+moaEBg8FAXl7evF67k5OT9PX1oVKpiIuLu+Mz8CjwUBVTunjxIg6HQyymFBQUJK4jn1OSeXR0lObmZmw2GwkJCZSVlZGYmMjMzAwXLlzg4MGDYjWzyMhIPB4PTU1N3L59m8rKSrEC7+zsLKGhofOa/gr4/P33Lly4wPHjx+nv72doaIiWlhYuXrzIxYsXcbvdbNy4kY0bNxISEkJ/fz83btygr6+PNWvWsGHDBrRaLdPT09y+fZv6+noiIiJYu3btomJKHR0d3Lhxg8nJSTZs2CAWU5LJZHi9XoaGhqioqGBoaIjk5GRKSkrEYkr19fXcvHlT7Jk1OjqK2WxmbGyM5uZmzp07x7Fjx+ju7iYvL4+nnnqKvLw8lEolk5OTXLt2jfr6ejIzMykrKyMyMpKAgADUarX4MgvNx8fHxxkYGKCtrY2amhouXrzI+Pg4BoMBnU63oviVkJCQuN8IhUHefvtt3nzzTQYGBoiIiBBbZ9XU1Ihjf1VVFd3d3SiVSrECpsyfQrJwcTgcXLx4kdraWhISEti4cSNxcXELdy8hcV/x+Qv6jI2NYbVaiYmJITQ0dOFqEvcBr9dLd3c3hw8f5tChQ7S1taHVagkLC2N6epr6+vp5dmNra6vodR8bG+Po0aMcPHiQpqYmgoKCSE5OJiQkZNFYIizj4+PcvHmT7u5uUlJSKCoqIiIiQjyOTz/9lOPHj9PV1cXIyAhdXV3U1dVx8uRJDh8+THd3N9nZ2ezdu5fCwkKCg4MX2a4L6ejooLm5mdDQULGbhsyfP6pWq5mamqKpqYnOzk7RQ1xfX8+RI0e4efMmMTEx7Nu3j9LSUkJCQhgfH+fo0aO89dZb3Lx5E6PRSFpaGoODgxw6dIhz587R3d0tti2sqanh1KlTHD16lO7ublavXs0PfvADcnNzUfvbhH3++eccPHiQ0dFRcnJyyMrKuuvoR5+/mNKtW7ew2+3k5+cvWUwJvzeyurqaW7ducenSJU6cOMHRo0epqanBYDCwf/9+9u/fT0JCghhxaLPZeO211zh48KBY/TghIUG0dxfeY0FsnjlzhtbWVtatW0dRUZEYCqz1F4gdHR2lpaWFvr4+bDYbk5OTdHZ2cvbsWT788ENGRkbYvXs3e/funacXmpubOX78OC6Xi/3795Odnb2sx/9R4aFRFUqlkqCgIIKDg9FoNEsKHqVSSVpaGnv27KG4uJjw8HACAwNRqVR4vV5MJhP19fV0dnbidrvxeDw0Nzdz+PBh3nvvPQ4ePMjBgwd57733OHToEBUVFUxOTs4Ld5iLkBx/6dIlXn/9df7v//2//Ou//itHjx7F4/GwZcsWsciTXC4XZ971ev28PFi5XE5AQAAhISHodLpFIbcymQyVP/E9KCgIjUYz7wUVBhVBqGs0mnkhH0LsfGxsLDk5OUxPT3Po0CF+97vf8dvf/pb333+f0dFRSktL+e53vzuvkplwbHq9fp7QVKlUpKWlceDAAQ4cOEB4eDjXr1/nT3/6E//yL//Cb37zG15++WWOHTtGZ2en2LJHQkJC4kHh8/lwOp3ijP3U1BQ6nY6ZmRkuXrzIRx99NG/sP3jwIMeOHaOtrW3ZcV9A5i/mFxISQqC/IqeEhMSjg9frpb+/n5qaGoaHhwGYmZmhvLycQ4cOiWPHe++9x3vvvcenn35Kc3Mzdrsdl8uFxWJhenqaqakprFar6AVdDkGoBAYGotVqRXtLiOCbnp6mpqaG9957j9/+9rf88z//M7/5zW/44IMPmJiYYP369Tz33HOsX79eFJwrER4eTlZWFkFBQfT29tLd3S1GxSkUCmJjY0Ubz+Px8NFHH/Gb3/yGf/3Xf+XGjRvEx8ezf/9+Nm7cKEaSeDweLBYLU1NTTE5OipGJLpeLqakpKisreeedd/jd737HP//zP/O73/2Ozz77DIvFwrZt28T0CUFICh01JiYmiI6OJjExcUnn0UqoVCoCAgJEB8tS+gF/OPOxY8f4/e9/zxtvvMGVK1fweDxs3LiRl156iWeeeWZeRxAhetJsNjM5OSl61O9k68rlctGeX3g8Go2G/Px8nn/+ebZs2YLJZOLtt9/mX/7lX/g//+f/8Je//AWLxcITTzzBs88+K1Z8xn/8HR0dDAwMkJCQQFZW1rK1Zh4lHgqPKv5ZcaVSSUZGBoWFhUuGNQiCLiQkBL1eT1xcHGvWrCE/Px+DwYDb7cZutxMaGkpubi55eXmkp6eTkpIybxHKfefl5ZGWlrZsjy+ZTIZSqRQFYmBgIGFhYWRkZLB161Yef/xxVq1aRUhICPjDCZRKJQkJCZSWlpKeno5SqRRDcIUy06tWrZoXcy4MUkqlktTUVEpLS0lMTJxnGAkDYHR0NAUFBWRkZBAYGIh9TnuaiIgIDhw4QFFRkSj2dTodycnJbNq0iSeeeILS0lIiIiLEbXv9lYAjIyNZs2YNOTk54vVQqVSEhYURFxdHXFycmAQeFBREWFgYsbGxFBQUUFpaSkpKyj0PLhISEhJfBpk/4sRms+FwOEhPT6eoqIicnBxxrJ877icnJ5OVlUVeXt6ivNWF+Hw+7HY74eHhFBYWsmrVKsmzJfGVI3lUHxw+n08UmHFxceTl5ZGbm0taWtqSY4dgnyYkJKBWq/F4PGi1WnJycsR2PCvlmno8HjweD5GRkaIdJ3hFVSoVwcHBhIeHExwcvKTNuWfPHkpLS4mOjr6rlDOFQiHm3/b39xMeHi7avIJ9q9friYmJISwsDI1GI7ZHKSwsZPfu3WzZsoWEhIR5DhSv14tSqSQrK4vt27eTnp6OTqcjODiY0NBQ8fiDgoIwGAxkZmaybds2nnzySUpLSzEYDOLY29vby9GjRxkeHmbLli1s2bIFo9G44tg8F5lMhsvlQi6Xk5ycTEFBAQkJCUt6GR0OB52dnXg8HuLj41m7di2PPfYYjz/+uNiGSq1Wi+cp81denp2dRa1WU1BQwObNm0lMTJy33lyE3yShenBZWRlpaWmifSyTydBqtURERBAXF0d4eDhqfyXtQH//3J07d7Jv3z5Wr149r1hSZ2cnx48fp6enh8cee4wtW7bctef5m4zMd6epgQeAz98oWYjT1uv1BAcHLzuD7XK5mJycZHp6WgzTCAgIEP9usVjE2fLlTk/h7/UUFha27APn9XqZnZ1lYmJCrJgLoNPpCA0NFT2ncrkcr9eL3W5ncnISu92OXq8XCwu4XC6xSptarRbDjYWHz+v1YrVamZiYwOVyYTAYFuVBzd12YGAgoaGhqFQqJicneffdd/nd735HdHQ0/+E//Aexhc7U1BQej4eAgADCw8NFD/Tc6+p0OsUkcUGAzr0ePn8pbIvFwuTkJGazGZfLhczfQDkkJGTJ7UpISEg8CITxc3R0VByblhv38bdmCAsLWzTGLsTrL8xnNpvRarUYDIYVjVAJifuB1+tlenqahoYGRkdHKS4uJjk5eeFqEvcBn88n2jZz628sNX74fD5U/mq5Qi/m8fFxRkdHkfuruwo233II9pbNZptnxzHH3lzoqZT7C1YJdqHuDkWUFjI1NcXHH3/Mxx9/TGxsLD/84Q9Zt26d6NEUJkZMJhOjo6PYbDYUCgVhYWFEREQQHBw8TxQLnt+BgQF8Ph/x8fGEhobi8/nmHb8wAaBQKAgMDCQ8PFy01eeK0JMnT/K///f/BuCv/uqv2L179x3H5oUI9rPH40Gv1y9b3NPpdNLT04PZbBadXkKk40LPp4DP52NkZITBwUE0Gg2xsbHLbl/A5XJhMpmYmZkRf2uEVD4B4X5PTk6Kk1L4q9ELz9Lc6NKZmRkx5Do4OJi/+7u/Y926dd8Kj+pDIVSZ42LH7za/00MqeAKFGQ/BOJm7nZUQZjaEZSW8fo+ocKnkcrm4zEXYv89fqnzu5945ZbeXOj/huH0+H4olepzOPa+5x7xQqP7n//yf2bFjByqVSkxml8vlKPyNpBdulznHttL1EPa/3HVY6jsSEhISD4K54+edEMa4heP3Utxp3JaQuN9IQvXB8mXGDsFDij817V7GlOXsLcHOEmwtYX8Kf1/de8Xr9VJXV8d7771HR0cH27dv58CBA8TGxi6yUYWUOZnf27qULTp3XZY476WOXzj2hdfH4/Hw5ptv8s4771BUVMQPfvADcnJyFkVT3omF9vHC/Qj4/NGLc6/r3YzrHo8Ht9stXpfltj8Xr1+jCNtfbh9zrzt+J9rCffh8Ppqbm3nrrbeoq6tj9+7dPP/88/MqEz/K3PlqPyDmPsx3c+Hl/pzQuesLD55SqbzjspJwW4jcHwYruOcXPkQCcweUhZ8Lf1/u/ITzVy6YdVn4+VLHLQywvjkiWekPWdZqtajV6mX3y10IWebsX61Wi+EhKpVqxe1KSEhIPAjmjp93WpYan5fjTuO2hITEN5svM3YINtFy3riluJO9JdibWq2WgICAeTbcF0Eul5Oamspjjz1GcXExWq1W7NG5cD21Wi3uU7mMLcqcdZc676WOX6VSLVoPv3c2NDSULVu2sGPHjnlFg+6Fhfbxcsj8IdZqf7eOux3XFQoFGo1myfNdDrlfiyx3nwXmXvflcmw9Hg92ux2DwcC2bdvYunUrYXeRo/yocHdXXOKhRXhBVSrVsoOBhISEhISEhITEt4/AwECKi4vZv38/a9euRa/XPxQiRy6Xk5+fz7PPPsuaNWvm5WNK/BsymYyoqCh27NjB/v37SUtLQ7mgKOujjPREfMNRKpXExcVRUlLC6tWrCQ8Pl150CQkJCQkJCQkJ5P5+npmZmWRkZKDX6x8KO1HpLz6amZmJwWD4Vomve0EulxMREUFubi6pqanfusKlD02OqsQXw+Vyif2qNBoNaWlp91QxTUJCQkJCQuLhQMpRlZCQkPg3JDXzDUfwqJaVlVFcXCyJVAkJCQkJCQkJCQmJbzxfq6IRiv8shcfjwWazMTMzg91uX5T4/ajh8zeun5mZwWKx4HK5lr02c5H5CycJBY4kkSohISEhISEhISEh8U3ngYb+CiWe5y74vYJKpRKVSoVSqcTn82EymWhubmZ0dJSEhARyc3MJCQmBO5TG/qII5a2F0tx3qh52v3G5XLS3t1NTU4NGoxGbSi8Vs+/1enG5XGI567tFuM4P8rwkJCQkJCQk7g4p9FdCQkLi33ggQtXr9YoNhTs6Omhvb2dkZERssKzT6YiOjiYnJ4fMzEx0Oh1NTU0cPHiQ2tpatm7dyg9+8AMSExPx+XyMjY3R2tqKXC4nPT0dg8HwhUt3CzgcDoaHh+nr60Oj0ZCenn7PTYe/DBaLhcOHD/OXv/yF0NBQfvazn7Ft27ZFDeY9Hg8mk4mmpib6+/tFYS0g/HvubfX5fKjVahISEsjJySE8PPyBnZeEhISEhITE3SEJVQkJCYl/4ysXqm63m5GREW7fvs358+epra1lZGQEh8MxT1TpdDrWr1/PT37yE3Jycqivr+f3v/89N27cYO/evfz93/896enpzM7Ocvr0aV5//XWCgoL47ne/y7Zt29Dr9Qt3fdd4vV4GBgb4/PPPOXfuHKGhoTz//PNs2rTpC/V0+iKYzWbeeOMN/uVf/gWDwcB//I//kf3796PT6eat53A4qK2t5e233+bq1avY7fa7EqpCr6rvf//7rFq1ShKqEhISEhISDxmSUJWQkJD4N77SGFCn00l7ezsfffQRv//97zly5AhjY2NkZmZy4MABfvKTn/DjH/+YPXv2kJGRgU6nm9eAd+5/hX+73W6Gh4eprq6moaGBkZERXC7XvP3eKz6fD5vNRm9vL3V1dTQ3NzMxMfHA82LnnudyQlImk6FWqwkNDSUiIoKoqChx8Xg8dHR00Nvbi8/nw2AwiJ8ZjUb0ev0DE94SEhISEhISEhISEhJfFMU//uM//uPCP94PXC4X3d3dHD58mEOHDjE6OkpJSQkvvPACTz31FNu2bWP9+vUUFRVRUFBAYWEhRUVFpKamotFoGBoa4vbt2/T395OZmUlpaSkGgwGZTIbH40GhULB69Wo2bNhAQkLClxJgMplMLOwUFBREfn4+paWlREVFPbB8TofDQU1NDTdu3CAgIICNGzeSmZm56LxkMhlarZbY2FgKCgrYuHEjmzZtYuPGjSgUCjo6OoiMjOTAgQM8++yzbN++nY0bN1JWVkZRURHx8fGLwoklJCQkJCQkvn58Ph8Oh4OxsTGsVisxMTGEhoYuXE1CQkLiW8FXosJ8Ph+Tk5Ncu3aN06dPMzU1xebNm/npT3/K008/zdq1a0lJSRE9gmlpaaxZs4b8/HzCwsJWFIcqlYpVq1bxs5/9TAxjvZPwEooPCQWYFiKTyQgNDWX9+vX86Ec/4jvf+Q6pqakr5r3OLb60UvS0z+fD4/HgdDpxuVx35aVdzpuKv/GvXq8nNzeXTZs2sWXLFjZv3szmzZvJzMwkICCA4OBgsrKyKCsrY/PmzWzZsoWNGzeSlZVFcHDwwk1KSEhISEhISEhISEg8VCyvCL8ETqeTzs5OLl++TG9vLzk5Oezdu5e1a9diMBhQq9ViVV25XI5SqUStVqNWq1cUqQJWq5Xh4WEmJiaw2Wx4vV68Xi/j4+PU1tZSVVXF0NAQU1NT1NfXc+TIEd555x0+/vhjrl27xsjIyKKKuW63G7PZzPj4OFNTUzidznmf4xe8ZrOZlpYWzp8/z6FDh/jggw84fPgwN2/eZHh4GLfbjc/nw2q10t7ezrlz5/jggw945513OHjwIKdPn6a1tRWbzbaiwF0JuVyOSqVCq9XOW5RKpRg+rFAoUKvV4mcajQaVSrWiCJaQkJCQkJCQkJCQkHgY+EpCf6enp7l+/TqnTp3C7Xaze/dudu7cSURExF0JUbfbzeDgIBUVFfNCf8PDw/F4PFRWVvLGG2/Q09NDZGQkERERyGQyOjo6OH78OOXl5VitVjo7Ozlx4gRnzpzh2rVrlJeX09rait1uR6/XExwcjEKhwOfzMTExIR7z8PAwsbGx4nbxh+Z2dXVx/vx5jh49yqlTp7h69Sq3b9+murqa3t5eAgICiI6OBqCqqoqPP/6Ys2fPUllZSV1dHVVVVWIxKbVaTVhYGBqNBplMNi/0V6fTsWHDhiVDf1eiurqaK1euoNPpWLt2rehhlZCQkJCQkHj4kUJ/JSQkJP6NO6vGL4DFYqG7u5uZmRliYmLIysoS80u/LD6fj6GhIS5fvkxFRQUjIyO43e55lfLOnj3LoUOHOHbsGH19fURERJCamgrAzZs3ef/99zl37hyjo6Ni6O7s7Czd3d3cvn2bhoYGJicnxX06nU5aWlr48MMPefPNN7l06RIzMzMYjUbi4uIICQnBbrczMzMj9ocdHBykv78fnU5Hbm4uJSUlpKamMjU1xalTp/jss89oaWlZ0nMrISEhISEhISEhISHxbea+C1Uh7FUQkNHR0URHR6PRaBau+oVxuVzMzMxgsVhwuVxiCK3X68VutzM4OEhraytKpZJdu3bx0ksv8fOf/5wXXniB1NRUWlpauHDhAu3t7djtdvG7DocDq9XK7OysKGB9Ph8jIyOcOnWKo0ePMjExQXFxMc8//zw//elP+dnPfsZLL73E008/TV5eHjqdDpVKRVpaGnv27OH73/8+P/7xj3nppZd46aWX2LVrFyqViqqqKmpqapienl5wdhISEhISEhISEhISEt9u7rtQ9Xq92Gw2zGYzPp+PkJAQAgMDVyxM9EUQcjHnemnn/jsqKoqtW7fyxBNPsHbtWtasWcO+fft47LHH0Gg0dHZ20tnZic1mW/T9udtxOByil3ZycpJ169bxwgsvsG/fPjZu3EhpaalYsCgjI4OAgADUajVZWVk8/vjjlJaWkpGRQVJSEnl5eZSVlZGamsrMzAwdHR3zPLcSEhISEhISEhISEhISX4FQnVsNF3/hn7vJS72fBAQEkJmZSWFhITExMQQEBBAQEEBcXByrVq0iKioKm82GyWQSQ2+XCkv2+XxMTU1RU1NDc3MzMTEx7Nixg8LCQqKjowkKCkKn0xEcHIxer0en04nnGxgYSFBQEDabjY6ODiorK6msrKSnp4fZ2Vnsdjvj4+PMzMx84aJKEhISEhISEhISEhISjyL3XUHKZDKxIq3P58Nms2G32++qLcv9QqVSER4eTmho6DyRrFQqCQkJQa/Xg99burD671y8Xi+Tk5N0dnZisVhISkoiMzOT4ODgJYWtgJAvW1dXx9GjR3nzzTf585//zKuvvsqhQ4doaGjAYrHgcDjmhS5LSEhISEhISEhISEhIfAVCVS6Xo9PpCAsLQyaTMTY2xsTExLI9TL8KZDLZsp5chUIhVtK9G4EohDErFArCwsLESsHL4fP5MJvN3Lhxgz//+c+89dZbVFVVYbPZxB6nX0UotISEhISEhISEhISExKPCYiX3JZHJZAQFBRETE4NKpaK/v5+uri5mZmYWrvqVspIIFT5bySsqIOTB+nw+3G63WGRpOYQKwR988AFnzpwhMDCQ/fv384tf/IJ//+//PT/60Y8oLS0VvboSEhISEhISEhISEhIS87nvQhUgODiY9PR0oqKimJiYoKKigvb29gfqVb1fBAQEoNfrcblcDA8P39E7bLfbxX6mQUFB7N+/n6eeeoqNGzdSUFBARkYGRqPxnvqjSkhISEhISEhISEhIfJv4SoSqTqcjOzubNWvWoNFouH79OsePH6e9vR2Xy4XX6xVbvwiL1+sV//6wIJfLMRgMpKamEhISQmdnJ9XV1UxOTi57Dna7nYGBAUZHR4mMjCQrK2ueMJ2dnWV6ehqHw7FwdxISEhISEhISEhISEhJflVBVKpUkJiayc+dO1q1bx9TUFB9++CF//OMfuXDhAgMDA5jNZux2OzabjYmJCXp7e+nr68Nmsz00YlUmkxEaGkpxcTG5ubn09vZy6NAhzpw5Q09Pj9hz1Ww2YzKZxAq+SqUSuVyOzWZjenpaDBceHx+nsrKSqqoqpqamFu5OQkJCQkJCQkJCQkJC4qsSqvi9qgUFBTz//PPs3LkTp9PJoUOH+O///b/z3/7bf+M3v/kNr7zyCi+//DL/83/+T/7rf/2v/OlPf6KlpQWn04nP58Pj8YjVgueKV6H9jeDJFPD580jnejsXInhu525D+O7cz4S/q9Vq8vPzefrpp0lLS6O6upo//OEP/NM//RO///3veeWVV/jtb3/Lv/7rv3LhwgWcTicZGRkkJyfT2trKJ598wtGjRzl+/Dhvvvkmn376KT09PTidTlwu17wwYmG/X9SzLJyTcA4SEhISEhISEhISEhLfRBT/+I//+I8L/3g/kMlkqNVqIiIiSExMxGAw4PP5GBsbo7W1ldraWiorK6murqajo4OpqSkMBgOrVq3CaDQyPT1NW1sbVquV3NxcSkpKCAsLw+v1iiG4MTExlJWVkZKSglKpZHR0lJaWFux2O/n5+RQWFhISEjLvuEZGRqivr8fj8VBQUMDq1asJCQnBYrHQ2dnJ8PAw0dHRrF27lvj4eGQyGVqtlqioKMLCwvB4PIyMjNDU1ERVVRXV1dW0tbVht9tJTEwkMzMTo9GIx+NhYGCAjo4OamtrqaqqYnh4mIiICOLj49FqtURGRlJUVER8fDxut5uOjg5aWlowGAxs2LCB9PR0lErlvONfidbWVpqamjAYDKxbt460tDS0Wu3C1SQkJCQkJCQeQnw+Hw6Hg7GxMaxWKzExMYSGhi5cTUJCQuJbwVcmVPHneGo0GiIiIkhJSSErK4usrCySk5OJjY0lPj6ezMxM1qxZw7Zt29i8eTMZGRkEBQWhUCgICgoiNTWVoqIiUlNTCQgIECv1GgwGiouLyc/PJyIiAoVCIVYcTktLo6CggKSkpCWFmlarJSMjg6KiIhISEtBoNODvvxodHU1eXh7Z2dno9Xqx1U1gYCBxcXGkpKSQkpJCXFwcsbGx4vFt3ryZ4uJiYmNjCQ0NJTY2ltjYWMLCwtDr9SQmJlJaWsr27dspKioiLS2N7OxsMjMzCQsLQy6XI5PJMBgMFBYWUlBQgNFoXLLFzkqEhYWRn58vXpd7EboSEhISEhISXx+SUJWQkJD4N2S+LxJjeo8IYbwulwubzcbMzAxWqxW3241SqUSn0xEUFERgYCAajQaZTIbL5cJiseBwOMT+o4LoslqtTE1NoVAoCAkJQavVIpPJcDqdzMzM4HQ6xW0uFGoOh4Pp6WncbjeBgYEEBgaiVCpxu91YrVZsNhtKpZKQkBBRwAp4PB4cDgcWi4Xp6WlmZ2eRyWTodDr0ej1BQUHid9xuN1NTU4yNjTE7O4tGoyE8PBy9Xo/P58Nms4G/QnJAQABerxer1YrZbEYul6PX6+cJ87vBarUyPT2NXC4Xt3uvQldCQkJCQkLi68Hr9TI9PU1DQwOjo6MUFxeTnJy8cDUJiXtGSAsTHDD3Yl9KfH3MTQmUy+XfOrv+gQjVuQiiVbjwgvDzeDzzepYK6/p8PvHvcz/T6XSEhISIntS56wvfWepmrrSO8CDM3d9SzM1lxR/m7PF4xHNQq9Uolcp5OaMymQyFQiHuTziPufsRrgl+b/Ry+1+OL/t9CQkJiUcVYSyeOw4vhdvtxul0imO5QqFYuIqExFeGJFS/Xnz+WidC/ZCvYgwQ7EfBTrtbW+2LCk2fz4fJZKK7uxufz0dSUhJGo3HReQljH3PO+273sRC32y12+VAqlahUqhXHXYnlcbvd9PX10d/fT0hICOnp6eh0ui98b75pPHChOheXy0VbWxuXL19meHgYj8cjfia8hHOFJf4XTqPRUFxczPbt2wkICBC/43Q6mZiYYHx8HJ/Ph9FoFMOC7zdevwd0YmKC0dFRRkdHMZvNKBQKMQ81OjqaoKCgb83DJCEhIfGw4PP5mJ6eZmJigpmZGcxmMyqViuTkZKKjoxeujsPhoL+/n97eXoaHh1EoFERHR5OYmEhkZCQ6nW7hVyQk7juSUP168Pkj3YaGhujt7WVsbAy5XE5UVBRJSUlERUUtmUp2N3i9XmZmZpiYmMBsNmM2m1Gr1SQkJBARESG2L1wKq9XK+Pg409PTYsRdTEwMMTExi6L+lsNsNnPp0iWuXbtGXFwcu3fvJjk5GaVSic8faj40NER3dzcjIyPI5XIiIyPF877b6D6n0ylGEo6MjDA+Po7L5SIkJISYmBji4+MxGAyLIh3n4na7mZ6exmQy4XQ6CQkJITo6+q7P9W5xuVyMj48zMTGBz+fDYDBgNBpXPLa7wev1Mjk5ydDQEC6Xi6ioKLFF5VLX0O12Mzk5yejoKC6Xi4iICCIjI+c9E263m8rKSo4fP47X62X//v0UFBSgVqvnbetR5WsVqna7nRs3bvDmm2/S1taGy+VC5vdO2mw2HA4HcrkcnU437yENDAxk//79/NVf/RXBwcHiA9fe3i4WZ1Kr1WzdupVt27Z9JQbG1NQUNTU13Lhxg/b2dkwmExaLBYDw8HAyMzPZtGkTa9asEXNQJSQkJCS+Wnw+HzMzM3R3d1NXV0draytjY2OYzWYSEhJ4+umnKS0tnbe+zWajsrKSs2fP0tzczMzMDPjH8lWrVrFp0yYKCwsJCgqasycJifuPJFQfPD5/+8CamhquXr1Kc3Mz09PTyGQywsPDycvLY/v27axatequRRtzxqKenh7q6+tpbW1ldHSUyclJkpKS2LNnD8XFxYvGFWFMGhgYoKGhgaamJoaHh5mYmCAiIoLHH3+cDRs2EBYWNu97S+HxeKiuruadd96hv7+fXbt2sW/fPqKiosTjq6mp4dKlSzQ2NjI9PY3P5yMsLIzVq1ezadMm8vLyCAkJWdGO9fl8dHR0cPXqVWpraxkYGGB6ehqXy0VAQAAJCQkUFxezZcsWkpOTF4ksj8fD9PQ03d3d1NbW0tzcjNPpJC8vj3379hEZGTlv/S+Kx+MR9UJVVRWdnZ1oNBrKysrYunXrogKs94IwOXrq1CmuX7+OzWbjiSeeYNOmTRgMhnnXT0gP7OrqoqqqiqamJpxOJ9u3b+exxx4jNDRUfM6Ea/v2229z8+ZNtm3bxo9//GOioqJWvCePCl9pMaU7IbyMdrudsLAwEhISSEpKIjw8nJmZGYaGhlCr1axatYr8/HySkpJISkoiOTmZvLw8MjIy8Pl8dHV1cfbsWY4ePcr58+epqKhgYGCA+Ph48vPzv/As2EqMjo5y+fJlrl27hslkQq1WExAQgMfjob+/n4aGBkwmExEREURFRaFWq+96cJOQkJCQuHd8Ph+jo6NcvHiRzz77jDNnztDe3s7MzAxutxuj0UhOTg7x8fHidxwOBzU1Nbz++utcuHABQJzR7u/vp6mpCbPZTFRUFJGRkV9JhI6EhIDg4ZKKKT04zGYzt27d4tChQ1y/fh2n0yl6/gR7TrgX4eHhdxUS6/F4GB0d5erVq+JY1NraKoo3g8FAVlYWsbGx80Sb4JG7desWR44c4eTJkzQ2NjI5OYnD4UCv15ORkUFiYuJd2baTk5OcPn2aq1evEhcXx+OPPy52yrDZbFRVVfH+++9z6dIlcYwUzru1tRWr1Up4eDhGo3GRuJyL1+ulurqa06dP09bWhtfrRafToVQqmZqaorW1lY6ODhQKBcnJyQQHB88TYsPDw1y5coWjR49y5swZbt68SXt7O1qtVnT4fFm8Xi89PT2cO3eOw4cPc+HCBcrLyxkYGCA6OprVq1cTGBi48Gt3jd1up6qqildffZULFy5QX19Pamoq2dnZ84S+0BXk/Pnzom65efMmzc3NxMXFUVBQMC8aU+bvPmK1Wqmvr2dgYIDk5GTi4+O/tAf4m8DXKlRlMhmBgYEkJiayevVqioqKxNnD6elphoaGSEhI4Nlnn+XAgQOUlJRQVFREYWEh6enpBAcHY7FYuHnzJidPnqSvr0+cIXI4HOTl5bF27dp54cH3C6vVyuTkJMHBwZSUlLBlyxZKS0vJzc1Fq9XS3t5Oa2srISEhZGRkoNfrvxUzHxISEhJfB4KBd/z4cd5++22ampoICgpizZo1bN68mfXr11NSUkJaWprowXC73QwMDPCXv/yFo0ePkpSUxHPPPcfOnTvJz88nICCAjo4OWltb0Wg0ZGRkfKkZd4mHH5+/jsbcuhkPkq9CqHq9XtxuN745NTgk/n/cbjdNTU188skn3Lp1i6ioKPbu3cuuXbtYvXo1AQEBtLa20tLSQmhoKCkpKQQGBq5ozwki9cyZM7zzzjvU1NQQHBxMUVERGzduZMOGDZSUlJCeni7WWmHOGHb58mXeffddbt68iUKhYPXq1eL31q5dK3aLuBuR0tjYyJEjR5ienmbz5s2UlZURGhqK2+2mp6eHjz/+mLNnzxIVFcWBAwfYvXs3hYWFaLVaOjs76ezsRKvVkpycvKId6/PnwTqdTjIzM9m8eTMbNmygqKiImJgYJicnaW5uZnx8nLy8PGJjY+edd21tLcePH6e5uVmMqpyZmSE+Pp7NmzdjMBgW7vKe8Xg8XLt2jaNHj9LX1wcgThwIbTAXerfvFpfLRVdXFwcPHuTq1avY7XYmJiZYt24dhYWFhIaGitfO5XJRVVXFJ598Qnd3N4GBgYyOjjI+Pk5RURGlpaXzhDwg5vkODAxQW1uLTqdj9erV34pc1a9dqKrVavR6vThjYzAYkMlktLW10d7eLoY5lJSUYDAYCA8PJzw8nMDAQBQKBXa7XYwFz83NJS0tjcnJScxmM0VFRaxbt+6uZp3uFZVKhdFoJDs7W/TuJiUlkZiYSEREBD09PVRUVBAaGkphYSFRUVF3NahISEhISNwbQnTOxYsX+dOf/kRvby+lpaU8++yz7N69m+LiYjIzM4mPjyc4OBi5XC5+58aNG7z88svY7XZ+8YtfsHfvXnHdqKgoJiYmqKurw263k5GRQXJy8iNvGHxb8fl8WCwWBgcHGRsbEz0ZyxnnXwX3W6h6PB4mJyfp6+vDYrGgVquXzZf7NjI5Ocn58+c5ceIEMpmMvXv3sm/fPjHyIiIigrGxMaqrq/F6vWRlZREdHb2sPefz+ZiamuLy5cu8/fbbtLS0UFhYyHPPPcfu3btZs2YN2dnZJCQkEBISglKpROavx2K1WikvL+fdd9+lsrKSjIwMvvOd7/Dkk0+ybt06cnJySExMJDQ09K7uocPh4PLly5w7d47o6Gh2795NWloaarWamZkZrl+/zscff4zNZuP5559n//794rFFRERgMploaGjA6XSKbSWX86oKjqfk5GRWr15NTk4OKSkpJCUlER0djdPppL6+nqGhIYqLi8nIyBBT+nw+H0NDQ0xMTJCRkcHq1atxOp2Mjo6SmJjIli1b7otQ9fl8dHd3MzMzIx7D5OQkNpuNvLw81qxZ84U8ql6vl9HRUT7//HMOHz6M0WhEr9czPj5OaWkpxcXF80S+x+NhaGgIk8lEfn4+ZWVldHd3Mzw8zNq1a5cUqsJYND09TWVlJRaLhcLCQiIiIh7o+PR18LWfncxfvUyoxCgswg1a+LlCoRD/jT9ftbi4mOeff56nn36a/Px8sf/pV4lGoyE6OpqEhASMRiOBgYEEBASIPVOjo6OR+dvszC0SJSEhISFxf3G5XHR3d/PWW2/R3NzMpk2beOmll9i5cycZGRkYjUZCQkIICAgQZ/GF6JuKigp6e3vJzs5m06ZNREdHo9VqCQwMJCUlhbVr1xITE0N3dzdNTU04HI6Fu5d4RHA6nfT19XH27FlOnDhBU1MTs7OzC1dbFu+cTgZC8RuLxSJWUr1bZHfoPHAv2O12GhoaOHz4MOfOnWNgYACXy7VwtW8tIyMj1NfXMzExQUpKCmvWrCE+Pp6AgACCgoJISUlh3bp1GI1GmpubaWtrY3Z2Ft8y5V0cDgdtbW2cOHGClpYWSktL+clPfsLu3bvJzs4mMjJSHIsEkYp/DOvr6+PUqVNUVlaSk5PDj3/8Y/bt28eqVauIiopCr9ej0+nuSqQCjI+P09rayuzsLAkJCcTHx6PVavH5cylramoYHBwkPT2d0tJS8bx1Oh2ZmZmUlJRgNBoZGBigpaVFrMOyFDKZjLCwMBITE4mJiRHPMTAwkIiICBISEggODsbjb1Xp9XeowF88NSMjg2effZbnn3+e0tJSIiIilp0M+KLI5XIKCgr4wQ9+wHPPPUdBQcGKXuK7QZjcqqmp4fPPP8fn87Fz506io6OX3a5SqSQnJ4fvf//7vPDCCxQXFy8SpksREBAghvwODAyIebyPOktfxYcI34KqvwtRqVRERUWRnp5OVFSU2If1q0YQ0HNFtc/nw263MzIywtjYGDqdjvj4eMLCwqS8JgkJCYmvAMFQuHLlCpcvXyY+Pp5nn32W5ORk0TM1NjYmhngJCGF2jY2NAJSUlCzylKjVahITE4mLi2NiYoKOjg7MZrP4ucSjhdPpZGBggLq6Oqqrq2lvb2d8fByLxXJXy+TkJO3t7dy4cYNLly5x6dIlbt26RXd396J1l1usVit2ux2Xy4Xb7RaF7xddJiYmaGtr49atW9TW1jI6Oiq2Xvm2I3jC+vr6UCqVpKSkEB0dLXoNBS9WUlISkZGRDA4O0t3djc1mmye0BAQBWFFRQU1NDfHx8ezbt4/s7GycTidjY2OMjo4yPT2N0+mcZ9da/GLn1q1bBAYGsm/fPoqKivD5Cz2NjY0xNTWFw+FY1h5eiFDJV6PRiB5cuVwuFhRqbW3FbreTnp6+aOzTarXExcURExOD1WplYGAAm802b/sLEeziuTa4UMV3ZGQEu91OZGSkaKvP/V54eDhpaWnEx8d/ZeGsMpmMqKgoMjIyxErCX3Y/LpeLjo4OPv/8c/r7+9m6dSubN29Go9Ese58UCgVGo5GsrCzi4uKW9VIvRCaTERkZSUpKChaLhba2NkmofhNYKBhXErVfBUIs/dTUFCMjI9TV1XH48GHq6urIzs5m48aNxMTESEJVQkJC4ivA6/UyMTHBhQsXsFgsbNiwAZVKxbFjx/j973/Pb37zG/7whz9w5MgRWltbRUPP6XRiMpno7e1FqVSSkZGBVqudZ7jI5XJCQ0MJDQ0VW1dYVvAqSHyzETyiDoeD6elp2trauHbtmig677ScO3eOI0eO8OGHH/L+++/zwQcf8OGHH3Ls2DEuXLiwaP2lFqFIY11dHW1tbZSXly9a516Wa9eu0dbWxszMDHa7HafTuaTI+jYidIwYHx8nICCA6OjoRaGfcrkcvV5PWFgYDocDk8mEzWZb0s50uVwMDg5SXV3N1NSUmON66tQpXn75ZX7zm9/w8ssvc/jwYZqampiZmcHr9YrCsaamhpGREVatWoXRaOTy5cu88sor/Pa3v+X//b//x0cffURNTQ3T09N3dQ8FgRscHDxPHArnLbThio2NXXTeAKGhoYSFhYnh41ar9Y4Rgj5/6LrQjqerq0sMP/Z6vWzbto2srKxF4myh4+erYuF+lrqPd4vX62V4eJgLFy5w69YtUlJSOHDgALGxsQtXXYTcHyF6r4SGhhIfH4/b7WZwcBC73f6lzuGbwNeao7ocQkhCc3Mzer2e0tJSUlJS7vgAu1wu+vv7qaioYHR0lMLCQtauXfuV5KgyZzbu4sWLHDt2jNOnT3PixAmuX7+O0WjkBz/4ATt37sRgMHyhB1JCQkJCYmXsdjuNjY28/fbbTExMUFxczI0bN7h48SK1tbXU19dTXV1NbW0tY2NjhIaGEh0djcvloqWlhU8//RSHw8EPf/hD0tPTF/U0tFqt1NTUUFNTQ0REBNu3b79vrRIkHi4cDgd9fX1iS6PJyUm6u7tpaGigvr7+jktDQwMdHR2MjIwwPT3N9PQ0U1NTDA0N0draumj95ZbGxkY6OzsZGBigs7OTxsbGRevc7dLc3MzAwAAOhwOj0UheXt49eXEeZYS2VNevX0er1bJhwwZycnLmFeD0+XNHq6qqaGxsJDk5mTVr1mA0GhfZdRaLherqak6ePMnY2BiRkZG0tbVx/vx5cSyqqqqitrYWk8lEcHAwRqMRgJaWFo4fP053dzfR0dH09fVx7tw5Kisrqa+vF8egwcFBAgICiIiIIGCFVjk+n4/q6mouX75MeHg4GzduJCkpCZVKhc1mo7GxkQsXLuDzh6rm5eUtspVnZmaoq6ujpaWF8PBwsTDSwvOey+zsrBgGe+rUKT7//HNOnz6NyWRi27ZtvPjii2RmZi4aZ+cyNjbG7du36ejoID4+/r7lqC6kr6+PmzdvYjKZyM3Nvecc1ZmZGS5dusRHH32E1+vlxRdfZOPGjbjdbs6ePUtrayvr1q2jqKhoxRDjqakpTp48SXd3N2vWrFkyR3UuPT09XL16leDgYDZt2kRYWNiy6z4KLH3VJO4Kn8/HxMQEN2/e5OOPP+ajjz7i7NmzDA8Pk5CQwOrVq4mIiFjxpZaQkJCQ+GL4/OkWvb29DA8P43Q6uXjxIrOzs+zfv59/+Id/4Fe/+hWbN29mamqKDz/8kHfeeUdsn2C327FYLMjl8mUrecrlcjQaDSqVCo/HI4VNfguQyWR4vV5mZ2eZnJxkfHwck8m07CJ45SYnJ5mdncXr9SLz55h6vV6sVusdtzF3OxMTE8zMzGC1WpmamhL/vnD9Oy3CtoScykfZmP0iOJ1ObDYbDocDhUKBRqNZZK/JZDJUKhVarRalUonT6VwUtivgcDgYGRnBZDIxOTlJVVUVMzMz7Nq1i7//+7/nb//2b9myZQtWq5Vjx47x0UcfiX2bTSYTQ0NDTE5OUl1dzeDgIBs3buRXv/oV//AP/8ATTzyBTCbj9OnTHDx4kMrKSqxW68JDEHG5XFgsFux2O1qtlqCgIDG0V4gE9Hg8qNVqtFrtovNmTqVZwUvqcDju6FF1OBy0trZy8uRJPvroIw4fPkxtbS0qlYpVq1aRkpIyL+z3m4rH46G5uZkTJ04wNjbG9u3b2bp1K8HBwUs+G/cLhUJBYGAgOp0Oq9UqeuUfZb51HlWv14vJZKK5uZn29na6u7vp6em5q2VychKVSoVarZ4XOqDVaomPjycjI4OIiAgx/GNiYoLg4GAiIiLuOvldQkJCQuLuMZvN3Lx5kxMnTgCwfv16fvnLX7Jr1y6KiorEquwej4e2tjZGRkaIiYlh1apVdHV1cezYMXw+Hy+88AIJCQnz8rR8Ph9ms5mqqiqqqqqIiooSC2VIPHo4HA56e3tpaWkRqzyvX7+e4uJiVq1ateKSl5dHUlIScrkcs9mMw+FA5q+EmpeXx9atW1m9evWi7y21pKWliZ0QCgsLKSkpITc3d9F6d1ry8vJITU3F68/HDg0NZdWqVcTHx0seVb9Hta6ujtu3b6PT6SgtLSUtLW2ezejzF127efMmNTU1pKWlUVZWtiinE79n7Pbt29y6dQubzUZpaSk//OEP2bt3r/gMpaWl4fV6aW9vZ2pqSuzP3NPTw+XLlxkfHyc/P58f/vCHPPXUU6xZs4a8vDyysrJQKpV0d3czOjpKWFgYqampyxYPtdvtlJeXU15eTlxcHBs2bCAqKgq5XI7NZqOlpYWbN28CsGXLFjIzMxc9E0KF2cbGRiIiIli/fj3x8fErekPxi6mIiAgx51Sj0TA5OcnQ0BBer5e4uLh5fUIX8k3wqPb19fHpp59y48YNCgsL+f73v09aWhpKf3/ac+fO0dLSQllZ2X31qHo8Hnp7e7l+/ToAmzZtmtfq51HkWydUnU4nlZWVvPXWWxw5cuSu80YuXbrEwMAAkZGRREZGolarkclkaDQaYmJiyMnJIT8/n7y8PKKiouju7hYbRycmJopNlCUkJCQk7h+CUD1//jxGo5H/8l/+C9u2bSMsLEz0Fgg9B7u7u2lubiYsLIyNGzdiMpk4efIkTqeTZ555hqSkpEVCdWpqips3b3L79m3i4+PZvXu3FPr7iCII1aamJpxOJ4WFhezYsYOioiIyMjLuuCQnJxMeHk5ISAixsbGkpqaSm5vLpk2b2Lhx46L1l1rS09NJSEgQvWBr166lpKRk0Xp3s2RmZhIVFYXJZKKjo4OQkBBWr14tCVU/DoeDlpYWqqurUavVFBcXk5aWNi/0VxD5V69epba2lpycHDZt2kRkZOQicTA9Pc3t27epra3FaDTy4x//mD179mA0GsWxSGjB2NfXx+DgIKGhoSQnJzM8PMytW7dQKpW8+OKLPPXUU8TGxqLRaNBoNISFhaHVahkcHKSzsxONRkNOTg7R0dGLjgP/uVVWVorjVmlpKZGRkcjlcpxO5zwbdcOGDWRmZi7ydI6Pj1NeXk5LSwvx8fFs3LiRuLi4FW1ZhUIhiui8vDwKCgpIS0vD6XRSVVVFS0sLkZGRJCYmLgo1FnjYhaogLA8dOoRMJuOxxx4jMzMTp9OJ2WxmaGiIc+fO0dHRIbYUUqlUKJVKlHMqPS/c3t0K1e7ubq5cuYJMJmPr1q3ExcUt+Qw8Kiwt7x9h5HI5wcHBJCcnk5WVdU9LYmIiwcHB8x4IpVJJUFAQBoOB+Ph4CgoK2Lt3L0888QQ6nY6Kigpqa2uxWCxfaTiAhISExLcR2ZxWHoIhLuRuCYtarSYuLo6EhATcbjcjIyPYbDaCg4MJDQ3F6/UyNTW1KITK5/PhcrmwWq243W4CAwMXGXMSjw5qtRqDwUBsbCwJCQkkJSURGxuL0WgkIiLijkt8fDxr167lqaee4vnnn+e73/0u+/fvp6ioiMjIyEXrL7cYDAZCQkIICgoiLCzsrve/cDEajURHR5OUlERycjJxcXGEhoauKDS+TWg0GkJCQtBqtbjdbvE9n4uQXmA2m3E6neh0OnQ63bLeMZk/VDgqKoqUlBSx0q4wFmk0GuLi4oiNjcXj8TA2Nobdbkcul6NSqTAYDKSkpBAaGjrveyqVipiYGOLj4/F6vWIe9MLjFVAoFKjVahQKBV5/wSbBBlWpVAQHB6NWq7Hb7czMzCy5Hbvdjs1mQ+aPDJgbPrwccrkcrVZLaGioWGF327ZtPPPMM2RnZ4vtn0ZHRxd+9RtDR0cHly9fprW1ldHRUa5du8Yf//hHfvOb3/Db3/6WV155RWxlduPGDf785z/z3nvv0drael9aQ7ndblwulxjhuZSgfZRY+k17hFEoFKSlpfGd73yHv/qrv+IXv/jFXS9PPfUUKSkpi8IeZHN6vWo0GqKiosjPzyc+Ph6TyURPTw8Wi2WRESQhISEh8eVQKpXo9Xo0Gs2yuWOCWNX42xG43W5kMploTHk8Hvr6+hYZET5/65uZmRm0Wi3R0dEEBQXNW0fi0UGtVpOcnMxjjz3Gk08+SV5eHsHBwcjn9HhfaVGr1YSHh5OUlCR6RxMTE8Wwv7tZBGEiINgXX3QJDAykoKCAp59+mscff5yEhIRFNsy3FY1GQ2hoKCEhITgcDsbHx7Hb7fPWEUJ/JycnUavVGI3GZdunKBQKdDodSqUSl79X6ML1BNEpeLS9Xq+Yd7jS9/ALTEGYeDyeFW1KlUpFUFCQOC4KOanCZ+Hh4ej1ehz+Fl5L9Qs2m81MTk6iUCgIDQ1dUaDPRXiG5XK5OD6npaWRlpaGTCajtbWV6enpJcfqbwJWqxWZv1WMVqulu7ub27dvU15eLrYmGh8fx+PxMDQ0RE1NDQ0NDUxMTNwxx/dOeP21FaxWKzqdjqCgoLu6J99kHu2zWwK5XE5ISAjJyclkZ2eTk5Nz10tycvIij+pSKBQKFAoFcrkcr9eL2+1ecUCRkJCQkPhiaLVaEhISMBqNzMzM0N7ejnNBbzmfz4fNZmNmZga5v91EQEAAISEhpKam4nK5qKmpWRT54vF4GBwcZGhoiLCwMNFDIvFoolAoMBgMFBYWsm7dui8k6gTjXKVSieF+92pICs/g/TDkVSoVCQkJlJWVUVBQIPV1n4PC388yKiqK2dlZ+vr6FkVWuN1uhoaGMJlMREVFkZiYuKxg02g0REZGEhgYKBZHWih88XsqrVYrKpUKvV5PcHAwBoOB0NBQLBYLg4ODS/YsnZ2dxWq1olQqCQsLIygoaNl7qVQqCQ4OJjAwEJvNhtlsFr2mSqVSnFBRKBT09PQs6g8tRJ6MjIwQEBAgtrBZSkDfCZlMNu89cLlc9+XZ9voLnpnNZiwWy33b7lL45rS+TEhIYO/evfzyl7/k5z//OS+++CLPP/88L7zwAt/97nfZt2+fWGE5NzeXffv2iZNEd/JI3wmXyyV690NCQsSJtEeZR/vslkHuD7FQq9X3tKhUKlF8CkbPwhl8r9fL+Pg4TU1N9Pf3E+zvX7XcDJyEhISExBdDJpOh1WpJSUkhLy8Pm83G6dOnGRkZEWeufT4fs7OzdHR00NXVhV6vJysri+DgYIKDgyksLCQwMJDq6mrq6upEz4LXX3ivpqaGvr4+4uLiyM7OXjavSuLRQAiLFLz03/TfbZk/3DQ0NJTg4OB7Ft6POkJ4qlKppL29Xew5i3+iamxsjOrqaoaGhkhLSyM9PZ2AgAA8Hg/Dw8PiuDE2NoZGoyE5OZmkpCSsVisVFRX09vbO86JZLBY6Ojro6elBo9GQmJgohpunp6cjk8m4ffs2nZ2d8yI8HA4HXV1ddHR0oFKpSElJISIiYlnhI5PJCAsLQ6/XMzMzw9jYGA6HA+b0h87Ly0Ov19PU1CRWHxbs2eHhYerr6xkZGRGvUVBQEG63G5PJRHV1NZWVlZhMJjz+auhmsxmbzbbIMWOz2eju7qarqwuXy0VCQsJd5YLeibGxMa5evcrhw4epqKj4yry0Q0NDVFRUUF9fz8TEBNHR0WzdupVnn32W7373u/OW55577isVqjMzM4yMjCCTyYiIiPhWaItHTqjOfUjnzoDcT2w2G83NzZw9e5bz589TXV1Nc3Mzzc3NVFZWcuLECU6ePMnk5CRZWVnk5uZ+K9zzEhISEg8apVJJbGwsu3btwmg0cv78eY4dO0ZNTQ1dXV20t7dz7do1Tp8+zcDAALm5uZSWlhIQEEBgYCAlJSWsW7eO4eFhDh06xI0bN+jo6KC5uZlz585x+fJlvF4vRUVF5OTkSOP4twAhdPFRMQAftfO5nwiVlVNTUxkaGuLMmTPcuHGDtrY2GhoaOHfuHFeuXEGlUrF27Vox/WtqaoqrV6/yl7/8hbfffpuKigocDgdJSUmUlpZiNBq5fv06x44do6qqShyLrly5wpkzZxgcHCQpKYlVq1YRHh5OVFSU6MWvqanh6NGjlJeX09HRQWdnJzdu3OD06dO0t7cTExNDfn4+EXdofxgVFUVsbCxWq5WBgQFsNptoEwcHB1NQUEB2djbDw8McO3aMa9eu0d7eLtq3165dQy6XU1BQQEZGBgEBAVitVm7evMkbb7zBn/70J27evCkK4UuXLnHq1Clu3bpFQ0MDLS0t1NfXc+nSJY4cOUJjYyNhYWFs2LABo9G47PMo2O53suHb2tr49NNP+fDDD2loaBCF+L2y3L58/hoF586d47XXXuONN96gtrYWl8uFXq+flzs+NwfdYDCg0WiQy+XodDoMBgPh4eErTnwtdwwLmZiYoLu7G61WS3JyshhC/ijz0Fb9ra2tpbm5mdDQUNatW3dPVX9v377N6OgoBQUFrF27dl4Ft/vB9PQ05eXlHD16lOvXr9PY2EhDQwOVlZVcu3aNixcv0tPTQ2ZmJgcOHKCsrIywsDDJwJGQkJC4z8j8OV8hISFYLBa6urpoa2tjYGCAjo4OKioqOHfuHA0NDURFRbF//362bdsmhkwJOWWdnZ1icYyenh7Ky8s5d+4cw8PDFBcX8/TTT7Nq1aovPSMuIbESPn/PyrGxMaxWKzExMYSGhi5cTeI+oVQq0Wg0ov3Y0dFBf38/XV1dVFRUcPHiRUZGRigrK+Ppp58mIyMDtVrN8PAwJ0+e5MiRI/T19REZGUlmZiZGo5GAgABsNpsoTnt7e+no6KCysnLeWLRr1y42bNhAREQEarUanU6Hy+Wit7eX1tZWenp66O7uprq6mvPnz1NVVUVgYCA7duxg27Ztd2xLolQq6e3tpaGhAa1WS05OjihuFQoFWq0Wn89Hf38/zc3NDA4O0tfXR3l5ORcuXGBkZITCwkL27t1Lbm4uAQEBTExMcOrUKT799FPq6upISEggJycHk8nEkSNHOHfuHPX19TQ2NlJTU8OtW7e4dOkSlZWVqFQqtm/fzlNPPSWGHS/F2NgYlZWVK1b99Xq9XLp0iaNHj2Kz2VizZg2rV6++Jw9jf38/t27dwmQysWrVqiWr/trtdt566y1OnDhBf38/qamppKWlEejvuz13EkjYr9ls5ty5c7S2tlJaWkpRUZFYHGsppqenOXnyJD09PStW/RVSVD7//HN0Oh3PPPMMycnJj/xv0kMpVO12O8PDw1itVhITEykpKSEuLm7haovweDxMT08zMjKC2l9qPC8v775XaRRCH/r6+hgZGWF4eJje3l76+vqYnJxEqVSSn5/PU089xbZt24iJiUG5RElqCQkJCYkvj9xfe0Aw3MbGxuaNyzabjbS0NJ588kl27txJbGysaGSo1WqxKMbU1BSjo6Ni6wiAoqIiDhw4sKzxICFxP5GE6oNFJpOh0+nQ6/UolUosFgvDw8P09/czPDyMTCZjzZo1PPPMMxQXF4vRcVarlc7OTvr7+9Hr9WLEhRBibTAYUKlUTE5OMjg4OG8sSklJYffu3Wzfvp2EhATUajVyuZygoCCMRqM4Fg0NDdHX10dvby9TU1PExMTw2GOP8fjjj4v9Xlcaj1QqFdPT0zQ1NWE2m0lISBDbwsj8IeEGgwGtVsvk5CQjIyMMDAwwNDQE/rFv7969rFmzRhRas7OzYhivRqOhrKyMvLw8PB4P/f39DA0Nidvp6+tjeHgYu91OTEwMO3bs4MCBA+Tm5q547FarlaGhIVwuF1lZWaxduxa9Xj9vHZvNxpkzZ7h58ybp6ek8/vjjpKSk3JOHUbg3arWagoICVq1aNc+xJZPJ8Hq9VFdXMzAwgMFgYP369aJ3eanj9/mrRHd2duJ0OikrKyM3N3fF3w6bzUZ7ezter5f169eTn5+/ZD7w+Pg458+fp7y8nPz8fPbu3UtYWNii9R41ZL47+Zm/BoR49r6+PnQ6HVlZWXfVt87j8Yj9wqampkhOTiY9Pf2eHty7we12Mz4+Lh7j8PCwmIAfGhpKdHQ0KSkpYonxR322Q0JCQuLrxufz4XQ66e/vp7GxkZ6eHnHiMDo6mvT0dDIyMjAu0dNayEWrra2lvb2diYkJNBoN8fHxZGVlkZKSsmLDdgmJ+4XX62V6epqGhgZGR0cpLi4mOTl54WoS9xmHw8Hw8DAtLS10dHTMGwOys7NJTU2dl8Jls9lobGykrq4OlUpFfn6+KGB8/rz4oaEhWltb6ezsZGJiApVKRWRkJOnp6aSlpYn9VQWhIYxho6OjtLa20t7eztjYGDKZDKPRKObIRkVFrSj05tLZ2clrr73GtWvX2LhxIz/84Q9JT08XvZkul4uxsTEaGxtpbW0VzzsuLm7e2CesPzs7S3t7O+Xl5bjdbjZs2EBGRgZut5u+vj56enoYGBjAZDJht9vRaDRERESQmJhIamoqMTExdzx2s9lMR0cHQ0NDGI1GMX1uLt3d3fzTP/0Tly9f5plnnuGll14iOckZbIoAAP/0SURBVDl5WS/tUphMJlpbWzGbzeLxLaxB4PV6KS8vp7KykqCgINatW0dycvKyDjDh3tfV1dHf309mZiapqakrenqtVis1NTUMDw+Lv1MLr5HH4+HmzZu88sordHd387Of/Yxnnnlm0XV5FPnahapQFXfuYXi9XlwuFy6XS5z1WWhYKBSKRX/z+Xx4PB6cTider1csmLTcw/FlEI7R4XBgt9vFKpMqlYqAgAC0Wi0qleor2beEhISExNIIlSCtVisOhwO5XE5AQAA6ne6OOUILv6fz90yUxnKJB4UkVL8+PB6P2DvU4XCg8LebEcaAuQieM6FVidBjeaG4ELZn9/dKFcYiwYu6FF6vF4fDgdVqFasGa7VacQy7FzFmt9s5c+YMb7/9Nj6fj+eee44dO3YQHh4uHqt3TsuTO419gsdfqJAeEhIiOoME+9tut+NwOHC73WKIsbAsd85z8Xq9OJ1O8ftCvudcLl68yP/6X/8Lj8fDz372M3bu3HnPkQcejweHw3FHvTA7O8vMzAwKhYKgoKBl1xMQ7p/L5ULtL8a68PjnIlx/t9u95Po+n4+RkRE++OADDh8+TE5ODr/61a/IyMi4p2fhm8rXGvrr9TdZ7+npET2Tw8PDjIyMMD4+zuTkJBMTE4yOjoqfDQ8PMzo6is/nW1SgSDanb5NMJhNfGK+/T9VKD9a9IvOX29ZoNAQGBhISEiI26BYGkvu5PwkJCQmJlRGMR8H4ECY0NRoNarV6xR91mT/XNTAwkODgYLRarWhAOBwOccyXkPgqEYSAFPr79eD1evF4PKI9KdiUC206YbwQBN1S6V1yf29dtVqN0t+yKCAgYJEQmYsgnux2Ox6PB7m/S4Uwhi21n5VQKpWo1WoGBwdpaGgAIC0tjfDw8HnjoXDe+I9bGDuXOm+lUolOpxN7v8rm9E0VjlUQuL45RYKE7S51/IKon5mZwWKxiOeP3zEll///qRr4j/X27dvU1dVRWFjI9u3biY6OXnF8n8vcyUy73S62tZHJZEsen/C7sNx9novPX4DJ6XTi8vfEXXj8Pp9PPAaLxYLFYhF/s/Dfs7nn4na7qa6u5tNPP8Vms3HgwAHWrFmzyPv7qPK1elQdDgfV1dV88skndHV1iT2ehJspPOT4b6xAQEAAjz/+ON/97ncXJT4LhkpPTw9NTU1YLBbS0tLIy8uT+t9JSEhIPIIIxsHU1BQ1NTViCJvb7SYgIIDU1FQKCgpISkpa5PWYiyASLBYLfX19dHZ2MjQ0REBAAGvWrKGgoGDhVyQk7iteyaP6teB2u5mYmKC5uVm89nK5nOjoaAoKCsSWVssJzKUQxJdgjzqdTnJzc8nMzFxU5FOwXUdGRmhubhZTEDweD1p/hdfVq1eTlJQkFvK5WwYGBnjzzTc5deoUhYWF/OQnPyE3NxeVSoXH48FisdDQ0EBNTQ2jo6Pgrxicn59PVlYWoaGhdy0CPR6P2KKxsbFx3nUUthcSEjLv+J1Op3jeHR0djI+P43Q60Wq1xMXFkZ+fT1paGkFBQchkMjweD+Xl5bS2tpKZmXnHHNC5eDweJiYmqKuro7GxkfHxceRyObGxseTn55OZmXnP95k5XlGz2Ux3dzednZ2Mjo5iNBrZuHGj2JpG+I0ZGhoS7/PU1BQul4uAgAASExNZt24dcXFxogfa5XJx6dIl/vCHPzA5OckvfvEL9u7d+60I++XrFqp2u51Lly7xxz/+kYaGBtxuN3K5HLfbPS8EITAwUJw58Hq9BAUF8cILL/C3f/u3i8Sn2/3/sffe0XGc2Z320xmNRmjknDNBgARzTmImRTGJVBqFCfbYO94Ze9fnrDfMN54Nx+uwa1vWaDSj0UiiqMycxUyCCYwgCBA55ww0Oqfvn65aRJLKDO9zTh3pENXV9VZVV72/uvf+rou6ujr27dvHwYMHcTgcrFmzhpdffpmkpKQR6woEAoHg0cdms3H37l0+/fRTrl69SkdHB06nU46MhIaGMnv2bDZu3Mjs2bPx9/cfvQk8Hg+Dg4PcvHmTc+fOUVJSIrd0SElJ4aWXXmLr1q2jPyYQfKMIofrd43a7aWpq4sSJExw7doyqqirsdjterxedTkd+fj5bt25l4cKFD2ReI4mRlpYWrly5wsmTJykpKUGv1/Piiy+yefNmwsPDR3zGarVSVlbG3r17uXjxotz3VIqyhYSEMGfOHJ5++mnZXOh++4GvBvXMmTO899572Gw2tm7dyvLlywkLC8Pj6xV98uRJ9uzZQ2VlpRwF1Gq15OXlsWHDBhYtWkRkZOR9xarX66WxsZFjx45x7NgxampqsPlSl/V6Pbm5uWzdupXFixdjNBrl/S8pKWHfvn1cuHCBtrY2ORMSXxudqVOnsnXrVubPn09QUBBer5ehoSEcDodcavcgwtLr9dLU1MShQ4c4evQo9fX1OBwOvF4v/v7+5Ofns2XLFhYtWkRQUNADHV+vr+Swu7uba9euUVhYSGlpKW1tbVitVqZMmcLPfvYzpk2bhp+fH263m5s3b7J7926Kioro7OyU05wVvhTyhQsX8txzz5Gfn09AQABeX+rvxx9/zL59+5gyZQr//t//+y9dk/uo8r2m/uLLu5feICxdupRly5bJb617enqIjY1l8+bNbN++naVLl7JkyRKWLFnC7Nmzx1hze71eent7OXv2LJ9++ilFRUUMDQ2RnJzMrFmzCA0NHfbNAoFAIHjU8Xq9mEwmjh8/zltvvYVKpWL+/PksWrSIvLw8NBoNlZWV3L59G6vVSmJiIrGxsSMmIV6vl+7ubj7++GN++9vfcurUKfr6+oiJiWHq1KnMmTOHKVOmEB0dPeK7BYJvGknkiNTf747Ozk4OHz7Mzp07qa+vJz8/n9WrV5OdnU1fXx83b96kra2N2NhYYmNj75v+abVaKSoq4ve//z2ffPIJxcXFNDU1YbPZyMvLkwXIcOx2O1VVVZw5cwaz2czMmTNZsmSJfA+rq6ujvLwch8NBbGwsERERY+pmx6O1tZV9+/ZRUlJCQUEBq1evJi4uDqVSyeDgIMePH+cPf/gDZWVlFBQUsH79enJzc+nv7+fWrVt0dnYSGhoqR/juRW9vL/v372fnzp20tbUxZcoUVq5cSXZ2tvwSsLm5meTkZPk4AlRUVHD69GmGhobIz89n0aJF5Ofno9frqa+vp7y8nL6+PjIyMmTBrNPpxq2hvReDg4N89tlnfPDBB3R1dTF9+nRWrVpFRkYGPT093Lhxg46ODhITE4mOjn6g4+t0Oqmurubjjz/mD3/4A4WFhfJzZtasWcyZM4fJkyePiEqXlJRw6tQpHA4Hs2bNkserVqspKSmRU7TT09MJCQlBrVbLLsBVVVVUVFTIBoFSffDjzPcqVJU+O27JWTE7O5vs7GwiIiLk1gIJCQls2bKFVatWkZ2dTU5ODpmZmcTExIy5QC0WCzdu3GD//v3U1NTIF0V2djZz584VQlUgEAgeQ6S0q8DAQF544QXWrl3L3LlzKSgoYPLkyahUKrk/YlhYGLm5uSOydPr6+nj33Xd57733aG9vZ/78+bz88sts2bKFZcuWUVBQQGxs7ANNXAQPF1LS2INOZr8JvL56t6+CEKrfLQ6Hg6tXr/LJJ5/Q0NDAwoULefnll1mxYgV5eXlERUVRV1cnu75mZmbe1wHcbDZTVFTE2bNnCQ8Pp6CgALvdjsPhYPr06RQUFIwRqgBarZaEhASWLl3KihUrmD17NlOnTmXSpEk4nU6qqqoYGhoiLi6OlJSUMaVv43H16lUOHjyISqVi5cqVTJkyBX9/f+x2O2VlZbz77rvcuHGD5cuX8+Mf/5innnqKqVOnEh4eTmtrK3fv3kWpVJKWlkZYWNiEETyv18uVK1f46KOPaGlpYcmSJbz00ks89dRT5OfnExkZSWNjI2VlZahUKnJzc+XrWqlUEhcXx/z581m+fLl8787KykKj0XD37l3ZQVdyxP2ySPv3xz/+kZaWFtasWcNLL73EkiVLmDJlCqGhoXL/WpVKxZQpU8ZkbI7G7XZTUVHBRx99xJ49e7BYLKxYsYJXX31Vbk+Zn59PeHj4CL2iVqtJSEhg2bJlLF++XO61mp+fj9Pp5M6dO3R1dTFp0iQSEhLkiLGfn58cuQWYOXPmA6c8P8p8r0IV3wWq0WhGLBaLhZKSEioqKjAajcybN4/MzMwR64x+o+VyuaitrWX//v0UFxcTFxdHSEgIfX19pKWlMW/ePCFUBQKB4DFD4TPAkARoXl4ekZGRBAQEEODrS2gwGKitraW0tJSQkBBmzZpFSEgIXq8Xs9nMwYMH+e1vf4vFYuHFF1/kpZdeYuHChaSmphIaGkpAQMCYF6OChxvHsFZFXV1d6PX6MXWB3yTStVRdXU1FRQVms1l2d/0yCKH63dLW1sbRo0c5d+4cMTExbNu2jfnz5xMWFkZAQAChoaGYTCZKSkqwWCxkZWWRkJBwz/uB9HIkKSmJlStXkpCQINfNT5s2bVyhKgVu4uLiSEpKIiwsDIPBQEBAABEREVgsFiorKzGZTKSkpDyQ74rJZOLkyZNcvnyZjIwMVq1aRXx8PCqVir6+Pk6dOsXRo0cJDQ3lhz/8IQsWLJD7wEZERDA4OMjdu3cxm80kJCSQlJQ04W/IZDKxe/duTp48SWJiIps3b2b27NmEhYURGBhIYGAgg4OD3L59m66uLmbMmEFcXBwqn7NybGwsSUlJREREEBgYSEBAgJwefPfuXdra2sjJyWHKlCljjt398Prqf3fs2MGJEyfIzMxk27ZtzJgxg5CQENkIVfI4GBgYYOrUqWOyNofj9aUR79u3j3379uHn58dLL73E9u3bmTVrFomJiYSEhIwxYJLSe+Pj48ecZ6l12vnz52lvb2fWrFlkZ2fj72tto9PpGBwc5NatW/T29pKbmysfw8eZiV8JfccofK5hw3/40o/9XuswLG3rwoUL3Lx5k4iICObPn09cXNyYbQgEAoHg8UKlUhEcHEx8fLz89ll6Vmg0GmJiYoiJiQHfhMpqtYJPzFRVVfHhhx/S1tbGxo0b2bZtG1OmTJF7Bw7fluDRwOtLB7958yb79u3jxIkT1NXVYTKZ6O3tpbu7m+7ubgYHB+VauK+L11d6dOHCBT777DPOnDkjG9MIHl7a29uprKzE5XLJfUqlKJVarSYkJITJkycTExNDXV0d1dXV8v1jInQ6HVlZWaxcuZKZM2eO27t5NNK9argrsHTfGd6yRO1zMb9XRFeio6ODmpoaABITE+X9kLJIbt++TV9fH9nZ2WRmZsomTQqFgrCwMLKysoiJiaG3t5eamhqGhoZGf4VMS0uLnJqckZFBWlqavD2VSkVoaCh5eXmEh4fT3NxMRUWF3OJGGvfwjhkK3wtIra8VjEKhwN/f/yuJMq/XS3t7O7du3cJqtTJp0iRSUlLQ6/Uofc7OkZGRcvSzo6ODu3fvYrFYRm9Kxmq1cu3aNY4fP45CoeDpp59mw4YNZGdnYzAYRjw7RqPxuUWPPs9KpVI+t1LtrXQ88EVi4+LiSE1NlQ2r7Hb76M0/dtz/Sn8EGBoa4saNG5w5cwan08mCBQuYNm0aer0et9stxKpAIBA85kgTm/EmBgqfg7w0GZTcF4eGhrhy5Qo3btwgOzubVatWAXDhwgX27t3L8ePHKS8vv+cETfDw4fX1xG1ra6OhoYG6ujpKS0s5e/Ysu3fvZteuXezatYvjx49TV1dHf38/g4ODDAwMfKVF+mx3dzeNjY3U1NTQ1NSEyWQavWuChwjJobajo0P2SwkJCRkhhtRqNVFRUYSHh9PX10dLSwtms/meLzik6GhISAh+fn7j3pMmYvS6LpeL+vp6bt68SXd3N7GxsaSkpIxrCDeajo4OWlpa5EitFJmTHI4bGhpwu90kJydjNBpHiF+VSkVERASRkZGyK6/FYplwPt3c3Ex7ezv+/v4kJiaOqaGVHG0jIiKw2+3U1dUxODgob2/0uB0OB62trdy8eZPOzk4SEhLIzMx8oHGPxuPxUF9fT1tbGwEBAXIa8/CXB/7+/kRHRxMREYHD4aChoUE2ghqP1tZWrl27RkdHB7m5ucydO5ehoSFOnTrF7t27OX36NHV1ddhstjHHTBKmEl6vV84AkfwR8vLySE1NHRPBDgsLIzk5GbvdTmNjI06nc8TfH0ceeaHqdDqpqanh5MmTNDc3k5+fz7x584iIiBi9qkAgEAieMCRny66uLvz8/IiNjSUoKEiepF67dg2z2UxWVhbl5eW8++67/O53v+PNN9/k9ddf59/+7d/YvXs3NTU195ycCh4uPB4PLpcLl8tFd3c3V69e5ciRIxw/flxejhw5Iqfu7d27V/7/L7vs3buX/fv3c+bMGZqamnC5XHg8HnG9POTY7XZ6e3sZGBhAq9USFhY2pv5RqVQSGBgol4719/djsVjue24lMTJagN0PyUG2tLSUixcvcuDAAd59910uX75MXFwcy5YtY/LkyQ9Un9rX10dfXx8Gg4GwsDA5Dd3pdNLb20t/fz9arZaIiIgxggif425wcDAenyP60NAQbl9v09F0dXUxMDCAXq+XBfpo4RscHCyn83Z1dY0Qvh6Ph56eHsrLy7l06RKHDh1i586dnD17lsjISDZu3Ehubi46nW7Ytz4YHo+HlpYWhoaG5FRqyZxIQunrMCKVhHR2dt5TBNbX11NWVobX68VgMHDr1i3eeecd+dnxL//yL7z++uscOXKE9vb2McfN7XbT1dXF7du3uXjxIvv37+cPf/gDZ8+eJSsri82bN5OZmTnmRUdAQABRUVHyPlqt1jFC+HHjkRaqUjj/7Nmz3L59m4SEBBYvXkxqaioqleqxP3kCgUAgmBgpanrr1i3q6uqIjY0lLy+P4OBgnE4nnZ2dlJeX43K5aGtr4+zZszQ1NREYGEhYWBj9/f2cOnWKP/7xj+zbt4+mpqbRXyF4iJEi6QMDA1RXV1NdXU1XVxc9PT309PTQ0NDAuXPnOHjwIAcOHPhay8GDBzl//jxtbW3ydwsebux2O4ODg1gsFjQaDQaDYUQUUEKn0xEQEIBarcZqtX6r4sDpdFJSUsKOHTt4/fXXeeONN9i1axdms5l58+axaNEi4uLi7ptK7Ha7MZlMWCwW9Ho9QUFB8mecTicDAwPY7Xb0ej3BwcHjjtvPzw+9Xo/X68VisWCxWMYILgnpOOp0OvR6/ZgUXYUvlVpKB5bay0g4nU7Kysr49NNPefPNN/nNb37Drl276OrqYvbs2axevZqYmJgx230QvL60fLvdjp+fn5xCPPo3Kl0D+EpEXC7XiL9LOJ1OWlpaaGlpwWQyUVlZyYULF+jq6iI0NJTQ0FDa29vZt28fv/vd7zh58iSdnZ0jXm7YbDbu3LnD22+/zeuvv86bb77JJ598IrfUXLJkybgtgbRaLUFBQWi1Wjmb434vTR51HmmhajKZuH79OoWFhfj5+bFkyRKmTZs2xgVr9MUoEAgEgscfp9NJaWkp586dY2BggIKCAgoKCvDz88PpdNLd3U1raytut5vOzk5SU1PZsGEDL774Iq+++irPPfccOTk5NDQ0cPjwYS5dunTPdDDBw4nSZ9qoVCrlSKfH40GhUKDX6wkMDCQoKOhrLwaD4b4CQvDw4Ha7sdvtuFwulEolWq12jDBQ+GoH1Wo1SqVSjtJ/W0LV6zPTktLRHQ4HTqcTq9UqR0gfRCg7nU7MZjM2m02uiZTGJo3b7XajVqvHHTe+34307y6XC6evx+p42O12nE4nKpUK9QTteySxqlQqcTgcI0SvlP4qpdFL58VisdDf309PTw92X2/br4LNZpPHO55IxTdeqSzEPqyH7WgsFotc4242m3E6nWRlZbFp0yZ+8IMf8Nprr7F9+3bi4uK4ffs2+/fvp6KiYsSzw+NzqpfEpnQ8bDYbvb29E45Xql/V6/VYLJb7pqE/DjyyQtXhcFBRUcGJEyfo7u5m2rRpssOY19eAVzp5Xq9XfjCNPukCgUAgePxwu93U1tZy8OBB7ty5Q3p6OsuWLSM1NRWFr05LMtdRq9VMnTqVTZs2sXr1aubMmcP8+fN55pln2LRpEykpKVRWVnLp0iV6e3tHf5XgIUV63huNRnJycpg6dSppaWmkpKTIzqkrV66Uz/PXWaR2FLGxseCbiAoebiQRKomWieaH0hzS6/Wi9JnvfFtoNBoyMjJ45pln+MEPfsArr7zCxo0bCQkJ4fLlyxw4cIDbt2/LRkQT4XK5sNlsuFwuWTxK+z183F6vV15GM/xvkmgdT+DhE1DS9sfbFqOOo8pnNiShVqtJS0tj9erVvPDCC/zgBz/gmWeeISYmhqKiIj766CNu3rx5XyOriRi+7/fbP3z7M9FYzWYzAwMDOBwOjEYjs2fPZuPGjSxfvpyZM2eycOFCtm/fzqZNmzAajdy4cYPbt28zMDAgb1+n05GZmcmWLVvk87x161aCg4M5efIkH330EWVlZePWBatUKjQaDU6nc0RU+nHl2/u1fYt4fS6/hYWFXLp0CavVilKppK6ujgsXLnD27FmKiopoaWnBbrfT0tLClStXuHbtGp2dnROmLggEAoHg0cfj8citA06ePInBYGD16tXMmzdPbm3g9b3Bl9Lfli9fTk5ODqGhofj7+8u1QNOmTSM3Nxe73U5tbS1dXV2jv07wEKJSqdDpdPj5+REREcH06dNZt24dGzdulJenn36a5cuXs3jxYhYtWvS1loULFzJjxgzi4+NlB9Px0ikFDw9SqqdOpxsRZRyO1+uVI5oul0u+pr4tsapSqUhISGDBggWsXr2ajRs38vLLL7NmzRrUajWFhYWcPXtWzgS5FxMJLbVaLbdNcTqd2Gy2cV+sSPdHhUIhpwGPF3nFZ0ak1WrlyOtocYXvvmy1WnG73WPSrFUqFbGxscyZM4dVq1axceNGXnzxRZ555hn8/f05d+4cR44cobOzc9xt3wuFQkGAr8WY0+mcMCLudruxWq0ofC1kJhqry+XC4XDg9XqJj49n9uzZZGZmyu1oAgICiImJYdmyZaSkpDAwMEBtbS29vb3yOdNoNCQkJLBkyRLWrFnDM888wyuvvMKWLVtwuVwcPnyYc+fO0dXVNebcDH958G1dhw8Tj+QIvV4vHR0dlJaWyrUm586d449//CNvvPEGb775Jjt37pTfOt25c4f333+fjz/+mKqqqgnzzgUCgUDwaOPxeGhubmbPnj3s3r0bp9PJqlWrWLFiBTExMfKDXelLB9XpdKjVamJjY9HpdCMmd0qlEqPRSFRUFH5+fnKqleDhRppopqSkkJ+fT25uLjk5ORQUFLBo0SKWLl3K0qVLmTlzJrGxsRiNxjFpvF92ka6T7Oxspk2bRnZ2NsHBwaN3TfAQodPpCA4OxmAw4HQ65RTM4Xh99ZlSLWBQUJDsnvttoPC1owkMDMRoNBIWFkZmZibLli0jNzeXnp4ebt26RWNjI/Z7tCbRaDT4+fmh0Whwu90j0nY1Gg1GoxG9Xi+nFI+3LYvFwtDQEEqlkiBfr9GJxJvRaCQgIAC73Y7FYhkzz5ZEqslkwuv1ysZV0nGUxi31T42IiCAzM5MlS5YwY8YMbDYbhYWFtLW13Vegj0ahUBAeHi7fw4eGhsaIaa+v1+rg4CD43HUnetGk0WjkUoIAX69dqY2OhEKhICEhgcjISLxeL319fZjNZvk7pfFK946IiAgyMjJ4+umnyc/PZ3BwkJs3b9Le3j7iWEovTux2O1qtdswz63HkkRWqWq2WxMREZs2aRX5+vnxRqdVq1Go1Go1G/kEpfXnnw1MfBAKBQPB44fF4aGtrY8+ePXz00UdYLBZWr17Nhg0bSEtLQz2sflDt65EYERGBy+UakZY1HOntNaNqtgQPL5JQzc/PZ/369SxfvpykpCQMBgPBwcHycq+J95dFoVAQEhLCvHnz2Lx5MwsXLhTdBx5ytFotISEhGI1GbDYbnZ2dWEb1znS73XKNpJRl4e/v/53OJTUaDbGxscTExODxueP29/ePEYPDUavVBAQE4Ofnh91ux2w2j4jmhYaGEh4ejstnJDd63F6vVx63RqMhLCzsnuOOiooiJCQEs9lMV1fXGIdgh8NBZ2enXGoRHx9PYGDgiG2MRtrP+Ph4NBoNLS0tE5oHDb9Pj0apVJKQkEBQUBCDg4O0trZiMplGbMfpdNLX1yfvX0JCwhgHaIkAX+shnU6H1WplaGho3H3Ct1+KYbW590Kj0RAXF0diYiJarZbOzs4x4/V4PFgsFqxWKwaDgYCAgPtu91HnkRyddNFt376dv/7rv+av//qv+au/+it5+cu//EteffVVpk6dSmBgIFOmTOHHP/4xL7/8MllZWRO+JREIBALBo4nbZ/e/Z88edu7cic1mY8OGDWzfvp3s7Gy5NQPD3mbHxsaSnp6Ow+Hg1q1bY+q+vF4vJpOJrq4uHA4HISEhhISEyH8XPLxoNBo5KpOSkiKnfH+b6HQ6YmNjycrKIi4u7iu10hB8dygUCiIiIoiLi8PhcFBfXz+iLYkUZaurq6Ozs5O4uDhSU1PlXp52n2uwyWQaE6H7Kkwktry+qK4UkdNqtWg0mntG0lQqlRwFNZvN9PX1ydFilUpFSEgIGRkZ+Pn5ySUNw4Wl1WqlqamJ9vZ2AgMDSUxMxGAwyBE9qYewdKzi4+OJi4vDarVSW1tLW1ub/DeAoaEhKisr6erqIiwsjIyMDIKCglAoFHgm8I/xeDzY7XZZ9EoRYmncDoeD3t5eOjo66O/vl9NxR6NUKklMTCQ5ORmHw0FVVRUdHR0jhH5/fz/V1dV0d3djNBrJzMyUW/bYfeZW0nn29/cnPj5e7q1bV1c3Iloq0dzcTEdHByqVipiYGIKDg1Eqlfc9z5LjsFQ+MPw822w2+vr6cLlcGI3GMeaxjyOPpFBVKBQEBgaSnp5OQUEB06dPH7FMmzaNyZMnExkZiVarJTIykry8PLn+6HF/+yAQCARPEpJI/fzzz/nDH/5AX18fa9as4emnnyY+Ph6n04nJZMJkMskujRqNhqioKGbNmoVCoeCLL76grKyMwcFBXD5nz8HBQe7cucPdu3cJCgqSnyuCRwMpvftexijfJAqFQjY6+aYitYJvl+joaCZPnkxAQAA1NTVyuqXTV5daX1/PpUuX6OjoIDs7m/T0dNk1vLq6mqNHj3LixAkaGhpGCLMvg9fnMiu5vZpMJhwOh1wLOTAwwK1btygtLUWtVpOcnCyXKtwLqVXK4OAg7e3tcnqvQqHAaDQyZcoUwsPDKS0tlT1cnD6DnqqqKq5fv05vby8JCQlkZ2cTEBCA0+mksbGRI0eOcPDgQblvcGRkpJzdWFVVxZ07d+jp6ZGPY2NjI0VFRZhMJvLy8khJSZFrg/v6+ujq6sJkMmH3uQc7HA76+/spLy/n5s2bOBwOJk2aREREhPzbknwI3n77bc6ePUtfX9+4kU2FQkFYWJhsuFpaWkppaSl9fX04fWm09fX1XL9+HavVyqRJk8jIyECn0+H1eqmqqmLfvn2cOHGClpYW3G436enpTJo0CZPJxNWrV6mqqsJsNuPy1egODQ1RWFhIQ0MD0dHRZGVlERYWhtPplEsWpRY9w8/z5cuXuXHjBjabjdTU1BHjBRgYGKC1tVUWv09C6q/qV7/61a9G/+P3TX9/P7du3eLu3bsEBwcza9Ys2alRQuFzLZNSsYYv+BodX716lfLycjIzM5k/fz7h4eGP/QkVCASCJwmPx0N3dzeff/45r7/+OjU1NcTFxZGdnY3VapUnTdLkpLm5GbVaTXh4OFqtFoPBQHl5OeXl5fT19ck1qz09PRQWFvLZZ59RWlrKlClTePbZZ8nMzBQvOwXfGpJo6erqwmw2ExMTg9FoHL2a4BtCEiNtbW1UVFTQ2dmJTqdDq9XS0NDAwYMHOX78OEFBQTz77LPMnTsXg8FAR0cHBw4c4P3336e4uBiDwUBCQsK4kfumpiYKCwvp7OyUW2QNX8/tdtPS0sKRI0c4fvy4XJdosVior6/n9OnTfP7559y6dYv4+HjWrFnDrFmzCA4Ovuec1uPxUFVVRWVlJREREeTl5WE0GlH4UlE1Gg1tbW2UlZXR1tYmGyZJAvDEiRP4+/uzZs0aFi5ciNFopK+vj8OHD/POO+9w9uxZQkJCSE5OJjAwEI1GQ1NTE2VlZfT29sr30vr6eg4dOsSJEyfQ6/W89NJLzJ49G71eT1dXF/v375dFoJSm3NjYyPnz59m1axdXr17FaDTy3HPPMXv2bLnX6cWLF/nwww+5du2a/MJhogijSqVCr9dTU1NDaWkpAwMD6PV61Go1NTU1HDhwgJMnT8rfM2PGDDlt+t133+WDDz6gpKREjsCHhobicDioqamhqqqK/v5+/Pz8UKlUdHV1cfz4cd5//31aW1tZvXo1q1evJi4ujoaGBo4cOcLp06fp6OjA6XRisVhoaGiQe3bfvn2blJQUtm/fztSpUzEYDCh8Ds3V1dUcPnwYs9nMmjVryM3NHZEt9DjyUArVwcFBiouLqaiowOizfk5JSRn34hsPj8dDb28vV69epbKykszMTObNm0doaOjoVQUCgUDwCGO1WikuLuZf//VfKSkpwePx4HQ6qamp4fLlyxQWFnLhwgUuXLjApUuXaGhoICIigpycHLRaLUajkejoaBoaGrh+/TpFRUUUFhZy9OhRjh49Sn19PZMmTeKFF15g0aJFcjqYQPBtIITqd4vSZxTk5+dHR0cHJSUlXLt2jcLCQo4dO8bly5fx8/Nj27ZtrF+/nqioKFQqFa2trZw+fZrz589jMplISkpi8uTJ45YGNDU1cfHiRbmV4mihKqUdHzx4kIMHD1JYWMi5c+c4duyYLPDq6+tJTk5m06ZNrFq1iri4uPtG7f38/GhtbaW4uBiFQkFmZiZRUVFyvaS/vz/BwcH09PRw8+ZNrl+/zsWLFzl8+DCFhYVotVrWr1/P+vXrSUxMRK1W09vby8mTJzl9+jQtLS1kZWUxZcoUjEYjRqNR/s7bt29z/fp1+TheuXIFrVbLli1b2LBhA1FRUSgUChobGzlw4ABHjhyRHY2PHz/OkSNHOHHiBJWVlcTExLB161Y2bNhAdHS0nD575swZTpw4QUBAAEuWLCE3N/ee9+fg4GD0ej3Nzc3cuXOHGzducO7cOY4ePUpRUREBAQFs2rSJp59+Wg5sWa1WPvzwQy5dusTg4CC5ublydDQ0NBS1Wi0/O65cucK5c+c4fPgwhw8fpr29naVLl/LSSy/J+1ZRUcGBAwfkY3z27FmOHTvGwYMHOXnyJFVVVWRmZvLaa6/x1FNPjYioOhwOrl69ypEjR4iMjOTZZ58lNjb2sX9x+lAKVaevUbFWqyUrK4uCggIiIyMfWKhKOfRWq5XAwEA5FXi8N10CgUAgeHRxuVz09fXR0dFBYmIiubm5pKamEhMTQ1RUFNHR0SMWyQk2LS0NpVIp16pmZGRgMBgYGhpicHAQu91OVFQUK1as4IUXXmDevHnjTkIFgm8SIVS/e7RarRwp0+v1mM1mTCYTarWavLw8nnvuOdatW0diYqLsceLxeGT32NTUVBYuXEh2drZcvzocq9WK2WyWSw2k9GEJxTAHWIPBIEdTrVYrXq+XuLg4VqxYwfbt21m2bBkJCQkPFEVTq9XY7Xaqq6tpb28nMjKS1NRUOUKn0WgIDw8nMTERf39/+d4HMHnyZLZu3cq6detIS0uT04w9PvfewcFBEhISWL16NZMmTUKv18uldnFxcfj5+WH29RtVq9Xk5+fz7LPPsn79ehISElD7jO3UarXsvCxt22az4fV6iY6OZsmSJbzwwgusWrWKhIQE+fgPDAxw7Ngxbt26xbRp01i1ahXx8fHydsdDrVYTFRVFfHw8Wq1WHq9Go2Hq1Kls376dtWvXytuRMjclc6js7Gyeeuop+fwFBAQQHx9PUlISfn5+DA4OyrWy8fHxPPvsszz33HPk5+fLkV6dTic7R7vdbvk8A8TExLB69WpeffVVli5dKr9UkGhqauLIkSOUl5ezcOFCli9fTkBAwANro0cVhXe8it7vGalAuq+vT77w7+cONhzpRt/d3c3AwABBQUFERkbeN59fIBAIBI8Wbrcbk8kkp41Jb9vxPQuGI00UIiIiRpSCSM+MtrY22traMJvNKHy99yIjI4mOjkav1z/2EwLB94/H42FgYIDS0lI6OzuZNm0aycnJo1cTfMN4fUY27e3tdHR0YDab0Wg0hISEEBcXh9FoHCEanE4nnZ2dtLW1ofL1AA0LCxtXKJnNZjo6OrDZbISFhY27niRauru7ZWHkcrlQKpUYDAYiIyOJiIjAcI/+nuPR29vLBx98wN69e8nOzuaHP/wh+fn5stAd796nUqkIDQ0lNjaWkJCQEQakLpeLnp4eGhsb8Xq9JCUlER4eLu/T8OPY3t6OxWJB43PvlVpBDR+7tH5XVxfd3d2yYZEU8Y2IiCAqKmrMuEtLS/m7v/s7ysrK+MEPfsD27duJioq6b3TR6/ViNptpa2ujo6MDq9WKxudqLL0UGn1umpqaaGpqws/Pj8TEREJCQuR98Xg88vYk12ilUklgYKBsuKQd1rrG7XZj9jkjS3WqTqcTta+3bWRkJDExMfiN6tXrcDg4fvw4v/3tb3G73fzVX/0VCxYsGPHC43HloRSq+E6+x+OR32h82QmC1+eq5fF45M9/2W0IBAKB4OHH6/V+qd56ynEapUvPi+HPHun581WeQQLBV0EI1e+P8e4B0u9/9P2CYfNUJrinSEjb9Xq9D7SetK40PR++D1/2PuR2u7l+/TrvvPMODQ0NrF+/nk2bNhETEzPiRd2XHbd0v1WpVGPW+bLbG358pP9yn3EfPHiQf/qnfyIqKoof//jHcu3wgzD6ODPqu0YjjXf4OIYz3ngVPmO18bTH6O/3DNMpE423qqqKd955h0uXLrFy5UpeffVVOQ36ceehHaHS1/tUOtFfFumEq325+F9lGwKBQCB4+FH4zEEedBnv4S5NLDQajWymIrm3iueHQPD4M949YKL7BcPmqfdah2HbfdD1NBoNWq0WnU6H1KLkq96HVCoVmZmZrF69milTpgBgsVhGvNj7KuPWaDRoNJpx1/my2xt+fB5k3G63G7VazbRp01izZg3Z2dlfKrI4+jjfb/+k8U60znjjlY7N6H0fvb5Wq8XPz++ezxu3283g4CB+fn4sXryYFStWEBYWNu6+PI48tBFVgUAgEAgEgicJj4ioCr5hPB4PnZ2dNDc3o1KpSEhIGJG++qjhdrtpbGykq6tL9iF4nEv73G437e3tNDc34+fnR2pq6hNRmyohhKpAIBAIBALBQ4AQqoJvA7fbjdPpxOv1Thi5e1Twer24XC45svooj+VBkMbrdDpRqVQjal6fBJ6MuLFAIBAIBAKBQPAEolKp8PP1SVX7HG0fVRQ+x2I/P79HfiwPgjRef39/dDrdYz/e0QihKhAIBAKBQCAQCASChwohVAUCgUAgEAgEAoFA8FDxrQlVKafaZrPJzZOlxWKx4HQ6R39ExuPxyJ+1WCwMDQ3Jnx0aGsJms+FyuUZ/7FvB7XZjtVqxWq3f2XcKBAKBQCAQCAQCwZPMt2Km5PV6sVqttLe309bWxsDAAHa7HbfbjdLXxDc8PJzo6GiMRiMGg0HOufZ4PJhMJrl5rtlsxmazyT2MNBoNBoOB8PBwwsLCCAoKwt/fH/U4TZa/Lm63m87OTmpra/F6vaSmphIZGfmlv8vhcMh24DqdDr1e/8i6rQkEAoFAIPh2EGZKAoFA8P/4VoSq2+2mqamJI0eOcPbsWTo6OnC5XHh9zY51Oh1RUVHk5OQwe/Zspk6dKltl22w2SktLOXToENevX8dkMuFyueQmuiqVCoPBQHR0NCkpKeTm5jJ58mRiYmLw9/f/xvoKeb1ebDYbFy9eZOfOnXi9Xp577jkWLFjwwE2FXS4XQ0NDNDQ0cPfuXaxWKxkZGUyePBmj0Th6dYFAIBAIBE8wQqgKBALB/0P1q1/96lej//HrIvU4OnLkCOfPn8dmsxEfH09iYiJBQUHYbDaqq6u5efMmtbW1+Pv7ExMTg16vx2azUVxczJ49e7h27RoajYbExETi4uIIDQ3Fz8+PgYEBqqqqKC4u5vbt2/T09GAwGDAajd+oI5bdbufWrVvs27ePnp4eJk+eTGZm5n37NXm9Xux2O/X19Zw4cYJPPvmEPXv2cPPmTbRaLRkZGYSEhIz+mEAgEAgEgicYaf7Q1dWF2WwmJiZGvNgWCARPLN+KUPV4PLS1tXH58mVaWlqYNm0aL7/8Mhs3bmT+/PkUFBQQGxtLR0cH165dY3BwkOTkZKKiovB4PFRXV3Px4kVMJhNr1qzhJz/5CatWrWLBggXMmTOH6dOnk56ejtvtprKykrt379LX10doaCiRkZH3FZIPitPppKKiggsXLuD1epk9ezZZWVn4+fmNXnUETqeT27dv89577/HZZ59x584d2trasFqtpKamUlBQQHh4+OiPCQQCgUAgeIIRQlUgEAj+H99Mnuw4KBQKuaY0PDyclJQU0tPTycrKYs6cOWzfvp0XXniB2NhYKisrKS4uZnBwEK/XK39Wp9MRHx9PTk4OaWlppKenk5uby4IFC9i2bRu/+MUveP7559Hr9Zw/f56DBw9SW1uL2+0evTtfma8SnXW73bS1tVFTU0N8fDybN29m+vTpD5wyLBAIBAKBQCAQCARPMt+aUB2NJD6lGtXIyEgKCgqYPHkyVquVhoYGBgYGxohM6XPSolKp0Ol0hISEMHnyZDZv3szKlSvxeDxcvHiRy5cv093dPWIb3zUajYZJkybxZ3/2Z/yn//Sf2LBhA4mJiWg0mtGrCgQCgUAgEAgEAoFgFN+JUB3Pr0mhUODv709QUBAejwer1Tpuyxqv1zvu5wG0Wi3p6eksXbqU9PR0+vv7KS0tpaOjY/Sq3ykqlYrExEQWLFhAQUGBbBQlEAgEAoFAIBAIBIL7850I1Ykwm8309vaiVqsxGo34+/t/6VRbPz8/kpKSyMjIQK1W09LSQldX1/fa81ShUKDVavH390er1X7pMQkEAoFAIBAIBALBk8x3IlSVSuUIsebxeOjs7OTy5cvcvn0bf39/UlJSCAwM/NLtZRQKBQEBAURHR6PRaOjr66OnpwebzTZ61e8cIVAFAoFAIBAIBAKB4Mvz5VThV8DtdtPf309LSwsNDQ2yo++OHTv4+OOPGRwcZNq0aUydOpXAwMCvJO60Wi0GgwGlUonNZsNsNo+bRiwQCAQCgUAgEAgEgoefb12oms1mbty4wTvvvMM//MM/8A//8A/88z//M5988gnd3d0sWbKEzZs3k5GR8bXbygw3bHK5XPT29lJXV0dNTQ21tbUPtNTX19PT0/O9pg4LBAKBQCAQCAQCwZPMtypUFQoFbrebvr4+ampqKCkpobKyksHBQVJTU9m2bRuvvfYa8+bNw2g0fum0Xwmn04nFYsHj8eDv709AQABWq5XCwkJ+//vf88Ybb/Cb3/zmvssbb7zBO++8w4ULFxgcHBz9NQKBQCAQCAQCgUAg+A74asrwAfF6vej1erKysli7di3PPfcczz//PK+88go/+clPeOmll5gzZw6hoaFfyxXXbDbT2dmJ0+kkJCSEkJAQFAoF3d3dIqIqEAgEAoFAIBAIBI8Y36pQBdDpdKSnp7Ny5Uq2b9/O1q1bWb9+PfPmzSMpKUmuLf2q2O12Wltbqaurw+PxEBMTQ3h4OMHBwRQUFLBlyxaef/55tm/f/kDLpk2bmDp1KgaDYfRXCQQCgUAgEAgEAoHgO+CrK8QHRKFQoNPpCA4OJjQ0lNDQUIKDg/H390etVo9e/Uvh8Xhob2/n2rVrNDQ0EBwcTE5ODpGRkQQEBJCTk8PKlStZu3Yta9asue+ydu1ali9fTk5ODnq9fvTXCQQCgUAgEAgEAoHgO+BbF6r4UoC/KpJB0micTidtbW1cuHCBM2fOYLPZyMvLY+rUqYSGhqJUKvHz8yMoKOhLLYGBgfj5+Y2J8kr7Md6+CAQCgUAgEAgEAoHgm+M7EapfFa/Xi9PpxGw2Mzg4yODgIH19fXR0dFBWVsa+ffv46KOPqKmpITMzk+XLl5ORkYFWqx29qa+N2+1maGiI7u5uurq6xix9fX3YbLavJcoFAoFAIBAIBAKBQPAtClWv1ztCtH0ZASd91mKxUFZWxokTJzh+/DhHjhxh9+7d/OEPf+Cf/umfePvtt6muriYvL49t27axYMECQkJCRm/uayHtd09PD+fPn+eTTz7hgw8+kJcdO3bw4YcfcuTIEWprayfs3/plxi8QCAQCgUAgEAgETzKqX/3qV78a/Y9fF4/HQ3d3N8XFxXR2dpKWlsa0adOIiIgYveoY7HY7jY2N3Lp1i4aGBlpbW7l58yYXLlzg/PnzXLhwgWvXrtHU1ERYWBhr1qxh27ZtzJs3j8jIyK/lHjwal8tFTU0N169fp7W1ldbWVkpKSrh+/TrXrl2Tl9u3b9Pd3U1sbCzJycljIrpdXV3cvHmTzs5OMjIymD59OmFhYSPWEQgEAoFA8GTj9Xqx2+10dXVhNpuJiYnBaDSOXk0gEAieCBTebyHU53a75frR+vp6MjIymDdvHtHR0aNXHYPNZqO8vJwvvviCmzdvMjAwIEcpdTodoaGhJCYmkpKSQkZGBikpKYSHh6PT6cbUlX4dvF4vDoeDsrIyTp8+TXNzsxwVHX3I1Go1cXFxzJ8/n/z8fPz8/Eb8vbW1lXPnzlFfX092djbz589/INEuEAgEAoHgycHj8TAwMEBpaSmdnZ1MmzaN5OTk0asJBALBE8G3IlQBHA4HQ0NDOBwOdDodAQEBaDSa0auNwePxYLPZGBgYYGhoCKfTidvtBkClUqHT6fD398ff3x+9Xo9Go/nWDI68Xi9WqxWTyYTD4Rj9ZxmFQoFGoyEgIAB/f/8x++N0OuVt+Pn5ERAQ8LUdjwUCgUAgEDxeCKEqEAgE/49vTagyKvI4Wrzdj9G75fV6R2zjy27v6zB6Xybifvs0egwCgUAgEAgEEkKoCr4NBgcHaW1txel0Eh0dTWho6DdaKif49nA6nbS3t9Pd3U1wcDAJCQkPFPh7XPhWhapAIBAIBN8XXq8Xs9lMb28vdrudoKAgQkJCxvgIuFwuWltbsVqtI/5dQqlUEhgYSGho6JjPCgTfJEKofn+43W56enqor6+nvb0dpVJJXFwcqampBAcHj179nng8Hvr6+mhoaKC9vR2Hw0FgYCCJiYnExsaOm30nfc5kMtHY2Cjfk/R6PQkJCcTHxxMQEPCly9wsFgvnz5/n9OnTREREsG7dOtLT0+XMPq/XS39/P9XV1bS1tQEQFxdHcnIyRqPxSwtaj8dDT08PdXV1dHR0oFQqiY2NJTU1lcDAwAn33+1209XVRUNDAx0dHbjdbkJDQ0lJSSEmJuYbFWednZ3U1tbS2dkpl+8lJyffc/9G4/F4MJvNE3b98Hq9KJVKwsPDCQoKGpNJ6XQ66erqora2lq6uLjweDxEREWRnZxMaGiqv73Q6uXLlCgcPHkSn07F161ays7O/0ePxMCOEqkAgEAgeSywWCydOnODcuXPYbDZmz57NypUriYqKktfxeDy0t7fzu9/9joaGBpxO55hsoICAAGbMmMHatWuJjY2V/yYQfNMIofr9MDg4yJ07dzhz5gw3btygs7MThUJBTEwMc+fOZdWqVSPE3US4XC46Ojq4ceMGly9fpqKigu7ubpxOJ3q9npSUFObPn8+8efNISkpCp9OBT6T19vZSXFzMxYsXKSsro7OzE7vdjlarJSEhgdmzZ7Nw4UIyMjLQ6/Wjv3pcvF4vd+7c4b333qOmpobly5fzzDPPEBsbi1KpxOFwUFpaytGjR7l27RpdXV14vV6ioqKYM2cOy5YtIycn54G/b2hoiNu3b3PmzBlu3rxJR0cHCoWC2NhY+f6bnp4+5oVfd3c3V69e5cKFC5SXl9Pb24vb7cZgMJCRkcGSJUtYuHAhYWFh4wr8B8VisXDz5k1OnjzJrVu36O7uloX03Llzeeqpp8bdv/GwWq3cvHmTY8eO0djYOObZ4fV6ZWE5f/58goODUSgUeL1eOjo6uHz5MoWFhVRWVjI4OIjH4yEwMJCcnBxWrlzJjBkzZCO1qqoq3nvvPa5evcqaNWt4+eWXv/axeFT4Vlx/BQKBQCD4PnG5XNy4cYN3332Xo0ePUltbS2hoKFOmTBnRxszpdFJVVcXrr7/OjRs36O7uprOzk/b2dnnp7+8nLCyMvLy8b7wFmkAwHK9w/f3OMZlMFBUV8fHHH3P27FnsdjuxsbHodDpqamooKSnBarUSGxtLSEjIPSNuAwMDnDlzho8++oirV6/idrvlLI6uri4qKiqoq6vD4/EQGRlJUFAQKpUKs9lMUVERH374IWfPnsVqtRISEoJer6e/v5+qqiqqqqqw2WyEh4cTEhJyX9GMb3+OHz/OuXPniI2NZdWqVaSlpaHVarFarRQXF/Puu+9y4MABnE4nSUlJ+Pn5UVtby507d7BYLISHhxMaGnrfCJ7VauXy5ct88skn8nGUIqF1dXXcvXsXk8lEQkLCiOPY19fHF198wc6dO7l9+zb+/v6kpaURERFBf38/t27doqqqiqCgIOLj4x9YNI/G6XRSWFjIBx98wLlz5/B6vbJgl/bPYrGQkJCA0Wi853kGMJvNXLhwgY8++oiSkhK6urpGPDva2tro6elh8uTJpKWlyVH0trY2Dh8+zM6dOyktLSU8PJysrCwiIiJob2/n+vXr1NXVERERQWRkJH5+fvj7+2OxWCgpKaG1tZXU1FRiYmIe6Bp41HmoharT6WRoaAiz2SwbFgkEAoFAcC88Hg9NTU18/PHHXLx4ka6uLlwuF+np6cyePXtEezC73U5xcTG7du0iPDycLVu2sGDBAqZPn8706dOZNm0a06dPp6CggNTU1K88SRIIHgQhVL9bPB4PFRUV7Nmzh0uXLhEZGcmGDRtYs2YN+fn56PV6KioquHv3LiEhIaSkpEyYtotPrFVXV9PT00Nubi6rVq1i8eLFzJgxg9TUVGw2G1VVVQwODhIRESELL5vNRkNDA01NTaSmprJq1SqWLl3KzJkzycrKApBTRI1GI4mJiQQGBk64HxJ3795l//799Pb2smjRIubNm0dISAhut5umpiY+/fRTDh06RFRUFFu3bmXt2rVMnz5dFqv19fXo9fr7psV6vV6qqqr4/PPPuXjxIjExMaxbt47Vq1fLx7Gqqorq6mqMRiNpaWkYDAYArl+/zscff0xVVRVTpkxh48aNLFu2jIKCAuLi4ujp6eH27dsMDg4ydepUwsPDJ9yPe1FTU8O7775LYWEhqampbNiwgRUrVpCfn49Go6GqqoqGhgaCg4NJT0+/771+cHCQS5cuUVRURGpqKuvXr2f+/Pnys0NaZsyYQUxMDFqtVk7j3blzJ3V1dcydO5etW7eyePFipkyZQmJiIg0NDdy5cwedTkdaWhphYWHodDrUajUtLS3cvn0bg8FAXl4e/v7+o3frseOhFaoeXy/WoqIiiouL8ff3Fy1dBAKBQHBPvF4vJpOJgwcPsn//fkJCQlCpVFgsFnJycpg3bx6hoaHyulIU4NSpU8ydO5cf/vCHzJs3j7y8PPLy8sjPzyc3N5fk5OSvVB8m+H6RznF3dzc9PT0oFIoxLeS+DtL2Ozs7GRgYQKlUfq1uBEKofrf09/dz5swZDh8+jNfrZf369Tz99NPk5OQQHx9PZGQkXV1dFBcXA5CVlUVkZOSEkSyFQiGn+M6bN49p06aRmppKcnIyqampaLVaGhoaaGlpwWg0kpGRQWhoKEqlEj8/PxISEpg7dy4zZ84kPT2dpKQk0tLSCAwMpKmpidraWvR6PRkZGURERNyzftThcFBYWMipU6eIjIyU05e1Wi0mk4krV66we/duTCYTzz33HBs3biQrK4vExEQiIyPp6emhrKwMh8NBSkoKsbGxE6bE2u12jh49yr59+1Cr1axdu5a1a9eSk5NDYmIioaGhdHZ2ylHaqVOnEhkZicfj4fDhwxw9epSwsDA2btzIkiVLSE5OJioqioiICFwuF7du3aKpqYm5c+eSnJw84fGfCJfLxYEDB9i1axd6vZ6tW7eyatUqsrOzSUxMJDg4mI6ODsrKyrDZbBQUFNxXEPf09HD58mXq6upYsmQJzz//PLNnzx7x7MjLyyM2Nha9Xo9SqaSnp4cvvviCEydOEB8fz2uvvcb8+fOJi4sjMjKSxMRE+vr6uHnzJna7nby8PBITE9FoNPj5+dHX18f169flYxgWFnbPfXwceGhH5/F46O3t5dKlS3zxxRfU19ePXkUgEAgEghG43W5u377NwYMH8Xq9LFy4kJSUFLxe74j6IQmXy0V7eztut1ueHIWHh49YwsLCRFuxRxSn00lLSwtnz57l6NGjlJeX43K5wCcK3W63vHg8nnGvkXvhdDppbGzk1KlTHD9+nOrq6nu2sxM8XLS3t1NSUkJPTw9JSUlMmzaNuLg49Ho9gYGBpKamMnv2bMLDwykvL5fTbye6TnQ6HSkpKcyYMYP09HSCg4PlloqRkZHk5eWRnp4uX5f9/f243W60Wi3x8fHMmDFDNtORPhcaGkpeXh5ZWVm43W5aWlro7u6+73XW29tLZWUlZrNZNmPy8/PD6/UyMDDArVu3aG5uljNN4uLi5NaPGRkZTJs2jbCwMJqbm6moqGBoaGj0V8h0d3dTXFxMR0cHqampFBQUEBsbi8FgkI/jrFmzCAwMpLS0lOrqaqxWK263m87OTvr7+wkKCiIqKorAwEC0Wi1arZbg4GDZRGpwcBCLxYLb7Z7w+I+HNN6LFy/S3t5OTk4OU6dOJTo6Gn9/fwICAsjMzGTmzJn4+/tTUVFBRUUFNptt9KZGYLFYGBgYQKvVEhsbS2RkJGFhYWOeHZJIxVfD29nZidVqJSwsTI5UazQatFotISEhJCYm4ufnh8lkko8RgL+/P6mpqcTHx9Pc3Ex5efl9r4HHgYdWqOJ7APT19dHZ2YnFYhn9Z4FAIBAIZDweD62trezatYva2lrmzp0rm1h4PJ7Rq4PvOdPZ2YnX65WzdhwOhzw5UCgU8iJ49HA4HLS0tFBUVERhYaE84bZYLDQ2NnLjxg2uXr3K1atXuX37Nu3t7dhsNlwuF06n856Ly+XCYrFQV1fHpUuXuHTpEnV1dRO6RwseLjweD52dnTQ2NqJUKmV3WSlqqFAo8Pf3JyUlhaioKFpbW6mvr8disUwolBQKBVqtFr1ej1qtHnHfUPrcwwMCAlAoFLhcLll0SeVter1+TERe4TN0k1JvpWtvon2QaG9vp66uThbBQUFBKJVK2bipoqICi8VCeno6sbGxI8rr9D6n4ZiYGMxmM01NTZjN5gm/s7m5mYaGBtRqtSymJKMohUJBYGCgHI2Wam4HBwcBMBgM6HQ6TCaT7NAufY/D4aC3txebzUZERARGo3HMcb0fHo+HxsZGqqqqUCqVZGVljTnPRqOR9PR0wsPDGRwcpKqq6p6/Y68vc6e/vx+VSoW/vz9erxenz1Bp+HNj+L5qtVoMBgNKpZL+/n7a29txOp3yNm02Gx0dHXItslTDjG8/IyMjSUlJwWQyPTEvxR5qoSoQCAQCwYPg9bWiOXr0KMePHyclJYVVq1aRlJSEUqm8p1CVJgsNDQ2cOXOGEydOcOXKFWpraxkcHJRFq+DRw+tLzR0cHKS3t5e6ujpu3brF1atXOXr0KB9//DE7d+5k586dfPrpp5w6dYrr169TXFz8QMvt27epqqqiq6sLk8mExWKRI7aChxun00lPTw89PT34+fkRHR0ti0gJpVKJ0WgkNDRUTvG2WCwT3k/uh9lsxmw2o9FoMBqNsmi5H2azmaGhIdRqNUajkcDAwPtmeHR3d9PV1UVAQABRUVFyyrs07vb2dhQ+R97R41YoFISEhBAWFobL5aK3t/eeAr2trY3u7m4MBgNRUVEjBBY+gRYREUFoaChut5u2tjbMZjNqtZrs7GzS0tLo6OigsLCQmzdv0traSmdnJ6WlpVy6dAmXy8WCBQtISkr60n41Ho+H+vp6+vv75QitJNolpPMh7V9LSwt2u33EdoYjuXP39vZiMpkoLy/n1KlTnDp1imvXrtHQ0IDVah1znYSEhJCdnU18fDyNjY0cOXKE27dv09XVRXd3N1euXOHChQtoNBpmzpw5pmeq0WgkPj5ebqkmhOr3zPA3EV/m7YlAIBAIniwcDgfFxcV88sknqFQqNmzYQF5eHjqdbsLJlcfjwel0Yrfb0el0nDlzht/+9rf8n//zf/i///f/8u6773LmzBlaWlqE+HiEkeYSNpuNsrIyPv/8c1mUlpSUcPfuXcrKyrh58yZHjx7lo48+YseOHXzwwQf3XHbs2MFnn31GUVERJpNJzFMeMex2O/39/QwNDclpplIUUELhi6oGBwejVqvlaPxoAfIg2O126uvrZYOipKSkEf0yJ8LtdtPQ0CBHR6UShYnqRRkmpEwmEwaDYUQPaKcvW9FsNqPX6yfsD+3v74/BYMDr9TI0NITJZJrwPtjb28vQ0BB+fn5ymcRowe/n5ycLWKn3KEBBQQErVqwgJCSEwsJC3nvvPT755BM+/fRTduzYwbVr15g0aRLPPPMMcXFxDyTsh+P1euV0W+lc6nS6McJcp9PJ/XL7+vrkSOd4uN1urFYrDocDk8nE8ePHeeONN/jHf/xH/vmf/5n333+fixcv0tPTM+KY+fv7U1BQwKpVqzAYDBw6dIjf//73fP755+zatYu33nqLyspKFi5cyPLly4mJiRkh+KXzpVKp5GP+Va7FR4kvd7a/JbxeLy6XC4fDgcPhkNNqhuehu91unE6nvI603uN+ggQCgUBwb1wuF83NzezYsYPa2lrWrVvHsmXLZHffiYSq19eQferUqaxYsYK8vDx5IlRRUcFHH33E66+/zoEDB2hra5twO4KHH4VCgdvtpq+vj7q6Ourr6+nt7ZXnGh6PB7vdTmdnJ3V1dVRXVz/QUldXJ/fJlL5H8GjgdDqxWCzY7XZUKhV+fn5jzIkUvpRcPz8/1Go1drt9RGrqg+L1emltbaWoqIimpiZiYmLIycnBaDTe95rp7e3l2rVrVFZWEh4eTm5uLuHh4WP2dThut5uhoSFsNpssHqX1pZR1t6821t/ff1yxrNFoZOFut9ux2WwTZpdYLBZsNhtqtRqtVjuumJSOsVKpxGKxyL+Z6OhoVqxYwbx583A6nZw8eZK33nqLf/3Xf5Xb5syfP5/Jkyff14l3PLy+NF2n04lWqx2TWi2hVqvl7ZvN5vvqi5CQEKZPn86iRYuYPHkyUVFRuFwubt68ye9//3v+7//9v5w9e5a+vj55WwqFguTkZFauXMns2bMZHBzk0KFD/Nu//Rv/5//8H44cOYJOp2Px4sVkZmbiP8phWqVSYTAY0Ov1mEwmuf/q48zYK+l7wGq10tjYSFlZGaWlpZSWllJWVkZ1dTXd3d2YTCaam5tH/P3OnTtUV1fT19c34Q9HIBAIBI83Ho+Hnp4ejh07xuHDh5kyZQrbtm0jLi4OlUo17oREQqlUEhERwSuvvMJ//s//mb/5m7/hv/yX/8Jf//Vf8+KLLxIfH8+dO3fYtWsX58+fv6+5huDhQxIUXq8XrVZLQkIC8+bNY86cOSQlJaHT6VCpVPIEMDMzk3nz5rFkyRIWL17MokWLJlwWL17M/PnzycjI+EoTaMH3i8fjkV9SKBQKlErlhPcL6d+9E5iy3Q+TycSFCxe4ePEifn5+zJo1i5ycHLlFy0TYbDaKioo4c+YMLpeLadOmMXXqVDnyNxEOhwOLxYLD4UCtVqPT6WTx6PV68fiMw5RK5T3HzbAx32vcw7d3r20phmVKSttzOp10d3fLxkQJCQmy67IkyG7evMndu3cZGhq6536Mh9dnmuYdVjv6dVGr1eTm5vLDH/6Qv/mbv5GfH//xP/5Hnn32WUJCQrh06RIffPABd+/eldOIvcNcyAcHB+Ua6Pz8fNncqa+vj0uXLslGWMPHq/DVQPv5+WG327FarV/6eDxqPBRCtaWlhY8++oi/+7u/42//9m/51a9+xa9//WvefPNNioqKqK2t5ZNPPuFv//ZvRyxvvvkmN2/eFEZLAoFA8ATi9dWl3rhxgx07duDxeNi8eTORkZFYrVYGBgYYHBzE4XDg9XrlNK2hoSGcTidKpVJ2UszMzCQtLY2srCwWLVrEK6+8wmuvvUZaWhplZWWcP3+e1tbW0bsgeMhRKBTyJFun0zFp0iSeffZZnn/+eVatWkVeXh7Z2dlkZ2czY8YM1q9fzwsvvMBLL73ED37wA15++eV7Ls8++ywzZ84kMDDwvpN5wcOFJOA0Gs0IMTMaj8eDy+XC4/Gg9bnRfhmx43A4uHLlCnv37qWtrY2ZM2eybNky4uLixo1kSrh8bVk+++wz7t69y+TJk1mxYgXJycn3rdOU9lkK5AwXaCqVSn5BI4n18cbt9rlhS+JouNgdjVarRa1W4/F4JozweX1mQx6PB52vL6jb7ebatWu8++67XLp0iUmTJvHzn/+cX/7yl/zyl7/kpz/9KYmJiZw9e5bf/OY33L59+561o+Oh8LWkUqlU9/yNenylINL6E40V30vO4OBgkpOTSU9PJz09ndzcXJYtW8ZPf/pTXnnlFYKDg7lw4QLXrl2To6o2m40rV67w/vvvU1JSwsKFC/nP//k/88tf/pJf//rX/Pmf/zn+/v7s3r2bP/7xj5SVlY0Zr/RywTvshcPjzMRn4TtEqVSi0+nQ6/UYDAYCAgIICAiQ3c+kdIHhfzMYDHIqxpe5YQgEAoHg8cDj8dDR0cGBAwe4ffs2AOfPn+cf//Ef+du//Vt+/etf80//9E8UFxdjtVq5du0ab7zxBm+99Za8vkKhQKVSyQ9/6XkTFRXFwoULmT59Oh6fa6QQqo8eSqVSbjUitb+Ii4sjOTmZ5cuX8yd/8if87Gc/42c/+xmvvPIKc+fOJTExkaioqPsukZGRREVFER0dTUhIiJySdy/xIXh40Ol0BAYG4ufnh9vtHpGOKuH1ObGaTCYcDgf+vpYx9xIxwxkuxK5fv05eXh7r168nOzv7nlF4j8dDWVkZ77//PqdPnyY5OZmnn36agoKCMcZH46FSqeT5M8MinvgEumTGZLPZGBoaGrf2VIrYKRQKef490bUtzdmdvpr/0WJVehFgNptxu90EBQWh0+no7u7m8OHDFBYWkpCQwJYtW1ixYgX5+fnMnTuXF154gVdffZXIyEguX77MsWPH6OjoGLP9e6HwufpqtVrsdjsOh2PczzudTsxmM4Bck3wvpOeF9OxQq9X4+/sTHR3NmjVryM3NxeFwUFtbS09PD263m7q6Oo4ePcr169dJS0vj1VdfldN8586dy09/+lN++MMfEhgYyLFjx7h48SK9vb0j9ld6uaBSqZ4IDfRgv7Rvmfj4eF566SX+23/7b/z617/m17/+Nf/f//f/8ed//ufMnj2btLQ0tm/fLk88fv3rX/Pf//t/5y/+4i+YPn06/v7+ozcpEAgEgsccj8eDyWSiu7tbnjyePXuWgwcPsn//fg4cOMDx48dpamrC4XBQX1/PqVOnOHfuHC0tLaM3NwJpchMTE4PBYMBms92zXYHg4USn05GRkcG6devYvHkzBQUFspg0Go2kpqaSkZFBRkYGiYmJBAYGyinjD7Lo9XpycnJ4+umn2bBhA5MnT75vOqfg4cDPz4/Q0FACAwOx2+309fWNiV55PB6Ghobo6elBqVQSEhLywELV5XJRVFTEG2+8wenTp8nJyWHbtm3MnDmToKCgCQWGx+Ph7t27/O53v+PQoUMkJSXx/PPPs3jxYkJDQx/ouzUaDf7+/mi1WhwOxwgHWq1WK4/bYrHQ1dU17r3NZDIxMDCAUqkkKCgIg8EgC9/RhIWFydsbHBzE6WvTIuFyuejv76e/vx+vrxWYXq+nrq6O0tJS3G43BQUFFBQUyAZTOp2O2NhYFixYwMyZM1EoFFy/fp2urq4vFUVUKpXExMTg7++PyWSip6dnjCOv9EKir68Pha8NzP2i1hOh8Dkpx8XFodVqMZlM2Hy9d+vr6yktLUWr1VJQUEBmZqZ8XHU6HeHh4axdu5aCggLsdjvl5eV0dHTIkXGvL3VYMq4yPKBr9KPMQzE6nU5HVFQUKSkppKamkpKSQkpKCvHx8QQHB6PX6+XeQdIi9WmS+koJBAKB4MlCmoC8+OKL/PKXv+Rv/uZv+MUvfsHPf/5zfvGLX/CXf/mX/OQnP2HSpEn4+fmRn5/Pq6++yksvvUR2dvbozY3B5XJhNpux2+1ofb0RBY8WKpWKyMhIZs+ezVNPPUVaWpo8Z1D4ounSorxPfd14qNVqoqOjmTdvHosXL/5K7TME3w+S8IyIiMBisdDc3MzQ0NCIdTweD11dXfT19REZGUliYuIYg5vxsNvtXL58mTfeeIOzZ88ydepUXn31VRYsWEBISMiE81an00lJSQlvvfUWhw4dIjExkZdffpkVK1YQERExoVAcjVqtJigoCH9/f7k9kxQtVqvVhISEkJiYiFqtpqmpacy4vV4v3d3ddHR04OfnR0xMzD3vfwkJCURERDAwMEBjYyPd3d0jorR2u52mpia6urrQ6/VkZGRgNBrp7e1lcHAQtVpNcHDwmJcASqWSgIAAIiIi0Gq1DAwMfGkzK6VSSWpqKuHh4fT391NXVzfC4AifGVRzczOdnZ1otVpSU1PvOd77YbVaZZfkoKAg9Ho9CoVCNkDSarVylHf0tSRlaWg0Gsxmsyxy8V0fQ0ND2O12goKCxrTZeRx5aEY3+i2ltDzo3wUCgUDwZKFSqQgLC2PRokVs27aNrVu3snXrVp599lm2bdvGli1b2LhxI6mpqXJkbe3atTz11FMkJiaO3twIXC4X5eXllJWVAZCUlERsbOzo1QQPOQqfa2tAQABGoxHdqPYj3wQajYagoKBx214IHm6io6NJT0/H6/VSWVlJdXW1LNo8Hg/9/f0UFxfT1NQkR98l0TEwMEBVVRW1tbUjTH6sViuXL1/m7bff5tKlS0yfPp0f/ehHLF68+J5uvXa7ndu3b/POO+9w5MgRUlJS+OEPf8jq1auJjo6+byrqcBS+jJDg4GA568Th67kpCfT8/HwCAgK4c+cOtbW1IwRRV1cXZWVlNDc3ExYWRkZGhlyHbbFYqKiooKKiQk6VjYuLIzMzE7VaTVVVFfX19SOi04ODgxQXF9PT00NKSgoZGRkYDAYMBgNarRar1UpHRwf9/f0jBK7HV9fZ09OD0+kkKioKg8GAQqGgp6eHixcvsnfvXi5fvkxPT8+4Kb3SC02pXVlpaSnNzc0j0rw7Ozu5ffs2fX19JCQkMGnSJDlbc3BwkLKyMurq6saYG42H2+3m+vXrVFRUoNFoSElJkVvK6HQ6dDodZrOZzs5O+ZwMp7e3l46ODux2uxz5lsTo0NAQHR0dKBQKIiIiHuilyaOO6le/+tWvRv/jw4DH46Gzs5Pr16/T3d3N9OnTmTRp0ujVBAKBQPAEI9WUSrVj/r7ef9L/u91uzpw5Q1VVFfn5+SxbtkzuTWcymbh69SplZWUEBgaiUChwuVz09fVx+fJlPvzwQy5dukRCQgKbN29m1qxZIlr2iPJtv+D+prbv9Xqx2+10dXVhNpuJiYnBaDSOXk3wDaHVarFYLNTW1tLU1ITX6yUyMpKgoCAGBwc5f/48u3fvpqenhzVr1vDUU08REhJCf38/Z86c4eOPP+bWrVtoNBrCw8NxOp2yWc6ZM2eIjo5m7dq15ObmolAo6O/vp7e3l97eXlnkSbWixcXFfPDBBxw+fBh/f39WrVrF9OnT0Wg0DAwMyJ8zmUx4PB40Gs09o2kWi4XS0lIaGxuJi4sjNzeXwMBA8Ik3j8dDZWUlFRUVeL1eYmNjCQ4Oxmw2c+7cOfbv309vby/z589nxYoVxMTEYDabuXDhAh988AHnz5/HYDAQGRmJwWDAbrdTVVVFTU0NKpWK6OhogoOD5eP4+eef09XVxTPPPMNTTz1FcHAwKpWKqqoqqqqqsFgsBAUFyWnBkg44ffo0e/fuxWQy8eyzzzJv3jwCAgK4desWH330EadOncLPz08W0+P9BtVqNS6Xi5KSEmpqavD31ZIGBgbK53L37t2YTCbWrVvHU089RVBQEG63mwMHDrBz505KSkoIDAwkPDyczs5O7ty5Q2dnp3wOHA4HXV1dnD17lnfeeYebN28ye/ZsNm/eTFpa2ohrrby8HIvFQmRkJJGRkWi1Wnm8u3bt4siRI/j5+fHMM88wY8YMWZw3NDRw/Phx2traWLp0KdOnT/9WXr49TDz0QrWoqIiuri5mzJhBbm7u6NUEAoFA8IQzXCSMXkwmEydOnKCsrIzs7GzmzZtHeHg4breb1tZWduzYwa5du7h9+zbXrl2jsLCQY8eOcejQIW7cuEF4eDhbtmxhzZo1hIeHjzsJEgi+KYRQ/W5RqVTo9XrsdjsNDQ1UVlZSW1vL3bt3OXfuHEePHqW+vp45c+awdetWsrKy0Gq1tLS0cPjwYQ4dOkRjYyNhYWHExcXR0NDAjh07OHbsmCxiBgYGuHXrFmfPnuXUqVOcPn2a06dPU1FRgU6nw2g00tjYyMcff8yBAwdobm6GYULz3LlznD59Wv5sSUkJCoVCbmcyEWq1moaGBkpLSzEYDEyaNImwsDCUw0zjPB6PPN76+nrKy8s5ffo0hw4doqGhgalTp/L000+Tl5eHv78/3d3dHDx4kH379lFWVkZMTAzZ2dkYjUYCAwOx2WzU1NRQUVEhb/fMmTMcPnyYuro6Zs+ezfPPP096ejoajUaOTnd2dlJdXU1tbS11dXWUl5dz5coVjhw5wtGjR+no6GDx4sVs27ZNdj0+f/48Bw8exGQyMX36dPLz82VBNxqFL8JssViorKyksrKS+vp6ysrKOHHiBEeOHKG9vZ25c+eyfft2UlNTUavVmM1m3nnnHfk6SEpKIi0tjYqKCj799FOOHTvG1atX5WfHkSNHOHjwIMXFxeTk5MgGbVKKrpRO3NraKot66ThdvnyZ/fv3c/DgQWw2G+vWrWPt2rUkJCSg0WjweDyUlJRw6NAhdDodmzZtkvfzceahFqomX/9UhULBjBkzSEtLG72aQCAQCAQTYrPZKCsrw2KxMG3aNGbMmIHRaJRNKSorKykvL6ehoYG6ujpqampobGzE5XKRl5fHpk2bWLVqFYmJiROm7AkE3xRCqH63KHyGWFK9YH9/P42NjfJ9wOv1MmvWLLZs2cL06dPlNMyhoSGqq6tpbGwkICCAgoICUlNT6ejo4ObNmwwNDREaGipHGgcGBujr65MNhfr6+lCpVKSlpREbG0tPTw/Xrl2jp6cHo9FIUFAQLpdL/pz02d7eXrxeL4mJiaSnpxMQEDB6SDLSeKT+owkJCSQkJODn54dCoUCn0xEWFoZer6evr4/GxkZZKHo8HmbOnMnTTz/NrFmz5Lpaq9VKTU0NVVVVaDQa5s2bJwtEf39/QkND0Wq19PX10dTURG1trXwcZ8+ezbPPPjsiQqhSqQgJCSEkJAR8aa/S8a+srKSlpQW9Xs/SpUvZsmWLLJhtNhsnT57k4sWLpKamsnLlSjlqORF+fn5ERESgVqvp6ekZcZ7VajXz589ny5YtFBQUyIZoXq+X69ev09jYiNFoZP78+WRlZWE2m2WhWVdXR21tLdXV1bS0tKBQKJgzZw7PP/88S5Yskb8TnydPaGio/Azq7OykoaFBFveNjY2Ehoaybt06NmzYQFZWlpze29PTw9mzZ7l8+TKTJk1iw4YNhIaGjivMHycU3vslW39PeDweBgYGqKysZGBggKysLJKSkkavJhAIBALBhFgsFm7cuEFzczNJSUnk5uYSFBQ0QqiWlpbKwsDtduPn50d4eDjp6elkZGSMmGgIBN8m0tyntLSUzs5Opk2bRnJy8ujVBN8gXp/ja0tLC3fv3qWurg6TyYRGoyEqKoqcnBwyMjIIDg4eUStYWlpKSUkJGo2G/Px8kpOT6e3tpaysjJ6enhHbH2+qHRISQnZ2NvHx8QwMDHDnzh06Ojrkdcf7nNfrJTAwkMzMTLnO815UV1fz9ttvc+XKFZYsWcKLL75ISkoKKl9PUafTSVtbG3fu3KGmpgaTyYRKpSIqKors7GzS09MJCQmR739SRPLq1au4XC7mzJlDdna2LH4dDgdNTU2UlpZSX1+PyWRCq9USFRVFVlYWmZmZI44jvmu+r6+P2tpaampqaG9vx2KxoFAoCAwMJDY2VtYAksBtbGzk7//+7zl16hQbN27ktddeIyUl5b73aafTSUNDAyUlJTQ0NDA0NIROp5Mjw1L6sLR/Xq+Xy5cvc+PGDQICApg9ezYpKSmYTCZZqErPDo/Hg7+/P5GRkWRlZcnXzOgXnG63m56eHmpqaqiurqazsxObzYZSqcRoNBIXF8ekSZNkAyspTfv69ev89re/paqqitdee42tW7fKqdyPMw+tUMV38Ur9jrS+ZsICgUAgEDwoXl+EyuVyoVar0Wq1IyYhUt8/q9WK3df/T+Nr7eDn5zdifYHg20YI1e8Hr6/Pp81mk52+VSoVBl9v3NH1oB6fyY/ZbEbh6zOq0+lwu904HA65nci9UCqV8txWmu+63e4x4nQ0SqUSjUYzZp/Gw2KxcOzYMXbu3Ilareb5559n6dKlBAUFyeu4XC4sFgtmsxmHw4Ha1w9Ur9ePuf9J91OTyYTX65X7oQ6P6rlcrhHHUa1WYzAY5PvpeBFAj8cz4l5ss9lQKBSy/4BOp0M9rGfo+fPn+fu//3tsNhs/+tGPWL169QNnHkj7NzQ0JI/3XvsnuSar1WoCAgLQarV4vV4cDgd2ux2bzYbd50Ss1Wrla2G8bUlI47XZbFgsFtlUSfJW0Ol0qHxtsvCZW3366afs3r2b9PR0/uIv/oLs7OwnQhc91EJVIBAIBIIvgzThc7lceDweVCqVPBmcaNLAKNHqdrtR+hq4i5ekgu8SIVS/f4ZHMhXDDLIkEep0OlH43KTVajVKpfK+gnE0Xq8Xl8uF0+nE5XKhUCjk+83oCJyEx+ORl/Gm7gqFAqWv/lTaZ6/XS0NDA7t27eLatWtMnz6dzZs3k5SUhEqlwuVy0draSnl5OWFhYaSlpckRxdHjltx4h4vk+91Tpf1UKpXyy4Dh2xrv/uz1evF4PPKxH/0dHo+HvXv3snPnTrk3bXZ2tpz2K32PdGyl75HE3/DtSNzv/A3fH3zHRPr88H+XzoGEdI6lFxDSeIefI0m0NjU1UV5eLtfBSvW7breb4uJiduzYQVtbG1u2bGH16tVPRDQVIVQFAoFA8DjgdDrlOqumpia5zYG/vz+xsbGkpqYSHR09rkOix9crsaamZkRPwcDAQBITE0lNTSUsLGzCCaRA8E0hhOrDh9frZWBggLq6OrkHp1KpJDIykrS0NOLi4jAYDPcVOxI2m02uTWxtbcVkMqH0tYxJSkoiOTl5TMqo1+uV6zelHqWjp+9KpZLExESSkpLkukZ8brR3797lxo0b6PV6Zs6cKdfc9/T0sHfvXo4fP85TTz3Fhg0biIyMRKVS4Xa7GRgYoKGhgfr6enncUllEYmKiLKbuhccXfZbG3N7eLkdkAwICSEhIkO+x94pCSrhcLi5fvszdu3fJzs4mPz9fLuew2Wx0dXXR1NREW1vbiO+R7uUhISFoNJr7fs9EWCwWmpqaaG1tRa1Wk5SURExMDBqfI7zX99Kzu7ub+vp6WltbGRwclPcjLi6OlJQUIiIi5P2w2+0UFRXxL//yL6SmpvLyyy+TkZGBTqfD6XRSWlpKUVERgYGBLFy4UHaufxIQQlUgEAgEjzQOh4O6ujpOnDjBpUuXaG5uxmQy4XA4UKlUJCQksGDBApYvX86kSZNGNHJ3uVw0Nzdz9OhRzpw5Q2trq5wCrNVqSUlJ4amnnmLJkiXCUEnwrSOE6sOFVE948eJFjh49KhsTeb1ewsLCmDVrFitWrGDKlCkYjcb7ih+r1So74RYVFcn3G6/Xi16vJysri5UrV7Jw4UIiIiJk8etyubh69Sp79+7l9u3bWK3WMd+lVqvZsGEDmzZtIjY2doRwdjgcI+oodTodNpuNoqIiXn/9daxWKz/96U9ZunQpAQEBeDwe2tvbuXTpEqdOnaKsrAyTyQSA0Whk1qxZPP3000yZMuW+dbLSmI8fP05RUZFcg+p0OtFoNKSmpvLUU0+xdOlSUlJS8PPzG72JEXi9XoaGhnA6nej1enQ6HUqlksHBQdkl+fr167S1tWE2m+XvycjIkO/lSUlJDySKR+N2uykpKWH//v1cuXKFsLAwNm7cyIoVKwj09Zl1Op2UlZVx+vRpioqKaG5uxmw243K55GfKokWLWLZsGenp6XLKeGNjI//jf/wPiouL+elPf8r69euJjIwEnzi2WCxotVoCAgKeqCyfh9b1VyAQCASC+yFNWk6fPs2//Mu/0N3dTXx8PGlpaURHR+N0OqmurqasrAy73U5iYqLcZkaKpH700Ue8/fbbDAwMkJubS25uLomJiTgcDkpLS6moqMDPz4/09PR7toMQCL4uXuH6+9AgvTQ4c+YMv//977l16xYxMTHk5uYSEhJCW1ubLOAiIyPlCNlEuN1u7t69y6effsrhw4exWCxkZGTIxjkmk4ni4mJqamqIiooiISFBFlMOh4OioiIOHjxIdXU1Ho8Hpc9kx+VyyTWxmZmZcr/U4SJM5WvDo9frUavVeL1eOjo62L9/P0VFRSxfvpxVq1bJ7Wv6+vo4fvw4H330EaWlpYSHh5OTk0NYWBitra3cuHEDk8lEcnKy/JmJRN/AwIDcaqa/v1+ObEZGRjIwMEBZWRlSb9O4uLgRZkbjoVAo0Gq1cu2w9L2NjY0cPHiQw4cPYzKZiI+PJyUlhfDwcPnlz927dzEYDA/0PaPx+lx69+/fz+7duykuLsZut8vHXHoBajab5XrSwcFBOYIaHh6O2Wzm7t27VFZW4vV6SUlJISgoCJVKJb9AOHv2LENDQ2RmZspGflLtq2Su9CQhhKpAIBAIHmmcTietra0MDQ3xzDPPsH37dtasWcPChQvJycnBZrNRUVFBe3s74eHhTJo0CY1Gg9Vq5dq1a/zDP/wDPT09/PjHP+aHP/whTz31FHPmzCEtLY3u7m5u3bqFzWYjKyuLhISE0V8veIyQJv5erxfFOPVx3zaPmlD1eDy43W7cbvf3cry+Tex2O6WlpezYsYOioiLmzp3Ln/zJn7Bp0yZmz56Nv78/1dXV1NXVodVq5bTSiY7B4OAgR44cYe/eveh0OrZs2cKLL77I8uXLmTVrFvHx8TQ3N3Pz5k3UajXZ2dmyCLTZbFy5coXr16+TkJDA5s2bWbduHQsWLJCXefPmMX36dGJjYyeMFkrnyGazcefOHXbt2oVGo2H79u3k5uai9hk7Xb16lY8//pjy8nKmT5/Oq6++yubNm5k9ezZBQUHcvXuXO3fuyHWtAQEB434fw2prQ0JCWLZsGZs2bWLlypXMnz+fpKQkOjo6uHv3Lh6Ph5SUFHn/78V419rAwAAdHR2EhoayZs0atmzZwqpVq5g/fz4ZGRm0tbVx9+5dbDbbiO8ZvZ2JsNvtnDx5kr179yK1MDMYDBQUFDBlyhRZqDqdTqqqqtDpdKxfv37EfqSmpsqO0X19fSQkJJCSkiLXrRqNRu7cucOtW7dISUkhOTkZf3//e74IeNwRQlUgEAgEjywKXy++qKgoZs2axezZs4mPjyckJASj0UhMTAxBQUHU1NRw584djEaj3Et1YGCAY8eOsWfPHqZOncpf/dVfkZ6eTmBgIAEBAYSFhWE2mykvL2doaIhJkyYxefLk0bsgeExwuVz09vbS2toqp9ndb8L8dRheeSVNQr0+N9HOzs6HXqh6PB6GhoZoamqiu7sbpc+N9nGYVHu9Xvr7+/niiy84dOgQkZGRvPbaayxdupSIiAhCQ0MJDg6W29FYrVbS09OJi4ubMKoqlRhUVFQwc+ZMNm3aRHZ2NkFBQQQGBhIcHEx3dzd37tzBbrdTUFAgmx4NDQ1x6dIlKisrmTZtGlu2bGHGjBmkp6eTmppKWloaaWlpREZGjnHhHY++vj5Onz5NYWEhU6ZMYfXq1URERKDw9es8ePAgx48fJy4ujm3btrFw4UKio6MJDQ0lMjKSnp4eSkpKsNls5OXlER0dPWFZhFqtJjw8XG7/EhUVRVBQEEajkZSUFLq7uykvL8fpdMptd4aXZzwoOp2O5ORkZs6cSV5eHrGxsRiNRkJDQ0lOTkapVMotgKRjFhAQ8EARSo/Hw507d3j//fdpa2sjLi4OfJHqqVOnykJV4TPFiouLY86cOUyZMkV+Hg3fj8rKSjo6OoiMjGT69OlyTbFer5dTzQMDA0e8rHhSeXJHLhAIBILHArVaTWhoKCkpKQQHB8vpYEqlEn9/f1JTU+U6v97eXrnGTDJgcrvdhIWFySlYDEsvCwkJkWu2JAdJweNJf38/Z86c4Z133mHv3r00NTWNXuUbwe1rg2K1WuW2SJIr6HDuJza+b6SI486dO3njjTf4/PPP5RpOKRX1UUWqTb116xbt7e1MmjSJnJwcWVCoVCoSExOZOnUqISEhtLa2UllZycDAwOhNyVgsFtk4KTg4mMDAQLnWUKlUotPpCA4ORqfTjXDGHf5ZtVqN0WgkKChIbiEjtTQZnQo7ER5f39I7d+7gcrnIysoiNDRU/lxLSwvl5eXYbDY5rTU4OFged0REBHPmzCE0NJTy8nKqqqowm81jrl8JpVKJn5+fvM8qn+OtdH82Go1ySqtinEjpg6LX64mMjCQ6Olo+tsO/Z9q0aURFRdHf309nZycWi2XCfR5Nb28v+/fv5/r16+Tk5DB79mxCQ0PHFZAqlYro6Gji4+MJDg4esR8Gg4Hk5GSSk5Nxu910d3djs9nk/VAqlXKKdXl5Oc3NzTidztFf8UQx9ggLBAKBQPCIIU0ExkOtVssTOK/XK0+ItFotkZGReDweKisrqampwW63gy+iYjabqa+vp6OjA6PRSHR09OhNCx4jrFYrdXV1lJWVUVtby+Dg4OhVvjYOh4OamhoOHjzIhx9+yM6dOzlw4AAVFRXY7XZZDGg0GlQq1YTX9MPA8DTlu3fvcvDgQd5++20OHDhAXV2d/Ft6FHE4HLS2ttLS0oJerycjI0OOOEoYDAZiYmKIiIjAbrfT0tIiGw6NR1BQEMHBwVgsFurq6mhqasJms4FPPJrNZhobGxkcHCQ5OZnIyEj5/JtMJgYGBtBqtfLLuK+Ky+Wiu7ubhoYG9Ho9qampBAQEgO+ctre309HRQUhIiJzOPDxaqtVqSUhIICgoiPb2dhobG2Wjpi9Ld3c3VVVVdHd3ExkZSVxc3FfOYpCeARMJXak9zZcVxF6vl5MnT/LFF18QExPDihUrSE9Pv6eh0b32Q6PRyCnHynFaGyUkJJCYmEhjYyOtra04HI4HFtSPIyL1VyAQCASPLR6Ph+bmZk6ePElNTQ0zZszgqaeewmg0ypMJKSrQ399PYGAgQUFBDA4Ocvz4cXbt2oXZbGbNmjVPVO+6J5HBwUFKSkqor68H34Syv7+furo6amtrv/ZSV1dHRUUFhYWFnDt3jpKSEioqKuTWH4ODg7S0tFBVVUV5eTktLS0MDQ3R0dExZlvf91JXV0dDQwPNzc20t7fT19eH1WqVW6i0tbXhdrsJCAjAz89vzGT8YcdsNnP79m0KCwsBWLNmDVOmTBkRsVQoFHR3d1NaWkpLSwuRkZFy1G48NBoNAwMDVFVVUV9fj9lsxmAw4O/vT2dnJ4cPH2b//v1oNBpeeOEF5s2bJ6eT1tXVcf78eerr63E6nXR1dVFRUSGLXYPBMG7rrfEwm82UlJRw9uxZAgMDWbduHYmJiSh8pk1Xr16lsLAQg8HAggUL5EiyhNfrxWQyUVRURHV1NXl5eUydOlW+p06Ex+PBYrEwODhIT08P5eXlfPrppxw6dIjg4GA2bdrEggULCAkJued2vip37tzhyJEjeL1eli1bxtSpU8eYTo1HcXExv/nNb+jo6JAdfvv6+igqKsJqtY5I/X0QysvLOXHiBP39/cyaNYu5c+eOcE7WarVcu3aNW7duMXnyZCZNmoTBYLjvfj6uiPY0AoFAIHhssdls7N27l3/7t3/DZDLxp3/6p7zyyisYDAY8PlfPU6dO8fvf/57S0lLi4+PJz88HoKysDIVCwapVq9i4cSNZWVn3fIsueLRpamri448/5syZM9hsNgIDA79W5Go8vL5ejzabTY5AKX2pkZKg83g8OJ1OPL4WSSqV6qGNqLjdbux2u9xixeszoZLMgNatW8fs2bMJDg4e/dGHmp6eHnbv3s1bb72FUqnkv/7X/8q6devG1GGWlJTw+9//ntOnTzNt2jR+8YtfUFBQMGIdCY/HQ1NTE4cPH2bPnj00NjYSGxtLWloaDoeDqqoq/P39eeaZZ9iwYQPx8fHyuT916hSvv/46ly5dQqFQYDAY0PqcbxMTE1m4cCFr1qwhIyPjvtdsV1cXe/fu5e233yY5OZn/8l/+i3zPM5lMvPvuu7z99tvExsbyJ3/yJzz11FMEBQXJn3e5XDQ0NPC//tf/YteuXTz//PP8xV/8BZmZmfe8P5pMJs6cOcP58+dpa2ujublZrhfduHEjy5YtIz4+/itHVCfC6yvz+Md//EfefvttMjIy+PnPf86iRYvkSPJ4eL1eenp6+N//+3+zb98+li9fzmuvvcbkyZM5efIk//zP/0xfXx+vvPIKP/jBDwgJCRm9iTH09vayc+dO3nzzTYKDg/nLv/xL1q1bN0Koejwe/u7v/o63336b559/nh/96EdyrfKTyDf/yuIr4vV68ficwR50eVhv3AKBQCD4/nG73VRXV3Pq1Cmam5uZNGkS06ZNk998K321YvPmzSM/Px+LxUJxcTEHDhxg37593L59G6fTSUREBOHh4fechAkeH7xeL263G6vVitls/sYXqSZVWlwuFzabDbPZzNDQkLyOw+HAYrHI//YwLjabbUzttsvlwul0yk7AjyJSHbHUg1Or1Y4b5VMqlfJ9Ybw64+EolUpiY2MpKCggOTkZk8nE1atXOXjwIEeOHKGiogKFQiEbaA0XJvHx8WzatIlf/OIX/OxnP+Oll15i6dKlGI1Gbt68yR//+Efef/99qqur71sf7HA4GBwcxOVyERAQMEIYSuOWelCP54orpaxKx8ThcNx37PjccFtaWrh58yZXr16lpKSE1tZWrFYrHo8HxZdIx/0yuN1uioqKOHPmDE6nkxkzZpCamnrPCLT0QunQoUOcOHGCzMxM1q5dS0ZGxgOZVY2H29eDtbCwEJfLxdSpU8nPzx/TN1apVBIYGIhWq8VkMn2pWtrHke89ourxeGhpaeHatWu0trbKF+v98Hg8hIWFUVBQQGpq6pgTLRAIBIInF4/HQ1tbGzt27ODDDz8kICCAH/3oR2zZskV2UfX4TEX27t3L+++/T1dXF7NmzSI5OZnOzk5u3LhBT08P2dnZbN68mbVr106Y1id49GlqauLDDz/k3LlzGAwGpk+fLqdEfhMofG1BampqZAMaj8eDwWAgIyODtLQ0/P39sVqttLW1YTabiYuLIzQ0FEa5BH/fKBQKXC4XHR0d3L59m6amJlwuFyqVipCQELKzs5k1axYFBQXExMTcN8r3sNHZ2cknn3zC22+/TUBAAL/85S9ZuXLlmGuhtLSUt99+mxMnTjBlyhT+6q/+imnTpo1YR8Lr9VJdXc2+ffs4cuQIVquV7OxsYmJiaGtr4/bt25hMJqZOncoLL7zAokWLMBqNKBQKzGYzJpMJh8MBPtFjMpmorKzk8OHDnDx5En9/f/7Df/gPbN68+Z5tchobG3nvvffYvXs3c+bM4S//8i/JzMwEn6HY7373O/74xz+Snp7OT3/6UxYtWjSi5MHtdtPY2Mj//t//m08//ZTNmzfz85//nOzs7HueZ5vNRnl5ORUVFZhMJrq6urh16xbV1dWEhYWxbt06Vq9eLbdr+SZwuVxUVVXxL//yL+zbt4+ZM2fy7/7dv2Pu3Ln3TPu12+1cv36d//E//ge9vb38yZ/8CWvWrCEyMhKVSsXhw4fliOqrr77KCy+8cN+I6t27d3n33Xc5dOgQiYmJcrR6vNY+b731Fv/6r//KwoUL+dM//VMmT558z2P7OPO9C1WXy0VJSQkff/wxpaWlOJ3OMSdsNFL0NTk5mS1btjBv3rwRaQkCgUAgeHLx+lpLfP755+zYsQOTycSWLVt44YUX5PYAXl+d1fHjx/n7v/97TCYTL730EsuWLSM6OpqBgQGKi4s5fPgwt27dIiMjgx/96EesWbPmnm/iBY8uklA9e/Ys8fHxbN26lYKCgvvOSR4UhUIhR5Vqa2sxm80A+Pv7k5SUREJCghxFqaiooKenh9zcXOLj40dv6qHAarVy48YN9u7dS01NDUFBQaSmplJQUEBeXh6JiYkYjcYHcqJ92Bie+qtSqfiv//W/snbt2jHpl7dv3+att97i3LlzzJw5k5///OdMmTJlxDoSbW1t7Nq1iz179qBWq1mxYgULFy4kPDycnp4erl+/zsGDB6moqGDGjBn8u3/375g1axY6nQ6vL616+JTd4/HQ39/PlStXePPNN7l69SpbtmzhL/7iL8jKyhqzrxL3Eqomk4n33ntvROrvsmXLxqT+1tXV8T//5/9kz549/OAHP+BnP/vZfQ2GPB6PnCngdrsxm83U1tby+eefc/bsWaKjo3nppZdGtMr5OrhcLhobG9m5cyfvvfceoaGh/Nmf/RmrV6+WBed4OJ1OGhoaePPNN9m5cycLFy7kpZdeIikpSR7fuXPn+OCDDxgcHGTjxo0888wzREZGEhUVNW7grL6+no8++ohdu3ah0+l47rnn2LRpEzExMePux29/+1tef/11FixYwE9/+tMnWqg+FGZKUtpIREQEqamppKen33OR+kXl5OSQnZ1NRETEPX8cAoFAIHgy8Hq99PX1cejQIT766CO6urpYsWIFW7ZsISMjY0SaXktLCzt27ODMmTMsX76cH/7wh+Tk5BAaGkpYWBhxcXH4+flRW1vL3bt35RYHwlDp8URqV+RyuUhNTWX69OkkJCSg1+u/scXf35+QkBDi4+NH9L+Mi4uT23QoFAoGBgZwOp0kJycTExMzZjsPw6LVajGbzXR3d2MwGJg5cyZLly5l5syZJCcnj2gR8qjhcDhobm7mxo0bDA0NMXPmTLkGc/h4GhoauHDhAm1tbWRlZTF79mwiIiJGbEvi5s2bfP7557S0tLBgwQI2bNhAbm4uYWFhREREEBsbi1KppLS0lKqqKhISEsjIyMDf3182flP6XGKVSiUqlQo/Pz90Oh2NjY1UVFSg0+mYMWMG8fHx46YqAwwNDXH37l1KS0uJjIxk7ty5hIeHy3+vqamhuLgYhULB5MmTSUtLQz/MKMjtdsvmTzU1NSxYsIBZs2bd10xJ4atd1ul06PV6AgMD5Wh7RUUFVVVVBAUFkZGRQWho6LgC7kFxOp00Njayd+9edu3ahUql4sUXX2TNmjVER0ffUzPYbDauXbvGjh07qKurQ61W09LSwtWrV7lw4QKFhYVcuXKF6upq+vv7ZcO1rq4uUlNTx0RqGxsb2bNnD3v27MHj8bB27VqefvppEhISJhSfFy9epKioiKysLGbNmkVERMQ9j+3jzPc+aqVSSXR0NEuXLmXbtm08//zzPPfcc/dcnn/+eV544QXWrl1LamrqN5YiIBAIBIJHF0mkHj58mA8++ID29nYWL17Mpk2byMrKGjEpcDqdtLe3c+fOHQDmzJlDfHw8er1ers0KCwtjypQpZGVlyW//+/v7h32j4HEiICCAGTNmyMYuMTExI4TBN7GoVCr0ej2hoaFyBCYsLGxEf8nhk9zR4uRhWrRaLSkpKaxevZpt27axbt06ZsyYQUxMzCPp9DscrVZLREQEAQEBDAwM0NbWhslkGhHRdLvdDA4O0tfXh1KplM/jeHg8HhoaGqipqUGv15Oenk5sbCx+fn6y4IyOjmbWrFkkJSXR09NDdXU1fX19eO7R9kWlUmEwGOSWNVJt8L2SJTUaDYGBgahUKsxmM85hfTo1Gg3h4eEYjUZMJhPd3d2yUZaE2+1mYGCAvr4+9Ho94eHh6H0vWO6HdH1L17Wfnx/p6elER0djNptpbW2Ve1t/VRwOB/X19ezdu5fdu3fjcrnYunUr69atIzY29p4iVUKj0ZCcnCyLeOlYdHd309PTI6dhu1wuzGaz7No9ul67ubmZPXv2sGvXLhwOBytWrGDdunUkJydPKFK9vtZoTqeTgICABz62jysPxV1Eq9USGhpKVFTUAy/R0dHyj+NRvhkKBAKB4OsjpcEdO3aM9957j7a2NpYuXcpzzz1Hfn7+iIiAVD5isVgYGBhAoVDIE8bhSBMpPz8/vD6DnXtNGgWPNjqdjqSkJGbMmEFOTs63VlI0nvgcPhGVRMG9xMbDgFqtJjw8nIKCAubMmUNKSgoGg2HM7+hRRKPREBUVRWxsLE6nk+rqarq7u0ecE5PJRGNjI11dXRgMBhISEuRsC6/Xi8PhwOl0yim7FosFi8Uib3/0eZdEp5Q6Kt1v7nUdSLWqkqAMDw8fE9EbjU6nIywsDLVaTX9//wizHqUveBQVFcXg4CB1dXX09PSMEI4Oh4Pa2lr6+vqIi4sjKSlJbp/i8XhGjPtBcDqdssAbfky8PrdeaXwmk+m+91+Hw0FdXR0HDhxg7969OJ1OtmzZwrPPPivXvo53bNxut5ySrNFoyM7O5tVXX+XnP/85f/7nf85PfvITfvzjH/OTn/yEn/zkJ6xcuZK4uDgiIiKYN28eL7zwAmvWrCE0NFTefktLC7t37+azzz7DarWycuVKNm3aRHZ2Nn5+fuPuB76IriTWjUYj/v7+E677JPDQKLzxbtz3W6S3MgKBQCB4cnG73fT19XH8+HHefvtt6uvrmTdvHlu3biUnJwe1Wo3dbsdms8mOqyqViqCgICIiInA6nRQXF9Pd3T1iQma322ltbaW1tRWtVktMTMy3Jl4E3z+KYamJE7m8CkaiUqnQ6XT4+fmNSYt9lFGpVISHh5OXl0dISAh37tyhpKREjqpKdZrFxcWYTCYSExNJT08nICBATjs9d+4cFy5coL29HY/HQ3BwMEajkaGhIRobG+np6ZEFmiRk6+rq6OjokIVvcHCwLEalKJ4kfJ1OJx0dHVy7do2SkhKUSiWTJk0iMjLynteuTqeTo8X9/f10d3fLJk0AsbGxZGZmotFoKC8v5+7duwwMDMjf2dLSwqVLl+jr6yM3N1dODXa5XNTX11NYWEhRURHt7e04nU5sNhu9vb309fWNiM5KLxdv3bpFQ0MD/v7+xMfHyw7rTl+t6OHDh9m1axfV1dUj9nM0koA+ePAge/fuxWw2y+IwLi5OrpG1Wq3yc4BhqdBnzpzh5s2bWK1WYmNjWbp0KatXr2bVqlWsXr1a/v9Vq1Yxffp0wsLCCAoKIjs7m0WLFjF9+nQCAwPxeDy0trayZ88edu7cSX9/P0uWLGH9+vWkpaWhVCrHPI+G093dTVtbGwaDgbCwsCc+ovpQ1KgKBAKBQPBVkCY7J0+e5I033uD69etERkYyZ84cDAYDHR0d1NXVyUtnZydKpVJ20+zo6JBFalBQEHq9HqfTSX9/PxUVFRw9epRLly4RHh7O008/zaxZsyZM2RIIvi5erxe73U5XVxdms1luVSL4blEoFHJkuKGhgdLSUhwOB8HBwSgUCpqbmzl58iRnz55Fp9OxYsUK5s+fT0hICAMDAxw+fJh33nmH69evEx4eLhtiNTc3U1dXh8lkkgW+y+Wip6eHO3fucODAAW7cuEF6ejpbtmwhJyeH7u5url27Rnl5Ob29vXKqaW1tLYWFhbIBU25uLlu2bJHddycSNwqFAqvVSllZGQ0NDaSkpJCZmSmnLet0OhwOB42NjdTV1WG32+WIaVNTE8ePH+fQoUOo1Wq2b9/O7NmzMRgMDAwMcPDgQT744ANKS0sJCgoiMjKSjo4Ozp8/T2lpKSaTCZvNxsDAAE1NTVy4cIE9e/ZQXl5Oeno6a9asYcqUKRgMBgYHBzl79ixvvfUWxcXF5OfnT5gy63K5ZJH6+eefU1tbS2JiomyG1tTUJD8DamtrMZlM+Pn5odVqqaurY9euXXzyySc0NjaSmppKZGQkOp0OjUYz7lJTU8OVK1ew2WxMmzaN6dOnExAQgMfjob29nV27dvHee+9RVlZGWloaU6ZMQafT0dbWJu9HfX093d3d6HQ6uQ4Z4M6dO+zdu5eQkBBWrFhBWlraE13iKISqQCAQCB5Z7HY7FRUVvPHGG1y5ckVukdHe3s7Vq1c5f/48hYWFFBYWcuHCBWprawkJCSEzMxOdTkdgYCBdXV00NDRQVlZGa2srtbW1XL9+nS+++ILLly+j0+lYtWoVTz/9NJGRkRNOAAWCr4sQqg8PUiquJEzLyspk8Xb27FnOnz+Pw+Fg4cKFsmeKSqWip6eHffv28cUXX9DR0UFqaio5OTlERUWhVCrp6uqitraW6upqGhsbqampoaioiGPHjnHr1i3Cw8N59tlnWbx4MSEhIZSXl/PZZ59x4MABrl+/TmlpKdeuXePkyZOcPHmS5uZm0tLSeO6551i4cCFBQUH3vEcplUo8Hg8dHR3cuXMHf39/pkyZIqetSuN2uVw0NzdTUVFBXV0d1dXVFBYWcvLkSex2O+vWrZOjldI99+DBg5w8eZL+/n6SkpJITU2loaGBDz/8kEOHDlFcXExZWRk3btzg1KlTHDx4kJqaGhITE9mwYQOLFy8mOjoapVJJd3c3586d4+LFi8TGxrJmzRoSEhLGjRYPDAxw5swZPvvsM+7evSvX6tbX13Pp0qURz4Fz584xMDBAbGwsYWFhVFZWcujQIS5duoTVamXatGkkJiaOK4glqqqquHbtGk6nk6lTp5KXl4der8fhcHDlyhV+85vfUFFRgdfrlYVyUVGRvA/nz5/nwoULNDQ0EBcXJ9fOut1uTpw4walTp2Rzsns5FD8JCKEqEAgEgkcSqQ6sqamJ4uJiOXUsNDRUrgFTqVSoVCr5/0NDQ8nJyZEbt4eFhclvrPv6+qisrOTOnTuUl5czNDQk91B9+umnSU5OfqInDIJvHyFUHx4Uvtr1mJgYQkNDGRoaoq6ujoqKCtrb24mIiGD16tVs2LCBnJwcubZUuie1tLQQHh7OsmXLmDRpEkFBQbLPilqtpru7W77fVFdXy6Jn27ZtrFy5kujoaFQqFRaLRU7RlSKydXV19Pb2EhoayqJFi9i+fTuLFy8mLCxsXCE3GqVSicPhoLi4mK6uLvLy8mTBqVAo0Ov1REZGEhQUhMlkoqamhsrKSjo7O4mKimL9+vVs376dtLQ0WdBJ9aFtbW3ExsYyb948MjMz5TGYzeYRkc2Wlhb8/f2ZM2cOzz77LMuXL5edcD0ejxy9bWpqYunSpSxdulSOaI/GZDJRVVVFa2srAQEBREdHExQUhFqtHvEckMaXkJDA5MmTiYqKwmKx0NDQQF9fH2lpaTz11FPysZiI3t5eOjs7CQ4OpqCgQH6eOJ1OKisrqaqqkt29x9sP6f/Dw8OZMmUK8fHxqHwvOXbs2EFzczPr16+XI7XjjflJ4XvvoyoQCAQCwVfF7XbT399PfX09NpsN5f/P3ntHx3Hdd/vP7mIXi1303jtAFAIgCsHem6hGkaqWLFvFkmzLLc6bvE5OkpOT8yZO/MZ+YzuxLClWoaxGShYlihR7AUH03nvvbbEN2L6/P367EzRSpCotzXPOHOkQd2bu3JmduZ/7ba4aqdfCy8uLiIgIwsLCkEgkQtyVTqejq6uL4eFh9Hq9kCgmISGBiIiIr0ySGJFbG4fDgVarpbm5mYmJCfLy8oiPj1/aTOQLxOFwMD8/T19fH93d3czOzuLl5UVsbCzx8fEEBAQscrW1Wq0MDg7S0tKCQqEgMzNTEJ3uZEOTk5MMDAwwOjqK0WhEoVAQGhpKQkICoaGhi1xB3aEIw8PDQlZcm82GWq0mIiKCuLg4goODbyqu2i0EX3jhBY4fP85DDz3Et771LaFEDgsSNQ0MDNDX14dWq8XLy4vo6GgSEhKEhExu3HG7nZ2deHl5kZqaSmhoKE6nE51Ox+joKENDQ8zMzGC1WvH09BSuOSQkRMh8jSuh0JUrV/jlL3+JTqfjL/7iL9i/fz/e3t7C+RbiXtwZHx/HbDYv/fMiHA4HAQEBREZG4uvry9zcHN3d3fT39xMSEsLq1as/NiGVRqNheHgYm81GWFiYUCbT7irdMzg4iM1mE74x10KtVhMdHU1AQAA2m41Lly7xs5/9jJSUFH7yk5+Qm5srLIB8XRGFqoiIiIjInzUOhwO7qyTD9SYXbtwr2kuxurJPujNLenh44OHhIQpUkS8MUajeutjtdsGlVCqVCu+Hld457ra4Klssfd84HA5sNht2V2Zft8ut2xNkKU5X1nH3+8npdApWObe17mYxGo2Ulpbyr//6rzidTn7605+yffv2RVlmF573Rq7bZrMJAm3hu3Ol/l/vmqenpzl27Bh/+MMfSEtL46/+6q9YtWrVsnZunK5M7u539/Vwj517c7qSY7nDRq4X3+vGfS6n07nse+L+Ht0IElciWYDR0VH+4R/+gdLSUn70ox9xzz33fGxirK8DX++rFxERERH5s0cqlSKXy1EoFMuSXqy0XevDL5fL8fLyQq1Wo1ar8fT0FEWqiIgIuBa4lEolarUaLy+v6woad1vlNerJSl11aN3vG5VKhaen54ptWZCRWqlUolKphD6sJIJvFJVKRV5eHgcPHsRms9Hc3LysbuvC897IdbvbLn13rtT/612zwWBAp9MRHx/Pjh07hLjVa7FQ9H7cplAoFol7iUQivPuvVb5mKVKXYF/pe+L+Ht3I5u6H1Wqlra2Nrq4u9uzZw5YtW27YjfurjmhRFRERERERERG5BRAtqiJfJHa7nfHxcVpbW/Hx8SElJQU/P78vXSBptVoGBgYwmUzExsYSHBz8lV40tFqtQkbihIQEYmNjr1tr9euEKFRFRERERERERG4BRKEq8kVjt9uFuE6FQoHMlXDoy+TjXKe/ajhdSdRsNhuenp7XdK3+OvLVvvMiIiIiIiIiIiIiIisik8nw8vLCy8vrlhFIH+c6/VVDIpHg6emJWq1Gfh3X6q8jX/27LyIiIiIiIiIiIiKyIhKJRBRHXzLiPVgZUaiKiIiIiIiIiIiIiIiI3FJ8rYTq7OwsTU1NNDY2MjExgc1mW9rkc8FkMjEwMEBTUxO9vb0Yjcbr1lX6OuB0OpmenqalpYXW1lampqa+sPshIiIiIiIiIiIiInJr87kkU3IHBU9PTzM1NcXc3BwWiwWHw4FUKsXT0xN/f3/Cw8Px8/P7QkzdTqeT6upqjhw5AsDu3bvZsGEDPj4+S5t+5oyOjnL27Fnq6upITk5m7969JCQkfKkZzBwOB3q9nrGxMeRyOeHh4Xh5eX0h9wLX+a9evcrJkyfx9PRkx44d5OXlfSH3Q0RERERE5FZETKYkIiIi8j/I/vEf//Efl/7jp8XhcDAxMcGlS5f44IMPuHDhAiUlJZSVlVFeXk51dTWtra1MTEwgkUhQq9U3XLvoeriL9rqLJy89Xk1NDS+//DIDAwMkJCSQmpqKSqVa1ObzYGxsjI8++oizZ88ikUjIzMwkPDz8SxOqTqcTo9FIZWUl77zzDl1dXQQGBhIYGIiHh8fS5p8LTqeTq1evcuTIEUZHR4mPjycxMfELuR8iIiIiIiK3Iu6F/snJSYxGIxEREfj7+y9tJiIiIvK14HNx/XW7dVZUVHDmzBlqamqYnp7GZrNhNpsZHh7mwoUL/P73v+eFF16gtLQUrVa7qMjwzTI3N0dnZyclJSU0Njai0+mWNsFms2EymTCZTNhsti/M/dbhcGC1WjGZTIJl+cvE6XSi1+upqqrigw8+4NSpU3R1dWGxWL6wMcF1P8xms3A/RERERERERERERERE+DyFqtVqxWg0ApCZmcm3v/1t/uqv/oqf/vSnPPPMM+zduxeZTMbp06c5evQoHR0dQh2nm8XpdDIxMcHJkyd54YUXOH36NBMTE0ubIZFIkEqlK1pbP0++yHPdKHK5nJCQEBITE0lISCAgIOBLs/B+0fdDREREREREREREROTW5nMRqiwQZwqFgujoaPLy8tiwYQNbtmzhnnvu4dlnn+Whhx5CoVBQXV1NbW0tOp3uE1n0nE4ns7OzNDc309zczPj4uFAoWGQ5UqkUf39/du3axY9//GOeeuop1qxZg1Kp/EIF4xd5LhERERERERERERGRPx8+txjV8fFxqqqqGB4eJjExkcLCQiIiIvDw8EChUODr64unpyfd3d309/cTFhZGVlYW/v7+OBwOjEYjs7OzaDQaNBoNWq0Wk8mE0+lcVAzXarWi1+vp6+ujtLSU4eFhIiMjSUlJQalUYjabkUqleHh40N7ezsWLF5FIJBQUFLBq1SrsdjvT09NoNBqMRiN2ux0PD49rWhedTicWiwW9Xs/MzAwajYbZ2VlhX5lMtmzf6elpKisr6ezsJDo6msLCQiIjIxe1czqdmEwmNBqN0B+tVsv8/DxOpxOZTHbNoscOh4O5uTlhX3d/3LG6JpMJg8GA1WoVjiORSPDw8MDX15eQkBB8fHxWLPRss9mYm5sT7oVWq8VgMGA2m5FIJMhkMiQSCXa7fVG7mZmZRf338PBY1H+n00lDQwNlZWXI5XLy8vJYtWrVdWNUrVYrOp2O+fl54ZxarRaNRoPFYhHGXiKRCHE+7jGZmZlBr9cLz4O73ULcz93MzIwwjnq9HqvVumgfs9mMTqfDZDIJ1+R+Htz7zc/Pg6to9bUsxu775t5Po9Gg0+kWje3SMbNYLMIYyGQyHA4HOp1OeBYNBgM2m+2a1+gel5mZGaamppidnUWn02GxWFbcZ6VxdLdf+CyJiIiIiHx63O9cMUZVRERE5HPK+mu1WmloaOC5556jvLycHTt28Mwzz5CZmSm0cTqddHV18R//8R98+OGH7Nu3jx/+8IckJSUxOTlJTU0NNTU1DA4OMjc3h4eHB9HR0WzYsIGNGzcSHByMTCZjeHiYixcvUlRURGlpKePj48THx5Obm0toaCgRERFs3bqVzMxM3n//ff7+7/8eqVTKk08+ydq1a2ltbaW6uprp6Wn8/f3Jzc1ly5YtJCcno1AoFl2Xw+HAYDDQ2dlJeXk5TU1NTE5OAhASEkJWVhYbN24kJSVlUQbdjo4Ofve733Hy5EnWrVvHs88+S35+PnK5HFxicHZ2loaGBoqLi+ns7MRoNOLp6Ul0dDRr166loKCAyMhIPD09FwkDm83GzMwM1dXVXLlyhd7eXqxWK6Ghoaxdu5bMzExmZmbo6+sjMjKSdevWERoaitFopKamhtLSUoKDg9mxYwexsbFCMiWHw4HJZGJkZIT6+noaGhoYGRnBYrHg5eVFXFwcW7duJTs7G5VKxfj4uGAZHxgYQKfTIZVKiYyMpLCwkA0bNhAVFbXo+H/84x/5j//4D1QqFU8++SR33XUXwcHBwrUtxOl0MjQ0xLlz57BarRQUFOBwZQ7u6upi1apV7Nu3j4SEBKRSKXq9nubmZi5fvkxbWxsGgwGlUsmqVavYtm2bsCjiFoJ2u52pqSkqKiooLi6mr68Pq9WKv78/OTk57Nq1i5SUFBQKBW1tbRQXFwNQUFCAj48P5eXllJWVMTo6itPpJCYmhk2bNlFQUEBERMSi++Z0Jf2ampqiqqqKkpIS+vr6MJlMKJVKEhMT2bhxI2vWrCEkJER4Dm02Gz09PZw7dw6pVMrWrVuRyWRcvnyZmpoaNBoNarWaNWvWsGnTJlJTU/H29hbO63Bleq6vr+f8+fN0dnYyPz+Pt7c36enp7Ny5k8zMTGEftwhubW3l8uXLtLa2otfrUSgUpKamsnv3brKysvD19V206CIiIiIi8slwiFl/RURERAS+EItqQkICBQUFhIaGLmo3NjbG5cuXGRgYYPXq1axfvx6AM2fOcPjwYYqLixkZGWF8fJyenh5qamqoq6sDIDk5GZVKRX9/P++++y7nz58XRK1Wq6Wvr4+Ojg4MBgPJyckkJycLFlWLxYKHhwc1NTWcOnWKuro6Ojs7aWpqoqGhgZmZGSIjIwkPD18kLmZmZjhz5gzPPfccx44do7m5mbGxMYaHh2lpaaGyspLe3l58fX2JiooSBMb1LKpWq5WBgQHeffdd/uu//oszZ87Q39/PxMQEfX19gmDXarUEBQURFBS0SOAODw/zzjvv8Nvf/pZz584xNDTE5OQk3d3dNDU10dXVRU1NDeXl5TidTtLT0wkMDGR2dpYzZ87w6quvMjk5SUZGBtHR0chkMpwuV+ri4mL+8Ic/cPjwYa5cuUJHRwe9vb20tbXR0dFBYGAgqampSKVSTp06xUsvvURxcTEDAwOMj4/T399PfX09dXV1WK1W4uLi8Pf3FyyeN2tR7evr47XXXqO6uhqdTseFCxc4duwYbW1teHt7k5GRQWhoKDqdjo8++ohf//rXnDp1ipGREaampujp6aGyspLu7m5UKhURERHC+UZGRjh69CjPPfccly9fFp67zs5OpqenSUxMJC4uDk9PT2pqanjttdeoqanBaDRSXFzM0aNHqa2tZXBwkO7ubmpra6mtrcVmsxEWFoa/v78g0i0WC+3t7Rw+fJjnn3+e4uJihoeHmZycFPro3jc0NBRfX188PDywWq20tLTw4osvUl1djclk4vjx4xw/fpyWlha6urpobm6mqqqKqakpgoKCCAsLQ6FQ4HQ60el0nDlzhn//93/n9OnTwrPS2dnJyMgIkZGRxMfH4+3tDcDU1BSnTp3it7/9LWfOnGFkZITp6Wn6+vooLy+nra2NgIAAwsPDv3C3cREREZGvIqJFVUREROR/+EKEamJiIvn5+YJQdTqdzM/PU1lZyZ/+9CccDgfbt29n7dq1eHp6Mjs7i7e3N3fccQff/e53efjhh9m8eTNOp5Pa2lpGR0eJjo4mISEBpVJJUFAQgYGBgntrbm4uDz74IHfffTcbNmwgMzMTf39/Ojo6uHjxIoODg4yOjqJQKNizZw/f/OY32bRpEzKZjO7ubrq7u/H29iYtLU2YtM/Pz3P+/Hmee+45mpubycjI4Mknn+S73/0ud999N3FxcQwNDVFVVcXExAQxMTEkJCTAdYQqLoH07rvvcvjwYcbGxti3bx8//elPefLJJ9m5cydeXl50dnbS2tqKzWYjNjZWsDpOTk7y/vvv89JLLzE0NMTu3bv5yU9+wpNPPsmmTZswm81UV1fT0NCA2Wxm1apV5OfnExQUtMii6uvry4YNGwSLql6v5+LFi/zhD3/gypUreHt7s2/fPh599FEOHTokWOvWrFlDUlISHh4eTE1NoVar2b9/P08++SSPPvoo27Ztw9PTk+bmZrq6uoiOjiYpKUkQTjcrVCcnJ7l48SLt7e309PQwNDREZGQku3fvZufOnaSlpeF0Orl06RL/9V//RU9PD/fddx8/+9nPeOqpp9i8eTNzc3NUVlYyPT1NZGQkERERmEwmrl69yquvvkp/fz/3338/f/3Xf80jjzzCxo0bWb16tSCCPTw86O7u5urVqzQ3N9PR0cHw8DD5+fk8/fTTPProo+Tl5aHX6+no6KC7uxsfH59FArCnp4fXXnuNt99+m/n5eR588EH+4i/+gscee4zNmzdjtVppbW2lpaUFpVJJfHw8Pj4+OBwOBgYGOH/+PO3t7TQ3N2M0Grnzzjt58skn2b17N3K5nP7+frq7u/H09CQlJUVwp29ra+O3v/0tVVVV7N27l//9v/83Tz75JFu2bGH16tVkZ2cTHR2NQqFAp9Nx6dIlXnzxRXp7ezl48CA/+9nP+M53vsPu3buFrNHuZz0qKkpYQBERERER+WSIQlVERETkf/hChGpcXJwgVG02G+Pj45w/f57Dhw9TV1dHZmYm9957L0lJSajVaqKiosjJySEzM5OoqChCQkKEl/XQ0BCNjY2EhYVRWFiIv7+/YBnr7u5Go9GQn5/PoUOH2Lx5M4mJiQQEBCCVSgWLqkajISsriyeeeIK7776b7OxsUlJSiIyMZHZ2lt7eXmQyGampqcTGxgLQ3NzMa6+9Rm1tLXl5eTz11FPs27ePxMREoqOjSUxMxN/fn8HBQZqamlCr1aSlpeHr68vMzMyKQnVubo6ysjKOHDnCwMAABw8e5Pvf/z5r164lMjKSuLg4kpOTsdvtQpKooKAgYmNjkUql1NXV8eabb9La2spdd93Fs88+y4YNG4iJiSE+Pp7Y2FihbI/D4SArK4u8vDxBqDY0NFBVVUVQUBCbN28mNjYWiURCQ0MDb7/9NtXV1axatUpYLCgoKCAlJYX09HTWrFlDYmIiarUauVxOREQE2dnZZGZmEhMTQ2hoKJGRkYSEhDA+Pk53dzchISHCosEnFaqXL1+mvr4egNtuu41nnnmGO++8U1hUcIvApqYmDhw4wBNPPEFWVhbBwcHExMQQGBjI6OjoosUIi8XCpUuXKCsrIyYmhqeffpqNGzcSGRkp1NsNCwvD09MTXJbdsrIyenp6UKvVHDx4kCeffJJ169YRHx9PWloaKSkpTExM0NbWhtVqJTY2lqioKIxGI+fOnePNN9/EYrHw7W9/m8cee4zs7GzCw8OF/d3JwXQ6HREREcTExODh4cHw8DCXLl1icHCQ0NBQfvzjH3P//fezevVqUlJSSEpKYmZmhvb2dux2OwkJCcTGxmK1WqmpqeH999/H29ubH/3oR2zbtk1Y8ElLSyMyMhKlUglAW1sbR48epb29nf379/PUU0+xevVqgoODhXFpa2ujtbWVkJAQkpKS8PHxWRRTKyIiIiJyc4hCVUREROR/+FxnlRKJBIPBQHl5Oc8//zz/8i//wj/90z/xs5/9jH/5l3+hvLyc7OxsHnnkEbKyslAqlchkMtRqNQEBAXh7eyOXy5FKpSgUCgIDAwkJCcHsqsU6OzsLgKenJ0qlUkgG5OHhgZeXF97e3oKQcuN0OgkODmb9+vVCgieVSoW/vz/JyclkZWUREBDA0NAQIyMjOBwOzGYz7e3t1NfX4+fnx+bNm8nJySEoKEg4d3h4OBs3bmTDhg3IZDKqq6tpaWnBbrcvGJH/wemqNVtXV8fQ0BBpaWns3buXtLQ0VCoVcrkcLy8vkpKS2LZtG5mZmRgMBlpaWpiYmECv19PS0sLAwABJSUns3buX1atXC2OmUqlIS0tj06ZNJCUloVQqca4QjrzUXXN2dpa6ujrq6urw9fVl3759bN26lejoaGE8fXx8CAgIQK1WI5VKkUqlqNVqAgMD8fb2RqFQIJPJ8PT0xN/fn7CwMCGe2H3PPg1Wq5Xk5GR27NhBdnY2YWFheHt7Mzc3R1tbG11dXURGRrJ3715SUlLw9PREKpWiVCrJyMggNzcXp9NJd3c34+PjQg1Xm82GTqdDo9HgcDiQy+XC9S6NDQbw9vYmJyeH2267jZSUFLy9vfH09MTHx4eCggJ2795NdHQ0Q0NDdHd3YzQaGRkZobq6Gr1ez5o1a9i7dy9xcXEolUrhfGlpaWzfvp2EhASGh4dpbW1ldnZWuH8SiQSlUsmWLVvYtGkTkZGReHl5oVarycjIEBaFNBoNw8PDmBeUfXInHxsbG8Nms+Hh4YFKpcLHxwelUolUKmVubo7W1lYaGhoICgpi9+7dxMbGolAokEqleHp6kpmZSX5+PhKJRHAdFmvhioiIiIiIiIiIfFZ8rkIVwGQy0drayjvvvMMLL7zAK6+8QlFREZ6enjzwwAP89Kc/Zffu3QQGBgrWGHeMZGVlJS+//DL/9E//xN/8zd/wq1/9ioqKCmw2GxaLhfn5eRyuzLZOp3OZEFsqLNx/V6vVhIWFCbF/uEq2eHl5ERgYiJeXF0ajEaPRiNPpRKvV0tPTw/T0NGFhYaSnpwtWWjceHh4EBQWRnJxMUFAQw8PDDA0N4XA4hDYLcSdM6O3tRafTERcXR1xc3LIETgqFgtjYWFJTU5HJZIyOjjI5OYlWq6W/vx+NRkNcXByJiYmLEjjhEvDBwcEEBQUtO+61mJ2dpa+vD71eT0xMDNnZ2YSGhi7KBitZIYute1Girq6O1157jf/zf/4PP/vZz/jXf/1XLl68yKwrE7HFYlm0n5ul9+56eHl5CRZjt1gGMBgM9PT0MDU1xdzcHDU1Nbz77ru8/vrrvP7667zxxhucOHGC9vZ2NBoNU1NTTE1NCQI2Ojqa4eFhnn/+eX7/+99TVVWFXq9fenrhWVOr1SQkJBDpSnLlRiKR4OXlRUZGBrGxsRiNRsbGxtDpdEIcKq446/Dw8GUus56enqSlpREXF8f8/DwDAwNMTk5idZVccrqyKEdHR+Pv7y/cG7eADQkJwd/fX8jY7HA4UCqVJCQkkJmZidFo5KWXXuK3v/0tRUVFTE9PLxp/t6CenJzEYDBQXV29bBzfeecdenp6mJ+fF7IHX2tRRkRERERERERERORm+VyFqtPpRKVSkZ2dzQMPPMB3vvMdvv/97/Ozn/2Mv//7v+d73/seW7duJSQkRMgaajKZaGpq4uWXX+Zf//VfeeGFF/joo4+or69nbGxMKFHjdDoFEXgzIgdXyRD5ghI3bqSuMjYyV9kP98TbYDAwPj6O2WzG39+fkJCQRcIElzhxC0M/Pz+MRiM6nQ673b5i/xZa75xOJ0FBQUIM41J8fX0JDQ1FKpWi1WrR6XQYjUamp6eZm5vD19cXHx+fZdcjcZU48VhSGuZ6GI1GNBoNHh4ehIWFERgYuExILcVut9PR0cGrr77Kz3/+c373u99x/PhxampqGBkZEcTSSosJbpb2/Xp4eXnh7++PSqValG3WZDIxNTWFXq9flKDKvf3nf/4nL774IiUlJczPzyOVSrHZbCiVStasWcP9999PRkYGjY2N/P73v+cf/uEf+M1vfkN1dbWwaLEQDw8P1Go1CoViWf8lEonwLNhsNrRaLXq9Hp1Oh1arRSaTERISsmxxwU1ISAjBwcHY7XY0Gg16vV54Hp1OJxKJRPA2WIqHhwceHh7Cb8TpKumUkJDAI488wubNmxkYGODw4cP84z/+I//3//5fioqKmJmZwbGgRI/RaBSSlT333HOLxvF3v/sd5eXlQvmh691bERERERERERERkZtl+Sz3M0apVJKens6BAwf49re/zaOPPsp9993H9u3bSUlJwc/PTxAbVquVrq4u3n33Xf70pz8xNTXFunXreOqpp/jhD3/IY489RmFhIQqF4pqWyk+LWzQsnHTb7XYsFgsOhwPZglqdK7FQ6F6vj06nE7vdjtVqxfkxdVKlrvqWCy3ObiHtcDiQfoa1LG02GzabTRBCbnfq6zEwMMCf/vQn3nrrLYaGhsjNzeWxxx7jhz/8IY8//jibNm36TGNslo6HG4fDIdQDjYyMZO3atWzdunXRtm3bNiGm9ODBgyQlJeHl5UVYWBj79+/nxz/+Md/85jeJjo6mubmZV199lZdeeona2lrm5uYWnU8ikVx37JfeM/c9d7vIXm9s3de49Hlc+FxeSxyudEyJRIKvry9btmzhRz/6Ed/73vfIzMxkcHCQd999V8g+PDs7i9VqxWq1IpfLiYqKYt26dcvGcevWrdxzzz088cQTHDhwgISEhI9d0BARERERERERERG5UVZWRp8hUlf8YmhoKFFRUURERBAUFIRKpVo2UTcYDDQ0NFBaWorFYmHXrl1861vf4tChQ+zbt4+NGzcSHx+PzFVC5XqsNFn/pHh6euLn54eHhwcGgwGdTrdiPJ7DVXfSYDCgUqnw9va+ppCRyWRCXKHT6USv12MymZY2A2Bubo7Z2VkcDgfe3t74+Pjg5eUlxE7q9fplIsqNWwxfTzQvxB1zazabBava9Vw6bTYb9fX1nDt3DqPRyObNm3nkkUe4//77ue2224QYWS8vr6W7fmJWGk8WjKlSqSQ6Opo777yTxx9/fNH2xBNP8MQTT/Dkk09y++23Ex8fj0KhQKFQEBkZyY4dO3jyySf5X//rf/HAAw+gUCg4f/48ly9fFuI63biF57WeRa1Wi9FoxMPDAx8fH7y9vVGpVHh5eWG329FqtSs+RwA6nQ6dqxatj48PPj4+i6zHnwSZTEZQUBAbNmzgW9/6Fn/xF3/B448/TnBwMGVlZVy8eJH+/n4kLhdiuVwujOO3v/3tFcfyO9/5DnfccQdxcXGiUBUREREREREREfnM+NyFKgtcFaWuxDuSFWIcAfR6vRAL6rbkZGRk4O/vL1hRTSbTNYXTQuvTtcTDJ8Hf35+4uDh8fHyEDLYGg2FRG7vdLmQMnp6eJjw8nKioqGuKC5lMhr+/P1FRUSiVSgYHB1dMSONwZVDu6enBbrcTHh5OcHAwvr6+xMTE4Ofnx8DAAH19fYuS5uASuKOjo0xMTGA2m1cc86X4+PgIbsYDAwN0dXWtGKfpZn5+nu7ubgYGBggJCWHt2rWkp6cTFBQkJOexWq3XvGefJSqVSshcq9VqkUqlREdHC3V0F26JiYlCIi231VMmk+Ht7U1ycjK7du3iiSeeoLCwEJ1OR1tbG2NjY0KcKIDZbEaj0QiuzQtxOBz09fUxNjaGSqUSYqKDgoKIiorC4XAI8bRLx8bpdNLb28vg4CCenp5ERUURGBgoxFN/GtwiNCYmhs2bN/PNb36TXbt2IZfL6e7uZmxsDE9PT0JDQ1EoFOj1eqRSKTExMcvG0L1FRkaiUqlu6PkSERERERERERERuRG+EKF6o9hsNkGIylyxlW6hNz8/T29vLx0dHYJ7p3tiLHFl+nXHjbqtUW632k8rWtVqNampqSQlJTE5OUlJSQnt7e0YjUZwiRKNRkNtbS2VlZVYLBZycnJITU1d5p7qRiKREBAQQGZmJqGhobS3t3P16lUGBwcF4eJwOBgZGaG8vJy2tjbUajWrVq0iJCQEX19f0tLSiImJob+/n/Pnz9PY2IjBYMBms6HX66mrq6OoqIi+vr5rJjFaSkBAgHDcsbExzp07R3V1NRqNRnA1dt8ni8WC1WrFZDIJAs7t7iqRSDCZTPT399Pe3o5Wq116qs8cX19fVq1aRVRUFKOjo1y+fJnu7m6sVqvgSiuVSgW3afdzYbfbmZubY25uTnj2PD09CQ8PJyAgAIlEgt1uF+6Le6FFr9fT3NxMXV3doqy8bhFaUlLC0NAQUVFRJCYm4u3tTVhYGFlZWXh6etLY2EhJSQkTExOC0HU6nfT19XHlyhV6e3uJiIggLS1tWfKum8XpKnmg1+uF8VAoFAQHBxMcHIynp6cwLm6xHhcXx+joKBcvXqSnpwebzYbM5fq+dBxFkSoiIiIiIiIiIvJZ8rnVUR0bG6OiooLh4WHi4+OFkhnXw2w209/fT3NzMxqNRnBx1Wq1NDQ0cPbsWUpLS5mdnSU5OXlRIiaj0Uh3dzetra1otVrkcjkWiwWj0YhCocDLy4u2tjbOnTuHVColPz+fzMxM1Gq1cP75+Xna29upqqpifn6eDRs2kJubi8yVfEmv19Pe3k5/f7/gajs/P8/g4CClpaV8+OGHNDY2kpSUxP33309+fj5yuZzp6WmhjmpUVJRQR9Vd7mN8fJzW1laGh4ex2+1IJBJ0Oh3d3d2cPXuWEydOMD09TWFhIbfddptQbkYul6PT6ejo6KC7u5uZmRl0Oh2Dg4NUV1dz4cIFamtrmZiYQKFQkJ6evqiOam1tLVVVVQQGBrJp0yZiY2OF4+r1erq7u+nu7mZqagqDwcDMzAyDg4O0tbXR3NyM1WrFz8+P4eFhGhsb0Wq1gpuq0WikqamJc+fOUVxczOTkJLGxsWzevJmoqCgA6urqKC0tRS6Xk5ub+7F1VCcmJigqKmJgYIDMzExyc3MJDAwUFjM8PDwEK2BXVxednZ3odDpMJhMajYbx8XF6e3tpampiZGQEuauMj8FgoL6+nqqqKiE779jYGKWlpZw5cwatVsuWLVvYuHEjwcHB9Pf3U1paSl9fH0ajUcg+bbVa0Wg0tLe38/777/PRRx8hkUjYu3cv27dvJywsDKWrTNDg4CAdHR2Mj4+DS0jOzs7S3t7OBx98wEcffYTNZmPXrl3s3r2byMhIAAYHB7lw4QLT09OsX7+evLy8Rc8wQGtrK+Xl5RiNRlavXk1eXh5SqZSOjg6KiooYGRnBYDAwMTFBTU0NZ86cob+/n5ycHDZv3kx0dDReXl5CDV73OJrNZmZnZ4VxbGhoYHBwEIVCIbi5i4iIiIh8ctyLimIdVREREZHPUahOTk5SX1/P1NQUycnJ5OXlERISsrTpImQyGTabjeHhYXp6eujv76evr4+WlhbKy8sFt0STyURMTAwbN24kNDRUiHU1GAz09/fT1dVFR0cHbW1taLVaIiIiCA8Pp7Ozk5KSEjw9PcnPzycjI2ORMDKZTPT09NDc3Izdbmf9+vXk5OQglUpRqVT4+flhsVgEsdba2kpzczOlpaVcunSJvr4+4uLiuPfee9m1axf+/v5IJBJmZmaESX10dDRr164lIiIChUIhxC4aDAY6OztpaWmhvb2dhoYGLl68yJUrVzAYDBQWFnLgwAHy8/OFeEV3n2w2G4ODg7S2tlJfX091dTV1dXVYrVZCQkJwuDK/rlq1iry8PAIDAzEajTQ3N9Pc3ExoaCgbNmwgJiYGuVyOt7c3vr6+2Gw2xsbGaGtrE45bXl5OUVERtbW1+Pj4kJqailKpZGpqit7eXvr6+hgYGKC5uZnKykoGBwcFARMSEsKGDRuIjo4GEKyRKpWK3NxcUlJSritUp6amKC8vZ2JigqysLNasWbNIqLrdWgMCArDZbAwMDFBfX09jYyONjY1UVlZSXFwsxJuGhYURERHB7Owsp06d4ujRo1RWVgpC78yZM4yOjpKXl8eBAwfIzMzEy8uLnp4eSktLmZ6eJiQkBJvNRnNzMy0tLVRXV3Pq1CmuXLmCw+Fg9+7d3H333aSlpaF01fp1L8BMTU0J97yjo4Pa2lrOnj3L1atXcTqd7Ny5k3vuuYf09HSUSiV2u53h4WFKS0uZm5tj3bp1rFmzZtmYdXV1UV9fj9VqJTs7mzVr1mC32ykuLua1114TLPTV1dWcO3eOzs5OEhMT2b9/P3l5efj6+uLt7S2UuOnr66Ourk4Yx6qqKoqLi7lw4QJDQ0PExMQQFRUlxqiKiIiIfEpEoSoiIiLyP3wuQhWXddRgMODt7U1mZibp6en4+fktbbYI9yTe3U6j0TA6OopOpyMiIoJdu3axfv161Go1iYmJ5OTkCELFLfrUajUSiURwb4yKiiIzM5OwsDDBJTguLo78/Hzi4+MXlZmx2WwYXbU+3VljExISkLjiawMCAoiJiSEgIACn08nMzAwjIyPMzs7i7+/P+vXrOXToELt27SIsLEwQaGazGa1Wi0KhIDMzk9WrVy/qd2hoKDExMXh7e2MymRgbG2NwcBCTyURsbCx79uzhwIEDFBQUCOLXPV5BQUHEx8cTGhqKWq1GpVIREBBAeno6+/btIyUlhaGhIbRaLWlpaYJQtdvt6PV6bDabIGDd1mmZK+lOTEwMISEhKJVKHK74YKvVire3NwkJCeTl5ZGYmEhYWJjQL71ez8jICFqtlpCQELZs2cL69esJDAwkMjKSNWvWEBoaikQiYXZ2FpPJRHx8PGvWrCE2NnZZ2Z+FmEwmZmZm8PX1JS8vj7S0NHx8fBZZ8mQyGQEBAcTHxxMSEoKHhwcmk4nZ2VnB/Tg4OJj09HQyMjIICwsDV3y00WgULI06nQ5/f382btzIvffeS0FBAb6+vkgkEkGomkwmtmzZwtatW7Hb7fT09NDb28v8/DwJCQnccccd3HvvvaxevVp4LiWuGqsRERFCfLLRaGRoaIihoSHsdjspKSnceeedHDx4ULD6S1y1gufn59FqtQQHB7Nu3TqSk5OXjZnOVb4oJCREWACQyWTo9Xoh8db4+DjT09N4eXmRm5vLwYMH2bJli7DwI3PFULvHUaFQCOOv0+lwOBwEBweTmZlJTk4OYWFhwoKBiIiIiMgnQxSqIiIiIv+DxPlpAzhXwOl0Cu6W8/PzqNVqAgIClk2oV8LpdDI3N8fY2Bh9fX2CO2lCQgIRERFYrVamp6eRyWQEBwcvSobjcDgwGAyMjIwwOjqK0+kkIiJCEIF6vV5wtQwKCsLX13fR5Not3tzxmEFBQYuEobuN0WhkdHSU/v5+NBoNcrmc8PBw4uPjCQoKQr6kvqXFYmFmZgaDwYCXlxeBgYEolUrhuE6nE5urrurg4KDgUupOmBQeHo5arcbT0xP5CvVf7a7yOboFNTp9fX1RqVQUFxfz61//mrGxMR588EEefvhhYmJisLuSP01PT6NQKAgJCVmWEMdutzM/P8/09DRjY2PMzs4C4OfnR0REhCBiJRIJFotFSPo0PT2Nt7c3sbGxREREIJFIhHqxISEhgvByn9+9CPBxmW3NZjMTExPMz8/j5+cnJNlaOh64+m42m5mammJ0dBSNRoPD4RCSRYWEhODt7Y1cLhcE4MzMDOPj42g0GiSuOqiRkZH4+fkJ53E6nZw7d45f/epXDA4Oct999/GNb3wDmUxGd3c309PTqFQq4uPjiY6OFrJFL+2j0+nEYrGg1Wrp7e1lYGAAi8VCYGCg8Kyr1WpkS0rUzM3NMTk5idlsJigoiICAgGVjZjAYmJqawmaz4e/vj7+/PzKZbJHr7uTkJHa7nYCAAKKjo4Xf51L3XbvdLgjUkZERZmZmAPD29iYkJITQ0FB8fHxWvEYRERERkZvD4XCg1Wppbm5mYmKCvLw84uPjlzYTEbllccuKr9qcwGKxMDc3h8ViQeLy4PPy8vpMEl2KXJvPRaiyQubdpRPgj8PuqjdpddV0XHoshaukyMKJPK7zOhbUMJUuyDS8sE+Sa2QevtE2CxPJ4LLkLe3LQtz94QaOa7PZcLoS1MzMzNDX14fNZiM6OpqIiAiUSqWwj/taF16jm8nJSd555x1eeuklVCoVTz/9NHfeeScBAQGLzufuz0p9YsE5lo7p0nvqHhP3MWVL6oiy5NpvZKyX4nC5MUtcVu6PY2nf3f1a6Xzudu4+LXx23DiXCNX777+fJ554gqioKOG+4bJ2L913JZyuEjfuZ0m6IOnTSvu6x8zd9nptWGFc3ffcfZ3u8610nIWsNI4rjY+IyK3Awt+J+zdwI8/pJ91PROSzwiEK1a8V7nfNp2Xpu+tG5kcL+Sz64TbkWCwWQcQtXUhf2M/Pcv7gnn/ezLzmRnG6jARdXV3U1NQwMDCAXC5n1apVrF69mvDwcLy9vZddq8hnw+fm+rvwI3+zD4vD4cBisTA9PU13dzcVFRVcuHCBCxcuUFFRISQz8vDwEOL+3Odw/0DdwnHhD+FG+nSjbdzn8PDwuCFRcjPHdR9TIpFQXl7O7373O65cuYJSqSQ2NhZvb29wuSrPzMwIZVM8PDxwuoSITqfj6tWrHDt2jJGREfLy8rjtttuIj48XXmDu812vT3zMmC5t5x6The2Wbgvbr/Tv12Nhn2+EpX2/lkhdqe21zuPO6KvVasnIyCA/Px8/P7+beh7cuM/p3u9652XBmN1Im5Wu80avcSlL97uZfUVEvijc3w6dTsf09LQQXoBrMXGl34T7nen2cJiZmWF2dpb5+Xkk11nYEhH5PHCKrr9feRa+c8xmM3a7HekKi/83gtPpxGq1Cp5Us7Oz2Gw24XjXO6a7H+7qDZ+2H6Ojoxw9epSioiLkcrlQ5s79d5vNhsFgYHp6Go1GI5RNdM8nPilOVyheZ2cng4ODOJ1OwSPts8BkMvHhhx/y61//miNHjlBSUkJNTQ0NDQ2LcuF4e3uL34nPgc/NovpJcSfwuXLlCsePH6eiooLp6Wnsrmy4bgIDA7njjjt4+umnSUtLE34MXyVsNhsffPAB//7v/47FYuGRRx7hgQceICoqCqfTydTUFB988AHvvPMOvr6+rF+/nrCwMObm5mhoaODq1auMjIyQk5PDY489xp49ewgKCoIFLw1c1j/xx3VjOJ1Ozpw5wy9/+UvBovrUU08RExOztKmIiMgXiNVqZWBggKtXr3L58mV6enowm82EuOo779mzR4gXd+NwOJifn6evr4+rV69y5coVwQ0/ODiYtWvXsmvXLrKzs/Hx8Vl0PhGRzwPRovrVxukK++nr66O6upr+/n6ioqLYsWPHTc8jnK5qAVVVVZw6dYqamhrm5+dJSkpi3759bNu2jaioqGu6plqtVoaHh6moqKCpqYm4uDh27txJTEzMNfe5FjabjTfffJNXXnmF5ORkHnvsMXJzc4VKB0ajkcbGRj766CNKS0vRarXExMSwY8cO9u3bR1xc3Ceex9tsNi5fvswrr7zC+Pg4Bw8e5P777yc4OHhp00/EuXPn+Od//meqq6vJyMhg7dq1+Pn54XA46OrqYnJykm9/+9scOnQIX1/fpbuLfEo+N4vqJ8FsNtPY2MhLL73EH/7wBxobGwkICKCwsJAdO3awY8cO8vLyBDN7ZmamkGDo06zG3Ko4HA46OjooLS3FZrORk5NDZmYmvr6+OF2uCO5yK9XV1Vy6dInTp09z7tw5WltbUSqV7Nixg0ceeYStW7cSFBSEzWZjaGhIyCgslUqFJEoiN8bo6CgdHR1IJBKys7PFSayIyJeIexJ08eJFfvazn/HWW2/R3d2NzVVPur29nfLycpqampDJZCQkJAjhEyaTidraWv7qr/6Ko0ePMjQ0hMPhQK/X09HRQWVlJc3NzSgUikX7iYh8XjhFi+pXFovFQm9vL++//z7PPfccb7zxBmVlZVgsFnJycoQydDeCw+FgaGiIt956i1//+tdcvXpV+PeWlhZKS0sxGAxCPfiFwtNsNjMwMMDJkyf5zW9+w+HDhykqKsJms7F69WoiIyNvek7Y3NzM4cOH0ev17N+/nw0bNgiibXJykg8++IBf/epXnDp1SvAAbG1t5dKlS0xMTBAeHi4kwLxZ3HPloqIiJicnSU1NJTs7W/A+/KS4rdUvvvgily5dIj09nR//+Mc8/PDDbNu2jYKCAhQKBfX19YyNjZGRkUFwcPBXUo98mdwyQtVisdDY2Mirr77K6dOnUSgU3H333Xz3u9/lwQcfZPv27RQWFlJYWMj27dvZuXMnubm5hIeHr5hg6KuA+8dXUlKyTKhKJBI8PT2Jjo4mJyeH7OxsMjMzycrKorCwkH379vHQQw9x4MABsrKyBNdUvV5PSUkJr7zyCpWVlaSmprJq1apP9HL4OiJxBdDHx8ezdu1a8vLyiIiIEEuziIh8iRgMBoqLi7l06RJbt27l4Ycf5sEHH2Tnzp0kJiYKNYpnZ2cJCwsjISEBmUyG0+lEr9fT2tpKRkYGjzzyCPfffz87d+4kPj6e6elp2tvbMRgMREVFkZSUtPTUIiKfKaJQ/erS3NzMH/7wB9566y0GBwexWq1YLBYiIiIW1Zi/ESYmJjh16hRvvPEGs7Oz3HPPPTzzzDPceeedBAcH093dTVNTE0qlkri4OHx9fZFKpTgcDvr6+jh8+DCvvfYaAwMDSCQSdDod0dHRbNy48bpW2JWw2Wy8++67XLhwgdzcXPbv3y9YZXU6HUVFRbz00kv09PSwd+9evve973Ho0CHi4+MZGhqivr4eqVQqVNW4WZHscDjo7u6msrISg8FAVlYWOTk5n1qo4jJMvPHGG3R1dbFv3z72799PbGwsarVacC8eGhqiubmZkJAQUlJSxAXNz5hbRqgODg5y9OhRTp06hUql4r777uOhhx5izZo1hISECKVn3DU+AwMD8fX1/cqKVD5GqOJK9uPl5UVISAiJiYlkZWWRn59PQUEBOTk5JCcnExwcjFKpFFZ45ubmaG1tpaioCIPBwObNm8nIyLjpF8PXGaVSKZQUcpdu+ao+gyIitzruGCc/Pz+ys7M5dOgQBQUFJCUlER8fL5Sx6unpoaurC39/f2ESI5FI8Pb2Ji0tjR07drBmzRqSkpKIi4sjJSUFp9MpZPOOi4sjKytLXJT6M8C5IEkdnyCZ45fJn5tQdYcRORYkdRRZmf7+fjo6OoiOjmbr1q34+voyMTFBSEgIW7duvWGh6jbsHDlyhM7OTrZv386jjz7K2rVriYmJISkpCb1eT0tLCxaLhdjYWCIjI4XKG+Pj49TX1+Pj48Odd95JSEgIfX19hIWFsXnzZqKjo29KqPb19fHWW28xNTXFnj17WL9+Pb6+vjgcDjo7O3nvvfeor68nPz+fp556ig0bNhATE8OqVauwWCy0t7czOTlJTEwMiYmJNy303EK1qqpKEKpr1qxZFObxSXA4HPT29nLs2DGmp6fZv38/hYWFguh3f3u0Wi11dXXodDoKCgoICAgQfwefIbeEUDUajZSWlvL2228zMzPDjh07OHjwIBkZGXh5eQkPxMLNHfC99GGw2+1oNBra2tooLi6muLiYlpYWdDodnp6eQjkV934OV+Kh4eFhZmZmkMlkwkN/5coVSkpKGBkZQaFQoFarkUqlWCwWBgYGKC8vp7S0lN7eXqxWK2q1epmPvcFgYHBwkOnpaeGck5OT1NbWUlRURHV1NePj40ilUlQq1aKXw8cJVTcWi4WRkRFqa2uprq5mcHAQu92Ot7e3sOJjtVrRaDT09PRQXV1NbW2tUO9TpVIxPT2NzWbD09NTSB7idi92Jw+6fPkyjY2N6HQ6VCoVXl5ey8b/64BUKkUul6NQKMT4XhGRWwCpVIqfnx9xcXFCOS+FQoGnpyfe3t54enrS2dlJc3MzwcHBbNiwgeDgYCQSCXK5nMDAQIKCglCpVMJv28vLC71eT3NzM5OTk2RkZFBQUHDTkyiRLxan08n09DTFxcVUVFQI5cxupDzerYLVamVqagqTyURERMTH1qD/srBarfT29nL+/Hmqqqowm83C7038Li7H09OTuLg41q5dS1xcHGNjY3R2dhIYGHhTQnVqaoqioiLOnTuHSqXiwQcfZNOmTULJPR8fH6xWK+3t7QwNDREeHk5qaqpQd14ulxMVFcW6devIyspibGyMmpoagoODP5FQLS4u5vjx44SGhrJ3716Sk5NRKBTMz89TXl7OsWPHsFgsHDhwgO3btxMQEIBcLhfm1C0tLXR3dxMWFkZKSspNh/Ndy6KqUqmEONyBgQE8PDxQKBRMT09TX19PcXExzc3N6HQ65HK5YNRxukpsDg0NUVlZyfnz59HpdKSmpuLn54fRaMRutwuawmw209DQQH9/P3l5eZ8oxlfk2twSQnV0dJSTJ09SUlJCZGQk9957L2vXrr3pDFo6nY7q6mqOHj3KW2+9xfnz56msrKSyspKSkhLa29uRyWQEBQUJL1KbzUZraytHjhyhtLQUo9FIQ0MDr732GseOHePq1auUl5fT398vCMnS0lJee+01/vSnP3Hp0iUqKiro6OjAbrcL9TnddHR08NZbb1FaWorFYqG7u5t33nmHo0ePcv78eUpLS6mqqqKzsxOHwyHUM+UGhKo7ecjx48d59dVXOXv2LPX19VRXV1NZWcno6KhQw3Zubo7i4mL++Mc/cu7cOQYGBtDr9QwNDVFeXs7ly5exWq1CVmG73U5fXx8nTpzgj3/8I2fOnKG6uprq6mrKysoYHBzEz8+PwMDAr6VYW7jYISIi8uUikUiEScjShU1csah1dXU0NTURHR3N9u3bCQ0NFfZ1L84t3Gw2G42NjZSUlGC329m6dSvr1q0TvU9ucWw2G319fZw+fZq6ujo8PT2JiYm5ZcXeUmw2G5OTk3R0dDA5OYlcLsfDw0P476303TGbzbS1tXH27FmqqqoYHBwUarl7eXl9pT3ePgmenp4EBQUREhKCxWKhqamJ5ubmmxaqQ0NDnD9/npaWFpKSkrjzzjtJSEhYZOVbePywsDCysrKE+EmFQkFQUBBhYWEoFAoaGhooLy//RELVbrdz8uRJioqKyMvLE96tMpmMqakpiouLKSsrIyIigrvvvpuUlBTBK0XiCqVy99PHx4f09PSbDqe6llBVq9XodDqOHDnCH//4R+RyOYODg7z55pscPXqUc+fOcfXqVaqrq5mYmMDb25vAwEAABgYG+MMf/sB7771HZ2enUMO+traW4uJiYb7s6+uL2Wymvb2d9vZ24uPjycjIEBc0P0O+dKHqdDrp7e3lww8/ZHBwkJycHCED2M2sqGi1WsrKynjjjTc4f/48JpOJhIQEUlNT8fX1ZXR0lLq6OoaHh1Gr1UI9Urdrwvvvv09lZSXDw8O0t7ej0+mE1Np9fX20tLSg1WoZHh7mypUrDA4O4uPjg7e3N9PT03R0dDAxMUFwcDAxMTGCZbW3t5fjx49TVVXF0NAQDQ0N9Pb24uXlRWRkJF5eXoyNjdHa2srw8DD+/v7C/k6n85pC1S1S33//fY4cOcL09DTp6elkZ2fj7+/PyMgIzc3NGAwGwsLC8PLyYmRkRDiPTqfD6XTi7+8v1LpKSUkhPT0dlUpFX18fH3zwAR988AETExMkJiaSnZ1NYGCgYL01GAxERkYSFBR0wy81ERERkc+LlSbFTleG9KKiItra2sjIyGDnzp1CBvSlOJ1ONBoNdXV1vPfeezQ3N5OTk8Ndd91FQkLC0uYitxhWq5XBwUHhe65SqQgICMButzM9Pc3MzMwtuWk0Gqampujt7aWkpISSkhJ6enro6elheHgYq6umvEajWbbvl7VNT08L7qwjIyNMT08zMjLC2NgY8/PzyOVyvLy8bjmB/WUhXVAnfXZ2lvr6elpaWm5KqLrnzJcuXWJ0dJScnBy2bNlCSEjIonZms5nm5mZaWloICgoiJyeH8PBw4V64+2GxWKitrf1EQtXpyjr84Ycf0tLSwrZt29iwYQN+fn5IJBKGhoYoKiqiq6uLVatWsWfPHiIiIhbN7RUKBY2NjTQ2NqJUKsnMzCQuLu6mPCCuJ1Tn5uZ47733OHHiBHq9nrq6Ovr6+lCr1YSEhGA2m+np6aGzsxObzUZcXBx+fn7odDpqamro6+tjcnISm82Gv78/KpUKT09PkpOTSUtLE4SqO7FpQEAA69at+0ziY0X+f750oWqz2ejo6ODMmTPo9XoKCwsFt6wbxWKx0NLSwltvvUVxcTHh4eEcOnSIe+65h40bN7JmzRoiIyOZnJykrq6O+fl5YmJiCA0NxcPDg8HBQYqLi2lra8Nms5Gamsrdd9/Nvn37WLNmDQqFgo6ODrq7uxkeHsbb25vdu3dz++23C/7oo6Oj9PX14ePjw6pVq4RVmZGREUpLS2lqamJqago/Pz927NjBXXfdxbZt28jJySEkJISJiQlaW1uxWq0kJiYSHh4OLovsSkJVo9Fw4cIF3n33XUwmE/fccw8PPPAAGzduJCsrCx8fH3p7e+nr68Pb25ukpCQiIyMF8T02NoZSqeTee+/l/vvvZ8OGDaxZs4bw8HB0Oh3nz5/n+PHjWCwWbrvtNg4dOsTmzZvJzMwkJCSEnp4eYSUwMTERlUp1UwsLIiIiIl8ENpuNpqYmzpw5g1arZfv27Wzbtk3wXMFlFRgaGuLq1avU1tZy6dIlPvzwQ7q7u0lPT+fgwYOsW7cOLy+vRccWufWw2WyMjo4KLtsmk4nJyUna29tpamq65bf6+noaGhoYGBhgdnaWiYkJxsbGGBsbo7u7m+bm5mX7fFlbc3MzPT09TE5OMj8/j8PhwGg0MjExwcjICEajEV9fX/z8/G7KQvZ14JMKVZvNRldXF1euXEGj0ZCfny+US1mI1WqltbWV5uZm/Pz8yMrKWmREcfNpherw8DAnTpxgcnKSnTt3kpOTI7wn+/v7KSoqYnh4mIyMDDZv3rxsgVAmk9Hc3ExdXR1SqZSsrCxSUlJu6l17LaHq7e2NyWTi0qVL1NfXMzo6SmBgILfddht33HEHmzdvJiUlBavVSldXF7Ozs8TGxpKQkICPjw/BwcH4+/vT0dGBxWLh7rvv5t5772Xbtm3CfFmhUGC1WhkaGqK6uhq5XM7OnTuX3Q+RT86XLlQtFouQotpisbB27VrWrFlzUzd5enqaCxcu8NFHHyGTyTh48CD33nsv6enphIaGEh4eTnx8PBKJhIaGBkZGRggJCSE1NRWVSsXQ0BAlJSUMDQ2Rnp7Offfdx2233SYk1VCpVHR3d9Pe3o63tzd33HEHd999N1lZWcTFxeHv78/k5CQ9PT14eHiQmZlJTEwMEolEEKrt7e0EBwdz1113cfDgQXJzc4mJiSE2NpaIiAjBhWZwcJDY2FjS09Px8PBYUagqlUq6urp47733aGlpYe/evXzzm98kLS0Nf39/QkJCCA4OZmZmhpaWFhwOBxkZGaxatYqgoCB0Oh2NjY1IJBLuvfdebr/9dpKSkoTU4O3t7XzwwQf09fWxceNG7r33XrKysggKCiI4OJjIyEg0Gg01NTXI5XLS09OFfUVERERuFdzW1OPHj3P58mWio6O55557yMrKWuTCa7PZqKio4LnnnuPs2bMUFxfT5Fod379/P7t27SI8PFy0Cv0ZYLPZGB8fp7m5mbGxMQwGA5OTkwwODv5ZbGNjY+j1ehwOBxJXrgiLxcLMzAzDw8PL2n+Z2/DwMFNTU4JIdePur81mIzIyksjISNEVcgmfVKi6kw+VlJRgNBrJz88nNzd3WYk89wJdfX09KpWKnJycFUtsfRqh6nBlED516hQWi4Xt27eTlpYmnKO3t5crV64wMTHB6tWrWbdu3Ypz+5aWFmpqanA6neTk5JCenv6ZCFW1Ws38/DxFRUU0NDQgl8t5+OGHOXToEFlZWcTGxhIbG4tMJqOnp4fx8XGCg4PJyckhKChICA8pKipCp9Nxzz33sH//fjIzMwWjj0QiweFwMDY2RllZGVarldtvv10wVol8er50E5g7Y5zdbhfcEW52MjA9PU1LSwt6vZ6UlBQKCgqE9NoymQy5XE5wcDD5+flkZ2ej1WppbW1lYmICq9UKrn6oVCpSUlLIyMjA398fDw8PIb7F/QOPiIgQHlJPT0/BhTclJQU/Pz+mpqYEN4GFeHp6smrVKjZu3Eh8fDxKpRIPDw+USiXR0dGsW7eO5ORkxsfHaWlpYWZmBqfTuegYbubn5+nt7aWnpwelUklaWhre3t6CS5BGo0GhUBAZGYmHhwejo6OMjIxgNpsXja/T6RQ+hnK5HJlMhtlspq+vj+7ubjw9PUlKSsLb2xu9Xs/MzAxarRapK424r68vw8PDjI2NCeMoIiIicqswNzdHeXm5sBC6bt061qxZs8y6I5FIUKlUREZGEhcXR1JSElFRUZhMJpqammhsbGRqamrRPiK3Lu5vp0wmIzAwkNTUVNasWUNOTs4tvWVnZ5OSkkJgYOAiDyWVSkV8fDzZ2dnL9vkyt6ysLJKSkgRXT4fDgcPhQC6XEx4eTkJCAsHBwct+byKfHIfDsSij9fXcqt0xq06n85rzyU+D05Vwc25uDoUred3CvjgcDmEu7O7LSrj/5n5+Puu+uo+XnJxMYWGhkAHZw8MDf39/UlJSSExMxGazMTw8jNFoBNf7Y2F/ls6X3dfj4eEhJC41GAzL5v8in44v3aLqcDgYHBykrKwMvV5PamoqWVlZBAQELG26Ik6nk56eHj766CMmJyfJz89n8+bNhIWFLWoncSXI6O3tpbq6Gm9vb7KysggPD2d8fJzi4mKmp6cpKChg/fr1wvklEomQYKmpqYmEhAS2b9++KKuXyWSiv7+fhoYGzGYzeXl5ZGRk4OHhwfDwMCUlJYyPj5OXl8fu3bsJCwtb9IOVSCTY7XY6OjpoamoiNDSUvLw8goOD6erqWmZRtdvtlJeXU1JSgsFgQKlUMjIyQk1NDXV1dYLrUF1dHW1tbUilUjIyMkhOTkYqldLZ2UllZSVWq5VNmzYJfQXQaDSUlpZSXFyMXq9HLpczNjYmHK++vp7GxkYaGhpobW0FIMdVCkfpyqgsIiIi8mVjsVioq6vjj3/8I01NTRQUFPDQQw+RlZW1LExBKpUSFBREXl4eW7ZsobCwkJiYGKanp6murqa/v5/AwEDi4uLESfctjs1mE75ZWq2W9PR09u3bx5YtW245obd0y87OJiEhAQ8PD4xGI3K5nJCQEKF80pYtW24pwZ2eno6Pjw/j4+NMTEwA4OfnR0pKCps3b2bbtm2kpqaiVqvFucESPqlF1W6309/fT3V1NXq9nqysLCHcayEmk4nq6mpqamrw9/ensLCQxMTEZbGfn9ai2tPTw/nz5wHYtGkTSUlJgnvx8PAwVVVVTE5OkpqaSkFBwYoW1ZqaGioqKvDw8KCgoOAzt6hevnyZhoYGMjIy2LVrFxEREYJHjUQiQavV0tzcLHg+btmyRQg/HBoa4uzZs8zOzrJp0yZWr169LNGr3W5ncHCQS5cuYTabOXTo0E2FL4pcny/dourh4YGfnx++vr5YLBYmJiYwGo03vKLicDiYn5/HaDQicdXEW+ra4EalUhEYGIhMJmN+fp65uTkcC9xV3GJ2KUv/fWkb998lC1aulvZfJpOhuEY5E6lUilqtxt/fH7lczvz8PPPz88uO4cZqtaLT6TAYDIyNjXHy5En++7//m1deeYVXXnmFl19+mcOHD1NWVoZMJiM0NBSVSrXsvCthsVjQ6XTMzc0xOjrK2bNnOXz4MC+//LJw7JdffpmioiIAgoODl734RERERL5MLBYLbW1tvP7665SUlBAfHy+EXCx0+XXj/nbExcWxatUq1q1bxyOPPMJjjz1GfHw8VVVVnD59msHBwaW7itxiSKVSlEolarUaHx8fwsPDSU5OZtWqVaSnp9/yW35+Pjt37mTLli3k5+dz++23c/DgQWFReWn7L3NzlxJxOBwolUri4uLYvn07DzzwAHfddReZmZlCSRSRzwa5q6yLO8Z+fn5+RQuexWJhbm4Oi8Ui/B5Wevd9WmQyGTKZTPDQc89bJa6MvmpXLVOTySRYgZcyNzeHyWQSvBQ/r+flWseVuEpeurnW3PtaLLQEy8VM1585K9+1LxCZTEZAQACRkZE4HA4GBgYYHR3FZDItbXpNFj5kdrt9kfhciN1ux2q14nQ68XCle7/RB+rjHly3OF0qapdyrePYbDYsFgsOl9vMjfRNLpcTFxfHgQMH+O53v7tse/bZZ/nJT37CY489Rl5envDC+Li+uv/mPvbTTz+97Njf//73+fGPf8zjjz/OmjVrblgIi4iIiHyeuJONvPzyy5w+fZqgoCAefPBBtm/fvszqsBD3d0QqleLh4YGPjw+FhYXk5uZit9vp6uqiv79/6W4itxgeHh6Eh4dTWFjI1q1bBQ8t94T6Vt7cLoTx8fFkZmaSlpbG2rVrycnJITAwUHA5vFU2T09PoqKiWLt2LXv27OGBBx7gvvvuo7CwUHD5FecFny0eHh54e3vj7e2Nw+FgZmZmxfny3Nyc8DeVSoWPj88NWUlvBokrZELlqldqsVgWzXFVKhX+/v7gqsyx1DiEy/AyOzvL3Nyc0E/Z5yCouc78W+IyMn1S7HY7c3Nz2O12VCrV59b/rytfulDFZZXLzMxErVbT3d0t1Om81urLQtzWSF9fX+FHazAYVnzotFotIyMjOBwOAgIChKLDH8dKx7pZ7HY7FosFm8227Hg2m03I7me1WgkICLhuwWO5XI6vry9qtZrQ0FB2797Nk08+yVNPPbVse/LJJzlw4ACpqanXtDQvxNPTE19fX1QqFREREezdu5fHH3982XGfeuopnn76aQ4ePEhKSopoVRUREfnSsbvqP7/wwgu89957BAYG8sQTT7B//36Cg4NvatIscVkE3CW8TCaTELskcusilUoJDQ1lz549PPTQQ6xfv16YLP854Z4nSF0lTW7m2f2ikMvlpKSkcO+99/LYY4+xe/duoqKihCQzIp8NS+eM3t7eBAcH43A4GBkZQavVLmszOzvL+Pg4EomE0NBQIe/KZ4lEIsHX1xd/f3+MRiN6vR673S70xc/Pj4iICCQSCaOjo4yOjmKxWBYdw13SyGq1EhYWRkhIiDAvdzqdQjzu0uu7lTCbzWg0GqxWK0FBQTekK0RunJWV0BdMUFAQ69atIzs7G4PBwLlz5ygqKmJ8fPyaD+hCq6C/vz8JCQnIXJm7+vv7mZ+fX9TeZrPR29tLY2MjCoWC+Ph4IaD688RttTSZTIyNjTExMYHZbF7UxmQy0dvbS29vL56eniQmJhIaGnpNoapSqYiOjsbPz4+RkRG6u7sXBbMv3dyrsO4Ph/u/C90V3Hh7exMbG0toaCgzMzO0trYyOzu74rEVCgUKheKa/RQRERH5orDb7YyOjvLb3/6WI0eOEBISwve//30OHDhw3Yy9DldykqU4HA5mZ2cZHR3FYDCgUqnw9fVd2kzkFkQmk+Ht7U1AQMCfpbeP+5u80tznVkIikaBQKPD39ycgIECcD3wO2O12QQSazWacTieBgYEkJSXh6elJX18fPT09ixbRHK5svMPDw4SHhwsu2p/1vZFIJAQHBxMSErLIgrtQqLpLvQwODtLR0YHBYBD2dzqdtLa20t3djUKhIDk5WVjocBtw3NmlV7LG3iqYTCYmJiawWCxERUV97rri68Zn+9R+QmQyGatWreLOO+8kISGB1tZWXnrpJV5//XVaWlowGo2CqHI4HMzNzTExMcHMzAx2u53Q0FByc3MJDAykpaWF06dP09zcjNVqxeFwCDWSjh8/Tk1NDeHh4eTn5xMQEPCFfcDm5+epra3l3Llz9PX1CX2bn5+nq6uLCxcu0N3dTUZGBvn5+cuCtReiUqlITU0lPT0do9HIhx9+yJUrV4TVLPc4Wa1WTCaT4FLMArcRhULB7Ows/f39wjg6nU6USiUpKSmkp6ej0Wg4deoUJSUlaDSaRffAbrdjNpuXuXqIiIiIfNHYXXVQf/7zn/Pqq68SGBjI9773Pfbt24e/vz8WiwWz2Sy8s9zC1GKxMDg4SGdnp/CedL/f3LWqS0pKkEgkJCUlkZCQsPTUIrco7kVikc8fcaw/P/r6+jh8+DC//OUvuXDhAhqNhsDAQHJcSSynp6c5d+4cvb29wvyvr6+P8+fP09nZSXx8PBkZGfj4+Hzm90gikRAUFER0dDQymYyRkRFhPgng5eVFamoqubm5WCwWLl++THd3N2azGYfDgVarpaioSOhneno6fn5+SKVShoeHefnll3n22Wf5t3/7Nzo7O1dcULwVMBqNDA8P43Q6hcSiIp8dX3rWXzcKhYLQ0FB8fHyYmpqiqamJsrIySktLhRWXtrY2ysrKOHbsGG+//TaDg4PExMQQFBSEt7c38/PztLW1UV9fz9DQkFA/raysjJdeeon33nuPgIAAHn74Ye68806CgoJwOp0MDAxQXFzM1NQUWVlZgoh1o9VqqayspL6+nqioKDZu3CiUfsElQjs6OqipqcFms1FYWEhmZiZyuVyoo9rb24ter2doaIjh4WF0Oh2jo6OUlJTwxhtvcO7cOby8vHjooYe4/fbb8fb2xul0Lqqjmp2dTWZmJv7+/iiVSlQqFSMjI5SVlVFbW8vg4CCTk5OC5fj8+fNCXaegoCDhxzM/P09dXR1NTU1MTk6i1WoZGxvDZrMJbscKhYKRkRFqa2upqamhr6+PiYkJ+vr6aG5u5ty5c1y8eBGn00lISIjo6iMiIvKlYLVa6enp4de//jUvv/wyJpNJ8LCpqanh4sWLXLp0SfhvS0sLUqmU8PBw+vr6+PnPf85//ud/MjExwcjIiJAZ/u233+b111+nt7eXwsJCvvWtb5GXl/eZWyVERBbidDoxm81MTk5iNBqJiIj4s3RdFrk+s7Oz1NXV0dzcjL+/P1u3biU6OnpRG4vFwsmTJ3n55Zc5d+4cVquVhIQEQkNDUavVWK1WmpqaqKurY3p6GovFQk9PD2+88QYnTpwgJCSEQ4cOsWnTpmsaZiyurL9lZWUEBQXdVNZfXGJ1fHyc+vp6rFYrq1atIjo6WpgTKpVKnE4nLS0t1NfXMzY2ht1uZ2RkhDfffJN3330Xh8PBfffdx549ewgODkYqldLR0cE777xDc3MzqampbN++ncDAwBWvweHK+ltRUbFi1t9Lly7R0NBAfHw8W7ZsISwsbFEc6dTUFDU1NbS2thIREcG2bdsICQkBYHBwkNOnT6PRaNiyZcuyrL92u53u7m4++ugj5ubmePDBB0lOTr7h8RP5eG4ZoSqRSPDy8iImJoakpCT8/f0xGAx0d3dTU1NDSUkJFy5c4PLly1RXV6PVaklJSRESJfj6+hIeHo5arWZqaoq6ujouXrzIyZMnOXv2LD09PaSkpPD4449z8OBBoc6qw5XA6cqVK0xNTZGdnU1eXt4yoVpRUUFdXR2RkZFs2rRpkVCdm5ujs7OT6upqrFYr69atE4SquzzN5OQkWVlZgsX4ww8/5Pjx45w7d46uri6io6P51re+xb333ktERARSqRSHwyEUdl5YnsbX1xe5qzZsVFQUEomE1tZWSktLuXTpEqdOneL06dOUlpYyNzcnWALcQd5ut4ShoSFaW1upqamhtLQUHx8fMjMz8fPzIzg4mPDwcHCt6FVUVHDx4kXh2EVFRRgMBjIyMkhMTBRL04iIiHzhOJ1OjEYjVVVV/Nd//Rfj4+M4nU4hbMFdnsG91dfXMzIyQnh4ODk5ORgMBurr6ykrK6O8vJwLFy5w6tQpzp49S11dHQqFQojT37Jly02VTBAR+SSIQvXrwcLyNNcSqjabjcbGRkpLS5mcnCQlJYXCwkJhrhscHIxSqWRoaIjy8nLOnj3LyZMnqampITo6mkceeYT9+/cTERFxTeFkNpuF8jA3W57GjUKhoL6+nq6uLhITE0lJSRFc7hUKBYGBgfj6+jI2NkZ5eTnnzp3j5MmTwrzz4Ycf5sCBA8TGxqJQKAQB/tFHH2Gz2di/fz/5+flCpuOluMWiW6iuXr2anJwcwYB14cIFGhsbiY+PZ+vWrcuEqrsMWWtrK+Hh4Wzfvl0QqgMDA4uEalZW1iKhOjs7S3FxMUVFRaxatYoDBw7cdD4Ekesjcd5ifptud9jJyUn6+vro7e1lbGwMnU6Hw+HAy8sLPz8/IiMjycjIICEhQchma7VamZiYoK2tjcbGRiFWVa1WExcXR05ODhkZGQQEBAhlYhyuYPTKykpmZmZIS0tj9erVi2o96fV66uvrhYc4Pz+f0NDQRRbV3t5eGhoasNvt5OXlkZKSgoeHBxUVFfzyl7+kurqaffv2cdddd6HT6WhubmZychK5XE5UVBTZ2dlkZWURGhoqBGI7XDWqqqqqsNlsZGRkkJqaire3t/B3o9HIyMgIzc3NdHZ2otFosNvteHl5ERwcTFJSEhkZGYLfP66X3/T0tFB3VaPR4Ovry+bNmykoKECtVuN0FXIeHh4WLNrT09NYrVaUSiVBQUEkJSWRnZ1NZGSkGDwuIiLypWCxWOjv7+fy5ctotVphAnKtiYK/vz85OTlkZWVhsVjo6+ujpqaGnp4epqammJ+fx9PTk9DQUFJTU8nMzCQuLu664RgiIp8VbpfI5uZmJiYmyMvLIz4+fmkzkT9ztFotLS0tdHZ24ufnx7p16wTjgBuHw0FHRwfnz59ncnKS/Px81q9fLwghq9UqWDPr6uoYHh4GIDIykoKCArKysoTkRNd6d1ksFpqbm6mqqhLyxYSHh99U5lqLxcLvf/97Xn31VdatW8cTTzxBVlaWYBSx2WzMzMzQ1NREdXU1fX192Gw2wsLCyM3NJScnR8gZI5FImJmZ4ciRIzz//PNERUXxt3/7t6xdu/aa80yHw0F/fz91dXUYDAbS09PJyMhApVJhMpkoKyujqamJ2NhYYfwWesZoNBoaGhro7OwkPDyc9evXCx6Xo6OjFBUVodVqKSwsZNWqVYvi3ltaWnjhhRcoLS3liSee4MEHHxQXlj5jbjmh6sYdA2kymTCZTFitVnDFs8rlcjxd9ZbkcvmiB85ut2MymdDr9UK6aA8PDyHttVKpXNTe6XRitVqZm5vDZrOhVCrx8vJa9CN1uOJiTSYTcrkclUolCF33381ms5DASaVSCT+4hUL17rvv5plnniEsLAydTofZbEYqlQp9W3pep9OJxVULyy3SV+q/3ZUa22g0CnFWHh4ewhi5rZ02mw2Hw4HMlVreZDKh0+mwWCyLMgm7j+90OrHZbMy7as66jy1z1YRVqVQolcpFYyEiIiLyReJwxeO7Y/Sv9y5yukqTeXl5CdZRm82G0WjEaDRictX6c3ueeHt7o1KprjvRExH5LBGF6tcD91zVZDIJc9SVhJjJZGJ2dhar1YqPjw/e3t6LrJ3u+Z9Op2Nubg5cc1A/P79lc8qVcDqdzM/PYzQa8XDlMFmpHx9HbW0t//Zv/8b4+Djf/OY3ufvuuxdZFt1GKJ1Oh9FoxOnKieLn5yd4+7nbtre384c//IFLly6xZ88ennnmGWJiYq77DjabzcJc2T2Pd3smzs3NMedKOLp0/FgwhmazGbmrTq27zcJvi1qtXjQH1+l0vP/++7z00ktER0fzl3/5l6xevXrZ8UU+HbeMUHWLRYfDgaenp/AwXK9713tona6swCxo93Ht+ZRtVvq7W6hWVVVx4MABnn32WRITE1dsfzPHXcr1xsnuSjRSUVHB8PAw6enpFBYWEhgYuGy/lc6xtM1CVmov8tlgd9X9lUgkyxZkREREFnO999RSlr633PsuPMbHvZdFRD4PRKH69eJm53crtVv6/pKskNxqdnaW4eFh7HY7kZGRQm1hNzfSj+thNBo5cuQI7777LmlpaXzjG99g9erVyzLgOm9gbl5aWsqLL76IwWDgO9/5Dps3b76m2+9Clh536b+v9Dc312uz0nEdDgcNDQ28+uqr9PT08NBDD7F//378/PyW7f9psbsy2o+Pj+Pj40NcXNyycf0qc0vEqNpdte9OnDhBVVUVTqeTgIAAwRJ4re16LG17o+2vx8e1Wenvw8PDlJaWMjIyQlpamiAQl/Zt6X4L+bi/c43rdW9Wq5Xu7m6OHz/OlStXUKlUrFq1Cn9//2VtV2Jpm49rL/LpMZvNQpz10NAQarV6kbVbRERkMUvfTRKXF8nk5CT9/f10d3czNTUlrJgvxO0C3NbWRktLC21tbQwODmI0GlEoFGJsqsgXhlOMUf3SMJvNjI2N0dzcTGNjI11dXczMzCCXywUL3fVwW+9GRkaE8jBjY2NCDdGl2/T0NHa7HU9PzxWtcHq9XijP4m630PLoZul7b+nfDQYDly9f5tixY0xOThIVFUVgYOAi77mxsTGamppoaGigq6uLqakpZDIZSqXyY62yuOJUAwICMLtqiur1esbGxujp6WFwcJC5uTmhrKFUKl2xr3Nzc/T391NSUkJ9fT1KpZK4uDi8vLxQq9Ufa+lderyl/770b7Ozs/T19TE2NiZ4La50rSvta3clhBoaGsLPz4+wsDDGxsbo6OhgeHgYk8kkWG+X7suCZ629vZ3m5mZaWlro7+9Hq9Uu8xZ1usr4vPvuuzQ0NBASEkJwcPCKff0qcktYVG02G8XFxfz6179mdnaWe++9V0h49OdORUUF//7v/y5YVH/wgx+QlJS0tNnnislkoqKigueff566ujruuusunn76acGy+0mx2+3MzMwwMTGBt7c34eHhX6tVns+T4eFhDh8+zIkTJ4iLi+Ob3/wmW7ZsEeKTRUREro3VaqWzs1OYePX396PT6UhMTOTee+9l8+bN4Pr2jI2NcfnyZYqLi4Vs8Xa7HaVSSWRkJBs3bmTHjh0kJiZ+bSYGIl8eokX1y8Gd3MidIXZmZgaAwMBACgoK2L9/P2lpaSivU3rEYrHQ29vLiRMnqK6uxmQyLW0CCyxzISEhbN26lR07dgjxqU6XK25vby9lZWXU1NQwNzfHjh072LNnD2FhYR8rmBfidDqpq6vj5Zdfpqenh9tuu40DBw4IiTjn5uZoamri9OnT1NbWotFowHXd+fn57N69m8zMTNRq9YqCy43D4aCrq4v333+fS5cuodFokMlkSKVSPD09hYoZu3btIjY2dpkwdydaKioqoqqqiuHhYWG/pKQktm3bxrZt2276+ldCp9PR2dlJeXk59fX1eHh4COO7MD/N9TCbzVRVVfHBBx/Q3t4uuHHb7XZUKhUxMTHs2rWLbdu2LcppY7PZGB0dFRJYtbe3o9FosFqtQuKp9evXs3fvXpKSkoTnrbOzk5dffpmysjL27dvH448/Tmho6HXvyVeFW8ai2tXVxalTp5iamiI9PX1ZQqM/V+bm5jAYDAQEBJCXl0dmZuYXLjbcKz9VVVWMjY2xatWqZSV4bhan08nExARnz57l+PHjWCwWYmJiFgWZi3xydDqdkC7dz8+PnJwcYmNjxYUAEZHr4HQ60Wq1XLp0iTfffJNjx45RX1+PTqdDLpcTERFBZmYmMTEx4JpYdnR08Nxzz9HU1ISXl5dQ/stdJq2jowOpVEpsbKxo2RL53BEtql88Op2OsrIy3njjDS5fvozZbBaSEPX09NDY2Mj8/DyRkZEEBgZec8HKbrczOTkpfLtnZ2cxGAzCZjQa0el0DAwM0NTUhEajIS4ujoyMDPz8/LBarQwNDXHhwgXefvtt3n//fYqLi+ns7BSSbvr7+9+UUJudneX06dMUFxeTkJDA7bffTlJSEnK5XChV+Oqrr3Ly5ElsNhvh4eEoFAp6e3tpampibm6OkJAQgoKCrmvRtNvtlJeXc/78ecbHx1Gr1QQEBCCXy5mamqKhoYGenh7kcjnx8fGLktPNzMxw6tQpXn/9dZqamvDz8xOSgOr1eiHRkY+PD7GxsYK35c3idDrp7e3l9OnTHDlyhBMnTlBWVsbY2BgxMTFCSZsbwWw2U1tby8WLF5mYmECpVAqlHUdHR6murqazs5OgoCCioqLw8vJCIpFgMpkoLS3ltddeo6ysDJurLKRKpUKv11NbW0tLSws2m43o6Gj8/f2RyWT4+PhgsVhoampicHCQxMREoXrJV51bQqg6XAWKr1y5wvz8PDk5OWRnZ38lhKpSqSQmJoY1a9aQmZlJcHDwF/5g2e12hoeHP1OhCtDb28sbb7zBRx99RHh4OHl5efj6+n6iF8gnxbkkGZZUKr2pl/itiju5QkxMDGvXriU7O/u6H0gRka87DocDg8HAiRMnePHFFykvL8fPz49NmzZx2223sXfvXjZs2EBSUpLgyutO8DEyMkJubi6HDh1i7969rF+/nvj4eDQaDa2trWi1WuLi4khJSflKvF9Ebo6VYtQ+Lz4LoepcIQ5QZGXsdjutra0cOXKEq1evEhkZyQMPPMB9991HYWEharWatrY2mpubCQgIIDk5GZVKdc33gFwuJzAwkFWrVrF27VrWr1+/aMvIyBA8OcLDw9mxY8eiDLXV1dWCYFOpVFgsFubn58nOzqagoICAgIBrnnslmpubOXbsGFqtlh07drBhwwb8/Pyw2Wz09/fzxhtvcPz4caKiovjmN7/Jfffdx4YNG/Dy8qKrq4uuri6USiWJiYn4+vpe99zT09OYzWays7O5/fbbhXdpVFQUGo2GtrY2pqamyMrKIioqSpjPVFRU8Nprr9HW1sbatWuFZEybNm0iPj6emZkZampq0Gg05ObmEhISct1+XAu73c6lS5d4/fXX6evrQ6FQYLFYkMlkZGVlCVUvbgSHw8HU1BQ2m421a9dy5513smvXLtatW0d0dDRDQ0M0NjbidDpJT08XrKo2m43Ozk6GhobIyMjgnnvuYf/+/WzZskV4Npqamujt7SUuLo64uDgh0ZZCoWBkZITa2lq8vLxYs2bNDcXu/rlzSwnVoqKiZULV6cp8azabAZC6sngZjUa0Wi1GoxG73S4IlI97KVssFmF1a25uTsgmvNK+7g+GVqsVzuVObrNSe7vdvqiv7lgCmSuDpFwuR+bKuOv+kbkzTrqP73Bl7F36I3S4MgubzWacTidSV6Ipo9HI7Owser0ek8mERCJZ5hN/M0LVYrGg1+sXXa9UKhWuxel04nA4MJlM9PT0cOHCBbq6usjMzGTNmjV4enpid2XedG8sEJR6vV5YZVx67E+CzWYTSvhMTk7i6+t701Zdd99MJpMgdiUSCfPz80Jflz5j7jHQ6XTo9XrMZrNw31Y6t/v+6fV6dDodBoMBs9ksPB9L9/Hw8CA0NJS0tDRSUlIWlVRaiPsZ0Gq1QqZrm80mPGML2y+8d+6Xs1QqZW5uTsgquNJ+IiJ/DphMJq5cucKvfvUrenp62LhxI48//rgw8UpNTSU8PFxY2cb1jvb19SUzM5MNGzaQnp5OVFQUUVFRJCYmCpOKqakpEhISyM3NFcp8iXy1cX8XZmZmGB8fx2w231Cc4qfl0whVd5+np6cZHR3F5qpksPBbLLIYrVbLhQsXOHHiBJ6entx7770cOHCA1NRUIiIiCA8PZ3JyUsifkpaWRnh4+IoGB6lUipeXF5GRkaSmppKenr5oS0tLw9PTk6amJsGte+/evcTGxiKTyQQBOz09zdq1a9m5cydarZaxsTFWr15NQUHBotjSj8NsNnP58mUuXLhAZGQk+/btIzExEblcjl6vp7S0lLfffpv5+XmeeOIJDh06RFJSEjExMYSHhzM9PU1TUxNms5nExEQiIyOv+/4LDAwkMzOTgoIC0tLSiI6OJiYmhqioKBwOB83NzYyMjAglHN3zxQ8++IDTp08THR3Ngw8+yPbt24mKiiI4OJjQ0FCcLvfl3t5eNm/eTEJCworzpo/D6bKo6vV6Nm3aRG5uLnq9HqPRKPT7RoWqVColKCiInJwc1q5dS2pqKlFRUcTExJCcnIxer6epqQmtVktBQQEJCQmCBvD29iYzM5OdO3eSn59PXFyc4OIcFRVFU1MT7e3tREREkJ6eTlBQkPBsabVaqqqqMBgM5OfnC3/7KnNLC1VfX1+MRiNdXV00NzdjcpWH6evr4+rVq5SUlNDY2Mjo6ChOV6prd6D2QpxOJyaTidHRUZqbmykvL6eqqoqmpib6+vowGo2L0lk7XTECIyMj1NTUcOXKFcrLy2lsbGRgYID5+XnkrhI57h+LWzy746LsdjtyuZzW1laKi4spKyujra0NvV4vZDV2xyGUlpZSXFxMfX09ExMTgjVNvqAkgtunvrOzUxCkIyMjlJeXc+XKFaqqqujs7MRoNOLp6bmobzciVG2u2qrNzc1cvXqV0tJS6uvrGRgYwGKxoFQq8XSV3JmdnaWuro6rV69SVVXFxMQEvr6+yGQyRkZG0Gg0KJVKYdXRfeympiauXLlCSUkJdXV1y4699L7dCPPz8xQXF3PkyBHGx8dJTk5eViPr47BYLIyMjNDY2Mj4+DhKpZLp6WlKS0u5cuUK1dXVjIyMIJFIhNWriYkJamtrKSoqorKykt7eXiwWC2q1etG1uJ+loaEh6urqKC0tpaKigtraWjo7OzEYDHh6egrp2d04HA56e3tpbGxkZmZGaLPwuAaDgb6+PsrLy7l69SqVlZU0NTUxOjqK1WoVnoOF+8zOzlJbW0tPTw9qtZq5uTkqKiooKipCp9Ph5+cnJm0S+bPDarXS29vLL37xC6qrq9mzZw8/+MEP2Lx5s+Cy5l6AWTq5kbncqtyJNCSuhUipVMrMzAwNDQ1MTU0JExJP0f3+a4HD4WB6epqqqiqhjmJYWNgNTWSdrrJxZleJPYvFct1F8YU4XYvzk5OTzM3N3ZRQdTgczMzMUFJSwrlz5zCZTERFRQnfbpHl9PT0cPLkSVpaWsjMzOTAgQOkpKTg4eEhzMVMJpMgLlNTUwWRtdKYut8fMpdRYuFmtVq5evUqp0+fxsvLi9tuu43CwkJ8fX3B9Wy4Q302b96Mr68vlZWVdHd3fyKhOjExwZkzZ2hrayM3N5cdO3YQEhIi/O3DDz+koqKCrKwsHn74YZKSkoQFcV9fX3Q6Ha2trWg0GiIjI1m1atU1Q9ckEsmisoUL36USV23U6upqNBoNmzdvJjMzE6VSicVi4fTp01RVVZGcnMy2bduIj49HoVAgcRlHNBoNZWVljI+Ps3v3blJSUoS/3wwSiYSAgAAKCgrYsGEDEomE+vp6pqamyMjIuCmhKpFI8PT0XDTnc1+vXC5nbGyMq1evYrVa2bFjB0lJSUI7X19fwsLC8PX1FcZb4jJaBAUF0dHRQXt7O/7+/uTl5REZGYlMJsPDwwOj0Uhra6vg/puSknJdl+yvAre0UPXx8WF8fJwPP/yQN954g8nJSfR6Pe+//z5vv/0258+f58qVK1RUVDAyMoJKpSI4OHjRirnD4RD8vo8ePcrrr7/Ohx9+SFFRESUlJVRWVjI2NkZISAiRkZF4eHig0+moq6vj6NGjHD58mLNnz1JdXU1FRQVlZWW0trYyPz+Pv7+/8KA5HA7GxsZ4//33ef311zEajWg0Gt566y2OHTvGhQsXKC4uprW1FavVilKppKenh6NHj/Lmm29y/vx5ioqKqKioQKPRCDEB7lW74eFhPvjgA06cOMHMzAwzMzOcOHGCN998k0uXLlFSUkJxcTENDQ3Mz88TEBCAr68vcrn8Y4Wq3W5ncHCQkydP8tprr3Hy5EkqKiqorKykoqKC7u5upFIpISEhKJVK+vv7efXVV3nvvfcYGBjAaDQKxZzLysqYnp4mKiqK8PBwJBIJw8PDnD59msOHD3P8+HEqKyuprq6mrKyM7u5uPDw8CAkJ+UQCyWKx0N7eTkNDA97e3uTl5REaGnpTx9Hr9ZSVlfHqq69SU1ODTCbj/PnzvP7665w7d46LFy9SXl7O9PQ0arUag8HAuXPn+OMf/8iHH34oJGLp7OxErVYTERGxyKrb3d3NsWPHeOuttzh79qwwtmVlZTQ0NAiTiYVuNRaLhffee4/nn3+e7u5uIiMjiYiIQKFQCJORq1ev8uqrr/LWW29x+fJlYUzLy8vp6elBIpEQGBgojKvVaqWvr4/nn3+eU6dO4ePjQ0VFBS+99BLvvfceTqeT1NRUQkJCVlwtFhG5FXE6neh0Oj766CNefPFF4uPj+du//VuSk5OZd9Xtm3fVuJYt8GZZiHui4MbpdKLX66moqKC0tBRPT09h9XvhgpLIVxebzcbg4KCwuGq1WklISCA4OBiHw3HdzWazMTMzQ0dHB62trQwMDDA8PIzVahVi85bus3Azm81MTExgNBoJCwvDx8dnWZuVNqvVysDAAOfOnePy5ct4enqSlpaGn5/fis/91x2n00lzczNnz55Fr9ezbt06Nm3aRHBw8KJ2RqORqqoqWltbWbVqFdnZ2Z9ovtLb28t7771HQ0MD2dnZ3HbbbcTFxQnfW6nLaubn54fSFSd/5coVenp6PpFQ7ejo4PTp08zPz7NhwwbWrFmDt7c3dleljffee4/e3l62bdvG9u3bCQwMFPaVyWRC6MPw8DBhYWGsWbNmUZuVWCoeHa75SlVVFSUlJXh5eXHw4EFSU1OFuXNtbS2NjY0olUrS0tKIiYlB6UoipNfrqa+v5/LlyygUCg4dOiQktlt6ro9D4jI2uMd3cHCQ8vLyTyRUWeG7get6dTodFy9epLS0lMTEROE+uwWle7+l+0pcQre6upr6+npCQ0MF12n3M2JxJexqamoiPDycgoICYay+qtzSQtXX1xeNRkNJSQkXLlygr6+PxsZGhoaGWL16NWvXrkWtVjMwMEBbWxsGg4Ho6GgiIiKEH4BOp+PKlSv85je/4f3332d+fp7k5GQKCwtJT0/H29sbtVpNWloacXFxmF2ZvP77v/+bY8eOIZVK2bp1K7fffjuZmZnY7Xbq6+tpaGjAbrcTtSDNt0ajobi4mHPnzjE0NERrayvT09Pk5eWRlpaG1Wqlo6ODnp4ehoeHqa6upr29nbi4OAoLC1EqlXR3d9PS0oJMJiMlJQU/Pz9kMhlTU1OCJbi/v5+mpiYhwH779u2kpaVhNpuF0gpSqZSYmBhhJfZaQtXpSop05MgRXnnlFWZnZ9mwYQN33nknubm5OJ1OGhsb6ezsxN/fn5iYGBwOB6Ojo8zOzqLVajGZTIKrS3R0NCkpKWRmZhISEsLExATHjh3j5ZdfZnR0lO3bt3Po0CHWrl2LzWajqqqK3t5e/Pz8iIqKumm3XYsrGYo76dAnEarz8/O0trZy5swZWlpahDIVsbGxrF+/Hh8fH0ZGRmhra2NsbIzW1lYqKiqQSqUUFhYSHx/PxMQETU1NjIyMkJKSIix6AHR1dQlB85s2bWLv3r3k5+ejUChobGykurqa0NBQIXZOIpFgsVg4f/48Z86cwcPDg9zcXBISElAoFGi1Ws6fP8+vf/1riouLCQsLY8+ePezcuZPExERmZ2epqqqivb0dpVJJbGwsarUah2sx5YMPPqDJlcjh0qVLTE1NERUVxbp168jOziYoKEicjIv82eBwOBgeHua///u/aWtr4xvf+AZr166lsrKSEydOcOnSJVpaWjAajXh5eaFSqVZciLFYLBiNRiGcoqqqiqNHj9LT08OmTZu46667iPoKZKIXuTHcnkDuUkVKpZKQkBBkMhkzMzNoNJprbuPj49TV1XHixAkuXrwozBmmpqbw9PTEYrEs28e9TU9PMzExwcDAANPT03i44tqWtrvWNjg4KGQMjomJISsri4AlNTNF/n8sFosggiQSCZs2bSInJ2eR1dDhin2vrq6mubmZlJQUYf50M/MMq9XKxYsX+eCDD1Aqlezbt4/169fjt6Tu5kIBMzU1RXFx8ScWqk1NTVy4cAGVSsWWLVtITU3F09MTs9lMW1sbJ0+eRKfTsWfPnhVFmk6no7m5me7ubkJCQsjPz/9YjzW3R8Dc3BxGo5HJyUkqKyt5//33BYvoHXfcQUhICBKXFXF2dpbu7m56e3uRSCQEBwejVquFfh47dozu7m527tzJ7bffLuz7SVg4vp9WqLIgrMv97Zienubq1au88soraDQa7r//frZt23ZD983tKXfixAnq6+vJyclhy5YthIWFLfr9Dg4OUlpaSnBwMFu3br3pPv+5ccsLVZ1OR2NjI1VVVYyOjhIXF8ePfvQjvvOd7yya8Hd0dDA6OkpQUBBJSUn4+flhMpmoq6vjxRdf5OzZs2RmZvKTn/yEZ555hrvuuotdu3axa9cutm7dSmpqKgqFgu7ubo4ePcrp06eFc333u99l69atrF+/nuzsbEG8DQ4OEhgYSHx8PGq1Gq1WS319PbW1tYyPj7Nq1Sp++MMf8uijj7Jjxw6ioqKYmpqitbWVjo4OlEolDz74IN/73ve47bbbyM7ORq/XU1dXh9VqJTk5WXCB0Gg0NDQ0UFlZSV9fHwEBAXzjG9/gBz/4AXfeeSfbtm0jJyeH+fl5IbV6REQEcXFxQgD2SkLVbrdz9uxZXnrpJZxOJ48++ihPPPEE27Zto6CggJSUFEHImUwmwe0lJyeHmJgY+vr6mJiY4K677uIv/uIvuO+++4QVILPZzNWrV3nttdfQarU8+eSTfPe732Xz5s2sXbuWzMxMwRXVZrORkJCwKI33jWCxWOjs7KS5uXmRUL2Zl5jJFW9bXl5OX18fMpmMb3/72zz77LPccccd5OfnC+dxj+3GjRt59tlnuf/++9m4cSOBgYG0trbS1tZGREQEqampgoXUz8+P7Oxs9u7dy549eygsLBQyQLufb4PBQF5enpB63Wq1Ul5eTnV1NUFBQaxfv57ExEScTicNDQ0899xz1NbWsmXLFv76r/+ab3zjG2zevJmNGzeSmpoqjOvk5KQQJ+Lh4SGs0HZ3d9PX10dGRgY/+MEPeOqpp9i8eTMRERGLXM5FRG513At0hw8fRqvVsmXLFt59912OHTsmuNlfvXqV4uJixsfHCQsLIyIiYtGkwWaz0dXVxYkTJ7h8+TLvvvsur7/+OkNDQ+zatYvHH3+cnJwccbL/NcLuKr/W2dlJX1+f8P9lZWVcuXKF4uLia25Xr16ltraWgYEB9Ho98/Pz6PV6RkdHaWpqEsJ9VtquXr1KWVkZTU1NdHV10djYKIShLG27dHOf1x0O5U7keCOT5K8jc3Nz1NbWCl4TGzZsIC0tbVmCmrm5Oerq6mhrayM+Pp6CgoKbrmPZ39/P22+/TXV1NWvWrOH2228nPj7+um6bn0aoOl1xnVeuXCEoKIjNmzcTGxuLXC5nbm6OlpYWioqKcDgc7N69m9WrVy+zzOldGXfb2toIDAwkNzf3mvG5bkwmE83NzVy6dImzZ8/y7rvv8u677zI2NsauXbt48sknSU5OXjR2QUFBWK1Wuru7qa2tFYwCzc3N/OlPf6K2tpbc3Fy+853vkJaWdt3z3wyfhVB1j9GpU6e4cOEC77zzDn/84x+ZmZnh0Ucf5eGHH15kNb8eTqeT9vZ2XnnlFQYHB7njjjuE5FcL7/nAwADFxcX4+PiwefNm/P39v9Jzto9/2m8RPDw8SExM5P777xdWY9RqNenp6dx2221kZWUJgndqakpwNyguLqaiokKYkD/44IMkJSXh7++Pn58f4eHhREVF4ePjg9FoFMSgVCrljjvu4K677iIwMBC5XI5KpSIzM5ODBw+yadMmjEajIG4cDofQV6mrlME999zD7t27CQoKIigoiIKCAjZu3EhAQABqtZpNmzYJNaX8/PyE4OqkpCQmJycZGhrC7ErM5MbpdBIUFMTtt9/OPffcQ2JiIl5eXvj4+FBYWMgjjzxCYWEh4+PjQmylOzZmKXa7naGhIS5fvszAwACbN2/m9ttvJyoqCoVCgVKpJDk5mS1bthAcHEyTq1SD3W7Hz8+PoKAgIa7X29ub0NBQQkND8ff3Ry6XMz4+TmVlJTMzM+zcuZP9+/cTHh6OzBWvkZ6ezq5du4iKiqKvr4/29nYMBsPSbgo4XcmAFm5SqRQPVyyJe8O1+OHenDdYKtjpinPevn07d9xxBwkJCXh7e5Oens6ePXvIzMxELpeTmJjI/v37ycrKwt/fn6ioKG677TZyc3ORSCR0dnYyPT0tPBO+vr7Ex8cL5XukUikKhYKIiAg2bNiAv7+/EB+78DlaCbelp7W1lYiICB5//HHWr18vuHn7+PiwadMmDh48SHp6OmNjY1RVVaHRaIRxcFtsg4KC+Na3vsXzA4+vAAB8XElEQVSdd95JRkYGoaGh14y7ERG5FXG6YsD7+/uZmJjAZDLx5ptvMjExwX333ccvfvEL/umf/ondu3czPz/PkSNHeP7552lvb190HLvdTlNTE7/97W/5xS9+wRtvvEFHRwfp6encddddZGZm3tBEQ+Sriduq5vbqampquu7mdpe0umojenh4IJPJmJubo6enZ1n7pVtbWxsDAwOMjo7S2dl5Q+d0bz09Peh0uqWXILICFldyzfn5eWSupJcr/c5lMpmQ/8RqtWKxWG54XoHrPVVTU0NNTY0QI7kw+/jngdWVvHJ+fl6IpXSLQ5sriafNZsPTlf9ipev28PAQYkEtrkShHzdHcee9ePHFF/mP//gP3n77bQYGBsjIyBDE+dJzBQYGcv/99/ONb3yDoKAgrly5ws9//nP+7u/+jjNnzhAREcEjjzxCdnb2LZcjQKfTUVxczP/7f/+PX/7yl7zzzjv09/ezfft27rnnHsFIcCOYzWZOnz5Nd3c3mZmZ5OXlLVuYkMlkqNVqvL29MRqN6PX6j70nf+782QhVmUxGTEwM6enpi9xDJRKJ4DaqUCjQu7LfWq1WRkdHaWlpwWAwkJubS35+/rKJuNsNwOnKnjo4OIhWqyUlJYXc3NxlbhkeHh5ERkaSlpaGVCqlu7ub4eFhLBYLuF5IUqmU+Ph4kpOTBeuURCJBrVYTHByMj48Pfn5+xMXFLXJhkMlkREdHExkZidlsZmZmBqMrq7EblUpFcnIy2dnZyyyHUqmUlJQUVq9eLfixT0xMXFOoOhwO+vv76ezsRKVSERoaitlsZnx8nOHhYUZGRgTRr1KpMBgMjI+PY3IVsXYLx4UCEteYLhx/k8lEUFAQNleh4+HhYYaHhxkdHUUmk+Hn58fc3BwTExNCLNlSnE4nk5OTNDU1UVVVJcS5VlVV0dbWxsTEBENDQ9TW1lJZWSm0qayspKurC6PReN0Pi/tvvr6+5OTkLBpbiURCaGgowcHBBAYGEhcXR0REhPDClEql+Pj4kJiYiLe3N7Ozs8zPzy8638Ixqaqq4tSpU5w4cYKKigoMBgMmkwm9Xo/Var1mP+12u5CUymq1sm7dOiGt/cLnQC6Xk56eTlZWFmazmY6ODmHSxIJr3bBhA5mZmfj4+CD7BPEeIiK3AhaLhampKbRaLVKplIyMDH75y1/y05/+lEOHDvHYY4/x85//nMcffxwfHx+qqqq4dOmS8M7G9e5NT0/nmWee4cc//jGPPPIIq1evpqKign/+53/mtddeY3x8fNF5Rb4+yGQywsLC2LRpE/fcc8/HbnfccQe5ubkolUr0rqyiZrOZ4OBgtm3bxj333MPBgweX7efe9u/fL4Ri7Ny5c9nfr7UdOHCALVu2EBERcc3viMj/4HSV8XGP1bUsle45HAv2uRmGhoYoLS1lYGCAtLQ08vPz8fucyy+63W8trgz/7oRyLJm7Lby2pSz89xu9ZpVKRX5+vuCV9tBDD5GQkMDVq1f553/+Z95++22mp6cX7WOz2WhubqasrAyNRkNqaip79uxh3bp1qNVqamtreeGFFygqKrquMePLwNfXl/Xr1/O9732PH/3oRzzwwAOkpKRw7Ngx/vZv/5aPPvqImZmZjxWTJpOJy5cv89prr2EwGLjrrrtYvXr1opw7btwLCPPz8xhd1UK+yqz8q7wFkbjKrihWSI3t4eEhZGx0//gsFgvj4+NMTU0REBBAamoqYWFhy264G5vNhlarZXJyEovFQkRExDXbq9VqwsPD8fX1ZW5ujqmpKebm5mDBS0yhUCxb+XFfg3t1dak4kLiypikUCuyuUjc2m23RMRQKBQEBAfj5+a24SqN2JfPx9fXFbDZjMBiWHcON0+lkenqa2dlZpqameOutt/jpT3/KM888wzPPPMPTTz/Ns88+yy9+8QvKy8vR6/XoXaVYlrL0JWa1WoXjjoyM8M477/CXf/mXPP3004uO/2//9m9UVlYyOzvL3NzcIlHuxul0YrPZuHTpEn/zN3/Dt7/9bb797W/zrW99i6effprf/e53VFdXc/bsWf7u7/6Oxx57TGjz6KOP8pvf/Iaurq5rjsP/195/R8dV34n//3P6SBpp1Ea9d0u2Zcu9YzCuOAYbsIFAyMlCSAKfsMkn+exmd7N88sluNrtnk03PZpMQujEm2OCKe5VtyZLVe+9dGkkzo6m/P75z70/VlinBJu/HOXMOWLfPnfe9r3d5vcdTqVTovRnrJv/7+M/k+0KhUMjrOZ3OCefhdDqpqKjgD3/4A3/7t3/LV77yFZ555hm+9a1v8cc//pGOjg6U3mzTNytwXC4XQ0NDtLe343Q6iY6Oxs/Pb8qx4O1KEx4ejtvtpru7m8HBwSnnHxMTMyGBkyDcjVwul9w6EBISwle/+lU5/4BWq8XHx4e4uDjuvfdesrOzaW1t5fr16wwPD8vbUKlUpKWl8aUvfYlvf/vb/Ou//iv/+Z//ya5du+jt7eXll19m//79oqXqr4zb7cblnZosPj6enTt38vzzz9/y8/Wvf51nnnmG3bt388ADD7Bt2za+8IUv8NRTT/HCCy/wjW98g2984xtT1nv++ef5xje+wbPPPsuOHTu47777ePLJJ6csM9PnueeeY+fOnSQkJOBwOHC5XB8psPproVar0el0aLVa+T1jumewy+XC4XDgdrvReOeznO65Ox23282NGzcoKCggODiYJUuWkJiYOOX98JPm9ib1Gt+AIFF5W4+VSiUul2vG83Y6nXLlufROe6v3Bb1eT3Z2No8//rhclv7rv/4r27dvp7m5mV/+8pccP36coaEheZ0LFy7wq1/9iuvXr7N27Vp++MMf8stf/pLf/va3vPTSS+Tk5JCXl8d//Md/kJeXh81mu2PuaYPBwJIlS3jmmWf4zne+w49//GN++tOfcv/991NaWsp//dd/ceXKFSwWy4zHPDY2RlFRET/72c9oaGhg+/btbNmyZcrYVMn4yoWZtvl5cvM77i4z/stzeydyHxsbQ6fT4e/vP6X//Xge79xlUgumj4/PjN0y1N6U5TqdDrd3IPXkIGA60z0wZirsxv/7+HUU3sHnMxUWUqAlHZtUuDLNvqRzttvtKLytymPedPrSx+6dcmXOnDksXbqUpKSkm15HidPpxGq14vDOOytdp8nb9/HxIS0tjUWLFsndmCdTeDOhxcbGyomttm7dyrZt29i0aZM8biI+Pp41a9awZcsWeZmtW7eSk5NDYGDgjNdstqb7/m7F4XBw5coVfv7zn/OrX/2KmpoaFi1axPPPP8/3vvc9nn76aWJiYma9bamrktvtlitnpqPRaNB758+TKjwmb1/jndNLEO52Su90MiEhIcyZM2dKLbTUEyY2NhaFQiFX3kgU3krCgIAAAgMDCQsLIycnhyeeeILFixfT0NDA+fPnqampkdcRPt9U3i52Ugb94OBgeaqYW31CQ0PJzMzkoYcekitlv/zlL3PfffcRFRVFUFDQlHWkj9E7RZjUZdjX13fKMjf7mEwmTCYTRqORgIAA/D5Cdtq/FjqdjoCAAHx8fHCO6w47nsc7vGBoaIixsTEMBgMGg2FW19TtdtPe3s7Zs2epqakhMzNTbk2d/D72SZOCcKlBwz1uGJRU1kmtcmazecp5423ls1gsKBQKDAYD/v7+0zaQjKfwTtvi7+9PUFCQPMTpiSeeYNGiRfT29vLhhx/S2dmJx+Oho6ODw4cPU1BQwPz583n00UdZsWIFsbGxpKam8oUvfIHnnnuOtLQ0ysvLOXr0qDwG+06gVCrR6/UYjUaCg4OJiIhg+fLlPPfcc6SkpFBWVsbFixdpb2+ftiHGarVSWFjIz372M65fv87q1av58pe/LE/BM5nHO1eyw+G47UqTu9Wtf2l3KYVCgUajQa1WMzY2NmNLoERaXq/Xo1QqsVgsM3ZDdTqdWCwWbDYbKpUKX1/faW+omcz2B/ZRbj6psJXGXIxvHZxuv1LQGxERwcMPP8w//uM/8oMf/GDK51/+5V/43ve+x7333ou/v//kzUyh9I4d1Wg0RERE8NBDD/G9732P//t//++02/7Od77Dhg0bCJxhvjilUsncuXN58skn+V//63/xzW9+kxdeeIGvfe1rbN26ldTUVHJycvjiF7/ICy+8IC/z4osvsm3bNiIiImb1YJnJdNduNqRpfy5cuEBkZKTckvr000+za9cu1q9fT0hIyISHyM2MD0BtNtu0BR/eANnmnW9XqlT5OOcvCHcqjUYjj9G2WCzTtgxMLt9v9XtTKBT4+PiQnJxMeno6Pj4+dHd309nZOXlR4XNK5e3ue8899/D000/Lz5HZUCqV6HQ6goKC5NwNJpNJHmZxK1LF5c3u0emo1WoiIiLYtGkTzz33HFu2bCEkJESU/TOQviOpB1p/f788tEni9o5PHhgYQKPRyLk5ZvN+5nQ6uXHjBtevX8ff358lS5aQlJT0qbem4j03qYFmfCMM3kA1JCRE7hU407Cr4eFhhoaGUKvVBAYGThjnOltKpRJfX1/i4uJITU1FpVJRVVUlt6jW1dVRVVWFx+MhKyuLrKwsOXmQWq0mNDSUnJwcFi5ciEqlkpNETlfO3wmkd67s7GxSU1NRKpU0NDTQ19c35X3NYrFQUFDA7373Oy5evMjcuXN58cUXycnJmTKkS+LxNiiNjIzg6+s760qTu9nn9uw0Gg3BwcEEBATI2fq6urpmLPjVajUBAQGEhoai0Whob2+f8aVkdHSUjo4OrN65VE0m07QtgZ8Gh8MhD/6f7lykcaRjY2NyjepMNWBKb0Zaf39/7HY7Rm922qVLl075LFmyhOzs7AkZ36T9K6YZ4yC9PPr7+6PwjiPOysqasl1p2/PnzycqKmrGgF+hUODv709kZCRxcXHyJyYmRn5wGAwGIiIiJvxdGges+wySBHk8HhoaGigrK0OtVrNq1So2bNhAZmYmERERBAUF3dYDS+kdCytN/tzQ0MDw8PC090Fvb688BjgyMpKQcXPyCsLnidS1NzQ0lKGhIWpqauTx2BKPx4PFYsFsNuN2u+WWpltRe4dpMK4rnfDXQXrhTElJYfny5WRkZHyk57z0fPxLPH+kY05LS2Pt2rVkZGTIFZvCVCqVipCQEMLCwrBYLLS0tEwYEoC3229nZye9vb2Eh4cTFxeHrzcp4s24XC66u7s5d+4c1dXVZGZmfmK9u2ZD6U1y6evri9WbdVoqv1QqFUFBQfLcntOdt9s7bKizsxO9Xk9kZORHuv8Z1ytOrVajUChwuVxyoDk4OMjw8DAqlQqDwSBXJkqkng3SO8zo6OiU8l0qm++k4FU1bojY+POVWCwWrl+/zssvv8zFixfJyMjg+eefZ8WKFQQEBMz4m3V4k2Q5HA4CAgLkoP7z7HN7dlqtlqioKFJTU9HpdBQUFHDp0iX5RWUyKRBKSEggODiYhoYGrl69SkdHx4TlbDabnDLe5XKRmppKTEzMXywIsHozXFZXV0/ouoa39q66uprS0lJ0Oh1JSUmEhYWhmSH9udKbnTgpKYnh4WEKCgpobGzE5XKh0Wim/Yz/8UkvcR7vmGC73S5fW423JTU5ORmPx0NRURGtra0ovC0b4z9arRaNd6D/TD9OyfiH/vhlpWBtcvA8ebm/JI/Hw9DQEGazGZ1OR2hoKIGBgXJhbbfbaWlpwWw2z+o4VSoVoaGhcvbhgoICrl+/jtlsnhCsjoyMcOPGDXkC7fT0dMLCwm67JlQQ7nSKcS2fWVlZWCwWPvzwQ4aGhib8JpxOJ42NjdTX1xMYGMicOXMICAjA4+1GNd0zweVy0djYSE1NDRaLBaPRSGho6OTFhM8xqWXU399/1q1onzWltyui1Jp2NxzzZykyMlJu+aqpqaGmpkYO2lzeKYpu3LhBa2srSUlJpKSk4OPjg9vtpre3l7KyMiorKxkcHJxQjtjtdsrKyrh+/To+Pj4sW7aMlJSU26qc/jgUCgWBgYEEBAQwPDws51+R/hYUFMS8efPw9/enpKRELuekcrOrq4vy8nI6OzsxmUykp6fj7++P2+1maGiIkpISSkpK5LLW4x3jK42LHm9sbIy2tjbq6uoYGxsjNjZWnqvWYDDg4+OD1Wqlvb2dvr6+CRWCbrdbbhyy2+1ERUVhMBhQKBT09fWRm5vL+++/z7Vr12aVtOij6O3tpbCwkIqKCoaGhnB7x65PN6SKcVnk6+vrsdlsRERETAgoLRYL+fn5vP7661y9epWsrCyef/551q9ff8tu4SMjI3R3d6Pwzjf71/Abv2MCVelGn/zf4/9+M9I60nIqlQqTycSKFSuYP38+DQ0NvPnmm+zdu5e8vDy5QJJShnd1deHj40NmZibZ2dk4nU6OHTvG/v37qa6uxmw2093dzaVLlzhw4AClpaWEh4ezfPlyYmNjp63RuNkxz/S3m10DvD+AlpYWjh07xtGjR6mvr2d4eJju7m4uXLjA/v375bm+Fi1aJM9LOvn64H2gxcbGsmbNGmJiYrhy5Qqvv/46p06dklugOzs7qa6upqCggPr6+gndQwwGg5w6u7q6mmvXrlFZWUlHRwdjY2NERESwYsUKoqKiyMvL48033+TUqVPU1dXJNXVVVVXTbvt2THdut8szLgvercx2Xwpv5YfBYJBbelpaWrBarfT29pKbm8uJEyfo6emZVUEjPXgWL14sTz3zxhtvcPz4cTngbW1t5fjx4xw8eJDW1lZSU1NZsmTJhBTnszl2QbhbqFQqoqOj2bZtGwaDgWPHjnHgwAGqqqowm8309PRw5coVDh06RH19PXPmzGHFihXodDrMZjNnzpzhzTffJD8/n5aWFnp6emhqauLSpUvs3buXq1evEhgYyIIFC0hMTJy8e0H4xM3meSB8MkwmEzk5OSQlJcnvVtevX6enp4eWlhZOnz7N2bNnUSqVcrCp1WoZHBzkzJkz/OxnP+PXv/41Fy9elLuzulwuent75XHtc+bMkacauZ0K4/HvNh/luR0eHk5UVBRms5m2tjY56adCoSAgIICcnBzS09Npb2+X553u6+ujvb2dU6dOcfbsWTweD9nZ2aSnp+Pr68vw8DAXL17kF7/4Bf/xH//BhQsX5ED49OnTHD58mOvXr9PU1ERXV5c8vv/dd9/lxo0bGAwGVq9eLc+skJSURGZmJhqNhqtXr/Lhhx/KAe3Y2Bh1dXUcO3aMvLw8dDodq1evlhOdlpeX8/rrr/P73/+e/Pz8Kd22Z+tm19dut3Ps2DF++tOfyok7R0ZGaG5u5tSpUxw9epTCwkJaW1vp7u6moaGBs2fP8uqrr1JZWUlMTAyLFi2SEyOZzWYuX77Ma6+9xsmTJ/F4PGRmZuLn50d1dTVXr17lypUrXLlyhby8PLq6uiYE7n19fTQ0NKDT6UhISJixF+Lnieqll156afI//qW53W75ZrZarcyfP5/58+cTEBDA0NAQN27coLi4mLCwMFatWkVcXNyE9fv7+ykoKKC2thaTycTSpUuJi4tDpVLJg7/b29upqKigsrKS6upqSkpKuHLlCufOnaOmpoagoCA5C6pOp2NgYIDy8nIqKyvlmqBLly5x6NAh8vLyCA4OZuvWrWzYsIHo6GgUCgVDQ0MUFBRQXFxMVFQUq1evJioqSg4QbDYblZWV5OXl4Xa7WbJkCZmZmXJyIrfbTUdHB5cuXaKtrY3s7GxycnIwGo0MDg5SVFREVVUVLm8GuubmZurr66murubSpUu8//77XLlyhaCgILZv3869994rj6lpa2sjPz+fzs5O0tPTWbRokTw/rNFoxOl0UldXR3l5uRzEl5SUcO3aNc6ePcvVq1dxOp3ExsbK3XlVKhVdXV3ynG8tLS1yd9Tg4GBMJhMBAQFya4Y0cbTUIj1+2y6Xi5iYGLmmbLbsdrvciiwVvGFhYdNWHMxEaiXPzc3FarWydu1aMjMzJ9R8dnV1cfXqVZqamkhKSmLJkiWYTCZ5P1arVZ4yJyQkhHXr1skVGG1tbVRXV8vT/TQ1NZGbm8vp06dpa2uTkyOtX7+e9PR0dDodTqeTK1eukJ+fT0hICMuWLSMpKQlfX1/8/PzQaDS0tbVRXFxMY2Mjra2tVFZWcvbsWd5//32qqqpITU3loYcekieEdrvd9PT0cPbsWRoaGli2bBmLFi0iQGT+Fe5iCm8vjZCQEMxmM+Xl5VRVVdHa2kptbS1Xr17l/fffJy8vj7CwMB5++GHuu+8+fHx8aG9v55VXXuHtt9+murqayspKbty4wYULFzhy5Ajnzp3D4/GwceNGdu7cSVpa2m29aArC7fJ4eyj19vZitVrlBE7Cp0PtnTXC4XDQ0NBAZWWl/C6Tm5vLsWPHaG1tZe3atTz88MNykpu2tjYOHTrEgQMHaGpqIiwsjPT0dAIDA7FarVy7do133nmH/v5+OYNzUFDQbT1re3t7uXDhAnV1dcybN29KpfOtaDQampqaKCsrkxtiQkNDUXq74Uq9BBobGyktLaWtrY3m5mYuX77M4cOHaWlpYcmSJezYsUN+V+3r6+ODDz7gnXfeoaioiNjYWDIzM2lra2Pv3r0cPnyY4uJiKioqKCws5MKFCxw9epTLly+jVCq5//772bVrF/Hx8ahUKnx8fFAqlfT29lJTU0NDQwPt7e00NTVRUFDA8ePHOXr0KAMDA9xzzz3s3r2b+Ph41Go1586d48CBA5jNZhYvXsz8+fNnnAlhOi0tLVy9epXe3l450ZXU0ov3t2ixWPjDH/7AoUOHaGpqIjk5mZSUFKqqqti7dy/Hjx+fcL7nzp3jgw8+4Pz58xiNRnbv3s2WLVuIiopCrVZTVlYmX6euri7UajVOp5OSkhIuXbrEpUuXuHz5MhcvXiQ/Px+TySQPi3O73RQVFXH48GH0ej27du0iMTHxc/9MuiMCVY/HQ39/P83NzQQEBLBw4UIyMjLw8/OTuwMMDAyQlJTEsmXLpiQ0GB0dpa2tDavVSmJiIosWLZKT50jTtUjBi9lspqmpifr6elpbWxkZGZG7U0qBkjRmQaVS0dPTQ1lZmdzsPzo6SkZGBl/4whfYsmULiYmJco2G1Wqlra2NoaEh0tPTpwQzTqeTnp4eurq6CAkJYcmSJXLtnHQdhoaGaGpqQqFQsGjRInmeSylQbWhoICYmhsWLF6NUKiktLeXq1avcuHEDs9lMWloaDz74oDyxsnRzDw4OytOgzJ07l3nz5sn94AMCAoiKipID1q6uLmpra6mqqqK+vp7e3l60Wi2pqamkpqbi702mpNVq0ev1uFwuefu9vb0EBASQmppKREQEgYGB8oPWbrfT0dExYds9PT1oNBpSU1NJSUmRg+DZcrlc9PT0MDg4SHR0NHPnziU4OPi2tuFwOOjt7aWzs5PAwEBWr15NcnIymnFdpoeHh2lubsbpdJKZmcmCBQsmPHSkioOenh6Sk5NZsWIFERER8pgLu91OZ2cnFRUVlJeXy/fAmjVr5LGqy5cvJzk5GZ1Oh91uJzc3l+vXr2MymVi+fLmchEGv1xMVFUVwcDBOp5OWlhZKS0spLCykpqYGhULB4sWL2blzJ+vXr5dr8tzepBD19fU4HA5WrVrF3Llzb7tyQBDuNFKlZFJSklxuV1ZWcv36dUpKShgdHWXOnDk8/PDDbNmyRZ5n0mKx0NTURGdnpzye/MaNG1RVVTE8PExcXBxbtmxh586d8ryYwp3P7c3639fXR29vLwMDAwwODn6iH7PZjNlsZmBg4BPffm9vL83NzfT29qLzZvD/JPcxNDQkfwYHBz/RbUsfaX5HtVo968Dqs+Lr60tISIjcSFFZWUlRURG1tbWo1WpWr17N7t27JyS5GRkZoa6ujtbWVgIDA1m0aJH8PB0ZGaGwsJD6+noyMjLYsWMHGRkZE94pZmNkZITGxkacTicLFy4kOzv7tiqWtVotZrOZsrIyhoeHiY2NJTY2Vu4uqtPpCAsLw9fXl4GBAaqqquTyT6lUsmLFCh566CGWLl0qvy9arVbq6upoaGhAr9ezZs0auRdiW1sbbW1tNDY2UlZWRlFREdXV1YyOjpKcnMzWrVt5+OGHJzQESEOapPe2vr4+Kioq5Ir/trY2goKC2LBhA3v27CErKwu9Xo/VauXUqVNcu3aN9PR0Nm/eTFJS0m21MA4MDNDa2opKpSI7O1uet3Q8t9tNQUEBTU1NhISEsHr1atLT07FarbS2ttLW1kZ9fT0lJSXyPWO1WklLS2PXrl1yMKn1Zuetrq6msLAQq9VKaGgoAd5EXoPe36VUrgwNDWG1WsnOzpbfC/v6+jhz5gxXrlwhOzubHTt2EBQU9Ll/f1N4Zmrv/gtyewdtl5eXY7PZSEhIICEhAR8fHywWCw0NDdTV1WE0Gpk7d+6UcUIjIyPU1tbS1taG0WgkPT0dk8kk/116IWlubpZb/4aHh9HpdERERJCamkpycrLcLcPj8WCz2Whvb6e4uJiysjL6+vrw8fEhMTGR+fPnk5qaitFolGsyPB4Po6Oj1NfX09DQQHBwMJmZmROCJrvdTltbGzU1NbjdblJTU4mLi5MLL+lhVF5eTl9fH0lJSSQnJ+Pr60tdXR2vvPIKR48eJTU1lS9+8YsEBwdTXFxMfX09breb2NhYFixYQEZGBsHBwfK4WWmcRU1NDf39/URHR5Oamjql5shsNlNfX09VVZUc+Gu1WkwmEwkJCaSkpBAeHj6hIHA4HDQ2NlJUVERTUxMqlYqMjAyys7PlYN/tdjM8PExjYyMVFRVy91e9Xk9oaOiEbd/u+A2n00l7ezvNzc34+fmRlJQkF6izJQXQ1dXV2O12MjMziY2NnTDueHBwkIqKCnp6eoiMjCQtLW3Cfux2OzU1NVRVVWE0Gpk3b55cc2mxWKitraWwsJC6ujrcbjfx8fEsXLiQ+Ph46uvraW9vZ86cOSQkJKDT6ejv7+cnP/kJr732GtnZ2Tz//POsXr1aTgDj8abMr6uro6CgQB5fYjQaSU1NZf78+cTHx0+YmsDtdmM2mykpKaG9vZ2MjAxSUlJmzC4nCHcb6VlSWFhIcXEx3d3daDQaEhMTWbBgAenp6RPGANntdnp6eqiurqaiooK2tjZGR0fx8fEhJiaGOXPmMGfOHEwm018sD4Hw8Y2OjlJaWsq1a9fo6emZ9Yv97XC73bjdblTTzKv9cdlsNrq6uhgdHZWns/kkX9U84+bsVs4iN8TtcnunT5OSM4aGhn7i+/ikSd11S0tLuXHjBp2dnfj6+pKenk5OTg4JCQkTKqqsVqs8BlWj0bB48WLS0tLQ6XSMjo5SUVFBc3MzYWFhU94FZ8tsNlNRUUFnZyfx8fEkJyffdsVyQ0MDv//977l48SJr167lySefJDk5WX53dXsbMkpKSsjPz6e9vR0fH58J5z3+HUHqgXbhwgVcLhf33HMPaWlpeDweOjs75R550jukXq8nJiaGzMxM0tPTCQ0NnbYstdlsNDc3U15eTnV1NV1dXSgUCqKiosjKymLu3LkTcq40NTXx4x//mHPnzrFr1y6efvppuZV2tnp7e6msrMRsNhMXF0dKSsqUykiPx0NeXh4XL17EaDSyevVqEhMTcTqd8ntjbW0t7e3tWK1WDAYDcXFxzJ07V86FMP6YWlpaqKiooL+/X/5NS7/F8TweDxqNRh5yolarycvL49e//jX19fU8++yz7Ny5c1ZJAe92d0SgKhl/KON/iDP9+3i3s4zH2x9dMS6BzXTrjL+JpP+WCvXplmcWxzH5ct9qGenvtbW1vPLKKxw5coT09HS+/vWvs2zZMjkQ5BM4Nj7CNWLcstK6Cm+Gt8mm2zbe5Wfa9myN3/dHdavr83H+Lp2z2+2Wz1f6TLdedXU1P/nJTzh+/Dhr1qzh61//OgsXLpwSyEvrSvfo5G1PZ7r9CcLnifRbk+712ZSN49eRlv00XuKFT19nZyd79+7lvffew+PxfOzpySYbGxujubmZ/v5+4uPjZ3z5/ig84yrWzWYziYmJhIWFTV7sI/N4K6VbW1txOBxER0d/4oGk1Mq8atUqvvKVrzBnzpzbCiA+S1IZMJvnqbQck95jZvr3j+LjPq+lfCt/+MMfUCqVPPHEE9x7771TkvZI5Z/0jnKzMlNadrprM74sZdz5T15uOtK5ji+7xx/LeOfOnePHP/4xTqeTZ555ho0bN2I0GicsMxuzub4zna+0rvR3j8cz4brdbHu3Q6FQ0Nvby969e9m3bx9ZWVl861vfknsQfd7dUYGqMLPxgWpaWhpf+9rXWLFixW13JRHubC6Xi5GREY4fP87vfvc72traeOSRRz5SbaEgCMJfo9bWVt544w2Ki4tZu3Ytq1at+sQCVYVCQX9/P4cOHaK4uJgHH3xQ7hL6SbxOud1uOjs7OXLkCHV1dezcuZOlS5fCR3jBnY7H46G+vp7jx49jNpvZuHEjOTk5KCZVmn5UCm+Sm8OHDxMSEsITTzzB3LlzP7FAXrh97e3tvP3225w/f56cnBz27NlzVwc5Ho+Hd955h1deeYWcnBwee+wxUlNTP7fvwx5vq+4f/vAH+vr6ePLJJ7n//vvx9fWdvOjnkghU7xK1tbX86U9/kltURaD6+WO322lububKlSu8/fbbXL9+nQULFvA3f/M3bNiwgYCAgMmrCIIgCJO0trby1ltvUV9fz0MPPcT9998/Y+vGR9HT08PevXu5du0aX/rSl1ixYsUn1gXP5XLR3t7Ovn37KC0t5emnn2bdunWTF/vIPB4P1dXV7N+/n/7+fnbu3MmqVasmL/axFBUV8eabb6JUKtm9e7cIVD9jbreb+vp6CgoKUCqV5OTkEBsbe9e+P7pcLvLy8qirqyMjI4OMjIzP9RAmp9Mp508IDg5m1apVfxVjUyWfTBWj8KlTeDNb6vV6tFrtJ1Y7LNw56uvr+dGPfsTf/d3fceHCBZKTk9m1axcrV66cMJ5YEARBuDW3d75DqRviJ8Xj8cjbdU0zb+TH5XQ65fl9P41jd46b71L6fJI847p+Cp89pVJJSkoKO3fu5Atf+AJxcXF3dcWBUqlk8eLF7Nmzh5ycnNvK9Hs3UiqVzJkzh8cff5xt27Z9pPHOdzMR7dwlpGzI27ZtY926dURGRopg9XNG5U3VPn/+fL75zW/yH//xH+zevZvw8HDxXQuCIAifiMlj7D5Nn0YgLHw0arUarVaLWq2+qwMdhUKBWq3+VBKZ3YmUSiVarRaNRvNX+S7413fGd6nQ0FC2bdvGd7/7XZ566qm7enyBML3ExER+/OMfs3//fv7xH/+RpUuX3naGP0EQBEG4GSl4/Es8WxQ3SSojCIJwKyJQvUsoFApUKhUajeaurw0TpqdWq/H19cXX1/evtuZMEARBEARBEBCBqiDcWUQFhCAIgiAIgiCIQFUQBEEQBEEQBEG4w4hAVRAEQRAEQRAEQbijiEBVEARBEARBEARBuKOIQFUQBEEQBEEQBEG4o4hAVRAEQRCEzxVpCpZPcw7Pv8T2P02f5vY/7WsjCMJfBxGoCoIgCILwueLxeHC73ZP/+RMhbdvtdn9qmdql7X9apHP4NILJ8ZUEn8b2BUH46yECVUEQBEEQPjc0Gg2hoaGEh4fj6+v7iQeTGo2G4OBgIiIiMBgMn/ic11qtluDgYMLCwvD19Z38549FoVCg0+kIDg7GZDLh4+PziV8fvV5PaGgoISEh6PX6T3z7giD89VC99NJLL03+R0EQBEEQhLuRUqnE19eXiIgIkpKSCAoKmrzIx6JQKNBqtURFRZGWlkZAQMAnFqwqFAqUSiV6vZ7o6GhSU1Px9/efvNhHJm3fz8+PmJgY4uPjP9Ht473+BoOB+Ph44uPjP5XKAkEQ/jooPKJfhiAIgiAIgiAIgnAH+WSqAAVBEARBEARBEAThEyICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y4iAlVBEARBEARBEAThjiICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y4iAlVBEARBEARBEAThjiICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y4iAlVBEARBEARBEAThjiICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y4iAlVBEARBEARBEAThjiICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y4iAlVBEARBEARBEAThjiICVUEQBEEQBEEQBOGOIgJVQRAEQRAEQRAE4Y6i8Hg8nsn/KAiCIAiCcDdyu9243W6k1xulUolSqUShUExedIrx6yoUChQKxazXBfB4PBP2PZl0LLcibQfvOrPdP+PO4aMc+/j9TiZta6btjT/3j3LtBUEQJhOBqiAIgiAIdz2Px8Po6CjV1dWUlJTQ09ODn58fGRkZzJ07l5CQkBmDRI/Hw/DwMFVVVZSWltLX14e/vz+ZmZlkZWURFBR0y2DL7XbT399PeXk5zc3N8r9LAZyPjw9paWmkp6ej1+un3Z7H42FsbIz29naqqqpwu91kZWURFxc347FLXC4Xo6Oj1NfXU1NTQ3h4OAsXLsRgMEy7r/HcbjdDQ0NUVlZSX18vB6sKhQKPx4NerychIYHU1FSMRuOU7blcLgYGBqioqKCqqoqBgQE0Gg0JCQlkZWURExMz4zkLgiDMRASqgiAIgiDc1TweD729vRw7doz9+/dTXl6O1WpFrVYTHx/P1q1b2bVrF8nJyVOCJY/HQ3d3N4cPH+bPf/4zlZWV2Gw2OdDavn07u3btIi4ubsq641mtVq5fv87vfvc7Tp8+PaX1MSwsjN27d/Pkk08SFhY2JfC02+20trZy8eJFjh49SnFxMTExMXz9619n69ataDSaCctLpAC9vLycY8eOcebMGZqbm9m4cSPf/e53iY2NRa1WT15tAofDQWlpKb/5zW84evQoeINUSVhYGFu3buXxxx8nPT19wt9sNhtFRUXs37+fCxcu0NnZicPhAMBoNLJ8+XIefvhhVq5cSWBgoLyeIAjCraheeumllyb/oyAIgiAIwt1iZGSEU6dO8fvf/57BwUG2bNnCzp07SUxMpLm5maKiIrRaLenp6fj4+ExYd2hoiA8//JDXXnsNi8XC1q1b2blzJ7GxsTQ2NlJcXCy3zOp0ugnrjmexWCgpKSE3NxeNRsPGjRu55557yMnJIScnh8WLF7No0SLi4+PR6XQTgj2Hw0F9fT179+7lrbfeor6+nqGhIdRqNUuWLGHOnDmoVKoJ+5OMjIyQm5vLq6++ytmzZ+nu7qa3t5fIyEjuuecegoKCpgTFkzmdTmprazl69CgOh4Pt27ezZs0aFi1aJB97Tk4OSUlJ+Pn5yccutQBfu3aNCxcuEB0dzUMPPcQDDzxARkYGw8PDlJeXMzAwQFRUFJGRkTOehyAIwmQiUBUEQRAE4a7ldrtpaGjgrbfeoq6uji1btrB7926WL19OYmIiHo+Hmpoa+vv7SUxMJCEhQV7X6XRSWVnJW2+9RUtLC1u2bOHRRx9l6dKlJCUl4XQ6qaiowGw2k5aWRnR09IR9jzc8PExxcTG1tbVkZWXxxBNPsG7dOhYsWEBOTg7Z2dnEx8fj5+c3JXB0u90MDg7S3t6OyWRi8eLF2Gw2bDYby5YtIzMzc8ZW0bGxMTo7OxkdHWX+/PkkJSXR2NhIeHg4GzZsmFWg6nA4qKys5MKFCyQlJfHVr36VNWvWyEF2dnY2iYmJBAQETAg0pVZjX19f0tLSuPfee1m1ahVz584lMzMTo9FIU1MTbW1thIaGkpSUhMFgmLBvQRCEmdy85BIEQRAEQbiDjY2NUVNTQ3FxMZGRkaxcuZLk5GSCgoKIi4uTg86GhgZKSkpwOp3yujabjerqaqqqqoiLi2PlypUkJSURFBREbGwsixcvJj4+ntraWoqLi+UkQdOx2+0MDQ2hVCqJj48nMTGR8PBwoqKiiIqKIjw8HH9//2mDRpVKRXR0NNu3b+epp55i+fLlBAcHT15sWr6+vsyfP589e/bwyCOPkJGRgVarnbzYjDweD3a7ncHBQTweD/Hx8cTFxREZGTnh2I1G47Tdj6Uu0qtXr2bevHmYTCaMRiNRUVHMnTuXlJQUXC4Xra2tmM3myasLgiDMaGppKQiCIAiCcJewWq00NzdjNptJTEwkLi4OvV4PgE6nIzo6mpiYGKxWK01NTQwNDcnrjo6O0tzczNjYGImJiXLSn/HrxsbGMjw8TGNjIzabTV53MinYs1qtOJ1OBgYG6Ovrw2az4XK5bhrkKpVKDAYD8fHxxMfHy8cwG2q1Wm6tDA8Pn7HldSYejwebzUZfXx9OpxOVSkVPTw+9vb3yudzs2PEGq3q9HrVaLXcLVigUaLVafHx8UKlUclIpQRCE2RKBqiAIgiAIdy2bzUZ3dzcKhYLw8HACAgLkVkuVSoXBYCAwMBClUkl/fz+Dg4Pyularla6uLpRKJaGhoRPGX6pUKgIDAwkNDcXtdtPb2ztji6DH48HhcGA2m2lra+PixYv8/ve/53e/+x179+4lPz8fs9k860DNM26Kl0+bFKgODg7S399Pfn4+f/jDH/jtb3/L66+/Tm5uLj09PRNaomfD7XYzMjLCwMAACoUCk8mEv7//5MUEQRBmJAJVQRAEQRDuWlKXWykoHd+qhzfg9PHxQaPRYLFYsFgsMClAk8ZZjm+NVCqV6HQ6fHx8UCqVWCwWRkdH5b9PplarCQ8PJzY2FofDwY0bN3j//ff59a9/zW9+8xtOnTpFf3//rIPVvySlUklwcDBJSUmo1WoqKio4fPgw//3f/81vf/tbjh8/Tnt7+20Fq2azmZqaGlpaWggMDCQ1NZWgoKDJiwmCIMxIBKqCIAiCINy1XC4XY2Nj4A0WJ48BVSgUKJVKlEolLpdrQrDldDoZGxvD4/GgUqkmBLgShXcuUafTicvlmvxnWXBwMBs2bOBrX/sazz77LE888QQbN24kJCSEixcv8uqrr1JQUIDNZvuLtZbOhkKhwGg0smbNGp577jmee+45nnrqKbZv305kZCQFBQW888475ObmTug2fTM2m42qqiouXLjAyMgICxYsYM6cOVMyLguCINyMCFQFQRAEQbhrKZVKOcmP2+2eEgR6PB5cLhdutxu1Wj0hIZBKpUKr1crB6HTrut1uFAoFGo1m2mRCeIO9wMBAFi1axLZt23jwwQd54oknePHFF3nhhRfIzMyksLCQCxcu3HGtqkqlkoCAABYsWMC2bdvYvn07e/bs4Zvf/CYvvPACCxcupLGxkUuXLtHW1jblGk3mcDhobGzkxIkTlJeXk5KSwr333nvLeWgFQRAmE4GqIAiCIAh3La1WS0BAAG63G4vFMqV7qsvlwmaz4XQ6MRgM8vQoCoUCvV6P0WgE73jV8S2mbrcbu90uJ1Dy9/e/5dQqk7scBwYGsmTJEtauXStPAdPT03PTltnPisI71Yz03/7+/ixYsIBVq1bh4+NDQ0MDvb29Nw2ynU4nLS0tHDlyhDNnzhAaGsq2bdtYuHAhvr6+kxcXBEG4KRGoCoIgCIJw19Lr9ZhMJjweD93d3YyOjsqBoMvlkhP6uN1uQkJCCAwMlNf18fHBZDLhdrvp6+vDarXKLYYul4vBwUF6e3vlZEvjkwHdqmWRcZlvg4ODMRgMjI2N4XA4ZrXunUCv1xMSEoKPj8+UbtOTOZ1OWltbOXjwIO+99x5arZYHHniANWvWiLGpgiB8JCJQFQRBEAThruXj40NsbCx6vZ6Ghgba2trkMatjY2O0tbXR1taGwWAgMTGRgIAAeV0/Pz9iY2NRKBQ0NDTQ0dGB3W6fsG5raysBAQEkJiai0+lwu91YrVZGR0cnBJ3TdR2Wlu3t7cXpdE7JSvxZcDqdcmIoh8MBMxy7x+PBYrHIrahSsD1d912Xy0VXVxfvv/8++/fvx8fHh0ceeYRNmzYRFhY27TqCIAi38tmVlIIgCIIgCB+TTqcjNTWVjIwMmpqayM/Pp7OzE6vVSk9PDzdu3KChoYGEhATmzp07IUjU6/WkpqYSHx9PbW0t+fn5dHR0yMFlSUkJjY2NpKSkMH/+fACGhoa4du0aJ0+epL6+nrGxMZxOJ8PDwwwODjIyMoLNZsNmszEwMEBBQQHnzp1Dr9eTk5NDZGTkrOc6nS6AnK3p1nM6nXR2dnL58mXOnz9PS0sLdrud0dFR+vv7Jxy72WymtLSUy5cv43Q6yczMJDIyckrQ6XK56O7u5r333uPVV19Fq9Xy+OOPc//99+Pn58fIyAjDw8NYLJY7ssuzIAh3LtVLL7300uR/FARBEARBuBsolUr0ej0Oh4Nr165RUVGB3W6nv7+f8+fP8/777zM6OsqOHTvYtGkTOp1OXleaukaaTqa6upqxsTH6+vo4ffo0hw8fxuVysWvXLjZs2IBSqeT69et8//vfZ9++fTidTubMmcPY2BhHjx7l2LFjNDQ00NfXR11dHSdOnOAPf/gDxcXF3HfffezZs4eIiAhUKtWEcxjP6XTS3t7O1atX6evrY8WKFWRlZc0quLXb7ZSXl3PhwgVMJhMbNmwgKChIDs4HBwc5duwY//7v/86hQ4cICAggKiqKvLw83nnnHerq6hgcHKSpqYnTp0/z6quvUlJSQnZ2Ng8++CAZGRkTEkpJXab379/Pr371Kzo6OkhKSsJoNFJfX09BQQEFBQWUlJTQ3d2Nv7+/PCZYEAThVkSgKgiCIAjCXU2n0xEWFoaPjw/V1dWcOHGCQ4cOUVBQQGhoKI899hgPPvggJpNpSougXq8nLCwMlUpFRUUFx48f59ChQxQVFREWFsbjjz/Ojh07MBqNuN1umpubuXDhAhaLhczMTBYvXoxSqaSgoIDDhw9z8OBBDh48yAcffMDVq1fR6/Xs2bOHr3zlK6Snp6PRaKYcw3hOp5Ouri6Ki4uxWCwsX76cOXPm3DS4lTidTurq6sjLyyMiIoJ7772XwMBAOVC1WCzU1NRw48YN7HY7OTk5pKWlUVdXx4EDB3jvvffk47906RIAW7du5YknnmDBggX4+vpOOHan00ltbS1//vOfyc/Pl4PsvLw8Ll68yIULF7h48SJ5eXkMDAyQmppKQkKCvL4gCMLNKDzT9Q0RBEEQBEG4i7hcLvr6+igtLaWyspKhoSGCgoKYM2cOc+bMISQkZMZgz+Vy0dPTQ0lJCVVVVQwPDxMSEkJmZiZz5syZ0CrZ09PDlStX6OvrY/78+WRkZKBWq+ns7KS6uprGxsYJyZtSUlLIyMggODj4lkEq486joqKC4eFhMjMzSUhImNW4VqfTSXNzM0VFRRiNRhYvXozBYJDXdTgcNDc3U1xcjN1uZ968eSQmJjI0NERVVRX19fXyeNqgoCBSUlJIT0/HZDKh1WqnHIPUolpUVERzc/OUv+PtgqxSqYiIiGDevHlERkZOXkQQBGFaIlAVBEEQBOFzwe12MzY2Jk9Ho1ar8fHxmTbImsztdsvjM10ul7yuTqebEFy6XC55Khu9Xo9Wq5X/3W63Y7fb5ey4arUanU6HTqe75f7Hc7lcjI2N4Xa70el0qNXqWwa4eINCh8PB2NgYSqUSHx+fCfv1eDw4nU5sNhsejwe9Xo9Go8HtdsvrSQmi1Go1er3+lsfuGjf9z81I12I2XZgFQRAQgaogCIIgCIIgCIJwp5m5ikwQBEEQBEEQBEEQPgMiUBUEQRAEQRAEQRDuKCJQFQRBEARBEARBEO4oIlAVBEEQBEEQBEEQ7igiUBUEQRAEQRAEQRDuKCJQFQRBEARBEARBEO4oIlAVBEEQBEEQBEEQ7ihiHlVBEARBuIt4PB48Hg8KhQKFQjH5z4IgCJ+5yeGFKKuEj0IEqoIgCJ+x2RbDn+cHvRR4CTPzeDw4HA6GhoZwOBz4+/vj6+uLSqWavOgE0v3ldrvlf5OCXHHNBeHjkyqPpN/Y+N/XX+NvzOPxYLFYGB4eRqlUYjAY0Ov1KJU378gpXcfxz0Rpnb/G6yiIQFUQBOEzNzw8zOjoqPySM7lYVigUaLVaAgIC0Gq1E/52t3O73dhsNsbGxtDpdPj6+k5eRPByu920tbVx4MABWltbuf/++1m6dCkBAQGTFwXvfWS32xkdHZWvscvlQqVSodPp8PHxwcfHB61We8sXSEEQpnK5XNjtdiwWCyMjI1gsFlwuF1qtFoPBgMFgwMfHB7Va/VcVaI2NjZGfn8+ZM2fQ6XTcd999ZGZmotfrJy8K3rLNarVitVoZGxtjbGwMt9uNSqWSyym9Xo9Wq/2ruo6CCFQFQRA+c4cOHeLs2bMMDQ1NqU32eDyo1WpSUlJ45JFHSEhI+Nw8qD0eD4ODg+Tn55Ofn092djb33XcfOp1u8qJ3LY/Hg8vlwuPxoFKpPlZA6HQ6KSkp4Xvf+x5VVVW88MILPPbYY0RERExeFI/Hg81mo7KyksOHD9Pc3MzAwAA2mw2NRkNoaCjp6eksWLCArKwsTCbTLVtmb0VqUXK5XCiVStRq9eRFcLvduN3uT+R6CMJnRaoE6uzspLS0lMLCQioqKujo6MBut+Pn50d8fDyLFi1i/fr1JCYmotFoJm/mUyf9Jt1uN0qlEqVS+Rd5foyMjLBv3z5+9rOf4e/vz4svvsimTZvw9/efvCgAZrOZy5cvk5ubS2trK4ODg9jtdnQ6HREREWRmZrJo0SIyMjLw9/f/2OXG+HJZqVROW/a53W6cTqf897/EdROmUr300ksvTf5HQRAE4S/nrbfe4s033yQ/P5+Ghgaampqor6+nvr6euro6mpubAViyZAnh4eGfmwemx+Ohrq6OP/7xj7z66qv09/ezfv16DAbD5EXvSi6Xi76+PsrKyqirqyMwMBAfH5/Ji82a2+2mu7ubU6dO0dfXx7Jly5g3b96010uqBDh+/Dj/9m//RmlpKU6nE5fLxdDQEJWVlVy4cIG8vDyGh4eJiIggJCTkI99bUmDc0NBAfn4+brebwMDACS+ATqeT3t5eKisraW5uRq1Wz9gaLAh3KrfbTV9fH2fPnuW3v/0tf/zjH7l06RJdXV3g7ao6MDBAeXk5zc3NpKSkkJycPG3FzafNYrFQW1tLTU0NVqsVPz+/v0jAbLfbKSsr49q1a+h0OlasWEFycvKMlZCdnZ289dZbvP7661RWVsplVV9fHzdu3OD06dNcu3YNlUpFdHQ0vr6+HytYHf/9APj5+U0pq1pbW7l8+TJ2ux1/f380Gs1HLh+Fj04EqoIg3JXGtzre7Q+PM2fOkJ+fT0ZGBk8//TS7d+9my5YtbN68mU2bNrFp0ybuuece0tLS8PHxuevPdzybzUZnZycjIyOsXLmS1atXz/gyczfxeDyYzWbOnz/Pr371K4qLi1myZAmhoaGTF501t9tNT08PZ86cobe3l+XLl980ULVYLJSWlnLq1CkiIyP57ne/y549e9i0aRMrVqwgMDCQuro6iouLUalUpKenT7ut2XC73bS2tvLaa6/xyiuvEBoaSkZGxoTvcnh4mLNnz/LKK69QUlJCbGwsCQkJE7YjCHcyj8dDb28vH3zwAS+//DJlZWUkJiby4IMP8thjj7Fr1y62bdvG+vXrWbx4McuWLSMnJ4eQkJCPFVh9VGVlZbz22mucOHECtVpNYmLiR/6N347Jgery5ctvGqgODQ1x6dIl6urqyMnJ4Stf+Qq7d+9m48aNLFq0CLVaTVFREcXFxcTHxxMbG4tOp/vIz8Jz587xu9/9juLiYsLDw4mJiZGH1UiVfG+99RY///nPCQgIICUlBYPB8JH393knvY99GtfnL/+rEQRB+Bg83oQyg4OD9PX1MTY2NiFovRtJhXt0dDQrV66Ug9NNmzaxefNmNm7cyJIlSzAajeBtqZO6LU1H6n7pHpc8R/o3idT1yeFw4HQ6Jyw7k/HrOByOGY9BWk7apvT/TqdzSgVDREQEe/bs4d/+7d946qmnJoxRHd9NVPp/p9M5477HH9v49Wbi8Xjk7c20TWk56Vik/5+8r8k83q6B7e3tVFRU0NvbO+G6jN+PtH3pWKTvY7pjkcz2hUDhTeYSEBBAdnY2CxYsYPHixWzYsIEnnniCdevW4XQ6KS0tlVsXJht/bNNdW+m8zGYzjY2NtLW1YbFY5FYRafmxsTE6Ojqor6+nt7dXvuaTtye51X4lk6+r9P8zfZ+C8FFZrVYuXLjAu+++S09PDxs2bODFF1/kK1/5Cps3b2bp0qUsXLiQVatW8eCDD7Jt2zZiY2OndC29nd+8tOz4+3vyutOt53a76e/vp76+nra2NkZHRyf8Jm+17emOx+19jtyqzJTMtpySaDQaIiIiyMrKYsGCBSxZsoQHHniAr33ta8ybN4/m5mauXbtGT08PrnHPMyY9Z8Zf08nLuN1u2tvbqampobu7Wx67P/4ajI2NUV9fT3Nz87Rl2eRtjr8m0+1XWu5m1/pu5fFWyvb19TE8PHzLe+J2iRZVQRDuCh5vUDEwMEBBQQGHDx+mrq4Ok8lEQEDAZ1Jb/Uk5e/YsBQUFxMfHs3btWuLi4uTEEdJHo9GgVCpxOBw0NjbS2dmJwptkafxL0NjYGF1dXbS3t+NwODAYDDgcDlpbW2lra8NoNOLxeOjq6qKhoYHGxkZ6enpwOBxoNJoZk344HA56enpoaGigurpaDkZUKtWEZDweb0teQ0MDIyMjGAwGhoeH5ZclvV4/ofur2+3Gbrfjdrvx8/PDz88PhUIhB3l9fX1otVqcTidtbW3U1NTQ2trK6OgoarUanU6Hx+NheHiYhoYGampq6OjowOl0otPppj0f6UWkt7eX+vp6ampqaGtrw2q1TrjWeINfs9lMR0cHo6Oj6PV6LBYLTU1N1NbW0t7eztjYmLyeQqHA7XYzODhIfX09eXl5FBYWotVqmTt3Lm63G7PZLB+b0+lkcHCQtrY26uvraWhooLu7G7vdLl9b6fjd3q6/p0+fpre395Zdfy0WC2VlZZw9e5bQ0FB27NhBRETEhHuqra2NyspKNBoNixcvJjExccI2rFYrHR0d1NXVUVtbK7/YqdVq+XzHxsbo7u6mrKyMS5cu0dLSQmpqKiaTSU4uMzY2RnNzM1evXqW0tBSVSkV8fDw+Pj4MDw+j0Wjk1ha3243FYqGzs1PuAt/V1YXdbpf3K30/UpnQ3t6O0zuerK+vj6amJgYHB9FqtTMmcBGE21VdXc2+ffsoKipi4cKF7N69m6VLlxIaGir/pqV7VKfTodPpJpTPUlBjNpvl33xjYyO9vb3y/a1Wqyc8z2w2G93d3QwMDMjr9/b2ysNEBgYG5GeBNAbVZrPR1dVFYWEhV69eZWhoiIiICIKDg3E4HHg8HjQaDQ6Hg87OTvr7+1GpVDgcDtra2mhvb8flcsnHL5UF0jOgtraWtrY2Oauv9JuUyqrxLaparXZWLaq5ubnU1dWRlJTE0qVLiYiIkK+hRqPh+vXrlJWVER8fz+LFiwkNDZWvrdPpZHh4mNbWVmpra2lsbKS/v18+T+k5MDo6Snt7O5cvX6agoAClUklsbCx6vR6bzSYHXTU1NZw7d47q6mpSUlIICwvDarXicrkmbM/pdDIyMkJzczO1tbU0NDQwMDAAID+bpWtitVrp6upicHAQvM/Ujo4OmpubcTqd+Pn53ZXvMQqFgsuXL/Puu+/S0tIiJ7+afB9/VCJQFQThjiYFqH19fRQVFXHw4EEOHDhAQ0MDUVFRZGZmEhgY+IkUiJ+V8YHqypUriYyMnPZ8PB4PIyMjvP766/zpT3+ir6+P+Ph4AgICUCgUuFwuiouLeeWVVzh+/Di+vr6kpKQwODjIH//4R15++WXmzZtHXV0db7zxBu+88w7Hjx/n5MmTlJSU4HQ6CQ4OntLFyW63c+3aNV577TX27dvH6dOnOX/+PFeuXKG7uxuj0Sh3bXO5XDQ0NPDP//zP1NfXExUVxQcffMAf//hH8vLySElJISYmRj6f7u5u+e82m43MzEw0Gg39/f28/PLLnDhxAq1WK3dh279/P6dPnyYvLw+LxUJYWBjDw8O88847/O53v+PDDz/k9OnTlJWVoVarCQsLm9Bd2u12MzAwwLVr13jjjTd46623OHv2LOfOnePy5csMDQ0RFBSEv78/KpUKq9VKfn4+r7/+OsXFxRgMBs6dO8fvf/97jhw5wunTp7lx4wYOh4PQ0FD8/PxwOBxcvnyZV199lRMnTtDR0YHZbKa6upqLFy9SUVFBUlISRqORuro69u/fz1tvvcXRo0c5c+YM58+f58aNG1gsFkJCQjAajXIA/FEC1TNnzhASEsIXvvAFTCaT/ILV19dHbm6u/PK3fv16IiMj5evU19fHqVOneOONNzh48CBnzpzh4sWLFBcXMzo6SmBgIH5+frS3t3Po0CFeeeUVSktLGRwcpKuri/z8fPLy8uTu3e+99x7Hjx+nra2NgYEBamtryc3NpaamhoiICGJiYnC5XHR1dXHmzBn27t3LgQMHOHXqFBcvXqSkpITR0VGCgoLk3gWjo6OcP3+e3//+93L2bKmMaG9vJyoqivDw8ElXRxBun9Pp5OzZsxw4cAC9Xs+2bdtYs2bNbXXrtVqtVFRUcOjQId5++20OHTokl6fFxcUMDw8THBw8IWFQY2Mj7733HhcuXMBsNtPU1MT777/PO++8w7Fjx7hw4QKtra34+/sTHByMRqOhubmZvXv3sn//fsrLy+nv76etrY2CggKKi4vxeDxERETQ19fHG2+8wblz51AqlZSWlvLGG29w6dIltFotUVFR6HQ6urq6uHjxIu+88w779+/nxIkTnD17Vt63TqfDaDTKFWsfJ1BNTExk8eLFmEwmlN7K2a6uLo4cOUJDQwPr16+Xhy4olUrGxsaoqanh0KFDvPXWWxw5ckQuq2pqatBoNJhMJnQ6HaWlpfzpT3/iyJEjNDY2yhWKubm5VFVVAVBaWsqrr77KtWvXGBwcpLe3l8LCQs6dO4fVaiU8PByj0YjD4aC2tpYPPviAN954gyNHjnD27FnOnj1LbW0ter2eoKAguYtyQ0MD+/fv5/z581itVvk5fPLkSXQ63U2vz52upaWFy5cvc+7cOcrLy7FYLOj1enks8Wx/H9MRgaogCHckKUAdHh7mxo0bHDlyhIMHD1JVVUVISAjr1q3jnnvuITY2dkKr091IClSjo6PJycmRa73tdjt2u12uAZdqtjs6Oti/fz9VVVXExsYSExODj48PHR0d/PnPf5ZfpO677z7i4+Mxm8288cYbHD16FIPBwOnTp2lvb8dgMODv7y8nlqipqQEgOTkZPz8/8LbQXr58mZ/97GcUFxcTEhJCQkIC/v7+tLe3c+PGDYaHh4mOjsZkMuHxeGhtbeWHP/whg4ODjIyMcOjQIQYHBzGZTKxYsYLo6Gj53Lu6ujh27BgffPABJpOJ9evXo9PpGBoa4s033+TcuXP09vZSXl7OwMAAPj4+jIyMUFlZSUNDA8PDw9TU1HDkyBG0Wi3+/v50dHRQWlpKR0cH0dHRREVFodFo8Hg8DAwMcP78ef74xz9SVFREZGQk8fHxGAwGWltbKSoqwul0EhUVRWBgIA6Hg8LCQg4ePEhJSQmDg4MUFhbidDrx9/dncHCQGzduUFdXh9FoJDo6Gr1eT2trK5WVlbS2tjI0NIRWqyUyMhJ/f38CAwPJyckhICBAboW0Wq2YTCZMJhNOp5Pa2loqKytRq9WkpaWh1+s/VqBqNBq5//77CQgIwGaz0djYKL9UKRQK7rvvPlauXImfnx9ut5ve3l6OHDnCK6+8Qnt7O+Hh4URHR6NUKmloaKCqqgq3201kZCQKhYL6+nqqq6vp7e3FZrMRGhoqV3okJCTg6+tLS0sLTU1NDA8Po1arCQ0NxWg0EhwczNy5c4mKiqKnp4cPPviAt99+m7a2NkwmE1FRUSiVShobG6msrMTtdhMXF4e/vz82m40rV67w5ptvYjabqa+vJz8/H6vVSkJCAllZWYSFhU2+PIJw24aGhjh8+DCXL19mzpw5bN68+baCC5vNRkFBAW+//TYnT55kcHCQ4OBggoKCcDgc1NTUUFJSwtjYGDExMQQGBqJQKGhububYsWNcvnyZxsZG6urq6OzslCsGm5qaqKioYHh4mPj4eEJDQzGbzVRVVcnd7F0uF4GBgQQFBREYGEhSUhIJCQkMDg7y7rvvcuPGDbq7u7l69SoNDQ0EBASQlZVFQkICAwMDHDt2jL1791JaWoperyciIgKDwUBHRwdFRUW0t7cTGBgotyw7HI6PFKjW1tYSHR3NvHnzCAgIYGRkhOrqao4dO8a5c+eIi4tjz549zJkzB51Oh8vloqysjH379nHy5EmsVitRUVGYTCZsNhulpaXU1dURGRlJeHg4/f39VFdXyy2uarVarhgIDQ0lKSkJp9NJXV0dHR0dDA8PExISQlBQEHq9nqSkJNLS0jAYDFRWVvLOO+/w4YcfYrPZiI2NJSwsDJvNxvXr12lsbCQyMpKwsDC0Wi1NTU0cPnyY69ev09HRQWFhIVVVVfj4+DBv3jzS09PR3qXTz/n6+hIUFITL5aK5uZni4mKqq6vlnk9SsqqPErCKQFUQhDuKFKCazWaKioo4duwYBw8epLKykoCAANasWcPWrVtZvXo1CQkJcm3l3UwKVMfGxrBardTU1HD9+nV52pbS0lJGR0dJSEhAo9EQHh5Od3c3eXl5jI6OkpqaSlBQEGfPnuXtt98GYPfu3dx7771yYHfixAlKSkro7u4mMjKSL3zhC2zdupVVq1aRlpaGxWKhqKiIrq4uYmJiSExMxOPx0NzczL//+7+Tn5/Ptm3beOyxx7jnnntYvHgxERERVFdXU1RUhNFoZO7cuWg0Gnp6evjTn/6E2Wymv7+ftLQ0HnzwQTZu3Eh6evqEcah9fX1cvXqV4uJiMjIy2LBhA3q9ntHRUU6cOEFpaSlms5msrCx27Nghb8NisVBQUEBNTQ0DAwMsXLiQJ598klWrVhEbGysHUyaTibS0NAIDA7Hb7RQXF/Paa69RWlrK5s2befrpp1m7di05OTlERkZSUlJCdXU1kZGRJCQkoFarqamp4dKlS9TX16NUKlm5ciWPPvooa9euJS0tjY6ODsrKynA6naSnpxMVFUVAQADh4eFyC3N0dDRf//rX2bx5s9zFVq/X4/F4MJlMrFy5kvXr17Ns2TIyMzNxOp0UFhYyNDQkB3EfJVAtLy/n7NmzOJ1O8HZdvHr1KidPnuTMmTM4HA42bNggj6VTKBRYLBauXr3Kb3/7W4aGhti1axe7du1izZo1zJs3D61WK2fMjIyMJD09Xe5W2NXVxcDAADt27OCJJ55gzZo1zJ07l/j4eCIiIrDb7XR3dxMVFcWjjz7Krl27WLRokXy/5ebm8tprr2G1Wtm6dSsPPfQQa9euJSsrC61WS1VVFU1NTURGRpKSkiK/EB8/fpzBwUEUCgU5OTls27aNVatWER8fL7r+Cp+I9vZ2jh07Rm1tLUuXLmXdunWEhYXN+uW7traW/fv3c+bMGYKDg9m+fTs7duxg7dq1zJs3D7VaTVlZGeXl5ZhMJhISEvDx8ZEDyKKiIsxmM3Fxcdx///1s3ryZnJwcfHx8qK6upqqqioSEBJKTk/H395e7+Xd2dqJWq7nvvvt49NFHWbduHXPmzCEoKEiuuKuurqarq4vw8HA2btzI5s2byc7ORqVScfnyZfbt20dLSwsrVqyQkxwtW7aMxMREWlpaKCwsxG63ExsbS2hoKB6P5yMFqmVlZdhsNjlAzc3N5dixY5w+fZqQkBB5XH1QUBBKpZLOzk4OHDjAyZMnCQsLY+fOnTzwwAOsWLGCtLQ0zGYzV65cwW63M2fOHCIiIkhISMBqtdLc3ExUVBQPPvggDz30kLxObGws0dHRcrfcbdu2sWfPHu677z4WLlxIZGQkfX19HDp0iA8//BCTycTu3bvZtm0bK1euZN68efT19XHlyhWUSiUpKSkEBQXR1dXFlStXKC0tpb+/H39/fzZu3MgDDzzAggULCA4OnjKW+W7h5+cnl8lRUVF4PB5aWlooLi6WhwFJXYJvt4VVBKqCINwxnE4nQ0NDVFVVceLECY4cOUJhYSE+Pj6sWLGC7du3c88995CamjphXKpnXFICpzfpwa0+7nFzy0n7dnkTMUxedrqP2+1G4U1UI+33dtb1eOdvw5uBsKCggJ6eHlpbWykvL6eoqIiioiJu3LghdyNasWIFGo0Gg8GAyWSiqqqKkpISOQj74IMPqKmpYdOmTTz66KNyl8fh4WFOnDhBWVkZQUFBvPjii2zZsoWUlBSio6NJSEjAz8+P+vp6SktL8fPzY/ny5SgUCs6ePcvPfvYzlixZwje+8Q0WLFhAWFiY3NLV1dXFtWvX8Hg8LFy4kJCQEHp6enj99dcZGhoiKyuLF154gfvuu4+UlBR5DKqkv7+f/Px8SkpKyMrKkgPVkZERTp48SW1tLenp6Tz11FNs2LCBpKQk4uLicLlcFBYW0tHRQVZWFt/61rdYtGgRMTExxMbG0t7eTnl5OVqtlvnz5xMVFUV/fz8nTpzg0KFDpKWl8a1vfYu5c+cSHByMyWQiIiKCjo4OCgoK8Pf3Z86cOQQEBFBTU8PVq1cZGRlh1apVfP3rXycnJ4eYmBj5WPLz8+XzTU5OlmvpOzs7uX79OuHh4TzzzDPk5OQQFRWFXq9HpVIRFBREQkKC3BJiNBrl77O8vJyenh4yMzPl8a0fJVA9c+YMIyMjDAwMyK02UotzcHAwixcvZt68efL45fEvf1u3buXxxx8nPT0dk8lEWFgYRqORhoYGysvLCQwMZOHChcTGxqL2ZuZsbW1l+/btPPDAA/K1MBqNGAwG2tvb5QqEHTt2sG7dOiIjI/Hx8aGrq4t3332XvLw81q9fz86dO+U5XsPCwggICKClpYWioiKCgoLkF+ny8nKOHz+OUqlk/fr17Nmzh9WrV8tjz1ze3/Xt/D7xjr1ye5PH3M66UtngGZfcZTbrS/uS9n23V8DN5Havi3RtGPed3O66Ho9H/k5ud13p+2xtbeX06dN0dHSwZMkSli1bJrd63ordbufMmTO8++67eDweHnjgAb7whS8wd+5cYmJiiImJwWQy0dXVJQ8lmDNnDuHh4fT09HD16lVqampITExk165dbN68maysLOLj4wkMDKS5uZmKigrCw8OZN28eYWFhhIWFMTIyQql3aqrVq1ezadMmMjIyCAwMBKCnp4eLFy9SVlZGREQEjz/+OA899BBz584lKChI7mZcWFjIvHnz+OIXvyjnUYiMjCQxMRGXy0VRUREtLS3ExMSQlJSERqOhvLz8tgPV4uJiBgYG6O7unlBW9fb2kpCQwNq1a+VKPoC8vDzeffdd7HY727ZtY/PmzSQkJGAymQgPD0er1ZKXl0dlZSVLliyRKxKlVr/Q0FC2bt3K2rVrSUhIwGg0YjQaCQgI4MaNG5SVlbF161a2bdtGVlYWoaGhaLVa8vPzeffdd7FarTz44INs2bKF+Ph4QkJC5PL96tWrtLS0MH/+fOLi4uTgtbS0lNDQUHbu3Mmjjz5Kdna23H3c4U3GNPk+nOnzSbyHjP9duG6jrJPWle5/jUZDcHAw8fHxpKWlERUVhWtcC2trayvDw8P4+vqi1+vlcb63IgJVQRDuCE6nk/b2do4fP84HH3xAXl4eer2e5cuX89BDD3HvvfeSkpIy7WTfTqeTzs5OioqK5AQTt/o0NzczPDxMQEAAY2NjlJSUUFNTM2W5mT7d3d3ovIke6uvrKSsro7Gxccpy031aW1sZGxsjODgYpVLJuXPnuH79OiEhISxfvpwFCxaQlpZGamoqaWlpZGRkyF2DpBpXk7ebbXFxMc3NzZSUlFBbW8v8+fN57LHHyMrKkq/T8PAwH374IWVlZWzevJkvf/nLhIaGyg8JrVaLr68v7e3tXL16Fa1Wy7333otarWbv3r2cPXtWvv7SWKeOjg4GBgaoq6ujtLQUj8fDggULSEpKoquri1deeQW73c6TTz7Jjh075BrwyQ+m/v5+8vLyKCkpITMzc0Kg+uGHH1JfX88DDzzAli1bCAsLQ6FQoNFoGBkZoaysjL6+PjZv3szOnTvB+yKr0Wjo7OwkLy8Pt9vNkiVLSEhIoL6+nsOHD1NWVsbcuXOZO3cu7e3tcvKQ/v5+mpqaKCsrQ6/Xs3DhQsLDw6mpqeHatWtoNBoeeeQR7rnnHvk8pOQnH374IQMDA8ybN4+MjAx8fX0ZHR2VWxUCAgLYvHkzJpNJPnfpBUHKhltZWSlXTkj3o81mIzs7m8WLF3/kQPX06dMEBASwadMmFixYQGpqqtx1dmhoiO7ublQqFZGRkej1eurq6nj33Xdpb2+XWy96enpoa2ujq6uLnp4eqqurqa+vx9/fn+zsbMLCwuju7ubixYs0NTWxcuVKFixYMOHF1GKxUFJSQnFxsVwZkpSUBN6kVXV1dezbt4/e3l5ycnIICgqS77fx+62srMRoNJKTk4O/vz+l3il4oqOjeeSRR1i+fLk8hnVkZITGxkYqKiqo92bxnPx7nPzp6urC6XSiVqvp7++Xu8XPZt2WlhaGhoZQexNl1dXVUVFRMauyobm5mZ6eHphmXsfPC7c3mdjtXpfu7m48Ho/cQljmnZt4Nt+JlHxNr9czPDxMZWXlrMv65uZm+vr60Ov1DA0NcfHiRdrb28nOzpa7708u06bT39/PoUOHuHLlCpmZmWzfvp309HT596FWq/Hx8cFsNlNcXEx3d7f8W+3t7eXKlSu0t7ezdOlStm3bRkJCAiqVCpVKhVqtpqGhgYqKCgIDA1m8eDHh4eEolUrq6+u5evUqo6OjZGVlkZWVhb+/P3h/cz09PVy4cIGqqio2bNjAww8/TGJiIlqtFrfbzfXr1zl06BB2u53777+f9evXExQUBN7yS6fT4efnJ7cER0ZGkpGRgZ+fH5WVlbcdqNbU1MjZ7xcsWEBKSgqxsbHy0Jaenh4CAwMxmUxyuXvmzBn8/f1JT09HrVbT3d1NR0cHnZ2d9PX1yV1sV6xYQXp6Onq9nhs3bnDt2jV8fX3lHi5St1uPN6HShQsXKC0tZdmyZWRnZ8vvHjabjdOnT3Py5EkMBgPz5s1DoVDQ2dlJR0cHHR0dDA4Ocu3aNerq6li6dClpaWkMDg5y9epV6urqWLhwIV/84hdJTU2V9yv1EqqtrZ1yH870aW9vx8/PD71eT21tLRUVFbf1DuRyufD396evr4/y8vJZ77uxsZG+vj4CAgLQThp6pdFoCAoKIjExUa5ssdvtck+x1tZW/Pz8CAkJmbLudP7ysw8LgiBMw+kdl/fGG29QWVnJPffcw2OPPSZPy3KzlzYpmcK+ffsYGRm5ZcHn8XhQq9XMmTOHsLAwHA4Hhw8fpqmpSa6hnInHm3bdZDLxyCOP4OfnR35+PmfPnsVms910Xbzr6/V6li5dSlJSkjzuFCArK4uvfvWrLFiwYEIwrlAoUKlUaMZN1K7RaNi4cSMFBQW89957dHR0kJ2dzX333cf8+fOnXC+p9jMpKWna7tL+/v7ExMRgNBoZGhpiaGgInU5HbW0tABUVFbz55pt4vGn1Je3e7JBS4iG8+/J4sy0mJydPOO7bpVAoCA0NxWdcpmBAfkGSWpjHUygUGAwG1Go1VqsVu92Oy+VicHCQDm/23qqqKn7/+99POB+lUklbWxsO71Qodrtd/ptCocDX15eQkJAJ106pVGI0GtF4M2jabDYcDof89/HbH3/d8L4odnd3U1BQQF5eHk1NTQwNDWG1Wunv76ezsxM/b3KmyevOllRrHhkZydNPP01GRgZKpZKhoSFKS0s5cOAAZ8+eZf/+/Zi8Y4QHBgZo805nkZubS319/YTzsNvtNDU1yf82NjY2ebezMv66OLxZpdva2hgcHOTy5cs0NDSgVCrl5aTMwUrv2DybzSavr1AoCA4OljOF4r2+vb295Obmcu3aNUZHR6fc99MJCQlh1apVLFy4kJaWFo4fP05LS8uUCrLJPN5AKjU1lfXr12M0GuVKKJfLdct9K5VKIiIiWLt2rZwU5/PG6XTKwdH169ex2+23vC4KhYKwsDDWrVvHokWLKCsr48iRIwwODs7qO9Hr9WRnZ7Np0yaGhoY4evQo9fX1tyzr8e47Li6Ohx56CF9fX3x9fXG5XHLiLpfLhVp961dp6feMdxqyyMjIKUGbVqslNjaWoKAgamtr6e/vn1AGaTQaAgIC8PcmemNcxZzBYECj0WC1WieUP7MhbT8mJmZCYijpu+rt7cXPz4/o6Ogp5TBAXFycnCCvu7ubwcHBjzwu3MfHhwULFvClL32JjIwMFAoF/f39XL9+nddff51Tp06hUqnkLrzd3d0MDQ1hs9k4efIk+fn5E75Tq9VKX18fPj4+ctk8uSyd/P/Sv0337wBms5nu7m7MZjM2m43jx4+Tm5sr/12pVGKxWBgYGEDlzaQstUAC6PV6wsPDiYiIkO8dj3fu1gMHDtDV1SWXaTfj8Xjw9/fnK1/5Ckajkby8PHJzcxkZGZm86BQeb86LDRs2EB4eTmNjI++//z7t7e0znrdEujZxcXGEhIRgMBim/R1qNBqio6MJCwtj/vz5nDhxgpdffpnXXnsNvV5PYmLilB5W05m6ZUEQhM+AFAhEebN0Kr3jT+rr6xkYGMDuncJkOgpvzW5QUBDBwcGz+gSNy+yqVqsJCAggODiYkJCQKctO9wkMDESn06FUKuVEApOXmekTFBQ0bQGt9k63ovdO4SJ99Hr9tC+tAQEBxMbGotFocLlc8jlINbTT0XinFJlMpVLJLcRSkOb0JrPCmwikv7+fgYEBBgcH5Y+fnx9Llixh+fLlREREyNvzeAPV6YLi2zWbB+dk4x+c0t/tdjtj3nl37XY7AwMDE86nv78fX19flixZIie1Gu9mLy+zOcfxy0gvJidOnOC3v/0t77//PoODg8yZM0duuYiPj5+w/sehVCrl79fHx4eIiAh5rsf09HRqa2vJz8/HYrHgcDiwWCy43W5GRkamfO9Wq5WIiAi59V/qRni7xl8Pl8uF1WqV92uxWCbcZ4ODg9hsNsLDw1m9ejWLFi2SW02lbel0ugk19AqFArVaja+vL4GBgVN+hzN9AgMD8fFOr6DzZjOdvMxMH6lc0XmnKjEYDFOWudknICAAvV4/q/vpbiR9J7O9LlK5ajQa0ev1KJVK9Hr9bX2fQUFBcsWVVquddVkv7TsgIEBuJZICsI6ODrq8UybNhs1mY2xsDJVKhV6vl58d40n3sFSej42NTQk6b1YGMctyaCZarRb1uO6Y0jG4vFOy6CZNtSORnlkKb7bf6YLB26HyTsul81ZGxsbGsnHjRnbv3k1QUJDcDXpoaIixsTHc3q7go6OjU8oMu3ds6saNG0lMTJzx+Xc7pFwSLm832cn77e/vZ2xsTB7KIrXWSvuV7sPJ379KpcJoNBIUFHTLe1P6BAYGytu+3XIuODhYzsqr0WhmXc6FhIQQ4s1Gf7NKGrfbjdVqnfAeZzQaiY+PJygoaMK9djMKz8e5mwRBED4hHo+H0dFRKisrOX/+PKdPn8ZisZCQkMC6devkhCzSS8Pkl34pAcNsijSPt7ZS680S6/F29XF6E87cisdbG+nv749Wq2VkZASr1Spv92akZfR6Pf7+/igUCl566SX+53/+hzVr1vC///f/ZuHChdO+EIzn8Xb7/dGPfkRJSQlmsxl/f392797Nl770JeLj41F4u5a2t7fz7W9/m3feeYd/+Id/4MUXXyR4UhA2MDDA66+/zn/+538SFxfHr3/9awIDA3n22Wc5fvw4P/zhD+VuuZOvsfSQNJlM+Pr6UlxczH333YfH4+EPf/gDW7ZsmZBASeLxeKipqeHXv/41b7zxBg8//DA/+tGPMBqNdHZ28p3vfIcTJ07wne98hyeffFIec+tyuSgoKOA///M/uXr1Ks8//zzf/va35e3aveN1f/CDH6DVavmnf/onNm7cyOXLl/npT39KRUUFjz/+OA8//PC4o/n/UygU+Pv7y92rDx8+zC9+8QucTid///d/z44dO+RlPR4PDQ0NfPGLX6SpqYkXXniBL37xi3IG23379vGLX/yC2NhYfvGLX5CZmQneOfSuX7/OSy+9RHV1NTt27OCRRx5h7ty56PV6SkpK+M1vfsPFixd5/vnn+cY3voHL5aK0tJR/+Id/oLKykhdeeIHHHntMvi7jub2Ze/ft28f3v/990tLS+O///m95+h/pGCorK/nNb37DwYMH2bJlC9///veprKzk//yf/8Pg4CDf//73yc7ORuPNmjyeSqUiICCA0NBQNBoNZWVl/Pu//zvnz5/nO9/5Dk8//TQBAQHy8r29vbz11lu8/vrrhIWF8eKLL8r3ic1m49SpU3zve98D4Gtf+xqLFi3Cx8fnpvsdGxtj7969/OM//iNLlizh7//+71myZIm8nhQA22y2WbWg4Q3qfXx80Hrn77VYLDidzlmt6/G2qvp4k4ZYrdbbanFWqVRy5dTkF9nPA493LJx0XSZ/tzMZH+DZ7XZGR0dn/X3iDaZ8fX3lSpDJAeBMPN4KN6li8U9/+hO//OUv8ff350tf+hLbt2+XK1ZvprKykp/85CecOXOGrVu38uyzz8pdVSWjo6OcO3eOf/3Xf6WlpYV//ud/5tFHH6W2tpaf//zn5Obmsn37dr761a+SlJQkn3tvby9/+tOf+J//+R/mzJnD3/3d37F48WLUajWnTp3iF7/4Bd3d3Tz66KPs3r2bSO8UVGNjY5SXl/Mv//IvHD16lL/7u7/j2WefxeSdFkb6bf3iF79Ap9Px3HPP8cADD8hdfyVDQ0O89NJLvPPOO2zcuJGvfvWrJCcn8/777/PLX/4Sg8HAN7/5TTZu3Ch3O56sqamJn/zkJxw/fpx169bxta99jaysrCll1TPPPENjYyP/8A//wNatW3n55ZfZt28f2dnZ7N69m+TkZNRq9ZT7SmqFDQwMRKVS8fLLL/OrX/0Kk8nE1772Ne699165Z47b7aatrY0f/ehH7N27l29961t86UtfIioqCpVKRUdHB7/+9a/Zu3cv8+fP5+mnnyY2Nnbae0DlHVJhNBopKiriv/7rvzh//jwPPvgg3/3ud4n0Zk2XyqqhoSFc3nHqt+Lx5rmQut+OjIzcVjmHtwXbz88Pu93OyMjIrHp+MO534e/vP6USXaro7uvro66ujry8PC5fvkxXVxcpKSls3ryZ5cuXExUVddNKdcnUqyoIgvAZUHi7ay5atIjnnnuO//f//h8bN26koaGBX//61/z85z/n8OHDVFRU0N/fP6HWVqFQ4OPjIyddudUnPDycsLAw+aGl9qaon7zcTJ/w8HA5Db8U1Izf7s0+0jK3Gtvk8dacj/+MNzg4yFtvvcW1a9dYs2YNe/bsQavVcvjwYc6ePcvo6OiE5SVtbW1yq5XE4522pbGxkZGREcLDwwnypuNPTk4Gb/AXFxdHVlYW8+fPn/CZO3cuycnJE4KSO43S20XXZDLhcrmw2+0kJSUxb968Keczb948ErxTqkx37T8JY2NjlJaWUlNTQ2hoKA888ADLli0jICAAj3d86Wy6cN2OyS9SLpcLi8WCxWKRAwGp5UiaQkij0ZCUlDTt956VlSWPH5vsZtdt8j2t8LaymUwmoqOjUalU+Pn5kZSUxNy5c2fcr/4W2Xyl7UqVDrP5fYaFhRHqnQ9Xo9Hg4+NDSEjIrNcd/9vRarUYjcYpy9zsExISIrdyfB4pvF1VAwICZl1eS9fFz89PbiG/ne8zzJsATGoVlFpGZ/MJDw8nODhYbq2fO3cuWVlZdHd3k5ubS2VlJcPDw3IX+/HG3+OhoaFERUWhUChoaWmhpaUFi8UiL+t2uxkdHaWuro6BgQEiIiLkbuw3e07M1s1+jzPReDPMm0wmRkdHaW5uxmw2T3l21NTU0NjYiEajkbP+Tg5ebodiUiIxjzeIk7pCS9+jwWAgLCxMrgQ1Go2kpaVNKTPmzZtHVlYWISEhcgXw+Gsx3XUZv//x54t3P9J+PR4PAQEBZGRkTCmnpP0GzyKbr1RWhYSETLkHZ/pI383495Db/V34e8fd6vV6QkNDZ72u9LsY/z17vBWOXd45tN966y1+8pOfcODAAZRKJc888ww/+MEPeOSRR0hISJhVkIoIVAVBuNMovK1zCxYs4G//9m/56U9/ypYtW2hra+NnP/sZP/7xjzlw4ABVVVVTHpqfB3a7XQ4eJn+kVgCHw8GJEyd46623MJlMPPTQQ3z961/nvvvuo7W1lYMHD8rzgUqkB+/58+cpKiqSu0XZ7XaGh4cpLCzk+vXrGI1GFi9eLL9sL1u2DIPBwHvvvcf169flbk0OhwOHd0ymNA70TqZUKomKiiIrKwuACxcucPnyZUZGRuTuag6HQ+5+OtvW9ZuRXsrVajUOh0MeSyWNWZLuX61WK3cjczgcDA4OUltbS11d3eRNfmQeb2Zs6TsbHR2ls7OT/Px8qqqqCAoKIi0tDT8/P0JDQ5k3bx6jo6N88MEH8su4dJ3sdjtWqxWr1TrhOqm8XfacTieDg4OMjo4yNjaG0+nE4+1JoFar5ZZGaYyXw+GQWx7mz5/P6Ogop06doqKiArPZLN9vM+1XEP5SMjMzWbduHUajkdzcXP785z+Tn59PV1cXFotF7uJrtVoZHh7GbDZjt9sJCgpi7ty5REZGUldXx5UrV2htbZXLzuHhYaqqqsjNzcVsNssJfj5uhYXam+xN2ofFYsHuHbN/K0qlkvj4eObOnSv3YikvL2doaAi7dxhFf38/J0+epKKiQk6kND4g/KjGl1UjIyM0Nzdz/PhxOjs7iYuLI8E7l/ecOXOIi4ujtraWixcv0tzcLJ+jw+FgbGxMLofGB6QajQaVN6/C4OCgvI70PqHy5oRQKBQMeucDl8oyvV5Peno6cXFx1NTUcOLECXm/0nNkpv1+XjkcDvr6+igoKOCVV17hhz/8IW+++SZarZZnnnmGn//85zz11FPExcXd9r0hsv4KgnBHkl5qpeQiCxYswOPxcOPGDU6ePEl1dTV+fn5ERETI42PuVmfOnKGgoACVSoWvry99fX3U19dTW1srf5qamlB7x9LW1NTw0ksv0d7ezt/8zd9w//33Exsbi06no7GxkaKiIlQqlZwRdtQ7J2lZWRlWq5WmpiZ8fHxwe7PIXrx4kT/96U/k5+ezatUqvvzlL8sPFKPRSGNjI/n5+TQ1NaFSqXB6pxHq7OykqqqKhoYG8LYauN1uurq6ePnllwHYsWMHqampM9aw93uz/hYXF0/J+nv8+HEaGhpYuXIl8+fPl7tmebzdmS9fvkxraytLly5l5cqV8jZdLhdVVVWcP38epVLJ2rVr5flbtVotHR0d5OfnU11djY+PjxwcdnZ2UllZSXNzszw+yul0Ul1dzbVr13C73axevZqMjIxxZ/D/dZv+85//zODgIEuXLiU7O1tuGe3q6qKoqIj29nZ5LJfFYsFgMDAyMkJubi5dXV0EBgZiMBgYGBjg0qVLHDx4kMLCQnkM8NKlS+XtnTp1ir6+vlll/S0rK+PUqVNotVqSk5Ox2Wy0tbVRUlLCBx98wL59++jo6ODee+/l0UcfJTY2Fq13rFpFRQU3btygp6cHhUIhv5i2trZSXV1NZ2cnWu+YP6k2vcY756zb7cZgMOBwOFB4u7p7vFPflJaW0tzcjF6vx8/PD6vViq+vr9wtsLi4mOLiYnp6euTW74GBAVpbW6mpqaGjo0Pe75g3Y/eZM2eIiopizZo1REdHz3i/CcLHIbU8ORwOqqqquH79OhUVFfT19TE8PExfXx+dnZ3U1dVRUFBAdXU1vr6+BAcHy7/vGzduUFdXx9jYGAqFgqGhIQoLC3n77bfJzc0lISGBL3/5yyxatAiNRkOXd/7N1tZW0tLSWLRoEcHBwfIzz2KxyBWNJpOJ1atXExUVhVKpxGw2U15eTlVVFS6XC19vMigpEOvr6+P8+fPU1tayevVqcnJyJuRP8PX1xel0UlNTQ3l5Od3d3Wi8ieOam5s5ePAgb775JmazmYceeohNmzYR7p0/uqysjCtXrqDValm2bBkpKSnoZsj6Ozg4yJUrV6isrJSvl9U712lhYSH79+/nnXfewW638/jjj3PvvfcS7B1H3N/fT2FhoVyhJpV9vb29NDU1UVxcjMvlksdUKhQK2tvb5Yz5Km9+BofDgV6vl8uq6upqrl+/zvDwMP7+/nJwr9frMRqNDA8Pk5+fT1lZmdyDyWq1yvstKCjA4/Fg8Ca66uzsJDc3l6amJubMmcOqVavk4T93u5aWFt555x1++ctfkpubS0xMDI8//jjPP/88q1atumUPspsRgaogCHc8hUKByWSS08T7+vrS1NSExWIhMTGR0NDQj13z/Fm6cOEClZWVNDU1ceXKFY4ePcrhw4c5cuSI/MnLyyM4OJi0tDR+/OMfc+nSJdavX8+Xv/xleaqC4OBgbDYbFRUVtLa2EhAQwLx587BarRw/fpyysjLuv/9++f/Pnz/PsWPHOHz4MB0dHaxbt45nn32WZcuWoVKpUCqVGAwGkpOT6enpobi4mA8//JCLFy9y9uxZjh49yv79+ykoKCAsLIwFCxbIgerrr7+OWq1m+/btNw1UpRe3mpoa0tLSpsyj2tnZyYoVK6YEqp3e6Wd6e3tZtGgRK1askLfpcrmo8U4po1arWbNmDWlpaahUKgIDAwkLC5MD5DNnzsjnc/jwYfbt20d5ebk8X6vH46G2tpbCwkLUajUrVqyYEqgOerM1joyMTAhUlUqlfD3y8/O5ceMGFy5coKmpiZycHOLi4hgeHpYTGeXl5clz6ur1eqKiohgZGSErK4slS5agUCjo7u7m3LlzDA8Ps3TpUrKysm4aqFZUVHDhwgWGh4cpKiri5MmTfPDBB7z//vsUFRVhNBp54IEHePzxx5nvzRat8c6HZzKZaGlpIT8/n5MnT3LhwgVOnTrFoUOHOHz4MM3NzcTFxcnj5VQqFTabTf4+L1++TFFREVqtlri4OIxGo/ySWFpaSmFhIWfPnqW9vZ3U1FQ562hgYCAdHR1cv36dM2fOyGPW33//fY4cOUJLSwsJCQkkJCRgs9morKwkNzeXiIgIVq9eLQJV4VMVEBBAQkICISEhjIyMUFVVxeXLlzlx4gQnTpzg2LFjHDx4kA8//JDW1lYyMjJISEiYkIypoaGBvLw8Ll68KM8ZXldXR2ZmJs8++yzr1q2Tf9ddXV0UFBTQ2dkpB6pBQUETAtXi4mLKy8sJCwtj5cqVcqCq0+nkHholJSVcvHiR8vJyDAYD0dHRjI6OcunSJVpbW1m7di0LFy6cEKhqNBpCvfM79/T0UFhYyLlz5zh//jyHDx/m3LlzaLVaHnvsMXbv3k1KSgparRa7dx7ovLw8dDrdrKanKSgokKd5Kygo4OTJkxw6dIhDhw5RWVlJbGwsTz31FI899hhxcXGovVP6hIWFoVaraWxs5PLly5w5c4YLFy5w4sQJDh48yOHDhzEYDKSnp2MwGFB4e7p0dHRQVVVFcXEx586do6GhgdjYWCIjI1F7x7mWlJRQVVUlZ9RVKBRy1uaIiAg0Gg1NTU3k5uZy9uxZzp8/z4kTJ3jvvfc4ePAgQUFB8rR60vfY3t5Oeno6q1atko/nbnfixAkOHDhAUFAQTz/9NF/5yldYvXo1RqPxY7+biUBVEIS7gtKbmS48PFweA5KWlkZcXBx+fn4fuzD8LI2NjREUFCSPA5w3b96UT3Z2NkuXLiU0NJS6ujrS09PZvXs3mZmZ8hhB6aUiPDyckJAQYmJiSE1NxeZNoV9RUcGePXvkZD9utxudTkdmZiY7d+7k8ccfZ/HixRNeJlQqFSaTiZycHBITEwkLC0PnzWgaEhIiT4mzfPly+SXM4+3muXjxYtauXUt4ePiM3X2kZU0mEytXrpyQ7MftdhMTE8OKFSuIj4+fcFxutxu1Wk1cXBzLly8nISFh3Fb/v2DVx8eHefPmsXjxYkzeBCFqtZrw8HCys7NJSkoi1DufrFarJSQkhEWLFnH//ffLWX+lYNPPz4+MjAwWLVokn6fE4x3/lZmZyYoVK0hISEDvTYbj7+8vp+g3GAyEhITIgWdoaChJSUlERUXh5+eHVqslJiaG+++/n4ceeoi5c+diMplYsGABCQkJ8suTSqUiKSmJpUuXEhcXN+PLn0KhQOkdmxsfH09kZCTh4eEkJiayePFiNm3axCOPPMK2bdtIS0uTxwwpvNlHY2NjmTdvnjxlhtabJCg6OprFixezfv16srOz5QBU7R1nmpiYiL+/PwEBAcTHx7Nw4UJ5KgKDwUBERATh4eH4+/sTEhLCnDlz5HlTdTodcXFxcpc+Kbu2Xq+X93vPPffIlQF4v2t/f3+WLl3KggULCAoKmvF+E4SPS+EdD5icnEx2djaZmZnEx8cTEhJCgDfJV2pqKqtWreL+++9n4cKF8j0ZFBREcnIyycnJhISEoPOOtZTmVn388cdZunTphBYot9uNUqkkLi6ORYsWkZqaio+Pj/x3qfwJDAxkwYIFzJ8/n8DAQLlcCw0NlRMJGY1GEhMTWbBgAXFxcWi1WjQaDXFxcaxcuZLExER048bFKry9IaKjo8nIyCA2NhaDN4NyuDcD9xe/+EUeeOABedyhwpscyO12ExgYKM85KwWUM3G73QQFBcnBYmRkJMnJySxfvpxt27axZ88eNm3aJAeSeI/PaDSSlJREWloakZGR8vhyX19fEhMTWbduHevWrZOfIQpvPgypPAzwZoFOT09n0aJFmEwmtFotJpNJLvsMBgMxMTHk5OSQmpqKv78/gYGBJCcny/v19fWVg+ekpCTWr18v71ev1094Zi1dupTU1FT0txhnfzfweJM6ZWRksG3bNlauXInJZELzCWRYBpH1VxCEu5DHO72I2+1G4x0DeDcbGRnBMinB0WTSw1WlUjE4OIhCoSAgIADdpGkOHN6pRWw2Gxpv0pKuri6+/e1vs3//fv75n/+ZZ555BrVazcDAADabDYPBQGBgoBwsTcfpTcMvjbtyOBxovVmTDQYDPj4+csDkcDgYGBgAb+vD+BefyaQMoBaLBR8fHwzeOdncbjfDw8Py8UlZVCUOh4PR0VHsdjsGg0FOqIH3/pDGCAEYDIYpwZy0/ujoKAMDA7hcLnQ6nXw+0ksH3oqE0dFRuRvX5JcL17hsjb6+vhOOVbpXpakLnE4nwcHBhIaGolarcXnnZBz0Tvvi651iQOqSbLVa5S6ySqUSp3fKIKfTiZ93oveZKmncbjc2m43h4WGs3ukUPN45hHXeqWr03kyq0wV20rGPjIxgNpvlayC9XEvfy/jWS5c3y+7AwABms1nuKindu9I2zWazPE46MDBQfjmU9itdc7PZLP829Ho9BoMBPz8/+fvxeDxYrVZGRkbQeLOzflIvSIJwMx7v/L82mw2LN/mZzTuXtvSblcqD8b8Rp9OJzWbDbDYzPDwslxtS2SMFe+OXHx0dxeFwoPNmLx7/e3V7pwEZHR1FM25O1fHrW7zTPY2OjqLT6Qjxzn/p8Xjk8ZfS8U5Xnri9mVyl3+To6ChqtRqj0Yi/vz8+Pj4TjsnjHQpgsVhQePNO3Ow54PYmk5KORepmq1ar5TJK701QNt3xubzzKg8PD8vlndI7dZxUVk0uK6VxuwPe6e8MBgMmkwm9dyiRVLYMDAwwNDSE2ls5GxAQgNrbhVjar1RGWq1W+Vnt5+eHv3eqKqVSKT+b7XY7er1+yvd4t5LKdJd3GqPx994nQQSqgiAIdxGpyJ7pgT+etKw0Pc3+/fv5p3/6J1544QWCg4PlwEWpVE778J+Ox1tT7vG2hCqVylkdy51MSszzaZ7P+OumUqmm7EP626e1//HfGd5zvZ39uN1uuSJlNtfJ483UebNlpW3e7P673f0Kwmdl/L0q3ac3u1fHlwk3+w18UqTj+zi/I4+39fbjbmcm0jNr/HPudrY//pri/R5udl2l5RlXvkw2m7LsdvcrzJ64ioIgCHeR23lwS8tJLxeTqbxT89zOA1XhHYuoVqunDbjuRmpvZsxP83zGX7fp9qFUKj/V/Uvbl16gbnc/Sm+36dleJ4W3K/DNlpW2ebP773b3KwiflfH36mx+Y+PLhJv9Bj4p0vF9nN+RwhusfdztzEThfb591HJq/DWdzXWVlpfKxunMpiy73f0KsyeupCAIwuec9BA1eLvVCoIgCIIg3OnEG4sgCMLnnK+vL+vXr+fJJ59k4cKFU8ZrCoIgCIIg3GnEGFVBEITPOafTSXd3N8PDw4SGhhIYGIjqc5DEQRAEQRCEzy8RqAqCIAiCIAiCIAh3FNH1VxAEQRAEQRAEQbijiEBVEARBEARBEARBuKOIQFUQBEEQBEEQBEG4o4hAVRAEQRAEQRAEQbijiEBVEARBEARBEARBuKOIQFUQBEEQBEEQBEG4o/z/ADfd+ze8kEB7AAAAAElFTkSuQmCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI &lt;=25 &gt;25  25  0.7 (0.21, 2.3)
+Smoking Status Never or former smoker  35  0.2 (0.08, 0.53)
+Surgery No Yes  13  0.31 (0.06, 1.47)
+Histology Non-squamous Squamous  51  0.66 (0.31, 1.42)
+Clinical N N0 N1 N2 multiple N2 simple  15  0.48 (0.09, 2.49)
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response Complete Incomplete + major  23  0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI &lt;=25 &gt;25  25  0.7 (0.21, 2.3)
+Smoking Status Never or former smoker  35  0.2 (0.08, 0.53)
+Surgery No Yes  13  0.31 (0.06, 1.47)
+Histology Non-squamous Squamous  51  0.66 (0.31, 1.42)
+Clinical N N0 N1 N2 multiple N2 simple  15  0.48 (0.09, 2.49)
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response Complete Incomplete + major  23  0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33
+     N2  simple         24
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response
+       Complete     23             0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33
+     N2  simple         24
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response
+       Complete     23             0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33  0.39(0.16, 0.94)
+     N2  simple         24
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response
+       Complete     23             0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33  0.39(0.16, 0.94)
+     N2  simple         24
+Clinical T T1-3 T4 PD-L1 + Pathological response Complete Incomplete + major  60  0.66 (0.31, 1.41)
+Pathological response
+       Complete     23             0.13 (0.03, 0.63)
+Pathological response Complete Incomplete + major  63  0.22 (0.08, 0.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33  0.39(0.16, 0.94)
+     N2  simple         24  2.42(0.3, 19.46)
+Clinical T 
+     T1-3             60     0.66（0.31， 1.41）
+     T4                26      0.13（0.03， 0.63）
+PD-L1 
+     +              45     0.22(0.08, 0.58)
+     -               28       0.85(0.3, 2.42)
+Pathological response 
+        Complete      23    1.01(0, inf)
+        Incomplete + major  63   0.71(0.38, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS) 
+Subgroup      Number of Patients     HR (95% CI)
+Overall          86                                0.47 (0.25, 0.88)
+Age 
+       &lt;65        47                                 0.51 (0.22, 1.21)
+       &gt;65        39                                  0.42（0.17， 1.06）  
+BMI 
+    &lt;=25  25  0.7 (0.21, 2.3)
+      &gt;25  61 0.39（0.19， 0.8）
+Smoking Status
+     Never or former smoker  35  0.2 (0.08, 0.53)
+     Smoker                           51  0.57（0.25， 1.32）
+Surgery 
+      No   13  0.31 (0.06, 1.47)
+      Yes   73  0.66(0.31, 1.42)
+Histology
+      Non-squamous  51  0.35 (0.15, 0.81)
+      Squamous    35   0.6390.24, 1.63)
+Clinical N
+     N0                   15  0.48 (0.09, 2.49)
+     N1                    14   0.07(0.01, 0.69)
+     N1  multiple       33  0.39(0.16, 0.94)
+     N2  simple         24  2.42(0.3, 19.46)
+Clinical T 
+     T1-3             60     0.66（0.31， 1.41）
+     T4                26      0.13（0.03， 0.63）
+PD-L1 
+     +              45     0.22(0.08, 0.58)
+     -               28       0.85(0.3, 2.42)
+Pathological response 
+        Complete      23    1.01(0, inf)
+        Incomplete + major  63   0.71(0.38, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS)
+Subgroup                            Number of Patients   HR (95% CI)
+Overall                             86                   0.47 (0.25, 0.88)
+Age
+      &lt;65                           47                   0.51 (0.22, 1.21)
+      &gt;65                           39                   0.42 (0.17, 1.06)
+BMI
+      &lt;=25                          25                   0.70 (0.21, 2.30)
+      &gt;25                           61                   0.39 (0.19, 0.80)
+Smoking Status
+      Never or former smoker        35                   0.20 (0.08, 0.53)
+      Smoker                        51                   0.57 (0.25, 1.32)
+Surgery
+      No                            13                   0.31 (0.06, 1.47)
+      Yes                           73                   0.66 (0.31, 1.42)
+Histology
+      Non-squamous                  51                   0.35 (0.15, 0.81)
+      Squamous                      35                   0.63 (0.24, 1.63)
+Clinical N
+      N0                            15                   0.48 (0.09, 2.49)
+      N1                            14                   0.07 (0.01, 0.69)
+      N1 multiple                   33                   0.39 (0.16, 0.94)
+      N2 simple                     24                   2.42 (0.30, 19.46)
+Clinical T
+      T1-3                          60                   0.66 (0.31, 1.41)
+      T4                            26                   0.13 (0.03, 0.63)
+PD-L1
+      +                             45                   0.22 (0.08, 0.58)
+      -                             28                   0.85 (0.30, 2.42)
+Pathological response
+      Complete                      23                   1.01 (0, inf)
+      Incomplete + major            63                   0.71 (0.38, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS)
+Subgroup                            Number of Patients   HR (95% CI)
+Overall                             86                   0.47 (0.25, 0.88)
+Age
+      &lt;65                           47                   0.51 (0.22, 1.21)
+      &gt;65                           39                   0.42 (0.17, 1.06)
+BMI
+      &lt;=25                          25                   0.70 (0.21, 2.30)
+      &gt;25                           61                   0.39 (0.19, 0.80)
+Smoking Status
+      Never or former smoker        35                   0.20 (0.08, 0.53)
+      Smoker                        51                   0.57 (0.25, 1.32)
+Surgery
+      No                            13                   0.31 (0.06, 1.47)
+      Yes                           73                   0.66 (0.31, 1.42)
+Histology
+      Non-squamous                  51                   0.35 (0.15, 0.81)
+      Squamous                      35                   0.63 (0.24, 1.63)
+Clinical N
+      N0                            15                   0.48 (0.09, 2.49)
+      N1                            14                   0.07 (0.01, 0.69)
+      N1 multiple                   33                   0.39 (0.16, 0.94)
+      N2 simple                     24                   2.42 (0.30, 19.46)
+Clinical T
+      T1-3                          60                   0.66 (0.31, 1.41)
+      T4                            26                   0.13 (0.03, 0.63)
+PD-L1
+      +                             45                   0.22 (0.08, 0.58)
+      -                             28                   0.85 (0.30, 2.42)
+Pathological response
+      Complete                      23                   1.01 (0, inf)
+      Incomplete + major            63                   0.71 (0.38, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard Ratio (PFS)
+Subgroup                            Number of Patients   HR (95% CI)
+Overall                             86                   0.47 (0.25, 0.88)
+Age
+      &lt;65                           47                   0.51 (0.22, 1.21)
+      &gt;65                           39                   0.42 (0.17, 1.06)
+BMI
+      &lt;=25                          25                   0.70 (0.21, 2.30)
+      &gt;25                           61                   0.39 (0.19, 0.80)
+Smoking Status
+      Never or former smoker        35                   0.20 (0.08, 0.53)
+      Smoker                        51                   0.57 (0.25, 1.32)
+Surgery
+      No                            13                   0.31 (0.06, 1.47)
+      Yes                           73                   0.66 (0.31, 1.42)
+Histology
+      Non-squamous                  51                   0.35 (0.15, 0.81)
+      Squamous                      35                   0.63 (0.24, 1.63)
+Clinical N
+      N0                            15                   0.48 (0.09, 2.49)
+      N1                            14                   0.07 (0.01, 0.69)
+      N1 multiple                   33                   0.39 (0.16, 0.94)
+      N2 simple                     24                   2.42 (0.30, 19.46)
+Clinical T
+      T1-3                          60                   0.66 (0.31, 1.41)
+      T4                            26                   0.13 (0.03, 0.63)
+PD-L1
+      +                             45                   0.22 (0.08, 0.58)
+      -                             28                   0.85 (0.30, 2.42)
+Pathological response
+      Complete                      23                   1.01 (0, inf)
+      Incomplete + major            63                   0.71 (0.38, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is the table formatted with the original English terms, without translation:
+---
+### Table 1. Demographic and Disease Characteristics of the Participants at Baseline (Intention-to-Treat Population)
+| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+|----------------|------------------------------|-------------------------|
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)*** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)†** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| &amp;emsp; IIIA | 217 (54.7) | 225 (56.2) |
+| &amp;emsp; IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| &amp;emsp; 1–49% | 127 (32.0) | 115 (28.8) |
+| &amp;emsp; &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |
+---
+*The intention-to-treat population included all the participants who had undergone randomization. Percentages may not total 100 because of rounding. PD-L1 denotes programmed death ligand 1.  
+* Race and ethnic group were reported by the participant.  
+† Eastern Cooperative Oncology Group (ECOG) performance-status scores range from 0 to 5, with higher scores indicating greater disability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+| :--- | :--- | :--- |
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)†** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)‡** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| IIIA | 217 (54.7) | 225 (56.2) |
+| IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| 1–49% | 127 (32.0) | 115 (28.8) |
+| &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，已将您提供的文本数据整理为以下表格。
+| Group / Subgroup | Pembrolizumab (events/participants) | Placebo (events/participants) | Hazard Ratio (95% CI) |
+| :--- | :--- | :--- | :--- |
+| **All patients** | 139/397 | 205/400 | 0.58 (0.46-0.72) |
+| **Age** | | | |
+| &lt;65 yr | 74/221 | 113/214 | 0.53 (0.39-0.71) |
+| &gt;65 yr | 65/176 | 92/186 | 0.64 (0.46-0.88) |
+| **Sex** | | | |
+| Female | 31/118 | 55/116 | 0.44 (0.28-0.68) |
+| Male | 108/279 | 150/284 | 0.63 (0.49-0.80) |
+| **Race** | | | |
+| White | 85/250 | 123/239 | 0.54 (0.41-0.72) |
+| Other | 46/134 | 70/145 | 0.62 (0.42-0.89) |
+| **Geographic region** | | | |
+| East Asia | 43/123 | 57/121 | 0.66 (0.45-0.99) |
+| Other | 96/274 | 148/279 | 0.54 (0.41-0.69) |
+| **Smoking status** | | | |
+| Current smoker | 37/96 | 57/103 | 0.52 (0.34-0.78) |
+| Former smoker | 84/247 | 128/250 | 0.57 (0.43-0.75) |
+| Never smoked | 18/54 | 20/47 | 0.68 (0.36-1.30) |
+| **Pathological stage** | | | |
+| I | 34/118 | 48/121 | 0.65 (0.42-1.01) |
+| II | 105/279 | 157/279 | 0.54 (0.42-0.70) |
+| III | 73/226 | 107/227 | 0.58 (0.43-0.78) |
+| **Histologic features** | | | |
+| Nonsquamous | 66/171 | 98/173 | 0.57 (0.41-0.77) |
+| Squamous | 107/265 | 142/266 | 0.64 (0.49-0.82) |
+| **PD-L1 TPS (50% cutoff)** | | | |
+| &lt;50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| ≥50% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS (1% cutoff)** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| ≥1% | 63/138 | 80/151 | 0.77 (0.55-1.07) |
+| **PD-L1 TPS** | | | |
+| &lt;1% | 76/259 | 125/249 | 0.47 (0.36-0.63) |
+| 1-49% | 44/127 | 62/115 | 0.51 (0.34-0.75) |
+| ≥50% | 32/132 | 63/134 | 0.42 (0.28-0.65) |
+| **EGFR mutation** | | | |
+| No | 31/111 | 64/127 | 0.48 (0.31-0.74) |
+| Yes | 1/14 | 10/19 | 0.09 (0.01-0.74) |
+| Unknown | 107/272 | 131/254 | 0.64 (0.49-0.83) |
+| **ALK translocation** | | | |
+| No | 29/104 | 76/133 | 0.41 (0.26-0.62) |
+| Unknown | 106/281 | 128/258 | 0.63 (0.49-0.82) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">| Characteristic | Pembrolizumab Group (N = 397) | Placebo Group (N = 400) |
+| :--- | :--- | :--- |
+| **Age** | | |
+| Median (range) — yr | 63 (26–83) | 64 (35–81) |
+| ≥65 yr — no. (%) | 176 (44.3) | 186 (46.5) |
+| **Male sex — no. (%)** | 279 (70.3) | 284 (71.0) |
+| **Race or ethnic group — no. (%)†** | | |
+| American Indian or Alaska Native | 1 (0.3) | 0 |
+| Asian | 124 (31.2) | 125 (31.2) |
+| Black | 6 (1.5) | 10 (2.5) |
+| Multiple | 3 (0.8) | 10 (2.5) |
+| White | 250 (63.0) | 239 (59.8) |
+| Missing data | 13 (3.3) | 16 (4.0) |
+| **Geographic region — no. (%)** | | |
+| East Asia | 123 (31.0) | 121 (30.2) |
+| Other | 274 (69.0) | 279 (69.8) |
+| **ECOG performance-status score — no. (%)‡** | | |
+| 0 | 253 (63.7) | 246 (61.5) |
+| 1 | 144 (36.3) | 154 (38.5) |
+| **Smoking status — no. (%)** | | |
+| Current smoker | 96 (24.2) | 103 (25.8) |
+| Former smoker | 247 (62.2) | 250 (62.5) |
+| Never smoked | 54 (13.6) | 47 (11.8) |
+| **Pathological stage at baseline — no. (%)** | | |
+| II | 118 (29.7) | 121 (30.2) |
+| III | 279 (70.3) | 279 (69.8) |
+| IIIA | 217 (54.7) | 225 (56.2) |
+| IIIB | 62 (15.6) | 54 (13.5) |
+| **Tumor stage — no. (%)** | | |
+| T1 | 55 (13.9) | 61 (15.2) |
+| T2 | 106 (26.7) | 126 (31.5) |
+| T3 | 121 (30.5) | 109 (27.2) |
+| T4 | 115 (29.0) | 104 (26.0) |
+| **Node stage — no. (%)** | | |
+| N0 | 148 (37.3) | 142 (35.5) |
+| N1 | 81 (20.4) | 71 (17.8) |
+| N2 | 168 (42.3) | 187 (46.8) |
+| **Histologic features — no. (%)** | | |
+| Nonsquamous | 226 (56.9) | 227 (56.8) |
+| Squamous | 171 (43.1) | 173 (43.2) |
+| **PD-L1 tumor proportion score — no. (%)** | | |
+| ≥50% | 132 (33.2) | 134 (33.5) |
+| &lt;50% | 265 (66.8) | 266 (66.5) |
+| 1–49% | 127 (32.0) | 115 (28.8) |
+| &lt;1% | 138 (34.8) | 151 (37.8) |
+| **EGFR mutation status — no. (%)** | | |
+| No | 111 (28.0) | 127 (31.8) |
+| Yes | 14 (3.5) | 19 (4.8) |
+| Unknown | 272 (68.5) | 254 (63.5) |
+| **ALK translocation status — no. (%)** | | |
+| No | 104 (26.2) | 133 (33.2) |
+| Yes | 12 (3.0) | 9 (2.2) |
+| Unknown | 281 (70.8) | 258 (64.5) |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Demographic and Clinical Characteristics of the Patients at Baseline (Intention-to-Treat Population).*
+| Characteristic | Nivolumab plus Chemotherapy (N = 57) | Chemotherapy Alone (N = 29) |
+| :--- | ---: | ---: |
+| Median age (IQR) — yr | 65 (58–70) | 63 (57–66) |
+| Body‑mass index — no. (%)† | | |
+| &amp;nbsp;&amp;nbsp;≤25 | 15 (26) | 10 (34) |
+| &amp;nbsp;&amp;nbsp;&gt;25 | 42 (74) | 19 (66) |
+| Female sex — no. (%) | 21 (37) | 13 (45) |
+| History of tobacco use — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Never smoked | 5 (9) | 0 |
+| &amp;nbsp;&amp;nbsp;Former smoker | 22 (39) | 8 (28) |
+| &amp;nbsp;&amp;nbsp;Current smoker | 30 (53) | 21 (72) |
+| ECOG performance‑status score — no. (%)‡ | | |
+| &amp;nbsp;&amp;nbsp;0 | 31 (54) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;1 | 26 (46) | 13 (45) |
+| Histologic type — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;Adenocarcinoma | 25 (44) | 11 (38) |
+| &amp;nbsp;&amp;nbsp;Adenosquamous carcinoma | 1 (2) | 0 |
+| &amp;nbsp;&amp;nbsp;Squamous‑cell carcinoma | 21 (37) | 14 (48) |
+| &amp;nbsp;&amp;nbsp;Large‑cell carcinoma | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;Not otherwise specified or undifferentiated | 7 (12) | 2 (7) |
+| &amp;nbsp;&amp;nbsp;Other | 1 (2) | 1 (3) |
+| TNM classification — no. (%)§ | | |
+| &amp;nbsp;&amp;nbsp;T1N2M0 | 12 (21) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;T2N2M0 | 16 (28) | 7 (24) |
+| &amp;nbsp;&amp;nbsp;T3N1M0 | 2 (4) | 1 (3) |
+| &amp;nbsp;&amp;nbsp;T3N2M0 | 13 (23) | 5 (17) |
+| &amp;nbsp;&amp;nbsp;T4N0M0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;T4N1M0 | 8 (14) | 3 (10) |
+| Median tumor size (range) — mm | 50 (15–155) | 52 (15–166) |
+| Node stage — no. (%) | | |
+| &amp;nbsp;&amp;nbsp;N0 | 6 (11) | 9 (31) |
+| &amp;nbsp;&amp;nbsp;N1 | 10 (18) | 4 (14) |
+| &amp;nbsp;&amp;nbsp;N2 | 41 (72) | 16 (55) |
+| &amp;nbsp;&amp;nbsp;N2, multiple stations | 22 (39) | 11 (38) |</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -257,7 +3987,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,121 +4280,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.4609375" customWidth="1"/>
-    <col min="4" max="4" width="15.61328125" customWidth="1"/>
-    <col min="6" max="6" width="16.3046875" customWidth="1"/>
-    <col min="7" max="7" width="17.921875" customWidth="1"/>
+    <col min="1" max="1" width="24.4609375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.61328125" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.3046875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.921875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2023</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
+      <c r="G2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2023</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
+      <c r="G3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2023</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
+      <c r="G4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
